--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="986" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22BB9BF-4A4C-44CD-AD8E-303767EA4E98}"/>
+  <xr:revisionPtr revIDLastSave="1004" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C39365A8-E987-4FF2-BA00-A7F54868048B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="345" yWindow="345" windowWidth="13170" windowHeight="10920" activeTab="2" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="143">
   <si>
     <t>Experiment</t>
   </si>
@@ -483,6 +483,18 @@
   </si>
   <si>
     <t>maybe cut leaf number at bolting because it includes all the under leaves information. Could be supplemental only?</t>
+  </si>
+  <si>
+    <t>days emergence to bolting was cut for 2022 because plants had the same treatment for most of this time.</t>
+  </si>
+  <si>
+    <t>if below 0.10, counted here</t>
+  </si>
+  <si>
+    <t>sla (IT=53, Sw=57)</t>
+  </si>
+  <si>
+    <t>Days Emergence to Flowering</t>
   </si>
 </sst>
 </file>
@@ -947,6 +959,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1010,7 +1025,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1373,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5A7F3D-2808-4753-A174-BBEAF62E0D16}">
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -1387,24 +1401,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="39">
+      <c r="C1" s="40">
         <v>2021</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="39">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="40">
         <v>2022</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1455,7 +1469,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1503,7 +1517,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1547,7 +1561,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
@@ -1591,16 +1605,16 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1623,7 +1637,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1669,7 +1683,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1713,7 +1727,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -1757,16 +1771,16 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1789,7 +1803,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1814,18 +1828,18 @@
         <v>3.2053459705297903E-5</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="38" t="s">
+      <c r="J11" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1848,16 +1862,16 @@
         <v>2.0059373392474201E-2</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1880,4197 +1894,4319 @@
         <v>0.213540969734523</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>11</v>
+      <c r="A15" s="36" t="s">
+        <v>142</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="1">
-        <v>4.1857799097373602</v>
+        <v>47.107649150023398</v>
       </c>
       <c r="D15" s="1">
-        <v>4.1857799097373602</v>
+        <v>47.107649150023398</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>58.775295215237101</v>
+        <v>57.289916371421597</v>
       </c>
       <c r="G15" s="1">
-        <v>309.45174334807001</v>
-      </c>
-      <c r="H15" s="4">
-        <v>4.2882526567544902E-25</v>
+        <v>3.32662663622179</v>
+      </c>
+      <c r="H15" s="3">
+        <v>7.3383790508167401E-2</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <v>107.186966242618</v>
-      </c>
-      <c r="N15" s="1">
-        <v>18.487688610543501</v>
-      </c>
-      <c r="O15" s="4">
-        <v>3.7826149790259799E-5</v>
-      </c>
+      <c r="J15" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="37"/>
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>3.6571648177047403E-2</v>
+        <v>1124.2901171196299</v>
       </c>
       <c r="D16" s="1">
-        <v>3.6571648177047403E-2</v>
+        <v>1124.2901171196299</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>14.508066856775899</v>
+        <v>13.2534687161866</v>
       </c>
       <c r="G16" s="1">
-        <v>2.7037160408679202</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0.121602132726155</v>
+        <v>79.394610385672607</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5.8229847066576205E-7</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <v>12.379734112886799</v>
-      </c>
-      <c r="N16" s="1">
-        <v>11.3779349310574</v>
-      </c>
-      <c r="O16" s="2">
-        <v>5.3176769657787898E-3</v>
-      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="1">
-        <v>9.5456152618234799E-2</v>
+        <v>0.222326126836178</v>
       </c>
       <c r="D17" s="1">
-        <v>9.5456152618234799E-2</v>
+        <v>0.222326126836178</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>58.775295214428802</v>
+        <v>57.289916368165599</v>
       </c>
       <c r="G17" s="1">
-        <v>7.0570057379977396</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1.01489929112641E-2</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="K17" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1">
-        <v>106.783841827976</v>
-      </c>
-      <c r="N17" s="1">
-        <v>3.5502596702509801</v>
-      </c>
-      <c r="O17" s="2">
-        <v>6.2255752292747699E-2</v>
-      </c>
+        <v>1.5700125750403499E-2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.90072460165650603</v>
+      </c>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1">
-        <v>5.2456643231190104E-3</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2.6228321615595E-3</v>
-      </c>
-      <c r="L18" s="1">
-        <v>2</v>
-      </c>
-      <c r="M18" s="1">
-        <v>106.82092564483</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0.202058479881251</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0.81735870029617597</v>
-      </c>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>37</v>
+      <c r="A19" s="36" t="s">
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1">
-        <v>3.75533617845436</v>
+        <v>4.1857799097373602</v>
       </c>
       <c r="D19" s="1">
-        <v>3.75533617845436</v>
+        <v>4.1857799097373602</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>58.450172749992298</v>
+        <v>58.775295215237101</v>
       </c>
       <c r="G19" s="1">
-        <v>275.61367619126997</v>
+        <v>309.45174334807001</v>
       </c>
       <c r="H19" s="4">
-        <v>8.5561055144156804E-24</v>
+        <v>4.2882526567544902E-25</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1">
-        <v>0.12745796635020001</v>
+        <v>0.23998054577629399</v>
       </c>
       <c r="K19" s="1">
-        <v>0.12745796635020001</v>
+        <v>0.23998054577629399</v>
       </c>
       <c r="L19" s="1">
         <v>1</v>
       </c>
       <c r="M19" s="1">
-        <v>106.169152592015</v>
+        <v>107.186966242618</v>
       </c>
       <c r="N19" s="1">
-        <v>9.7924313998268993</v>
-      </c>
-      <c r="O19" s="2">
-        <v>2.2627938793836001E-3</v>
+        <v>18.487688610543501</v>
+      </c>
+      <c r="O19" s="4">
+        <v>3.7826149790259799E-5</v>
       </c>
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="1">
-        <v>3.8005186893600197E-2</v>
+        <v>3.6571648177047403E-2</v>
       </c>
       <c r="D20" s="1">
-        <v>3.8005186893600197E-2</v>
+        <v>3.6571648177047403E-2</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>14.0776142021772</v>
+        <v>14.508066856775899</v>
       </c>
       <c r="G20" s="1">
-        <v>2.7892973561671002</v>
+        <v>2.7037160408679202</v>
       </c>
       <c r="H20" s="1">
-        <v>0.116971279359414</v>
+        <v>0.121602132726155</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
-        <v>0.116553339771977</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="K20" s="1">
-        <v>0.116553339771977</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="L20" s="1">
         <v>1</v>
       </c>
       <c r="M20" s="1">
-        <v>12.391275226041101</v>
+        <v>12.379734112886799</v>
       </c>
       <c r="N20" s="1">
-        <v>8.9546429840398503</v>
+        <v>11.3779349310574</v>
       </c>
       <c r="O20" s="2">
-        <v>1.08776102041225E-2</v>
+        <v>5.3176769657787898E-3</v>
       </c>
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>7.7542068403545703E-2</v>
+        <v>9.5456152618234799E-2</v>
       </c>
       <c r="D21" s="1">
-        <v>7.7542068403545703E-2</v>
+        <v>9.5456152618234799E-2</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>58.450172750997197</v>
+        <v>58.775295214428802</v>
       </c>
       <c r="G21" s="1">
-        <v>5.6910096770543701</v>
+        <v>7.0570057379977396</v>
       </c>
       <c r="H21" s="2">
-        <v>2.0312618497821299E-2</v>
+        <v>1.01489929112641E-2</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>7.3363893765149693E-2</v>
+        <v>4.6084357610204602E-2</v>
       </c>
       <c r="K21" s="1">
-        <v>7.3363893765149693E-2</v>
+        <v>4.6084357610204602E-2</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
       </c>
       <c r="M21" s="1">
-        <v>105.814592900958</v>
+        <v>106.783841827976</v>
       </c>
       <c r="N21" s="1">
-        <v>5.6364534716137902</v>
+        <v>3.5502596702509801</v>
       </c>
       <c r="O21" s="2">
-        <v>1.9393437026140801E-2</v>
+        <v>6.2255752292747699E-2</v>
       </c>
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>7.5239018444935397E-3</v>
+        <v>5.2456643231190104E-3</v>
       </c>
       <c r="K22" s="1">
-        <v>3.7619509222467699E-3</v>
+        <v>2.6228321615595E-3</v>
       </c>
       <c r="L22" s="1">
         <v>2</v>
       </c>
       <c r="M22" s="1">
-        <v>105.84740366368401</v>
+        <v>106.82092564483</v>
       </c>
       <c r="N22" s="1">
-        <v>0.28902584428814998</v>
+        <v>0.202058479881251</v>
       </c>
       <c r="O22" s="1">
-        <v>0.74958204967156605</v>
+        <v>0.81735870029617597</v>
       </c>
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="A23" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C23">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="D23">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>57.941257724360497</v>
-      </c>
-      <c r="G23">
-        <v>114.44647303148901</v>
-      </c>
-      <c r="H23" s="7">
-        <v>2.4310901681812699E-15</v>
+      <c r="C23" s="1">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>58.450172749992298</v>
+      </c>
+      <c r="G23" s="1">
+        <v>275.61367619126997</v>
+      </c>
+      <c r="H23" s="4">
+        <v>8.5561055144156804E-24</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="5">
-        <v>3.27228460982109E-6</v>
-      </c>
-      <c r="K23" s="5">
-        <v>3.27228460982109E-6</v>
+      <c r="J23" s="1">
+        <v>0.12745796635020001</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.12745796635020001</v>
       </c>
       <c r="L23" s="1">
         <v>1</v>
       </c>
       <c r="M23" s="1">
-        <v>108.162570470471</v>
+        <v>106.169152592015</v>
       </c>
       <c r="N23" s="1">
-        <v>0.81526923567301701</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0.36857341395755699</v>
+        <v>9.7924313998268993</v>
+      </c>
+      <c r="O23" s="2">
+        <v>2.2627938793836001E-3</v>
       </c>
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="D24">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>14.016499111022799</v>
-      </c>
-      <c r="G24">
-        <v>4.0830664272103698</v>
-      </c>
-      <c r="H24" s="9">
-        <v>6.28474981350714E-2</v>
+      <c r="C24" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>14.0776142021772</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2.7892973561671002</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.116971279359414</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="K24" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="L24" s="1">
         <v>1</v>
       </c>
       <c r="M24" s="1">
-        <v>13.1287610221782</v>
+        <v>12.391275226041101</v>
       </c>
       <c r="N24" s="1">
-        <v>28.038855933179999</v>
+        <v>8.9546429840398503</v>
       </c>
       <c r="O24" s="2">
-        <v>1.4035037213878999E-4</v>
+        <v>1.08776102041225E-2</v>
       </c>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="D25">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>57.941257724235903</v>
-      </c>
-      <c r="G25">
-        <v>0.82228421440567401</v>
-      </c>
-      <c r="H25">
-        <v>0.36826900260683199</v>
+      <c r="C25" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>58.450172750997197</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5.6910096770543701</v>
+      </c>
+      <c r="H25" s="2">
+        <v>2.0312618497821299E-2</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="5">
-        <v>7.3359735284969697E-6</v>
-      </c>
-      <c r="K25" s="5">
-        <v>7.3359735284969697E-6</v>
+      <c r="J25" s="1">
+        <v>7.3363893765149693E-2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>7.3363893765149693E-2</v>
       </c>
       <c r="L25" s="1">
         <v>1</v>
       </c>
       <c r="M25" s="1">
-        <v>107.80326229592799</v>
+        <v>105.814592900958</v>
       </c>
       <c r="N25" s="1">
-        <v>1.82771190303713</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0.179227673464389</v>
+        <v>5.6364534716137902</v>
+      </c>
+      <c r="O25" s="2">
+        <v>1.9393437026140801E-2</v>
       </c>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="5">
-        <v>7.2143853443936604E-6</v>
-      </c>
-      <c r="K26" s="5">
-        <v>3.6071926721968302E-6</v>
+      <c r="J26" s="1">
+        <v>7.5239018444935397E-3</v>
+      </c>
+      <c r="K26" s="1">
+        <v>3.7619509222467699E-3</v>
       </c>
       <c r="L26" s="1">
         <v>2</v>
       </c>
       <c r="M26" s="1">
-        <v>107.842517864377</v>
+        <v>105.84740366368401</v>
       </c>
       <c r="N26" s="1">
-        <v>0.89870948387585703</v>
+        <v>0.28902584428814998</v>
       </c>
       <c r="O26" s="1">
-        <v>0.41012132536637402</v>
+        <v>0.74958204967156605</v>
       </c>
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="1">
-        <v>3.2828058473639601</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3.2828058473639601</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>57.1027846481349</v>
-      </c>
-      <c r="G27" s="1">
-        <v>315.57785828471202</v>
-      </c>
-      <c r="H27" s="4">
-        <v>6.2556135251351003E-25</v>
+      <c r="C27">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="D27">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>57.941257724360497</v>
+      </c>
+      <c r="G27">
+        <v>114.44647303148901</v>
+      </c>
+      <c r="H27" s="7">
+        <v>2.4310901681812699E-15</v>
       </c>
       <c r="I27" s="1"/>
-      <c r="J27" s="1">
-        <v>4.9581564592565801</v>
-      </c>
-      <c r="K27" s="1">
-        <v>4.9581564592565801</v>
+      <c r="J27" s="5">
+        <v>3.27228460982109E-6</v>
+      </c>
+      <c r="K27" s="5">
+        <v>3.27228460982109E-6</v>
       </c>
       <c r="L27" s="1">
         <v>1</v>
       </c>
       <c r="M27" s="1">
-        <v>107.087389174327</v>
+        <v>108.162570470471</v>
       </c>
       <c r="N27" s="1">
-        <v>15.8163561438312</v>
-      </c>
-      <c r="O27" s="2">
-        <v>1.2711861864362099E-4</v>
+        <v>0.81526923567301701</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0.36857341395755699</v>
       </c>
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="1">
-        <v>6.9098899300225596E-4</v>
-      </c>
-      <c r="D28" s="1">
-        <v>6.9098899300225596E-4</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>13.6400199665374</v>
-      </c>
-      <c r="G28" s="1">
-        <v>6.6425136498724599E-2</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0.80046236006191795</v>
+      <c r="C28">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="D28">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>14.016499111022799</v>
+      </c>
+      <c r="G28">
+        <v>4.0830664272103698</v>
+      </c>
+      <c r="H28" s="9">
+        <v>6.28474981350714E-2</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="K28" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="L28" s="1">
         <v>1</v>
       </c>
       <c r="M28" s="1">
-        <v>11.8724826464864</v>
+        <v>13.1287610221782</v>
       </c>
       <c r="N28" s="1">
-        <v>6.1829928610262298E-2</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0.80787586394532096</v>
+        <v>28.038855933179999</v>
+      </c>
+      <c r="O28" s="2">
+        <v>1.4035037213878999E-4</v>
       </c>
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="1">
-        <v>0.13315844295854501</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.13315844295854501</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>57.102784645779103</v>
-      </c>
-      <c r="G29" s="1">
-        <v>12.800591382864701</v>
-      </c>
-      <c r="H29" s="2">
-        <v>7.1467481949516205E-4</v>
+      <c r="C29">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="D29">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>57.941257724235903</v>
+      </c>
+      <c r="G29">
+        <v>0.82228421440567401</v>
+      </c>
+      <c r="H29">
+        <v>0.36826900260683199</v>
       </c>
       <c r="I29" s="1"/>
-      <c r="J29" s="1">
-        <v>1.5642063102591399</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1.5642063102591399</v>
+      <c r="J29" s="5">
+        <v>7.3359735284969697E-6</v>
+      </c>
+      <c r="K29" s="5">
+        <v>7.3359735284969697E-6</v>
       </c>
       <c r="L29" s="1">
         <v>1</v>
       </c>
       <c r="M29" s="1">
-        <v>106.739383464101</v>
+        <v>107.80326229592799</v>
       </c>
       <c r="N29" s="1">
-        <v>4.9897667184944403</v>
-      </c>
-      <c r="O29" s="2">
-        <v>2.7582949079364601E-2</v>
+        <v>1.82771190303713</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0.179227673464389</v>
       </c>
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1">
-        <v>0.34951867520347901</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0.17475933760173901</v>
+      <c r="J30" s="5">
+        <v>7.2143853443936604E-6</v>
+      </c>
+      <c r="K30" s="5">
+        <v>3.6071926721968302E-6</v>
       </c>
       <c r="L30" s="1">
         <v>2</v>
       </c>
       <c r="M30" s="1">
-        <v>106.790362785864</v>
+        <v>107.842517864377</v>
       </c>
       <c r="N30" s="1">
-        <v>0.55747654308262395</v>
+        <v>0.89870948387585703</v>
       </c>
       <c r="O30" s="1">
-        <v>0.57430971602825098</v>
+        <v>0.41012132536637402</v>
       </c>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>14</v>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="1">
-        <v>1.36628969679729</v>
+        <v>3.2828058473639601</v>
       </c>
       <c r="D31" s="1">
-        <v>1.36628969679729</v>
+        <v>3.2828058473639601</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>54.103865456753802</v>
+        <v>57.1027846481349</v>
       </c>
       <c r="G31" s="1">
-        <v>323.52191769489502</v>
+        <v>315.57785828471202</v>
       </c>
       <c r="H31" s="4">
-        <v>1.7309716058161699E-24</v>
+        <v>6.2556135251351003E-25</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1">
-        <v>11.8595223504753</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="K31" s="1">
-        <v>11.8595223504753</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="L31" s="1">
         <v>1</v>
       </c>
       <c r="M31" s="1">
-        <v>107.201241552043</v>
+        <v>107.087389174327</v>
       </c>
       <c r="N31" s="1">
-        <v>9.5506130348868208</v>
+        <v>15.8163561438312</v>
       </c>
       <c r="O31" s="2">
-        <v>2.54688520800141E-3</v>
+        <v>1.2711861864362099E-4</v>
       </c>
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>3.0303710819429698E-3</v>
+        <v>6.9098899300225596E-4</v>
       </c>
       <c r="D32" s="1">
-        <v>3.0303710819429698E-3</v>
+        <v>6.9098899300225596E-4</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>10.659214250737501</v>
+        <v>13.6400199665374</v>
       </c>
       <c r="G32" s="1">
-        <v>0.71755753267807798</v>
+        <v>6.6425136498724599E-2</v>
       </c>
       <c r="H32" s="1">
-        <v>0.41556047753360997</v>
+        <v>0.80046236006191795</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1">
-        <v>1.06298370497324</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="K32" s="1">
-        <v>1.06298370497324</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="L32" s="1">
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <v>12.0506128910075</v>
+        <v>11.8724826464864</v>
       </c>
       <c r="N32" s="1">
-        <v>0.85603329784886595</v>
+        <v>6.1829928610262298E-2</v>
       </c>
       <c r="O32" s="1">
-        <v>0.37300851361203902</v>
+        <v>0.80787586394532096</v>
       </c>
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="1">
-        <v>5.2728177270368402E-2</v>
+        <v>0.13315844295854501</v>
       </c>
       <c r="D33" s="1">
-        <v>5.2728177270368402E-2</v>
+        <v>0.13315844295854501</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>54.1038654583488</v>
+        <v>57.102784645779103</v>
       </c>
       <c r="G33" s="1">
-        <v>12.4854348730384</v>
+        <v>12.800591382864701</v>
       </c>
       <c r="H33" s="2">
-        <v>8.48284866637566E-4</v>
+        <v>7.1467481949516205E-4</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1">
-        <v>5.8391786603145501</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="K33" s="1">
-        <v>5.8391786603145501</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
       </c>
       <c r="M33" s="1">
-        <v>106.84246065981201</v>
+        <v>106.739383464101</v>
       </c>
       <c r="N33" s="1">
-        <v>4.7023593512598696</v>
+        <v>4.9897667184944403</v>
       </c>
       <c r="O33" s="2">
-        <v>3.23394599501459E-2</v>
+        <v>2.7582949079364601E-2</v>
       </c>
       <c r="P33" s="1"/>
     </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="38"/>
       <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
-        <v>2.5021778012642701</v>
+        <v>0.34951867520347901</v>
       </c>
       <c r="K34" s="1">
-        <v>1.25108890063213</v>
+        <v>0.17475933760173901</v>
       </c>
       <c r="L34" s="1">
         <v>2</v>
       </c>
       <c r="M34" s="1">
-        <v>106.889741706824</v>
+        <v>106.790362785864</v>
       </c>
       <c r="N34" s="1">
-        <v>1.0075166274888401</v>
+        <v>0.55747654308262395</v>
       </c>
       <c r="O34" s="1">
-        <v>0.36856517791115101</v>
+        <v>0.57430971602825098</v>
       </c>
       <c r="P34" s="1"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
-        <v>15</v>
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1">
-        <v>0.37589798145214498</v>
+        <v>1.36628969679729</v>
       </c>
       <c r="D35" s="1">
-        <v>0.37589798145214498</v>
+        <v>1.36628969679729</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>62.693513739662698</v>
+        <v>54.103865456753802</v>
       </c>
       <c r="G35" s="1">
-        <v>83.6813648995563</v>
+        <v>323.52191769489502</v>
       </c>
       <c r="H35" s="4">
-        <v>3.75722082106105E-13</v>
+        <v>1.7309716058161699E-24</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1">
-        <v>0.25198523874622702</v>
+        <v>11.8595223504753</v>
       </c>
       <c r="K35" s="1">
-        <v>0.25198523874622702</v>
+        <v>11.8595223504753</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
       </c>
       <c r="M35" s="1">
-        <v>110.096333617363</v>
+        <v>107.201241552043</v>
       </c>
       <c r="N35" s="1">
-        <v>42.058288147666097</v>
-      </c>
-      <c r="O35" s="4">
-        <v>2.5984972877347698E-9</v>
+        <v>9.5506130348868208</v>
+      </c>
+      <c r="O35" s="2">
+        <v>2.54688520800141E-3</v>
       </c>
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="1">
-        <v>0.18866486223902701</v>
+        <v>3.0303710819429698E-3</v>
       </c>
       <c r="D36" s="1">
-        <v>0.18866486223902701</v>
+        <v>3.0303710819429698E-3</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>12.9224641855406</v>
+        <v>10.659214250737501</v>
       </c>
       <c r="G36" s="1">
-        <v>42.000047778278599</v>
-      </c>
-      <c r="H36" s="4">
-        <v>2.1245490728025998E-5</v>
+        <v>0.71755753267807798</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.41556047753360997</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1">
-        <v>0.73996860487093596</v>
+        <v>1.06298370497324</v>
       </c>
       <c r="K36" s="1">
-        <v>0.73996860487093596</v>
+        <v>1.06298370497324</v>
       </c>
       <c r="L36" s="1">
         <v>1</v>
       </c>
       <c r="M36" s="1">
-        <v>14.054733420670001</v>
+        <v>12.0506128910075</v>
       </c>
       <c r="N36" s="1">
-        <v>123.506491724426</v>
-      </c>
-      <c r="O36" s="4">
-        <v>2.3925201381821199E-8</v>
+        <v>0.85603329784886595</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0.37300851361203902</v>
       </c>
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="1">
-        <v>8.5519255858093002E-2</v>
+        <v>5.2728177270368402E-2</v>
       </c>
       <c r="D37" s="1">
-        <v>8.5519255858093002E-2</v>
+        <v>5.2728177270368402E-2</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1">
-        <v>62.6935137438185</v>
+        <v>54.1038654583488</v>
       </c>
       <c r="G37" s="1">
-        <v>19.0380592834087</v>
-      </c>
-      <c r="H37" s="4">
-        <v>4.8750646383530901E-5</v>
+        <v>12.4854348730384</v>
+      </c>
+      <c r="H37" s="2">
+        <v>8.48284866637566E-4</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1">
-        <v>1.5798173670143599E-2</v>
+        <v>5.8391786603145501</v>
       </c>
       <c r="K37" s="1">
-        <v>1.5798173670143599E-2</v>
+        <v>5.8391786603145501</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
       </c>
       <c r="M37" s="1">
-        <v>109.918842223097</v>
+        <v>106.84246065981201</v>
       </c>
       <c r="N37" s="1">
-        <v>2.6368375533891002</v>
-      </c>
-      <c r="O37" s="3">
-        <v>0.107275586121823</v>
+        <v>4.7023593512598696</v>
+      </c>
+      <c r="O37" s="2">
+        <v>3.23394599501459E-2</v>
       </c>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
-        <v>4.9184876384352101E-2</v>
+        <v>2.5021778012642701</v>
       </c>
       <c r="K38" s="1">
-        <v>2.4592438192175999E-2</v>
+        <v>1.25108890063213</v>
       </c>
       <c r="L38" s="1">
         <v>2</v>
       </c>
       <c r="M38" s="1">
-        <v>110.02134132950501</v>
+        <v>106.889741706824</v>
       </c>
       <c r="N38" s="1">
-        <v>4.1046684198111398</v>
-      </c>
-      <c r="O38" s="2">
-        <v>1.9087014953066299E-2</v>
+        <v>1.0075166274888401</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0.36856517791115101</v>
       </c>
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
-        <v>16</v>
+      <c r="A39" s="36" t="s">
+        <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="1">
-        <v>0.48460569188395097</v>
+        <v>0.37589798145214498</v>
       </c>
       <c r="D39" s="1">
-        <v>0.48460569188395097</v>
+        <v>0.37589798145214498</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>66.433120310954493</v>
+        <v>62.693513739662698</v>
       </c>
       <c r="G39" s="1">
-        <v>275.25199949565803</v>
+        <v>83.6813648995563</v>
       </c>
       <c r="H39" s="4">
-        <v>2.5677289076389099E-25</v>
+        <v>3.75722082106105E-13</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1">
-        <v>0.251919036972449</v>
+        <v>0.25198523874622702</v>
       </c>
       <c r="K39" s="1">
-        <v>0.251919036972449</v>
+        <v>0.25198523874622702</v>
       </c>
       <c r="L39" s="1">
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <v>120.000000000931</v>
+        <v>110.096333617363</v>
       </c>
       <c r="N39" s="1">
-        <v>45.935699808275302</v>
+        <v>42.058288147666097</v>
       </c>
       <c r="O39" s="4">
-        <v>4.8525436598560696E-10</v>
+        <v>2.5984972877347698E-9</v>
       </c>
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="1">
-        <v>1.0223913414274E-2</v>
+        <v>0.18866486223902701</v>
       </c>
       <c r="D40" s="1">
-        <v>1.0223913414274E-2</v>
+        <v>0.18866486223902701</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>16.820702919437998</v>
+        <v>12.9224641855406</v>
       </c>
       <c r="G40" s="1">
-        <v>5.8070977231181704</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2.77082234476239E-2</v>
+        <v>42.000047778278599</v>
+      </c>
+      <c r="H40" s="4">
+        <v>2.1245490728025998E-5</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1">
-        <v>0.24754938321325901</v>
+        <v>0.73996860487093596</v>
       </c>
       <c r="K40" s="1">
-        <v>0.24754938321325901</v>
+        <v>0.73996860487093596</v>
       </c>
       <c r="L40" s="1">
         <v>1</v>
       </c>
       <c r="M40" s="1">
-        <v>120.000000000876</v>
+        <v>14.054733420670001</v>
       </c>
       <c r="N40" s="1">
-        <v>45.138923567144403</v>
+        <v>123.506491724426</v>
       </c>
       <c r="O40" s="4">
-        <v>6.5162497916437297E-10</v>
+        <v>2.3925201381821199E-8</v>
       </c>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="37"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>3.4754513300900097E-2</v>
+        <v>8.5519255858093002E-2</v>
       </c>
       <c r="D41" s="1">
-        <v>3.4754513300900097E-2</v>
+        <v>8.5519255858093002E-2</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
       <c r="F41" s="1">
-        <v>66.433120314017799</v>
+        <v>62.6935137438185</v>
       </c>
       <c r="G41" s="1">
-        <v>19.740274284401199</v>
+        <v>19.0380592834087</v>
       </c>
       <c r="H41" s="4">
-        <v>3.4416590783058898E-5</v>
+        <v>4.8750646383530901E-5</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1">
-        <v>1.81876043094546E-2</v>
+        <v>1.5798173670143599E-2</v>
       </c>
       <c r="K41" s="1">
-        <v>1.81876043094546E-2</v>
+        <v>1.5798173670143599E-2</v>
       </c>
       <c r="L41" s="1">
         <v>1</v>
       </c>
       <c r="M41" s="1">
-        <v>120.000000000876</v>
+        <v>109.918842223097</v>
       </c>
       <c r="N41" s="1">
-        <v>3.3163842710393201</v>
+        <v>2.6368375533891002</v>
       </c>
       <c r="O41" s="3">
-        <v>7.1083850624745398E-2</v>
+        <v>0.107275586121823</v>
       </c>
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
-        <v>3.6858467316493698E-2</v>
+        <v>4.9184876384352101E-2</v>
       </c>
       <c r="K42" s="1">
-        <v>1.8429233658246901E-2</v>
+        <v>2.4592438192175999E-2</v>
       </c>
       <c r="L42" s="1">
         <v>2</v>
       </c>
       <c r="M42" s="1">
-        <v>120.00000000096099</v>
+        <v>110.02134132950501</v>
       </c>
       <c r="N42" s="1">
-        <v>3.3604437171390802</v>
+        <v>4.1046684198111398</v>
       </c>
       <c r="O42" s="2">
-        <v>3.8017401028842102E-2</v>
+        <v>1.9087014953066299E-2</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="35" t="s">
-        <v>17</v>
+      <c r="A43" s="36" t="s">
+        <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="1">
-        <v>6.7693630421350404E-2</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="D43" s="1">
-        <v>6.7693630421350404E-2</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
       </c>
       <c r="F43" s="1">
-        <v>67.474634134516194</v>
+        <v>66.433120310954493</v>
       </c>
       <c r="G43" s="1">
-        <v>56.9929468926208</v>
+        <v>275.25199949565803</v>
       </c>
       <c r="H43" s="4">
-        <v>1.50306538610143E-10</v>
+        <v>2.5677289076389099E-25</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1">
-        <v>9.6428494366839604E-2</v>
+        <v>0.251919036972449</v>
       </c>
       <c r="K43" s="1">
-        <v>9.6428494366839604E-2</v>
+        <v>0.251919036972449</v>
       </c>
       <c r="L43" s="1">
         <v>1</v>
       </c>
       <c r="M43" s="1">
-        <v>108.528246395583</v>
+        <v>120.000000000931</v>
       </c>
       <c r="N43" s="1">
-        <v>81.178081408719805</v>
+        <v>45.935699808275302</v>
       </c>
       <c r="O43" s="4">
-        <v>7.9655542624253594E-15</v>
+        <v>4.8525436598560696E-10</v>
       </c>
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="10" t="s">
+      <c r="A44" s="37"/>
+      <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="1">
-        <v>2.0802366421830801E-4</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="D44" s="1">
-        <v>2.0802366421830801E-4</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
       <c r="F44" s="1">
-        <v>15.419684823909099</v>
+        <v>16.820702919437998</v>
       </c>
       <c r="G44" s="1">
-        <v>0.17514028385546801</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0.68135395106469998</v>
+        <v>5.8070977231181704</v>
+      </c>
+      <c r="H44" s="2">
+        <v>2.77082234476239E-2</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1">
-        <v>1.64063711986129E-2</v>
+        <v>0.24754938321325901</v>
       </c>
       <c r="K44" s="1">
-        <v>1.64063711986129E-2</v>
+        <v>0.24754938321325901</v>
       </c>
       <c r="L44" s="1">
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <v>13.3017704428868</v>
+        <v>120.000000000876</v>
       </c>
       <c r="N44" s="1">
-        <v>13.811661641381701</v>
-      </c>
-      <c r="O44" s="2">
-        <v>2.49480079562349E-3</v>
+        <v>45.138923567144403</v>
+      </c>
+      <c r="O44" s="4">
+        <v>6.5162497916437297E-10</v>
       </c>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="37"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="1">
-        <v>3.8321573511002202E-3</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="D45" s="1">
-        <v>3.8321573511002202E-3</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
       </c>
       <c r="F45" s="1">
-        <v>67.4746341327685</v>
+        <v>66.433120314017799</v>
       </c>
       <c r="G45" s="1">
-        <v>3.2263883475591602</v>
-      </c>
-      <c r="H45" s="3">
-        <v>7.6936893211417001E-2</v>
+        <v>19.740274284401199</v>
+      </c>
+      <c r="H45" s="4">
+        <v>3.4416590783058898E-5</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1">
-        <v>9.3368633870387803E-3</v>
+        <v>1.81876043094546E-2</v>
       </c>
       <c r="K45" s="1">
-        <v>9.3368633870387803E-3</v>
+        <v>1.81876043094546E-2</v>
       </c>
       <c r="L45" s="1">
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <v>108.444542227017</v>
+        <v>120.000000000876</v>
       </c>
       <c r="N45" s="1">
-        <v>7.8602145674046398</v>
-      </c>
-      <c r="O45" s="2">
-        <v>5.9886663878832899E-3</v>
+        <v>3.3163842710393201</v>
+      </c>
+      <c r="O45" s="3">
+        <v>7.1083850624745398E-2</v>
       </c>
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="37"/>
+      <c r="A46" s="38"/>
       <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
-        <v>3.4846897009296399E-3</v>
+        <v>3.6858467316493698E-2</v>
       </c>
       <c r="K46" s="1">
-        <v>1.7423448504648199E-3</v>
+        <v>1.8429233658246901E-2</v>
       </c>
       <c r="L46" s="1">
         <v>2</v>
       </c>
       <c r="M46" s="1">
-        <v>108.56084481953199</v>
+        <v>120.00000000096099</v>
       </c>
       <c r="N46" s="1">
-        <v>1.4667885570734001</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0.23519968422781001</v>
+        <v>3.3604437171390802</v>
+      </c>
+      <c r="O46" s="2">
+        <v>3.8017401028842102E-2</v>
       </c>
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
-        <v>27</v>
+      <c r="A47" s="36" t="s">
+        <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
+      <c r="C47" s="1">
+        <v>6.7693630421350404E-2</v>
+      </c>
+      <c r="D47" s="1">
+        <v>6.7693630421350404E-2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>67.474634134516194</v>
+      </c>
+      <c r="G47" s="1">
+        <v>56.9929468926208</v>
+      </c>
+      <c r="H47" s="4">
+        <v>1.50306538610143E-10</v>
+      </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1">
-        <v>2.20343269025562E-2</v>
+        <v>9.6428494366839604E-2</v>
       </c>
       <c r="K47" s="1">
-        <v>2.20343269025562E-2</v>
+        <v>9.6428494366839604E-2</v>
       </c>
       <c r="L47" s="1">
         <v>1</v>
       </c>
       <c r="M47" s="1">
-        <v>108.759068663758</v>
+        <v>108.528246395583</v>
       </c>
       <c r="N47" s="1">
-        <v>6.5138864797470797</v>
-      </c>
-      <c r="O47" s="2">
-        <v>1.20915323151938E-2</v>
+        <v>81.178081408719805</v>
+      </c>
+      <c r="O47" s="4">
+        <v>7.9655542624253594E-15</v>
       </c>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="37"/>
+      <c r="B48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
+      <c r="C48" s="1">
+        <v>2.0802366421830801E-4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2.0802366421830801E-4</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>15.419684823909099</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.17514028385546801</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0.68135395106469998</v>
+      </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1">
-        <v>2.98483856205864E-2</v>
+        <v>1.64063711986129E-2</v>
       </c>
       <c r="K48" s="1">
-        <v>2.98483856205864E-2</v>
+        <v>1.64063711986129E-2</v>
       </c>
       <c r="L48" s="1">
         <v>1</v>
       </c>
       <c r="M48" s="1">
-        <v>13.393007197198701</v>
+        <v>13.3017704428868</v>
       </c>
       <c r="N48" s="1">
-        <v>8.8239135416321304</v>
+        <v>13.811661641381701</v>
       </c>
       <c r="O48" s="2">
-        <v>1.05420955332634E-2</v>
+        <v>2.49480079562349E-3</v>
       </c>
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
+      <c r="C49" s="1">
+        <v>3.8321573511002202E-3</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3.8321573511002202E-3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>67.4746341327685</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3.2263883475591602</v>
+      </c>
+      <c r="H49" s="3">
+        <v>7.6936893211417001E-2</v>
+      </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1">
-        <v>1.15818782663304E-3</v>
+        <v>9.3368633870387803E-3</v>
       </c>
       <c r="K49" s="1">
-        <v>1.15818782663304E-3</v>
+        <v>9.3368633870387803E-3</v>
       </c>
       <c r="L49" s="1">
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <v>108.463193154259</v>
+        <v>108.444542227017</v>
       </c>
       <c r="N49" s="1">
-        <v>0.342388676462696</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0.55966903975183102</v>
+        <v>7.8602145674046398</v>
+      </c>
+      <c r="O49" s="2">
+        <v>5.9886663878832899E-3</v>
       </c>
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
-        <v>2.0797141885883202E-3</v>
+        <v>3.4846897009296399E-3</v>
       </c>
       <c r="K50" s="1">
-        <v>1.0398570942941601E-3</v>
+        <v>1.7423448504648199E-3</v>
       </c>
       <c r="L50" s="1">
         <v>2</v>
       </c>
       <c r="M50" s="1">
-        <v>108.513064659973</v>
+        <v>108.56084481953199</v>
       </c>
       <c r="N50" s="1">
-        <v>0.30740721499443802</v>
+        <v>1.4667885570734001</v>
       </c>
       <c r="O50" s="1">
-        <v>0.73598934665486404</v>
+        <v>0.23519968422781001</v>
       </c>
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="35" t="s">
-        <v>41</v>
+      <c r="A51" s="36" t="s">
+        <v>27</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1">
-        <v>98.415000000000006</v>
-      </c>
-      <c r="D51" s="1">
-        <v>98.415000000000006</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="1">
-        <v>76.629206352881397</v>
-      </c>
-      <c r="G51" s="1">
-        <v>22.0523657327007</v>
-      </c>
-      <c r="H51" s="4">
-        <v>1.14210478822229E-5</v>
-      </c>
+      <c r="C51" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
-        <v>12.0886854422992</v>
+        <v>2.20343269025562E-2</v>
       </c>
       <c r="K51" s="1">
-        <v>12.0886854422992</v>
+        <v>2.20343269025562E-2</v>
       </c>
       <c r="L51" s="1">
         <v>1</v>
       </c>
       <c r="M51" s="1">
-        <v>105.014389608965</v>
+        <v>108.759068663758</v>
       </c>
       <c r="N51" s="1">
-        <v>8.0365295092000704</v>
+        <v>6.5138864797470797</v>
       </c>
       <c r="O51" s="2">
-        <v>5.4997814524115098E-3</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
+        <v>1.20915323151938E-2</v>
+      </c>
+      <c r="P51" s="1"/>
+    </row>
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="37"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="1">
-        <v>1.3649942556635E-2</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1.3649942556635E-2</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="1">
-        <v>18.4755555564075</v>
-      </c>
-      <c r="G52" s="1">
-        <v>3.0586142914115701E-3</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0.95648937143107404</v>
-      </c>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
-        <v>0.22882333097613</v>
+        <v>2.98483856205864E-2</v>
       </c>
       <c r="K52" s="1">
-        <v>0.22882333097613</v>
+        <v>2.98483856205864E-2</v>
       </c>
       <c r="L52" s="1">
         <v>1</v>
       </c>
       <c r="M52" s="1">
-        <v>10.434949913469801</v>
+        <v>13.393007197198701</v>
       </c>
       <c r="N52" s="1">
-        <v>0.152121209585661</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0.70435948589617503</v>
+        <v>8.8239135416321304</v>
+      </c>
+      <c r="O52" s="2">
+        <v>1.05420955332634E-2</v>
       </c>
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
+      <c r="A53" s="37"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="1">
-        <v>2.5350000000000001</v>
-      </c>
-      <c r="D53" s="1">
-        <v>2.5350000000000001</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="1">
-        <v>76.629206352881397</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.56803075885176302</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0.45335209406133298</v>
-      </c>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
-        <v>0.59262860980916598</v>
+        <v>1.15818782663304E-3</v>
       </c>
       <c r="K53" s="1">
-        <v>0.59262860980916598</v>
+        <v>1.15818782663304E-3</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <v>104.507129666586</v>
+        <v>108.463193154259</v>
       </c>
       <c r="N53" s="1">
-        <v>0.39397809906299802</v>
+        <v>0.342388676462696</v>
       </c>
       <c r="O53" s="1">
-        <v>0.531584837508144</v>
+        <v>0.55966903975183102</v>
       </c>
       <c r="P53" s="1"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
-        <v>1.0524858270047699</v>
+        <v>2.0797141885883202E-3</v>
       </c>
       <c r="K54" s="1">
-        <v>0.52624291350238295</v>
+        <v>1.0398570942941601E-3</v>
       </c>
       <c r="L54" s="1">
         <v>2</v>
       </c>
       <c r="M54" s="1">
-        <v>104.544741057998</v>
+        <v>108.513064659973</v>
       </c>
       <c r="N54" s="1">
-        <v>0.34984504506760999</v>
+        <v>0.30740721499443802</v>
       </c>
       <c r="O54" s="1">
-        <v>0.70561922195466797</v>
+        <v>0.73598934665486404</v>
       </c>
       <c r="P54" s="1"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="35" t="s">
-        <v>65</v>
+      <c r="A55" s="36" t="s">
+        <v>41</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="1">
-        <v>247.041666666667</v>
+        <v>98.415000000000006</v>
       </c>
       <c r="D55" s="1">
-        <v>247.041666666667</v>
+        <v>98.415000000000006</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
       </c>
       <c r="F55" s="1">
-        <v>76.679407978372694</v>
+        <v>76.629206352881397</v>
       </c>
       <c r="G55" s="1">
-        <v>10.693902247591801</v>
-      </c>
-      <c r="H55" s="2">
-        <v>1.61142062466842E-3</v>
+        <v>22.0523657327007</v>
+      </c>
+      <c r="H55" s="4">
+        <v>1.14210478822229E-5</v>
       </c>
       <c r="I55" s="1"/>
-      <c r="J55" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="38"/>
-      <c r="P55" s="1"/>
+      <c r="J55" s="1">
+        <v>12.0886854422992</v>
+      </c>
+      <c r="K55" s="1">
+        <v>12.0886854422992</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <v>105.014389608965</v>
+      </c>
+      <c r="N55" s="1">
+        <v>8.0365295092000704</v>
+      </c>
+      <c r="O55" s="2">
+        <v>5.4997814524115098E-3</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="1">
-        <v>1.07440437093056</v>
+        <v>1.3649942556635E-2</v>
       </c>
       <c r="D56" s="1">
-        <v>1.07440437093056</v>
+        <v>1.3649942556635E-2</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
       </c>
       <c r="F56" s="1">
-        <v>18.594235723709598</v>
+        <v>18.4755555564075</v>
       </c>
       <c r="G56" s="1">
-        <v>4.6508653670231298E-2</v>
+        <v>3.0586142914115701E-3</v>
       </c>
       <c r="H56" s="1">
-        <v>0.83160181683106904</v>
+        <v>0.95648937143107404</v>
       </c>
       <c r="I56" s="1"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
-      <c r="L56" s="38"/>
-      <c r="M56" s="38"/>
-      <c r="N56" s="38"/>
-      <c r="O56" s="38"/>
+      <c r="J56" s="1">
+        <v>0.22882333097613</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0.22882333097613</v>
+      </c>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <v>10.434949913469801</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0.152121209585661</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0.70435948589617503</v>
+      </c>
       <c r="P56" s="1"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="1">
-        <v>5.0416666666666696</v>
+        <v>2.5350000000000001</v>
       </c>
       <c r="D57" s="1">
-        <v>5.0416666666666696</v>
+        <v>2.5350000000000001</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
       </c>
       <c r="F57" s="1">
-        <v>76.679407978372694</v>
+        <v>76.629206352881397</v>
       </c>
       <c r="G57" s="1">
-        <v>0.21824290301207799</v>
+        <v>0.56803075885176302</v>
       </c>
       <c r="H57" s="1">
-        <v>0.64170681971566501</v>
+        <v>0.45335209406133298</v>
       </c>
       <c r="I57" s="1"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="38"/>
+      <c r="J57" s="1">
+        <v>0.59262860980916598</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0.59262860980916598</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1">
+        <v>104.507129666586</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0.39397809906299802</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0.531584837508144</v>
+      </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
       <c r="I58" s="1"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
-      <c r="L58" s="38"/>
-      <c r="M58" s="38"/>
-      <c r="N58" s="38"/>
-      <c r="O58" s="38"/>
+      <c r="J58" s="1">
+        <v>1.0524858270047699</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0.52624291350238295</v>
+      </c>
+      <c r="L58" s="1">
+        <v>2</v>
+      </c>
+      <c r="M58" s="1">
+        <v>104.544741057998</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0.34984504506760999</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0.70561922195466797</v>
+      </c>
       <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="35" t="s">
-        <v>64</v>
+      <c r="A59" s="36" t="s">
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="38" t="s">
+      <c r="C59" s="1">
+        <v>247.041666666667</v>
+      </c>
+      <c r="D59" s="1">
+        <v>247.041666666667</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
+        <v>76.679407978372694</v>
+      </c>
+      <c r="G59" s="1">
+        <v>10.693902247591801</v>
+      </c>
+      <c r="H59" s="2">
+        <v>1.61142062466842E-3</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1">
-        <v>40.695777417400599</v>
-      </c>
-      <c r="K59" s="1">
-        <v>40.695777417400599</v>
-      </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="1">
-        <v>106.469733462525</v>
-      </c>
-      <c r="N59" s="1">
-        <v>3.9616716048998302</v>
-      </c>
-      <c r="O59" s="2">
-        <v>4.9110369455561902E-2</v>
-      </c>
+      <c r="K59" s="39"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
+      <c r="N59" s="39"/>
+      <c r="O59" s="39"/>
       <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
+      <c r="A60" s="37"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
+      <c r="C60" s="1">
+        <v>1.07440437093056</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1.07440437093056</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>18.594235723709598</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4.6508653670231298E-2</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0.83160181683106904</v>
+      </c>
       <c r="I60" s="1"/>
-      <c r="J60" s="1">
-        <v>0.27305635622259</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0.27305635622259</v>
-      </c>
-      <c r="L60" s="1">
-        <v>1</v>
-      </c>
-      <c r="M60" s="1">
-        <v>11.2140015489656</v>
-      </c>
-      <c r="N60" s="1">
-        <v>2.6581618085072201E-2</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0.87338900665270902</v>
-      </c>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="39"/>
       <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
+      <c r="A61" s="37"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
+      <c r="C61" s="1">
+        <v>5.0416666666666696</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5.0416666666666696</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
+        <v>76.679407978372694</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.21824290301207799</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.64170681971566501</v>
+      </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="1">
-        <v>3.4613576315483399</v>
-      </c>
-      <c r="K61" s="1">
-        <v>3.4613576315483399</v>
-      </c>
-      <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="1">
-        <v>105.963614551601</v>
-      </c>
-      <c r="N61" s="1">
-        <v>0.33695786426837399</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0.56282293519802495</v>
-      </c>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="39"/>
+      <c r="M61" s="39"/>
+      <c r="N61" s="39"/>
+      <c r="O61" s="39"/>
       <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="37"/>
+      <c r="A62" s="38"/>
       <c r="B62" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="43"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="43"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="1">
-        <v>0.72850411949349603</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0.36425205974674801</v>
-      </c>
-      <c r="L62" s="1">
-        <v>2</v>
-      </c>
-      <c r="M62" s="1">
-        <v>106.003775172066</v>
-      </c>
-      <c r="N62" s="1">
-        <v>3.5459380154461803E-2</v>
-      </c>
-      <c r="O62" s="1">
-        <v>0.96517338143039799</v>
-      </c>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
-        <v>42</v>
+      <c r="A63" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="C63" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
-        <v>948.25120936445398</v>
+        <v>40.695777417400599</v>
       </c>
       <c r="K63" s="1">
-        <v>948.25120936445398</v>
+        <v>40.695777417400599</v>
       </c>
       <c r="L63" s="1">
         <v>1</v>
       </c>
       <c r="M63" s="1">
-        <v>106.240864481111</v>
+        <v>106.469733462525</v>
       </c>
       <c r="N63" s="1">
-        <v>41.507015861186602</v>
-      </c>
-      <c r="O63" s="4">
-        <v>3.5100798344271602E-9</v>
+        <v>3.9616716048998302</v>
+      </c>
+      <c r="O63" s="2">
+        <v>4.9110369455561902E-2</v>
       </c>
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
-        <v>0.22870622612837599</v>
+        <v>0.27305635622259</v>
       </c>
       <c r="K64" s="1">
-        <v>0.22870622612837599</v>
+        <v>0.27305635622259</v>
       </c>
       <c r="L64" s="1">
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <v>11.1643211838896</v>
+        <v>11.2140015489656</v>
       </c>
       <c r="N64" s="1">
-        <v>1.0010968466705201E-2</v>
+        <v>2.6581618085072201E-2</v>
       </c>
       <c r="O64" s="1">
-        <v>0.92207493031292298</v>
+        <v>0.87338900665270902</v>
       </c>
       <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
-        <v>37.771893612281502</v>
+        <v>3.4613576315483399</v>
       </c>
       <c r="K65" s="1">
-        <v>37.771893612281502</v>
+        <v>3.4613576315483399</v>
       </c>
       <c r="L65" s="1">
         <v>1</v>
       </c>
       <c r="M65" s="1">
-        <v>105.741872376204</v>
+        <v>105.963614551601</v>
       </c>
       <c r="N65" s="1">
-        <v>1.6533578568518801</v>
+        <v>0.33695786426837399</v>
       </c>
       <c r="O65" s="1">
-        <v>0.201311196369207</v>
+        <v>0.56282293519802495</v>
       </c>
       <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="37"/>
+      <c r="A66" s="38"/>
       <c r="B66" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
-        <v>3.9110782596565699</v>
+        <v>0.72850411949349603</v>
       </c>
       <c r="K66" s="1">
-        <v>1.95553912982829</v>
+        <v>0.36425205974674801</v>
       </c>
       <c r="L66" s="1">
         <v>2</v>
       </c>
       <c r="M66" s="1">
-        <v>105.779973230129</v>
+        <v>106.003775172066</v>
       </c>
       <c r="N66" s="1">
-        <v>8.5598196846334906E-2</v>
+        <v>3.5459380154461803E-2</v>
       </c>
       <c r="O66" s="1">
-        <v>0.91802651568849802</v>
+        <v>0.96517338143039799</v>
       </c>
       <c r="P66" s="1"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="35" t="s">
-        <v>43</v>
+      <c r="A67" s="36" t="s">
+        <v>42</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="1">
-        <v>1281.0265339451901</v>
-      </c>
-      <c r="D67" s="1">
-        <v>1281.0265339451901</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="1">
-        <v>62.592670114845198</v>
-      </c>
-      <c r="G67" s="1">
-        <v>122.161105137921</v>
-      </c>
-      <c r="H67" s="4">
-        <v>2.3819311555743102E-16</v>
-      </c>
+      <c r="C67" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="K67" s="38"/>
-      <c r="L67" s="38"/>
-      <c r="M67" s="38"/>
-      <c r="N67" s="38"/>
-      <c r="O67" s="38"/>
+      <c r="J67" s="1">
+        <v>948.25120936445398</v>
+      </c>
+      <c r="K67" s="1">
+        <v>948.25120936445398</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>106.240864481111</v>
+      </c>
+      <c r="N67" s="1">
+        <v>41.507015861186602</v>
+      </c>
+      <c r="O67" s="4">
+        <v>3.5100798344271602E-9</v>
+      </c>
       <c r="P67" s="1"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="1">
-        <v>170.11572143894901</v>
-      </c>
-      <c r="D68" s="1">
-        <v>170.11572143894901</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="1">
-        <v>15.0473384379988</v>
-      </c>
-      <c r="G68" s="1">
-        <v>16.222555881270999</v>
-      </c>
-      <c r="H68" s="2">
-        <v>1.0894169628446399E-3</v>
-      </c>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
       <c r="I68" s="1"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
-      <c r="L68" s="38"/>
-      <c r="M68" s="38"/>
-      <c r="N68" s="38"/>
-      <c r="O68" s="38"/>
+      <c r="J68" s="1">
+        <v>0.22870622612837599</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0.22870622612837599</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+      <c r="M68" s="1">
+        <v>11.1643211838896</v>
+      </c>
+      <c r="N68" s="1">
+        <v>1.0010968466705201E-2</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0.92207493031292298</v>
+      </c>
       <c r="P68" s="1"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="1">
-        <v>0.40196988959221502</v>
-      </c>
-      <c r="D69" s="1">
-        <v>0.40196988959221502</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1">
-        <v>62.592670115082399</v>
-      </c>
-      <c r="G69" s="1">
-        <v>3.8332606424258599E-2</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0.84541099798019603</v>
-      </c>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
-      <c r="L69" s="38"/>
-      <c r="M69" s="38"/>
-      <c r="N69" s="38"/>
-      <c r="O69" s="38"/>
+      <c r="J69" s="1">
+        <v>37.771893612281502</v>
+      </c>
+      <c r="K69" s="1">
+        <v>37.771893612281502</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
+        <v>105.741872376204</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1.6533578568518801</v>
+      </c>
+      <c r="O69" s="1">
+        <v>0.201311196369207</v>
+      </c>
       <c r="P69" s="1"/>
     </row>
-    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="37"/>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="38"/>
       <c r="B70" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
-      <c r="L70" s="38"/>
-      <c r="M70" s="38"/>
-      <c r="N70" s="38"/>
-      <c r="O70" s="38"/>
+      <c r="J70" s="1">
+        <v>3.9110782596565699</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1.95553912982829</v>
+      </c>
+      <c r="L70" s="1">
+        <v>2</v>
+      </c>
+      <c r="M70" s="1">
+        <v>105.779973230129</v>
+      </c>
+      <c r="N70" s="1">
+        <v>8.5598196846334906E-2</v>
+      </c>
+      <c r="O70" s="1">
+        <v>0.91802651568849802</v>
+      </c>
       <c r="P70" s="1"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="35" t="s">
-        <v>18</v>
+      <c r="A71" s="36" t="s">
+        <v>43</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="1">
+        <v>1281.0265339451901</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1281.0265339451901</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>62.592670114845198</v>
+      </c>
+      <c r="G71" s="1">
+        <v>122.161105137921</v>
+      </c>
+      <c r="H71" s="4">
+        <v>2.3819311555743102E-16</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1">
-        <v>7.7190184322692705E-4</v>
-      </c>
-      <c r="K71" s="1">
-        <v>7.7190184322692705E-4</v>
-      </c>
-      <c r="L71" s="1">
-        <v>1</v>
-      </c>
-      <c r="M71" s="1">
-        <v>109.162762099391</v>
-      </c>
-      <c r="N71" s="1">
-        <v>0.132778478118667</v>
-      </c>
-      <c r="O71" s="1">
-        <v>0.71627332791354703</v>
-      </c>
+      <c r="K71" s="39"/>
+      <c r="L71" s="39"/>
+      <c r="M71" s="39"/>
+      <c r="N71" s="39"/>
+      <c r="O71" s="39"/>
       <c r="P71" s="1"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
+      <c r="C72" s="1">
+        <v>170.11572143894901</v>
+      </c>
+      <c r="D72" s="1">
+        <v>170.11572143894901</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>15.0473384379988</v>
+      </c>
+      <c r="G72" s="1">
+        <v>16.222555881270999</v>
+      </c>
+      <c r="H72" s="2">
+        <v>1.0894169628446399E-3</v>
+      </c>
       <c r="I72" s="1"/>
-      <c r="J72" s="1">
-        <v>0.26383928794443301</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0.26383928794443301</v>
-      </c>
-      <c r="L72" s="1">
-        <v>1</v>
-      </c>
-      <c r="M72" s="1">
-        <v>14.2035557007019</v>
-      </c>
-      <c r="N72" s="1">
-        <v>45.384240792485897</v>
-      </c>
-      <c r="O72" s="4">
-        <v>8.8402488312841299E-6</v>
-      </c>
+      <c r="J72" s="39"/>
+      <c r="K72" s="39"/>
+      <c r="L72" s="39"/>
+      <c r="M72" s="39"/>
+      <c r="N72" s="39"/>
+      <c r="O72" s="39"/>
       <c r="P72" s="1"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
+      <c r="C73" s="1">
+        <v>0.40196988959221502</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0.40196988959221502</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>62.592670115082399</v>
+      </c>
+      <c r="G73" s="1">
+        <v>3.8332606424258599E-2</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0.84541099798019603</v>
+      </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="1">
-        <v>6.5298294112546198E-3</v>
-      </c>
-      <c r="K73" s="1">
-        <v>6.5298294112546198E-3</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1</v>
-      </c>
-      <c r="M73" s="1">
-        <v>108.83042432675499</v>
-      </c>
-      <c r="N73" s="1">
-        <v>1.12322676673025</v>
-      </c>
-      <c r="O73" s="1">
-        <v>0.29157119540922299</v>
-      </c>
+      <c r="J73" s="39"/>
+      <c r="K73" s="39"/>
+      <c r="L73" s="39"/>
+      <c r="M73" s="39"/>
+      <c r="N73" s="39"/>
+      <c r="O73" s="39"/>
       <c r="P73" s="1"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="37"/>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="38"/>
       <c r="B74" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="43"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
+      <c r="H74" s="43"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="1">
-        <v>7.3489818378573097E-3</v>
-      </c>
-      <c r="K74" s="1">
-        <v>3.6744909189286501E-3</v>
-      </c>
-      <c r="L74" s="1">
-        <v>2</v>
-      </c>
-      <c r="M74" s="1">
-        <v>108.867449329857</v>
-      </c>
-      <c r="N74" s="1">
-        <v>0.63206652031892696</v>
-      </c>
-      <c r="O74" s="1">
-        <v>0.53343128963438502</v>
-      </c>
+      <c r="J74" s="39"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
+      <c r="M74" s="39"/>
+      <c r="N74" s="39"/>
+      <c r="O74" s="39"/>
       <c r="P74" s="1"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="35" t="s">
-        <v>19</v>
+      <c r="A75" s="36" t="s">
+        <v>18</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="1">
-        <v>1628.5396493139699</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1628.5396493139699</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="1">
-        <v>62.368989869052001</v>
-      </c>
-      <c r="G75" s="1">
-        <v>132.99387365734901</v>
-      </c>
-      <c r="H75" s="4">
-        <v>4.1643897411378698E-17</v>
-      </c>
+      <c r="C75" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="K75" s="38"/>
-      <c r="L75" s="38"/>
-      <c r="M75" s="38"/>
-      <c r="N75" s="38"/>
-      <c r="O75" s="38"/>
+      <c r="J75" s="1">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="K75" s="1">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
+        <v>109.162762099391</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0.132778478118667</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0.71627332791354703</v>
+      </c>
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
+      <c r="A76" s="37"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="1">
-        <v>230.82876413714999</v>
-      </c>
-      <c r="D76" s="1">
-        <v>230.82876413714999</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="1">
-        <v>16.563800911315401</v>
-      </c>
-      <c r="G76" s="1">
-        <v>18.8505152497026</v>
-      </c>
-      <c r="H76" s="2">
-        <v>4.6861954719532999E-4</v>
-      </c>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="38"/>
+      <c r="J76" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1</v>
+      </c>
+      <c r="M76" s="1">
+        <v>14.2035557007019</v>
+      </c>
+      <c r="N76" s="1">
+        <v>45.384240792485897</v>
+      </c>
+      <c r="O76" s="4">
+        <v>8.8402488312841299E-6</v>
+      </c>
       <c r="P76" s="1"/>
     </row>
-    <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="37"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="1">
-        <v>14.980580034264699</v>
-      </c>
-      <c r="D77" s="1">
-        <v>14.980580034264699</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1">
-        <v>62.368989867379298</v>
-      </c>
-      <c r="G77" s="1">
-        <v>1.22338155489803</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0.27294624360005199</v>
-      </c>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
-      <c r="L77" s="38"/>
-      <c r="M77" s="38"/>
-      <c r="N77" s="38"/>
-      <c r="O77" s="38"/>
+      <c r="J77" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="K77" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1">
+        <v>108.83042432675499</v>
+      </c>
+      <c r="N77" s="1">
+        <v>1.12322676673025</v>
+      </c>
+      <c r="O77" s="1">
+        <v>0.29157119540922299</v>
+      </c>
       <c r="P77" s="1"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="37"/>
+      <c r="A78" s="38"/>
       <c r="B78" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="42"/>
-      <c r="D78" s="42"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="H78" s="42"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="38"/>
-      <c r="L78" s="38"/>
-      <c r="M78" s="38"/>
-      <c r="N78" s="38"/>
-      <c r="O78" s="38"/>
+      <c r="J78" s="1">
+        <v>7.3489818378573097E-3</v>
+      </c>
+      <c r="K78" s="1">
+        <v>3.6744909189286501E-3</v>
+      </c>
+      <c r="L78" s="1">
+        <v>2</v>
+      </c>
+      <c r="M78" s="1">
+        <v>108.867449329857</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0.63206652031892696</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0.53343128963438502</v>
+      </c>
       <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>39</v>
+      <c r="A79" s="36" t="s">
+        <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="38" t="s">
+      <c r="C79" s="1">
+        <v>1628.5396493139699</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1628.5396493139699</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1">
+        <v>62.368989869052001</v>
+      </c>
+      <c r="G79" s="1">
+        <v>132.99387365734901</v>
+      </c>
+      <c r="H79" s="4">
+        <v>4.1643897411378698E-17</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1">
-        <v>4.0252880405239402E-2</v>
-      </c>
-      <c r="K79" s="1">
-        <v>4.0252880405239402E-2</v>
-      </c>
-      <c r="L79" s="1">
-        <v>1</v>
-      </c>
-      <c r="M79" s="1">
-        <v>107.364526662513</v>
-      </c>
-      <c r="N79" s="1">
-        <v>3.06304929618606</v>
-      </c>
-      <c r="O79" s="3">
-        <v>8.2948057027609101E-2</v>
-      </c>
+      <c r="K79" s="39"/>
+      <c r="L79" s="39"/>
+      <c r="M79" s="39"/>
+      <c r="N79" s="39"/>
+      <c r="O79" s="39"/>
       <c r="P79" s="1"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="36"/>
+      <c r="A80" s="37"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
+      <c r="C80" s="1">
+        <v>230.82876413714999</v>
+      </c>
+      <c r="D80" s="1">
+        <v>230.82876413714999</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>16.563800911315401</v>
+      </c>
+      <c r="G80" s="1">
+        <v>18.8505152497026</v>
+      </c>
+      <c r="H80" s="2">
+        <v>4.6861954719532999E-4</v>
+      </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="1">
-        <v>0.42132164214255802</v>
-      </c>
-      <c r="K80" s="1">
-        <v>0.42132164214255802</v>
-      </c>
-      <c r="L80" s="1">
-        <v>1</v>
-      </c>
-      <c r="M80" s="1">
-        <v>13.0099671316875</v>
-      </c>
-      <c r="N80" s="1">
-        <v>32.060536946437701</v>
-      </c>
-      <c r="O80" s="4">
-        <v>7.7465741239532106E-5</v>
-      </c>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
+      <c r="L80" s="39"/>
+      <c r="M80" s="39"/>
+      <c r="N80" s="39"/>
+      <c r="O80" s="39"/>
       <c r="P80" s="1"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="36"/>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="37"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
+      <c r="C81" s="1">
+        <v>14.980580034264699</v>
+      </c>
+      <c r="D81" s="1">
+        <v>14.980580034264699</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>62.368989867379298</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1.22338155489803</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0.27294624360005199</v>
+      </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="1">
-        <v>7.8254362282741005E-2</v>
-      </c>
-      <c r="K81" s="1">
-        <v>7.8254362282741005E-2</v>
-      </c>
-      <c r="L81" s="1">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1">
-        <v>106.96971991586101</v>
-      </c>
-      <c r="N81" s="1">
-        <v>5.9547780655825902</v>
-      </c>
-      <c r="O81" s="2">
-        <v>1.63202510112339E-2</v>
-      </c>
+      <c r="J81" s="39"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="39"/>
+      <c r="M81" s="39"/>
+      <c r="N81" s="39"/>
+      <c r="O81" s="39"/>
       <c r="P81" s="1"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="37"/>
+      <c r="A82" s="38"/>
       <c r="B82" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="43"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1">
-        <v>2.6614614752845599E-3</v>
-      </c>
-      <c r="K82" s="1">
-        <v>1.33073073764228E-3</v>
-      </c>
-      <c r="L82" s="1">
-        <v>2</v>
-      </c>
-      <c r="M82" s="1">
-        <v>106.998307117191</v>
-      </c>
-      <c r="N82" s="1">
-        <v>0.101262165795663</v>
-      </c>
-      <c r="O82" s="1">
-        <v>0.90378258302877301</v>
-      </c>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
+      <c r="L82" s="39"/>
+      <c r="M82" s="39"/>
+      <c r="N82" s="39"/>
+      <c r="O82" s="39"/>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="35" t="s">
-        <v>40</v>
+      <c r="A83" s="36" t="s">
+        <v>39</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="1">
-        <v>1.1481734714944201</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1.1481734714944201</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="1">
-        <v>57.458627569308902</v>
-      </c>
-      <c r="G83" s="1">
-        <v>62.871367396090498</v>
-      </c>
-      <c r="H83" s="4">
-        <v>8.5554572534297795E-11</v>
-      </c>
+      <c r="C83" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" s="39"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="K83" s="38"/>
-      <c r="L83" s="38"/>
-      <c r="M83" s="38"/>
-      <c r="N83" s="38"/>
-      <c r="O83" s="38"/>
+      <c r="J83" s="1">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1">
+        <v>107.364526662513</v>
+      </c>
+      <c r="N83" s="1">
+        <v>3.06304929618606</v>
+      </c>
+      <c r="O83" s="3">
+        <v>8.2948057027609101E-2</v>
+      </c>
       <c r="P83" s="1"/>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="36"/>
+      <c r="A84" s="37"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="1">
-        <v>9.2911254906166099E-2</v>
-      </c>
-      <c r="D84" s="1">
-        <v>9.2911254906166099E-2</v>
-      </c>
-      <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="1">
-        <v>14.883763903298201</v>
-      </c>
-      <c r="G84" s="1">
-        <v>5.0876089610695701</v>
-      </c>
-      <c r="H84" s="2">
-        <v>3.9589780561885203E-2</v>
-      </c>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
       <c r="I84" s="1"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
-      <c r="L84" s="38"/>
-      <c r="M84" s="38"/>
-      <c r="N84" s="38"/>
-      <c r="O84" s="38"/>
+      <c r="J84" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1">
+        <v>13.0099671316875</v>
+      </c>
+      <c r="N84" s="1">
+        <v>32.060536946437701</v>
+      </c>
+      <c r="O84" s="4">
+        <v>7.7465741239532106E-5</v>
+      </c>
       <c r="P84" s="1"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="36"/>
+      <c r="A85" s="37"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="1">
-        <v>1.37366591368214E-2</v>
-      </c>
-      <c r="D85" s="1">
-        <v>1.37366591368214E-2</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="1">
-        <v>57.458627570771498</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.75218820572632805</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0.38939195861388898</v>
-      </c>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
       <c r="I85" s="1"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
-      <c r="L85" s="38"/>
-      <c r="M85" s="38"/>
-      <c r="N85" s="38"/>
-      <c r="O85" s="38"/>
+      <c r="J85" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="K85" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="L85" s="1">
+        <v>1</v>
+      </c>
+      <c r="M85" s="1">
+        <v>106.96971991586101</v>
+      </c>
+      <c r="N85" s="1">
+        <v>5.9547780655825902</v>
+      </c>
+      <c r="O85" s="2">
+        <v>1.63202510112339E-2</v>
+      </c>
       <c r="P85" s="1"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="37"/>
+      <c r="A86" s="38"/>
       <c r="B86" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="42"/>
-      <c r="D86" s="42"/>
-      <c r="E86" s="42"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="42"/>
-      <c r="H86" s="42"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="38"/>
-      <c r="L86" s="38"/>
-      <c r="M86" s="38"/>
-      <c r="N86" s="38"/>
-      <c r="O86" s="38"/>
+      <c r="J86" s="1">
+        <v>2.6614614752845599E-3</v>
+      </c>
+      <c r="K86" s="1">
+        <v>1.33073073764228E-3</v>
+      </c>
+      <c r="L86" s="1">
+        <v>2</v>
+      </c>
+      <c r="M86" s="1">
+        <v>106.998307117191</v>
+      </c>
+      <c r="N86" s="1">
+        <v>0.101262165795663</v>
+      </c>
+      <c r="O86" s="1">
+        <v>0.90378258302877301</v>
+      </c>
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="35" t="s">
-        <v>22</v>
+      <c r="A87" s="36" t="s">
+        <v>40</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="1">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="D87" s="1">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
       </c>
       <c r="F87" s="1">
-        <v>67.383586408567496</v>
+        <v>57.458627569308902</v>
       </c>
       <c r="G87" s="1">
-        <v>224.10765385608801</v>
+        <v>62.871367396090498</v>
       </c>
       <c r="H87" s="4">
-        <v>4.0821399088527701E-23</v>
+        <v>8.5554572534297795E-11</v>
       </c>
       <c r="I87" s="1"/>
-      <c r="J87" s="38" t="s">
+      <c r="J87" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K87" s="38"/>
-      <c r="L87" s="38"/>
-      <c r="M87" s="38"/>
-      <c r="N87" s="38"/>
-      <c r="O87" s="38"/>
+      <c r="K87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="39"/>
+      <c r="N87" s="39"/>
+      <c r="O87" s="39"/>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="36"/>
+      <c r="A88" s="37"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="D88" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
       </c>
       <c r="F88" s="1">
-        <v>19.7769266057722</v>
+        <v>14.883763903298201</v>
       </c>
       <c r="G88" s="1">
-        <v>6.8764153859934604E-2</v>
-      </c>
-      <c r="H88" s="1">
-        <v>0.79585674296255904</v>
+        <v>5.0876089610695701</v>
+      </c>
+      <c r="H88" s="2">
+        <v>3.9589780561885203E-2</v>
       </c>
       <c r="I88" s="1"/>
-      <c r="J88" s="38"/>
-      <c r="K88" s="38"/>
-      <c r="L88" s="38"/>
-      <c r="M88" s="38"/>
-      <c r="N88" s="38"/>
-      <c r="O88" s="38"/>
+      <c r="J88" s="39"/>
+      <c r="K88" s="39"/>
+      <c r="L88" s="39"/>
+      <c r="M88" s="39"/>
+      <c r="N88" s="39"/>
+      <c r="O88" s="39"/>
       <c r="P88" s="1"/>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="36"/>
+      <c r="A89" s="37"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="D89" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
       </c>
       <c r="F89" s="1">
-        <v>67.3835864091361</v>
+        <v>57.458627570771498</v>
       </c>
       <c r="G89" s="1">
-        <v>0.63854715062201595</v>
+        <v>0.75218820572632805</v>
       </c>
       <c r="H89" s="1">
-        <v>0.42704513346780898</v>
+        <v>0.38939195861388898</v>
       </c>
       <c r="I89" s="1"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38"/>
-      <c r="M89" s="38"/>
-      <c r="N89" s="38"/>
-      <c r="O89" s="38"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="39"/>
+      <c r="M89" s="39"/>
+      <c r="N89" s="39"/>
+      <c r="O89" s="39"/>
       <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="37"/>
+      <c r="A90" s="38"/>
       <c r="B90" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="42"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="42"/>
-      <c r="F90" s="42"/>
-      <c r="G90" s="42"/>
-      <c r="H90" s="42"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="43"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="43"/>
+      <c r="G90" s="43"/>
+      <c r="H90" s="43"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
-      <c r="L90" s="38"/>
-      <c r="M90" s="38"/>
-      <c r="N90" s="38"/>
-      <c r="O90" s="38"/>
+      <c r="J90" s="39"/>
+      <c r="K90" s="39"/>
+      <c r="L90" s="39"/>
+      <c r="M90" s="39"/>
+      <c r="N90" s="39"/>
+      <c r="O90" s="39"/>
       <c r="P90" s="1"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="35" t="s">
-        <v>23</v>
+      <c r="A91" s="36" t="s">
+        <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="1">
-        <v>5.0694430563116102</v>
+        <v>10.9358082393645</v>
       </c>
       <c r="D91" s="1">
-        <v>5.0694430563116102</v>
+        <v>10.9358082393645</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
       </c>
       <c r="F91" s="1">
-        <v>67.962550016506</v>
+        <v>67.383586408567496</v>
       </c>
       <c r="G91" s="1">
-        <v>123.23450697288</v>
-      </c>
-      <c r="H91" s="8">
-        <v>6.4779999000469503E-17</v>
+        <v>224.10765385608801</v>
+      </c>
+      <c r="H91" s="4">
+        <v>4.0821399088527701E-23</v>
       </c>
       <c r="I91" s="1"/>
-      <c r="J91" s="38" t="s">
+      <c r="J91" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K91" s="38"/>
-      <c r="L91" s="38"/>
-      <c r="M91" s="38"/>
-      <c r="N91" s="38"/>
-      <c r="O91" s="38"/>
+      <c r="K91" s="39"/>
+      <c r="L91" s="39"/>
+      <c r="M91" s="39"/>
+      <c r="N91" s="39"/>
+      <c r="O91" s="39"/>
       <c r="P91" s="1"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="36"/>
+      <c r="A92" s="37"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="1">
-        <v>0.289278337816473</v>
+        <v>3.35549271707291E-3</v>
       </c>
       <c r="D92" s="1">
-        <v>0.289278337816473</v>
+        <v>3.35549271707291E-3</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
       </c>
       <c r="F92" s="1">
-        <v>23.487577951072801</v>
+        <v>19.7769266057722</v>
       </c>
       <c r="G92" s="1">
-        <v>7.0321478992377502</v>
-      </c>
-      <c r="H92" s="2">
-        <v>1.4106574908243E-2</v>
+        <v>6.8764153859934604E-2</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0.79585674296255904</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="38"/>
-      <c r="K92" s="38"/>
-      <c r="L92" s="38"/>
-      <c r="M92" s="38"/>
-      <c r="N92" s="38"/>
-      <c r="O92" s="38"/>
+      <c r="J92" s="39"/>
+      <c r="K92" s="39"/>
+      <c r="L92" s="39"/>
+      <c r="M92" s="39"/>
+      <c r="N92" s="39"/>
+      <c r="O92" s="39"/>
       <c r="P92" s="1"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="36"/>
+      <c r="A93" s="37"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="1">
-        <v>5.3673365621619298E-2</v>
+        <v>3.11592623939527E-2</v>
       </c>
       <c r="D93" s="1">
-        <v>5.3673365621619298E-2</v>
+        <v>3.11592623939527E-2</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
       </c>
       <c r="F93" s="1">
-        <v>67.962550017652504</v>
+        <v>67.3835864091361</v>
       </c>
       <c r="G93" s="1">
-        <v>1.30476083397765</v>
+        <v>0.63854715062201595</v>
       </c>
       <c r="H93" s="1">
-        <v>0.25735376158301099</v>
+        <v>0.42704513346780898</v>
       </c>
       <c r="I93" s="1"/>
-      <c r="J93" s="38"/>
-      <c r="K93" s="38"/>
-      <c r="L93" s="38"/>
-      <c r="M93" s="38"/>
-      <c r="N93" s="38"/>
-      <c r="O93" s="38"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="39"/>
+      <c r="N93" s="39"/>
+      <c r="O93" s="39"/>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="37"/>
+      <c r="A94" s="38"/>
       <c r="B94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="42"/>
-      <c r="D94" s="42"/>
-      <c r="E94" s="42"/>
-      <c r="F94" s="42"/>
-      <c r="G94" s="42"/>
-      <c r="H94" s="42"/>
+      <c r="C94" s="43"/>
+      <c r="D94" s="43"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="43"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="43"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="38"/>
-      <c r="K94" s="38"/>
-      <c r="L94" s="38"/>
-      <c r="M94" s="38"/>
-      <c r="N94" s="38"/>
-      <c r="O94" s="38"/>
+      <c r="J94" s="39"/>
+      <c r="K94" s="39"/>
+      <c r="L94" s="39"/>
+      <c r="M94" s="39"/>
+      <c r="N94" s="39"/>
+      <c r="O94" s="39"/>
       <c r="P94" s="1"/>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="35" t="s">
-        <v>31</v>
+      <c r="A95" s="36" t="s">
+        <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="1">
-        <v>7.8223335347028398</v>
+        <v>5.0694430563116102</v>
       </c>
       <c r="D95" s="1">
-        <v>7.8223335347028398</v>
+        <v>5.0694430563116102</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
       </c>
       <c r="F95" s="1">
-        <v>56.420511723736702</v>
+        <v>67.962550016506</v>
       </c>
       <c r="G95" s="1">
-        <v>269.35108163868898</v>
-      </c>
-      <c r="H95" s="4">
-        <v>3.8248319558473298E-23</v>
+        <v>123.23450697288</v>
+      </c>
+      <c r="H95" s="8">
+        <v>6.4779999000469503E-17</v>
       </c>
       <c r="I95" s="1"/>
-      <c r="J95" s="38" t="s">
+      <c r="J95" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K95" s="38"/>
-      <c r="L95" s="38"/>
-      <c r="M95" s="38"/>
-      <c r="N95" s="38"/>
-      <c r="O95" s="38"/>
+      <c r="K95" s="39"/>
+      <c r="L95" s="39"/>
+      <c r="M95" s="39"/>
+      <c r="N95" s="39"/>
+      <c r="O95" s="39"/>
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="36"/>
+      <c r="A96" s="37"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="1">
-        <v>3.7421662066775302E-2</v>
+        <v>0.289278337816473</v>
       </c>
       <c r="D96" s="1">
-        <v>3.7421662066775302E-2</v>
+        <v>0.289278337816473</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
       </c>
       <c r="F96" s="1">
-        <v>11.2818684676293</v>
+        <v>23.487577951072801</v>
       </c>
       <c r="G96" s="1">
-        <v>1.28856243596449</v>
-      </c>
-      <c r="H96" s="1">
-        <v>0.27985440517664001</v>
+        <v>7.0321478992377502</v>
+      </c>
+      <c r="H96" s="2">
+        <v>1.4106574908243E-2</v>
       </c>
       <c r="I96" s="1"/>
-      <c r="J96" s="38"/>
-      <c r="K96" s="38"/>
-      <c r="L96" s="38"/>
-      <c r="M96" s="38"/>
-      <c r="N96" s="38"/>
-      <c r="O96" s="38"/>
+      <c r="J96" s="39"/>
+      <c r="K96" s="39"/>
+      <c r="L96" s="39"/>
+      <c r="M96" s="39"/>
+      <c r="N96" s="39"/>
+      <c r="O96" s="39"/>
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="36"/>
+      <c r="A97" s="37"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="1">
-        <v>3.631254937336E-3</v>
+        <v>5.3673365621619298E-2</v>
       </c>
       <c r="D97" s="1">
-        <v>3.631254937336E-3</v>
+        <v>5.3673365621619298E-2</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
       </c>
       <c r="F97" s="1">
-        <v>56.420511720510099</v>
+        <v>67.962550017652504</v>
       </c>
       <c r="G97" s="1">
-        <v>0.125037169629515</v>
+        <v>1.30476083397765</v>
       </c>
       <c r="H97" s="1">
-        <v>0.72495214931683005</v>
+        <v>0.25735376158301099</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="38"/>
-      <c r="K97" s="38"/>
-      <c r="L97" s="38"/>
-      <c r="M97" s="38"/>
-      <c r="N97" s="38"/>
-      <c r="O97" s="38"/>
+      <c r="J97" s="39"/>
+      <c r="K97" s="39"/>
+      <c r="L97" s="39"/>
+      <c r="M97" s="39"/>
+      <c r="N97" s="39"/>
+      <c r="O97" s="39"/>
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="37"/>
+      <c r="A98" s="38"/>
       <c r="B98" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C98" s="42"/>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="42"/>
-      <c r="G98" s="42"/>
-      <c r="H98" s="42"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="43"/>
+      <c r="E98" s="43"/>
+      <c r="F98" s="43"/>
+      <c r="G98" s="43"/>
+      <c r="H98" s="43"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="38"/>
-      <c r="K98" s="38"/>
-      <c r="L98" s="38"/>
-      <c r="M98" s="38"/>
-      <c r="N98" s="38"/>
-      <c r="O98" s="38"/>
+      <c r="J98" s="39"/>
+      <c r="K98" s="39"/>
+      <c r="L98" s="39"/>
+      <c r="M98" s="39"/>
+      <c r="N98" s="39"/>
+      <c r="O98" s="39"/>
       <c r="P98" s="1"/>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="35" t="s">
-        <v>29</v>
+      <c r="A99" s="36" t="s">
+        <v>31</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C99" s="38" t="s">
+      <c r="C99" s="1">
+        <v>7.8223335347028398</v>
+      </c>
+      <c r="D99" s="1">
+        <v>7.8223335347028398</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1">
+        <v>56.420511723736702</v>
+      </c>
+      <c r="G99" s="1">
+        <v>269.35108163868898</v>
+      </c>
+      <c r="H99" s="4">
+        <v>3.8248319558473298E-23</v>
+      </c>
+      <c r="I99" s="1"/>
+      <c r="J99" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D99" s="38"/>
-      <c r="E99" s="38"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="38"/>
-      <c r="H99" s="38"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1">
-        <v>4.9920514192076698E-4</v>
-      </c>
-      <c r="K99" s="1">
-        <v>4.9920514192076698E-4</v>
-      </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-      <c r="M99" s="1">
-        <v>109.501348528158</v>
-      </c>
-      <c r="N99" s="1">
-        <v>3.3446840501390498</v>
-      </c>
-      <c r="O99" s="2">
-        <v>7.0143959578357298E-2</v>
-      </c>
+      <c r="K99" s="39"/>
+      <c r="L99" s="39"/>
+      <c r="M99" s="39"/>
+      <c r="N99" s="39"/>
+      <c r="O99" s="39"/>
       <c r="P99" s="1"/>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="36"/>
+      <c r="A100" s="37"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="38"/>
-      <c r="D100" s="38"/>
-      <c r="E100" s="38"/>
-      <c r="F100" s="38"/>
-      <c r="G100" s="38"/>
-      <c r="H100" s="38"/>
+      <c r="C100" s="1">
+        <v>3.7421662066775302E-2</v>
+      </c>
+      <c r="D100" s="1">
+        <v>3.7421662066775302E-2</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1">
+        <v>11.2818684676293</v>
+      </c>
+      <c r="G100" s="1">
+        <v>1.28856243596449</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0.27985440517664001</v>
+      </c>
       <c r="I100" s="1"/>
-      <c r="J100" s="1">
-        <v>4.3245963051368403E-3</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4.3245963051368403E-3</v>
-      </c>
-      <c r="L100" s="1">
-        <v>1</v>
-      </c>
-      <c r="M100" s="1">
-        <v>14.3846326295774</v>
-      </c>
-      <c r="N100" s="1">
-        <v>28.974878402548999</v>
-      </c>
-      <c r="O100" s="4">
-        <v>8.7931651517614295E-5</v>
-      </c>
+      <c r="J100" s="39"/>
+      <c r="K100" s="39"/>
+      <c r="L100" s="39"/>
+      <c r="M100" s="39"/>
+      <c r="N100" s="39"/>
+      <c r="O100" s="39"/>
       <c r="P100" s="1"/>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="36"/>
+      <c r="A101" s="37"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="38"/>
-      <c r="D101" s="38"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38"/>
-      <c r="G101" s="38"/>
-      <c r="H101" s="38"/>
+      <c r="C101" s="1">
+        <v>3.631254937336E-3</v>
+      </c>
+      <c r="D101" s="1">
+        <v>3.631254937336E-3</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1">
+        <v>56.420511720510099</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.125037169629515</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0.72495214931683005</v>
+      </c>
       <c r="I101" s="1"/>
-      <c r="J101" s="5">
-        <v>4.4673218852987901E-5</v>
-      </c>
-      <c r="K101" s="5">
-        <v>4.4673218852987901E-5</v>
-      </c>
-      <c r="L101" s="1">
-        <v>1</v>
-      </c>
-      <c r="M101" s="1">
-        <v>109.203333776652</v>
-      </c>
-      <c r="N101" s="1">
-        <v>0.29931142534119798</v>
-      </c>
-      <c r="O101" s="1">
-        <v>0.58543070585289902</v>
-      </c>
+      <c r="J101" s="39"/>
+      <c r="K101" s="39"/>
+      <c r="L101" s="39"/>
+      <c r="M101" s="39"/>
+      <c r="N101" s="39"/>
+      <c r="O101" s="39"/>
       <c r="P101" s="1"/>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="37"/>
+      <c r="A102" s="38"/>
       <c r="B102" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C102" s="38"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="38"/>
-      <c r="H102" s="38"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="43"/>
+      <c r="E102" s="43"/>
+      <c r="F102" s="43"/>
+      <c r="G102" s="43"/>
+      <c r="H102" s="43"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="1">
-        <v>2.5092673060789E-4</v>
-      </c>
-      <c r="K102" s="1">
-        <v>1.25463365303945E-4</v>
-      </c>
-      <c r="L102" s="1">
-        <v>2</v>
-      </c>
-      <c r="M102" s="1">
-        <v>109.245496603218</v>
-      </c>
-      <c r="N102" s="1">
-        <v>0.84060696008511204</v>
-      </c>
-      <c r="O102" s="1">
-        <v>0.43421981831232398</v>
-      </c>
+      <c r="J102" s="39"/>
+      <c r="K102" s="39"/>
+      <c r="L102" s="39"/>
+      <c r="M102" s="39"/>
+      <c r="N102" s="39"/>
+      <c r="O102" s="39"/>
       <c r="P102" s="1"/>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="35" t="s">
-        <v>30</v>
+      <c r="A103" s="36" t="s">
+        <v>29</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="38" t="s">
+      <c r="C103" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D103" s="38"/>
-      <c r="E103" s="38"/>
-      <c r="F103" s="38"/>
-      <c r="G103" s="38"/>
-      <c r="H103" s="38"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
-        <v>1.4241127553301099E-4</v>
+        <v>4.9920514192076698E-4</v>
       </c>
       <c r="K103" s="1">
-        <v>1.4241127553301099E-4</v>
+        <v>4.9920514192076698E-4</v>
       </c>
       <c r="L103" s="1">
         <v>1</v>
       </c>
       <c r="M103" s="1">
-        <v>108.252981550744</v>
+        <v>109.501348528158</v>
       </c>
       <c r="N103" s="1">
-        <v>4.8961312702676701E-2</v>
-      </c>
-      <c r="O103" s="1">
-        <v>0.82529746395827397</v>
+        <v>3.3446840501390498</v>
+      </c>
+      <c r="O103" s="2">
+        <v>7.0143959578357298E-2</v>
       </c>
       <c r="P103" s="1"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="36"/>
+      <c r="A104" s="37"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="38"/>
-      <c r="D104" s="38"/>
-      <c r="E104" s="38"/>
-      <c r="F104" s="38"/>
-      <c r="G104" s="38"/>
-      <c r="H104" s="38"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="39"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
-        <v>4.6725153189010001E-2</v>
+        <v>4.3245963051368403E-3</v>
       </c>
       <c r="K104" s="1">
-        <v>4.6725153189010001E-2</v>
+        <v>4.3245963051368403E-3</v>
       </c>
       <c r="L104" s="1">
         <v>1</v>
       </c>
       <c r="M104" s="1">
-        <v>13.540354095849599</v>
+        <v>14.3846326295774</v>
       </c>
       <c r="N104" s="1">
-        <v>16.0642114032417</v>
-      </c>
-      <c r="O104" s="2">
-        <v>1.3790795758093499E-3</v>
+        <v>28.974878402548999</v>
+      </c>
+      <c r="O104" s="4">
+        <v>8.7931651517614295E-5</v>
       </c>
       <c r="P104" s="1"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="36"/>
+      <c r="A105" s="37"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="38"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="38"/>
-      <c r="F105" s="38"/>
-      <c r="G105" s="38"/>
-      <c r="H105" s="38"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="39"/>
+      <c r="F105" s="39"/>
+      <c r="G105" s="39"/>
+      <c r="H105" s="39"/>
       <c r="I105" s="1"/>
-      <c r="J105" s="1">
-        <v>2.8302586845141399E-2</v>
-      </c>
-      <c r="K105" s="1">
-        <v>2.8302586845141399E-2</v>
+      <c r="J105" s="5">
+        <v>4.4673218852987901E-5</v>
+      </c>
+      <c r="K105" s="5">
+        <v>4.4673218852987901E-5</v>
       </c>
       <c r="L105" s="1">
         <v>1</v>
       </c>
       <c r="M105" s="1">
-        <v>107.87081438761901</v>
+        <v>109.203333776652</v>
       </c>
       <c r="N105" s="1">
-        <v>9.7304921933546105</v>
-      </c>
-      <c r="O105" s="2">
-        <v>2.3248319291652099E-3</v>
+        <v>0.29931142534119798</v>
+      </c>
+      <c r="O105" s="1">
+        <v>0.58543070585289902</v>
       </c>
       <c r="P105" s="1"/>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="37"/>
+      <c r="A106" s="38"/>
       <c r="B106" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C106" s="38"/>
-      <c r="D106" s="38"/>
-      <c r="E106" s="38"/>
-      <c r="F106" s="38"/>
-      <c r="G106" s="38"/>
-      <c r="H106" s="38"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="39"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
-        <v>6.3796317056246301E-3</v>
+        <v>2.5092673060789E-4</v>
       </c>
       <c r="K106" s="1">
-        <v>3.1898158528123098E-3</v>
+        <v>1.25463365303945E-4</v>
       </c>
       <c r="L106" s="1">
         <v>2</v>
       </c>
       <c r="M106" s="1">
-        <v>107.90322647445799</v>
+        <v>109.245496603218</v>
       </c>
       <c r="N106" s="1">
-        <v>1.0966657720673001</v>
+        <v>0.84060696008511204</v>
       </c>
       <c r="O106" s="1">
-        <v>0.33767591593294399</v>
+        <v>0.43421981831232398</v>
       </c>
       <c r="P106" s="1"/>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="35" t="s">
-        <v>24</v>
+      <c r="A107" s="36" t="s">
+        <v>30</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="1">
-        <v>11.9812815608671</v>
-      </c>
-      <c r="D107" s="1">
-        <v>11.9812815608671</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="1">
-        <v>56.633285935703199</v>
-      </c>
-      <c r="G107" s="1">
-        <v>9.9997158132458601</v>
-      </c>
-      <c r="H107" s="2">
-        <v>2.5160186313214301E-3</v>
-      </c>
+      <c r="C107" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" s="39"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="39"/>
       <c r="I107" s="1"/>
-      <c r="J107" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="K107" s="38"/>
-      <c r="L107" s="38"/>
-      <c r="M107" s="38"/>
-      <c r="N107" s="38"/>
-      <c r="O107" s="38"/>
+      <c r="J107" s="1">
+        <v>1.4241127553301099E-4</v>
+      </c>
+      <c r="K107" s="1">
+        <v>1.4241127553301099E-4</v>
+      </c>
+      <c r="L107" s="1">
+        <v>1</v>
+      </c>
+      <c r="M107" s="1">
+        <v>108.252981550744</v>
+      </c>
+      <c r="N107" s="1">
+        <v>4.8961312702676701E-2</v>
+      </c>
+      <c r="O107" s="1">
+        <v>0.82529746395827397</v>
+      </c>
       <c r="P107" s="1"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="36"/>
+      <c r="A108" s="37"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="1">
-        <v>3.02703955159041</v>
-      </c>
-      <c r="D108" s="1">
-        <v>3.02703955159041</v>
-      </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="1">
-        <v>15.4038748263026</v>
-      </c>
-      <c r="G108" s="1">
-        <v>2.5264021313232998</v>
-      </c>
-      <c r="H108" s="1">
-        <v>0.13226601261193599</v>
-      </c>
+      <c r="C108" s="39"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="39"/>
+      <c r="F108" s="39"/>
+      <c r="G108" s="39"/>
+      <c r="H108" s="39"/>
       <c r="I108" s="1"/>
-      <c r="J108" s="38"/>
-      <c r="K108" s="38"/>
-      <c r="L108" s="38"/>
-      <c r="M108" s="38"/>
-      <c r="N108" s="38"/>
-      <c r="O108" s="38"/>
+      <c r="J108" s="1">
+        <v>4.6725153189010001E-2</v>
+      </c>
+      <c r="K108" s="1">
+        <v>4.6725153189010001E-2</v>
+      </c>
+      <c r="L108" s="1">
+        <v>1</v>
+      </c>
+      <c r="M108" s="1">
+        <v>13.540354095849599</v>
+      </c>
+      <c r="N108" s="1">
+        <v>16.0642114032417</v>
+      </c>
+      <c r="O108" s="2">
+        <v>1.3790795758093499E-3</v>
+      </c>
       <c r="P108" s="1"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="36"/>
+      <c r="A109" s="37"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="1">
-        <v>26.523989627052899</v>
-      </c>
-      <c r="D109" s="1">
-        <v>26.523989627052899</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="1">
-        <v>56.633285937971998</v>
-      </c>
-      <c r="G109" s="1">
-        <v>22.1372277378326</v>
-      </c>
-      <c r="H109" s="4">
-        <v>1.67603779088435E-5</v>
-      </c>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
+      <c r="H109" s="39"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="38"/>
-      <c r="K109" s="38"/>
-      <c r="L109" s="38"/>
-      <c r="M109" s="38"/>
-      <c r="N109" s="38"/>
-      <c r="O109" s="38"/>
+      <c r="J109" s="1">
+        <v>2.8302586845141399E-2</v>
+      </c>
+      <c r="K109" s="1">
+        <v>2.8302586845141399E-2</v>
+      </c>
+      <c r="L109" s="1">
+        <v>1</v>
+      </c>
+      <c r="M109" s="1">
+        <v>107.87081438761901</v>
+      </c>
+      <c r="N109" s="1">
+        <v>9.7304921933546105</v>
+      </c>
+      <c r="O109" s="2">
+        <v>2.3248319291652099E-3</v>
+      </c>
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="37"/>
+      <c r="A110" s="38"/>
       <c r="B110" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C110" s="42"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="42"/>
-      <c r="F110" s="42"/>
-      <c r="G110" s="42"/>
-      <c r="H110" s="42"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="39"/>
       <c r="I110" s="1"/>
-      <c r="J110" s="38"/>
-      <c r="K110" s="38"/>
-      <c r="L110" s="38"/>
-      <c r="M110" s="38"/>
-      <c r="N110" s="38"/>
-      <c r="O110" s="38"/>
+      <c r="J110" s="1">
+        <v>6.3796317056246301E-3</v>
+      </c>
+      <c r="K110" s="1">
+        <v>3.1898158528123098E-3</v>
+      </c>
+      <c r="L110" s="1">
+        <v>2</v>
+      </c>
+      <c r="M110" s="1">
+        <v>107.90322647445799</v>
+      </c>
+      <c r="N110" s="1">
+        <v>1.0966657720673001</v>
+      </c>
+      <c r="O110" s="1">
+        <v>0.33767591593294399</v>
+      </c>
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="35" t="s">
-        <v>20</v>
+      <c r="A111" s="36" t="s">
+        <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1">
-        <v>331.79409767299302</v>
+        <v>11.9812815608671</v>
       </c>
       <c r="D111" s="1">
-        <v>331.79409767299302</v>
+        <v>11.9812815608671</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
       </c>
       <c r="F111" s="1">
-        <v>63.731078470330502</v>
+        <v>56.633285935703199</v>
       </c>
       <c r="G111" s="1">
-        <v>64.149644494127003</v>
-      </c>
-      <c r="H111" s="4">
-        <v>3.1891308959839999E-11</v>
+        <v>9.9997158132458601</v>
+      </c>
+      <c r="H111" s="2">
+        <v>2.5160186313214301E-3</v>
       </c>
       <c r="I111" s="1"/>
-      <c r="J111" s="38" t="s">
+      <c r="J111" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K111" s="38"/>
-      <c r="L111" s="38"/>
-      <c r="M111" s="38"/>
-      <c r="N111" s="38"/>
-      <c r="O111" s="38"/>
+      <c r="K111" s="39"/>
+      <c r="L111" s="39"/>
+      <c r="M111" s="39"/>
+      <c r="N111" s="39"/>
+      <c r="O111" s="39"/>
       <c r="P111" s="1"/>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="36"/>
+      <c r="A112" s="37"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C112" s="1">
-        <v>33.852970049497699</v>
+        <v>3.02703955159041</v>
       </c>
       <c r="D112" s="1">
-        <v>33.852970049497699</v>
+        <v>3.02703955159041</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
       </c>
       <c r="F112" s="1">
-        <v>18.1476666615299</v>
+        <v>15.4038748263026</v>
       </c>
       <c r="G112" s="1">
-        <v>6.5451917589140702</v>
-      </c>
-      <c r="H112" s="2">
-        <v>1.9668218703936501E-2</v>
+        <v>2.5264021313232998</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0.13226601261193599</v>
       </c>
       <c r="I112" s="1"/>
-      <c r="J112" s="38"/>
-      <c r="K112" s="38"/>
-      <c r="L112" s="38"/>
-      <c r="M112" s="38"/>
-      <c r="N112" s="38"/>
-      <c r="O112" s="38"/>
+      <c r="J112" s="39"/>
+      <c r="K112" s="39"/>
+      <c r="L112" s="39"/>
+      <c r="M112" s="39"/>
+      <c r="N112" s="39"/>
+      <c r="O112" s="39"/>
       <c r="P112" s="1"/>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" s="36"/>
+      <c r="A113" s="37"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C113" s="1">
-        <v>18.294225807761201</v>
+        <v>26.523989627052899</v>
       </c>
       <c r="D113" s="1">
-        <v>18.294225807761201</v>
+        <v>26.523989627052899</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
       </c>
       <c r="F113" s="1">
-        <v>63.731078469087997</v>
+        <v>56.633285937971998</v>
       </c>
       <c r="G113" s="1">
-        <v>3.5370372471779099</v>
-      </c>
-      <c r="H113" s="3">
-        <v>6.4583181614334004E-2</v>
+        <v>22.1372277378326</v>
+      </c>
+      <c r="H113" s="4">
+        <v>1.67603779088435E-5</v>
       </c>
       <c r="I113" s="1"/>
-      <c r="J113" s="38"/>
-      <c r="K113" s="38"/>
-      <c r="L113" s="38"/>
-      <c r="M113" s="38"/>
-      <c r="N113" s="38"/>
-      <c r="O113" s="38"/>
+      <c r="J113" s="39"/>
+      <c r="K113" s="39"/>
+      <c r="L113" s="39"/>
+      <c r="M113" s="39"/>
+      <c r="N113" s="39"/>
+      <c r="O113" s="39"/>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" s="37"/>
+      <c r="A114" s="38"/>
       <c r="B114" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="42"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="42"/>
-      <c r="F114" s="42"/>
-      <c r="G114" s="42"/>
-      <c r="H114" s="42"/>
+      <c r="C114" s="43"/>
+      <c r="D114" s="43"/>
+      <c r="E114" s="43"/>
+      <c r="F114" s="43"/>
+      <c r="G114" s="43"/>
+      <c r="H114" s="43"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="38"/>
-      <c r="K114" s="38"/>
-      <c r="L114" s="38"/>
-      <c r="M114" s="38"/>
-      <c r="N114" s="38"/>
-      <c r="O114" s="38"/>
+      <c r="J114" s="39"/>
+      <c r="K114" s="39"/>
+      <c r="L114" s="39"/>
+      <c r="M114" s="39"/>
+      <c r="N114" s="39"/>
+      <c r="O114" s="39"/>
       <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" s="35" t="s">
-        <v>21</v>
+      <c r="A115" s="36" t="s">
+        <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1">
-        <v>24482.794046813899</v>
+        <v>331.79409767299302</v>
       </c>
       <c r="D115" s="1">
-        <v>24482.794046813899</v>
+        <v>331.79409767299302</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
       </c>
       <c r="F115" s="1">
-        <v>54.370003117736701</v>
+        <v>63.731078470330502</v>
       </c>
       <c r="G115" s="1">
-        <v>850.32626657220897</v>
+        <v>64.149644494127003</v>
       </c>
       <c r="H115" s="4">
-        <v>7.05414701429731E-35</v>
+        <v>3.1891308959839999E-11</v>
       </c>
       <c r="I115" s="1"/>
-      <c r="J115" s="38" t="s">
+      <c r="J115" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K115" s="38"/>
-      <c r="L115" s="38"/>
-      <c r="M115" s="38"/>
-      <c r="N115" s="38"/>
-      <c r="O115" s="38"/>
+      <c r="K115" s="39"/>
+      <c r="L115" s="39"/>
+      <c r="M115" s="39"/>
+      <c r="N115" s="39"/>
+      <c r="O115" s="39"/>
       <c r="P115" s="1"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A116" s="36"/>
+      <c r="A116" s="37"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="1">
-        <v>151.803221723246</v>
+        <v>33.852970049497699</v>
       </c>
       <c r="D116" s="1">
-        <v>151.803221723246</v>
+        <v>33.852970049497699</v>
       </c>
       <c r="E116" s="1">
         <v>1</v>
       </c>
       <c r="F116" s="1">
-        <v>12.607670268557801</v>
+        <v>18.1476666615299</v>
       </c>
       <c r="G116" s="1">
-        <v>5.2723666479708697</v>
+        <v>6.5451917589140702</v>
       </c>
       <c r="H116" s="2">
-        <v>3.9509565365961799E-2</v>
+        <v>1.9668218703936501E-2</v>
       </c>
       <c r="I116" s="1"/>
-      <c r="J116" s="38"/>
-      <c r="K116" s="38"/>
-      <c r="L116" s="38"/>
-      <c r="M116" s="38"/>
-      <c r="N116" s="38"/>
-      <c r="O116" s="38"/>
+      <c r="J116" s="39"/>
+      <c r="K116" s="39"/>
+      <c r="L116" s="39"/>
+      <c r="M116" s="39"/>
+      <c r="N116" s="39"/>
+      <c r="O116" s="39"/>
       <c r="P116" s="1"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="36"/>
+      <c r="A117" s="37"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="1">
-        <v>191.244540460943</v>
+        <v>18.294225807761201</v>
       </c>
       <c r="D117" s="1">
-        <v>191.244540460943</v>
+        <v>18.294225807761201</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
       </c>
       <c r="F117" s="1">
-        <v>54.370003120174303</v>
+        <v>63.731078469087997</v>
       </c>
       <c r="G117" s="1">
-        <v>6.64222620104238</v>
-      </c>
-      <c r="H117" s="2">
-        <v>1.2703272318058401E-2</v>
+        <v>3.5370372471779099</v>
+      </c>
+      <c r="H117" s="3">
+        <v>6.4583181614334004E-2</v>
       </c>
       <c r="I117" s="1"/>
-      <c r="J117" s="38"/>
-      <c r="K117" s="38"/>
-      <c r="L117" s="38"/>
-      <c r="M117" s="38"/>
-      <c r="N117" s="38"/>
-      <c r="O117" s="38"/>
+      <c r="J117" s="39"/>
+      <c r="K117" s="39"/>
+      <c r="L117" s="39"/>
+      <c r="M117" s="39"/>
+      <c r="N117" s="39"/>
+      <c r="O117" s="39"/>
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A118" s="37"/>
+      <c r="A118" s="38"/>
       <c r="B118" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C118" s="42"/>
-      <c r="D118" s="42"/>
-      <c r="E118" s="42"/>
-      <c r="F118" s="42"/>
-      <c r="G118" s="42"/>
-      <c r="H118" s="42"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="43"/>
+      <c r="E118" s="43"/>
+      <c r="F118" s="43"/>
+      <c r="G118" s="43"/>
+      <c r="H118" s="43"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="38"/>
-      <c r="K118" s="38"/>
-      <c r="L118" s="38"/>
-      <c r="M118" s="38"/>
-      <c r="N118" s="38"/>
-      <c r="O118" s="38"/>
+      <c r="J118" s="39"/>
+      <c r="K118" s="39"/>
+      <c r="L118" s="39"/>
+      <c r="M118" s="39"/>
+      <c r="N118" s="39"/>
+      <c r="O118" s="39"/>
       <c r="P118" s="1"/>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A119" s="35" t="s">
-        <v>25</v>
+      <c r="A119" s="36" t="s">
+        <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C119" s="1">
-        <v>8.1889606725674895</v>
+        <v>24482.794046813899</v>
       </c>
       <c r="D119" s="1">
-        <v>8.1889606725674895</v>
+        <v>24482.794046813899</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
       </c>
       <c r="F119" s="1">
-        <v>38.960439075121599</v>
+        <v>54.370003117736701</v>
       </c>
       <c r="G119" s="1">
-        <v>229.518131380033</v>
+        <v>850.32626657220897</v>
       </c>
       <c r="H119" s="4">
-        <v>6.3990332076812E-18</v>
+        <v>7.05414701429731E-35</v>
       </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="38" t="s">
+      <c r="J119" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K119" s="38"/>
-      <c r="L119" s="38"/>
-      <c r="M119" s="38"/>
-      <c r="N119" s="38"/>
-      <c r="O119" s="38"/>
+      <c r="K119" s="39"/>
+      <c r="L119" s="39"/>
+      <c r="M119" s="39"/>
+      <c r="N119" s="39"/>
+      <c r="O119" s="39"/>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" s="36"/>
+      <c r="A120" s="37"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="1">
-        <v>0.23039707874839899</v>
+        <v>151.803221723246</v>
       </c>
       <c r="D120" s="1">
-        <v>0.23039707874839899</v>
+        <v>151.803221723246</v>
       </c>
       <c r="E120" s="1">
         <v>1</v>
       </c>
       <c r="F120" s="1">
-        <v>4.1944106114323096</v>
+        <v>12.607670268557801</v>
       </c>
       <c r="G120" s="1">
-        <v>6.45751141129504</v>
-      </c>
-      <c r="H120" s="3">
-        <v>6.1070966449770503E-2</v>
+        <v>5.2723666479708697</v>
+      </c>
+      <c r="H120" s="2">
+        <v>3.9509565365961799E-2</v>
       </c>
       <c r="I120" s="1"/>
-      <c r="J120" s="38"/>
-      <c r="K120" s="38"/>
-      <c r="L120" s="38"/>
-      <c r="M120" s="38"/>
-      <c r="N120" s="38"/>
-      <c r="O120" s="38"/>
+      <c r="J120" s="39"/>
+      <c r="K120" s="39"/>
+      <c r="L120" s="39"/>
+      <c r="M120" s="39"/>
+      <c r="N120" s="39"/>
+      <c r="O120" s="39"/>
       <c r="P120" s="1"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" s="36"/>
+      <c r="A121" s="37"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C121" s="1">
-        <v>0.24741116524293899</v>
+        <v>191.244540460943</v>
       </c>
       <c r="D121" s="1">
-        <v>0.24741116524293899</v>
+        <v>191.244540460943</v>
       </c>
       <c r="E121" s="1">
         <v>1</v>
       </c>
       <c r="F121" s="1">
-        <v>38.960439070902197</v>
+        <v>54.370003120174303</v>
       </c>
       <c r="G121" s="1">
-        <v>6.9343779509581998</v>
+        <v>6.64222620104238</v>
       </c>
       <c r="H121" s="2">
-        <v>1.2062369794193201E-2</v>
+        <v>1.2703272318058401E-2</v>
       </c>
       <c r="I121" s="1"/>
-      <c r="J121" s="38"/>
-      <c r="K121" s="38"/>
-      <c r="L121" s="38"/>
-      <c r="M121" s="38"/>
-      <c r="N121" s="38"/>
-      <c r="O121" s="38"/>
+      <c r="J121" s="39"/>
+      <c r="K121" s="39"/>
+      <c r="L121" s="39"/>
+      <c r="M121" s="39"/>
+      <c r="N121" s="39"/>
+      <c r="O121" s="39"/>
       <c r="P121" s="1"/>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" s="37"/>
+      <c r="A122" s="38"/>
       <c r="B122" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C122" s="42"/>
-      <c r="D122" s="42"/>
-      <c r="E122" s="42"/>
-      <c r="F122" s="42"/>
-      <c r="G122" s="42"/>
-      <c r="H122" s="42"/>
+      <c r="C122" s="43"/>
+      <c r="D122" s="43"/>
+      <c r="E122" s="43"/>
+      <c r="F122" s="43"/>
+      <c r="G122" s="43"/>
+      <c r="H122" s="43"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="38"/>
-      <c r="K122" s="38"/>
-      <c r="L122" s="38"/>
-      <c r="M122" s="38"/>
-      <c r="N122" s="38"/>
-      <c r="O122" s="38"/>
+      <c r="J122" s="39"/>
+      <c r="K122" s="39"/>
+      <c r="L122" s="39"/>
+      <c r="M122" s="39"/>
+      <c r="N122" s="39"/>
+      <c r="O122" s="39"/>
       <c r="P122" s="1"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="35" t="s">
-        <v>35</v>
+      <c r="A123" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="5">
-        <v>1.2047850194397301E-5</v>
-      </c>
-      <c r="D123" s="5">
-        <v>1.2047850194397301E-5</v>
+      <c r="C123" s="1">
+        <v>8.1889606725674895</v>
+      </c>
+      <c r="D123" s="1">
+        <v>8.1889606725674895</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
       </c>
       <c r="F123" s="1">
-        <v>59.264824422698197</v>
+        <v>38.960439075121599</v>
       </c>
       <c r="G123" s="1">
-        <v>0.77970315894266595</v>
-      </c>
-      <c r="H123" s="1">
-        <v>0.38079976992345599</v>
+        <v>229.518131380033</v>
+      </c>
+      <c r="H123" s="4">
+        <v>6.3990332076812E-18</v>
       </c>
       <c r="I123" s="1"/>
-      <c r="J123" s="38" t="s">
+      <c r="J123" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K123" s="38"/>
-      <c r="L123" s="38"/>
-      <c r="M123" s="38"/>
-      <c r="N123" s="38"/>
-      <c r="O123" s="38"/>
+      <c r="K123" s="39"/>
+      <c r="L123" s="39"/>
+      <c r="M123" s="39"/>
+      <c r="N123" s="39"/>
+      <c r="O123" s="39"/>
       <c r="P123" s="1"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" s="36"/>
+      <c r="A124" s="37"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="1">
-        <v>1.70151152581477E-4</v>
+        <v>0.23039707874839899</v>
       </c>
       <c r="D124" s="1">
-        <v>1.70151152581477E-4</v>
+        <v>0.23039707874839899</v>
       </c>
       <c r="E124" s="1">
         <v>1</v>
       </c>
       <c r="F124" s="1">
-        <v>12.5741045864533</v>
+        <v>4.1944106114323096</v>
       </c>
       <c r="G124" s="1">
-        <v>11.0117065721159</v>
-      </c>
-      <c r="H124" s="2">
-        <v>5.7804446105462802E-3</v>
+        <v>6.45751141129504</v>
+      </c>
+      <c r="H124" s="3">
+        <v>6.1070966449770503E-2</v>
       </c>
       <c r="I124" s="1"/>
-      <c r="J124" s="38"/>
-      <c r="K124" s="38"/>
-      <c r="L124" s="38"/>
-      <c r="M124" s="38"/>
-      <c r="N124" s="38"/>
-      <c r="O124" s="38"/>
+      <c r="J124" s="39"/>
+      <c r="K124" s="39"/>
+      <c r="L124" s="39"/>
+      <c r="M124" s="39"/>
+      <c r="N124" s="39"/>
+      <c r="O124" s="39"/>
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="36"/>
+      <c r="A125" s="37"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="5">
-        <v>1.25476892781706E-5</v>
-      </c>
-      <c r="D125" s="5">
-        <v>1.25476892781706E-5</v>
+      <c r="C125" s="1">
+        <v>0.24741116524293899</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0.24741116524293899</v>
       </c>
       <c r="E125" s="1">
         <v>1</v>
       </c>
       <c r="F125" s="1">
-        <v>59.264824426186202</v>
+        <v>38.960439070902197</v>
       </c>
       <c r="G125" s="1">
-        <v>0.81205134607087903</v>
-      </c>
-      <c r="H125" s="1">
-        <v>0.37116202943872301</v>
+        <v>6.9343779509581998</v>
+      </c>
+      <c r="H125" s="2">
+        <v>1.2062369794193201E-2</v>
       </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="38"/>
-      <c r="K125" s="38"/>
-      <c r="L125" s="38"/>
-      <c r="M125" s="38"/>
-      <c r="N125" s="38"/>
-      <c r="O125" s="38"/>
+      <c r="J125" s="39"/>
+      <c r="K125" s="39"/>
+      <c r="L125" s="39"/>
+      <c r="M125" s="39"/>
+      <c r="N125" s="39"/>
+      <c r="O125" s="39"/>
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="37"/>
+      <c r="A126" s="38"/>
       <c r="B126" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C126" s="42"/>
-      <c r="D126" s="42"/>
-      <c r="E126" s="42"/>
-      <c r="F126" s="42"/>
-      <c r="G126" s="42"/>
-      <c r="H126" s="42"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="43"/>
+      <c r="E126" s="43"/>
+      <c r="F126" s="43"/>
+      <c r="G126" s="43"/>
+      <c r="H126" s="43"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="38"/>
-      <c r="K126" s="38"/>
-      <c r="L126" s="38"/>
-      <c r="M126" s="38"/>
-      <c r="N126" s="38"/>
-      <c r="O126" s="38"/>
+      <c r="J126" s="39"/>
+      <c r="K126" s="39"/>
+      <c r="L126" s="39"/>
+      <c r="M126" s="39"/>
+      <c r="N126" s="39"/>
+      <c r="O126" s="39"/>
       <c r="P126" s="1"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" s="35" t="s">
-        <v>36</v>
+      <c r="A127" s="36" t="s">
+        <v>35</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="1">
-        <v>0.15432652470222299</v>
-      </c>
-      <c r="D127" s="1">
-        <v>0.15432652470222299</v>
+      <c r="C127" s="5">
+        <v>1.2047850194397301E-5</v>
+      </c>
+      <c r="D127" s="5">
+        <v>1.2047850194397301E-5</v>
       </c>
       <c r="E127" s="1">
         <v>1</v>
       </c>
       <c r="F127" s="1">
-        <v>73.999999999267601</v>
+        <v>59.264824422698197</v>
       </c>
       <c r="G127" s="1">
-        <v>34.870200464865299</v>
-      </c>
-      <c r="H127" s="4">
-        <v>9.94550983787633E-8</v>
+        <v>0.77970315894266595</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0.38079976992345599</v>
       </c>
       <c r="I127" s="1"/>
-      <c r="J127" s="38" t="s">
+      <c r="J127" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K127" s="38"/>
-      <c r="L127" s="38"/>
-      <c r="M127" s="38"/>
-      <c r="N127" s="38"/>
-      <c r="O127" s="38"/>
+      <c r="K127" s="39"/>
+      <c r="L127" s="39"/>
+      <c r="M127" s="39"/>
+      <c r="N127" s="39"/>
+      <c r="O127" s="39"/>
       <c r="P127" s="1"/>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" s="36"/>
+      <c r="A128" s="37"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="1">
-        <v>0.111292819337707</v>
+        <v>1.70151152581477E-4</v>
       </c>
       <c r="D128" s="1">
-        <v>0.111292819337707</v>
+        <v>1.70151152581477E-4</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
       </c>
       <c r="F128" s="1">
-        <v>73.999999999267601</v>
+        <v>12.5741045864533</v>
       </c>
       <c r="G128" s="1">
-        <v>25.146700660135899</v>
-      </c>
-      <c r="H128" s="4">
-        <v>3.5283045440115499E-6</v>
+        <v>11.0117065721159</v>
+      </c>
+      <c r="H128" s="2">
+        <v>5.7804446105462802E-3</v>
       </c>
       <c r="I128" s="1"/>
-      <c r="J128" s="38"/>
-      <c r="K128" s="38"/>
-      <c r="L128" s="38"/>
-      <c r="M128" s="38"/>
-      <c r="N128" s="38"/>
-      <c r="O128" s="38"/>
+      <c r="J128" s="39"/>
+      <c r="K128" s="39"/>
+      <c r="L128" s="39"/>
+      <c r="M128" s="39"/>
+      <c r="N128" s="39"/>
+      <c r="O128" s="39"/>
       <c r="P128" s="1"/>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" s="36"/>
+      <c r="A129" s="37"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C129" s="1">
-        <v>7.5267632704079004E-2</v>
-      </c>
-      <c r="D129" s="1">
-        <v>7.5267632704079004E-2</v>
+      <c r="C129" s="5">
+        <v>1.25476892781706E-5</v>
+      </c>
+      <c r="D129" s="5">
+        <v>1.25476892781706E-5</v>
       </c>
       <c r="E129" s="1">
         <v>1</v>
       </c>
       <c r="F129" s="1">
-        <v>73.999999999270102</v>
+        <v>59.264824426186202</v>
       </c>
       <c r="G129" s="1">
-        <v>17.006781212570601</v>
-      </c>
-      <c r="H129" s="4">
-        <v>9.6345615419962495E-5</v>
+        <v>0.81205134607087903</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0.37116202943872301</v>
       </c>
       <c r="I129" s="1"/>
-      <c r="J129" s="38"/>
-      <c r="K129" s="38"/>
-      <c r="L129" s="38"/>
-      <c r="M129" s="38"/>
-      <c r="N129" s="38"/>
-      <c r="O129" s="38"/>
+      <c r="J129" s="39"/>
+      <c r="K129" s="39"/>
+      <c r="L129" s="39"/>
+      <c r="M129" s="39"/>
+      <c r="N129" s="39"/>
+      <c r="O129" s="39"/>
       <c r="P129" s="1"/>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" s="37"/>
+      <c r="A130" s="38"/>
       <c r="B130" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C130" s="42"/>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42"/>
-      <c r="F130" s="42"/>
-      <c r="G130" s="42"/>
-      <c r="H130" s="42"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="43"/>
+      <c r="E130" s="43"/>
+      <c r="F130" s="43"/>
+      <c r="G130" s="43"/>
+      <c r="H130" s="43"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="38"/>
-      <c r="K130" s="38"/>
-      <c r="L130" s="38"/>
-      <c r="M130" s="38"/>
-      <c r="N130" s="38"/>
-      <c r="O130" s="38"/>
+      <c r="J130" s="39"/>
+      <c r="K130" s="39"/>
+      <c r="L130" s="39"/>
+      <c r="M130" s="39"/>
+      <c r="N130" s="39"/>
+      <c r="O130" s="39"/>
       <c r="P130" s="1"/>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" s="35" t="s">
-        <v>26</v>
+      <c r="A131" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C131" s="1">
-        <v>11.0082179168385</v>
+        <v>0.15432652470222299</v>
       </c>
       <c r="D131" s="1">
-        <v>11.0082179168385</v>
+        <v>0.15432652470222299</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
       </c>
       <c r="F131" s="1">
-        <v>48.794824022977402</v>
+        <v>73.999999999267601</v>
       </c>
       <c r="G131" s="1">
-        <v>408.97170017139501</v>
+        <v>34.870200464865299</v>
       </c>
       <c r="H131" s="4">
-        <v>2.2809234413835001E-25</v>
+        <v>9.94550983787633E-8</v>
       </c>
       <c r="I131" s="1"/>
-      <c r="J131" s="38" t="s">
+      <c r="J131" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K131" s="38"/>
-      <c r="L131" s="38"/>
-      <c r="M131" s="38"/>
-      <c r="N131" s="38"/>
-      <c r="O131" s="38"/>
+      <c r="K131" s="39"/>
+      <c r="L131" s="39"/>
+      <c r="M131" s="39"/>
+      <c r="N131" s="39"/>
+      <c r="O131" s="39"/>
       <c r="P131" s="1"/>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" s="36"/>
+      <c r="A132" s="37"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="1">
-        <v>0.12480779741629899</v>
+        <v>0.111292819337707</v>
       </c>
       <c r="D132" s="1">
-        <v>0.12480779741629899</v>
+        <v>0.111292819337707</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
       </c>
       <c r="F132" s="1">
-        <v>6.2935571141001798</v>
+        <v>73.999999999267601</v>
       </c>
       <c r="G132" s="1">
-        <v>4.6367956638934302</v>
-      </c>
-      <c r="H132" s="3">
-        <v>7.2640986050278702E-2</v>
+        <v>25.146700660135899</v>
+      </c>
+      <c r="H132" s="4">
+        <v>3.5283045440115499E-6</v>
       </c>
       <c r="I132" s="1"/>
-      <c r="J132" s="38"/>
-      <c r="K132" s="38"/>
-      <c r="L132" s="38"/>
-      <c r="M132" s="38"/>
-      <c r="N132" s="38"/>
-      <c r="O132" s="38"/>
+      <c r="J132" s="39"/>
+      <c r="K132" s="39"/>
+      <c r="L132" s="39"/>
+      <c r="M132" s="39"/>
+      <c r="N132" s="39"/>
+      <c r="O132" s="39"/>
       <c r="P132" s="1"/>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" s="36"/>
+      <c r="A133" s="37"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C133" s="1">
-        <v>0.74925429491560802</v>
+        <v>7.5267632704079004E-2</v>
       </c>
       <c r="D133" s="1">
-        <v>0.74925429491560802</v>
+        <v>7.5267632704079004E-2</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
       </c>
       <c r="F133" s="1">
-        <v>48.794824017520803</v>
+        <v>73.999999999270102</v>
       </c>
       <c r="G133" s="1">
-        <v>27.8359136026586</v>
+        <v>17.006781212570601</v>
       </c>
       <c r="H133" s="4">
-        <v>3.01236497113781E-6</v>
+        <v>9.6345615419962495E-5</v>
       </c>
       <c r="I133" s="1"/>
-      <c r="J133" s="38"/>
-      <c r="K133" s="38"/>
-      <c r="L133" s="38"/>
-      <c r="M133" s="38"/>
-      <c r="N133" s="38"/>
-      <c r="O133" s="38"/>
+      <c r="J133" s="39"/>
+      <c r="K133" s="39"/>
+      <c r="L133" s="39"/>
+      <c r="M133" s="39"/>
+      <c r="N133" s="39"/>
+      <c r="O133" s="39"/>
       <c r="P133" s="1"/>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" s="37"/>
+      <c r="A134" s="38"/>
       <c r="B134" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C134" s="42"/>
-      <c r="D134" s="42"/>
-      <c r="E134" s="42"/>
-      <c r="F134" s="42"/>
-      <c r="G134" s="42"/>
-      <c r="H134" s="42"/>
+      <c r="C134" s="43"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="43"/>
+      <c r="F134" s="43"/>
+      <c r="G134" s="43"/>
+      <c r="H134" s="43"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="38"/>
-      <c r="K134" s="38"/>
-      <c r="L134" s="38"/>
-      <c r="M134" s="38"/>
-      <c r="N134" s="38"/>
-      <c r="O134" s="38"/>
+      <c r="J134" s="39"/>
+      <c r="K134" s="39"/>
+      <c r="L134" s="39"/>
+      <c r="M134" s="39"/>
+      <c r="N134" s="39"/>
+      <c r="O134" s="39"/>
       <c r="P134" s="1"/>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" s="6"/>
+      <c r="A135" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="1">
+        <v>11.0082179168385</v>
+      </c>
+      <c r="D135" s="1">
+        <v>11.0082179168385</v>
+      </c>
+      <c r="E135" s="1">
+        <v>1</v>
+      </c>
+      <c r="F135" s="1">
+        <v>48.794824022977402</v>
+      </c>
+      <c r="G135" s="1">
+        <v>408.97170017139501</v>
+      </c>
+      <c r="H135" s="4">
+        <v>2.2809234413835001E-25</v>
+      </c>
+      <c r="I135" s="1"/>
+      <c r="J135" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="K135" s="39"/>
+      <c r="L135" s="39"/>
+      <c r="M135" s="39"/>
+      <c r="N135" s="39"/>
+      <c r="O135" s="39"/>
+      <c r="P135" s="1"/>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" s="6"/>
+      <c r="A136" s="37"/>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="1">
+        <v>0.12480779741629899</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0.12480779741629899</v>
+      </c>
+      <c r="E136" s="1">
+        <v>1</v>
+      </c>
+      <c r="F136" s="1">
+        <v>6.2935571141001798</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4.6367956638934302</v>
+      </c>
+      <c r="H136" s="3">
+        <v>7.2640986050278702E-2</v>
+      </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="39"/>
+      <c r="K136" s="39"/>
+      <c r="L136" s="39"/>
+      <c r="M136" s="39"/>
+      <c r="N136" s="39"/>
+      <c r="O136" s="39"/>
+      <c r="P136" s="1"/>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A137" s="37"/>
+      <c r="B137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1">
+        <v>0.74925429491560802</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0.74925429491560802</v>
+      </c>
+      <c r="E137" s="1">
+        <v>1</v>
+      </c>
+      <c r="F137" s="1">
+        <v>48.794824017520803</v>
+      </c>
+      <c r="G137" s="1">
+        <v>27.8359136026586</v>
+      </c>
+      <c r="H137" s="4">
+        <v>3.01236497113781E-6</v>
+      </c>
+      <c r="I137" s="1"/>
+      <c r="J137" s="39"/>
+      <c r="K137" s="39"/>
+      <c r="L137" s="39"/>
+      <c r="M137" s="39"/>
+      <c r="N137" s="39"/>
+      <c r="O137" s="39"/>
+      <c r="P137" s="1"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" s="6"/>
+      <c r="A138" s="38"/>
+      <c r="B138" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C138" s="43"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="43"/>
+      <c r="F138" s="43"/>
+      <c r="G138" s="43"/>
+      <c r="H138" s="43"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="39"/>
+      <c r="K138" s="39"/>
+      <c r="L138" s="39"/>
+      <c r="M138" s="39"/>
+      <c r="N138" s="39"/>
+      <c r="O138" s="39"/>
+      <c r="P138" s="1"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A141" s="6"/>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A140" s="6"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
     </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A143" s="6"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="6"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="83">
+  <mergeCells count="86">
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C110:H110"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
     <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C70:H70"/>
-    <mergeCell ref="C78:H78"/>
-    <mergeCell ref="C47:H50"/>
-    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
     <mergeCell ref="J91:O94"/>
     <mergeCell ref="J95:O98"/>
-    <mergeCell ref="C99:H102"/>
+    <mergeCell ref="J99:O102"/>
     <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="C107:H110"/>
     <mergeCell ref="C94:H94"/>
     <mergeCell ref="C98:H98"/>
-    <mergeCell ref="J67:O70"/>
-    <mergeCell ref="C71:H74"/>
-    <mergeCell ref="J75:O78"/>
-    <mergeCell ref="C79:H82"/>
-    <mergeCell ref="J83:O86"/>
-    <mergeCell ref="C86:H86"/>
-    <mergeCell ref="J55:O58"/>
-    <mergeCell ref="C59:H62"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J59:O62"/>
     <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C67:H70"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="C34:H34"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="J111:O114"/>
+    <mergeCell ref="C46:H46"/>
     <mergeCell ref="J115:O118"/>
     <mergeCell ref="J119:O122"/>
     <mergeCell ref="J123:O126"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
     <mergeCell ref="C118:H118"/>
     <mergeCell ref="C122:H122"/>
     <mergeCell ref="C126:H126"/>
     <mergeCell ref="C130:H130"/>
-    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C134:H134"/>
     <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A3:A6"/>
@@ -6080,7 +6216,6 @@
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A15:A18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A27:A30"/>
@@ -6088,8 +6223,8 @@
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="A39:A42"/>
     <mergeCell ref="A43:A46"/>
-    <mergeCell ref="J107:O110"/>
     <mergeCell ref="A47:A50"/>
+    <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A58"/>
     <mergeCell ref="A59:A62"/>
@@ -6104,13 +6239,14 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A107:A110"/>
     <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A135:A138"/>
     <mergeCell ref="A111:A114"/>
     <mergeCell ref="A115:A118"/>
     <mergeCell ref="A119:A122"/>
     <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6164,7 +6300,7 @@
       <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="44">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6188,7 +6324,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
+      <c r="A3" s="45"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -6207,7 +6343,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="45"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -6227,7 +6363,7 @@
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="A5" s="45"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -6247,7 +6383,7 @@
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6264,7 +6400,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6282,7 +6418,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6298,7 +6434,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6317,7 +6453,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6331,7 +6467,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="44">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6359,7 +6495,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+      <c r="A12" s="45"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>81</v>
@@ -6380,7 +6516,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -6397,7 +6533,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6410,7 +6546,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6423,7 +6559,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+      <c r="A16" s="45"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6436,7 +6572,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="45"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6449,7 +6585,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -6538,7 +6674,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055498A3-AD3E-49E0-8565-96458FC406F5}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -6547,7 +6683,7 @@
     <col min="5" max="5" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.42578125" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
@@ -6575,10 +6711,13 @@
       <c r="H1" s="12" t="s">
         <v>49</v>
       </c>
+      <c r="I1" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="44">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6601,7 +6740,7 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
+      <c r="A3" s="45"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -6615,7 +6754,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="45"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="E4" s="20" t="s">
@@ -6629,7 +6768,7 @@
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="A5" s="45"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -6644,7 +6783,7 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6657,7 +6796,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6670,7 +6809,7 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6681,7 +6820,7 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6697,7 +6836,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6710,7 +6849,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="44">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6723,17 +6862,15 @@
         <v>87</v>
       </c>
       <c r="G11" s="34"/>
-      <c r="H11" s="23" t="s">
-        <v>88</v>
-      </c>
+      <c r="H11" s="23"/>
       <c r="I11" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+      <c r="A12" s="45"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="20" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="1"/>
@@ -6742,12 +6879,12 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="21" t="s">
-        <v>91</v>
+      <c r="H12" s="31" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -6758,7 +6895,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6770,7 +6907,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6782,7 +6919,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+      <c r="A16" s="45"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6792,7 +6929,7 @@
       <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="45"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6802,7 +6939,7 @@
       <c r="H17" s="26"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -6842,7 +6979,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6857,9 +6994,6 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>99</v>
-      </c>
       <c r="B30" t="s">
         <v>135</v>
       </c>
@@ -6892,6 +7026,11 @@
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -6932,22 +7071,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="39">
+      <c r="C1" s="40">
         <v>2021</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="39">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="40">
         <v>2022</v>
       </c>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="42"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6992,7 +7131,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7014,17 +7153,17 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="47" t="s">
+      <c r="I3" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="50"/>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
@@ -7044,15 +7183,15 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="52"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="53"/>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="1" t="s">
         <v>118</v>
       </c>
@@ -7072,15 +7211,15 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="52"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="53"/>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
@@ -7100,27 +7239,27 @@
         <v>0.1837454</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="55"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="56"/>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="50"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1">
         <v>1.3166119999999999</v>
@@ -7140,15 +7279,15 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1">
         <v>-0.5619845</v>
@@ -7168,15 +7307,15 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="53"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1">
         <v>-9.109356</v>
@@ -7196,15 +7335,15 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="56"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1">
         <v>-11.02596</v>
@@ -7224,7 +7363,7 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -7264,7 +7403,7 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="1" t="s">
         <v>108</v>
       </c>
@@ -7302,7 +7441,7 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="1" t="s">
         <v>109</v>
       </c>
@@ -7340,7 +7479,7 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="1" t="s">
         <v>110</v>
       </c>
@@ -7378,7 +7517,7 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -7418,7 +7557,7 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="1" t="s">
         <v>108</v>
       </c>
@@ -7456,7 +7595,7 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="1" t="s">
         <v>109</v>
       </c>
@@ -7494,7 +7633,7 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="1" t="s">
         <v>110</v>
       </c>
@@ -7532,7 +7671,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="36" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -7572,7 +7711,7 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="1" t="s">
         <v>108</v>
       </c>
@@ -7610,7 +7749,7 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="1" t="s">
         <v>109</v>
       </c>
@@ -7648,7 +7787,7 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="1" t="s">
         <v>110</v>
       </c>
@@ -7686,7 +7825,7 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -7726,7 +7865,7 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="1" t="s">
         <v>108</v>
       </c>
@@ -7764,7 +7903,7 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
@@ -7802,7 +7941,7 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="1" t="s">
         <v>110</v>
       </c>
@@ -7840,7 +7979,7 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -7882,7 +8021,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="1" t="s">
         <v>108</v>
       </c>
@@ -7922,7 +8061,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="1" t="s">
         <v>109</v>
       </c>
@@ -7962,7 +8101,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="1" t="s">
         <v>110</v>
       </c>
@@ -8002,7 +8141,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -8044,7 +8183,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
@@ -8084,7 +8223,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="1" t="s">
         <v>109</v>
       </c>
@@ -8124,7 +8263,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
+      <c r="A34" s="38"/>
       <c r="B34" s="1" t="s">
         <v>110</v>
       </c>
@@ -8164,7 +8303,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8204,7 +8343,7 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
@@ -8242,7 +8381,7 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="1" t="s">
         <v>109</v>
       </c>
@@ -8280,7 +8419,7 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
+      <c r="A38" s="38"/>
       <c r="B38" s="1" t="s">
         <v>110</v>
       </c>
@@ -8318,19 +8457,19 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="36" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1">
         <v>5.4104409999999999E-2</v>
@@ -8350,15 +8489,15 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1">
         <v>4.687269E-3</v>
@@ -8378,15 +8517,15 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1">
         <v>-0.16190650000000001</v>
@@ -8406,15 +8545,15 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1">
         <v>-0.22064059999999999</v>
@@ -8434,19 +8573,19 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="36" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1">
         <v>-1.7348269999999999E-2</v>
@@ -8466,15 +8605,15 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1">
         <v>1.2575930000000001E-2</v>
@@ -8494,15 +8633,15 @@
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1">
         <v>3.5116069999999999E-2</v>
@@ -8522,15 +8661,15 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="37"/>
+      <c r="A46" s="38"/>
       <c r="B46" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1">
         <v>6.7801109999999998E-2</v>
@@ -8550,7 +8689,7 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -8572,17 +8711,17 @@
         <v>6.5310590000000004E-6</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="I47" s="38" t="s">
+      <c r="I47" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J47" s="38"/>
-      <c r="K47" s="38"/>
-      <c r="L47" s="38"/>
-      <c r="M47" s="38"/>
+      <c r="J47" s="39"/>
+      <c r="K47" s="39"/>
+      <c r="L47" s="39"/>
+      <c r="M47" s="39"/>
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="1" t="s">
         <v>108</v>
       </c>
@@ -8602,15 +8741,15 @@
         <v>0.31967210000000001</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="38"/>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="39"/>
+      <c r="K48" s="39"/>
+      <c r="L48" s="39"/>
+      <c r="M48" s="39"/>
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
@@ -8630,15 +8769,15 @@
         <v>4.9434029999999999E-3</v>
       </c>
       <c r="H49" s="1"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
@@ -8658,15 +8797,15 @@
         <v>0.72019759999999999</v>
       </c>
       <c r="H50" s="1"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="39"/>
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="35" t="s">
+      <c r="A51" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -8688,17 +8827,17 @@
         <v>2.2222259999999999E-4</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="38" t="s">
+      <c r="I51" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J51" s="38"/>
-      <c r="K51" s="38"/>
-      <c r="L51" s="38"/>
-      <c r="M51" s="38"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="39"/>
+      <c r="M51" s="39"/>
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="1" t="s">
         <v>108</v>
       </c>
@@ -8718,15 +8857,15 @@
         <v>1.142512E-8</v>
       </c>
       <c r="H52" s="1"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
+      <c r="A53" s="37"/>
       <c r="B53" s="1" t="s">
         <v>109</v>
       </c>
@@ -8746,15 +8885,15 @@
         <v>0.17826230000000001</v>
       </c>
       <c r="H53" s="1"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39"/>
+      <c r="K53" s="39"/>
+      <c r="L53" s="39"/>
+      <c r="M53" s="39"/>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="1" t="s">
         <v>110</v>
       </c>
@@ -8774,15 +8913,15 @@
         <v>2.8002340000000001E-2</v>
       </c>
       <c r="H54" s="1"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="36" t="s">
         <v>21</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -8804,17 +8943,17 @@
         <v>3.9052140000000001E-5</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="38" t="s">
+      <c r="I55" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
+      <c r="J55" s="39"/>
+      <c r="K55" s="39"/>
+      <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
@@ -8834,15 +8973,15 @@
         <v>1.9085240000000001E-25</v>
       </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
-      <c r="L56" s="38"/>
-      <c r="M56" s="38"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="1" t="s">
         <v>109</v>
       </c>
@@ -8862,15 +9001,15 @@
         <v>1.377838E-2</v>
       </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="39"/>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="1" t="s">
         <v>110</v>
       </c>
@@ -8890,15 +9029,15 @@
         <v>0.46767300000000001</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
-      <c r="L58" s="38"/>
-      <c r="M58" s="38"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
+      <c r="L58" s="39"/>
+      <c r="M58" s="39"/>
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="35" t="s">
+      <c r="A59" s="36" t="s">
         <v>25</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -8920,17 +9059,17 @@
         <v>2.5221599999999999E-9</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="38" t="s">
+      <c r="I59" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38"/>
-      <c r="M59" s="38"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
+      <c r="A60" s="37"/>
       <c r="B60" s="1" t="s">
         <v>108</v>
       </c>
@@ -8950,15 +9089,15 @@
         <v>1.7821690000000001E-12</v>
       </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
-      <c r="L60" s="38"/>
-      <c r="M60" s="38"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
+      <c r="A61" s="37"/>
       <c r="B61" s="1" t="s">
         <v>109</v>
       </c>
@@ -8978,15 +9117,15 @@
         <v>0.46755279999999999</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="38"/>
-      <c r="L61" s="38"/>
-      <c r="M61" s="38"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="39"/>
+      <c r="M61" s="39"/>
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="37"/>
+      <c r="A62" s="38"/>
       <c r="B62" s="1" t="s">
         <v>110</v>
       </c>
@@ -9006,15 +9145,15 @@
         <v>4.1726619999999999E-2</v>
       </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="38"/>
-      <c r="M62" s="38"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -9036,17 +9175,17 @@
         <v>0.30992960000000003</v>
       </c>
       <c r="H63" s="1"/>
-      <c r="I63" s="38" t="s">
+      <c r="I63" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
-      <c r="L63" s="38"/>
-      <c r="M63" s="38"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39"/>
+      <c r="L63" s="39"/>
+      <c r="M63" s="39"/>
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="1" t="s">
         <v>108</v>
       </c>
@@ -9066,15 +9205,15 @@
         <v>5.4385229999999998E-11</v>
       </c>
       <c r="H64" s="1"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="38"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
+      <c r="L64" s="39"/>
+      <c r="M64" s="39"/>
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="1" t="s">
         <v>109</v>
       </c>
@@ -9094,15 +9233,15 @@
         <v>1.343811E-5</v>
       </c>
       <c r="H65" s="1"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
-      <c r="L65" s="38"/>
-      <c r="M65" s="38"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39"/>
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="37"/>
+      <c r="A66" s="38"/>
       <c r="B66" s="1" t="s">
         <v>110</v>
       </c>
@@ -9122,15 +9261,15 @@
         <v>0.56057069999999998</v>
       </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
-      <c r="L66" s="38"/>
-      <c r="M66" s="38"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="35" t="s">
+      <c r="A67" s="36" t="s">
         <v>26</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -9152,17 +9291,17 @@
         <v>2.974355E-8</v>
       </c>
       <c r="H67" s="1"/>
-      <c r="I67" s="38" t="s">
+      <c r="I67" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
-      <c r="L67" s="38"/>
-      <c r="M67" s="38"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
@@ -9182,15 +9321,15 @@
         <v>1.3818109999999999E-22</v>
       </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
-      <c r="L68" s="38"/>
-      <c r="M68" s="38"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
+      <c r="L68" s="39"/>
+      <c r="M68" s="39"/>
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="1" t="s">
         <v>109</v>
       </c>
@@ -9210,15 +9349,15 @@
         <v>0.18392030000000001</v>
       </c>
       <c r="H69" s="1"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
-      <c r="L69" s="38"/>
-      <c r="M69" s="38"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39"/>
+      <c r="K69" s="39"/>
+      <c r="L69" s="39"/>
+      <c r="M69" s="39"/>
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="37"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="1" t="s">
         <v>110</v>
       </c>
@@ -9238,11 +9377,11 @@
         <v>1.86768E-3</v>
       </c>
       <c r="H70" s="1"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
-      <c r="L70" s="38"/>
-      <c r="M70" s="38"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
+      <c r="L70" s="39"/>
+      <c r="M70" s="39"/>
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1004" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C39365A8-E987-4FF2-BA00-A7F54868048B}"/>
+  <xr:revisionPtr revIDLastSave="1010" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3257DA11-BD6E-4106-98BA-D5927AD34A08}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -919,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -974,6 +974,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -981,9 +984,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1025,6 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,24 +1402,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="40">
+      <c r="C1" s="41">
         <v>2021</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="40">
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="41">
         <v>2022</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1609,12 +1610,12 @@
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1640,7 +1641,7 @@
       <c r="A7" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1">
@@ -1677,7 +1678,7 @@
       <c r="N7" s="1">
         <v>1.6096699122529901</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="57">
         <v>0.20766835063809</v>
       </c>
       <c r="P7" s="1"/>
@@ -1775,12 +1776,12 @@
       <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1907,12 +1908,12 @@
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="1"/>
       <c r="J14" s="39"/>
       <c r="K14" s="39"/>
@@ -2026,12 +2027,12 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="1"/>
       <c r="J18" s="39"/>
       <c r="K18" s="39"/>
@@ -2170,7 +2171,7 @@
       <c r="N21" s="1">
         <v>3.5502596702509801</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="3">
         <v>6.2255752292747699E-2</v>
       </c>
       <c r="P21" s="1"/>
@@ -2180,12 +2181,12 @@
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2346,12 +2347,12 @@
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2512,12 +2513,12 @@
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2678,12 +2679,12 @@
       <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2844,12 +2845,12 @@
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -3010,12 +3011,12 @@
       <c r="B42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3176,12 +3177,12 @@
       <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3342,12 +3343,12 @@
       <c r="B50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3642,12 +3643,12 @@
       <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3774,12 +3775,12 @@
       <c r="B62" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="43"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
       <c r="I62" s="1"/>
       <c r="J62" s="39"/>
       <c r="K62" s="39"/>
@@ -4158,12 +4159,12 @@
       <c r="B74" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="43"/>
-      <c r="H74" s="43"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
       <c r="I74" s="1"/>
       <c r="J74" s="39"/>
       <c r="K74" s="39"/>
@@ -4410,12 +4411,12 @@
       <c r="B82" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="43"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
       <c r="I82" s="1"/>
       <c r="J82" s="39"/>
       <c r="K82" s="39"/>
@@ -4662,12 +4663,12 @@
       <c r="B90" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="43"/>
-      <c r="D90" s="43"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="43"/>
-      <c r="H90" s="43"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="40"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="40"/>
+      <c r="H90" s="40"/>
       <c r="I90" s="1"/>
       <c r="J90" s="39"/>
       <c r="K90" s="39"/>
@@ -4782,12 +4783,12 @@
       <c r="B94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="43"/>
-      <c r="D94" s="43"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="43"/>
+      <c r="C94" s="40"/>
+      <c r="D94" s="40"/>
+      <c r="E94" s="40"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="40"/>
       <c r="I94" s="1"/>
       <c r="J94" s="39"/>
       <c r="K94" s="39"/>
@@ -4902,12 +4903,12 @@
       <c r="B98" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C98" s="43"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="43"/>
-      <c r="H98" s="43"/>
+      <c r="C98" s="40"/>
+      <c r="D98" s="40"/>
+      <c r="E98" s="40"/>
+      <c r="F98" s="40"/>
+      <c r="G98" s="40"/>
+      <c r="H98" s="40"/>
       <c r="I98" s="1"/>
       <c r="J98" s="39"/>
       <c r="K98" s="39"/>
@@ -5022,12 +5023,12 @@
       <c r="B102" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C102" s="43"/>
-      <c r="D102" s="43"/>
-      <c r="E102" s="43"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="43"/>
-      <c r="H102" s="43"/>
+      <c r="C102" s="40"/>
+      <c r="D102" s="40"/>
+      <c r="E102" s="40"/>
+      <c r="F102" s="40"/>
+      <c r="G102" s="40"/>
+      <c r="H102" s="40"/>
       <c r="I102" s="1"/>
       <c r="J102" s="39"/>
       <c r="K102" s="39"/>
@@ -5068,7 +5069,7 @@
       <c r="N103" s="1">
         <v>3.3446840501390498</v>
       </c>
-      <c r="O103" s="2">
+      <c r="O103" s="3">
         <v>7.0143959578357298E-2</v>
       </c>
       <c r="P103" s="1"/>
@@ -5406,12 +5407,12 @@
       <c r="B114" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="43"/>
-      <c r="D114" s="43"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="43"/>
-      <c r="G114" s="43"/>
-      <c r="H114" s="43"/>
+      <c r="C114" s="40"/>
+      <c r="D114" s="40"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="40"/>
+      <c r="H114" s="40"/>
       <c r="I114" s="1"/>
       <c r="J114" s="39"/>
       <c r="K114" s="39"/>
@@ -5526,12 +5527,12 @@
       <c r="B118" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C118" s="43"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="43"/>
-      <c r="F118" s="43"/>
-      <c r="G118" s="43"/>
-      <c r="H118" s="43"/>
+      <c r="C118" s="40"/>
+      <c r="D118" s="40"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="40"/>
+      <c r="H118" s="40"/>
       <c r="I118" s="1"/>
       <c r="J118" s="39"/>
       <c r="K118" s="39"/>
@@ -5646,12 +5647,12 @@
       <c r="B122" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C122" s="43"/>
-      <c r="D122" s="43"/>
-      <c r="E122" s="43"/>
-      <c r="F122" s="43"/>
-      <c r="G122" s="43"/>
-      <c r="H122" s="43"/>
+      <c r="C122" s="40"/>
+      <c r="D122" s="40"/>
+      <c r="E122" s="40"/>
+      <c r="F122" s="40"/>
+      <c r="G122" s="40"/>
+      <c r="H122" s="40"/>
       <c r="I122" s="1"/>
       <c r="J122" s="39"/>
       <c r="K122" s="39"/>
@@ -5766,12 +5767,12 @@
       <c r="B126" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C126" s="43"/>
-      <c r="D126" s="43"/>
-      <c r="E126" s="43"/>
-      <c r="F126" s="43"/>
-      <c r="G126" s="43"/>
-      <c r="H126" s="43"/>
+      <c r="C126" s="40"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="40"/>
+      <c r="F126" s="40"/>
+      <c r="G126" s="40"/>
+      <c r="H126" s="40"/>
       <c r="I126" s="1"/>
       <c r="J126" s="39"/>
       <c r="K126" s="39"/>
@@ -5886,12 +5887,12 @@
       <c r="B130" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C130" s="43"/>
-      <c r="D130" s="43"/>
-      <c r="E130" s="43"/>
-      <c r="F130" s="43"/>
-      <c r="G130" s="43"/>
-      <c r="H130" s="43"/>
+      <c r="C130" s="40"/>
+      <c r="D130" s="40"/>
+      <c r="E130" s="40"/>
+      <c r="F130" s="40"/>
+      <c r="G130" s="40"/>
+      <c r="H130" s="40"/>
       <c r="I130" s="1"/>
       <c r="J130" s="39"/>
       <c r="K130" s="39"/>
@@ -6006,12 +6007,12 @@
       <c r="B134" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C134" s="43"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="43"/>
-      <c r="F134" s="43"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="43"/>
+      <c r="C134" s="40"/>
+      <c r="D134" s="40"/>
+      <c r="E134" s="40"/>
+      <c r="F134" s="40"/>
+      <c r="G134" s="40"/>
+      <c r="H134" s="40"/>
       <c r="I134" s="1"/>
       <c r="J134" s="39"/>
       <c r="K134" s="39"/>
@@ -6126,12 +6127,12 @@
       <c r="B138" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C138" s="43"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="43"/>
-      <c r="F138" s="43"/>
-      <c r="G138" s="43"/>
-      <c r="H138" s="43"/>
+      <c r="C138" s="40"/>
+      <c r="D138" s="40"/>
+      <c r="E138" s="40"/>
+      <c r="F138" s="40"/>
+      <c r="G138" s="40"/>
+      <c r="H138" s="40"/>
       <c r="I138" s="1"/>
       <c r="J138" s="39"/>
       <c r="K138" s="39"/>
@@ -6161,68 +6162,14 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -6239,14 +6186,68 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7071,22 +7072,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="40">
+      <c r="C1" s="41">
         <v>2021</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="40">
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="41">
         <v>2022</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -9404,21 +9405,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="I3:M6"/>
-    <mergeCell ref="C7:G10"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="C39:G42"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="I67:M70"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="I59:M62"/>
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="I51:M54"/>
     <mergeCell ref="A55:A58"/>
@@ -9427,12 +9419,21 @@
     <mergeCell ref="C43:G46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="I47:M50"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="I63:M66"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="I67:M70"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="C39:G42"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="I3:M6"/>
+    <mergeCell ref="C7:G10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1010" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3257DA11-BD6E-4106-98BA-D5927AD34A08}"/>
+  <xr:revisionPtr revIDLastSave="1228" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CD660A-167D-4D24-B084-C35870E3A6F4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="150">
   <si>
     <t>Experiment</t>
   </si>
@@ -495,6 +495,27 @@
   </si>
   <si>
     <t>Days Emergence to Flowering</t>
+  </si>
+  <si>
+    <t>no color = an interaction. Grey with values = no interation but ran models</t>
+  </si>
+  <si>
+    <t>leaf number at bolting</t>
+  </si>
+  <si>
+    <t>leaf number at harvest (after fruit)</t>
+  </si>
+  <si>
+    <t>Repro:Ros</t>
+  </si>
+  <si>
+    <t>1.9499-1e-4</t>
+  </si>
+  <si>
+    <t>stomatal density</t>
+  </si>
+  <si>
+    <t>below ground</t>
   </si>
 </sst>
 </file>
@@ -919,7 +940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -974,9 +995,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -984,6 +1002,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1025,7 +1046,41 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1389,39 +1444,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5A7F3D-2808-4753-A174-BBEAF62E0D16}">
   <dimension ref="A1:P146"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="9" max="9" width="24.28515625" customWidth="1"/>
-    <col min="16" max="16" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" customWidth="1"/>
+    <col min="16" max="16" width="45.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="41">
+      <c r="C1" s="40">
         <v>2021</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="41">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="40">
         <v>2022</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="43"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1469,7 +1524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
@@ -1517,7 +1572,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="37"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -1561,7 +1616,7 @@
       </c>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="37"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
@@ -1605,17 +1660,17 @@
       </c>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1637,7 +1692,7 @@
       </c>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>33</v>
       </c>
@@ -1678,12 +1733,12 @@
       <c r="N7" s="1">
         <v>1.6096699122529901</v>
       </c>
-      <c r="O7" s="57">
+      <c r="O7" s="1">
         <v>0.20766835063809</v>
       </c>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="37"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -1727,7 +1782,7 @@
       </c>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="37"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -1771,17 +1826,17 @@
       </c>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="38"/>
       <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1803,7 +1858,7 @@
       </c>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>10</v>
       </c>
@@ -1839,7 +1894,7 @@
       <c r="O11" s="39"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -1871,7 +1926,7 @@
       <c r="O12" s="39"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="37"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
@@ -1903,17 +1958,17 @@
       <c r="O13" s="39"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="1"/>
       <c r="J14" s="39"/>
       <c r="K14" s="39"/>
@@ -1923,7 +1978,7 @@
       <c r="O14" s="39"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>142</v>
       </c>
@@ -1959,7 +2014,7 @@
       <c r="O15" s="39"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="37"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -1991,7 +2046,7 @@
       <c r="O16" s="39"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="37"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
@@ -2022,17 +2077,17 @@
       <c r="O17" s="39"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="38"/>
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
       <c r="J18" s="39"/>
       <c r="K18" s="39"/>
@@ -2042,7 +2097,7 @@
       <c r="O18" s="39"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>11</v>
       </c>
@@ -2088,7 +2143,7 @@
       </c>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="11" t="s">
         <v>7</v>
@@ -2132,7 +2187,7 @@
       </c>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -2176,17 +2231,17 @@
       </c>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="38"/>
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2208,7 +2263,7 @@
       </c>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
         <v>37</v>
       </c>
@@ -2254,7 +2309,7 @@
       </c>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -2298,7 +2353,7 @@
       </c>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="37"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -2342,17 +2397,17 @@
       </c>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="38"/>
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2374,7 +2429,7 @@
       </c>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
         <v>12</v>
       </c>
@@ -2420,7 +2475,7 @@
       </c>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="37"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -2464,7 +2519,7 @@
       </c>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="37"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -2508,17 +2563,17 @@
       </c>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="38"/>
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2540,7 +2595,7 @@
       </c>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="36" t="s">
         <v>13</v>
       </c>
@@ -2586,7 +2641,7 @@
       </c>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="37"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -2630,7 +2685,7 @@
       </c>
       <c r="P32" s="1"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="37"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -2674,17 +2729,17 @@
       </c>
       <c r="P33" s="1"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="38"/>
       <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2706,7 +2761,7 @@
       </c>
       <c r="P34" s="1"/>
     </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="36" t="s">
         <v>14</v>
       </c>
@@ -2752,7 +2807,7 @@
       </c>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="37"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -2796,7 +2851,7 @@
       </c>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="37"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -2840,17 +2895,17 @@
       </c>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="38"/>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -2872,7 +2927,7 @@
       </c>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="36" t="s">
         <v>15</v>
       </c>
@@ -2918,7 +2973,7 @@
       </c>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="37"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -2962,7 +3017,7 @@
       </c>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
@@ -3006,17 +3061,17 @@
       </c>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="38"/>
       <c r="B42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3038,7 +3093,7 @@
       </c>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="36" t="s">
         <v>16</v>
       </c>
@@ -3084,7 +3139,7 @@
       </c>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="37"/>
       <c r="B44" s="1" t="s">
         <v>7</v>
@@ -3128,7 +3183,7 @@
       </c>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="37"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
@@ -3172,17 +3227,17 @@
       </c>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="38"/>
       <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3204,7 +3259,7 @@
       </c>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="36" t="s">
         <v>17</v>
       </c>
@@ -3250,7 +3305,7 @@
       </c>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="37"/>
       <c r="B48" s="10" t="s">
         <v>7</v>
@@ -3294,7 +3349,7 @@
       </c>
       <c r="P48" s="1"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="37"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
@@ -3338,17 +3393,17 @@
       </c>
       <c r="P49" s="1"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="38"/>
       <c r="B50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3370,7 +3425,7 @@
       </c>
       <c r="P50" s="1"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="36" t="s">
         <v>27</v>
       </c>
@@ -3406,7 +3461,7 @@
       </c>
       <c r="P51" s="1"/>
     </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="37"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
@@ -3438,7 +3493,7 @@
       </c>
       <c r="P52" s="1"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="37"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
@@ -3470,7 +3525,7 @@
       </c>
       <c r="P53" s="1"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="38"/>
       <c r="B54" s="1" t="s">
         <v>38</v>
@@ -3502,7 +3557,7 @@
       </c>
       <c r="P54" s="1"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>41</v>
       </c>
@@ -3550,7 +3605,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="37"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
@@ -3594,7 +3649,7 @@
       </c>
       <c r="P56" s="1"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="37"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
@@ -3638,17 +3693,17 @@
       </c>
       <c r="P57" s="1"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="38"/>
       <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3670,7 +3725,7 @@
       </c>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="36" t="s">
         <v>65</v>
       </c>
@@ -3706,7 +3761,7 @@
       <c r="O59" s="39"/>
       <c r="P59" s="1"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="37"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
@@ -3738,7 +3793,7 @@
       <c r="O60" s="39"/>
       <c r="P60" s="1"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="37"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
@@ -3770,17 +3825,17 @@
       <c r="O61" s="39"/>
       <c r="P61" s="1"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="38"/>
       <c r="B62" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="40"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="40"/>
-      <c r="F62" s="40"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="43"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="43"/>
       <c r="I62" s="1"/>
       <c r="J62" s="39"/>
       <c r="K62" s="39"/>
@@ -3790,7 +3845,7 @@
       <c r="O62" s="39"/>
       <c r="P62" s="1"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="36" t="s">
         <v>64</v>
       </c>
@@ -3826,7 +3881,7 @@
       </c>
       <c r="P63" s="1"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="37"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
@@ -3858,7 +3913,7 @@
       </c>
       <c r="P64" s="1"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="37"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
@@ -3890,7 +3945,7 @@
       </c>
       <c r="P65" s="1"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="38"/>
       <c r="B66" s="1" t="s">
         <v>38</v>
@@ -3922,7 +3977,7 @@
       </c>
       <c r="P66" s="1"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="36" t="s">
         <v>42</v>
       </c>
@@ -3958,7 +4013,7 @@
       </c>
       <c r="P67" s="1"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="37"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
@@ -3990,7 +4045,7 @@
       </c>
       <c r="P68" s="1"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="37"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
@@ -4022,7 +4077,7 @@
       </c>
       <c r="P69" s="1"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="38"/>
       <c r="B70" s="1" t="s">
         <v>38</v>
@@ -4054,7 +4109,7 @@
       </c>
       <c r="P70" s="1"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="36" t="s">
         <v>43</v>
       </c>
@@ -4090,7 +4145,7 @@
       <c r="O71" s="39"/>
       <c r="P71" s="1"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="37"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
@@ -4122,7 +4177,7 @@
       <c r="O72" s="39"/>
       <c r="P72" s="1"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="37"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
@@ -4154,17 +4209,17 @@
       <c r="O73" s="39"/>
       <c r="P73" s="1"/>
     </row>
-    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="38"/>
       <c r="B74" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C74" s="40"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="40"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="43"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
+      <c r="H74" s="43"/>
       <c r="I74" s="1"/>
       <c r="J74" s="39"/>
       <c r="K74" s="39"/>
@@ -4174,7 +4229,7 @@
       <c r="O74" s="39"/>
       <c r="P74" s="1"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="36" t="s">
         <v>18</v>
       </c>
@@ -4210,7 +4265,7 @@
       </c>
       <c r="P75" s="1"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="37"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
@@ -4242,7 +4297,7 @@
       </c>
       <c r="P76" s="1"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="37"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
@@ -4274,7 +4329,7 @@
       </c>
       <c r="P77" s="1"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="38"/>
       <c r="B78" s="1" t="s">
         <v>38</v>
@@ -4306,7 +4361,7 @@
       </c>
       <c r="P78" s="1"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="36" t="s">
         <v>19</v>
       </c>
@@ -4342,7 +4397,7 @@
       <c r="O79" s="39"/>
       <c r="P79" s="1"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="37"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
@@ -4374,7 +4429,7 @@
       <c r="O80" s="39"/>
       <c r="P80" s="1"/>
     </row>
-    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="37"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
@@ -4406,17 +4461,17 @@
       <c r="O81" s="39"/>
       <c r="P81" s="1"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="38"/>
       <c r="B82" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="40"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="43"/>
       <c r="I82" s="1"/>
       <c r="J82" s="39"/>
       <c r="K82" s="39"/>
@@ -4426,7 +4481,7 @@
       <c r="O82" s="39"/>
       <c r="P82" s="1"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="36" t="s">
         <v>39</v>
       </c>
@@ -4462,7 +4517,7 @@
       </c>
       <c r="P83" s="1"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="37"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
@@ -4494,7 +4549,7 @@
       </c>
       <c r="P84" s="1"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="37"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
@@ -4526,7 +4581,7 @@
       </c>
       <c r="P85" s="1"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="38"/>
       <c r="B86" s="1" t="s">
         <v>38</v>
@@ -4558,7 +4613,7 @@
       </c>
       <c r="P86" s="1"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="36" t="s">
         <v>40</v>
       </c>
@@ -4594,7 +4649,7 @@
       <c r="O87" s="39"/>
       <c r="P87" s="1"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="37"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
@@ -4626,7 +4681,7 @@
       <c r="O88" s="39"/>
       <c r="P88" s="1"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="37"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
@@ -4658,17 +4713,17 @@
       <c r="O89" s="39"/>
       <c r="P89" s="1"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="38"/>
       <c r="B90" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="40"/>
-      <c r="D90" s="40"/>
-      <c r="E90" s="40"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="40"/>
-      <c r="H90" s="40"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="43"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="43"/>
+      <c r="G90" s="43"/>
+      <c r="H90" s="43"/>
       <c r="I90" s="1"/>
       <c r="J90" s="39"/>
       <c r="K90" s="39"/>
@@ -4678,7 +4733,7 @@
       <c r="O90" s="39"/>
       <c r="P90" s="1"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="36" t="s">
         <v>22</v>
       </c>
@@ -4714,7 +4769,7 @@
       <c r="O91" s="39"/>
       <c r="P91" s="1"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="37"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
@@ -4746,7 +4801,7 @@
       <c r="O92" s="39"/>
       <c r="P92" s="1"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="37"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
@@ -4778,17 +4833,17 @@
       <c r="O93" s="39"/>
       <c r="P93" s="1"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="38"/>
       <c r="B94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="40"/>
-      <c r="D94" s="40"/>
-      <c r="E94" s="40"/>
-      <c r="F94" s="40"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="40"/>
+      <c r="C94" s="43"/>
+      <c r="D94" s="43"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="43"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="43"/>
       <c r="I94" s="1"/>
       <c r="J94" s="39"/>
       <c r="K94" s="39"/>
@@ -4798,7 +4853,7 @@
       <c r="O94" s="39"/>
       <c r="P94" s="1"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="36" t="s">
         <v>23</v>
       </c>
@@ -4834,7 +4889,7 @@
       <c r="O95" s="39"/>
       <c r="P95" s="1"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="37"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
@@ -4866,7 +4921,7 @@
       <c r="O96" s="39"/>
       <c r="P96" s="1"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="37"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
@@ -4898,17 +4953,17 @@
       <c r="O97" s="39"/>
       <c r="P97" s="1"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="38"/>
       <c r="B98" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C98" s="40"/>
-      <c r="D98" s="40"/>
-      <c r="E98" s="40"/>
-      <c r="F98" s="40"/>
-      <c r="G98" s="40"/>
-      <c r="H98" s="40"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="43"/>
+      <c r="E98" s="43"/>
+      <c r="F98" s="43"/>
+      <c r="G98" s="43"/>
+      <c r="H98" s="43"/>
       <c r="I98" s="1"/>
       <c r="J98" s="39"/>
       <c r="K98" s="39"/>
@@ -4918,7 +4973,7 @@
       <c r="O98" s="39"/>
       <c r="P98" s="1"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="36" t="s">
         <v>31</v>
       </c>
@@ -4954,7 +5009,7 @@
       <c r="O99" s="39"/>
       <c r="P99" s="1"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="37"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
@@ -4986,7 +5041,7 @@
       <c r="O100" s="39"/>
       <c r="P100" s="1"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="37"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
@@ -5018,17 +5073,17 @@
       <c r="O101" s="39"/>
       <c r="P101" s="1"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="38"/>
       <c r="B102" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C102" s="40"/>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="40"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="40"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="43"/>
+      <c r="E102" s="43"/>
+      <c r="F102" s="43"/>
+      <c r="G102" s="43"/>
+      <c r="H102" s="43"/>
       <c r="I102" s="1"/>
       <c r="J102" s="39"/>
       <c r="K102" s="39"/>
@@ -5038,7 +5093,7 @@
       <c r="O102" s="39"/>
       <c r="P102" s="1"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="36" t="s">
         <v>29</v>
       </c>
@@ -5074,7 +5129,7 @@
       </c>
       <c r="P103" s="1"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="37"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
@@ -5106,7 +5161,7 @@
       </c>
       <c r="P104" s="1"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="37"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
@@ -5138,7 +5193,7 @@
       </c>
       <c r="P105" s="1"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="38"/>
       <c r="B106" s="1" t="s">
         <v>38</v>
@@ -5170,7 +5225,7 @@
       </c>
       <c r="P106" s="1"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="36" t="s">
         <v>30</v>
       </c>
@@ -5206,7 +5261,7 @@
       </c>
       <c r="P107" s="1"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="37"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
@@ -5238,7 +5293,7 @@
       </c>
       <c r="P108" s="1"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="37"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
@@ -5270,7 +5325,7 @@
       </c>
       <c r="P109" s="1"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="38"/>
       <c r="B110" s="1" t="s">
         <v>38</v>
@@ -5302,7 +5357,7 @@
       </c>
       <c r="P110" s="1"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="36" t="s">
         <v>24</v>
       </c>
@@ -5338,7 +5393,7 @@
       <c r="O111" s="39"/>
       <c r="P111" s="1"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="37"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
@@ -5370,7 +5425,7 @@
       <c r="O112" s="39"/>
       <c r="P112" s="1"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="37"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
@@ -5402,17 +5457,17 @@
       <c r="O113" s="39"/>
       <c r="P113" s="1"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="38"/>
       <c r="B114" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="40"/>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-      <c r="F114" s="40"/>
-      <c r="G114" s="40"/>
-      <c r="H114" s="40"/>
+      <c r="C114" s="43"/>
+      <c r="D114" s="43"/>
+      <c r="E114" s="43"/>
+      <c r="F114" s="43"/>
+      <c r="G114" s="43"/>
+      <c r="H114" s="43"/>
       <c r="I114" s="1"/>
       <c r="J114" s="39"/>
       <c r="K114" s="39"/>
@@ -5422,7 +5477,7 @@
       <c r="O114" s="39"/>
       <c r="P114" s="1"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="36" t="s">
         <v>20</v>
       </c>
@@ -5458,7 +5513,7 @@
       <c r="O115" s="39"/>
       <c r="P115" s="1"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="37"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
@@ -5490,7 +5545,7 @@
       <c r="O116" s="39"/>
       <c r="P116" s="1"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="37"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
@@ -5522,17 +5577,17 @@
       <c r="O117" s="39"/>
       <c r="P117" s="1"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="38"/>
       <c r="B118" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C118" s="40"/>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="40"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="43"/>
+      <c r="E118" s="43"/>
+      <c r="F118" s="43"/>
+      <c r="G118" s="43"/>
+      <c r="H118" s="43"/>
       <c r="I118" s="1"/>
       <c r="J118" s="39"/>
       <c r="K118" s="39"/>
@@ -5542,7 +5597,7 @@
       <c r="O118" s="39"/>
       <c r="P118" s="1"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="36" t="s">
         <v>21</v>
       </c>
@@ -5578,7 +5633,7 @@
       <c r="O119" s="39"/>
       <c r="P119" s="1"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="37"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
@@ -5610,7 +5665,7 @@
       <c r="O120" s="39"/>
       <c r="P120" s="1"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="37"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
@@ -5642,17 +5697,17 @@
       <c r="O121" s="39"/>
       <c r="P121" s="1"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="38"/>
       <c r="B122" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C122" s="40"/>
-      <c r="D122" s="40"/>
-      <c r="E122" s="40"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="40"/>
+      <c r="C122" s="43"/>
+      <c r="D122" s="43"/>
+      <c r="E122" s="43"/>
+      <c r="F122" s="43"/>
+      <c r="G122" s="43"/>
+      <c r="H122" s="43"/>
       <c r="I122" s="1"/>
       <c r="J122" s="39"/>
       <c r="K122" s="39"/>
@@ -5662,7 +5717,7 @@
       <c r="O122" s="39"/>
       <c r="P122" s="1"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="36" t="s">
         <v>25</v>
       </c>
@@ -5698,7 +5753,7 @@
       <c r="O123" s="39"/>
       <c r="P123" s="1"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="37"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
@@ -5730,7 +5785,7 @@
       <c r="O124" s="39"/>
       <c r="P124" s="1"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="37"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
@@ -5762,17 +5817,17 @@
       <c r="O125" s="39"/>
       <c r="P125" s="1"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="38"/>
       <c r="B126" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C126" s="40"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="40"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="43"/>
+      <c r="E126" s="43"/>
+      <c r="F126" s="43"/>
+      <c r="G126" s="43"/>
+      <c r="H126" s="43"/>
       <c r="I126" s="1"/>
       <c r="J126" s="39"/>
       <c r="K126" s="39"/>
@@ -5782,7 +5837,7 @@
       <c r="O126" s="39"/>
       <c r="P126" s="1"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="36" t="s">
         <v>35</v>
       </c>
@@ -5818,7 +5873,7 @@
       <c r="O127" s="39"/>
       <c r="P127" s="1"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="37"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
@@ -5850,7 +5905,7 @@
       <c r="O128" s="39"/>
       <c r="P128" s="1"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="37"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
@@ -5882,17 +5937,17 @@
       <c r="O129" s="39"/>
       <c r="P129" s="1"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="38"/>
       <c r="B130" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C130" s="40"/>
-      <c r="D130" s="40"/>
-      <c r="E130" s="40"/>
-      <c r="F130" s="40"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="40"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="43"/>
+      <c r="E130" s="43"/>
+      <c r="F130" s="43"/>
+      <c r="G130" s="43"/>
+      <c r="H130" s="43"/>
       <c r="I130" s="1"/>
       <c r="J130" s="39"/>
       <c r="K130" s="39"/>
@@ -5902,7 +5957,7 @@
       <c r="O130" s="39"/>
       <c r="P130" s="1"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="36" t="s">
         <v>36</v>
       </c>
@@ -5938,7 +5993,7 @@
       <c r="O131" s="39"/>
       <c r="P131" s="1"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="37"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
@@ -5970,7 +6025,7 @@
       <c r="O132" s="39"/>
       <c r="P132" s="1"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="37"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
@@ -6002,17 +6057,17 @@
       <c r="O133" s="39"/>
       <c r="P133" s="1"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" s="38"/>
       <c r="B134" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C134" s="40"/>
-      <c r="D134" s="40"/>
-      <c r="E134" s="40"/>
-      <c r="F134" s="40"/>
-      <c r="G134" s="40"/>
-      <c r="H134" s="40"/>
+      <c r="C134" s="43"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="43"/>
+      <c r="F134" s="43"/>
+      <c r="G134" s="43"/>
+      <c r="H134" s="43"/>
       <c r="I134" s="1"/>
       <c r="J134" s="39"/>
       <c r="K134" s="39"/>
@@ -6022,7 +6077,7 @@
       <c r="O134" s="39"/>
       <c r="P134" s="1"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="36" t="s">
         <v>26</v>
       </c>
@@ -6058,7 +6113,7 @@
       <c r="O135" s="39"/>
       <c r="P135" s="1"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="37"/>
       <c r="B136" s="1" t="s">
         <v>7</v>
@@ -6090,7 +6145,7 @@
       <c r="O136" s="39"/>
       <c r="P136" s="1"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="37"/>
       <c r="B137" s="1" t="s">
         <v>8</v>
@@ -6122,17 +6177,17 @@
       <c r="O137" s="39"/>
       <c r="P137" s="1"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="38"/>
       <c r="B138" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C138" s="40"/>
-      <c r="D138" s="40"/>
-      <c r="E138" s="40"/>
-      <c r="F138" s="40"/>
-      <c r="G138" s="40"/>
-      <c r="H138" s="40"/>
+      <c r="C138" s="43"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="43"/>
+      <c r="F138" s="43"/>
+      <c r="G138" s="43"/>
+      <c r="H138" s="43"/>
       <c r="I138" s="1"/>
       <c r="J138" s="39"/>
       <c r="K138" s="39"/>
@@ -6142,34 +6197,88 @@
       <c r="O138" s="39"/>
       <c r="P138" s="1"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -6186,68 +6295,14 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6257,22 +6312,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B906023B-20D8-44CB-AA51-E431F089CEA5}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="24.44140625" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>44</v>
@@ -6300,7 +6355,7 @@
       </c>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="44">
         <v>2021</v>
       </c>
@@ -6324,7 +6379,7 @@
       </c>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="45"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6343,7 +6398,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="45"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6363,7 +6418,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="45"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6383,7 +6438,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="45"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6400,7 +6455,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="45"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6418,7 +6473,7 @@
       </c>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="45"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -6434,7 +6489,7 @@
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="45"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6453,7 +6508,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="46"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -6467,7 +6522,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="44">
         <v>2022</v>
       </c>
@@ -6495,7 +6550,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="45"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
@@ -6516,7 +6571,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="45"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -6533,7 +6588,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="45"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -6546,7 +6601,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="45"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -6559,7 +6614,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="45"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6572,7 +6627,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="45"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -6585,7 +6640,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="47"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -6596,47 +6651,47 @@
       <c r="H18" s="14"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -6644,22 +6699,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>105</v>
       </c>
@@ -6676,20 +6731,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055498A3-AD3E-49E0-8565-96458FC406F5}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>44</v>
@@ -6717,7 +6772,7 @@
       </c>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="44">
         <v>2021</v>
       </c>
@@ -6740,7 +6795,7 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="45"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6754,7 +6809,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="45"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6768,7 +6823,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="45"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6783,7 +6838,7 @@
       </c>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="45"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6796,7 +6851,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="45"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6809,7 +6864,7 @@
       </c>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="45"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -6820,7 +6875,7 @@
       <c r="H8" s="26"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="45"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6836,7 +6891,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="46"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -6849,7 +6904,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="44">
         <v>2022</v>
       </c>
@@ -6868,7 +6923,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="45"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
@@ -6884,7 +6939,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="45"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -6895,7 +6950,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="45"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -6907,7 +6962,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="45"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -6919,7 +6974,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="45"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6929,7 +6984,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="26"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="45"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -6939,7 +6994,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="26"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="47"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -6949,87 +7004,87 @@
       <c r="G18" s="14"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>139</v>
       </c>
@@ -7045,51 +7100,53 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDA28D4-5A8D-4B82-B1F2-D70FA6918129}">
-  <dimension ref="A1:N78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N106"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="41">
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="40">
         <v>2021</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="41">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="40">
         <v>2022</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="42"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7131,7 +7188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
@@ -7163,7 +7220,7 @@
       <c r="M3" s="50"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="37"/>
       <c r="B4" s="1" t="s">
         <v>108</v>
@@ -7191,7 +7248,7 @@
       <c r="M4" s="53"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="37"/>
       <c r="B5" s="1" t="s">
         <v>118</v>
@@ -7219,7 +7276,7 @@
       <c r="M5" s="53"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="B6" s="1" t="s">
         <v>110</v>
@@ -7247,20 +7304,28 @@
       <c r="M6" s="56"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="50"/>
+      <c r="C7" s="57">
+        <v>-0.67962469999999997</v>
+      </c>
+      <c r="D7" s="58">
+        <v>0.72532470000000004</v>
+      </c>
+      <c r="E7" s="58">
+        <v>23.402695999999999</v>
+      </c>
+      <c r="F7" s="58">
+        <v>-0.93699370000000004</v>
+      </c>
+      <c r="G7" s="59">
+        <v>0.35833147122850001</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1">
         <v>1.3166119999999999</v>
@@ -7279,16 +7344,26 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="37"/>
       <c r="B8" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
+      <c r="C8" s="60">
+        <v>-0.8024289</v>
+      </c>
+      <c r="D8" s="61">
+        <v>0.59150590000000003</v>
+      </c>
+      <c r="E8" s="61">
+        <v>37.766705999999999</v>
+      </c>
+      <c r="F8" s="61">
+        <v>-1.600039</v>
+      </c>
+      <c r="G8" s="64">
+        <v>0.11792329999999999</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1">
         <v>-0.5619845</v>
@@ -7307,16 +7382,26 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="37"/>
       <c r="B9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="53"/>
+      <c r="C9" s="60">
+        <v>-11.448639999999999</v>
+      </c>
+      <c r="D9" s="61">
+        <v>1.2781750000000001</v>
+      </c>
+      <c r="E9" s="61">
+        <v>14.82489</v>
+      </c>
+      <c r="F9" s="61">
+        <v>-8.9570209999999992</v>
+      </c>
+      <c r="G9" s="64">
+        <v>2.2889089999999999E-7</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1">
         <v>-9.109356</v>
@@ -7335,16 +7420,26 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="38"/>
       <c r="B10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="56"/>
+      <c r="C10" s="62">
+        <v>-10.27468</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.2625949999999999</v>
+      </c>
+      <c r="E10" s="63">
+        <v>13.73147</v>
+      </c>
+      <c r="F10" s="63">
+        <v>-8.1377450000000007</v>
+      </c>
+      <c r="G10" s="65">
+        <v>1.280514E-6</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1">
         <v>-11.02596</v>
@@ -7363,7 +7458,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>11</v>
       </c>
@@ -7403,7 +7498,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
       <c r="B12" s="1" t="s">
         <v>108</v>
@@ -7441,7 +7536,7 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="37"/>
       <c r="B13" s="1" t="s">
         <v>109</v>
@@ -7479,7 +7574,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
       <c r="B14" s="1" t="s">
         <v>110</v>
@@ -7517,7 +7612,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>37</v>
       </c>
@@ -7557,7 +7652,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="37"/>
       <c r="B16" s="1" t="s">
         <v>108</v>
@@ -7595,7 +7690,7 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="37"/>
       <c r="B17" s="1" t="s">
         <v>109</v>
@@ -7633,7 +7728,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="38"/>
       <c r="B18" s="1" t="s">
         <v>110</v>
@@ -7671,911 +7766,949 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="1">
-        <v>0.26141530000000002</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2.107347E-2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>22.795461</v>
-      </c>
-      <c r="F19" s="1">
-        <v>12.404952</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1.2861529999999999E-11</v>
+      <c r="C19" s="66">
+        <v>0.16267690000000001</v>
+      </c>
+      <c r="D19" s="66">
+        <v>2.342762E-2</v>
+      </c>
+      <c r="E19" s="66">
+        <v>23.465475999999999</v>
+      </c>
+      <c r="F19" s="66">
+        <v>6.9438079999999998</v>
+      </c>
+      <c r="G19" s="66">
+        <v>3.98194E-7</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="1">
-        <v>0.1080815</v>
-      </c>
-      <c r="J19" s="1">
-        <v>6.8329970000000004E-2</v>
-      </c>
-      <c r="K19" s="1">
-        <v>55.203989999999997</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1.581758</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0.11941789999999999</v>
+      <c r="I19" s="66">
+        <v>-2.5494809999999999E-4</v>
+      </c>
+      <c r="J19" s="66">
+        <v>1.9431219999999999E-4</v>
+      </c>
+      <c r="K19" s="66">
+        <v>55.507640000000002</v>
+      </c>
+      <c r="L19" s="66">
+        <v>-1.3120540000000001</v>
+      </c>
+      <c r="M19" s="66">
+        <v>0.19490214432</v>
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="1">
-        <v>0.16795750000000001</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1.305196E-2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>38.406829999999999</v>
-      </c>
-      <c r="F20" s="1">
-        <v>12.86838</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1.6708039999999999E-15</v>
+      <c r="C20" s="66">
+        <v>0.1318241</v>
+      </c>
+      <c r="D20" s="66">
+        <v>1.53215E-2</v>
+      </c>
+      <c r="E20" s="66">
+        <v>38.868819999999999</v>
+      </c>
+      <c r="F20" s="66">
+        <v>8.603866</v>
+      </c>
+      <c r="G20" s="67">
+        <v>1.5523469999999999E-10</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1">
-        <v>0.34042270000000002</v>
-      </c>
-      <c r="J20" s="1">
-        <v>7.1749140000000003E-2</v>
-      </c>
-      <c r="K20" s="1">
-        <v>54.122332999999998</v>
-      </c>
-      <c r="L20" s="1">
-        <v>4.7446250000000001</v>
-      </c>
-      <c r="M20" s="2">
-        <v>1.5661770000000001E-5</v>
+      <c r="I20" s="66">
+        <v>2.431771E-4</v>
+      </c>
+      <c r="J20" s="66">
+        <v>3.0047830000000001E-4</v>
+      </c>
+      <c r="K20" s="66">
+        <v>54.111055</v>
+      </c>
+      <c r="L20" s="66">
+        <v>0.80930000000000002</v>
+      </c>
+      <c r="M20" s="66">
+        <v>0.4218870666026</v>
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="1">
-        <v>2.4449390000000001E-2</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4.0505119999999999E-2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>15.698370000000001</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0.60361220000000004</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.55472399999999999</v>
+      <c r="C21" s="66">
+        <v>-7.6752669999999995E-2</v>
+      </c>
+      <c r="D21" s="66">
+        <v>5.0189159999999997E-2</v>
+      </c>
+      <c r="E21" s="66">
+        <v>16.372039999999998</v>
+      </c>
+      <c r="F21" s="66">
+        <v>-1.5292680000000001</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0.14528840000000001</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="1">
-        <v>-0.11951639999999999</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0.1459646</v>
-      </c>
-      <c r="K21" s="1">
-        <v>11.39526</v>
-      </c>
-      <c r="L21" s="1">
-        <v>-0.81880399999999998</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0.4296896</v>
+      <c r="I21" s="66">
+        <v>-2.3284180000000001E-3</v>
+      </c>
+      <c r="J21" s="66">
+        <v>4.9925909999999998E-4</v>
+      </c>
+      <c r="K21" s="66">
+        <v>11.371589999999999</v>
+      </c>
+      <c r="L21" s="66">
+        <v>-4.6637459999999997</v>
+      </c>
+      <c r="M21" s="66">
+        <v>6.3120474729999999E-4</v>
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="38"/>
       <c r="B22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="1">
-        <v>-2.5180310000000001E-2</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2.9583849999999998E-2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>15.65354</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-0.85115050000000003</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0.4075182</v>
+      <c r="C22" s="66">
+        <v>-6.6752569999999997E-2</v>
+      </c>
+      <c r="D22" s="66">
+        <v>3.12787E-2</v>
+      </c>
+      <c r="E22" s="66">
+        <v>14.8775</v>
+      </c>
+      <c r="F22" s="66">
+        <v>-2.1341220000000001</v>
+      </c>
+      <c r="G22" s="67">
+        <v>4.9892260000000001E-2</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="1">
-        <v>0.1035258</v>
-      </c>
-      <c r="J22" s="1">
-        <v>8.4846459999999999E-2</v>
-      </c>
-      <c r="K22" s="1">
-        <v>10.68332</v>
-      </c>
-      <c r="L22" s="1">
-        <v>1.2201550000000001</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0.2486556</v>
+      <c r="I22" s="66">
+        <v>-1.939112E-3</v>
+      </c>
+      <c r="J22" s="66">
+        <v>3.8723229999999999E-4</v>
+      </c>
+      <c r="K22" s="66">
+        <v>13.92292</v>
+      </c>
+      <c r="L22" s="66">
+        <v>-5.0076210000000003</v>
+      </c>
+      <c r="M22" s="66" t="s">
+        <v>147</v>
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C23" s="1">
-        <v>0.16815289999999999</v>
+        <v>0.26141530000000002</v>
       </c>
       <c r="D23" s="1">
-        <v>1.333603E-2</v>
+        <v>2.107347E-2</v>
       </c>
       <c r="E23" s="1">
-        <v>22.543147000000001</v>
+        <v>22.795461</v>
       </c>
       <c r="F23" s="1">
-        <v>12.608919999999999</v>
+        <v>12.404952</v>
       </c>
       <c r="G23" s="2">
-        <v>1.085642E-11</v>
+        <v>1.2861529999999999E-11</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1">
-        <v>5.9286020000000002E-2</v>
+        <v>0.1080815</v>
       </c>
       <c r="J23" s="1">
-        <v>0.1302239</v>
+        <v>6.8329970000000004E-2</v>
       </c>
       <c r="K23" s="1">
-        <v>55.180911999999999</v>
+        <v>55.203989999999997</v>
       </c>
       <c r="L23" s="1">
-        <v>0.45526230000000001</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0.65070680000000003</v>
+        <v>1.581758</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0.11941789999999999</v>
       </c>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C24" s="1">
-        <v>0.1095054</v>
+        <v>0.16795750000000001</v>
       </c>
       <c r="D24" s="1">
-        <v>7.9211479999999994E-3</v>
+        <v>1.305196E-2</v>
       </c>
       <c r="E24" s="1">
-        <v>39.579543000000001</v>
+        <v>38.406829999999999</v>
       </c>
       <c r="F24" s="1">
-        <v>13.82443</v>
+        <v>12.86838</v>
       </c>
       <c r="G24" s="2">
-        <v>9.7457139999999995E-17</v>
+        <v>1.6708039999999999E-15</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1">
-        <v>0.51176239999999995</v>
+        <v>0.34042270000000002</v>
       </c>
       <c r="J24" s="1">
-        <v>0.1491497</v>
+        <v>7.1749140000000003E-2</v>
       </c>
       <c r="K24" s="1">
-        <v>54.192520000000002</v>
+        <v>54.122332999999998</v>
       </c>
       <c r="L24" s="1">
-        <v>3.4312</v>
+        <v>4.7446250000000001</v>
       </c>
       <c r="M24" s="2">
-        <v>1.157145E-3</v>
+        <v>1.5661770000000001E-5</v>
       </c>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="37"/>
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C25" s="1">
-        <v>4.9169679999999999E-3</v>
+        <v>2.4449390000000001E-2</v>
       </c>
       <c r="D25" s="1">
-        <v>2.157123E-2</v>
+        <v>4.0505119999999999E-2</v>
       </c>
       <c r="E25" s="1">
-        <v>14.439249999999999</v>
+        <v>15.698370000000001</v>
       </c>
       <c r="F25" s="1">
-        <v>0.227941</v>
+        <v>0.60361220000000004</v>
       </c>
       <c r="G25" s="1">
-        <v>0.82288839999999996</v>
+        <v>0.55472399999999999</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1">
-        <v>-0.38848120000000003</v>
+        <v>-0.11951639999999999</v>
       </c>
       <c r="J25" s="1">
-        <v>0.30375679999999999</v>
+        <v>0.1459646</v>
       </c>
       <c r="K25" s="1">
-        <v>10.94359</v>
+        <v>11.39526</v>
       </c>
       <c r="L25" s="1">
-        <v>-1.2789219999999999</v>
+        <v>-0.81880399999999998</v>
       </c>
       <c r="M25" s="1">
-        <v>0.22737859999999999</v>
+        <v>0.4296896</v>
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="38"/>
       <c r="B26" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C26" s="1">
-        <v>-2.9254499999999999E-2</v>
+        <v>-2.5180310000000001E-2</v>
       </c>
       <c r="D26" s="1">
-        <v>1.6422550000000001E-2</v>
+        <v>2.9583849999999998E-2</v>
       </c>
       <c r="E26" s="1">
-        <v>14.43604</v>
+        <v>15.65354</v>
       </c>
       <c r="F26" s="1">
-        <v>-1.781361</v>
-      </c>
-      <c r="G26" s="3">
-        <v>9.5896949999999995E-2</v>
+        <v>-0.85115050000000003</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.4075182</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1">
-        <v>5.3543380000000002E-2</v>
+        <v>0.1035258</v>
       </c>
       <c r="J26" s="1">
-        <v>0.17968680000000001</v>
+        <v>8.4846459999999999E-2</v>
       </c>
       <c r="K26" s="1">
-        <v>11.420360000000001</v>
+        <v>10.68332</v>
       </c>
       <c r="L26" s="1">
-        <v>0.29798170000000002</v>
+        <v>1.2201550000000001</v>
       </c>
       <c r="M26" s="1">
-        <v>0.77106850000000005</v>
+        <v>0.2486556</v>
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="1">
-        <v>0.10404770000000001</v>
+        <v>0.16815289999999999</v>
       </c>
       <c r="D27" s="1">
-        <v>1.3194920000000001E-2</v>
+        <v>1.333603E-2</v>
       </c>
       <c r="E27" s="1">
-        <v>22.166536000000001</v>
+        <v>22.543147000000001</v>
       </c>
       <c r="F27" s="1">
-        <v>7.8854410000000001</v>
+        <v>12.608919999999999</v>
       </c>
       <c r="G27" s="2">
-        <v>7.1088440000000002E-8</v>
+        <v>1.085642E-11</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1">
-        <v>3.2186840000000001E-2</v>
+        <v>5.9286020000000002E-2</v>
       </c>
       <c r="J27" s="1">
-        <v>1.052636E-2</v>
+        <v>0.1302239</v>
       </c>
       <c r="K27" s="1">
-        <v>55.036504999999998</v>
+        <v>55.180911999999999</v>
       </c>
       <c r="L27" s="1">
-        <v>3.0577380000000001</v>
-      </c>
-      <c r="M27" s="2">
-        <v>3.439386E-3</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.45526230000000001</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0.65070680000000003</v>
+      </c>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="37"/>
       <c r="B28" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C28" s="1">
-        <v>3.6833039999999997E-2</v>
+        <v>0.1095054</v>
       </c>
       <c r="D28" s="1">
-        <v>8.9172230000000002E-3</v>
+        <v>7.9211479999999994E-3</v>
       </c>
       <c r="E28" s="1">
-        <v>38.799550000000004</v>
+        <v>39.579543000000001</v>
       </c>
       <c r="F28" s="1">
-        <v>4.1305500000000004</v>
+        <v>13.82443</v>
       </c>
       <c r="G28" s="2">
-        <v>1.8621800000000001E-4</v>
+        <v>9.7457139999999995E-17</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1">
-        <v>5.4472277E-2</v>
+        <v>0.51176239999999995</v>
       </c>
       <c r="J28" s="1">
-        <v>8.6164620000000001E-3</v>
+        <v>0.1491497</v>
       </c>
       <c r="K28" s="1">
-        <v>52.260210000000001</v>
+        <v>54.192520000000002</v>
       </c>
       <c r="L28" s="1">
-        <v>6.321885</v>
+        <v>3.4312</v>
       </c>
       <c r="M28" s="2">
-        <v>5.8418710000000002E-8</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.157145E-3</v>
+      </c>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="37"/>
       <c r="B29" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C29" s="1">
-        <v>0.1045321</v>
+        <v>4.9169679999999999E-3</v>
       </c>
       <c r="D29" s="1">
-        <v>8.9959949999999997E-3</v>
+        <v>2.157123E-2</v>
       </c>
       <c r="E29" s="1">
-        <v>41</v>
+        <v>14.439249999999999</v>
       </c>
       <c r="F29" s="1">
-        <v>11.61985</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1.497837E-14</v>
+        <v>0.227941</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.82288839999999996</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1">
-        <v>9.9455870000000002E-2</v>
+        <v>-0.38848120000000003</v>
       </c>
       <c r="J29" s="1">
-        <v>1.0855979999999999E-2</v>
+        <v>0.30375679999999999</v>
       </c>
       <c r="K29" s="1">
-        <v>13.36983</v>
+        <v>10.94359</v>
       </c>
       <c r="L29" s="1">
-        <v>9.1613889999999998</v>
-      </c>
-      <c r="M29" s="2">
-        <v>3.9456639999999998E-7</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-1.2789219999999999</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0.22737859999999999</v>
+      </c>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="38"/>
       <c r="B30" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C30" s="1">
-        <v>3.843543E-2</v>
+        <v>-2.9254499999999999E-2</v>
       </c>
       <c r="D30" s="1">
-        <v>1.6573709999999998E-2</v>
+        <v>1.6422550000000001E-2</v>
       </c>
       <c r="E30" s="1">
-        <v>12.793609999999999</v>
+        <v>14.43604</v>
       </c>
       <c r="F30" s="1">
-        <v>2.319061</v>
-      </c>
-      <c r="G30" s="2">
-        <v>3.7607300000000003E-2</v>
+        <v>-1.781361</v>
+      </c>
+      <c r="G30" s="3">
+        <v>9.5896949999999995E-2</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1">
-        <v>0.12323046</v>
+        <v>5.3543380000000002E-2</v>
       </c>
       <c r="J30" s="1">
-        <v>1.5396505E-2</v>
+        <v>0.17968680000000001</v>
       </c>
       <c r="K30" s="1">
-        <v>15.15973</v>
+        <v>11.420360000000001</v>
       </c>
       <c r="L30" s="1">
-        <v>8.0037950000000002</v>
-      </c>
-      <c r="M30" s="2">
-        <v>7.9669659999999998E-7</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.29798170000000002</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0.77106850000000005</v>
+      </c>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C31" s="1">
-        <v>-9.9169900000000005E-2</v>
+        <v>0.10404770000000001</v>
       </c>
       <c r="D31" s="1">
-        <v>7.6156770000000004E-3</v>
+        <v>1.3194920000000001E-2</v>
       </c>
       <c r="E31" s="1">
-        <v>24.117732</v>
+        <v>22.166536000000001</v>
       </c>
       <c r="F31" s="1">
-        <v>-13.02181</v>
+        <v>7.8854410000000001</v>
       </c>
       <c r="G31" s="2">
-        <v>2.1010249999999999E-12</v>
+        <v>7.1088440000000002E-8</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1">
-        <v>-3.4572279999999997E-2</v>
+        <v>3.2186840000000001E-2</v>
       </c>
       <c r="J31" s="1">
-        <v>8.7322029999999991E-3</v>
+        <v>1.052636E-2</v>
       </c>
       <c r="K31" s="1">
-        <v>60</v>
+        <v>55.036504999999998</v>
       </c>
       <c r="L31" s="1">
-        <v>-3.9591699999999999</v>
+        <v>3.0577380000000001</v>
       </c>
       <c r="M31" s="2">
-        <v>2.0194479999999999E-4</v>
+        <v>3.439386E-3</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="37"/>
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C32" s="1">
-        <v>-5.779488E-2</v>
+        <v>3.6833039999999997E-2</v>
       </c>
       <c r="D32" s="1">
-        <v>5.7489029999999997E-3</v>
+        <v>8.9172230000000002E-3</v>
       </c>
       <c r="E32" s="1">
-        <v>40.271169999999998</v>
+        <v>38.799550000000004</v>
       </c>
       <c r="F32" s="1">
-        <v>-10.0532</v>
+        <v>4.1305500000000004</v>
       </c>
       <c r="G32" s="2">
-        <v>1.5358250000000001E-12</v>
+        <v>1.8621800000000001E-4</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1">
-        <v>-5.8530619999999998E-2</v>
+        <v>5.4472277E-2</v>
       </c>
       <c r="J32" s="1">
-        <v>9.5787719999999993E-3</v>
+        <v>8.6164620000000001E-3</v>
       </c>
       <c r="K32" s="1">
-        <v>51.236131</v>
+        <v>52.260210000000001</v>
       </c>
       <c r="L32" s="1">
-        <v>-6.1104520000000004</v>
+        <v>6.321885</v>
       </c>
       <c r="M32" s="2">
-        <v>1.3548390000000001E-7</v>
+        <v>5.8418710000000002E-8</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="37"/>
       <c r="B33" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C33" s="1">
-        <v>-4.2352229999999998E-2</v>
+        <v>0.1045321</v>
       </c>
       <c r="D33" s="1">
-        <v>7.6791539999999997E-3</v>
+        <v>8.9959949999999997E-3</v>
       </c>
       <c r="E33" s="1">
-        <v>17.375530000000001</v>
+        <v>41</v>
       </c>
       <c r="F33" s="1">
-        <v>-5.5152200000000002</v>
+        <v>11.61985</v>
       </c>
       <c r="G33" s="2">
-        <v>3.5006389999999997E-5</v>
+        <v>1.497837E-14</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1">
-        <v>-3.2332029999999998E-2</v>
+        <v>9.9455870000000002E-2</v>
       </c>
       <c r="J33" s="1">
-        <v>1.088914E-2</v>
+        <v>1.0855979999999999E-2</v>
       </c>
       <c r="K33" s="1">
-        <v>61</v>
+        <v>13.36983</v>
       </c>
       <c r="L33" s="1">
-        <v>-2.9692001000000001</v>
+        <v>9.1613889999999998</v>
       </c>
       <c r="M33" s="2">
-        <v>4.2635360000000001E-3</v>
+        <v>3.9456639999999998E-7</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="38"/>
       <c r="B34" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="1">
-        <v>7.5999539999999999E-3</v>
+        <v>3.843543E-2</v>
       </c>
       <c r="D34" s="1">
-        <v>1.132999E-2</v>
+        <v>1.6573709999999998E-2</v>
       </c>
       <c r="E34" s="1">
-        <v>12.42445</v>
+        <v>12.793609999999999</v>
       </c>
       <c r="F34" s="1">
-        <v>0.67078190000000004</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0.51463610000000004</v>
+        <v>2.319061</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3.7607300000000003E-2</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1">
-        <v>-5.6981190000000001E-2</v>
+        <v>0.12323046</v>
       </c>
       <c r="J34" s="1">
-        <v>9.5599729999999994E-3</v>
+        <v>1.5396505E-2</v>
       </c>
       <c r="K34" s="1">
-        <v>16.19933</v>
+        <v>15.15973</v>
       </c>
       <c r="L34" s="1">
-        <v>-5.9603929999999998</v>
+        <v>8.0037950000000002</v>
       </c>
       <c r="M34" s="2">
-        <v>1.895906E-5</v>
+        <v>7.9669659999999998E-7</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C35" s="1">
-        <v>3.6476649999999999E-2</v>
+        <v>-9.9169900000000005E-2</v>
       </c>
       <c r="D35" s="1">
-        <v>5.8868899999999997E-3</v>
+        <v>7.6156770000000004E-3</v>
       </c>
       <c r="E35" s="1">
-        <v>25.09554</v>
+        <v>24.117732</v>
       </c>
       <c r="F35" s="1">
-        <v>6.1962510000000002</v>
+        <v>-13.02181</v>
       </c>
       <c r="G35" s="2">
-        <v>1.7340119999999999E-6</v>
+        <v>2.1010249999999999E-12</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1">
-        <v>5.2231909999999999E-2</v>
+        <v>-3.4572279999999997E-2</v>
       </c>
       <c r="J35" s="1">
-        <v>3.8609439999999998E-3</v>
+        <v>8.7322029999999991E-3</v>
       </c>
       <c r="K35" s="1">
-        <v>57.451040999999996</v>
+        <v>60</v>
       </c>
       <c r="L35" s="1">
-        <v>13.528280000000001</v>
+        <v>-3.9591699999999999</v>
       </c>
       <c r="M35" s="2">
-        <v>1.648921E-19</v>
-      </c>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.0194479999999999E-4</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="37"/>
       <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C36" s="1">
-        <v>2.235734E-2</v>
+        <v>-5.779488E-2</v>
       </c>
       <c r="D36" s="1">
-        <v>4.8859400000000001E-3</v>
+        <v>5.7489029999999997E-3</v>
       </c>
       <c r="E36" s="1">
-        <v>41.205199999999998</v>
+        <v>40.271169999999998</v>
       </c>
       <c r="F36" s="1">
-        <v>4.5758530000000004</v>
+        <v>-10.0532</v>
       </c>
       <c r="G36" s="2">
-        <v>4.3017260000000003E-5</v>
+        <v>1.5358250000000001E-12</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1">
-        <v>3.4868650000000001E-2</v>
+        <v>-5.8530619999999998E-2</v>
       </c>
       <c r="J36" s="1">
-        <v>4.8541469999999996E-3</v>
+        <v>9.5787719999999993E-3</v>
       </c>
       <c r="K36" s="1">
-        <v>52.909427000000001</v>
+        <v>51.236131</v>
       </c>
       <c r="L36" s="1">
-        <v>7.1832700000000003</v>
+        <v>-6.1104520000000004</v>
       </c>
       <c r="M36" s="2">
-        <v>2.3070910000000001E-9</v>
-      </c>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.3548390000000001E-7</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="37"/>
       <c r="B37" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C37" s="1">
-        <v>4.6180759999999996E-3</v>
+        <v>-4.2352229999999998E-2</v>
       </c>
       <c r="D37" s="1">
-        <v>6.2062740000000003E-3</v>
+        <v>7.6791539999999997E-3</v>
       </c>
       <c r="E37" s="1">
-        <v>9.3979540000000004</v>
+        <v>17.375530000000001</v>
       </c>
       <c r="F37" s="1">
-        <v>0.74409800000000004</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.4750103</v>
+        <v>-5.5152200000000002</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3.5006389999999997E-5</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1">
-        <v>-8.2717769999999993E-3</v>
+        <v>-3.2332029999999998E-2</v>
       </c>
       <c r="J37" s="1">
-        <v>4.5580619999999999E-3</v>
+        <v>1.088914E-2</v>
       </c>
       <c r="K37" s="1">
-        <v>11.38397</v>
+        <v>61</v>
       </c>
       <c r="L37" s="1">
-        <v>-1.8147580000000001</v>
-      </c>
-      <c r="M37" s="3">
-        <v>9.5976409999999998E-2</v>
-      </c>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-2.9692001000000001</v>
+      </c>
+      <c r="M37" s="2">
+        <v>4.2635360000000001E-3</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="38"/>
       <c r="B38" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C38" s="1">
-        <v>-8.7482029999999995E-3</v>
+        <v>7.5999539999999999E-3</v>
       </c>
       <c r="D38" s="1">
-        <v>6.7380959999999998E-3</v>
+        <v>1.132999E-2</v>
       </c>
       <c r="E38" s="1">
-        <v>11.10463</v>
+        <v>12.42445</v>
       </c>
       <c r="F38" s="1">
-        <v>-1.2983199999999999</v>
+        <v>0.67078190000000004</v>
       </c>
       <c r="G38" s="1">
-        <v>0.22049369999999999</v>
+        <v>0.51463610000000004</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1">
-        <v>-2.4618979999999999E-2</v>
+        <v>-5.6981190000000001E-2</v>
       </c>
       <c r="J38" s="1">
-        <v>6.5856999999999999E-3</v>
+        <v>9.5599729999999994E-3</v>
       </c>
       <c r="K38" s="1">
-        <v>14.47678</v>
+        <v>16.19933</v>
       </c>
       <c r="L38" s="1">
-        <v>-3.738248</v>
+        <v>-5.9603929999999998</v>
       </c>
       <c r="M38" s="2">
-        <v>2.090588E-3</v>
-      </c>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.895906E-5</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="36" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
+      <c r="C39" s="1">
+        <v>3.6476649999999999E-2</v>
+      </c>
+      <c r="D39" s="1">
+        <v>5.8868899999999997E-3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>25.09554</v>
+      </c>
+      <c r="F39" s="1">
+        <v>6.1962510000000002</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1.7340119999999999E-6</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1">
-        <v>5.4104409999999999E-2</v>
+        <v>5.2231909999999999E-2</v>
       </c>
       <c r="J39" s="1">
-        <v>1.586684E-2</v>
+        <v>3.8609439999999998E-3</v>
       </c>
       <c r="K39" s="1">
-        <v>55.294079000000004</v>
+        <v>57.451040999999996</v>
       </c>
       <c r="L39" s="1">
-        <v>3.4099050000000002</v>
+        <v>13.528280000000001</v>
       </c>
       <c r="M39" s="2">
-        <v>1.2200878E-3</v>
+        <v>1.648921E-19</v>
       </c>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="37"/>
       <c r="B40" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
+      <c r="C40" s="1">
+        <v>2.235734E-2</v>
+      </c>
+      <c r="D40" s="1">
+        <v>4.8859400000000001E-3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>41.205199999999998</v>
+      </c>
+      <c r="F40" s="1">
+        <v>4.5758530000000004</v>
+      </c>
+      <c r="G40" s="2">
+        <v>4.3017260000000003E-5</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1">
-        <v>4.687269E-3</v>
+        <v>3.4868650000000001E-2</v>
       </c>
       <c r="J40" s="1">
-        <v>1.2589380000000001E-2</v>
+        <v>4.8541469999999996E-3</v>
       </c>
       <c r="K40" s="1">
-        <v>54.088656</v>
+        <v>52.909427000000001</v>
       </c>
       <c r="L40" s="1">
-        <v>0.37231940000000002</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0.71110989999999996</v>
+        <v>7.1832700000000003</v>
+      </c>
+      <c r="M40" s="2">
+        <v>2.3070910000000001E-9</v>
       </c>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
       <c r="B41" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
+      <c r="C41" s="1">
+        <v>4.6180759999999996E-3</v>
+      </c>
+      <c r="D41" s="1">
+        <v>6.2062740000000003E-3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>9.3979540000000004</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.74409800000000004</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.4750103</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1">
-        <v>-0.16190650000000001</v>
+        <v>-8.2717769999999993E-3</v>
       </c>
       <c r="J41" s="1">
-        <v>4.2269439999999998E-2</v>
+        <v>4.5580619999999999E-3</v>
       </c>
       <c r="K41" s="1">
-        <v>12.56658</v>
+        <v>11.38397</v>
       </c>
       <c r="L41" s="1">
-        <v>-3.8303449999999999</v>
-      </c>
-      <c r="M41" s="2">
-        <v>2.2091979999999999E-3</v>
+        <v>-1.8147580000000001</v>
+      </c>
+      <c r="M41" s="3">
+        <v>9.5976409999999998E-2</v>
       </c>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="38"/>
       <c r="B42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
+      <c r="C42" s="1">
+        <v>-8.7482029999999995E-3</v>
+      </c>
+      <c r="D42" s="1">
+        <v>6.7380959999999998E-3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>11.10463</v>
+      </c>
+      <c r="F42" s="1">
+        <v>-1.2983199999999999</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.22049369999999999</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1">
-        <v>-0.22064059999999999</v>
+        <v>-2.4618979999999999E-2</v>
       </c>
       <c r="J42" s="1">
-        <v>3.0408129999999998E-2</v>
+        <v>6.5856999999999999E-3</v>
       </c>
       <c r="K42" s="1">
-        <v>12.94289</v>
+        <v>14.47678</v>
       </c>
       <c r="L42" s="1">
-        <v>-7.2559740000000001</v>
+        <v>-3.738248</v>
       </c>
       <c r="M42" s="2">
-        <v>6.5639129999999997E-6</v>
+        <v>2.090588E-3</v>
       </c>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="36" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>107</v>
@@ -8588,24 +8721,24 @@
       <c r="F43" s="39"/>
       <c r="G43" s="39"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1">
-        <v>-1.7348269999999999E-2</v>
-      </c>
-      <c r="J43" s="1">
-        <v>6.5396389999999999E-3</v>
-      </c>
-      <c r="K43" s="1">
-        <v>55.709558000000001</v>
-      </c>
-      <c r="L43" s="1">
-        <v>-2.652787</v>
-      </c>
-      <c r="M43" s="2">
-        <v>1.038058E-2</v>
+      <c r="I43" s="66">
+        <v>-1.7478199999999999E-2</v>
+      </c>
+      <c r="J43" s="66">
+        <v>7.7458099999999997E-3</v>
+      </c>
+      <c r="K43" s="66">
+        <v>56.319026999999998</v>
+      </c>
+      <c r="L43" s="66">
+        <v>-2.256472</v>
+      </c>
+      <c r="M43" s="67">
+        <v>2.2794061000000001E-2</v>
       </c>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="37"/>
       <c r="B44" s="1" t="s">
         <v>108</v>
@@ -8616,24 +8749,24 @@
       <c r="F44" s="39"/>
       <c r="G44" s="39"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1">
-        <v>1.2575930000000001E-2</v>
-      </c>
-      <c r="J44" s="1">
-        <v>7.0812319999999998E-3</v>
-      </c>
-      <c r="K44" s="1">
-        <v>54.114787999999997</v>
-      </c>
-      <c r="L44" s="1">
-        <v>1.775952</v>
-      </c>
-      <c r="M44" s="3">
-        <v>8.1363409999999997E-2</v>
+      <c r="I44" s="66">
+        <v>-2.3552070000000001E-2</v>
+      </c>
+      <c r="J44" s="66">
+        <v>6.7560479999999997E-3</v>
+      </c>
+      <c r="K44" s="66">
+        <v>54.097791000000001</v>
+      </c>
+      <c r="L44" s="66">
+        <v>-3.4860709999999999</v>
+      </c>
+      <c r="M44" s="67">
+        <v>9.8065299999999995E-4</v>
       </c>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="37"/>
       <c r="B45" s="1" t="s">
         <v>109</v>
@@ -8644,24 +8777,24 @@
       <c r="F45" s="39"/>
       <c r="G45" s="39"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1">
-        <v>3.5116069999999999E-2</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1.7176980000000001E-2</v>
-      </c>
-      <c r="K45" s="1">
-        <v>13.180910000000001</v>
-      </c>
-      <c r="L45" s="1">
-        <v>2.044368</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6.1427379999999997E-2</v>
+      <c r="I45" s="66">
+        <v>-2.6797439999999999E-2</v>
+      </c>
+      <c r="J45" s="66">
+        <v>1.099955E-2</v>
+      </c>
+      <c r="K45" s="66">
+        <v>13.570510000000001</v>
+      </c>
+      <c r="L45" s="66">
+        <v>-2.4262299999999999</v>
+      </c>
+      <c r="M45" s="67">
+        <v>2.928103E-2</v>
       </c>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="38"/>
       <c r="B46" s="1" t="s">
         <v>110</v>
@@ -8672,160 +8805,160 @@
       <c r="F46" s="39"/>
       <c r="G46" s="39"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1">
-        <v>6.7801109999999998E-2</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1.328505E-2</v>
-      </c>
-      <c r="K46" s="1">
-        <v>13.75198</v>
-      </c>
-      <c r="L46" s="1">
-        <v>5.1035659999999998</v>
-      </c>
-      <c r="M46" s="2">
-        <v>1.698402E-4</v>
+      <c r="I46" s="66">
+        <v>-3.3645590000000003E-2</v>
+      </c>
+      <c r="J46" s="66">
+        <v>1.265696E-2</v>
+      </c>
+      <c r="K46" s="66">
+        <v>13.256600000000001</v>
+      </c>
+      <c r="L46" s="66">
+        <v>-2.6582690000000002</v>
+      </c>
+      <c r="M46" s="67">
+        <v>1.943344E-2</v>
       </c>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="36" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="1">
-        <v>-0.9841491</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.17118269999999999</v>
-      </c>
-      <c r="E47" s="1">
-        <v>23.803190000000001</v>
-      </c>
-      <c r="F47" s="1">
-        <v>-5.7491139999999996</v>
-      </c>
-      <c r="G47" s="2">
-        <v>6.5310590000000004E-6</v>
-      </c>
+      <c r="C47" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
+      <c r="I47" s="66">
+        <v>-8.3753321000000006E-3</v>
+      </c>
+      <c r="J47" s="66">
+        <v>8.9984460000000002E-3</v>
+      </c>
+      <c r="K47" s="66">
+        <v>56.69021</v>
+      </c>
+      <c r="L47" s="66">
+        <v>-0.93075200000000002</v>
+      </c>
+      <c r="M47" s="67">
+        <v>0.35592869999999999</v>
+      </c>
       <c r="N47" s="1"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="37"/>
       <c r="B48" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="1">
-        <v>0.17573549999999999</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0.1739916</v>
-      </c>
-      <c r="E48" s="1">
-        <v>33.744075000000002</v>
-      </c>
-      <c r="F48" s="1">
-        <v>1.0100229999999999</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0.31967210000000001</v>
-      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
+      <c r="I48" s="66">
+        <v>6.2885479999999997E-3</v>
+      </c>
+      <c r="J48" s="66">
+        <v>1.0130220000000001E-2</v>
+      </c>
+      <c r="K48" s="66">
+        <v>54.056728</v>
+      </c>
+      <c r="L48" s="66">
+        <v>0.62077130000000003</v>
+      </c>
+      <c r="M48" s="67">
+        <v>0.53735880000000003</v>
+      </c>
       <c r="N48" s="1"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="37"/>
       <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="1">
-        <v>-1.1202160000000001</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0.33875499999999997</v>
-      </c>
-      <c r="E49" s="1">
-        <v>14.597720000000001</v>
-      </c>
-      <c r="F49" s="1">
-        <v>-3.3068610000000001</v>
-      </c>
-      <c r="G49" s="2">
-        <v>4.9434029999999999E-3</v>
-      </c>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="39"/>
-      <c r="K49" s="39"/>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
+      <c r="I49" s="66">
+        <v>-0.1092133</v>
+      </c>
+      <c r="J49" s="66">
+        <v>2.1070729999999999E-2</v>
+      </c>
+      <c r="K49" s="66">
+        <v>11.89181</v>
+      </c>
+      <c r="L49" s="66">
+        <v>-5.1831759999999996</v>
+      </c>
+      <c r="M49" s="67">
+        <v>2.34916E-4</v>
+      </c>
       <c r="N49" s="1"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="38"/>
       <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="1">
-        <v>0.14184459999999999</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.38861230000000002</v>
-      </c>
-      <c r="E50" s="1">
-        <v>15.02059</v>
-      </c>
-      <c r="F50" s="1">
-        <v>0.36500280000000002</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.72019759999999999</v>
-      </c>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="39"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
+      <c r="I50" s="66">
+        <v>-9.8989809999999998E-2</v>
+      </c>
+      <c r="J50" s="66">
+        <v>1.5884120000000002E-2</v>
+      </c>
+      <c r="K50" s="66">
+        <v>13.67961</v>
+      </c>
+      <c r="L50" s="66">
+        <v>-6.2319979999999999</v>
+      </c>
+      <c r="M50" s="67">
+        <v>2.433112E-5</v>
+      </c>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="36" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="1">
-        <v>1.6038840000000001</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.37562440000000002</v>
-      </c>
-      <c r="E51" s="1">
-        <v>26.557427000000001</v>
-      </c>
-      <c r="F51" s="1">
-        <v>4.2699150000000001</v>
-      </c>
-      <c r="G51" s="2">
-        <v>2.2222259999999999E-4</v>
+      <c r="C51" s="66">
+        <v>-4.1460160000000004</v>
+      </c>
+      <c r="D51" s="66">
+        <v>0.6769811</v>
+      </c>
+      <c r="E51" s="66">
+        <v>24.376617</v>
+      </c>
+      <c r="F51" s="66">
+        <v>-6.1242720000000004</v>
+      </c>
+      <c r="G51" s="66">
+        <v>2.350653E-6</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="39" t="s">
@@ -8837,25 +8970,25 @@
       <c r="M51" s="39"/>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="37"/>
       <c r="B52" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="1">
-        <v>2.5716009999999998</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.35089939999999997</v>
-      </c>
-      <c r="E52" s="1">
-        <v>36.412089999999999</v>
-      </c>
-      <c r="F52" s="1">
-        <v>7.3285999999999998</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1.142512E-8</v>
+      <c r="C52" s="66">
+        <v>-5.1080050000000004</v>
+      </c>
+      <c r="D52" s="66">
+        <v>0.46945019999999998</v>
+      </c>
+      <c r="E52" s="66">
+        <v>38.858649999999997</v>
+      </c>
+      <c r="F52" s="66">
+        <v>-10.88082</v>
+      </c>
+      <c r="G52" s="67">
+        <v>2.3278650000000001E-13</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="39"/>
@@ -8865,25 +8998,25 @@
       <c r="M52" s="39"/>
       <c r="N52" s="1"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="37"/>
       <c r="B53" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="1">
-        <v>0.61386540000000001</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.440166</v>
-      </c>
-      <c r="E53" s="1">
-        <v>20.222460000000002</v>
-      </c>
-      <c r="F53" s="1">
-        <v>1.3946229999999999</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.17826230000000001</v>
+      <c r="C53" s="66">
+        <v>-3.7989480000000002</v>
+      </c>
+      <c r="D53" s="66">
+        <v>1.208588</v>
+      </c>
+      <c r="E53" s="66">
+        <v>17.432320000000001</v>
+      </c>
+      <c r="F53" s="66">
+        <v>-3.143294</v>
+      </c>
+      <c r="G53" s="67">
+        <v>5.789537E-3</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="39"/>
@@ -8893,25 +9026,25 @@
       <c r="M53" s="39"/>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="38"/>
       <c r="B54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="1">
-        <v>1.3966069999999999</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.56956130000000005</v>
-      </c>
-      <c r="E54" s="1">
-        <v>13.935140000000001</v>
-      </c>
-      <c r="F54" s="1">
-        <v>2.4520749999999998</v>
-      </c>
-      <c r="G54" s="2">
-        <v>2.8002340000000001E-2</v>
+      <c r="C54" s="66">
+        <v>-4.4755320000000003</v>
+      </c>
+      <c r="D54" s="66">
+        <v>0.98680710000000005</v>
+      </c>
+      <c r="E54" s="66">
+        <v>15.62265</v>
+      </c>
+      <c r="F54" s="66">
+        <v>-4.5353669999999999</v>
+      </c>
+      <c r="G54" s="67">
+        <v>3.5774789999999998E-4</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="39"/>
@@ -8921,27 +9054,27 @@
       <c r="M54" s="39"/>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="1">
-        <v>16.64274</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1.1608540000000001</v>
-      </c>
-      <c r="E55" s="1">
-        <v>4.8165345999999998</v>
-      </c>
-      <c r="F55" s="1">
-        <v>14.33663</v>
-      </c>
-      <c r="G55" s="2">
-        <v>3.9052140000000001E-5</v>
+      <c r="C55" s="68">
+        <v>0.142703</v>
+      </c>
+      <c r="D55" s="68">
+        <v>2.4577999999999999E-2</v>
+      </c>
+      <c r="E55" s="68">
+        <v>23.670773000000001</v>
+      </c>
+      <c r="F55" s="68">
+        <v>5.5574009999999996</v>
+      </c>
+      <c r="G55" s="68">
+        <v>1.0710269999999999E-5</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="39" t="s">
@@ -8953,25 +9086,25 @@
       <c r="M55" s="39"/>
       <c r="N55" s="1"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="37"/>
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="1">
-        <v>19.986529999999998</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0.71962550000000003</v>
-      </c>
-      <c r="E56" s="1">
-        <v>35.025179999999999</v>
-      </c>
-      <c r="F56" s="1">
-        <v>27.773520000000001</v>
-      </c>
-      <c r="G56" s="2">
-        <v>1.9085240000000001E-25</v>
+      <c r="C56" s="68">
+        <v>0.10728550000000001</v>
+      </c>
+      <c r="D56" s="68">
+        <v>1.8656389999999998E-2</v>
+      </c>
+      <c r="E56" s="68">
+        <v>36.899675999999999</v>
+      </c>
+      <c r="F56" s="68">
+        <v>5.7506050000000002</v>
+      </c>
+      <c r="G56" s="68">
+        <v>1.3791302849E-6</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="39"/>
@@ -8981,25 +9114,25 @@
       <c r="M56" s="39"/>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="37"/>
       <c r="B57" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="1">
-        <v>-4.4803540000000002</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1.6178699999999999</v>
-      </c>
-      <c r="E57" s="1">
-        <v>15.836600000000001</v>
-      </c>
-      <c r="F57" s="1">
-        <v>-2.7692920000000001</v>
-      </c>
-      <c r="G57" s="2">
-        <v>1.377838E-2</v>
+      <c r="C57" s="68">
+        <v>-0.1020605</v>
+      </c>
+      <c r="D57" s="68">
+        <v>5.7317760000000002E-2</v>
+      </c>
+      <c r="E57" s="68">
+        <v>16.319230000000001</v>
+      </c>
+      <c r="F57" s="68">
+        <v>-1.7806090000000001</v>
+      </c>
+      <c r="G57" s="68">
+        <v>9.3598610230064994E-2</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="39"/>
@@ -9009,25 +9142,25 @@
       <c r="M57" s="39"/>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="38"/>
       <c r="B58" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="1">
-        <v>-0.82880399999999999</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1.112787</v>
-      </c>
-      <c r="E58" s="1">
-        <v>15.309240000000001</v>
-      </c>
-      <c r="F58" s="1">
-        <v>-0.74480009999999996</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.46767300000000001</v>
+      <c r="C58" s="68">
+        <v>-8.9823520000000004E-2</v>
+      </c>
+      <c r="D58" s="68">
+        <v>3.9384450000000001E-2</v>
+      </c>
+      <c r="E58" s="68">
+        <v>14.65358</v>
+      </c>
+      <c r="F58" s="68">
+        <v>-2.2806850000000001</v>
+      </c>
+      <c r="G58" s="69">
+        <v>3.7977520000000001E-2</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="39"/>
@@ -9037,143 +9170,143 @@
       <c r="M58" s="39"/>
       <c r="N58" s="1"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="36" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="1">
-        <v>0.28573979999999999</v>
-      </c>
-      <c r="D59" s="1">
-        <v>2.892964E-2</v>
-      </c>
-      <c r="E59" s="1">
-        <v>20.899597</v>
-      </c>
-      <c r="F59" s="1">
-        <v>9.8770609999999994</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2.5221599999999999E-9</v>
-      </c>
+      <c r="C59" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
+      <c r="I59" s="1">
+        <v>5.4104409999999999E-2</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1.586684E-2</v>
+      </c>
+      <c r="K59" s="1">
+        <v>55.294079000000004</v>
+      </c>
+      <c r="L59" s="1">
+        <v>3.4099050000000002</v>
+      </c>
+      <c r="M59" s="2">
+        <v>1.2200878E-3</v>
+      </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="37"/>
       <c r="B60" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="1">
-        <v>0.38685409999999998</v>
-      </c>
-      <c r="D60" s="1">
-        <v>2.990483E-2</v>
-      </c>
-      <c r="E60" s="1">
-        <v>24.614989999999999</v>
-      </c>
-      <c r="F60" s="1">
-        <v>12.936170000000001</v>
-      </c>
-      <c r="G60" s="2">
-        <v>1.7821690000000001E-12</v>
-      </c>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="39"/>
-      <c r="M60" s="39"/>
+      <c r="I60" s="1">
+        <v>4.687269E-3</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1.2589380000000001E-2</v>
+      </c>
+      <c r="K60" s="1">
+        <v>54.088656</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0.37231940000000002</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0.71110989999999996</v>
+      </c>
       <c r="N60" s="1"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="37"/>
       <c r="B61" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="1">
-        <v>2.0270739999999999E-2</v>
-      </c>
-      <c r="D61" s="1">
-        <v>2.7636999999999998E-2</v>
-      </c>
-      <c r="E61" s="1">
-        <v>40</v>
-      </c>
-      <c r="F61" s="1">
-        <v>0.733464</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.46755279999999999</v>
-      </c>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="39"/>
-      <c r="M61" s="39"/>
+      <c r="I61" s="1">
+        <v>-0.16190650000000001</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4.2269439999999998E-2</v>
+      </c>
+      <c r="K61" s="1">
+        <v>12.56658</v>
+      </c>
+      <c r="L61" s="1">
+        <v>-3.8303449999999999</v>
+      </c>
+      <c r="M61" s="2">
+        <v>2.2091979999999999E-3</v>
+      </c>
       <c r="N61" s="1"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="38"/>
       <c r="B62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="1">
-        <v>0.13333100000000001</v>
-      </c>
-      <c r="D62" s="1">
-        <v>5.6024570000000003E-2</v>
-      </c>
-      <c r="E62" s="1">
-        <v>8.8358460000000001</v>
-      </c>
-      <c r="F62" s="1">
-        <v>2.3798659999999998</v>
-      </c>
-      <c r="G62" s="2">
-        <v>4.1726619999999999E-2</v>
-      </c>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
       <c r="H62" s="1"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
+      <c r="I62" s="1">
+        <v>-0.22064059999999999</v>
+      </c>
+      <c r="J62" s="1">
+        <v>3.0408129999999998E-2</v>
+      </c>
+      <c r="K62" s="1">
+        <v>12.94289</v>
+      </c>
+      <c r="L62" s="1">
+        <v>-7.2559740000000001</v>
+      </c>
+      <c r="M62" s="2">
+        <v>6.5639129999999997E-6</v>
+      </c>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="36" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="1">
-        <v>1.3623919999999999E-2</v>
-      </c>
-      <c r="D63" s="1">
-        <v>1.319795E-2</v>
-      </c>
-      <c r="E63" s="1">
-        <v>31</v>
-      </c>
-      <c r="F63" s="1">
-        <v>1.032276</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.30992960000000003</v>
+      <c r="C63" s="68">
+        <v>0.2325074</v>
+      </c>
+      <c r="D63" s="68">
+        <v>1.6652759999999999E-2</v>
+      </c>
+      <c r="E63" s="68">
+        <v>25.056222999999999</v>
+      </c>
+      <c r="F63" s="68">
+        <v>13.96209</v>
+      </c>
+      <c r="G63" s="69">
+        <v>2.524047E-13</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="39" t="s">
@@ -9185,25 +9318,25 @@
       <c r="M63" s="39"/>
       <c r="N63" s="1"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="37"/>
       <c r="B64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="1">
-        <v>7.6710570000000006E-2</v>
-      </c>
-      <c r="D64" s="1">
-        <v>8.8472120000000001E-3</v>
-      </c>
-      <c r="E64" s="1">
-        <v>43</v>
-      </c>
-      <c r="F64" s="1">
-        <v>8.6705930000000002</v>
-      </c>
-      <c r="G64" s="2">
-        <v>5.4385229999999998E-11</v>
+      <c r="C64" s="68">
+        <v>0.28619260000000002</v>
+      </c>
+      <c r="D64" s="68">
+        <v>3.6218710000000001E-2</v>
+      </c>
+      <c r="E64" s="68">
+        <v>41.139429999999997</v>
+      </c>
+      <c r="F64" s="68">
+        <v>7.901789</v>
+      </c>
+      <c r="G64" s="68">
+        <v>8.8521990000000004E-10</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="39"/>
@@ -9213,25 +9346,25 @@
       <c r="M64" s="39"/>
       <c r="N64" s="1"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="37"/>
       <c r="B65" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="1">
-        <v>-6.9491259999999999E-2</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1.0221040000000001E-2</v>
-      </c>
-      <c r="E65" s="1">
-        <v>12.84778</v>
-      </c>
-      <c r="F65" s="1">
-        <v>-6.7988470000000003</v>
-      </c>
-      <c r="G65" s="2">
-        <v>1.343811E-5</v>
+      <c r="C65" s="68">
+        <v>8.0073980000000003E-2</v>
+      </c>
+      <c r="D65" s="68">
+        <v>4.5945039999999999E-2</v>
+      </c>
+      <c r="E65" s="68">
+        <v>20.778459999999999</v>
+      </c>
+      <c r="F65" s="68">
+        <v>1.742821</v>
+      </c>
+      <c r="G65" s="69">
+        <v>9.6146709999999996E-2</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="39"/>
@@ -9241,25 +9374,25 @@
       <c r="M65" s="39"/>
       <c r="N65" s="1"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="38"/>
       <c r="B66" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="1">
-        <v>-6.8129929999999998E-3</v>
-      </c>
-      <c r="D66" s="1">
-        <v>1.1591260000000001E-2</v>
-      </c>
-      <c r="E66" s="1">
-        <v>34</v>
-      </c>
-      <c r="F66" s="1">
-        <v>-0.58776980000000001</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0.56057069999999998</v>
+      <c r="C66" s="68">
+        <v>0.1221365</v>
+      </c>
+      <c r="D66" s="68">
+        <v>3.947755E-2</v>
+      </c>
+      <c r="E66" s="68">
+        <v>16.65624</v>
+      </c>
+      <c r="F66" s="68">
+        <v>3.0938219999999998</v>
+      </c>
+      <c r="G66" s="68">
+        <v>6.7150146952E-3</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="39"/>
@@ -9269,171 +9402,995 @@
       <c r="M66" s="39"/>
       <c r="N66" s="1"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="36" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C67" s="1">
-        <v>0.29603849999999998</v>
-      </c>
-      <c r="D67" s="1">
-        <v>3.2874760000000003E-2</v>
-      </c>
-      <c r="E67" s="1">
-        <v>18.839901000000001</v>
-      </c>
-      <c r="F67" s="1">
-        <v>9.0050399999999993</v>
-      </c>
-      <c r="G67" s="2">
-        <v>2.974355E-8</v>
-      </c>
+      <c r="C67" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
-      <c r="L67" s="39"/>
-      <c r="M67" s="39"/>
+      <c r="I67" s="66">
+        <v>3.8010990000000001E-3</v>
+      </c>
+      <c r="J67" s="66">
+        <v>1.2390599999999999E-3</v>
+      </c>
+      <c r="K67" s="66">
+        <v>56.226177999999997</v>
+      </c>
+      <c r="L67" s="66">
+        <v>3.0677270000000001</v>
+      </c>
+      <c r="M67" s="66">
+        <v>3.3149447299999999E-3</v>
+      </c>
       <c r="N67" s="1"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="37"/>
       <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="1">
-        <v>0.48750929999999998</v>
-      </c>
-      <c r="D68" s="1">
-        <v>2.0179229999999999E-2</v>
-      </c>
-      <c r="E68" s="1">
-        <v>33.068705000000001</v>
-      </c>
-      <c r="F68" s="1">
-        <v>24.15896</v>
-      </c>
-      <c r="G68" s="2">
-        <v>1.3818109999999999E-22</v>
-      </c>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="39"/>
-      <c r="M68" s="39"/>
+      <c r="I68" s="66">
+        <v>2.6998579999999999E-3</v>
+      </c>
+      <c r="J68" s="66">
+        <v>1.7967930000000001E-3</v>
+      </c>
+      <c r="K68" s="66">
+        <v>54.259734999999999</v>
+      </c>
+      <c r="L68" s="66">
+        <v>1.502599</v>
+      </c>
+      <c r="M68" s="66">
+        <v>0.13874061215931999</v>
+      </c>
       <c r="N68" s="1"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="37"/>
       <c r="B69" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="1">
-        <v>-4.929849E-2</v>
-      </c>
-      <c r="D69" s="1">
-        <v>3.1121630000000001E-2</v>
-      </c>
-      <c r="E69" s="1">
-        <v>4.2666779999999997</v>
-      </c>
-      <c r="F69" s="1">
-        <v>-1.5840590000000001</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.18392030000000001</v>
-      </c>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
-      <c r="L69" s="39"/>
-      <c r="M69" s="39"/>
+      <c r="I69" s="66">
+        <v>-1.146374E-2</v>
+      </c>
+      <c r="J69" s="66">
+        <v>2.9301919999999999E-3</v>
+      </c>
+      <c r="K69" s="66">
+        <v>12.84609</v>
+      </c>
+      <c r="L69" s="66">
+        <v>-3.9122840000000001</v>
+      </c>
+      <c r="M69" s="66">
+        <v>1.8229571331547E-3</v>
+      </c>
       <c r="N69" s="1"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="38"/>
       <c r="B70" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="66">
+        <v>-1.288595E-2</v>
+      </c>
+      <c r="J70" s="66">
+        <v>2.4782379999999998E-3</v>
+      </c>
+      <c r="K70" s="66">
+        <v>14.11434</v>
+      </c>
+      <c r="L70" s="66">
+        <v>-5.1996440000000002</v>
+      </c>
+      <c r="M70" s="66">
+        <v>1.3118094177569999E-4</v>
+      </c>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1">
+        <v>-1.7348269999999999E-2</v>
+      </c>
+      <c r="J71" s="1">
+        <v>6.5396389999999999E-3</v>
+      </c>
+      <c r="K71" s="1">
+        <v>55.709558000000001</v>
+      </c>
+      <c r="L71" s="1">
+        <v>-2.652787</v>
+      </c>
+      <c r="M71" s="2">
+        <v>1.038058E-2</v>
+      </c>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="37"/>
+      <c r="B72" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1">
+        <v>1.2575930000000001E-2</v>
+      </c>
+      <c r="J72" s="1">
+        <v>7.0812319999999998E-3</v>
+      </c>
+      <c r="K72" s="1">
+        <v>54.114787999999997</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1.775952</v>
+      </c>
+      <c r="M72" s="3">
+        <v>8.1363409999999997E-2</v>
+      </c>
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="37"/>
+      <c r="B73" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1">
+        <v>3.5116069999999999E-2</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1.7176980000000001E-2</v>
+      </c>
+      <c r="K73" s="1">
+        <v>13.180910000000001</v>
+      </c>
+      <c r="L73" s="1">
+        <v>2.044368</v>
+      </c>
+      <c r="M73" s="3">
+        <v>6.1427379999999997E-2</v>
+      </c>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="38"/>
+      <c r="B74" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1">
+        <v>6.7801109999999998E-2</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1.328505E-2</v>
+      </c>
+      <c r="K74" s="1">
+        <v>13.75198</v>
+      </c>
+      <c r="L74" s="1">
+        <v>5.1035659999999998</v>
+      </c>
+      <c r="M74" s="2">
+        <v>1.698402E-4</v>
+      </c>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C75" s="1">
+        <v>-0.9841491</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0.17118269999999999</v>
+      </c>
+      <c r="E75" s="1">
+        <v>23.803190000000001</v>
+      </c>
+      <c r="F75" s="1">
+        <v>-5.7491139999999996</v>
+      </c>
+      <c r="G75" s="2">
+        <v>6.5310590000000004E-6</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="M75" s="39"/>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="37"/>
+      <c r="B76" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.17573549999999999</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0.1739916</v>
+      </c>
+      <c r="E76" s="1">
+        <v>33.744075000000002</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1.0100229999999999</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.31967210000000001</v>
+      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
+      <c r="K76" s="39"/>
+      <c r="L76" s="39"/>
+      <c r="M76" s="39"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="37"/>
+      <c r="B77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" s="1">
+        <v>-1.1202160000000001</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0.33875499999999997</v>
+      </c>
+      <c r="E77" s="1">
+        <v>14.597720000000001</v>
+      </c>
+      <c r="F77" s="1">
+        <v>-3.3068610000000001</v>
+      </c>
+      <c r="G77" s="2">
+        <v>4.9434029999999999E-3</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="39"/>
+      <c r="L77" s="39"/>
+      <c r="M77" s="39"/>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="38"/>
+      <c r="B78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.14184459999999999</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0.38861230000000002</v>
+      </c>
+      <c r="E78" s="1">
+        <v>15.02059</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.36500280000000002</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.72019759999999999</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39"/>
+      <c r="K78" s="39"/>
+      <c r="L78" s="39"/>
+      <c r="M78" s="39"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1.6038840000000001</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0.37562440000000002</v>
+      </c>
+      <c r="E79" s="1">
+        <v>26.557427000000001</v>
+      </c>
+      <c r="F79" s="1">
+        <v>4.2699150000000001</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2.2222259999999999E-4</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J79" s="39"/>
+      <c r="K79" s="39"/>
+      <c r="L79" s="39"/>
+      <c r="M79" s="39"/>
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="37"/>
+      <c r="B80" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2.5716009999999998</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0.35089939999999997</v>
+      </c>
+      <c r="E80" s="1">
+        <v>36.412089999999999</v>
+      </c>
+      <c r="F80" s="1">
+        <v>7.3285999999999998</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1.142512E-8</v>
+      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
+      <c r="L80" s="39"/>
+      <c r="M80" s="39"/>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="37"/>
+      <c r="B81" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.61386540000000001</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0.440166</v>
+      </c>
+      <c r="E81" s="1">
+        <v>20.222460000000002</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1.3946229999999999</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.17826230000000001</v>
+      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="39"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="39"/>
+      <c r="M81" s="39"/>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="38"/>
+      <c r="B82" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1.3966069999999999</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0.56956130000000005</v>
+      </c>
+      <c r="E82" s="1">
+        <v>13.935140000000001</v>
+      </c>
+      <c r="F82" s="1">
+        <v>2.4520749999999998</v>
+      </c>
+      <c r="G82" s="2">
+        <v>2.8002340000000001E-2</v>
+      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
+      <c r="L82" s="39"/>
+      <c r="M82" s="39"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C83" s="1">
+        <v>16.64274</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1.1608540000000001</v>
+      </c>
+      <c r="E83" s="1">
+        <v>4.8165345999999998</v>
+      </c>
+      <c r="F83" s="1">
+        <v>14.33663</v>
+      </c>
+      <c r="G83" s="2">
+        <v>3.9052140000000001E-5</v>
+      </c>
+      <c r="H83" s="1"/>
+      <c r="I83" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J83" s="39"/>
+      <c r="K83" s="39"/>
+      <c r="L83" s="39"/>
+      <c r="M83" s="39"/>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="37"/>
+      <c r="B84" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C84" s="1">
+        <v>19.986529999999998</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0.71962550000000003</v>
+      </c>
+      <c r="E84" s="1">
+        <v>35.025179999999999</v>
+      </c>
+      <c r="F84" s="1">
+        <v>27.773520000000001</v>
+      </c>
+      <c r="G84" s="2">
+        <v>1.9085240000000001E-25</v>
+      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="39"/>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="37"/>
+      <c r="B85" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C85" s="1">
+        <v>-4.4803540000000002</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1.6178699999999999</v>
+      </c>
+      <c r="E85" s="1">
+        <v>15.836600000000001</v>
+      </c>
+      <c r="F85" s="1">
+        <v>-2.7692920000000001</v>
+      </c>
+      <c r="G85" s="2">
+        <v>1.377838E-2</v>
+      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="39"/>
+      <c r="K85" s="39"/>
+      <c r="L85" s="39"/>
+      <c r="M85" s="39"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="38"/>
+      <c r="B86" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="1">
+        <v>-0.82880399999999999</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1.112787</v>
+      </c>
+      <c r="E86" s="1">
+        <v>15.309240000000001</v>
+      </c>
+      <c r="F86" s="1">
+        <v>-0.74480009999999996</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.46767300000000001</v>
+      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="39"/>
+      <c r="J86" s="39"/>
+      <c r="K86" s="39"/>
+      <c r="L86" s="39"/>
+      <c r="M86" s="39"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0.28573979999999999</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2.892964E-2</v>
+      </c>
+      <c r="E87" s="1">
+        <v>20.899597</v>
+      </c>
+      <c r="F87" s="1">
+        <v>9.8770609999999994</v>
+      </c>
+      <c r="G87" s="2">
+        <v>2.5221599999999999E-9</v>
+      </c>
+      <c r="H87" s="1"/>
+      <c r="I87" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J87" s="39"/>
+      <c r="K87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="39"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="37"/>
+      <c r="B88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.38685409999999998</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2.990483E-2</v>
+      </c>
+      <c r="E88" s="1">
+        <v>24.614989999999999</v>
+      </c>
+      <c r="F88" s="1">
+        <v>12.936170000000001</v>
+      </c>
+      <c r="G88" s="2">
+        <v>1.7821690000000001E-12</v>
+      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="39"/>
+      <c r="J88" s="39"/>
+      <c r="K88" s="39"/>
+      <c r="L88" s="39"/>
+      <c r="M88" s="39"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="37"/>
+      <c r="B89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C89" s="1">
+        <v>2.0270739999999999E-2</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2.7636999999999998E-2</v>
+      </c>
+      <c r="E89" s="1">
+        <v>40</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0.733464</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.46755279999999999</v>
+      </c>
+      <c r="H89" s="1"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="39"/>
+      <c r="M89" s="39"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="38"/>
+      <c r="B90" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.13333100000000001</v>
+      </c>
+      <c r="D90" s="1">
+        <v>5.6024570000000003E-2</v>
+      </c>
+      <c r="E90" s="1">
+        <v>8.8358460000000001</v>
+      </c>
+      <c r="F90" s="1">
+        <v>2.3798659999999998</v>
+      </c>
+      <c r="G90" s="2">
+        <v>4.1726619999999999E-2</v>
+      </c>
+      <c r="H90" s="1"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="39"/>
+      <c r="K90" s="39"/>
+      <c r="L90" s="39"/>
+      <c r="M90" s="39"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1.3623919999999999E-2</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1.319795E-2</v>
+      </c>
+      <c r="E91" s="1">
+        <v>31</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1.032276</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0.30992960000000003</v>
+      </c>
+      <c r="H91" s="1"/>
+      <c r="I91" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J91" s="39"/>
+      <c r="K91" s="39"/>
+      <c r="L91" s="39"/>
+      <c r="M91" s="39"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="37"/>
+      <c r="B92" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="1">
+        <v>7.6710570000000006E-2</v>
+      </c>
+      <c r="D92" s="1">
+        <v>8.8472120000000001E-3</v>
+      </c>
+      <c r="E92" s="1">
+        <v>43</v>
+      </c>
+      <c r="F92" s="1">
+        <v>8.6705930000000002</v>
+      </c>
+      <c r="G92" s="2">
+        <v>5.4385229999999998E-11</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="I92" s="39"/>
+      <c r="J92" s="39"/>
+      <c r="K92" s="39"/>
+      <c r="L92" s="39"/>
+      <c r="M92" s="39"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="37"/>
+      <c r="B93" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C93" s="1">
+        <v>-6.9491259999999999E-2</v>
+      </c>
+      <c r="D93" s="1">
+        <v>1.0221040000000001E-2</v>
+      </c>
+      <c r="E93" s="1">
+        <v>12.84778</v>
+      </c>
+      <c r="F93" s="1">
+        <v>-6.7988470000000003</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1.343811E-5</v>
+      </c>
+      <c r="H93" s="1"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="39"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="38"/>
+      <c r="B94" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C94" s="1">
+        <v>-6.8129929999999998E-3</v>
+      </c>
+      <c r="D94" s="1">
+        <v>1.1591260000000001E-2</v>
+      </c>
+      <c r="E94" s="1">
+        <v>34</v>
+      </c>
+      <c r="F94" s="1">
+        <v>-0.58776980000000001</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.56057069999999998</v>
+      </c>
+      <c r="H94" s="1"/>
+      <c r="I94" s="39"/>
+      <c r="J94" s="39"/>
+      <c r="K94" s="39"/>
+      <c r="L94" s="39"/>
+      <c r="M94" s="39"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.29603849999999998</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3.2874760000000003E-2</v>
+      </c>
+      <c r="E95" s="1">
+        <v>18.839901000000001</v>
+      </c>
+      <c r="F95" s="1">
+        <v>9.0050399999999993</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2.974355E-8</v>
+      </c>
+      <c r="H95" s="1"/>
+      <c r="I95" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J95" s="39"/>
+      <c r="K95" s="39"/>
+      <c r="L95" s="39"/>
+      <c r="M95" s="39"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="37"/>
+      <c r="B96" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.48750929999999998</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2.0179229999999999E-2</v>
+      </c>
+      <c r="E96" s="1">
+        <v>33.068705000000001</v>
+      </c>
+      <c r="F96" s="1">
+        <v>24.15896</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1.3818109999999999E-22</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="39"/>
+      <c r="J96" s="39"/>
+      <c r="K96" s="39"/>
+      <c r="L96" s="39"/>
+      <c r="M96" s="39"/>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="37"/>
+      <c r="B97" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97" s="1">
+        <v>-4.929849E-2</v>
+      </c>
+      <c r="D97" s="1">
+        <v>3.1121630000000001E-2</v>
+      </c>
+      <c r="E97" s="1">
+        <v>4.2666779999999997</v>
+      </c>
+      <c r="F97" s="1">
+        <v>-1.5840590000000001</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.18392030000000001</v>
+      </c>
+      <c r="H97" s="1"/>
+      <c r="I97" s="39"/>
+      <c r="J97" s="39"/>
+      <c r="K97" s="39"/>
+      <c r="L97" s="39"/>
+      <c r="M97" s="39"/>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" s="38"/>
+      <c r="B98" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C98" s="1">
         <v>0.15619479999999999</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D98" s="1">
         <v>2.6369159999999999E-2</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E98" s="1">
         <v>5.0675150000000002</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F98" s="1">
         <v>5.9233900000000004</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G98" s="2">
         <v>1.86768E-3</v>
       </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="39"/>
-      <c r="M70" s="39"/>
-      <c r="N70" s="1"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="6"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="6"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="6"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="6"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="6"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="39"/>
+      <c r="K98" s="39"/>
+      <c r="L98" s="39"/>
+      <c r="M98" s="39"/>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" s="6"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A103" s="6"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A106" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="41">
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="C67:G70"/>
+    <mergeCell ref="I51:M54"/>
+    <mergeCell ref="I55:M58"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="I63:M66"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="I67:M70"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="I51:M54"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C43:G46"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="I47:M50"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="C39:G42"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C1:H1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="I3:M6"/>
-    <mergeCell ref="C7:G10"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="C59:G62"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C47:G50"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C43:G46"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="I79:M82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="I83:M86"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="C71:G74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="I75:M78"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1228" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CD660A-167D-4D24-B084-C35870E3A6F4}"/>
+  <xr:revisionPtr revIDLastSave="1279" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2390976E-4F24-4B7F-A5C6-375CD9B01615}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="16095" yWindow="0" windowWidth="12705" windowHeight="15600" firstSheet="2" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="152">
   <si>
     <t>Experiment</t>
   </si>
@@ -516,6 +516,12 @@
   </si>
   <si>
     <t>below ground</t>
+  </si>
+  <si>
+    <t>Avg Seed Weight</t>
+  </si>
+  <si>
+    <t>dry repro G - log - harvest</t>
   </si>
 </sst>
 </file>
@@ -983,6 +989,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1045,41 +1086,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1444,39 +1450,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5A7F3D-2808-4753-A174-BBEAF62E0D16}">
   <dimension ref="A1:P146"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" customWidth="1"/>
-    <col min="16" max="16" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" customWidth="1"/>
+    <col min="16" max="16" width="45.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="40">
+      <c r="C1" s="53">
         <v>2021</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="40">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="53">
         <v>2022</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="55"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1524,8 +1530,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1572,8 +1578,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1616,8 +1622,8 @@
       </c>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
@@ -1660,17 +1666,17 @@
       </c>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1692,8 +1698,8 @@
       </c>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="49" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -1738,8 +1744,8 @@
       </c>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1782,8 +1788,8 @@
       </c>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -1826,17 +1832,17 @@
       </c>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="51"/>
       <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1858,8 +1864,8 @@
       </c>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="49" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1884,18 +1890,18 @@
         <v>3.2053459705297903E-5</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1918,16 +1924,16 @@
         <v>2.0059373392474201E-2</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="50"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1950,36 +1956,36 @@
         <v>0.213540969734523</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2004,18 +2010,18 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="50"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -2038,16 +2044,16 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="50"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2069,36 +2075,36 @@
       <c r="H17" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="51"/>
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="49" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2143,8 +2149,8 @@
       </c>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="50"/>
       <c r="B20" s="11" t="s">
         <v>7</v>
       </c>
@@ -2187,8 +2193,8 @@
       </c>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="50"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -2231,17 +2237,17 @@
       </c>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="51"/>
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2263,8 +2269,8 @@
       </c>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2309,8 +2315,8 @@
       </c>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="50"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2353,8 +2359,8 @@
       </c>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="50"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -2397,17 +2403,17 @@
       </c>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2429,8 +2435,8 @@
       </c>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -2475,8 +2481,8 @@
       </c>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="50"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -2519,8 +2525,8 @@
       </c>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="50"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -2563,17 +2569,17 @@
       </c>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
       <c r="B30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2595,8 +2601,8 @@
       </c>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2641,8 +2647,8 @@
       </c>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="50"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -2685,8 +2691,8 @@
       </c>
       <c r="P32" s="1"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="50"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -2729,17 +2735,17 @@
       </c>
       <c r="P33" s="1"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="38"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="51"/>
       <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2761,8 +2767,8 @@
       </c>
       <c r="P34" s="1"/>
     </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="49" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2807,8 +2813,8 @@
       </c>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="50"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -2851,8 +2857,8 @@
       </c>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="50"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -2895,17 +2901,17 @@
       </c>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="51"/>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -2927,8 +2933,8 @@
       </c>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="49" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2973,8 +2979,8 @@
       </c>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="50"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -3017,8 +3023,8 @@
       </c>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="50"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -3061,17 +3067,17 @@
       </c>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="51"/>
       <c r="B42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3093,8 +3099,8 @@
       </c>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="36" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="49" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -3139,8 +3145,8 @@
       </c>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="50"/>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -3183,8 +3189,8 @@
       </c>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="50"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
@@ -3227,17 +3233,17 @@
       </c>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="38"/>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="51"/>
       <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3259,8 +3265,8 @@
       </c>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="49" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -3305,8 +3311,8 @@
       </c>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="50"/>
       <c r="B48" s="10" t="s">
         <v>7</v>
       </c>
@@ -3349,8 +3355,8 @@
       </c>
       <c r="P48" s="1"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="50"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -3393,17 +3399,17 @@
       </c>
       <c r="P49" s="1"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="51"/>
       <c r="B50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3425,21 +3431,21 @@
       </c>
       <c r="P50" s="1"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="49" t="s">
         <v>27</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
         <v>2.20343269025562E-2</v>
@@ -3461,17 +3467,17 @@
       </c>
       <c r="P51" s="1"/>
     </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="50"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
         <v>2.98483856205864E-2</v>
@@ -3493,17 +3499,17 @@
       </c>
       <c r="P52" s="1"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="50"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
         <v>1.15818782663304E-3</v>
@@ -3525,17 +3531,17 @@
       </c>
       <c r="P53" s="1"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="38"/>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="51"/>
       <c r="B54" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
         <v>2.0797141885883202E-3</v>
@@ -3557,8 +3563,8 @@
       </c>
       <c r="P54" s="1"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="49" t="s">
         <v>41</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -3605,8 +3611,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="50"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -3649,8 +3655,8 @@
       </c>
       <c r="P56" s="1"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="50"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -3693,17 +3699,17 @@
       </c>
       <c r="P57" s="1"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="38"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="51"/>
       <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3725,8 +3731,8 @@
       </c>
       <c r="P58" s="1"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="36" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3751,18 +3757,18 @@
         <v>1.61142062466842E-3</v>
       </c>
       <c r="I59" s="1"/>
-      <c r="J59" s="39" t="s">
+      <c r="J59" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="39"/>
-      <c r="O59" s="39"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
       <c r="P59" s="1"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="50"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
@@ -3785,16 +3791,16 @@
         <v>0.83160181683106904</v>
       </c>
       <c r="I60" s="1"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="39"/>
-      <c r="M60" s="39"/>
-      <c r="N60" s="39"/>
-      <c r="O60" s="39"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52"/>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
       <c r="P60" s="1"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="50"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
@@ -3817,49 +3823,49 @@
         <v>0.64170681971566501</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="39"/>
-      <c r="M61" s="39"/>
-      <c r="N61" s="39"/>
-      <c r="O61" s="39"/>
+      <c r="J61" s="52"/>
+      <c r="K61" s="52"/>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
+      <c r="N61" s="52"/>
+      <c r="O61" s="52"/>
       <c r="P61" s="1"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="38"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="51"/>
       <c r="B62" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="43"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="39"/>
-      <c r="O62" s="39"/>
+      <c r="J62" s="52"/>
+      <c r="K62" s="52"/>
+      <c r="L62" s="52"/>
+      <c r="M62" s="52"/>
+      <c r="N62" s="52"/>
+      <c r="O62" s="52"/>
       <c r="P62" s="1"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="36" t="s">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="49" t="s">
         <v>64</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
         <v>40.695777417400599</v>
@@ -3881,17 +3887,17 @@
       </c>
       <c r="P63" s="1"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="50"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="52"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="52"/>
+      <c r="H64" s="52"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
         <v>0.27305635622259</v>
@@ -3913,17 +3919,17 @@
       </c>
       <c r="P64" s="1"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="50"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
+      <c r="H65" s="52"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
         <v>3.4613576315483399</v>
@@ -3945,17 +3951,17 @@
       </c>
       <c r="P65" s="1"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="38"/>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="51"/>
       <c r="B66" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
+      <c r="H66" s="52"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
         <v>0.72850411949349603</v>
@@ -3977,21 +3983,21 @@
       </c>
       <c r="P66" s="1"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="36" t="s">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="49" t="s">
         <v>42</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="52"/>
+      <c r="G67" s="52"/>
+      <c r="H67" s="52"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
         <v>948.25120936445398</v>
@@ -4013,17 +4019,17 @@
       </c>
       <c r="P67" s="1"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="50"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="52"/>
+      <c r="F68" s="52"/>
+      <c r="G68" s="52"/>
+      <c r="H68" s="52"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
         <v>0.22870622612837599</v>
@@ -4045,17 +4051,17 @@
       </c>
       <c r="P68" s="1"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="50"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
+      <c r="H69" s="52"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>37.771893612281502</v>
@@ -4077,17 +4083,17 @@
       </c>
       <c r="P69" s="1"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="38"/>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="51"/>
       <c r="B70" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
         <v>3.9110782596565699</v>
@@ -4109,8 +4115,8 @@
       </c>
       <c r="P70" s="1"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A71" s="36" t="s">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="49" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -4135,18 +4141,18 @@
         <v>2.3819311555743102E-16</v>
       </c>
       <c r="I71" s="1"/>
-      <c r="J71" s="39" t="s">
+      <c r="J71" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="52"/>
       <c r="P71" s="1"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="50"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
@@ -4169,16 +4175,16 @@
         <v>1.0894169628446399E-3</v>
       </c>
       <c r="I72" s="1"/>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="39"/>
-      <c r="O72" s="39"/>
+      <c r="J72" s="52"/>
+      <c r="K72" s="52"/>
+      <c r="L72" s="52"/>
+      <c r="M72" s="52"/>
+      <c r="N72" s="52"/>
+      <c r="O72" s="52"/>
       <c r="P72" s="1"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="50"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
@@ -4201,49 +4207,49 @@
         <v>0.84541099798019603</v>
       </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="39"/>
-      <c r="O73" s="39"/>
+      <c r="J73" s="52"/>
+      <c r="K73" s="52"/>
+      <c r="L73" s="52"/>
+      <c r="M73" s="52"/>
+      <c r="N73" s="52"/>
+      <c r="O73" s="52"/>
       <c r="P73" s="1"/>
     </row>
-    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="38"/>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="51"/>
       <c r="B74" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="43"/>
-      <c r="H74" s="43"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="39"/>
-      <c r="N74" s="39"/>
-      <c r="O74" s="39"/>
+      <c r="J74" s="52"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="52"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="52"/>
       <c r="P74" s="1"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" s="36" t="s">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="49" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="39" t="s">
+      <c r="C75" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1">
         <v>7.7190184322692705E-4</v>
@@ -4265,17 +4271,17 @@
       </c>
       <c r="P75" s="1"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="50"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="39"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1">
         <v>0.26383928794443301</v>
@@ -4297,17 +4303,17 @@
       </c>
       <c r="P76" s="1"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="50"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1">
         <v>6.5298294112546198E-3</v>
@@ -4329,17 +4335,17 @@
       </c>
       <c r="P77" s="1"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78" s="38"/>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="51"/>
       <c r="B78" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1">
         <v>7.3489818378573097E-3</v>
@@ -4361,8 +4367,8 @@
       </c>
       <c r="P78" s="1"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A79" s="36" t="s">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -4387,18 +4393,18 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I79" s="1"/>
-      <c r="J79" s="39" t="s">
+      <c r="J79" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K79" s="39"/>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-      <c r="N79" s="39"/>
-      <c r="O79" s="39"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="52"/>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="52"/>
       <c r="P79" s="1"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="50"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
@@ -4421,16 +4427,16 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="39"/>
-      <c r="O80" s="39"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="52"/>
+      <c r="M80" s="52"/>
+      <c r="N80" s="52"/>
+      <c r="O80" s="52"/>
       <c r="P80" s="1"/>
     </row>
-    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="50"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
@@ -4453,49 +4459,49 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="39"/>
-      <c r="K81" s="39"/>
-      <c r="L81" s="39"/>
-      <c r="M81" s="39"/>
-      <c r="N81" s="39"/>
-      <c r="O81" s="39"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="52"/>
+      <c r="L81" s="52"/>
+      <c r="M81" s="52"/>
+      <c r="N81" s="52"/>
+      <c r="O81" s="52"/>
       <c r="P81" s="1"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A82" s="38"/>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="51"/>
       <c r="B82" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="43"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
-      <c r="L82" s="39"/>
-      <c r="M82" s="39"/>
-      <c r="N82" s="39"/>
-      <c r="O82" s="39"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="52"/>
+      <c r="L82" s="52"/>
+      <c r="M82" s="52"/>
+      <c r="N82" s="52"/>
+      <c r="O82" s="52"/>
       <c r="P82" s="1"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A83" s="36" t="s">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="49" t="s">
         <v>39</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="39" t="s">
+      <c r="C83" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D83" s="39"/>
-      <c r="E83" s="39"/>
-      <c r="F83" s="39"/>
-      <c r="G83" s="39"/>
-      <c r="H83" s="39"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="52"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1">
         <v>4.0252880405239402E-2</v>
@@ -4517,17 +4523,17 @@
       </c>
       <c r="P83" s="1"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="50"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39"/>
-      <c r="G84" s="39"/>
-      <c r="H84" s="39"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1">
         <v>0.42132164214255802</v>
@@ -4549,17 +4555,17 @@
       </c>
       <c r="P84" s="1"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="50"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="39"/>
-      <c r="H85" s="39"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
+      <c r="H85" s="52"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1">
         <v>7.8254362282741005E-2</v>
@@ -4581,17 +4587,17 @@
       </c>
       <c r="P85" s="1"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A86" s="38"/>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="51"/>
       <c r="B86" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="39"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39"/>
-      <c r="G86" s="39"/>
-      <c r="H86" s="39"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1">
         <v>2.6614614752845599E-3</v>
@@ -4613,8 +4619,8 @@
       </c>
       <c r="P86" s="1"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A87" s="36" t="s">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="49" t="s">
         <v>40</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -4639,18 +4645,18 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I87" s="1"/>
-      <c r="J87" s="39" t="s">
+      <c r="J87" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K87" s="39"/>
-      <c r="L87" s="39"/>
-      <c r="M87" s="39"/>
-      <c r="N87" s="39"/>
-      <c r="O87" s="39"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
       <c r="P87" s="1"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A88" s="37"/>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="50"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
@@ -4673,16 +4679,16 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I88" s="1"/>
-      <c r="J88" s="39"/>
-      <c r="K88" s="39"/>
-      <c r="L88" s="39"/>
-      <c r="M88" s="39"/>
-      <c r="N88" s="39"/>
-      <c r="O88" s="39"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="52"/>
+      <c r="L88" s="52"/>
+      <c r="M88" s="52"/>
+      <c r="N88" s="52"/>
+      <c r="O88" s="52"/>
       <c r="P88" s="1"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A89" s="37"/>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="50"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
       </c>
@@ -4705,36 +4711,36 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I89" s="1"/>
-      <c r="J89" s="39"/>
-      <c r="K89" s="39"/>
-      <c r="L89" s="39"/>
-      <c r="M89" s="39"/>
-      <c r="N89" s="39"/>
-      <c r="O89" s="39"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="52"/>
+      <c r="L89" s="52"/>
+      <c r="M89" s="52"/>
+      <c r="N89" s="52"/>
+      <c r="O89" s="52"/>
       <c r="P89" s="1"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90" s="38"/>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="51"/>
       <c r="B90" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="43"/>
-      <c r="D90" s="43"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="43"/>
-      <c r="H90" s="43"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="56"/>
+      <c r="E90" s="56"/>
+      <c r="F90" s="56"/>
+      <c r="G90" s="56"/>
+      <c r="H90" s="56"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="39"/>
-      <c r="L90" s="39"/>
-      <c r="M90" s="39"/>
-      <c r="N90" s="39"/>
-      <c r="O90" s="39"/>
+      <c r="J90" s="52"/>
+      <c r="K90" s="52"/>
+      <c r="L90" s="52"/>
+      <c r="M90" s="52"/>
+      <c r="N90" s="52"/>
+      <c r="O90" s="52"/>
       <c r="P90" s="1"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A91" s="36" t="s">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="49" t="s">
         <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -4759,18 +4765,18 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I91" s="1"/>
-      <c r="J91" s="39" t="s">
+      <c r="J91" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K91" s="39"/>
-      <c r="L91" s="39"/>
-      <c r="M91" s="39"/>
-      <c r="N91" s="39"/>
-      <c r="O91" s="39"/>
+      <c r="K91" s="52"/>
+      <c r="L91" s="52"/>
+      <c r="M91" s="52"/>
+      <c r="N91" s="52"/>
+      <c r="O91" s="52"/>
       <c r="P91" s="1"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92" s="37"/>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="50"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
@@ -4793,16 +4799,16 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="39"/>
-      <c r="L92" s="39"/>
-      <c r="M92" s="39"/>
-      <c r="N92" s="39"/>
-      <c r="O92" s="39"/>
+      <c r="J92" s="52"/>
+      <c r="K92" s="52"/>
+      <c r="L92" s="52"/>
+      <c r="M92" s="52"/>
+      <c r="N92" s="52"/>
+      <c r="O92" s="52"/>
       <c r="P92" s="1"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A93" s="37"/>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="50"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
@@ -4825,36 +4831,36 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I93" s="1"/>
-      <c r="J93" s="39"/>
-      <c r="K93" s="39"/>
-      <c r="L93" s="39"/>
-      <c r="M93" s="39"/>
-      <c r="N93" s="39"/>
-      <c r="O93" s="39"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="52"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="52"/>
+      <c r="O93" s="52"/>
       <c r="P93" s="1"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94" s="38"/>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="51"/>
       <c r="B94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="43"/>
-      <c r="D94" s="43"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="43"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="56"/>
+      <c r="F94" s="56"/>
+      <c r="G94" s="56"/>
+      <c r="H94" s="56"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="39"/>
-      <c r="K94" s="39"/>
-      <c r="L94" s="39"/>
-      <c r="M94" s="39"/>
-      <c r="N94" s="39"/>
-      <c r="O94" s="39"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+      <c r="L94" s="52"/>
+      <c r="M94" s="52"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="52"/>
       <c r="P94" s="1"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A95" s="36" t="s">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="49" t="s">
         <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -4879,18 +4885,18 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I95" s="1"/>
-      <c r="J95" s="39" t="s">
+      <c r="J95" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K95" s="39"/>
-      <c r="L95" s="39"/>
-      <c r="M95" s="39"/>
-      <c r="N95" s="39"/>
-      <c r="O95" s="39"/>
+      <c r="K95" s="52"/>
+      <c r="L95" s="52"/>
+      <c r="M95" s="52"/>
+      <c r="N95" s="52"/>
+      <c r="O95" s="52"/>
       <c r="P95" s="1"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A96" s="37"/>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="50"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
@@ -4913,16 +4919,16 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I96" s="1"/>
-      <c r="J96" s="39"/>
-      <c r="K96" s="39"/>
-      <c r="L96" s="39"/>
-      <c r="M96" s="39"/>
-      <c r="N96" s="39"/>
-      <c r="O96" s="39"/>
+      <c r="J96" s="52"/>
+      <c r="K96" s="52"/>
+      <c r="L96" s="52"/>
+      <c r="M96" s="52"/>
+      <c r="N96" s="52"/>
+      <c r="O96" s="52"/>
       <c r="P96" s="1"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A97" s="37"/>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" s="50"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
       </c>
@@ -4945,36 +4951,36 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="39"/>
-      <c r="K97" s="39"/>
-      <c r="L97" s="39"/>
-      <c r="M97" s="39"/>
-      <c r="N97" s="39"/>
-      <c r="O97" s="39"/>
+      <c r="J97" s="52"/>
+      <c r="K97" s="52"/>
+      <c r="L97" s="52"/>
+      <c r="M97" s="52"/>
+      <c r="N97" s="52"/>
+      <c r="O97" s="52"/>
       <c r="P97" s="1"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A98" s="38"/>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" s="51"/>
       <c r="B98" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C98" s="43"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="43"/>
-      <c r="H98" s="43"/>
+      <c r="C98" s="56"/>
+      <c r="D98" s="56"/>
+      <c r="E98" s="56"/>
+      <c r="F98" s="56"/>
+      <c r="G98" s="56"/>
+      <c r="H98" s="56"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="39"/>
-      <c r="K98" s="39"/>
-      <c r="L98" s="39"/>
-      <c r="M98" s="39"/>
-      <c r="N98" s="39"/>
-      <c r="O98" s="39"/>
+      <c r="J98" s="52"/>
+      <c r="K98" s="52"/>
+      <c r="L98" s="52"/>
+      <c r="M98" s="52"/>
+      <c r="N98" s="52"/>
+      <c r="O98" s="52"/>
       <c r="P98" s="1"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A99" s="36" t="s">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" s="49" t="s">
         <v>31</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -4999,18 +5005,18 @@
         <v>3.8248319558473298E-23</v>
       </c>
       <c r="I99" s="1"/>
-      <c r="J99" s="39" t="s">
+      <c r="J99" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K99" s="39"/>
-      <c r="L99" s="39"/>
-      <c r="M99" s="39"/>
-      <c r="N99" s="39"/>
-      <c r="O99" s="39"/>
+      <c r="K99" s="52"/>
+      <c r="L99" s="52"/>
+      <c r="M99" s="52"/>
+      <c r="N99" s="52"/>
+      <c r="O99" s="52"/>
       <c r="P99" s="1"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A100" s="37"/>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="50"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
@@ -5033,16 +5039,16 @@
         <v>0.27985440517664001</v>
       </c>
       <c r="I100" s="1"/>
-      <c r="J100" s="39"/>
-      <c r="K100" s="39"/>
-      <c r="L100" s="39"/>
-      <c r="M100" s="39"/>
-      <c r="N100" s="39"/>
-      <c r="O100" s="39"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
+      <c r="L100" s="52"/>
+      <c r="M100" s="52"/>
+      <c r="N100" s="52"/>
+      <c r="O100" s="52"/>
       <c r="P100" s="1"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A101" s="37"/>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" s="50"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
       </c>
@@ -5065,49 +5071,49 @@
         <v>0.72495214931683005</v>
       </c>
       <c r="I101" s="1"/>
-      <c r="J101" s="39"/>
-      <c r="K101" s="39"/>
-      <c r="L101" s="39"/>
-      <c r="M101" s="39"/>
-      <c r="N101" s="39"/>
-      <c r="O101" s="39"/>
+      <c r="J101" s="52"/>
+      <c r="K101" s="52"/>
+      <c r="L101" s="52"/>
+      <c r="M101" s="52"/>
+      <c r="N101" s="52"/>
+      <c r="O101" s="52"/>
       <c r="P101" s="1"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A102" s="38"/>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" s="51"/>
       <c r="B102" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C102" s="43"/>
-      <c r="D102" s="43"/>
-      <c r="E102" s="43"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="43"/>
-      <c r="H102" s="43"/>
+      <c r="C102" s="56"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="56"/>
+      <c r="G102" s="56"/>
+      <c r="H102" s="56"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="39"/>
-      <c r="K102" s="39"/>
-      <c r="L102" s="39"/>
-      <c r="M102" s="39"/>
-      <c r="N102" s="39"/>
-      <c r="O102" s="39"/>
+      <c r="J102" s="52"/>
+      <c r="K102" s="52"/>
+      <c r="L102" s="52"/>
+      <c r="M102" s="52"/>
+      <c r="N102" s="52"/>
+      <c r="O102" s="52"/>
       <c r="P102" s="1"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103" s="36" t="s">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="49" t="s">
         <v>29</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="39" t="s">
+      <c r="C103" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D103" s="39"/>
-      <c r="E103" s="39"/>
-      <c r="F103" s="39"/>
-      <c r="G103" s="39"/>
-      <c r="H103" s="39"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
+      <c r="H103" s="52"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
         <v>4.9920514192076698E-4</v>
@@ -5129,17 +5135,17 @@
       </c>
       <c r="P103" s="1"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104" s="37"/>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="50"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="39"/>
-      <c r="D104" s="39"/>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39"/>
-      <c r="G104" s="39"/>
-      <c r="H104" s="39"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
+      <c r="H104" s="52"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
         <v>4.3245963051368403E-3</v>
@@ -5161,17 +5167,17 @@
       </c>
       <c r="P104" s="1"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105" s="37"/>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="50"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="39"/>
-      <c r="D105" s="39"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="39"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="52"/>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="52"/>
       <c r="I105" s="1"/>
       <c r="J105" s="5">
         <v>4.4673218852987901E-5</v>
@@ -5193,17 +5199,17 @@
       </c>
       <c r="P105" s="1"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106" s="38"/>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" s="51"/>
       <c r="B106" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C106" s="39"/>
-      <c r="D106" s="39"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39"/>
-      <c r="G106" s="39"/>
-      <c r="H106" s="39"/>
+      <c r="C106" s="52"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="52"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
         <v>2.5092673060789E-4</v>
@@ -5225,21 +5231,21 @@
       </c>
       <c r="P106" s="1"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107" s="36" t="s">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" s="49" t="s">
         <v>30</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="39" t="s">
+      <c r="C107" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D107" s="39"/>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39"/>
-      <c r="G107" s="39"/>
-      <c r="H107" s="39"/>
+      <c r="D107" s="52"/>
+      <c r="E107" s="52"/>
+      <c r="F107" s="52"/>
+      <c r="G107" s="52"/>
+      <c r="H107" s="52"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
         <v>1.4241127553301099E-4</v>
@@ -5261,17 +5267,17 @@
       </c>
       <c r="P107" s="1"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108" s="37"/>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="50"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="39"/>
-      <c r="D108" s="39"/>
-      <c r="E108" s="39"/>
-      <c r="F108" s="39"/>
-      <c r="G108" s="39"/>
-      <c r="H108" s="39"/>
+      <c r="C108" s="52"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52"/>
+      <c r="G108" s="52"/>
+      <c r="H108" s="52"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
         <v>4.6725153189010001E-2</v>
@@ -5293,17 +5299,17 @@
       </c>
       <c r="P108" s="1"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109" s="37"/>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="50"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="39"/>
-      <c r="D109" s="39"/>
-      <c r="E109" s="39"/>
-      <c r="F109" s="39"/>
-      <c r="G109" s="39"/>
-      <c r="H109" s="39"/>
+      <c r="C109" s="52"/>
+      <c r="D109" s="52"/>
+      <c r="E109" s="52"/>
+      <c r="F109" s="52"/>
+      <c r="G109" s="52"/>
+      <c r="H109" s="52"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1">
         <v>2.8302586845141399E-2</v>
@@ -5325,17 +5331,17 @@
       </c>
       <c r="P109" s="1"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110" s="38"/>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="51"/>
       <c r="B110" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
-      <c r="E110" s="39"/>
-      <c r="F110" s="39"/>
-      <c r="G110" s="39"/>
-      <c r="H110" s="39"/>
+      <c r="C110" s="52"/>
+      <c r="D110" s="52"/>
+      <c r="E110" s="52"/>
+      <c r="F110" s="52"/>
+      <c r="G110" s="52"/>
+      <c r="H110" s="52"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1">
         <v>6.3796317056246301E-3</v>
@@ -5357,8 +5363,8 @@
       </c>
       <c r="P110" s="1"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111" s="36" t="s">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="49" t="s">
         <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -5383,18 +5389,18 @@
         <v>2.5160186313214301E-3</v>
       </c>
       <c r="I111" s="1"/>
-      <c r="J111" s="39" t="s">
+      <c r="J111" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K111" s="39"/>
-      <c r="L111" s="39"/>
-      <c r="M111" s="39"/>
-      <c r="N111" s="39"/>
-      <c r="O111" s="39"/>
+      <c r="K111" s="52"/>
+      <c r="L111" s="52"/>
+      <c r="M111" s="52"/>
+      <c r="N111" s="52"/>
+      <c r="O111" s="52"/>
       <c r="P111" s="1"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112" s="37"/>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" s="50"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
@@ -5417,16 +5423,16 @@
         <v>0.13226601261193599</v>
       </c>
       <c r="I112" s="1"/>
-      <c r="J112" s="39"/>
-      <c r="K112" s="39"/>
-      <c r="L112" s="39"/>
-      <c r="M112" s="39"/>
-      <c r="N112" s="39"/>
-      <c r="O112" s="39"/>
+      <c r="J112" s="52"/>
+      <c r="K112" s="52"/>
+      <c r="L112" s="52"/>
+      <c r="M112" s="52"/>
+      <c r="N112" s="52"/>
+      <c r="O112" s="52"/>
       <c r="P112" s="1"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A113" s="37"/>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" s="50"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
       </c>
@@ -5449,36 +5455,36 @@
         <v>1.67603779088435E-5</v>
       </c>
       <c r="I113" s="1"/>
-      <c r="J113" s="39"/>
-      <c r="K113" s="39"/>
-      <c r="L113" s="39"/>
-      <c r="M113" s="39"/>
-      <c r="N113" s="39"/>
-      <c r="O113" s="39"/>
+      <c r="J113" s="52"/>
+      <c r="K113" s="52"/>
+      <c r="L113" s="52"/>
+      <c r="M113" s="52"/>
+      <c r="N113" s="52"/>
+      <c r="O113" s="52"/>
       <c r="P113" s="1"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A114" s="38"/>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" s="51"/>
       <c r="B114" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="43"/>
-      <c r="D114" s="43"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="43"/>
-      <c r="G114" s="43"/>
-      <c r="H114" s="43"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="56"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="56"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="39"/>
-      <c r="K114" s="39"/>
-      <c r="L114" s="39"/>
-      <c r="M114" s="39"/>
-      <c r="N114" s="39"/>
-      <c r="O114" s="39"/>
+      <c r="J114" s="52"/>
+      <c r="K114" s="52"/>
+      <c r="L114" s="52"/>
+      <c r="M114" s="52"/>
+      <c r="N114" s="52"/>
+      <c r="O114" s="52"/>
       <c r="P114" s="1"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A115" s="36" t="s">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" s="49" t="s">
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -5503,18 +5509,18 @@
         <v>3.1891308959839999E-11</v>
       </c>
       <c r="I115" s="1"/>
-      <c r="J115" s="39" t="s">
+      <c r="J115" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K115" s="39"/>
-      <c r="L115" s="39"/>
-      <c r="M115" s="39"/>
-      <c r="N115" s="39"/>
-      <c r="O115" s="39"/>
+      <c r="K115" s="52"/>
+      <c r="L115" s="52"/>
+      <c r="M115" s="52"/>
+      <c r="N115" s="52"/>
+      <c r="O115" s="52"/>
       <c r="P115" s="1"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A116" s="37"/>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116" s="50"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
@@ -5537,16 +5543,16 @@
         <v>1.9668218703936501E-2</v>
       </c>
       <c r="I116" s="1"/>
-      <c r="J116" s="39"/>
-      <c r="K116" s="39"/>
-      <c r="L116" s="39"/>
-      <c r="M116" s="39"/>
-      <c r="N116" s="39"/>
-      <c r="O116" s="39"/>
+      <c r="J116" s="52"/>
+      <c r="K116" s="52"/>
+      <c r="L116" s="52"/>
+      <c r="M116" s="52"/>
+      <c r="N116" s="52"/>
+      <c r="O116" s="52"/>
       <c r="P116" s="1"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A117" s="37"/>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117" s="50"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
       </c>
@@ -5569,36 +5575,36 @@
         <v>6.4583181614334004E-2</v>
       </c>
       <c r="I117" s="1"/>
-      <c r="J117" s="39"/>
-      <c r="K117" s="39"/>
-      <c r="L117" s="39"/>
-      <c r="M117" s="39"/>
-      <c r="N117" s="39"/>
-      <c r="O117" s="39"/>
+      <c r="J117" s="52"/>
+      <c r="K117" s="52"/>
+      <c r="L117" s="52"/>
+      <c r="M117" s="52"/>
+      <c r="N117" s="52"/>
+      <c r="O117" s="52"/>
       <c r="P117" s="1"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A118" s="38"/>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A118" s="51"/>
       <c r="B118" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C118" s="43"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="43"/>
-      <c r="F118" s="43"/>
-      <c r="G118" s="43"/>
-      <c r="H118" s="43"/>
+      <c r="C118" s="56"/>
+      <c r="D118" s="56"/>
+      <c r="E118" s="56"/>
+      <c r="F118" s="56"/>
+      <c r="G118" s="56"/>
+      <c r="H118" s="56"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="39"/>
-      <c r="K118" s="39"/>
-      <c r="L118" s="39"/>
-      <c r="M118" s="39"/>
-      <c r="N118" s="39"/>
-      <c r="O118" s="39"/>
+      <c r="J118" s="52"/>
+      <c r="K118" s="52"/>
+      <c r="L118" s="52"/>
+      <c r="M118" s="52"/>
+      <c r="N118" s="52"/>
+      <c r="O118" s="52"/>
       <c r="P118" s="1"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A119" s="36" t="s">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A119" s="49" t="s">
         <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -5623,18 +5629,18 @@
         <v>7.05414701429731E-35</v>
       </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="39" t="s">
+      <c r="J119" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K119" s="39"/>
-      <c r="L119" s="39"/>
-      <c r="M119" s="39"/>
-      <c r="N119" s="39"/>
-      <c r="O119" s="39"/>
+      <c r="K119" s="52"/>
+      <c r="L119" s="52"/>
+      <c r="M119" s="52"/>
+      <c r="N119" s="52"/>
+      <c r="O119" s="52"/>
       <c r="P119" s="1"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A120" s="37"/>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A120" s="50"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
@@ -5657,16 +5663,16 @@
         <v>3.9509565365961799E-2</v>
       </c>
       <c r="I120" s="1"/>
-      <c r="J120" s="39"/>
-      <c r="K120" s="39"/>
-      <c r="L120" s="39"/>
-      <c r="M120" s="39"/>
-      <c r="N120" s="39"/>
-      <c r="O120" s="39"/>
+      <c r="J120" s="52"/>
+      <c r="K120" s="52"/>
+      <c r="L120" s="52"/>
+      <c r="M120" s="52"/>
+      <c r="N120" s="52"/>
+      <c r="O120" s="52"/>
       <c r="P120" s="1"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A121" s="37"/>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A121" s="50"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
       </c>
@@ -5689,36 +5695,36 @@
         <v>1.2703272318058401E-2</v>
       </c>
       <c r="I121" s="1"/>
-      <c r="J121" s="39"/>
-      <c r="K121" s="39"/>
-      <c r="L121" s="39"/>
-      <c r="M121" s="39"/>
-      <c r="N121" s="39"/>
-      <c r="O121" s="39"/>
+      <c r="J121" s="52"/>
+      <c r="K121" s="52"/>
+      <c r="L121" s="52"/>
+      <c r="M121" s="52"/>
+      <c r="N121" s="52"/>
+      <c r="O121" s="52"/>
       <c r="P121" s="1"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A122" s="38"/>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A122" s="51"/>
       <c r="B122" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C122" s="43"/>
-      <c r="D122" s="43"/>
-      <c r="E122" s="43"/>
-      <c r="F122" s="43"/>
-      <c r="G122" s="43"/>
-      <c r="H122" s="43"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="56"/>
+      <c r="G122" s="56"/>
+      <c r="H122" s="56"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="39"/>
-      <c r="K122" s="39"/>
-      <c r="L122" s="39"/>
-      <c r="M122" s="39"/>
-      <c r="N122" s="39"/>
-      <c r="O122" s="39"/>
+      <c r="J122" s="52"/>
+      <c r="K122" s="52"/>
+      <c r="L122" s="52"/>
+      <c r="M122" s="52"/>
+      <c r="N122" s="52"/>
+      <c r="O122" s="52"/>
       <c r="P122" s="1"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A123" s="36" t="s">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A123" s="49" t="s">
         <v>25</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -5743,18 +5749,18 @@
         <v>6.3990332076812E-18</v>
       </c>
       <c r="I123" s="1"/>
-      <c r="J123" s="39" t="s">
+      <c r="J123" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K123" s="39"/>
-      <c r="L123" s="39"/>
-      <c r="M123" s="39"/>
-      <c r="N123" s="39"/>
-      <c r="O123" s="39"/>
+      <c r="K123" s="52"/>
+      <c r="L123" s="52"/>
+      <c r="M123" s="52"/>
+      <c r="N123" s="52"/>
+      <c r="O123" s="52"/>
       <c r="P123" s="1"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A124" s="37"/>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A124" s="50"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
@@ -5777,16 +5783,16 @@
         <v>6.1070966449770503E-2</v>
       </c>
       <c r="I124" s="1"/>
-      <c r="J124" s="39"/>
-      <c r="K124" s="39"/>
-      <c r="L124" s="39"/>
-      <c r="M124" s="39"/>
-      <c r="N124" s="39"/>
-      <c r="O124" s="39"/>
+      <c r="J124" s="52"/>
+      <c r="K124" s="52"/>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
       <c r="P124" s="1"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A125" s="37"/>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A125" s="50"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
@@ -5809,36 +5815,36 @@
         <v>1.2062369794193201E-2</v>
       </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="39"/>
-      <c r="K125" s="39"/>
-      <c r="L125" s="39"/>
-      <c r="M125" s="39"/>
-      <c r="N125" s="39"/>
-      <c r="O125" s="39"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
       <c r="P125" s="1"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A126" s="38"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A126" s="51"/>
       <c r="B126" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C126" s="43"/>
-      <c r="D126" s="43"/>
-      <c r="E126" s="43"/>
-      <c r="F126" s="43"/>
-      <c r="G126" s="43"/>
-      <c r="H126" s="43"/>
+      <c r="C126" s="56"/>
+      <c r="D126" s="56"/>
+      <c r="E126" s="56"/>
+      <c r="F126" s="56"/>
+      <c r="G126" s="56"/>
+      <c r="H126" s="56"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="39"/>
-      <c r="K126" s="39"/>
-      <c r="L126" s="39"/>
-      <c r="M126" s="39"/>
-      <c r="N126" s="39"/>
-      <c r="O126" s="39"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
       <c r="P126" s="1"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A127" s="36" t="s">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A127" s="49" t="s">
         <v>35</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -5863,18 +5869,18 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I127" s="1"/>
-      <c r="J127" s="39" t="s">
+      <c r="J127" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K127" s="39"/>
-      <c r="L127" s="39"/>
-      <c r="M127" s="39"/>
-      <c r="N127" s="39"/>
-      <c r="O127" s="39"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
       <c r="P127" s="1"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A128" s="37"/>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A128" s="50"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
@@ -5897,16 +5903,16 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I128" s="1"/>
-      <c r="J128" s="39"/>
-      <c r="K128" s="39"/>
-      <c r="L128" s="39"/>
-      <c r="M128" s="39"/>
-      <c r="N128" s="39"/>
-      <c r="O128" s="39"/>
+      <c r="J128" s="52"/>
+      <c r="K128" s="52"/>
+      <c r="L128" s="52"/>
+      <c r="M128" s="52"/>
+      <c r="N128" s="52"/>
+      <c r="O128" s="52"/>
       <c r="P128" s="1"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A129" s="37"/>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A129" s="50"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
       </c>
@@ -5929,36 +5935,36 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I129" s="1"/>
-      <c r="J129" s="39"/>
-      <c r="K129" s="39"/>
-      <c r="L129" s="39"/>
-      <c r="M129" s="39"/>
-      <c r="N129" s="39"/>
-      <c r="O129" s="39"/>
+      <c r="J129" s="52"/>
+      <c r="K129" s="52"/>
+      <c r="L129" s="52"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="52"/>
+      <c r="O129" s="52"/>
       <c r="P129" s="1"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A130" s="38"/>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A130" s="51"/>
       <c r="B130" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C130" s="43"/>
-      <c r="D130" s="43"/>
-      <c r="E130" s="43"/>
-      <c r="F130" s="43"/>
-      <c r="G130" s="43"/>
-      <c r="H130" s="43"/>
+      <c r="C130" s="56"/>
+      <c r="D130" s="56"/>
+      <c r="E130" s="56"/>
+      <c r="F130" s="56"/>
+      <c r="G130" s="56"/>
+      <c r="H130" s="56"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="39"/>
-      <c r="K130" s="39"/>
-      <c r="L130" s="39"/>
-      <c r="M130" s="39"/>
-      <c r="N130" s="39"/>
-      <c r="O130" s="39"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="52"/>
+      <c r="L130" s="52"/>
+      <c r="M130" s="52"/>
+      <c r="N130" s="52"/>
+      <c r="O130" s="52"/>
       <c r="P130" s="1"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A131" s="36" t="s">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A131" s="49" t="s">
         <v>36</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -5983,18 +5989,18 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I131" s="1"/>
-      <c r="J131" s="39" t="s">
+      <c r="J131" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K131" s="39"/>
-      <c r="L131" s="39"/>
-      <c r="M131" s="39"/>
-      <c r="N131" s="39"/>
-      <c r="O131" s="39"/>
+      <c r="K131" s="52"/>
+      <c r="L131" s="52"/>
+      <c r="M131" s="52"/>
+      <c r="N131" s="52"/>
+      <c r="O131" s="52"/>
       <c r="P131" s="1"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A132" s="37"/>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A132" s="50"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
@@ -6017,16 +6023,16 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I132" s="1"/>
-      <c r="J132" s="39"/>
-      <c r="K132" s="39"/>
-      <c r="L132" s="39"/>
-      <c r="M132" s="39"/>
-      <c r="N132" s="39"/>
-      <c r="O132" s="39"/>
+      <c r="J132" s="52"/>
+      <c r="K132" s="52"/>
+      <c r="L132" s="52"/>
+      <c r="M132" s="52"/>
+      <c r="N132" s="52"/>
+      <c r="O132" s="52"/>
       <c r="P132" s="1"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A133" s="37"/>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A133" s="50"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
       </c>
@@ -6049,36 +6055,36 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I133" s="1"/>
-      <c r="J133" s="39"/>
-      <c r="K133" s="39"/>
-      <c r="L133" s="39"/>
-      <c r="M133" s="39"/>
-      <c r="N133" s="39"/>
-      <c r="O133" s="39"/>
+      <c r="J133" s="52"/>
+      <c r="K133" s="52"/>
+      <c r="L133" s="52"/>
+      <c r="M133" s="52"/>
+      <c r="N133" s="52"/>
+      <c r="O133" s="52"/>
       <c r="P133" s="1"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A134" s="38"/>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A134" s="51"/>
       <c r="B134" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C134" s="43"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="43"/>
-      <c r="F134" s="43"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="43"/>
+      <c r="C134" s="56"/>
+      <c r="D134" s="56"/>
+      <c r="E134" s="56"/>
+      <c r="F134" s="56"/>
+      <c r="G134" s="56"/>
+      <c r="H134" s="56"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="39"/>
-      <c r="K134" s="39"/>
-      <c r="L134" s="39"/>
-      <c r="M134" s="39"/>
-      <c r="N134" s="39"/>
-      <c r="O134" s="39"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
       <c r="P134" s="1"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A135" s="36" t="s">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A135" s="49" t="s">
         <v>26</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -6103,18 +6109,18 @@
         <v>2.2809234413835001E-25</v>
       </c>
       <c r="I135" s="1"/>
-      <c r="J135" s="39" t="s">
+      <c r="J135" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="K135" s="39"/>
-      <c r="L135" s="39"/>
-      <c r="M135" s="39"/>
-      <c r="N135" s="39"/>
-      <c r="O135" s="39"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
       <c r="P135" s="1"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A136" s="37"/>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A136" s="50"/>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
@@ -6137,16 +6143,16 @@
         <v>7.2640986050278702E-2</v>
       </c>
       <c r="I136" s="1"/>
-      <c r="J136" s="39"/>
-      <c r="K136" s="39"/>
-      <c r="L136" s="39"/>
-      <c r="M136" s="39"/>
-      <c r="N136" s="39"/>
-      <c r="O136" s="39"/>
+      <c r="J136" s="52"/>
+      <c r="K136" s="52"/>
+      <c r="L136" s="52"/>
+      <c r="M136" s="52"/>
+      <c r="N136" s="52"/>
+      <c r="O136" s="52"/>
       <c r="P136" s="1"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A137" s="37"/>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A137" s="50"/>
       <c r="B137" s="1" t="s">
         <v>8</v>
       </c>
@@ -6169,50 +6175,50 @@
         <v>3.01236497113781E-6</v>
       </c>
       <c r="I137" s="1"/>
-      <c r="J137" s="39"/>
-      <c r="K137" s="39"/>
-      <c r="L137" s="39"/>
-      <c r="M137" s="39"/>
-      <c r="N137" s="39"/>
-      <c r="O137" s="39"/>
+      <c r="J137" s="52"/>
+      <c r="K137" s="52"/>
+      <c r="L137" s="52"/>
+      <c r="M137" s="52"/>
+      <c r="N137" s="52"/>
+      <c r="O137" s="52"/>
       <c r="P137" s="1"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A138" s="38"/>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A138" s="51"/>
       <c r="B138" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C138" s="43"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="43"/>
-      <c r="F138" s="43"/>
-      <c r="G138" s="43"/>
-      <c r="H138" s="43"/>
+      <c r="C138" s="56"/>
+      <c r="D138" s="56"/>
+      <c r="E138" s="56"/>
+      <c r="F138" s="56"/>
+      <c r="G138" s="56"/>
+      <c r="H138" s="56"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="39"/>
-      <c r="K138" s="39"/>
-      <c r="L138" s="39"/>
-      <c r="M138" s="39"/>
-      <c r="N138" s="39"/>
-      <c r="O138" s="39"/>
+      <c r="J138" s="52"/>
+      <c r="K138" s="52"/>
+      <c r="L138" s="52"/>
+      <c r="M138" s="52"/>
+      <c r="N138" s="52"/>
+      <c r="O138" s="52"/>
       <c r="P138" s="1"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
     </row>
   </sheetData>
@@ -6312,22 +6318,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B906023B-20D8-44CB-AA51-E431F089CEA5}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.44140625" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>44</v>
@@ -6355,8 +6361,8 @@
       </c>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="44">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="57">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6379,8 +6385,8 @@
       </c>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="45"/>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="58"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -6398,8 +6404,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="45"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -6418,8 +6424,8 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="58"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -6438,8 +6444,8 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="58"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6455,8 +6461,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="58"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6473,8 +6479,8 @@
       </c>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6489,8 +6495,8 @@
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="58"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6508,8 +6514,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="46"/>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="59"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6522,8 +6528,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="44">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6550,8 +6556,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="45"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>81</v>
@@ -6571,8 +6577,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="58"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -6588,8 +6594,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6601,8 +6607,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="58"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6614,8 +6620,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6627,8 +6633,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="45"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="58"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6640,8 +6646,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="47"/>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="60"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -6651,47 +6657,47 @@
       <c r="H18" s="14"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -6699,22 +6705,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>105</v>
       </c>
@@ -6731,20 +6737,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055498A3-AD3E-49E0-8565-96458FC406F5}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>44</v>
@@ -6772,8 +6778,8 @@
       </c>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="44">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="57">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6795,8 +6801,8 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="45"/>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="58"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -6809,8 +6815,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="45"/>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="E4" s="20" t="s">
@@ -6823,8 +6829,8 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="58"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -6838,8 +6844,8 @@
       </c>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="58"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6851,8 +6857,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="58"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6864,8 +6870,8 @@
       </c>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6875,8 +6881,8 @@
       <c r="H8" s="26"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="58"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6891,8 +6897,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="46"/>
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="59"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6904,8 +6910,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="44">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6923,8 +6929,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="45"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>81</v>
@@ -6939,8 +6945,8 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="58"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -6950,8 +6956,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6962,8 +6968,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="58"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6974,8 +6980,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6984,8 +6990,8 @@
       <c r="G16" s="1"/>
       <c r="H16" s="26"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="45"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="58"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6994,8 +7000,8 @@
       <c r="G17" s="1"/>
       <c r="H17" s="26"/>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="47"/>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="60"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -7004,87 +7010,87 @@
       <c r="G18" s="14"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>139</v>
       </c>
@@ -7100,53 +7106,53 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDA28D4-5A8D-4B82-B1F2-D70FA6918129}">
-  <dimension ref="A1:N106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="40">
+      <c r="C1" s="53">
         <v>2021</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="40">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="53">
         <v>2022</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7188,8 +7194,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7211,17 +7217,17 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="48" t="s">
+      <c r="I3" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="50"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="63"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
       <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
@@ -7241,15 +7247,15 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="53"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="66"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
       <c r="B5" s="1" t="s">
         <v>118</v>
       </c>
@@ -7269,15 +7275,15 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="66"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
         <v>110</v>
       </c>
@@ -7297,33 +7303,33 @@
         <v>0.1837454</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="49" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="36">
         <v>-0.67962469999999997</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="37">
         <v>0.72532470000000004</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="37">
         <v>23.402695999999999</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="37">
         <v>-0.93699370000000004</v>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="38">
         <v>0.35833147122850001</v>
       </c>
       <c r="H7" s="1"/>
@@ -7344,24 +7350,24 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
       <c r="B8" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="39">
         <v>-0.8024289</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="40">
         <v>0.59150590000000003</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="40">
         <v>37.766705999999999</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="40">
         <v>-1.600039</v>
       </c>
-      <c r="G8" s="64">
+      <c r="G8" s="43">
         <v>0.11792329999999999</v>
       </c>
       <c r="H8" s="1"/>
@@ -7382,24 +7388,24 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
       <c r="B9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="39">
         <v>-11.448639999999999</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="40">
         <v>1.2781750000000001</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="40">
         <v>14.82489</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="40">
         <v>-8.9570209999999992</v>
       </c>
-      <c r="G9" s="64">
+      <c r="G9" s="43">
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="H9" s="1"/>
@@ -7420,24 +7426,24 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="51"/>
       <c r="B10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="41">
         <v>-10.27468</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="42">
         <v>1.2625949999999999</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="42">
         <v>13.73147</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="42">
         <v>-8.1377450000000007</v>
       </c>
-      <c r="G10" s="65">
+      <c r="G10" s="44">
         <v>1.280514E-6</v>
       </c>
       <c r="H10" s="1"/>
@@ -7458,8 +7464,8 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="49" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -7498,8 +7504,8 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
       <c r="B12" s="1" t="s">
         <v>108</v>
       </c>
@@ -7536,8 +7542,8 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="50"/>
       <c r="B13" s="1" t="s">
         <v>109</v>
       </c>
@@ -7574,8 +7580,8 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
       <c r="B14" s="1" t="s">
         <v>110</v>
       </c>
@@ -7612,8 +7618,8 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -7652,8 +7658,8 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="50"/>
       <c r="B16" s="1" t="s">
         <v>108</v>
       </c>
@@ -7690,8 +7696,8 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="50"/>
       <c r="B17" s="1" t="s">
         <v>109</v>
       </c>
@@ -7728,8 +7734,8 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="51"/>
       <c r="B18" s="1" t="s">
         <v>110</v>
       </c>
@@ -7766,162 +7772,162 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="49" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="66">
+      <c r="C19" s="45">
         <v>0.16267690000000001</v>
       </c>
-      <c r="D19" s="66">
+      <c r="D19" s="45">
         <v>2.342762E-2</v>
       </c>
-      <c r="E19" s="66">
+      <c r="E19" s="45">
         <v>23.465475999999999</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F19" s="45">
         <v>6.9438079999999998</v>
       </c>
-      <c r="G19" s="66">
+      <c r="G19" s="45">
         <v>3.98194E-7</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="66">
+      <c r="I19" s="45">
         <v>-2.5494809999999999E-4</v>
       </c>
-      <c r="J19" s="66">
+      <c r="J19" s="45">
         <v>1.9431219999999999E-4</v>
       </c>
-      <c r="K19" s="66">
+      <c r="K19" s="45">
         <v>55.507640000000002</v>
       </c>
-      <c r="L19" s="66">
+      <c r="L19" s="45">
         <v>-1.3120540000000001</v>
       </c>
-      <c r="M19" s="66">
+      <c r="M19" s="45">
         <v>0.19490214432</v>
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="50"/>
       <c r="B20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="66">
+      <c r="C20" s="45">
         <v>0.1318241</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="45">
         <v>1.53215E-2</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="45">
         <v>38.868819999999999</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="45">
         <v>8.603866</v>
       </c>
-      <c r="G20" s="67">
+      <c r="G20" s="46">
         <v>1.5523469999999999E-10</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="66">
+      <c r="I20" s="45">
         <v>2.431771E-4</v>
       </c>
-      <c r="J20" s="66">
+      <c r="J20" s="45">
         <v>3.0047830000000001E-4</v>
       </c>
-      <c r="K20" s="66">
+      <c r="K20" s="45">
         <v>54.111055</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="45">
         <v>0.80930000000000002</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="45">
         <v>0.4218870666026</v>
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="50"/>
       <c r="B21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="45">
         <v>-7.6752669999999995E-2</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="45">
         <v>5.0189159999999997E-2</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="45">
         <v>16.372039999999998</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="45">
         <v>-1.5292680000000001</v>
       </c>
-      <c r="G21" s="67">
+      <c r="G21" s="46">
         <v>0.14528840000000001</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="66">
+      <c r="I21" s="45">
         <v>-2.3284180000000001E-3</v>
       </c>
-      <c r="J21" s="66">
+      <c r="J21" s="45">
         <v>4.9925909999999998E-4</v>
       </c>
-      <c r="K21" s="66">
+      <c r="K21" s="45">
         <v>11.371589999999999</v>
       </c>
-      <c r="L21" s="66">
+      <c r="L21" s="45">
         <v>-4.6637459999999997</v>
       </c>
-      <c r="M21" s="66">
+      <c r="M21" s="45">
         <v>6.3120474729999999E-4</v>
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="51"/>
       <c r="B22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="45">
         <v>-6.6752569999999997E-2</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="45">
         <v>3.12787E-2</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="45">
         <v>14.8775</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="45">
         <v>-2.1341220000000001</v>
       </c>
-      <c r="G22" s="67">
+      <c r="G22" s="46">
         <v>4.9892260000000001E-2</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="66">
+      <c r="I22" s="45">
         <v>-1.939112E-3</v>
       </c>
-      <c r="J22" s="66">
+      <c r="J22" s="45">
         <v>3.8723229999999999E-4</v>
       </c>
-      <c r="K22" s="66">
+      <c r="K22" s="45">
         <v>13.92292</v>
       </c>
-      <c r="L22" s="66">
+      <c r="L22" s="45">
         <v>-5.0076210000000003</v>
       </c>
-      <c r="M22" s="66" t="s">
+      <c r="M22" s="45" t="s">
         <v>147</v>
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -7960,8 +7966,8 @@
       </c>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="50"/>
       <c r="B24" s="1" t="s">
         <v>108</v>
       </c>
@@ -7998,8 +8004,8 @@
       </c>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="50"/>
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
@@ -8036,8 +8042,8 @@
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
       <c r="B26" s="1" t="s">
         <v>110</v>
       </c>
@@ -8074,8 +8080,8 @@
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -8114,8 +8120,8 @@
       </c>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="50"/>
       <c r="B28" s="1" t="s">
         <v>108</v>
       </c>
@@ -8152,8 +8158,8 @@
       </c>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="50"/>
       <c r="B29" s="1" t="s">
         <v>109</v>
       </c>
@@ -8190,8 +8196,8 @@
       </c>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
       <c r="B30" s="1" t="s">
         <v>110</v>
       </c>
@@ -8228,8 +8234,8 @@
       </c>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
         <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -8270,8 +8276,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="50"/>
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
@@ -8310,8 +8316,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="50"/>
       <c r="B33" s="1" t="s">
         <v>109</v>
       </c>
@@ -8350,8 +8356,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="38"/>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="51"/>
       <c r="B34" s="1" t="s">
         <v>110</v>
       </c>
@@ -8390,8 +8396,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="49" t="s">
         <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8432,8 +8438,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="50"/>
       <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
@@ -8472,8 +8478,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="50"/>
       <c r="B37" s="1" t="s">
         <v>109</v>
       </c>
@@ -8512,8 +8518,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="51"/>
       <c r="B38" s="1" t="s">
         <v>110</v>
       </c>
@@ -8552,8 +8558,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="49" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -8592,8 +8598,8 @@
       </c>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="50"/>
       <c r="B40" s="1" t="s">
         <v>108</v>
       </c>
@@ -8630,8 +8636,8 @@
       </c>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="50"/>
       <c r="B41" s="1" t="s">
         <v>109</v>
       </c>
@@ -8668,8 +8674,8 @@
       </c>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="51"/>
       <c r="B42" s="1" t="s">
         <v>110</v>
       </c>
@@ -8706,1656 +8712,1882 @@
       </c>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="36" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="49" t="s">
         <v>148</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="66">
+      <c r="I43" s="45">
         <v>-1.7478199999999999E-2</v>
       </c>
-      <c r="J43" s="66">
+      <c r="J43" s="45">
         <v>7.7458099999999997E-3</v>
       </c>
-      <c r="K43" s="66">
+      <c r="K43" s="45">
         <v>56.319026999999998</v>
       </c>
-      <c r="L43" s="66">
+      <c r="L43" s="45">
         <v>-2.256472</v>
       </c>
-      <c r="M43" s="67">
+      <c r="M43" s="46">
         <v>2.2794061000000001E-2</v>
       </c>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="50"/>
       <c r="B44" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="66">
+      <c r="I44" s="45">
         <v>-2.3552070000000001E-2</v>
       </c>
-      <c r="J44" s="66">
+      <c r="J44" s="45">
         <v>6.7560479999999997E-3</v>
       </c>
-      <c r="K44" s="66">
+      <c r="K44" s="45">
         <v>54.097791000000001</v>
       </c>
-      <c r="L44" s="66">
+      <c r="L44" s="45">
         <v>-3.4860709999999999</v>
       </c>
-      <c r="M44" s="67">
+      <c r="M44" s="46">
         <v>9.8065299999999995E-4</v>
       </c>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="50"/>
       <c r="B45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="66">
+      <c r="I45" s="45">
         <v>-2.6797439999999999E-2</v>
       </c>
-      <c r="J45" s="66">
+      <c r="J45" s="45">
         <v>1.099955E-2</v>
       </c>
-      <c r="K45" s="66">
+      <c r="K45" s="45">
         <v>13.570510000000001</v>
       </c>
-      <c r="L45" s="66">
+      <c r="L45" s="45">
         <v>-2.4262299999999999</v>
       </c>
-      <c r="M45" s="67">
+      <c r="M45" s="46">
         <v>2.928103E-2</v>
       </c>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="38"/>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="51"/>
       <c r="B46" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="66">
+      <c r="I46" s="45">
         <v>-3.3645590000000003E-2</v>
       </c>
-      <c r="J46" s="66">
+      <c r="J46" s="45">
         <v>1.265696E-2</v>
       </c>
-      <c r="K46" s="66">
+      <c r="K46" s="45">
         <v>13.256600000000001</v>
       </c>
-      <c r="L46" s="66">
+      <c r="L46" s="45">
         <v>-2.6582690000000002</v>
       </c>
-      <c r="M46" s="67">
+      <c r="M46" s="46">
         <v>1.943344E-2</v>
       </c>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="36" t="s">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="66">
+      <c r="I47" s="45">
         <v>-8.3753321000000006E-3</v>
       </c>
-      <c r="J47" s="66">
+      <c r="J47" s="45">
         <v>8.9984460000000002E-3</v>
       </c>
-      <c r="K47" s="66">
+      <c r="K47" s="45">
         <v>56.69021</v>
       </c>
-      <c r="L47" s="66">
+      <c r="L47" s="45">
         <v>-0.93075200000000002</v>
       </c>
-      <c r="M47" s="67">
+      <c r="M47" s="46">
         <v>0.35592869999999999</v>
       </c>
       <c r="N47" s="1"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="50"/>
       <c r="B48" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="66">
+      <c r="I48" s="45">
         <v>6.2885479999999997E-3</v>
       </c>
-      <c r="J48" s="66">
+      <c r="J48" s="45">
         <v>1.0130220000000001E-2</v>
       </c>
-      <c r="K48" s="66">
+      <c r="K48" s="45">
         <v>54.056728</v>
       </c>
-      <c r="L48" s="66">
+      <c r="L48" s="45">
         <v>0.62077130000000003</v>
       </c>
-      <c r="M48" s="67">
+      <c r="M48" s="46">
         <v>0.53735880000000003</v>
       </c>
       <c r="N48" s="1"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="50"/>
       <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="66">
+      <c r="I49" s="45">
         <v>-0.1092133</v>
       </c>
-      <c r="J49" s="66">
+      <c r="J49" s="45">
         <v>2.1070729999999999E-2</v>
       </c>
-      <c r="K49" s="66">
+      <c r="K49" s="45">
         <v>11.89181</v>
       </c>
-      <c r="L49" s="66">
+      <c r="L49" s="45">
         <v>-5.1831759999999996</v>
       </c>
-      <c r="M49" s="67">
+      <c r="M49" s="46">
         <v>2.34916E-4</v>
       </c>
       <c r="N49" s="1"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="51"/>
       <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="66">
+      <c r="I50" s="45">
         <v>-9.8989809999999998E-2</v>
       </c>
-      <c r="J50" s="66">
+      <c r="J50" s="45">
         <v>1.5884120000000002E-2</v>
       </c>
-      <c r="K50" s="66">
+      <c r="K50" s="45">
         <v>13.67961</v>
       </c>
-      <c r="L50" s="66">
+      <c r="L50" s="45">
         <v>-6.2319979999999999</v>
       </c>
-      <c r="M50" s="67">
+      <c r="M50" s="46">
         <v>2.433112E-5</v>
       </c>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="36" t="s">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="49" t="s">
         <v>145</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="66">
+      <c r="C51" s="45">
         <v>-4.1460160000000004</v>
       </c>
-      <c r="D51" s="66">
+      <c r="D51" s="45">
         <v>0.6769811</v>
       </c>
-      <c r="E51" s="66">
+      <c r="E51" s="45">
         <v>24.376617</v>
       </c>
-      <c r="F51" s="66">
+      <c r="F51" s="45">
         <v>-6.1242720000000004</v>
       </c>
-      <c r="G51" s="66">
+      <c r="G51" s="45">
         <v>2.350653E-6</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="39" t="s">
+      <c r="I51" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
-      <c r="M51" s="39"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="50"/>
       <c r="B52" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="66">
+      <c r="C52" s="45">
         <v>-5.1080050000000004</v>
       </c>
-      <c r="D52" s="66">
+      <c r="D52" s="45">
         <v>0.46945019999999998</v>
       </c>
-      <c r="E52" s="66">
+      <c r="E52" s="45">
         <v>38.858649999999997</v>
       </c>
-      <c r="F52" s="66">
+      <c r="F52" s="45">
         <v>-10.88082</v>
       </c>
-      <c r="G52" s="67">
+      <c r="G52" s="46">
         <v>2.3278650000000001E-13</v>
       </c>
       <c r="H52" s="1"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
       <c r="N52" s="1"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="50"/>
       <c r="B53" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="66">
+      <c r="C53" s="45">
         <v>-3.7989480000000002</v>
       </c>
-      <c r="D53" s="66">
+      <c r="D53" s="45">
         <v>1.208588</v>
       </c>
-      <c r="E53" s="66">
+      <c r="E53" s="45">
         <v>17.432320000000001</v>
       </c>
-      <c r="F53" s="66">
+      <c r="F53" s="45">
         <v>-3.143294</v>
       </c>
-      <c r="G53" s="67">
+      <c r="G53" s="46">
         <v>5.789537E-3</v>
       </c>
       <c r="H53" s="1"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="52"/>
+      <c r="M53" s="52"/>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="38"/>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="51"/>
       <c r="B54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="66">
+      <c r="C54" s="45">
         <v>-4.4755320000000003</v>
       </c>
-      <c r="D54" s="66">
+      <c r="D54" s="45">
         <v>0.98680710000000005</v>
       </c>
-      <c r="E54" s="66">
+      <c r="E54" s="45">
         <v>15.62265</v>
       </c>
-      <c r="F54" s="66">
+      <c r="F54" s="45">
         <v>-4.5353669999999999</v>
       </c>
-      <c r="G54" s="67">
+      <c r="G54" s="46">
         <v>3.5774789999999998E-4</v>
       </c>
       <c r="H54" s="1"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="52"/>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="36" t="s">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="49" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="47">
         <v>0.142703</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="47">
         <v>2.4577999999999999E-2</v>
       </c>
-      <c r="E55" s="68">
+      <c r="E55" s="47">
         <v>23.670773000000001</v>
       </c>
-      <c r="F55" s="68">
+      <c r="F55" s="47">
         <v>5.5574009999999996</v>
       </c>
-      <c r="G55" s="68">
+      <c r="G55" s="47">
         <v>1.0710269999999999E-5</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="39" t="s">
+      <c r="I55" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="52"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="52"/>
       <c r="N55" s="1"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="50"/>
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="68">
+      <c r="C56" s="47">
         <v>0.10728550000000001</v>
       </c>
-      <c r="D56" s="68">
+      <c r="D56" s="47">
         <v>1.8656389999999998E-2</v>
       </c>
-      <c r="E56" s="68">
+      <c r="E56" s="47">
         <v>36.899675999999999</v>
       </c>
-      <c r="F56" s="68">
+      <c r="F56" s="47">
         <v>5.7506050000000002</v>
       </c>
-      <c r="G56" s="68">
+      <c r="G56" s="47">
         <v>1.3791302849E-6</v>
       </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
+      <c r="K56" s="52"/>
+      <c r="L56" s="52"/>
+      <c r="M56" s="52"/>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="50"/>
       <c r="B57" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="68">
+      <c r="C57" s="47">
         <v>-0.1020605</v>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="47">
         <v>5.7317760000000002E-2</v>
       </c>
-      <c r="E57" s="68">
+      <c r="E57" s="47">
         <v>16.319230000000001</v>
       </c>
-      <c r="F57" s="68">
+      <c r="F57" s="47">
         <v>-1.7806090000000001</v>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="47">
         <v>9.3598610230064994E-2</v>
       </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="39"/>
-      <c r="M57" s="39"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="52"/>
+      <c r="L57" s="52"/>
+      <c r="M57" s="52"/>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="38"/>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="51"/>
       <c r="B58" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="68">
+      <c r="C58" s="47">
         <v>-8.9823520000000004E-2</v>
       </c>
-      <c r="D58" s="68">
+      <c r="D58" s="47">
         <v>3.9384450000000001E-2</v>
       </c>
-      <c r="E58" s="68">
+      <c r="E58" s="47">
         <v>14.65358</v>
       </c>
-      <c r="F58" s="68">
+      <c r="F58" s="47">
         <v>-2.2806850000000001</v>
       </c>
-      <c r="G58" s="69">
+      <c r="G58" s="48">
         <v>3.7977520000000001E-2</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="39"/>
-      <c r="M58" s="39"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
       <c r="N58" s="1"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="36" t="s">
-        <v>39</v>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="49" t="s">
+        <v>151</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="47">
+        <v>0.3732317</v>
+      </c>
+      <c r="D59" s="47">
+        <v>2.314503E-2</v>
+      </c>
+      <c r="E59" s="47">
+        <v>22.935904000000001</v>
+      </c>
+      <c r="F59" s="47">
+        <v>16.125781</v>
+      </c>
+      <c r="G59" s="47">
+        <v>5.242662E-14</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1">
-        <v>5.4104409999999999E-2</v>
-      </c>
-      <c r="J59" s="1">
-        <v>1.586684E-2</v>
-      </c>
-      <c r="K59" s="1">
-        <v>55.294079000000004</v>
-      </c>
-      <c r="L59" s="1">
-        <v>3.4099050000000002</v>
-      </c>
-      <c r="M59" s="2">
-        <v>1.2200878E-3</v>
-      </c>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="50"/>
       <c r="B60" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
+      <c r="C60" s="47">
+        <v>0.39719009999999999</v>
+      </c>
+      <c r="D60" s="47">
+        <v>3.5684239999999999E-2</v>
+      </c>
+      <c r="E60" s="47">
+        <v>42.630980000000001</v>
+      </c>
+      <c r="F60" s="47">
+        <v>11.130687</v>
+      </c>
+      <c r="G60" s="47">
+        <v>3.4043159999999998E-14</v>
+      </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="1">
-        <v>4.687269E-3</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1.2589380000000001E-2</v>
-      </c>
-      <c r="K60" s="1">
-        <v>54.088656</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0.37231940000000002</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0.71110989999999996</v>
-      </c>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52"/>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
       <c r="N60" s="1"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="50"/>
       <c r="B61" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
+      <c r="C61" s="47">
+        <v>-2.5815100000000001E-2</v>
+      </c>
+      <c r="D61" s="47">
+        <v>5.5261520000000001E-2</v>
+      </c>
+      <c r="E61" s="47">
+        <v>21.336089999999999</v>
+      </c>
+      <c r="F61" s="47">
+        <v>-0.46714420000000001</v>
+      </c>
+      <c r="G61" s="47">
+        <v>0.64513220100000002</v>
+      </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="1">
-        <v>-0.16190650000000001</v>
-      </c>
-      <c r="J61" s="1">
-        <v>4.2269439999999998E-2</v>
-      </c>
-      <c r="K61" s="1">
-        <v>12.56658</v>
-      </c>
-      <c r="L61" s="1">
-        <v>-3.8303449999999999</v>
-      </c>
-      <c r="M61" s="2">
-        <v>2.2091979999999999E-3</v>
-      </c>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
+      <c r="K61" s="52"/>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
       <c r="N61" s="1"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="38"/>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="51"/>
       <c r="B62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
+      <c r="C62" s="47">
+        <v>2.8353639999999999E-2</v>
+      </c>
+      <c r="D62" s="47">
+        <v>3.0635989999999998E-2</v>
+      </c>
+      <c r="E62" s="47">
+        <v>18.611360000000001</v>
+      </c>
+      <c r="F62" s="47">
+        <v>0.92550100000000002</v>
+      </c>
+      <c r="G62" s="47">
+        <v>0.36655130000000002</v>
+      </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="1">
-        <v>-0.22064059999999999</v>
-      </c>
-      <c r="J62" s="1">
-        <v>3.0408129999999998E-2</v>
-      </c>
-      <c r="K62" s="1">
-        <v>12.94289</v>
-      </c>
-      <c r="L62" s="1">
-        <v>-7.2559740000000001</v>
-      </c>
-      <c r="M62" s="2">
-        <v>6.5639129999999997E-6</v>
-      </c>
+      <c r="I62" s="52"/>
+      <c r="J62" s="52"/>
+      <c r="K62" s="52"/>
+      <c r="L62" s="52"/>
+      <c r="M62" s="52"/>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="36" t="s">
-        <v>146</v>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="68">
-        <v>0.2325074</v>
-      </c>
-      <c r="D63" s="68">
-        <v>1.6652759999999999E-2</v>
-      </c>
-      <c r="E63" s="68">
-        <v>25.056222999999999</v>
-      </c>
-      <c r="F63" s="68">
-        <v>13.96209</v>
-      </c>
-      <c r="G63" s="69">
-        <v>2.524047E-13</v>
-      </c>
+      <c r="C63" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
+      <c r="G63" s="52"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
-      <c r="L63" s="39"/>
-      <c r="M63" s="39"/>
+      <c r="I63" s="1">
+        <v>5.4104409999999999E-2</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1.586684E-2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>55.294079000000004</v>
+      </c>
+      <c r="L63" s="1">
+        <v>3.4099050000000002</v>
+      </c>
+      <c r="M63" s="2">
+        <v>1.2200878E-3</v>
+      </c>
       <c r="N63" s="1"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="50"/>
       <c r="B64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="68">
-        <v>0.28619260000000002</v>
-      </c>
-      <c r="D64" s="68">
-        <v>3.6218710000000001E-2</v>
-      </c>
-      <c r="E64" s="68">
-        <v>41.139429999999997</v>
-      </c>
-      <c r="F64" s="68">
-        <v>7.901789</v>
-      </c>
-      <c r="G64" s="68">
-        <v>8.8521990000000004E-10</v>
-      </c>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="52"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="52"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="39"/>
-      <c r="M64" s="39"/>
+      <c r="I64" s="1">
+        <v>4.687269E-3</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1.2589380000000001E-2</v>
+      </c>
+      <c r="K64" s="1">
+        <v>54.088656</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0.37231940000000002</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0.71110989999999996</v>
+      </c>
       <c r="N64" s="1"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="50"/>
       <c r="B65" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="68">
-        <v>8.0073980000000003E-2</v>
-      </c>
-      <c r="D65" s="68">
-        <v>4.5945039999999999E-2</v>
-      </c>
-      <c r="E65" s="68">
-        <v>20.778459999999999</v>
-      </c>
-      <c r="F65" s="68">
-        <v>1.742821</v>
-      </c>
-      <c r="G65" s="69">
-        <v>9.6146709999999996E-2</v>
-      </c>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39"/>
+      <c r="I65" s="1">
+        <v>-0.16190650000000001</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4.2269439999999998E-2</v>
+      </c>
+      <c r="K65" s="1">
+        <v>12.56658</v>
+      </c>
+      <c r="L65" s="1">
+        <v>-3.8303449999999999</v>
+      </c>
+      <c r="M65" s="2">
+        <v>2.2091979999999999E-3</v>
+      </c>
       <c r="N65" s="1"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="38"/>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="51"/>
       <c r="B66" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="68">
-        <v>0.1221365</v>
-      </c>
-      <c r="D66" s="68">
-        <v>3.947755E-2</v>
-      </c>
-      <c r="E66" s="68">
-        <v>16.65624</v>
-      </c>
-      <c r="F66" s="68">
-        <v>3.0938219999999998</v>
-      </c>
-      <c r="G66" s="68">
-        <v>6.7150146952E-3</v>
-      </c>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="39"/>
-      <c r="M66" s="39"/>
+      <c r="I66" s="1">
+        <v>-0.22064059999999999</v>
+      </c>
+      <c r="J66" s="1">
+        <v>3.0408129999999998E-2</v>
+      </c>
+      <c r="K66" s="1">
+        <v>12.94289</v>
+      </c>
+      <c r="L66" s="1">
+        <v>-7.2559740000000001</v>
+      </c>
+      <c r="M66" s="2">
+        <v>6.5639129999999997E-6</v>
+      </c>
       <c r="N66" s="1"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="36" t="s">
-        <v>149</v>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="49" t="s">
+        <v>146</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="47">
+        <v>0.2325074</v>
+      </c>
+      <c r="D67" s="47">
+        <v>1.6652759999999999E-2</v>
+      </c>
+      <c r="E67" s="47">
+        <v>25.056222999999999</v>
+      </c>
+      <c r="F67" s="47">
+        <v>13.96209</v>
+      </c>
+      <c r="G67" s="48">
+        <v>2.524047E-13</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="66">
-        <v>3.8010990000000001E-3</v>
-      </c>
-      <c r="J67" s="66">
-        <v>1.2390599999999999E-3</v>
-      </c>
-      <c r="K67" s="66">
-        <v>56.226177999999997</v>
-      </c>
-      <c r="L67" s="66">
-        <v>3.0677270000000001</v>
-      </c>
-      <c r="M67" s="66">
-        <v>3.3149447299999999E-3</v>
-      </c>
+      <c r="J67" s="52"/>
+      <c r="K67" s="52"/>
+      <c r="L67" s="52"/>
+      <c r="M67" s="52"/>
       <c r="N67" s="1"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="50"/>
       <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
+      <c r="C68" s="47">
+        <v>0.28619260000000002</v>
+      </c>
+      <c r="D68" s="47">
+        <v>3.6218710000000001E-2</v>
+      </c>
+      <c r="E68" s="47">
+        <v>41.139429999999997</v>
+      </c>
+      <c r="F68" s="47">
+        <v>7.901789</v>
+      </c>
+      <c r="G68" s="47">
+        <v>8.8521990000000004E-10</v>
+      </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="66">
-        <v>2.6998579999999999E-3</v>
-      </c>
-      <c r="J68" s="66">
-        <v>1.7967930000000001E-3</v>
-      </c>
-      <c r="K68" s="66">
-        <v>54.259734999999999</v>
-      </c>
-      <c r="L68" s="66">
-        <v>1.502599</v>
-      </c>
-      <c r="M68" s="66">
-        <v>0.13874061215931999</v>
-      </c>
+      <c r="I68" s="52"/>
+      <c r="J68" s="52"/>
+      <c r="K68" s="52"/>
+      <c r="L68" s="52"/>
+      <c r="M68" s="52"/>
       <c r="N68" s="1"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="50"/>
       <c r="B69" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
+      <c r="C69" s="47">
+        <v>8.0073980000000003E-2</v>
+      </c>
+      <c r="D69" s="47">
+        <v>4.5945039999999999E-2</v>
+      </c>
+      <c r="E69" s="47">
+        <v>20.778459999999999</v>
+      </c>
+      <c r="F69" s="47">
+        <v>1.742821</v>
+      </c>
+      <c r="G69" s="48">
+        <v>9.6146709999999996E-2</v>
+      </c>
       <c r="H69" s="1"/>
-      <c r="I69" s="66">
-        <v>-1.146374E-2</v>
-      </c>
-      <c r="J69" s="66">
-        <v>2.9301919999999999E-3</v>
-      </c>
-      <c r="K69" s="66">
-        <v>12.84609</v>
-      </c>
-      <c r="L69" s="66">
-        <v>-3.9122840000000001</v>
-      </c>
-      <c r="M69" s="66">
-        <v>1.8229571331547E-3</v>
-      </c>
+      <c r="I69" s="52"/>
+      <c r="J69" s="52"/>
+      <c r="K69" s="52"/>
+      <c r="L69" s="52"/>
+      <c r="M69" s="52"/>
       <c r="N69" s="1"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="38"/>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="51"/>
       <c r="B70" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
+      <c r="C70" s="47">
+        <v>0.1221365</v>
+      </c>
+      <c r="D70" s="47">
+        <v>3.947755E-2</v>
+      </c>
+      <c r="E70" s="47">
+        <v>16.65624</v>
+      </c>
+      <c r="F70" s="47">
+        <v>3.0938219999999998</v>
+      </c>
+      <c r="G70" s="47">
+        <v>6.7150146952E-3</v>
+      </c>
       <c r="H70" s="1"/>
-      <c r="I70" s="66">
-        <v>-1.288595E-2</v>
-      </c>
-      <c r="J70" s="66">
-        <v>2.4782379999999998E-3</v>
-      </c>
-      <c r="K70" s="66">
-        <v>14.11434</v>
-      </c>
-      <c r="L70" s="66">
-        <v>-5.1996440000000002</v>
-      </c>
-      <c r="M70" s="66">
-        <v>1.3118094177569999E-4</v>
-      </c>
+      <c r="I70" s="52"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="52"/>
+      <c r="M70" s="52"/>
       <c r="N70" s="1"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="36" t="s">
-        <v>30</v>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="49" t="s">
+        <v>149</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="39" t="s">
+      <c r="C71" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1">
-        <v>-1.7348269999999999E-2</v>
-      </c>
-      <c r="J71" s="1">
-        <v>6.5396389999999999E-3</v>
-      </c>
-      <c r="K71" s="1">
-        <v>55.709558000000001</v>
-      </c>
-      <c r="L71" s="1">
-        <v>-2.652787</v>
-      </c>
-      <c r="M71" s="2">
-        <v>1.038058E-2</v>
+      <c r="I71" s="45">
+        <v>3.8010990000000001E-3</v>
+      </c>
+      <c r="J71" s="45">
+        <v>1.2390599999999999E-3</v>
+      </c>
+      <c r="K71" s="45">
+        <v>56.226177999999997</v>
+      </c>
+      <c r="L71" s="45">
+        <v>3.0677270000000001</v>
+      </c>
+      <c r="M71" s="45">
+        <v>3.3149447299999999E-3</v>
       </c>
       <c r="N71" s="1"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="50"/>
       <c r="B72" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="1">
-        <v>1.2575930000000001E-2</v>
-      </c>
-      <c r="J72" s="1">
-        <v>7.0812319999999998E-3</v>
-      </c>
-      <c r="K72" s="1">
-        <v>54.114787999999997</v>
-      </c>
-      <c r="L72" s="1">
-        <v>1.775952</v>
-      </c>
-      <c r="M72" s="3">
-        <v>8.1363409999999997E-2</v>
+      <c r="I72" s="45">
+        <v>2.6998579999999999E-3</v>
+      </c>
+      <c r="J72" s="45">
+        <v>1.7967930000000001E-3</v>
+      </c>
+      <c r="K72" s="45">
+        <v>54.259734999999999</v>
+      </c>
+      <c r="L72" s="45">
+        <v>1.502599</v>
+      </c>
+      <c r="M72" s="45">
+        <v>0.13874061215931999</v>
       </c>
       <c r="N72" s="1"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="50"/>
       <c r="B73" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
+      <c r="C73" s="52"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="52"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="52"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1">
-        <v>3.5116069999999999E-2</v>
-      </c>
-      <c r="J73" s="1">
-        <v>1.7176980000000001E-2</v>
-      </c>
-      <c r="K73" s="1">
-        <v>13.180910000000001</v>
-      </c>
-      <c r="L73" s="1">
-        <v>2.044368</v>
-      </c>
-      <c r="M73" s="3">
-        <v>6.1427379999999997E-2</v>
+      <c r="I73" s="45">
+        <v>-1.146374E-2</v>
+      </c>
+      <c r="J73" s="45">
+        <v>2.9301919999999999E-3</v>
+      </c>
+      <c r="K73" s="45">
+        <v>12.84609</v>
+      </c>
+      <c r="L73" s="45">
+        <v>-3.9122840000000001</v>
+      </c>
+      <c r="M73" s="45">
+        <v>1.8229571331547E-3</v>
       </c>
       <c r="N73" s="1"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="38"/>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="51"/>
       <c r="B74" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1">
-        <v>6.7801109999999998E-2</v>
-      </c>
-      <c r="J74" s="1">
-        <v>1.328505E-2</v>
-      </c>
-      <c r="K74" s="1">
-        <v>13.75198</v>
-      </c>
-      <c r="L74" s="1">
-        <v>5.1035659999999998</v>
-      </c>
-      <c r="M74" s="2">
-        <v>1.698402E-4</v>
+      <c r="I74" s="45">
+        <v>-1.288595E-2</v>
+      </c>
+      <c r="J74" s="45">
+        <v>2.4782379999999998E-3</v>
+      </c>
+      <c r="K74" s="45">
+        <v>14.11434</v>
+      </c>
+      <c r="L74" s="45">
+        <v>-5.1996440000000002</v>
+      </c>
+      <c r="M74" s="45">
+        <v>1.3118094177569999E-4</v>
       </c>
       <c r="N74" s="1"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="36" t="s">
-        <v>24</v>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="49" t="s">
+        <v>30</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C75" s="1">
-        <v>-0.9841491</v>
-      </c>
-      <c r="D75" s="1">
-        <v>0.17118269999999999</v>
-      </c>
-      <c r="E75" s="1">
-        <v>23.803190000000001</v>
-      </c>
-      <c r="F75" s="1">
-        <v>-5.7491139999999996</v>
-      </c>
-      <c r="G75" s="2">
-        <v>6.5310590000000004E-6</v>
-      </c>
+      <c r="C75" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="39"/>
+      <c r="I75" s="1">
+        <v>-1.7348269999999999E-2</v>
+      </c>
+      <c r="J75" s="1">
+        <v>6.5396389999999999E-3</v>
+      </c>
+      <c r="K75" s="1">
+        <v>55.709558000000001</v>
+      </c>
+      <c r="L75" s="1">
+        <v>-2.652787</v>
+      </c>
+      <c r="M75" s="2">
+        <v>1.038058E-2</v>
+      </c>
       <c r="N75" s="1"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="50"/>
       <c r="B76" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="1">
-        <v>0.17573549999999999</v>
-      </c>
-      <c r="D76" s="1">
-        <v>0.1739916</v>
-      </c>
-      <c r="E76" s="1">
-        <v>33.744075000000002</v>
-      </c>
-      <c r="F76" s="1">
-        <v>1.0100229999999999</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.31967210000000001</v>
-      </c>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="39"/>
-      <c r="M76" s="39"/>
+      <c r="I76" s="1">
+        <v>1.2575930000000001E-2</v>
+      </c>
+      <c r="J76" s="1">
+        <v>7.0812319999999998E-3</v>
+      </c>
+      <c r="K76" s="1">
+        <v>54.114787999999997</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1.775952</v>
+      </c>
+      <c r="M76" s="3">
+        <v>8.1363409999999997E-2</v>
+      </c>
       <c r="N76" s="1"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="50"/>
       <c r="B77" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C77" s="1">
-        <v>-1.1202160000000001</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0.33875499999999997</v>
-      </c>
-      <c r="E77" s="1">
-        <v>14.597720000000001</v>
-      </c>
-      <c r="F77" s="1">
-        <v>-3.3068610000000001</v>
-      </c>
-      <c r="G77" s="2">
-        <v>4.9434029999999999E-3</v>
-      </c>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="39"/>
+      <c r="I77" s="1">
+        <v>3.5116069999999999E-2</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1.7176980000000001E-2</v>
+      </c>
+      <c r="K77" s="1">
+        <v>13.180910000000001</v>
+      </c>
+      <c r="L77" s="1">
+        <v>2.044368</v>
+      </c>
+      <c r="M77" s="3">
+        <v>6.1427379999999997E-2</v>
+      </c>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="38"/>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="51"/>
       <c r="B78" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="1">
-        <v>0.14184459999999999</v>
-      </c>
-      <c r="D78" s="1">
-        <v>0.38861230000000002</v>
-      </c>
-      <c r="E78" s="1">
-        <v>15.02059</v>
-      </c>
-      <c r="F78" s="1">
-        <v>0.36500280000000002</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.72019759999999999</v>
-      </c>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="39"/>
-      <c r="J78" s="39"/>
-      <c r="K78" s="39"/>
-      <c r="L78" s="39"/>
-      <c r="M78" s="39"/>
+      <c r="I78" s="1">
+        <v>6.7801109999999998E-2</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1.328505E-2</v>
+      </c>
+      <c r="K78" s="1">
+        <v>13.75198</v>
+      </c>
+      <c r="L78" s="1">
+        <v>5.1035659999999998</v>
+      </c>
+      <c r="M78" s="2">
+        <v>1.698402E-4</v>
+      </c>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="36" t="s">
-        <v>20</v>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
+        <v>24</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C79" s="1">
-        <v>1.6038840000000001</v>
+        <v>-0.9841491</v>
       </c>
       <c r="D79" s="1">
-        <v>0.37562440000000002</v>
+        <v>0.17118269999999999</v>
       </c>
       <c r="E79" s="1">
-        <v>26.557427000000001</v>
+        <v>23.803190000000001</v>
       </c>
       <c r="F79" s="1">
-        <v>4.2699150000000001</v>
+        <v>-5.7491139999999996</v>
       </c>
       <c r="G79" s="2">
-        <v>2.2222259999999999E-4</v>
+        <v>6.5310590000000004E-6</v>
       </c>
       <c r="H79" s="1"/>
-      <c r="I79" s="39" t="s">
+      <c r="I79" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J79" s="39"/>
-      <c r="K79" s="39"/>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="52"/>
+      <c r="M79" s="52"/>
       <c r="N79" s="1"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="50"/>
       <c r="B80" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C80" s="1">
-        <v>2.5716009999999998</v>
+        <v>0.17573549999999999</v>
       </c>
       <c r="D80" s="1">
-        <v>0.35089939999999997</v>
+        <v>0.1739916</v>
       </c>
       <c r="E80" s="1">
-        <v>36.412089999999999</v>
+        <v>33.744075000000002</v>
       </c>
       <c r="F80" s="1">
-        <v>7.3285999999999998</v>
-      </c>
-      <c r="G80" s="2">
-        <v>1.142512E-8</v>
+        <v>1.0100229999999999</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.31967210000000001</v>
       </c>
       <c r="H80" s="1"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
+      <c r="I80" s="52"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="52"/>
+      <c r="M80" s="52"/>
       <c r="N80" s="1"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="50"/>
       <c r="B81" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C81" s="1">
-        <v>0.61386540000000001</v>
+        <v>-1.1202160000000001</v>
       </c>
       <c r="D81" s="1">
-        <v>0.440166</v>
+        <v>0.33875499999999997</v>
       </c>
       <c r="E81" s="1">
-        <v>20.222460000000002</v>
+        <v>14.597720000000001</v>
       </c>
       <c r="F81" s="1">
-        <v>1.3946229999999999</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.17826230000000001</v>
+        <v>-3.3068610000000001</v>
+      </c>
+      <c r="G81" s="2">
+        <v>4.9434029999999999E-3</v>
       </c>
       <c r="H81" s="1"/>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39"/>
-      <c r="K81" s="39"/>
-      <c r="L81" s="39"/>
-      <c r="M81" s="39"/>
+      <c r="I81" s="52"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="52"/>
+      <c r="L81" s="52"/>
+      <c r="M81" s="52"/>
       <c r="N81" s="1"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="38"/>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="51"/>
       <c r="B82" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C82" s="1">
-        <v>1.3966069999999999</v>
+        <v>0.14184459999999999</v>
       </c>
       <c r="D82" s="1">
-        <v>0.56956130000000005</v>
+        <v>0.38861230000000002</v>
       </c>
       <c r="E82" s="1">
-        <v>13.935140000000001</v>
+        <v>15.02059</v>
       </c>
       <c r="F82" s="1">
-        <v>2.4520749999999998</v>
-      </c>
-      <c r="G82" s="2">
-        <v>2.8002340000000001E-2</v>
+        <v>0.36500280000000002</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.72019759999999999</v>
       </c>
       <c r="H82" s="1"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
-      <c r="L82" s="39"/>
-      <c r="M82" s="39"/>
+      <c r="I82" s="52"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="52"/>
+      <c r="L82" s="52"/>
+      <c r="M82" s="52"/>
       <c r="N82" s="1"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="36" t="s">
-        <v>21</v>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="49" t="s">
+        <v>20</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C83" s="1">
-        <v>16.64274</v>
+        <v>1.6038840000000001</v>
       </c>
       <c r="D83" s="1">
-        <v>1.1608540000000001</v>
+        <v>0.37562440000000002</v>
       </c>
       <c r="E83" s="1">
-        <v>4.8165345999999998</v>
+        <v>26.557427000000001</v>
       </c>
       <c r="F83" s="1">
-        <v>14.33663</v>
+        <v>4.2699150000000001</v>
       </c>
       <c r="G83" s="2">
-        <v>3.9052140000000001E-5</v>
+        <v>2.2222259999999999E-4</v>
       </c>
       <c r="H83" s="1"/>
-      <c r="I83" s="39" t="s">
+      <c r="I83" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J83" s="39"/>
-      <c r="K83" s="39"/>
-      <c r="L83" s="39"/>
-      <c r="M83" s="39"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="52"/>
+      <c r="M83" s="52"/>
       <c r="N83" s="1"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="50"/>
       <c r="B84" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C84" s="1">
-        <v>19.986529999999998</v>
+        <v>2.5716009999999998</v>
       </c>
       <c r="D84" s="1">
-        <v>0.71962550000000003</v>
+        <v>0.35089939999999997</v>
       </c>
       <c r="E84" s="1">
-        <v>35.025179999999999</v>
+        <v>36.412089999999999</v>
       </c>
       <c r="F84" s="1">
-        <v>27.773520000000001</v>
+        <v>7.3285999999999998</v>
       </c>
       <c r="G84" s="2">
-        <v>1.9085240000000001E-25</v>
+        <v>1.142512E-8</v>
       </c>
       <c r="H84" s="1"/>
-      <c r="I84" s="39"/>
-      <c r="J84" s="39"/>
-      <c r="K84" s="39"/>
-      <c r="L84" s="39"/>
-      <c r="M84" s="39"/>
+      <c r="I84" s="52"/>
+      <c r="J84" s="52"/>
+      <c r="K84" s="52"/>
+      <c r="L84" s="52"/>
+      <c r="M84" s="52"/>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="50"/>
       <c r="B85" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C85" s="1">
-        <v>-4.4803540000000002</v>
+        <v>0.61386540000000001</v>
       </c>
       <c r="D85" s="1">
-        <v>1.6178699999999999</v>
+        <v>0.440166</v>
       </c>
       <c r="E85" s="1">
-        <v>15.836600000000001</v>
+        <v>20.222460000000002</v>
       </c>
       <c r="F85" s="1">
-        <v>-2.7692920000000001</v>
-      </c>
-      <c r="G85" s="2">
-        <v>1.377838E-2</v>
+        <v>1.3946229999999999</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.17826230000000001</v>
       </c>
       <c r="H85" s="1"/>
-      <c r="I85" s="39"/>
-      <c r="J85" s="39"/>
-      <c r="K85" s="39"/>
-      <c r="L85" s="39"/>
-      <c r="M85" s="39"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="52"/>
+      <c r="K85" s="52"/>
+      <c r="L85" s="52"/>
+      <c r="M85" s="52"/>
       <c r="N85" s="1"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="38"/>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="51"/>
       <c r="B86" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C86" s="1">
-        <v>-0.82880399999999999</v>
+        <v>1.3966069999999999</v>
       </c>
       <c r="D86" s="1">
-        <v>1.112787</v>
+        <v>0.56956130000000005</v>
       </c>
       <c r="E86" s="1">
-        <v>15.309240000000001</v>
+        <v>13.935140000000001</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.74480009999999996</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.46767300000000001</v>
+        <v>2.4520749999999998</v>
+      </c>
+      <c r="G86" s="2">
+        <v>2.8002340000000001E-2</v>
       </c>
       <c r="H86" s="1"/>
-      <c r="I86" s="39"/>
-      <c r="J86" s="39"/>
-      <c r="K86" s="39"/>
-      <c r="L86" s="39"/>
-      <c r="M86" s="39"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="52"/>
+      <c r="L86" s="52"/>
+      <c r="M86" s="52"/>
       <c r="N86" s="1"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="36" t="s">
-        <v>25</v>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="49" t="s">
+        <v>21</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C87" s="1">
-        <v>0.28573979999999999</v>
+        <v>16.64274</v>
       </c>
       <c r="D87" s="1">
-        <v>2.892964E-2</v>
+        <v>1.1608540000000001</v>
       </c>
       <c r="E87" s="1">
-        <v>20.899597</v>
+        <v>4.8165345999999998</v>
       </c>
       <c r="F87" s="1">
-        <v>9.8770609999999994</v>
+        <v>14.33663</v>
       </c>
       <c r="G87" s="2">
-        <v>2.5221599999999999E-9</v>
+        <v>3.9052140000000001E-5</v>
       </c>
       <c r="H87" s="1"/>
-      <c r="I87" s="39" t="s">
+      <c r="I87" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J87" s="39"/>
-      <c r="K87" s="39"/>
-      <c r="L87" s="39"/>
-      <c r="M87" s="39"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="37"/>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="50"/>
       <c r="B88" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C88" s="1">
-        <v>0.38685409999999998</v>
+        <v>19.986529999999998</v>
       </c>
       <c r="D88" s="1">
-        <v>2.990483E-2</v>
+        <v>0.71962550000000003</v>
       </c>
       <c r="E88" s="1">
-        <v>24.614989999999999</v>
+        <v>35.025179999999999</v>
       </c>
       <c r="F88" s="1">
-        <v>12.936170000000001</v>
+        <v>27.773520000000001</v>
       </c>
       <c r="G88" s="2">
-        <v>1.7821690000000001E-12</v>
+        <v>1.9085240000000001E-25</v>
       </c>
       <c r="H88" s="1"/>
-      <c r="I88" s="39"/>
-      <c r="J88" s="39"/>
-      <c r="K88" s="39"/>
-      <c r="L88" s="39"/>
-      <c r="M88" s="39"/>
+      <c r="I88" s="52"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="52"/>
+      <c r="L88" s="52"/>
+      <c r="M88" s="52"/>
       <c r="N88" s="1"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="37"/>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="50"/>
       <c r="B89" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C89" s="1">
-        <v>2.0270739999999999E-2</v>
+        <v>-4.4803540000000002</v>
       </c>
       <c r="D89" s="1">
-        <v>2.7636999999999998E-2</v>
+        <v>1.6178699999999999</v>
       </c>
       <c r="E89" s="1">
-        <v>40</v>
+        <v>15.836600000000001</v>
       </c>
       <c r="F89" s="1">
-        <v>0.733464</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.46755279999999999</v>
+        <v>-2.7692920000000001</v>
+      </c>
+      <c r="G89" s="2">
+        <v>1.377838E-2</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="39"/>
-      <c r="K89" s="39"/>
-      <c r="L89" s="39"/>
-      <c r="M89" s="39"/>
+      <c r="I89" s="52"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="52"/>
+      <c r="L89" s="52"/>
+      <c r="M89" s="52"/>
       <c r="N89" s="1"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="38"/>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="51"/>
       <c r="B90" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C90" s="1">
-        <v>0.13333100000000001</v>
+        <v>-0.82880399999999999</v>
       </c>
       <c r="D90" s="1">
-        <v>5.6024570000000003E-2</v>
+        <v>1.112787</v>
       </c>
       <c r="E90" s="1">
-        <v>8.8358460000000001</v>
+        <v>15.309240000000001</v>
       </c>
       <c r="F90" s="1">
-        <v>2.3798659999999998</v>
-      </c>
-      <c r="G90" s="2">
-        <v>4.1726619999999999E-2</v>
+        <v>-0.74480009999999996</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.46767300000000001</v>
       </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="39"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="39"/>
-      <c r="L90" s="39"/>
-      <c r="M90" s="39"/>
+      <c r="I90" s="52"/>
+      <c r="J90" s="52"/>
+      <c r="K90" s="52"/>
+      <c r="L90" s="52"/>
+      <c r="M90" s="52"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91" s="36" t="s">
-        <v>36</v>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="49" t="s">
+        <v>25</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C91" s="1">
-        <v>1.3623919999999999E-2</v>
+        <v>0.28573979999999999</v>
       </c>
       <c r="D91" s="1">
-        <v>1.319795E-2</v>
+        <v>2.892964E-2</v>
       </c>
       <c r="E91" s="1">
-        <v>31</v>
+        <v>20.899597</v>
       </c>
       <c r="F91" s="1">
-        <v>1.032276</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.30992960000000003</v>
+        <v>9.8770609999999994</v>
+      </c>
+      <c r="G91" s="2">
+        <v>2.5221599999999999E-9</v>
       </c>
       <c r="H91" s="1"/>
-      <c r="I91" s="39" t="s">
+      <c r="I91" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J91" s="39"/>
-      <c r="K91" s="39"/>
-      <c r="L91" s="39"/>
-      <c r="M91" s="39"/>
+      <c r="J91" s="52"/>
+      <c r="K91" s="52"/>
+      <c r="L91" s="52"/>
+      <c r="M91" s="52"/>
       <c r="N91" s="1"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="37"/>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="50"/>
       <c r="B92" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C92" s="1">
-        <v>7.6710570000000006E-2</v>
+        <v>0.38685409999999998</v>
       </c>
       <c r="D92" s="1">
-        <v>8.8472120000000001E-3</v>
+        <v>2.990483E-2</v>
       </c>
       <c r="E92" s="1">
-        <v>43</v>
+        <v>24.614989999999999</v>
       </c>
       <c r="F92" s="1">
-        <v>8.6705930000000002</v>
+        <v>12.936170000000001</v>
       </c>
       <c r="G92" s="2">
-        <v>5.4385229999999998E-11</v>
+        <v>1.7821690000000001E-12</v>
       </c>
       <c r="H92" s="1"/>
-      <c r="I92" s="39"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="39"/>
-      <c r="L92" s="39"/>
-      <c r="M92" s="39"/>
+      <c r="I92" s="52"/>
+      <c r="J92" s="52"/>
+      <c r="K92" s="52"/>
+      <c r="L92" s="52"/>
+      <c r="M92" s="52"/>
       <c r="N92" s="1"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="37"/>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="50"/>
       <c r="B93" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C93" s="1">
-        <v>-6.9491259999999999E-2</v>
+        <v>2.0270739999999999E-2</v>
       </c>
       <c r="D93" s="1">
-        <v>1.0221040000000001E-2</v>
+        <v>2.7636999999999998E-2</v>
       </c>
       <c r="E93" s="1">
-        <v>12.84778</v>
+        <v>40</v>
       </c>
       <c r="F93" s="1">
-        <v>-6.7988470000000003</v>
-      </c>
-      <c r="G93" s="2">
-        <v>1.343811E-5</v>
+        <v>0.733464</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.46755279999999999</v>
       </c>
       <c r="H93" s="1"/>
-      <c r="I93" s="39"/>
-      <c r="J93" s="39"/>
-      <c r="K93" s="39"/>
-      <c r="L93" s="39"/>
-      <c r="M93" s="39"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="52"/>
+      <c r="M93" s="52"/>
       <c r="N93" s="1"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="38"/>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="51"/>
       <c r="B94" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C94" s="1">
-        <v>-6.8129929999999998E-3</v>
+        <v>0.13333100000000001</v>
       </c>
       <c r="D94" s="1">
-        <v>1.1591260000000001E-2</v>
+        <v>5.6024570000000003E-2</v>
       </c>
       <c r="E94" s="1">
-        <v>34</v>
+        <v>8.8358460000000001</v>
       </c>
       <c r="F94" s="1">
-        <v>-0.58776980000000001</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0.56057069999999998</v>
+        <v>2.3798659999999998</v>
+      </c>
+      <c r="G94" s="2">
+        <v>4.1726619999999999E-2</v>
       </c>
       <c r="H94" s="1"/>
-      <c r="I94" s="39"/>
-      <c r="J94" s="39"/>
-      <c r="K94" s="39"/>
-      <c r="L94" s="39"/>
-      <c r="M94" s="39"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+      <c r="L94" s="52"/>
+      <c r="M94" s="52"/>
       <c r="N94" s="1"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="36" t="s">
-        <v>26</v>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="49" t="s">
+        <v>36</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C95" s="1">
-        <v>0.29603849999999998</v>
+        <v>1.3623919999999999E-2</v>
       </c>
       <c r="D95" s="1">
-        <v>3.2874760000000003E-2</v>
+        <v>1.319795E-2</v>
       </c>
       <c r="E95" s="1">
-        <v>18.839901000000001</v>
+        <v>31</v>
       </c>
       <c r="F95" s="1">
-        <v>9.0050399999999993</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2.974355E-8</v>
+        <v>1.032276</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.30992960000000003</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="I95" s="39" t="s">
+      <c r="I95" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="J95" s="39"/>
-      <c r="K95" s="39"/>
-      <c r="L95" s="39"/>
-      <c r="M95" s="39"/>
+      <c r="J95" s="52"/>
+      <c r="K95" s="52"/>
+      <c r="L95" s="52"/>
+      <c r="M95" s="52"/>
       <c r="N95" s="1"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="37"/>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="50"/>
       <c r="B96" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C96" s="1">
-        <v>0.48750929999999998</v>
+        <v>7.6710570000000006E-2</v>
       </c>
       <c r="D96" s="1">
-        <v>2.0179229999999999E-2</v>
+        <v>8.8472120000000001E-3</v>
       </c>
       <c r="E96" s="1">
-        <v>33.068705000000001</v>
+        <v>43</v>
       </c>
       <c r="F96" s="1">
-        <v>24.15896</v>
+        <v>8.6705930000000002</v>
       </c>
       <c r="G96" s="2">
-        <v>1.3818109999999999E-22</v>
+        <v>5.4385229999999998E-11</v>
       </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="39"/>
-      <c r="J96" s="39"/>
-      <c r="K96" s="39"/>
-      <c r="L96" s="39"/>
-      <c r="M96" s="39"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="52"/>
+      <c r="K96" s="52"/>
+      <c r="L96" s="52"/>
+      <c r="M96" s="52"/>
       <c r="N96" s="1"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="37"/>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="50"/>
       <c r="B97" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C97" s="1">
-        <v>-4.929849E-2</v>
+        <v>-6.9491259999999999E-2</v>
       </c>
       <c r="D97" s="1">
-        <v>3.1121630000000001E-2</v>
+        <v>1.0221040000000001E-2</v>
       </c>
       <c r="E97" s="1">
-        <v>4.2666779999999997</v>
+        <v>12.84778</v>
       </c>
       <c r="F97" s="1">
-        <v>-1.5840590000000001</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0.18392030000000001</v>
+        <v>-6.7988470000000003</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1.343811E-5</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
-      <c r="K97" s="39"/>
-      <c r="L97" s="39"/>
-      <c r="M97" s="39"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="52"/>
+      <c r="K97" s="52"/>
+      <c r="L97" s="52"/>
+      <c r="M97" s="52"/>
       <c r="N97" s="1"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A98" s="38"/>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="51"/>
       <c r="B98" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C98" s="1">
+        <v>-6.8129929999999998E-3</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1.1591260000000001E-2</v>
+      </c>
+      <c r="E98" s="1">
+        <v>34</v>
+      </c>
+      <c r="F98" s="1">
+        <v>-0.58776980000000001</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.56057069999999998</v>
+      </c>
+      <c r="H98" s="1"/>
+      <c r="I98" s="52"/>
+      <c r="J98" s="52"/>
+      <c r="K98" s="52"/>
+      <c r="L98" s="52"/>
+      <c r="M98" s="52"/>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" s="45">
+        <v>2.012891E-5</v>
+      </c>
+      <c r="D99" s="45">
+        <v>4.0825490000000002E-4</v>
+      </c>
+      <c r="E99" s="45">
+        <v>25.336739999999999</v>
+      </c>
+      <c r="F99" s="45">
+        <v>4.9304760000000003E-2</v>
+      </c>
+      <c r="G99" s="45">
+        <v>0.96106304949900001</v>
+      </c>
+      <c r="H99" s="1"/>
+      <c r="I99" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="J99" s="52"/>
+      <c r="K99" s="52"/>
+      <c r="L99" s="52"/>
+      <c r="M99" s="52"/>
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="50"/>
+      <c r="B100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C100" s="45">
+        <v>8.7200299999999999E-4</v>
+      </c>
+      <c r="D100" s="45">
+        <v>7.1735829999999997E-4</v>
+      </c>
+      <c r="E100" s="45">
+        <v>43</v>
+      </c>
+      <c r="F100" s="45">
+        <v>1.2155750000000001</v>
+      </c>
+      <c r="G100" s="46">
+        <v>0.2307786</v>
+      </c>
+      <c r="H100" s="1"/>
+      <c r="I100" s="52"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
+      <c r="L100" s="52"/>
+      <c r="M100" s="52"/>
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="50"/>
+      <c r="B101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C101" s="45">
+        <v>-2.0367390000000001E-3</v>
+      </c>
+      <c r="D101" s="45">
+        <v>6.5130869999999999E-4</v>
+      </c>
+      <c r="E101" s="45">
+        <v>40</v>
+      </c>
+      <c r="F101" s="45">
+        <v>-3.127148</v>
+      </c>
+      <c r="G101" s="46">
+        <v>3.2851500000000001E-3</v>
+      </c>
+      <c r="H101" s="1"/>
+      <c r="I101" s="52"/>
+      <c r="J101" s="52"/>
+      <c r="K101" s="52"/>
+      <c r="L101" s="52"/>
+      <c r="M101" s="52"/>
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="51"/>
+      <c r="B102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C102" s="45">
+        <v>-1.576327E-3</v>
+      </c>
+      <c r="D102" s="45">
+        <v>8.643317E-4</v>
+      </c>
+      <c r="E102" s="45">
+        <v>11.874320000000001</v>
+      </c>
+      <c r="F102" s="45">
+        <v>-1.823752</v>
+      </c>
+      <c r="G102" s="46">
+        <v>9.3442800000000006E-2</v>
+      </c>
+      <c r="H102" s="1"/>
+      <c r="I102" s="52"/>
+      <c r="J102" s="52"/>
+      <c r="K102" s="52"/>
+      <c r="L102" s="52"/>
+      <c r="M102" s="52"/>
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.29603849999999998</v>
+      </c>
+      <c r="D103" s="1">
+        <v>3.2874760000000003E-2</v>
+      </c>
+      <c r="E103" s="1">
+        <v>18.839901000000001</v>
+      </c>
+      <c r="F103" s="1">
+        <v>9.0050399999999993</v>
+      </c>
+      <c r="G103" s="2">
+        <v>2.974355E-8</v>
+      </c>
+      <c r="H103" s="1"/>
+      <c r="I103" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="J103" s="52"/>
+      <c r="K103" s="52"/>
+      <c r="L103" s="52"/>
+      <c r="M103" s="52"/>
+      <c r="N103" s="1"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="50"/>
+      <c r="B104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" s="1">
+        <v>0.48750929999999998</v>
+      </c>
+      <c r="D104" s="1">
+        <v>2.0179229999999999E-2</v>
+      </c>
+      <c r="E104" s="1">
+        <v>33.068705000000001</v>
+      </c>
+      <c r="F104" s="1">
+        <v>24.15896</v>
+      </c>
+      <c r="G104" s="2">
+        <v>1.3818109999999999E-22</v>
+      </c>
+      <c r="H104" s="1"/>
+      <c r="I104" s="52"/>
+      <c r="J104" s="52"/>
+      <c r="K104" s="52"/>
+      <c r="L104" s="52"/>
+      <c r="M104" s="52"/>
+      <c r="N104" s="1"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="50"/>
+      <c r="B105" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C105" s="1">
+        <v>-4.929849E-2</v>
+      </c>
+      <c r="D105" s="1">
+        <v>3.1121630000000001E-2</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4.2666779999999997</v>
+      </c>
+      <c r="F105" s="1">
+        <v>-1.5840590000000001</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.18392030000000001</v>
+      </c>
+      <c r="H105" s="1"/>
+      <c r="I105" s="52"/>
+      <c r="J105" s="52"/>
+      <c r="K105" s="52"/>
+      <c r="L105" s="52"/>
+      <c r="M105" s="52"/>
+      <c r="N105" s="1"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="51"/>
+      <c r="B106" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" s="1">
         <v>0.15619479999999999</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D106" s="1">
         <v>2.6369159999999999E-2</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E106" s="1">
         <v>5.0675150000000002</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F106" s="1">
         <v>5.9233900000000004</v>
       </c>
-      <c r="G98" s="2">
+      <c r="G106" s="2">
         <v>1.86768E-3</v>
       </c>
-      <c r="H98" s="1"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="39"/>
-      <c r="K98" s="39"/>
-      <c r="L98" s="39"/>
-      <c r="M98" s="39"/>
-      <c r="N98" s="1"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="52"/>
+      <c r="J106" s="52"/>
+      <c r="K106" s="52"/>
+      <c r="L106" s="52"/>
+      <c r="M106" s="52"/>
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="6"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="6"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="C67:G70"/>
-    <mergeCell ref="I51:M54"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="I63:M66"/>
+  <mergeCells count="45">
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
@@ -10366,8 +10598,6 @@
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="C59:G62"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="A39:A42"/>
@@ -10377,20 +10607,32 @@
     <mergeCell ref="C47:G50"/>
     <mergeCell ref="A43:A46"/>
     <mergeCell ref="C43:G46"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="I79:M82"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="I83:M86"/>
     <mergeCell ref="A71:A74"/>
     <mergeCell ref="C71:G74"/>
+    <mergeCell ref="I51:M54"/>
+    <mergeCell ref="I55:M58"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="I67:M70"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="C63:G66"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
     <mergeCell ref="A75:A78"/>
-    <mergeCell ref="I75:M78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="I79:M82"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="I103:M106"/>
     <mergeCell ref="A91:A94"/>
     <mergeCell ref="I91:M94"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="I95:M98"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1279" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2390976E-4F24-4B7F-A5C6-375CD9B01615}"/>
+  <xr:revisionPtr revIDLastSave="1360" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{359C411E-E97C-4AF5-A0DA-89B201753963}"/>
   <bookViews>
-    <workbookView xWindow="16095" yWindow="0" windowWidth="12705" windowHeight="15600" firstSheet="2" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -143,9 +143,6 @@
     <t>Lat Branches</t>
   </si>
   <si>
-    <t>Fruit Number - log</t>
-  </si>
-  <si>
     <t>Fitness</t>
   </si>
   <si>
@@ -522,13 +519,16 @@
   </si>
   <si>
     <t>dry repro G - log - harvest</t>
+  </si>
+  <si>
+    <t>Fruit Number - BL counts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,6 +570,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF009999"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -946,7 +952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1036,6 +1042,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1043,9 +1052,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1087,6 +1093,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1463,24 +1479,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="53">
+      <c r="C1" s="54">
         <v>2021</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="53">
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="54">
         <v>2022</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1494,7 +1510,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -1506,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>2</v>
@@ -1515,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>4</v>
@@ -1527,12 +1543,12 @@
         <v>6</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -1575,7 +1591,7 @@
         <v>2.27699983576885E-5</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1669,14 +1685,14 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1700,7 +1716,7 @@
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>9</v>
@@ -1835,14 +1851,14 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="51"/>
       <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1891,7 +1907,7 @@
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K11" s="52"/>
       <c r="L11" s="52"/>
@@ -1967,14 +1983,14 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
       <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
       <c r="I14" s="1"/>
       <c r="J14" s="52"/>
       <c r="K14" s="52"/>
@@ -1986,7 +2002,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -2011,7 +2027,7 @@
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K15" s="52"/>
       <c r="L15" s="52"/>
@@ -2086,14 +2102,14 @@
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="51"/>
       <c r="B18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
       <c r="I18" s="1"/>
       <c r="J18" s="52"/>
       <c r="K18" s="52"/>
@@ -2240,14 +2256,14 @@
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
       <c r="B22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2271,7 +2287,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
@@ -2406,14 +2422,14 @@
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="51"/>
       <c r="B26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2572,14 +2588,14 @@
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="51"/>
       <c r="B30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2738,14 +2754,14 @@
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2904,14 +2920,14 @@
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51"/>
       <c r="B38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -3070,14 +3086,14 @@
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="51"/>
       <c r="B42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3236,14 +3252,14 @@
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="51"/>
       <c r="B46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3402,14 +3418,14 @@
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="51"/>
       <c r="B50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3433,13 +3449,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -3534,7 +3550,7 @@
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="51"/>
       <c r="B54" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="52"/>
       <c r="D54" s="52"/>
@@ -3565,7 +3581,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
@@ -3608,7 +3624,7 @@
         <v>5.4997814524115098E-3</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -3702,14 +3718,14 @@
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="51"/>
       <c r="B58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3733,7 +3749,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
@@ -3758,7 +3774,7 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K59" s="52"/>
       <c r="L59" s="52"/>
@@ -3834,14 +3850,14 @@
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="51"/>
       <c r="B62" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C62" s="56"/>
-      <c r="D62" s="56"/>
-      <c r="E62" s="56"/>
-      <c r="F62" s="56"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="53"/>
       <c r="I62" s="1"/>
       <c r="J62" s="52"/>
       <c r="K62" s="52"/>
@@ -3853,13 +3869,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -3954,7 +3970,7 @@
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="51"/>
       <c r="B66" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C66" s="52"/>
       <c r="D66" s="52"/>
@@ -3985,13 +4001,13 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D67" s="52"/>
       <c r="E67" s="52"/>
@@ -4086,7 +4102,7 @@
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="51"/>
       <c r="B70" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C70" s="52"/>
       <c r="D70" s="52"/>
@@ -4117,7 +4133,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
@@ -4142,7 +4158,7 @@
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K71" s="52"/>
       <c r="L71" s="52"/>
@@ -4218,14 +4234,14 @@
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="51"/>
       <c r="B74" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-      <c r="F74" s="56"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
       <c r="I74" s="1"/>
       <c r="J74" s="52"/>
       <c r="K74" s="52"/>
@@ -4243,7 +4259,7 @@
         <v>9</v>
       </c>
       <c r="C75" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D75" s="52"/>
       <c r="E75" s="52"/>
@@ -4338,7 +4354,7 @@
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="51"/>
       <c r="B78" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C78" s="52"/>
       <c r="D78" s="52"/>
@@ -4394,7 +4410,7 @@
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K79" s="52"/>
       <c r="L79" s="52"/>
@@ -4470,14 +4486,14 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="51"/>
       <c r="B82" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C82" s="56"/>
-      <c r="D82" s="56"/>
-      <c r="E82" s="56"/>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
       <c r="I82" s="1"/>
       <c r="J82" s="52"/>
       <c r="K82" s="52"/>
@@ -4489,13 +4505,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -4590,7 +4606,7 @@
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="51"/>
       <c r="B86" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C86" s="52"/>
       <c r="D86" s="52"/>
@@ -4621,7 +4637,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
@@ -4646,7 +4662,7 @@
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K87" s="52"/>
       <c r="L87" s="52"/>
@@ -4722,14 +4738,14 @@
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="51"/>
       <c r="B90" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" s="56"/>
-      <c r="D90" s="56"/>
-      <c r="E90" s="56"/>
-      <c r="F90" s="56"/>
-      <c r="G90" s="56"/>
-      <c r="H90" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="53"/>
       <c r="I90" s="1"/>
       <c r="J90" s="52"/>
       <c r="K90" s="52"/>
@@ -4766,7 +4782,7 @@
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K91" s="52"/>
       <c r="L91" s="52"/>
@@ -4842,14 +4858,14 @@
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="51"/>
       <c r="B94" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C94" s="56"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="56"/>
-      <c r="F94" s="56"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
       <c r="I94" s="1"/>
       <c r="J94" s="52"/>
       <c r="K94" s="52"/>
@@ -4886,7 +4902,7 @@
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K95" s="52"/>
       <c r="L95" s="52"/>
@@ -4962,14 +4978,14 @@
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="51"/>
       <c r="B98" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C98" s="56"/>
-      <c r="D98" s="56"/>
-      <c r="E98" s="56"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="56"/>
-      <c r="H98" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
       <c r="I98" s="1"/>
       <c r="J98" s="52"/>
       <c r="K98" s="52"/>
@@ -4981,7 +4997,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>9</v>
@@ -5006,7 +5022,7 @@
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K99" s="52"/>
       <c r="L99" s="52"/>
@@ -5082,14 +5098,14 @@
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="51"/>
       <c r="B102" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="56"/>
-      <c r="G102" s="56"/>
-      <c r="H102" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C102" s="53"/>
+      <c r="D102" s="53"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="53"/>
       <c r="I102" s="1"/>
       <c r="J102" s="52"/>
       <c r="K102" s="52"/>
@@ -5101,13 +5117,13 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D103" s="52"/>
       <c r="E103" s="52"/>
@@ -5202,7 +5218,7 @@
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="51"/>
       <c r="B106" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C106" s="52"/>
       <c r="D106" s="52"/>
@@ -5233,13 +5249,13 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="52"/>
@@ -5334,7 +5350,7 @@
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="51"/>
       <c r="B110" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C110" s="52"/>
       <c r="D110" s="52"/>
@@ -5390,7 +5406,7 @@
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K111" s="52"/>
       <c r="L111" s="52"/>
@@ -5466,14 +5482,14 @@
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="51"/>
       <c r="B114" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C114" s="56"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="56"/>
-      <c r="H114" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C114" s="53"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="53"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="53"/>
       <c r="I114" s="1"/>
       <c r="J114" s="52"/>
       <c r="K114" s="52"/>
@@ -5510,7 +5526,7 @@
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K115" s="52"/>
       <c r="L115" s="52"/>
@@ -5586,14 +5602,14 @@
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="51"/>
       <c r="B118" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C118" s="56"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="56"/>
-      <c r="F118" s="56"/>
-      <c r="G118" s="56"/>
-      <c r="H118" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C118" s="53"/>
+      <c r="D118" s="53"/>
+      <c r="E118" s="53"/>
+      <c r="F118" s="53"/>
+      <c r="G118" s="53"/>
+      <c r="H118" s="53"/>
       <c r="I118" s="1"/>
       <c r="J118" s="52"/>
       <c r="K118" s="52"/>
@@ -5630,7 +5646,7 @@
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K119" s="52"/>
       <c r="L119" s="52"/>
@@ -5706,14 +5722,14 @@
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="51"/>
       <c r="B122" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C122" s="56"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="56"/>
-      <c r="F122" s="56"/>
-      <c r="G122" s="56"/>
-      <c r="H122" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="53"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
       <c r="I122" s="1"/>
       <c r="J122" s="52"/>
       <c r="K122" s="52"/>
@@ -5724,33 +5740,33 @@
       <c r="P122" s="1"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="49" t="s">
-        <v>25</v>
+      <c r="A123" s="70" t="s">
+        <v>151</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1">
-        <v>8.1889606725674895</v>
+        <v>6176915.5049999999</v>
       </c>
       <c r="D123" s="1">
-        <v>8.1889606725674895</v>
+        <v>6176915.5049999999</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
       </c>
       <c r="F123" s="1">
-        <v>38.960439075121599</v>
+        <v>71.888440000000003</v>
       </c>
       <c r="G123" s="1">
-        <v>229.518131380033</v>
+        <v>167.3449876</v>
       </c>
       <c r="H123" s="4">
-        <v>6.3990332076812E-18</v>
+        <v>1.898803E-20</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K123" s="52"/>
       <c r="L123" s="52"/>
@@ -5760,27 +5776,27 @@
       <c r="P123" s="1"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" s="50"/>
+      <c r="A124" s="71"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="1">
-        <v>0.23039707874839899</v>
+        <v>50157.928</v>
       </c>
       <c r="D124" s="1">
-        <v>0.23039707874839899</v>
+        <v>50157.928</v>
       </c>
       <c r="E124" s="1">
         <v>1</v>
       </c>
       <c r="F124" s="1">
-        <v>4.1944106114323096</v>
+        <v>17.04102</v>
       </c>
       <c r="G124" s="1">
-        <v>6.45751141129504</v>
-      </c>
-      <c r="H124" s="3">
-        <v>6.1070966449770503E-2</v>
+        <v>1.3588785000000001</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0.2597892</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="52"/>
@@ -5792,27 +5808,27 @@
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="50"/>
+      <c r="A125" s="71"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="1">
-        <v>0.24741116524293899</v>
+        <v>5310.1710000000003</v>
       </c>
       <c r="D125" s="1">
-        <v>0.24741116524293899</v>
+        <v>5310.1710000000003</v>
       </c>
       <c r="E125" s="1">
         <v>1</v>
       </c>
       <c r="F125" s="1">
-        <v>38.960439070902197</v>
+        <v>71.888440000000003</v>
       </c>
       <c r="G125" s="1">
-        <v>6.9343779509581998</v>
-      </c>
-      <c r="H125" s="2">
-        <v>1.2062369794193201E-2</v>
+        <v>0.1438632</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0.7055884</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="52"/>
@@ -5824,16 +5840,16 @@
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="51"/>
+      <c r="A126" s="72"/>
       <c r="B126" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C126" s="56"/>
-      <c r="D126" s="56"/>
-      <c r="E126" s="56"/>
-      <c r="F126" s="56"/>
-      <c r="G126" s="56"/>
-      <c r="H126" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C126" s="53"/>
+      <c r="D126" s="53"/>
+      <c r="E126" s="53"/>
+      <c r="F126" s="53"/>
+      <c r="G126" s="53"/>
+      <c r="H126" s="53"/>
       <c r="I126" s="1"/>
       <c r="J126" s="52"/>
       <c r="K126" s="52"/>
@@ -5845,7 +5861,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
@@ -5870,7 +5886,7 @@
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K127" s="52"/>
       <c r="L127" s="52"/>
@@ -5946,14 +5962,14 @@
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="51"/>
       <c r="B130" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C130" s="56"/>
-      <c r="D130" s="56"/>
-      <c r="E130" s="56"/>
-      <c r="F130" s="56"/>
-      <c r="G130" s="56"/>
-      <c r="H130" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C130" s="53"/>
+      <c r="D130" s="53"/>
+      <c r="E130" s="53"/>
+      <c r="F130" s="53"/>
+      <c r="G130" s="53"/>
+      <c r="H130" s="53"/>
       <c r="I130" s="1"/>
       <c r="J130" s="52"/>
       <c r="K130" s="52"/>
@@ -5965,7 +5981,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
@@ -5990,7 +6006,7 @@
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K131" s="52"/>
       <c r="L131" s="52"/>
@@ -6066,14 +6082,14 @@
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="51"/>
       <c r="B134" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C134" s="56"/>
-      <c r="D134" s="56"/>
-      <c r="E134" s="56"/>
-      <c r="F134" s="56"/>
-      <c r="G134" s="56"/>
-      <c r="H134" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C134" s="53"/>
+      <c r="D134" s="53"/>
+      <c r="E134" s="53"/>
+      <c r="F134" s="53"/>
+      <c r="G134" s="53"/>
+      <c r="H134" s="53"/>
       <c r="I134" s="1"/>
       <c r="J134" s="52"/>
       <c r="K134" s="52"/>
@@ -6085,32 +6101,32 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C135" s="1">
-        <v>11.0082179168385</v>
+        <v>11.200752100000001</v>
       </c>
       <c r="D135" s="1">
-        <v>11.0082179168385</v>
+        <v>11.200752100000001</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
       </c>
       <c r="F135" s="1">
-        <v>48.794824022977402</v>
+        <v>51.667794999999998</v>
       </c>
       <c r="G135" s="1">
-        <v>408.97170017139501</v>
+        <v>471.893664</v>
       </c>
       <c r="H135" s="4">
-        <v>2.2809234413835001E-25</v>
+        <v>1.209274E-27</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K135" s="52"/>
       <c r="L135" s="52"/>
@@ -6125,22 +6141,22 @@
         <v>7</v>
       </c>
       <c r="C136" s="1">
-        <v>0.12480779741629899</v>
+        <v>0.12802530000000001</v>
       </c>
       <c r="D136" s="1">
-        <v>0.12480779741629899</v>
+        <v>0.12802530000000001</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
       </c>
       <c r="F136" s="1">
-        <v>6.2935571141001798</v>
+        <v>6.2246040000000002</v>
       </c>
       <c r="G136" s="1">
-        <v>4.6367956638934302</v>
-      </c>
-      <c r="H136" s="3">
-        <v>7.2640986050278702E-2</v>
+        <v>5.3937730000000004</v>
+      </c>
+      <c r="H136" s="4">
+        <v>5.7713939999999998E-2</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="52"/>
@@ -6157,22 +6173,22 @@
         <v>8</v>
       </c>
       <c r="C137" s="1">
-        <v>0.74925429491560802</v>
+        <v>0.70815150000000004</v>
       </c>
       <c r="D137" s="1">
-        <v>0.74925429491560802</v>
+        <v>0.70815150000000004</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
       </c>
       <c r="F137" s="1">
-        <v>48.794824017520803</v>
+        <v>51.667794999999998</v>
       </c>
       <c r="G137" s="1">
-        <v>27.8359136026586</v>
+        <v>29.834802</v>
       </c>
       <c r="H137" s="4">
-        <v>3.01236497113781E-6</v>
+        <v>1.363103E-6</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="52"/>
@@ -6186,14 +6202,14 @@
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="51"/>
       <c r="B138" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C138" s="56"/>
-      <c r="D138" s="56"/>
-      <c r="E138" s="56"/>
-      <c r="F138" s="56"/>
-      <c r="G138" s="56"/>
-      <c r="H138" s="56"/>
+        <v>37</v>
+      </c>
+      <c r="C138" s="53"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="53"/>
+      <c r="F138" s="53"/>
+      <c r="G138" s="53"/>
+      <c r="H138" s="53"/>
       <c r="I138" s="1"/>
       <c r="J138" s="52"/>
       <c r="K138" s="52"/>
@@ -6223,68 +6239,14 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -6301,14 +6263,68 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6336,28 +6352,28 @@
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="6"/>
     </row>
@@ -6367,21 +6383,20 @@
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="13"/>
+        <v>50</v>
+      </c>
       <c r="H2" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L2" s="6"/>
     </row>
@@ -6390,18 +6405,18 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -6409,18 +6424,18 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L4" s="6"/>
     </row>
@@ -6429,18 +6444,18 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L5" s="6"/>
     </row>
@@ -6448,17 +6463,19 @@
       <c r="A6" s="58"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="D6" s="73" t="s">
+        <v>74</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="32" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -6468,14 +6485,11 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L7" s="6"/>
     </row>
@@ -6486,12 +6500,12 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L8" s="6"/>
     </row>
@@ -6501,17 +6515,16 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6525,7 +6538,7 @@
       <c r="H10" s="16"/>
       <c r="I10" s="17"/>
       <c r="J10" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -6534,47 +6547,47 @@
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>88</v>
-      </c>
       <c r="J11" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -6582,16 +6595,16 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -6604,7 +6617,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -6617,7 +6630,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -6630,7 +6643,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -6643,7 +6656,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6659,70 +6672,70 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
         <v>99</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6753,28 +6766,28 @@
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>46</v>
-      </c>
       <c r="E1" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K1" s="6"/>
     </row>
@@ -6784,20 +6797,20 @@
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="32" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K2" s="6"/>
     </row>
@@ -6805,14 +6818,16 @@
       <c r="A3" s="58"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="D3" s="73" t="s">
+        <v>74</v>
+      </c>
       <c r="E3" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="24"/>
       <c r="H3" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -6820,12 +6835,12 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="E4" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="24"/>
       <c r="H4" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K4" s="6"/>
     </row>
@@ -6835,13 +6850,10 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="24"/>
-      <c r="H5" s="26" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -6850,11 +6862,11 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -6862,11 +6874,10 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="32"/>
       <c r="H7" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7" s="6"/>
     </row>
@@ -6891,10 +6902,10 @@
       <c r="G9" s="1"/>
       <c r="H9" s="26"/>
       <c r="I9" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6907,7 +6918,7 @@
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
       <c r="I10" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -6918,31 +6929,31 @@
       <c r="C11" s="13"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" s="34"/>
       <c r="H11" s="23"/>
       <c r="I11" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="58"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="25"/>
       <c r="H12" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -6953,7 +6964,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -6965,7 +6976,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -6977,7 +6988,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -7012,87 +7023,87 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -7133,24 +7144,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="53">
+        <v>142</v>
+      </c>
+      <c r="C1" s="54">
         <v>2021</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="53">
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="54">
         <v>2022</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="56"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7158,48 +7169,48 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1">
         <v>3.5206400000000002</v>
@@ -7218,7 +7229,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J3" s="62"/>
       <c r="K3" s="62"/>
@@ -7229,7 +7240,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1">
         <v>1.189046</v>
@@ -7257,7 +7268,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="50"/>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="1">
         <v>3.5619109999999998</v>
@@ -7285,7 +7296,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="1">
         <v>0.63656639999999998</v>
@@ -7312,10 +7323,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="36">
         <v>-0.67962469999999997</v>
@@ -7353,7 +7364,7 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="50"/>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="39">
         <v>-0.8024289</v>
@@ -7391,7 +7402,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="50"/>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="39">
         <v>-11.448639999999999</v>
@@ -7429,7 +7440,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="51"/>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="41">
         <v>-10.27468</v>
@@ -7469,7 +7480,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1">
         <v>0.27505610000000003</v>
@@ -7507,7 +7518,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="50"/>
       <c r="B12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="1">
         <v>0.19852059999999999</v>
@@ -7545,7 +7556,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="50"/>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="1">
         <v>-3.3437139999999997E-2</v>
@@ -7583,7 +7594,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
       <c r="B14" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="1">
         <v>-7.4605980000000002E-2</v>
@@ -7620,10 +7631,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1">
         <v>0.25910539999999999</v>
@@ -7661,7 +7672,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="50"/>
       <c r="B16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="1">
         <v>0.1893232</v>
@@ -7699,7 +7710,7 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="50"/>
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="1">
         <v>-3.3733069999999997E-2</v>
@@ -7737,7 +7748,7 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="51"/>
       <c r="B18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="1">
         <v>-7.235192E-2</v>
@@ -7777,7 +7788,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" s="45">
         <v>0.16267690000000001</v>
@@ -7815,7 +7826,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="50"/>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" s="45">
         <v>0.1318241</v>
@@ -7853,7 +7864,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="50"/>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="45">
         <v>-7.6752669999999995E-2</v>
@@ -7891,7 +7902,7 @@
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" s="45">
         <v>-6.6752569999999997E-2</v>
@@ -7922,7 +7933,7 @@
         <v>-5.0076210000000003</v>
       </c>
       <c r="M22" s="45" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N22" s="1"/>
     </row>
@@ -7931,7 +7942,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1">
         <v>0.26141530000000002</v>
@@ -7969,7 +7980,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="50"/>
       <c r="B24" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="1">
         <v>0.16795750000000001</v>
@@ -8007,7 +8018,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="50"/>
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="1">
         <v>2.4449390000000001E-2</v>
@@ -8045,7 +8056,7 @@
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="51"/>
       <c r="B26" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1">
         <v>-2.5180310000000001E-2</v>
@@ -8085,7 +8096,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="1">
         <v>0.16815289999999999</v>
@@ -8123,7 +8134,7 @@
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="50"/>
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="1">
         <v>0.1095054</v>
@@ -8161,7 +8172,7 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="50"/>
       <c r="B29" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" s="1">
         <v>4.9169679999999999E-3</v>
@@ -8199,7 +8210,7 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="51"/>
       <c r="B30" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" s="1">
         <v>-2.9254499999999999E-2</v>
@@ -8239,7 +8250,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" s="1">
         <v>0.10404770000000001</v>
@@ -8273,13 +8284,13 @@
         <v>3.439386E-3</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C32" s="1">
         <v>3.6833039999999997E-2</v>
@@ -8313,13 +8324,13 @@
         <v>5.8418710000000002E-8</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="50"/>
       <c r="B33" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" s="1">
         <v>0.1045321</v>
@@ -8353,13 +8364,13 @@
         <v>3.9456639999999998E-7</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1">
         <v>3.843543E-2</v>
@@ -8393,7 +8404,7 @@
         <v>7.9669659999999998E-7</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -8401,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C35" s="1">
         <v>-9.9169900000000005E-2</v>
@@ -8435,13 +8446,13 @@
         <v>2.0194479999999999E-4</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="50"/>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="1">
         <v>-5.779488E-2</v>
@@ -8475,13 +8486,13 @@
         <v>1.3548390000000001E-7</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="50"/>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1">
         <v>-4.2352229999999998E-2</v>
@@ -8515,13 +8526,13 @@
         <v>4.2635360000000001E-3</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="51"/>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" s="1">
         <v>7.5999539999999999E-3</v>
@@ -8555,7 +8566,7 @@
         <v>1.895906E-5</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -8563,7 +8574,7 @@
         <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C39" s="1">
         <v>3.6476649999999999E-2</v>
@@ -8601,7 +8612,7 @@
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="50"/>
       <c r="B40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1">
         <v>2.235734E-2</v>
@@ -8639,7 +8650,7 @@
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="50"/>
       <c r="B41" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C41" s="1">
         <v>4.6180759999999996E-3</v>
@@ -8677,7 +8688,7 @@
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="51"/>
       <c r="B42" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="1">
         <v>-8.7482029999999995E-3</v>
@@ -8714,13 +8725,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -8747,7 +8758,7 @@
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44" s="52"/>
       <c r="D44" s="52"/>
@@ -8775,7 +8786,7 @@
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C45" s="52"/>
       <c r="D45" s="52"/>
@@ -8803,7 +8814,7 @@
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="51"/>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" s="52"/>
       <c r="D46" s="52"/>
@@ -8830,13 +8841,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" s="52"/>
       <c r="E47" s="52"/>
@@ -8863,7 +8874,7 @@
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="50"/>
       <c r="B48" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C48" s="52"/>
       <c r="D48" s="52"/>
@@ -8891,7 +8902,7 @@
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="50"/>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C49" s="52"/>
       <c r="D49" s="52"/>
@@ -8919,7 +8930,7 @@
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="51"/>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -8946,10 +8957,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="45">
         <v>-4.1460160000000004</v>
@@ -8968,7 +8979,7 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J51" s="52"/>
       <c r="K51" s="52"/>
@@ -8979,7 +8990,7 @@
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="50"/>
       <c r="B52" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="45">
         <v>-5.1080050000000004</v>
@@ -9007,7 +9018,7 @@
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="50"/>
       <c r="B53" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C53" s="45">
         <v>-3.7989480000000002</v>
@@ -9035,7 +9046,7 @@
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="51"/>
       <c r="B54" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="45">
         <v>-4.4755320000000003</v>
@@ -9062,10 +9073,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="47">
         <v>0.142703</v>
@@ -9084,7 +9095,7 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J55" s="52"/>
       <c r="K55" s="52"/>
@@ -9095,7 +9106,7 @@
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="50"/>
       <c r="B56" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="47">
         <v>0.10728550000000001</v>
@@ -9123,7 +9134,7 @@
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="50"/>
       <c r="B57" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C57" s="47">
         <v>-0.1020605</v>
@@ -9151,7 +9162,7 @@
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="51"/>
       <c r="B58" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58" s="47">
         <v>-8.9823520000000004E-2</v>
@@ -9178,10 +9189,10 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C59" s="47">
         <v>0.3732317</v>
@@ -9200,7 +9211,7 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J59" s="52"/>
       <c r="K59" s="52"/>
@@ -9211,7 +9222,7 @@
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="50"/>
       <c r="B60" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" s="47">
         <v>0.39719009999999999</v>
@@ -9239,7 +9250,7 @@
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="50"/>
       <c r="B61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C61" s="47">
         <v>-2.5815100000000001E-2</v>
@@ -9267,7 +9278,7 @@
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="51"/>
       <c r="B62" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C62" s="47">
         <v>2.8353639999999999E-2</v>
@@ -9294,13 +9305,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -9327,7 +9338,7 @@
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="50"/>
       <c r="B64" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="52"/>
       <c r="D64" s="52"/>
@@ -9355,7 +9366,7 @@
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="50"/>
       <c r="B65" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="52"/>
       <c r="D65" s="52"/>
@@ -9383,7 +9394,7 @@
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="51"/>
       <c r="B66" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="52"/>
       <c r="D66" s="52"/>
@@ -9410,10 +9421,10 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C67" s="47">
         <v>0.2325074</v>
@@ -9432,7 +9443,7 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J67" s="52"/>
       <c r="K67" s="52"/>
@@ -9443,7 +9454,7 @@
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="50"/>
       <c r="B68" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C68" s="47">
         <v>0.28619260000000002</v>
@@ -9471,7 +9482,7 @@
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="50"/>
       <c r="B69" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C69" s="47">
         <v>8.0073980000000003E-2</v>
@@ -9499,7 +9510,7 @@
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="51"/>
       <c r="B70" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="47">
         <v>0.1221365</v>
@@ -9526,13 +9537,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C71" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -9559,7 +9570,7 @@
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="50"/>
       <c r="B72" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C72" s="52"/>
       <c r="D72" s="52"/>
@@ -9587,7 +9598,7 @@
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="50"/>
       <c r="B73" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C73" s="52"/>
       <c r="D73" s="52"/>
@@ -9615,7 +9626,7 @@
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="51"/>
       <c r="B74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C74" s="52"/>
       <c r="D74" s="52"/>
@@ -9642,13 +9653,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C75" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D75" s="52"/>
       <c r="E75" s="52"/>
@@ -9675,7 +9686,7 @@
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="50"/>
       <c r="B76" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C76" s="52"/>
       <c r="D76" s="52"/>
@@ -9703,7 +9714,7 @@
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="50"/>
       <c r="B77" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C77" s="52"/>
       <c r="D77" s="52"/>
@@ -9731,7 +9742,7 @@
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="51"/>
       <c r="B78" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C78" s="52"/>
       <c r="D78" s="52"/>
@@ -9761,7 +9772,7 @@
         <v>24</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" s="1">
         <v>-0.9841491</v>
@@ -9780,7 +9791,7 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J79" s="52"/>
       <c r="K79" s="52"/>
@@ -9791,7 +9802,7 @@
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="50"/>
       <c r="B80" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" s="1">
         <v>0.17573549999999999</v>
@@ -9819,7 +9830,7 @@
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="50"/>
       <c r="B81" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C81" s="1">
         <v>-1.1202160000000001</v>
@@ -9847,7 +9858,7 @@
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="51"/>
       <c r="B82" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C82" s="1">
         <v>0.14184459999999999</v>
@@ -9877,7 +9888,7 @@
         <v>20</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" s="1">
         <v>1.6038840000000001</v>
@@ -9896,7 +9907,7 @@
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J83" s="52"/>
       <c r="K83" s="52"/>
@@ -9907,7 +9918,7 @@
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="50"/>
       <c r="B84" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" s="1">
         <v>2.5716009999999998</v>
@@ -9935,7 +9946,7 @@
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="50"/>
       <c r="B85" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C85" s="1">
         <v>0.61386540000000001</v>
@@ -9963,7 +9974,7 @@
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="51"/>
       <c r="B86" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C86" s="1">
         <v>1.3966069999999999</v>
@@ -9993,7 +10004,7 @@
         <v>21</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="1">
         <v>16.64274</v>
@@ -10012,7 +10023,7 @@
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J87" s="52"/>
       <c r="K87" s="52"/>
@@ -10023,7 +10034,7 @@
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="50"/>
       <c r="B88" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" s="1">
         <v>19.986529999999998</v>
@@ -10051,7 +10062,7 @@
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="50"/>
       <c r="B89" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C89" s="1">
         <v>-4.4803540000000002</v>
@@ -10079,7 +10090,7 @@
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="51"/>
       <c r="B90" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C90" s="1">
         <v>-0.82880399999999999</v>
@@ -10105,30 +10116,30 @@
       <c r="N90" s="1"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="49" t="s">
-        <v>25</v>
+      <c r="A91" s="70" t="s">
+        <v>151</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C91" s="1">
-        <v>0.28573979999999999</v>
-      </c>
-      <c r="D91" s="1">
-        <v>2.892964E-2</v>
-      </c>
-      <c r="E91" s="1">
-        <v>20.899597</v>
-      </c>
-      <c r="F91" s="1">
-        <v>9.8770609999999994</v>
-      </c>
-      <c r="G91" s="2">
-        <v>2.5221599999999999E-9</v>
+        <v>106</v>
+      </c>
+      <c r="C91" s="45">
+        <v>264.8</v>
+      </c>
+      <c r="D91" s="45">
+        <v>32.234110000000001</v>
+      </c>
+      <c r="E91" s="45">
+        <v>30.811264000000001</v>
+      </c>
+      <c r="F91" s="45">
+        <v>8.2149009999999993</v>
+      </c>
+      <c r="G91" s="45">
+        <v>2.9384279999999999E-9</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J91" s="52"/>
       <c r="K91" s="52"/>
@@ -10137,24 +10148,24 @@
       <c r="N91" s="1"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="50"/>
+      <c r="A92" s="71"/>
       <c r="B92" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="1">
-        <v>0.38685409999999998</v>
-      </c>
-      <c r="D92" s="1">
-        <v>2.990483E-2</v>
-      </c>
-      <c r="E92" s="1">
-        <v>24.614989999999999</v>
-      </c>
-      <c r="F92" s="1">
-        <v>12.936170000000001</v>
-      </c>
-      <c r="G92" s="2">
-        <v>1.7821690000000001E-12</v>
+        <v>107</v>
+      </c>
+      <c r="C92" s="45">
+        <v>249.71430000000001</v>
+      </c>
+      <c r="D92" s="45">
+        <v>24.47692</v>
+      </c>
+      <c r="E92" s="45">
+        <v>40.626759999999997</v>
+      </c>
+      <c r="F92" s="45">
+        <v>10.202030000000001</v>
+      </c>
+      <c r="G92" s="45">
+        <v>9.0369680000000005E-13</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="52"/>
@@ -10165,24 +10176,24 @@
       <c r="N92" s="1"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="50"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C93" s="1">
-        <v>2.0270739999999999E-2</v>
-      </c>
-      <c r="D93" s="1">
-        <v>2.7636999999999998E-2</v>
-      </c>
-      <c r="E93" s="1">
-        <v>40</v>
-      </c>
-      <c r="F93" s="1">
-        <v>0.733464</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.46755279999999999</v>
+        <v>108</v>
+      </c>
+      <c r="C93" s="45">
+        <v>43.209679999999999</v>
+      </c>
+      <c r="D93" s="45">
+        <v>56.537500000000001</v>
+      </c>
+      <c r="E93" s="45">
+        <v>16.96773</v>
+      </c>
+      <c r="F93" s="45">
+        <v>0.7642658</v>
+      </c>
+      <c r="G93" s="45">
+        <v>0.45520664523399601</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="52"/>
@@ -10193,24 +10204,24 @@
       <c r="N93" s="1"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="51"/>
+      <c r="A94" s="72"/>
       <c r="B94" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0.13333100000000001</v>
-      </c>
-      <c r="D94" s="1">
-        <v>5.6024570000000003E-2</v>
-      </c>
-      <c r="E94" s="1">
-        <v>8.8358460000000001</v>
-      </c>
-      <c r="F94" s="1">
-        <v>2.3798659999999998</v>
-      </c>
-      <c r="G94" s="2">
-        <v>4.1726619999999999E-2</v>
+        <v>109</v>
+      </c>
+      <c r="C94" s="45">
+        <v>32.259779999999999</v>
+      </c>
+      <c r="D94" s="45">
+        <v>15.415459999999999</v>
+      </c>
+      <c r="E94" s="45">
+        <v>17.28622</v>
+      </c>
+      <c r="F94" s="45">
+        <v>2.0926900000000002</v>
+      </c>
+      <c r="G94" s="45">
+        <v>5.14251187538E-2</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="52"/>
@@ -10222,10 +10233,10 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95" s="1">
         <v>1.3623919999999999E-2</v>
@@ -10244,7 +10255,7 @@
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J95" s="52"/>
       <c r="K95" s="52"/>
@@ -10255,7 +10266,7 @@
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="50"/>
       <c r="B96" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C96" s="1">
         <v>7.6710570000000006E-2</v>
@@ -10283,7 +10294,7 @@
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="50"/>
       <c r="B97" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C97" s="1">
         <v>-6.9491259999999999E-2</v>
@@ -10311,7 +10322,7 @@
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="51"/>
       <c r="B98" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C98" s="1">
         <v>-6.8129929999999998E-3</v>
@@ -10338,10 +10349,10 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C99" s="45">
         <v>2.012891E-5</v>
@@ -10360,7 +10371,7 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J99" s="52"/>
       <c r="K99" s="52"/>
@@ -10371,7 +10382,7 @@
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="50"/>
       <c r="B100" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C100" s="45">
         <v>8.7200299999999999E-4</v>
@@ -10399,7 +10410,7 @@
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="50"/>
       <c r="B101" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C101" s="45">
         <v>-2.0367390000000001E-3</v>
@@ -10427,7 +10438,7 @@
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="51"/>
       <c r="B102" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C102" s="45">
         <v>-1.576327E-3</v>
@@ -10453,30 +10464,30 @@
       <c r="N102" s="1"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="49" t="s">
-        <v>26</v>
+      <c r="A103" s="70" t="s">
+        <v>25</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C103" s="1">
-        <v>0.29603849999999998</v>
+        <v>0.29653109999999999</v>
       </c>
       <c r="D103" s="1">
-        <v>3.2874760000000003E-2</v>
+        <v>3.0081920000000002E-2</v>
       </c>
       <c r="E103" s="1">
-        <v>18.839901000000001</v>
+        <v>12.984576000000001</v>
       </c>
       <c r="F103" s="1">
-        <v>9.0050399999999993</v>
+        <v>9.8574540000000006</v>
       </c>
       <c r="G103" s="2">
-        <v>2.974355E-8</v>
+        <v>2.1465810000000001E-7</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J103" s="52"/>
       <c r="K103" s="52"/>
@@ -10485,24 +10496,24 @@
       <c r="N103" s="1"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="50"/>
+      <c r="A104" s="71"/>
       <c r="B104" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C104" s="1">
-        <v>0.48750929999999998</v>
+        <v>0.48443409999999998</v>
       </c>
       <c r="D104" s="1">
-        <v>2.0179229999999999E-2</v>
+        <v>1.925058E-2</v>
       </c>
       <c r="E104" s="1">
-        <v>33.068705000000001</v>
+        <v>33.275270999999996</v>
       </c>
       <c r="F104" s="1">
-        <v>24.15896</v>
+        <v>25.164650000000002</v>
       </c>
       <c r="G104" s="2">
-        <v>1.3818109999999999E-22</v>
+        <v>3.0964249999999998E-23</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="52"/>
@@ -10513,24 +10524,24 @@
       <c r="N104" s="1"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="50"/>
+      <c r="A105" s="71"/>
       <c r="B105" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C105" s="1">
-        <v>-4.929849E-2</v>
+        <v>-4.9176770000000002E-2</v>
       </c>
       <c r="D105" s="1">
-        <v>3.1121630000000001E-2</v>
+        <v>3.2182200000000001E-2</v>
       </c>
       <c r="E105" s="1">
-        <v>4.2666779999999997</v>
+        <v>6.754302</v>
       </c>
       <c r="F105" s="1">
-        <v>-1.5840590000000001</v>
+        <v>-1.5280739999999999</v>
       </c>
       <c r="G105" s="1">
-        <v>0.18392030000000001</v>
+        <v>0.17187649999999999</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="52"/>
@@ -10541,24 +10552,24 @@
       <c r="N105" s="1"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="51"/>
+      <c r="A106" s="72"/>
       <c r="B106" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C106" s="1">
-        <v>0.15619479999999999</v>
+        <v>0.14682600000000001</v>
       </c>
       <c r="D106" s="1">
-        <v>2.6369159999999999E-2</v>
+        <v>2.4250879999999999E-2</v>
       </c>
       <c r="E106" s="1">
-        <v>5.0675150000000002</v>
+        <v>6.7890449999999998</v>
       </c>
       <c r="F106" s="1">
-        <v>5.9233900000000004</v>
+        <v>6.0544589999999996</v>
       </c>
       <c r="G106" s="2">
-        <v>1.86768E-3</v>
+        <v>5.7776140000000001E-4</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="52"/>
@@ -10588,22 +10599,20 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="I3:M6"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="I103:M106"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="I79:M82"/>
     <mergeCell ref="C47:G50"/>
     <mergeCell ref="A43:A46"/>
     <mergeCell ref="C43:G46"/>
@@ -10619,20 +10628,22 @@
     <mergeCell ref="C63:G66"/>
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C75:G78"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="I79:M82"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="I95:M98"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="I103:M106"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="I91:M94"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="I99:M102"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="I3:M6"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1360" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{359C411E-E97C-4AF5-A0DA-89B201753963}"/>
+  <xr:revisionPtr revIDLastSave="1387" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5163F1B2-54E7-46DB-B0D6-4C771C00F6A8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="152">
   <si>
     <t>Experiment</t>
   </si>
@@ -952,7 +952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1030,6 +1030,7 @@
     <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1042,9 +1043,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1052,6 +1050,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1093,16 +1094,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1547,7 +1538,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1595,7 +1586,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1639,7 +1630,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
@@ -1683,16 +1674,16 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1715,7 +1706,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="50" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -1761,7 +1752,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1805,7 +1796,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -1849,16 +1840,16 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1881,7 +1872,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="50" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1906,18 +1897,18 @@
         <v>3.2053459705297903E-5</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1940,16 +1931,16 @@
         <v>2.0059373392474201E-2</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1972,36 +1963,36 @@
         <v>0.213540969734523</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="50" t="s">
         <v>141</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2026,18 +2017,18 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -2060,16 +2051,16 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2091,36 +2082,36 @@
       <c r="H17" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="51"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="50" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2166,7 +2157,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="11" t="s">
         <v>7</v>
       </c>
@@ -2210,7 +2201,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -2254,16 +2245,16 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="51"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2286,7 +2277,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="50" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2332,7 +2323,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2376,7 +2367,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -2420,16 +2411,16 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2452,7 +2443,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -2498,7 +2489,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -2542,7 +2533,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -2586,16 +2577,16 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2618,7 +2609,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="50" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2664,7 +2655,7 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
+      <c r="A32" s="51"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -2708,7 +2699,7 @@
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -2752,16 +2743,16 @@
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="51"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2784,7 +2775,7 @@
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2830,7 +2821,7 @@
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -2874,7 +2865,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -2918,16 +2909,16 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="51"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -2950,7 +2941,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="50" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2996,7 +2987,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -3040,7 +3031,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -3084,16 +3075,16 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="51"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="53"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3116,7 +3107,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="50" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -3162,7 +3153,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -3206,7 +3197,7 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
@@ -3250,16 +3241,16 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="51"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="53"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3282,7 +3273,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="50" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -3328,7 +3319,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="10" t="s">
         <v>7</v>
       </c>
@@ -3372,7 +3363,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -3416,16 +3407,16 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="51"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3448,20 +3439,20 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="50" t="s">
         <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
         <v>2.20343269025562E-2</v>
@@ -3484,16 +3475,16 @@
       <c r="P51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
         <v>2.98483856205864E-2</v>
@@ -3516,16 +3507,16 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
         <v>1.15818782663304E-3</v>
@@ -3548,16 +3539,16 @@
       <c r="P53" s="1"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="51"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
         <v>2.0797141885883202E-3</v>
@@ -3580,7 +3571,7 @@
       <c r="P54" s="1"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="50" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -3628,7 +3619,7 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+      <c r="A56" s="51"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -3672,7 +3663,7 @@
       <c r="P56" s="1"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
+      <c r="A57" s="51"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -3716,16 +3707,16 @@
       <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="51"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3748,7 +3739,7 @@
       <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="49" t="s">
+      <c r="A59" s="50" t="s">
         <v>64</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3773,18 +3764,18 @@
         <v>1.61142062466842E-3</v>
       </c>
       <c r="I59" s="1"/>
-      <c r="J59" s="52" t="s">
+      <c r="J59" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K59" s="52"/>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52"/>
-      <c r="N59" s="52"/>
-      <c r="O59" s="52"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
+      <c r="N59" s="53"/>
+      <c r="O59" s="53"/>
       <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
+      <c r="A60" s="51"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
@@ -3807,16 +3798,16 @@
         <v>0.83160181683106904</v>
       </c>
       <c r="I60" s="1"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
-      <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
-      <c r="N60" s="52"/>
-      <c r="O60" s="52"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
+      <c r="M60" s="53"/>
+      <c r="N60" s="53"/>
+      <c r="O60" s="53"/>
       <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
@@ -3839,49 +3830,49 @@
         <v>0.64170681971566501</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="52"/>
-      <c r="K61" s="52"/>
-      <c r="L61" s="52"/>
-      <c r="M61" s="52"/>
-      <c r="N61" s="52"/>
-      <c r="O61" s="52"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
+      <c r="M61" s="53"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="53"/>
       <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="51"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="53"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="52"/>
-      <c r="N62" s="52"/>
-      <c r="O62" s="52"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
+      <c r="M62" s="53"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="53"/>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="49" t="s">
+      <c r="A63" s="50" t="s">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="52"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="53"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
         <v>40.695777417400599</v>
@@ -3904,16 +3895,16 @@
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
-      <c r="H64" s="52"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
         <v>0.27305635622259</v>
@@ -3936,16 +3927,16 @@
       <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
         <v>3.4613576315483399</v>
@@ -3968,16 +3959,16 @@
       <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="51"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
         <v>0.72850411949349603</v>
@@ -4000,20 +3991,20 @@
       <c r="P66" s="1"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="49" t="s">
+      <c r="A67" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="52" t="s">
+      <c r="C67" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
-      <c r="H67" s="52"/>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
         <v>948.25120936445398</v>
@@ -4036,16 +4027,16 @@
       <c r="P67" s="1"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
+      <c r="A68" s="51"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
-      <c r="H68" s="52"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
         <v>0.22870622612837599</v>
@@ -4068,16 +4059,16 @@
       <c r="P68" s="1"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="52"/>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
-      <c r="H69" s="52"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="53"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>37.771893612281502</v>
@@ -4100,16 +4091,16 @@
       <c r="P69" s="1"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="51"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="52"/>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="52"/>
-      <c r="G70" s="52"/>
-      <c r="H70" s="52"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="53"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
+      <c r="H70" s="53"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
         <v>3.9110782596565699</v>
@@ -4132,7 +4123,7 @@
       <c r="P70" s="1"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="49" t="s">
+      <c r="A71" s="50" t="s">
         <v>42</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -4157,18 +4148,18 @@
         <v>2.3819311555743102E-16</v>
       </c>
       <c r="I71" s="1"/>
-      <c r="J71" s="52" t="s">
+      <c r="J71" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K71" s="52"/>
-      <c r="L71" s="52"/>
-      <c r="M71" s="52"/>
-      <c r="N71" s="52"/>
-      <c r="O71" s="52"/>
+      <c r="K71" s="53"/>
+      <c r="L71" s="53"/>
+      <c r="M71" s="53"/>
+      <c r="N71" s="53"/>
+      <c r="O71" s="53"/>
       <c r="P71" s="1"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
+      <c r="A72" s="51"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
@@ -4191,16 +4182,16 @@
         <v>1.0894169628446399E-3</v>
       </c>
       <c r="I72" s="1"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
-      <c r="L72" s="52"/>
-      <c r="M72" s="52"/>
-      <c r="N72" s="52"/>
-      <c r="O72" s="52"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53"/>
+      <c r="M72" s="53"/>
+      <c r="N72" s="53"/>
+      <c r="O72" s="53"/>
       <c r="P72" s="1"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
+      <c r="A73" s="51"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
@@ -4223,49 +4214,49 @@
         <v>0.84541099798019603</v>
       </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="52"/>
-      <c r="K73" s="52"/>
-      <c r="L73" s="52"/>
-      <c r="M73" s="52"/>
-      <c r="N73" s="52"/>
-      <c r="O73" s="52"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
+      <c r="M73" s="53"/>
+      <c r="N73" s="53"/>
+      <c r="O73" s="53"/>
       <c r="P73" s="1"/>
     </row>
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="51"/>
+      <c r="A74" s="52"/>
       <c r="B74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="53"/>
-      <c r="D74" s="53"/>
-      <c r="E74" s="53"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="53"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="52"/>
-      <c r="M74" s="52"/>
-      <c r="N74" s="52"/>
-      <c r="O74" s="52"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
+      <c r="M74" s="53"/>
+      <c r="N74" s="53"/>
+      <c r="O74" s="53"/>
       <c r="P74" s="1"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="49" t="s">
+      <c r="A75" s="50" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="52" t="s">
+      <c r="C75" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1">
         <v>7.7190184322692705E-4</v>
@@ -4288,16 +4279,16 @@
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1">
         <v>0.26383928794443301</v>
@@ -4320,16 +4311,16 @@
       <c r="P76" s="1"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
-      <c r="H77" s="52"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="53"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1">
         <v>6.5298294112546198E-3</v>
@@ -4352,16 +4343,16 @@
       <c r="P77" s="1"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="51"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1">
         <v>7.3489818378573097E-3</v>
@@ -4384,7 +4375,7 @@
       <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="49" t="s">
+      <c r="A79" s="50" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -4409,18 +4400,18 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I79" s="1"/>
-      <c r="J79" s="52" t="s">
+      <c r="J79" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K79" s="52"/>
-      <c r="L79" s="52"/>
-      <c r="M79" s="52"/>
-      <c r="N79" s="52"/>
-      <c r="O79" s="52"/>
+      <c r="K79" s="53"/>
+      <c r="L79" s="53"/>
+      <c r="M79" s="53"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="53"/>
       <c r="P79" s="1"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="50"/>
+      <c r="A80" s="51"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
@@ -4443,16 +4434,16 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="52"/>
-      <c r="K80" s="52"/>
-      <c r="L80" s="52"/>
-      <c r="M80" s="52"/>
-      <c r="N80" s="52"/>
-      <c r="O80" s="52"/>
+      <c r="J80" s="53"/>
+      <c r="K80" s="53"/>
+      <c r="L80" s="53"/>
+      <c r="M80" s="53"/>
+      <c r="N80" s="53"/>
+      <c r="O80" s="53"/>
       <c r="P80" s="1"/>
     </row>
     <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="50"/>
+      <c r="A81" s="51"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
@@ -4475,49 +4466,49 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="52"/>
-      <c r="K81" s="52"/>
-      <c r="L81" s="52"/>
-      <c r="M81" s="52"/>
-      <c r="N81" s="52"/>
-      <c r="O81" s="52"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
+      <c r="M81" s="53"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
       <c r="P81" s="1"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="51"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="53"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="53"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="57"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="52"/>
-      <c r="K82" s="52"/>
-      <c r="L82" s="52"/>
-      <c r="M82" s="52"/>
-      <c r="N82" s="52"/>
-      <c r="O82" s="52"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
+      <c r="M82" s="53"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="53"/>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="49" t="s">
+      <c r="A83" s="50" t="s">
         <v>38</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="52" t="s">
+      <c r="C83" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="52"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
+      <c r="H83" s="53"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1">
         <v>4.0252880405239402E-2</v>
@@ -4540,16 +4531,16 @@
       <c r="P83" s="1"/>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="50"/>
+      <c r="A84" s="51"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="52"/>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="53"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1">
         <v>0.42132164214255802</v>
@@ -4572,16 +4563,16 @@
       <c r="P84" s="1"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="50"/>
+      <c r="A85" s="51"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="52"/>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1">
         <v>7.8254362282741005E-2</v>
@@ -4604,16 +4595,16 @@
       <c r="P85" s="1"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="51"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1">
         <v>2.6614614752845599E-3</v>
@@ -4636,7 +4627,7 @@
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="49" t="s">
+      <c r="A87" s="50" t="s">
         <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -4661,18 +4652,18 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I87" s="1"/>
-      <c r="J87" s="52" t="s">
+      <c r="J87" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="50"/>
+      <c r="A88" s="51"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
@@ -4695,16 +4686,16 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I88" s="1"/>
-      <c r="J88" s="52"/>
-      <c r="K88" s="52"/>
-      <c r="L88" s="52"/>
-      <c r="M88" s="52"/>
-      <c r="N88" s="52"/>
-      <c r="O88" s="52"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="53"/>
+      <c r="O88" s="53"/>
       <c r="P88" s="1"/>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="50"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
       </c>
@@ -4727,36 +4718,36 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I89" s="1"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="52"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
+      <c r="M89" s="53"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
       <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="51"/>
+      <c r="A90" s="52"/>
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="53"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="53"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
-      <c r="N90" s="52"/>
-      <c r="O90" s="52"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="53"/>
       <c r="P90" s="1"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="49" t="s">
+      <c r="A91" s="50" t="s">
         <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -4781,18 +4772,18 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I91" s="1"/>
-      <c r="J91" s="52" t="s">
+      <c r="J91" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
-      <c r="N91" s="52"/>
-      <c r="O91" s="52"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="53"/>
+      <c r="M91" s="53"/>
+      <c r="N91" s="53"/>
+      <c r="O91" s="53"/>
       <c r="P91" s="1"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="50"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
@@ -4815,16 +4806,16 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="52"/>
-      <c r="N92" s="52"/>
-      <c r="O92" s="52"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="53"/>
+      <c r="M92" s="53"/>
+      <c r="N92" s="53"/>
+      <c r="O92" s="53"/>
       <c r="P92" s="1"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="50"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
@@ -4847,36 +4838,36 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I93" s="1"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="52"/>
-      <c r="O93" s="52"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="53"/>
+      <c r="L93" s="53"/>
+      <c r="M93" s="53"/>
+      <c r="N93" s="53"/>
+      <c r="O93" s="53"/>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="51"/>
+      <c r="A94" s="52"/>
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="53"/>
-      <c r="D94" s="53"/>
-      <c r="E94" s="53"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="53"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
-      <c r="L94" s="52"/>
-      <c r="M94" s="52"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="52"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
+      <c r="N94" s="53"/>
+      <c r="O94" s="53"/>
       <c r="P94" s="1"/>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="49" t="s">
+      <c r="A95" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -4901,18 +4892,18 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I95" s="1"/>
-      <c r="J95" s="52" t="s">
+      <c r="J95" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K95" s="52"/>
-      <c r="L95" s="52"/>
-      <c r="M95" s="52"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="52"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="53"/>
+      <c r="M95" s="53"/>
+      <c r="N95" s="53"/>
+      <c r="O95" s="53"/>
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="50"/>
+      <c r="A96" s="51"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
@@ -4935,16 +4926,16 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I96" s="1"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
-      <c r="L96" s="52"/>
-      <c r="M96" s="52"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="52"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
+      <c r="M96" s="53"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="53"/>
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="50"/>
+      <c r="A97" s="51"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
       </c>
@@ -4967,36 +4958,36 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="52"/>
-      <c r="N97" s="52"/>
-      <c r="O97" s="52"/>
+      <c r="J97" s="53"/>
+      <c r="K97" s="53"/>
+      <c r="L97" s="53"/>
+      <c r="M97" s="53"/>
+      <c r="N97" s="53"/>
+      <c r="O97" s="53"/>
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="51"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="53"/>
-      <c r="D98" s="53"/>
-      <c r="E98" s="53"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
-      <c r="H98" s="53"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
-      <c r="M98" s="52"/>
-      <c r="N98" s="52"/>
-      <c r="O98" s="52"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
+      <c r="N98" s="53"/>
+      <c r="O98" s="53"/>
       <c r="P98" s="1"/>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="49" t="s">
+      <c r="A99" s="50" t="s">
         <v>30</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -5021,18 +5012,18 @@
         <v>3.8248319558473298E-23</v>
       </c>
       <c r="I99" s="1"/>
-      <c r="J99" s="52" t="s">
+      <c r="J99" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K99" s="52"/>
-      <c r="L99" s="52"/>
-      <c r="M99" s="52"/>
-      <c r="N99" s="52"/>
-      <c r="O99" s="52"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="53"/>
+      <c r="M99" s="53"/>
+      <c r="N99" s="53"/>
+      <c r="O99" s="53"/>
       <c r="P99" s="1"/>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="50"/>
+      <c r="A100" s="51"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
@@ -5055,16 +5046,16 @@
         <v>0.27985440517664001</v>
       </c>
       <c r="I100" s="1"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
-      <c r="L100" s="52"/>
-      <c r="M100" s="52"/>
-      <c r="N100" s="52"/>
-      <c r="O100" s="52"/>
+      <c r="J100" s="53"/>
+      <c r="K100" s="53"/>
+      <c r="L100" s="53"/>
+      <c r="M100" s="53"/>
+      <c r="N100" s="53"/>
+      <c r="O100" s="53"/>
       <c r="P100" s="1"/>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
+      <c r="A101" s="51"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
       </c>
@@ -5087,49 +5078,49 @@
         <v>0.72495214931683005</v>
       </c>
       <c r="I101" s="1"/>
-      <c r="J101" s="52"/>
-      <c r="K101" s="52"/>
-      <c r="L101" s="52"/>
-      <c r="M101" s="52"/>
-      <c r="N101" s="52"/>
-      <c r="O101" s="52"/>
+      <c r="J101" s="53"/>
+      <c r="K101" s="53"/>
+      <c r="L101" s="53"/>
+      <c r="M101" s="53"/>
+      <c r="N101" s="53"/>
+      <c r="O101" s="53"/>
       <c r="P101" s="1"/>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="51"/>
+      <c r="A102" s="52"/>
       <c r="B102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C102" s="53"/>
-      <c r="D102" s="53"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="53"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="52"/>
-      <c r="K102" s="52"/>
-      <c r="L102" s="52"/>
-      <c r="M102" s="52"/>
-      <c r="N102" s="52"/>
-      <c r="O102" s="52"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
+      <c r="M102" s="53"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="53"/>
       <c r="P102" s="1"/>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="49" t="s">
+      <c r="A103" s="50" t="s">
         <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="52" t="s">
+      <c r="C103" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="52"/>
-      <c r="H103" s="52"/>
+      <c r="D103" s="53"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="53"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
         <v>4.9920514192076698E-4</v>
@@ -5152,16 +5143,16 @@
       <c r="P103" s="1"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="50"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
-      <c r="H104" s="52"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
         <v>4.3245963051368403E-3</v>
@@ -5184,16 +5175,16 @@
       <c r="P104" s="1"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="50"/>
+      <c r="A105" s="51"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="52"/>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
-      <c r="H105" s="52"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="53"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="53"/>
       <c r="I105" s="1"/>
       <c r="J105" s="5">
         <v>4.4673218852987901E-5</v>
@@ -5216,16 +5207,16 @@
       <c r="P105" s="1"/>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="51"/>
+      <c r="A106" s="52"/>
       <c r="B106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C106" s="52"/>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="52"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="53"/>
+      <c r="E106" s="53"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="53"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
         <v>2.5092673060789E-4</v>
@@ -5248,20 +5239,20 @@
       <c r="P106" s="1"/>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="49" t="s">
+      <c r="A107" s="50" t="s">
         <v>29</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="52" t="s">
+      <c r="C107" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
-      <c r="H107" s="52"/>
+      <c r="D107" s="53"/>
+      <c r="E107" s="53"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="53"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
         <v>1.4241127553301099E-4</v>
@@ -5284,16 +5275,16 @@
       <c r="P107" s="1"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="50"/>
+      <c r="A108" s="51"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="52"/>
-      <c r="D108" s="52"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52"/>
-      <c r="G108" s="52"/>
-      <c r="H108" s="52"/>
+      <c r="C108" s="53"/>
+      <c r="D108" s="53"/>
+      <c r="E108" s="53"/>
+      <c r="F108" s="53"/>
+      <c r="G108" s="53"/>
+      <c r="H108" s="53"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
         <v>4.6725153189010001E-2</v>
@@ -5316,16 +5307,16 @@
       <c r="P108" s="1"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="50"/>
+      <c r="A109" s="51"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="52"/>
-      <c r="D109" s="52"/>
-      <c r="E109" s="52"/>
-      <c r="F109" s="52"/>
-      <c r="G109" s="52"/>
-      <c r="H109" s="52"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
+      <c r="H109" s="53"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1">
         <v>2.8302586845141399E-2</v>
@@ -5348,16 +5339,16 @@
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="51"/>
+      <c r="A110" s="52"/>
       <c r="B110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C110" s="52"/>
-      <c r="D110" s="52"/>
-      <c r="E110" s="52"/>
-      <c r="F110" s="52"/>
-      <c r="G110" s="52"/>
-      <c r="H110" s="52"/>
+      <c r="C110" s="53"/>
+      <c r="D110" s="53"/>
+      <c r="E110" s="53"/>
+      <c r="F110" s="53"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="53"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1">
         <v>6.3796317056246301E-3</v>
@@ -5380,7 +5371,7 @@
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="49" t="s">
+      <c r="A111" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -5405,18 +5396,18 @@
         <v>2.5160186313214301E-3</v>
       </c>
       <c r="I111" s="1"/>
-      <c r="J111" s="52" t="s">
+      <c r="J111" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K111" s="52"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="52"/>
-      <c r="N111" s="52"/>
-      <c r="O111" s="52"/>
+      <c r="K111" s="53"/>
+      <c r="L111" s="53"/>
+      <c r="M111" s="53"/>
+      <c r="N111" s="53"/>
+      <c r="O111" s="53"/>
       <c r="P111" s="1"/>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="50"/>
+      <c r="A112" s="51"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
@@ -5439,16 +5430,16 @@
         <v>0.13226601261193599</v>
       </c>
       <c r="I112" s="1"/>
-      <c r="J112" s="52"/>
-      <c r="K112" s="52"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="52"/>
-      <c r="N112" s="52"/>
-      <c r="O112" s="52"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="53"/>
+      <c r="L112" s="53"/>
+      <c r="M112" s="53"/>
+      <c r="N112" s="53"/>
+      <c r="O112" s="53"/>
       <c r="P112" s="1"/>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" s="50"/>
+      <c r="A113" s="51"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
       </c>
@@ -5471,36 +5462,36 @@
         <v>1.67603779088435E-5</v>
       </c>
       <c r="I113" s="1"/>
-      <c r="J113" s="52"/>
-      <c r="K113" s="52"/>
-      <c r="L113" s="52"/>
-      <c r="M113" s="52"/>
-      <c r="N113" s="52"/>
-      <c r="O113" s="52"/>
+      <c r="J113" s="53"/>
+      <c r="K113" s="53"/>
+      <c r="L113" s="53"/>
+      <c r="M113" s="53"/>
+      <c r="N113" s="53"/>
+      <c r="O113" s="53"/>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" s="51"/>
+      <c r="A114" s="52"/>
       <c r="B114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="53"/>
-      <c r="D114" s="53"/>
-      <c r="E114" s="53"/>
-      <c r="F114" s="53"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="53"/>
+      <c r="C114" s="57"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
-      <c r="L114" s="52"/>
-      <c r="M114" s="52"/>
-      <c r="N114" s="52"/>
-      <c r="O114" s="52"/>
+      <c r="J114" s="53"/>
+      <c r="K114" s="53"/>
+      <c r="L114" s="53"/>
+      <c r="M114" s="53"/>
+      <c r="N114" s="53"/>
+      <c r="O114" s="53"/>
       <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" s="49" t="s">
+      <c r="A115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -5525,18 +5516,18 @@
         <v>3.1891308959839999E-11</v>
       </c>
       <c r="I115" s="1"/>
-      <c r="J115" s="52" t="s">
+      <c r="J115" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K115" s="52"/>
-      <c r="L115" s="52"/>
-      <c r="M115" s="52"/>
-      <c r="N115" s="52"/>
-      <c r="O115" s="52"/>
+      <c r="K115" s="53"/>
+      <c r="L115" s="53"/>
+      <c r="M115" s="53"/>
+      <c r="N115" s="53"/>
+      <c r="O115" s="53"/>
       <c r="P115" s="1"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A116" s="50"/>
+      <c r="A116" s="51"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
@@ -5559,16 +5550,16 @@
         <v>1.9668218703936501E-2</v>
       </c>
       <c r="I116" s="1"/>
-      <c r="J116" s="52"/>
-      <c r="K116" s="52"/>
-      <c r="L116" s="52"/>
-      <c r="M116" s="52"/>
-      <c r="N116" s="52"/>
-      <c r="O116" s="52"/>
+      <c r="J116" s="53"/>
+      <c r="K116" s="53"/>
+      <c r="L116" s="53"/>
+      <c r="M116" s="53"/>
+      <c r="N116" s="53"/>
+      <c r="O116" s="53"/>
       <c r="P116" s="1"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="50"/>
+      <c r="A117" s="51"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
       </c>
@@ -5591,36 +5582,36 @@
         <v>6.4583181614334004E-2</v>
       </c>
       <c r="I117" s="1"/>
-      <c r="J117" s="52"/>
-      <c r="K117" s="52"/>
-      <c r="L117" s="52"/>
-      <c r="M117" s="52"/>
-      <c r="N117" s="52"/>
-      <c r="O117" s="52"/>
+      <c r="J117" s="53"/>
+      <c r="K117" s="53"/>
+      <c r="L117" s="53"/>
+      <c r="M117" s="53"/>
+      <c r="N117" s="53"/>
+      <c r="O117" s="53"/>
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A118" s="51"/>
+      <c r="A118" s="52"/>
       <c r="B118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="53"/>
-      <c r="D118" s="53"/>
-      <c r="E118" s="53"/>
-      <c r="F118" s="53"/>
-      <c r="G118" s="53"/>
-      <c r="H118" s="53"/>
+      <c r="C118" s="57"/>
+      <c r="D118" s="57"/>
+      <c r="E118" s="57"/>
+      <c r="F118" s="57"/>
+      <c r="G118" s="57"/>
+      <c r="H118" s="57"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="52"/>
-      <c r="K118" s="52"/>
-      <c r="L118" s="52"/>
-      <c r="M118" s="52"/>
-      <c r="N118" s="52"/>
-      <c r="O118" s="52"/>
+      <c r="J118" s="53"/>
+      <c r="K118" s="53"/>
+      <c r="L118" s="53"/>
+      <c r="M118" s="53"/>
+      <c r="N118" s="53"/>
+      <c r="O118" s="53"/>
       <c r="P118" s="1"/>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A119" s="49" t="s">
+      <c r="A119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -5645,18 +5636,18 @@
         <v>7.05414701429731E-35</v>
       </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="52" t="s">
+      <c r="J119" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K119" s="52"/>
-      <c r="L119" s="52"/>
-      <c r="M119" s="52"/>
-      <c r="N119" s="52"/>
-      <c r="O119" s="52"/>
+      <c r="K119" s="53"/>
+      <c r="L119" s="53"/>
+      <c r="M119" s="53"/>
+      <c r="N119" s="53"/>
+      <c r="O119" s="53"/>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" s="50"/>
+      <c r="A120" s="51"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
@@ -5679,16 +5670,16 @@
         <v>3.9509565365961799E-2</v>
       </c>
       <c r="I120" s="1"/>
-      <c r="J120" s="52"/>
-      <c r="K120" s="52"/>
-      <c r="L120" s="52"/>
-      <c r="M120" s="52"/>
-      <c r="N120" s="52"/>
-      <c r="O120" s="52"/>
+      <c r="J120" s="53"/>
+      <c r="K120" s="53"/>
+      <c r="L120" s="53"/>
+      <c r="M120" s="53"/>
+      <c r="N120" s="53"/>
+      <c r="O120" s="53"/>
       <c r="P120" s="1"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" s="50"/>
+      <c r="A121" s="51"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
       </c>
@@ -5711,36 +5702,36 @@
         <v>1.2703272318058401E-2</v>
       </c>
       <c r="I121" s="1"/>
-      <c r="J121" s="52"/>
-      <c r="K121" s="52"/>
-      <c r="L121" s="52"/>
-      <c r="M121" s="52"/>
-      <c r="N121" s="52"/>
-      <c r="O121" s="52"/>
+      <c r="J121" s="53"/>
+      <c r="K121" s="53"/>
+      <c r="L121" s="53"/>
+      <c r="M121" s="53"/>
+      <c r="N121" s="53"/>
+      <c r="O121" s="53"/>
       <c r="P121" s="1"/>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" s="51"/>
+      <c r="A122" s="52"/>
       <c r="B122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="53"/>
-      <c r="D122" s="53"/>
-      <c r="E122" s="53"/>
-      <c r="F122" s="53"/>
-      <c r="G122" s="53"/>
-      <c r="H122" s="53"/>
+      <c r="C122" s="57"/>
+      <c r="D122" s="57"/>
+      <c r="E122" s="57"/>
+      <c r="F122" s="57"/>
+      <c r="G122" s="57"/>
+      <c r="H122" s="57"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="52"/>
-      <c r="K122" s="52"/>
-      <c r="L122" s="52"/>
-      <c r="M122" s="52"/>
-      <c r="N122" s="52"/>
-      <c r="O122" s="52"/>
+      <c r="J122" s="53"/>
+      <c r="K122" s="53"/>
+      <c r="L122" s="53"/>
+      <c r="M122" s="53"/>
+      <c r="N122" s="53"/>
+      <c r="O122" s="53"/>
       <c r="P122" s="1"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="70" t="s">
+      <c r="A123" s="50" t="s">
         <v>151</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -5765,18 +5756,18 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I123" s="1"/>
-      <c r="J123" s="52" t="s">
+      <c r="J123" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K123" s="52"/>
-      <c r="L123" s="52"/>
-      <c r="M123" s="52"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="52"/>
+      <c r="K123" s="53"/>
+      <c r="L123" s="53"/>
+      <c r="M123" s="53"/>
+      <c r="N123" s="53"/>
+      <c r="O123" s="53"/>
       <c r="P123" s="1"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" s="71"/>
+      <c r="A124" s="51"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
@@ -5799,16 +5790,16 @@
         <v>0.2597892</v>
       </c>
       <c r="I124" s="1"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="52"/>
-      <c r="L124" s="52"/>
-      <c r="M124" s="52"/>
-      <c r="N124" s="52"/>
-      <c r="O124" s="52"/>
+      <c r="J124" s="53"/>
+      <c r="K124" s="53"/>
+      <c r="L124" s="53"/>
+      <c r="M124" s="53"/>
+      <c r="N124" s="53"/>
+      <c r="O124" s="53"/>
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="71"/>
+      <c r="A125" s="51"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
@@ -5831,36 +5822,36 @@
         <v>0.7055884</v>
       </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="52"/>
-      <c r="M125" s="52"/>
-      <c r="N125" s="52"/>
-      <c r="O125" s="52"/>
+      <c r="J125" s="53"/>
+      <c r="K125" s="53"/>
+      <c r="L125" s="53"/>
+      <c r="M125" s="53"/>
+      <c r="N125" s="53"/>
+      <c r="O125" s="53"/>
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="72"/>
+      <c r="A126" s="52"/>
       <c r="B126" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="53"/>
-      <c r="D126" s="53"/>
-      <c r="E126" s="53"/>
-      <c r="F126" s="53"/>
-      <c r="G126" s="53"/>
-      <c r="H126" s="53"/>
+      <c r="C126" s="57"/>
+      <c r="D126" s="57"/>
+      <c r="E126" s="57"/>
+      <c r="F126" s="57"/>
+      <c r="G126" s="57"/>
+      <c r="H126" s="57"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="52"/>
-      <c r="N126" s="52"/>
-      <c r="O126" s="52"/>
+      <c r="J126" s="53"/>
+      <c r="K126" s="53"/>
+      <c r="L126" s="53"/>
+      <c r="M126" s="53"/>
+      <c r="N126" s="53"/>
+      <c r="O126" s="53"/>
       <c r="P126" s="1"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" s="49" t="s">
+      <c r="A127" s="50" t="s">
         <v>34</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -5885,18 +5876,18 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I127" s="1"/>
-      <c r="J127" s="52" t="s">
+      <c r="J127" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
+      <c r="K127" s="53"/>
+      <c r="L127" s="53"/>
+      <c r="M127" s="53"/>
+      <c r="N127" s="53"/>
+      <c r="O127" s="53"/>
       <c r="P127" s="1"/>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" s="50"/>
+      <c r="A128" s="51"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
@@ -5919,16 +5910,16 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I128" s="1"/>
-      <c r="J128" s="52"/>
-      <c r="K128" s="52"/>
-      <c r="L128" s="52"/>
-      <c r="M128" s="52"/>
-      <c r="N128" s="52"/>
-      <c r="O128" s="52"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="53"/>
+      <c r="L128" s="53"/>
+      <c r="M128" s="53"/>
+      <c r="N128" s="53"/>
+      <c r="O128" s="53"/>
       <c r="P128" s="1"/>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" s="50"/>
+      <c r="A129" s="51"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
       </c>
@@ -5951,36 +5942,36 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I129" s="1"/>
-      <c r="J129" s="52"/>
-      <c r="K129" s="52"/>
-      <c r="L129" s="52"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="52"/>
-      <c r="O129" s="52"/>
+      <c r="J129" s="53"/>
+      <c r="K129" s="53"/>
+      <c r="L129" s="53"/>
+      <c r="M129" s="53"/>
+      <c r="N129" s="53"/>
+      <c r="O129" s="53"/>
       <c r="P129" s="1"/>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" s="51"/>
+      <c r="A130" s="52"/>
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C130" s="53"/>
-      <c r="D130" s="53"/>
-      <c r="E130" s="53"/>
-      <c r="F130" s="53"/>
-      <c r="G130" s="53"/>
-      <c r="H130" s="53"/>
+      <c r="C130" s="57"/>
+      <c r="D130" s="57"/>
+      <c r="E130" s="57"/>
+      <c r="F130" s="57"/>
+      <c r="G130" s="57"/>
+      <c r="H130" s="57"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
-      <c r="M130" s="52"/>
-      <c r="N130" s="52"/>
-      <c r="O130" s="52"/>
+      <c r="J130" s="53"/>
+      <c r="K130" s="53"/>
+      <c r="L130" s="53"/>
+      <c r="M130" s="53"/>
+      <c r="N130" s="53"/>
+      <c r="O130" s="53"/>
       <c r="P130" s="1"/>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" s="49" t="s">
+      <c r="A131" s="50" t="s">
         <v>35</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -6005,18 +5996,18 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I131" s="1"/>
-      <c r="J131" s="52" t="s">
+      <c r="J131" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K131" s="52"/>
-      <c r="L131" s="52"/>
-      <c r="M131" s="52"/>
-      <c r="N131" s="52"/>
-      <c r="O131" s="52"/>
+      <c r="K131" s="53"/>
+      <c r="L131" s="53"/>
+      <c r="M131" s="53"/>
+      <c r="N131" s="53"/>
+      <c r="O131" s="53"/>
       <c r="P131" s="1"/>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" s="50"/>
+      <c r="A132" s="51"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
@@ -6039,16 +6030,16 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I132" s="1"/>
-      <c r="J132" s="52"/>
-      <c r="K132" s="52"/>
-      <c r="L132" s="52"/>
-      <c r="M132" s="52"/>
-      <c r="N132" s="52"/>
-      <c r="O132" s="52"/>
+      <c r="J132" s="53"/>
+      <c r="K132" s="53"/>
+      <c r="L132" s="53"/>
+      <c r="M132" s="53"/>
+      <c r="N132" s="53"/>
+      <c r="O132" s="53"/>
       <c r="P132" s="1"/>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" s="50"/>
+      <c r="A133" s="51"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
       </c>
@@ -6071,36 +6062,36 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I133" s="1"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
-      <c r="L133" s="52"/>
-      <c r="M133" s="52"/>
-      <c r="N133" s="52"/>
-      <c r="O133" s="52"/>
+      <c r="J133" s="53"/>
+      <c r="K133" s="53"/>
+      <c r="L133" s="53"/>
+      <c r="M133" s="53"/>
+      <c r="N133" s="53"/>
+      <c r="O133" s="53"/>
       <c r="P133" s="1"/>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" s="51"/>
+      <c r="A134" s="52"/>
       <c r="B134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="53"/>
-      <c r="D134" s="53"/>
-      <c r="E134" s="53"/>
-      <c r="F134" s="53"/>
-      <c r="G134" s="53"/>
-      <c r="H134" s="53"/>
+      <c r="C134" s="57"/>
+      <c r="D134" s="57"/>
+      <c r="E134" s="57"/>
+      <c r="F134" s="57"/>
+      <c r="G134" s="57"/>
+      <c r="H134" s="57"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
-      <c r="L134" s="52"/>
-      <c r="M134" s="52"/>
-      <c r="N134" s="52"/>
-      <c r="O134" s="52"/>
+      <c r="J134" s="53"/>
+      <c r="K134" s="53"/>
+      <c r="L134" s="53"/>
+      <c r="M134" s="53"/>
+      <c r="N134" s="53"/>
+      <c r="O134" s="53"/>
       <c r="P134" s="1"/>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" s="49" t="s">
+      <c r="A135" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -6125,18 +6116,18 @@
         <v>1.209274E-27</v>
       </c>
       <c r="I135" s="1"/>
-      <c r="J135" s="52" t="s">
+      <c r="J135" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K135" s="52"/>
-      <c r="L135" s="52"/>
-      <c r="M135" s="52"/>
-      <c r="N135" s="52"/>
-      <c r="O135" s="52"/>
+      <c r="K135" s="53"/>
+      <c r="L135" s="53"/>
+      <c r="M135" s="53"/>
+      <c r="N135" s="53"/>
+      <c r="O135" s="53"/>
       <c r="P135" s="1"/>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" s="50"/>
+      <c r="A136" s="51"/>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
@@ -6159,16 +6150,16 @@
         <v>5.7713939999999998E-2</v>
       </c>
       <c r="I136" s="1"/>
-      <c r="J136" s="52"/>
-      <c r="K136" s="52"/>
-      <c r="L136" s="52"/>
-      <c r="M136" s="52"/>
-      <c r="N136" s="52"/>
-      <c r="O136" s="52"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="53"/>
+      <c r="L136" s="53"/>
+      <c r="M136" s="53"/>
+      <c r="N136" s="53"/>
+      <c r="O136" s="53"/>
       <c r="P136" s="1"/>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" s="50"/>
+      <c r="A137" s="51"/>
       <c r="B137" s="1" t="s">
         <v>8</v>
       </c>
@@ -6191,32 +6182,32 @@
         <v>1.363103E-6</v>
       </c>
       <c r="I137" s="1"/>
-      <c r="J137" s="52"/>
-      <c r="K137" s="52"/>
-      <c r="L137" s="52"/>
-      <c r="M137" s="52"/>
-      <c r="N137" s="52"/>
-      <c r="O137" s="52"/>
+      <c r="J137" s="53"/>
+      <c r="K137" s="53"/>
+      <c r="L137" s="53"/>
+      <c r="M137" s="53"/>
+      <c r="N137" s="53"/>
+      <c r="O137" s="53"/>
       <c r="P137" s="1"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" s="51"/>
+      <c r="A138" s="52"/>
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="53"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="53"/>
-      <c r="F138" s="53"/>
-      <c r="G138" s="53"/>
-      <c r="H138" s="53"/>
+      <c r="C138" s="57"/>
+      <c r="D138" s="57"/>
+      <c r="E138" s="57"/>
+      <c r="F138" s="57"/>
+      <c r="G138" s="57"/>
+      <c r="H138" s="57"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="52"/>
-      <c r="L138" s="52"/>
-      <c r="M138" s="52"/>
-      <c r="N138" s="52"/>
-      <c r="O138" s="52"/>
+      <c r="J138" s="53"/>
+      <c r="K138" s="53"/>
+      <c r="L138" s="53"/>
+      <c r="M138" s="53"/>
+      <c r="N138" s="53"/>
+      <c r="O138" s="53"/>
       <c r="P138" s="1"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
@@ -6239,14 +6230,68 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -6263,68 +6308,14 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6378,7 +6369,7 @@
       <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="57">
+      <c r="A2" s="58">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6401,7 +6392,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
+      <c r="A3" s="59"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -6420,7 +6411,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -6440,7 +6431,7 @@
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -6460,10 +6451,10 @@
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="49" t="s">
         <v>74</v>
       </c>
       <c r="E6" s="1"/>
@@ -6479,7 +6470,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6494,7 +6485,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6510,7 +6501,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6528,7 +6519,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6542,7 +6533,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="57">
+      <c r="A11" s="58">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6570,7 +6561,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="58"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>80</v>
@@ -6591,7 +6582,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="58"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -6608,7 +6599,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="58"/>
+      <c r="A14" s="59"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6621,7 +6612,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="59"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6634,7 +6625,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="59"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -6647,7 +6638,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
+      <c r="A17" s="59"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -6660,7 +6651,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -6792,7 +6783,7 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="57">
+      <c r="A2" s="58">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -6815,10 +6806,10 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
+      <c r="A3" s="59"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="49" t="s">
         <v>74</v>
       </c>
       <c r="E3" s="20" t="s">
@@ -6831,7 +6822,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="E4" s="20" t="s">
@@ -6845,7 +6836,7 @@
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -6857,7 +6848,7 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6870,7 +6861,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6882,7 +6873,7 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6893,7 +6884,7 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6909,7 +6900,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -6922,7 +6913,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="57">
+      <c r="A11" s="58">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -6941,7 +6932,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="58"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>80</v>
@@ -6957,7 +6948,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="58"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -6968,7 +6959,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="58"/>
+      <c r="A14" s="59"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -6980,7 +6971,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="59"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -6992,7 +6983,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="59"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -7002,7 +6993,7 @@
       <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
+      <c r="A17" s="59"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -7012,7 +7003,7 @@
       <c r="H17" s="26"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -7117,7 +7108,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDA28D4-5A8D-4B82-B1F2-D70FA6918129}">
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -7206,7 +7197,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7228,17 +7219,17 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="61" t="s">
+      <c r="I3" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="64"/>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="1" t="s">
         <v>107</v>
       </c>
@@ -7258,15 +7249,15 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="66"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="1" t="s">
         <v>117</v>
       </c>
@@ -7286,15 +7277,15 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="66"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="67"/>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="1" t="s">
         <v>109</v>
       </c>
@@ -7314,15 +7305,15 @@
         <v>0.1837454</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="69"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="50" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -7362,7 +7353,7 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="1" t="s">
         <v>107</v>
       </c>
@@ -7400,7 +7391,7 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="1" t="s">
         <v>108</v>
       </c>
@@ -7438,7 +7429,7 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="1" t="s">
         <v>109</v>
       </c>
@@ -7476,3174 +7467,3292 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
-        <v>11</v>
+      <c r="A11" s="50" t="s">
+        <v>141</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="1">
-        <v>0.27505610000000003</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2.398492E-2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>23.545262000000001</v>
-      </c>
-      <c r="F11" s="1">
-        <v>11.467879999999999</v>
-      </c>
-      <c r="G11" s="2">
-        <v>4.0475789999999998E-11</v>
+      <c r="C11" s="40">
+        <v>-0.67962469999999997</v>
+      </c>
+      <c r="D11" s="40">
+        <v>0.72532470000000004</v>
+      </c>
+      <c r="E11" s="40">
+        <v>23.402695999999999</v>
+      </c>
+      <c r="F11" s="40">
+        <v>-0.93699370000000004</v>
+      </c>
+      <c r="G11" s="40">
+        <v>0.35833147122850001</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1">
-        <v>3.6012679999999998E-2</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1.375581E-2</v>
-      </c>
-      <c r="K11" s="1">
-        <v>55.148274000000001</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2.617998</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1.1395529999999999E-2</v>
-      </c>
+      <c r="I11" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="1">
-        <v>0.19852059999999999</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1.444864E-2</v>
-      </c>
-      <c r="E12" s="1">
-        <v>39.39331</v>
-      </c>
-      <c r="F12" s="1">
-        <v>13.739739999999999</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1.3031699999999999E-16</v>
+      <c r="C12" s="40">
+        <v>-0.8024289</v>
+      </c>
+      <c r="D12" s="40">
+        <v>0.50150589999999995</v>
+      </c>
+      <c r="E12" s="40">
+        <v>37.766705999999999</v>
+      </c>
+      <c r="F12" s="40">
+        <v>-1.600039</v>
+      </c>
+      <c r="G12" s="40">
+        <v>0.11792329999999999</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1">
-        <v>7.6390949999999999E-2</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1.4668270000000001E-2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>54.133626</v>
-      </c>
-      <c r="L12" s="1">
-        <v>5.2079060000000004</v>
-      </c>
-      <c r="M12" s="2">
-        <v>3.0402339999999998E-6</v>
-      </c>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="67"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="1">
-        <v>-3.3437139999999997E-2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>4.8165840000000001E-2</v>
-      </c>
-      <c r="E13" s="1">
-        <v>16.692450000000001</v>
-      </c>
-      <c r="F13" s="1">
-        <v>-0.69420850000000001</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.49710019999999999</v>
+      <c r="C13" s="40">
+        <v>-11.448639999999999</v>
+      </c>
+      <c r="D13" s="40">
+        <v>1.2781750000000001</v>
+      </c>
+      <c r="E13" s="40">
+        <v>14.82489</v>
+      </c>
+      <c r="F13" s="40">
+        <v>-8.9570209999999992</v>
+      </c>
+      <c r="G13" s="40">
+        <v>2.2889089999999999E-7</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="1">
-        <v>-0.1025577</v>
-      </c>
-      <c r="J13" s="1">
-        <v>3.6524609999999999E-2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>11.814360000000001</v>
-      </c>
-      <c r="L13" s="1">
-        <v>-2.8079070000000002</v>
-      </c>
-      <c r="M13" s="2">
-        <v>1.6019390000000001E-2</v>
-      </c>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="67"/>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="1">
-        <v>-7.4605980000000002E-2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3.2539319999999997E-2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>15.191789999999999</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-2.2927949999999999</v>
-      </c>
-      <c r="G14" s="2">
-        <v>3.6532830000000002E-2</v>
+      <c r="C14" s="40">
+        <v>-10.27468</v>
+      </c>
+      <c r="D14" s="40">
+        <v>1.2625949999999999</v>
+      </c>
+      <c r="E14" s="40">
+        <v>13.73147</v>
+      </c>
+      <c r="F14" s="40">
+        <v>-8.1377450000000007</v>
+      </c>
+      <c r="G14" s="40">
+        <v>1.280514E-6</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1">
-        <v>-6.5260349999999995E-2</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2.0409139999999999E-2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>10.9194</v>
-      </c>
-      <c r="L14" s="1">
-        <v>-3.1976040000000001</v>
-      </c>
-      <c r="M14" s="2">
-        <v>8.565675E-3</v>
-      </c>
+      <c r="I14" s="68"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="70"/>
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
-        <v>36</v>
+      <c r="A15" s="50" t="s">
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C15" s="1">
-        <v>0.25910539999999999</v>
+        <v>0.27505610000000003</v>
       </c>
       <c r="D15" s="1">
-        <v>2.38897E-2</v>
+        <v>2.398492E-2</v>
       </c>
       <c r="E15" s="1">
-        <v>23.495559</v>
+        <v>23.545262000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>10.8459</v>
+        <v>11.467879999999999</v>
       </c>
       <c r="G15" s="2">
-        <v>1.261363E-10</v>
+        <v>4.0475789999999998E-11</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1">
-        <v>1.180838E-2</v>
+        <v>3.6012679999999998E-2</v>
       </c>
       <c r="J15" s="1">
-        <v>1.3507180000000001E-2</v>
+        <v>1.375581E-2</v>
       </c>
       <c r="K15" s="1">
-        <v>55.127535999999999</v>
+        <v>55.148274000000001</v>
       </c>
       <c r="L15" s="1">
-        <v>0.8742297</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0.38578590000000001</v>
+        <v>2.617998</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1.1395529999999999E-2</v>
       </c>
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C16" s="1">
-        <v>0.1893232</v>
+        <v>0.19852059999999999</v>
       </c>
       <c r="D16" s="1">
-        <v>1.4590860000000001E-2</v>
+        <v>1.444864E-2</v>
       </c>
       <c r="E16" s="1">
-        <v>39.182360000000003</v>
+        <v>39.39331</v>
       </c>
       <c r="F16" s="1">
-        <v>12.97547</v>
+        <v>13.739739999999999</v>
       </c>
       <c r="G16" s="2">
-        <v>9.1451869999999996E-16</v>
+        <v>1.3031699999999999E-16</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1">
-        <v>6.3492019999999996E-2</v>
+        <v>7.6390949999999999E-2</v>
       </c>
       <c r="J16" s="1">
-        <v>1.5105850000000001E-2</v>
+        <v>1.4668270000000001E-2</v>
       </c>
       <c r="K16" s="1">
-        <v>53.118403999999998</v>
+        <v>54.133626</v>
       </c>
       <c r="L16" s="1">
-        <v>4.2031409999999996</v>
+        <v>5.2079060000000004</v>
       </c>
       <c r="M16" s="2">
-        <v>1.0131990000000001E-4</v>
+        <v>3.0402339999999998E-6</v>
       </c>
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C17" s="1">
-        <v>-3.3733069999999997E-2</v>
+        <v>-3.3437139999999997E-2</v>
       </c>
       <c r="D17" s="1">
-        <v>4.5654569999999998E-2</v>
+        <v>4.8165840000000001E-2</v>
       </c>
       <c r="E17" s="1">
-        <v>16.29635</v>
+        <v>16.692450000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.73887599999999998</v>
+        <v>-0.69420850000000001</v>
       </c>
       <c r="G17" s="1">
-        <v>0.4704913</v>
+        <v>0.49710019999999999</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1">
-        <v>-9.7459550000000006E-2</v>
+        <v>-0.1025577</v>
       </c>
       <c r="J17" s="1">
-        <v>3.5986459999999998E-2</v>
+        <v>3.6524609999999999E-2</v>
       </c>
       <c r="K17" s="1">
-        <v>11.75554</v>
+        <v>11.814360000000001</v>
       </c>
       <c r="L17" s="1">
-        <v>-2.7082280000000001</v>
+        <v>-2.8079070000000002</v>
       </c>
       <c r="M17" s="2">
-        <v>1.9320850000000001E-2</v>
+        <v>1.6019390000000001E-2</v>
       </c>
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="51"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C18" s="1">
-        <v>-7.235192E-2</v>
+        <v>-7.4605980000000002E-2</v>
       </c>
       <c r="D18" s="1">
-        <v>3.050694E-2</v>
+        <v>3.2539319999999997E-2</v>
       </c>
       <c r="E18" s="1">
-        <v>14.92966</v>
+        <v>15.191789999999999</v>
       </c>
       <c r="F18" s="1">
-        <v>-2.3716539999999999</v>
+        <v>-2.2927949999999999</v>
       </c>
       <c r="G18" s="2">
-        <v>3.1591439999999998E-2</v>
+        <v>3.6532830000000002E-2</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1">
-        <v>-5.128456E-2</v>
+        <v>-6.5260349999999995E-2</v>
       </c>
       <c r="J18" s="1">
-        <v>2.117863E-2</v>
+        <v>2.0409139999999999E-2</v>
       </c>
       <c r="K18" s="1">
-        <v>11.11552</v>
+        <v>10.9194</v>
       </c>
       <c r="L18" s="1">
-        <v>-2.4215239999999998</v>
+        <v>-3.1976040000000001</v>
       </c>
       <c r="M18" s="2">
-        <v>3.3703570000000002E-2</v>
+        <v>8.565675E-3</v>
       </c>
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
-        <v>12</v>
+      <c r="A19" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="45">
-        <v>0.16267690000000001</v>
-      </c>
-      <c r="D19" s="45">
-        <v>2.342762E-2</v>
-      </c>
-      <c r="E19" s="45">
-        <v>23.465475999999999</v>
-      </c>
-      <c r="F19" s="45">
-        <v>6.9438079999999998</v>
-      </c>
-      <c r="G19" s="45">
-        <v>3.98194E-7</v>
+      <c r="C19" s="1">
+        <v>0.25910539999999999</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2.38897E-2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>23.495559</v>
+      </c>
+      <c r="F19" s="1">
+        <v>10.8459</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1.261363E-10</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="45">
-        <v>-2.5494809999999999E-4</v>
-      </c>
-      <c r="J19" s="45">
-        <v>1.9431219999999999E-4</v>
-      </c>
-      <c r="K19" s="45">
-        <v>55.507640000000002</v>
-      </c>
-      <c r="L19" s="45">
-        <v>-1.3120540000000001</v>
-      </c>
-      <c r="M19" s="45">
-        <v>0.19490214432</v>
+      <c r="I19" s="1">
+        <v>1.180838E-2</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.3507180000000001E-2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>55.127535999999999</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0.8742297</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0.38578590000000001</v>
       </c>
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="45">
-        <v>0.1318241</v>
-      </c>
-      <c r="D20" s="45">
-        <v>1.53215E-2</v>
-      </c>
-      <c r="E20" s="45">
-        <v>38.868819999999999</v>
-      </c>
-      <c r="F20" s="45">
-        <v>8.603866</v>
-      </c>
-      <c r="G20" s="46">
-        <v>1.5523469999999999E-10</v>
+      <c r="C20" s="1">
+        <v>0.1893232</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.4590860000000001E-2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>39.182360000000003</v>
+      </c>
+      <c r="F20" s="1">
+        <v>12.97547</v>
+      </c>
+      <c r="G20" s="2">
+        <v>9.1451869999999996E-16</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="45">
-        <v>2.431771E-4</v>
-      </c>
-      <c r="J20" s="45">
-        <v>3.0047830000000001E-4</v>
-      </c>
-      <c r="K20" s="45">
-        <v>54.111055</v>
-      </c>
-      <c r="L20" s="45">
-        <v>0.80930000000000002</v>
-      </c>
-      <c r="M20" s="45">
-        <v>0.4218870666026</v>
+      <c r="I20" s="1">
+        <v>6.3492019999999996E-2</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.5105850000000001E-2</v>
+      </c>
+      <c r="K20" s="1">
+        <v>53.118403999999998</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4.2031409999999996</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1.0131990000000001E-4</v>
       </c>
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="45">
-        <v>-7.6752669999999995E-2</v>
-      </c>
-      <c r="D21" s="45">
-        <v>5.0189159999999997E-2</v>
-      </c>
-      <c r="E21" s="45">
-        <v>16.372039999999998</v>
-      </c>
-      <c r="F21" s="45">
-        <v>-1.5292680000000001</v>
-      </c>
-      <c r="G21" s="46">
-        <v>0.14528840000000001</v>
+      <c r="C21" s="1">
+        <v>-3.3733069999999997E-2</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4.5654569999999998E-2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>16.29635</v>
+      </c>
+      <c r="F21" s="1">
+        <v>-0.73887599999999998</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.4704913</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="45">
-        <v>-2.3284180000000001E-3</v>
-      </c>
-      <c r="J21" s="45">
-        <v>4.9925909999999998E-4</v>
-      </c>
-      <c r="K21" s="45">
-        <v>11.371589999999999</v>
-      </c>
-      <c r="L21" s="45">
-        <v>-4.6637459999999997</v>
-      </c>
-      <c r="M21" s="45">
-        <v>6.3120474729999999E-4</v>
+      <c r="I21" s="1">
+        <v>-9.7459550000000006E-2</v>
+      </c>
+      <c r="J21" s="1">
+        <v>3.5986459999999998E-2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>11.75554</v>
+      </c>
+      <c r="L21" s="1">
+        <v>-2.7082280000000001</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1.9320850000000001E-2</v>
       </c>
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="51"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="45">
-        <v>-6.6752569999999997E-2</v>
-      </c>
-      <c r="D22" s="45">
-        <v>3.12787E-2</v>
-      </c>
-      <c r="E22" s="45">
-        <v>14.8775</v>
-      </c>
-      <c r="F22" s="45">
-        <v>-2.1341220000000001</v>
-      </c>
-      <c r="G22" s="46">
-        <v>4.9892260000000001E-2</v>
+      <c r="C22" s="1">
+        <v>-7.235192E-2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3.050694E-2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>14.92966</v>
+      </c>
+      <c r="F22" s="1">
+        <v>-2.3716539999999999</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3.1591439999999998E-2</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="45">
-        <v>-1.939112E-3</v>
-      </c>
-      <c r="J22" s="45">
-        <v>3.8723229999999999E-4</v>
-      </c>
-      <c r="K22" s="45">
-        <v>13.92292</v>
-      </c>
-      <c r="L22" s="45">
-        <v>-5.0076210000000003</v>
-      </c>
-      <c r="M22" s="45" t="s">
-        <v>146</v>
+      <c r="I22" s="1">
+        <v>-5.128456E-2</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2.117863E-2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>11.11552</v>
+      </c>
+      <c r="L22" s="1">
+        <v>-2.4215239999999998</v>
+      </c>
+      <c r="M22" s="2">
+        <v>3.3703570000000002E-2</v>
       </c>
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
-        <v>13</v>
+      <c r="A23" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="1">
-        <v>0.26141530000000002</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2.107347E-2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>22.795461</v>
-      </c>
-      <c r="F23" s="1">
-        <v>12.404952</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1.2861529999999999E-11</v>
+      <c r="C23" s="45">
+        <v>0.16267690000000001</v>
+      </c>
+      <c r="D23" s="45">
+        <v>2.342762E-2</v>
+      </c>
+      <c r="E23" s="45">
+        <v>23.465475999999999</v>
+      </c>
+      <c r="F23" s="45">
+        <v>6.9438079999999998</v>
+      </c>
+      <c r="G23" s="45">
+        <v>3.98194E-7</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="1">
-        <v>0.1080815</v>
-      </c>
-      <c r="J23" s="1">
-        <v>6.8329970000000004E-2</v>
-      </c>
-      <c r="K23" s="1">
-        <v>55.203989999999997</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1.581758</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0.11941789999999999</v>
+      <c r="I23" s="45">
+        <v>-2.5494809999999999E-4</v>
+      </c>
+      <c r="J23" s="45">
+        <v>1.9431219999999999E-4</v>
+      </c>
+      <c r="K23" s="45">
+        <v>55.507640000000002</v>
+      </c>
+      <c r="L23" s="45">
+        <v>-1.3120540000000001</v>
+      </c>
+      <c r="M23" s="45">
+        <v>0.19490214432</v>
       </c>
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="1">
-        <v>0.16795750000000001</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1.305196E-2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>38.406829999999999</v>
-      </c>
-      <c r="F24" s="1">
-        <v>12.86838</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1.6708039999999999E-15</v>
+      <c r="C24" s="45">
+        <v>0.1318241</v>
+      </c>
+      <c r="D24" s="45">
+        <v>1.53215E-2</v>
+      </c>
+      <c r="E24" s="45">
+        <v>38.868819999999999</v>
+      </c>
+      <c r="F24" s="45">
+        <v>8.603866</v>
+      </c>
+      <c r="G24" s="46">
+        <v>1.5523469999999999E-10</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="1">
-        <v>0.34042270000000002</v>
-      </c>
-      <c r="J24" s="1">
-        <v>7.1749140000000003E-2</v>
-      </c>
-      <c r="K24" s="1">
-        <v>54.122332999999998</v>
-      </c>
-      <c r="L24" s="1">
-        <v>4.7446250000000001</v>
-      </c>
-      <c r="M24" s="2">
-        <v>1.5661770000000001E-5</v>
+      <c r="I24" s="45">
+        <v>2.431771E-4</v>
+      </c>
+      <c r="J24" s="45">
+        <v>3.0047830000000001E-4</v>
+      </c>
+      <c r="K24" s="45">
+        <v>54.111055</v>
+      </c>
+      <c r="L24" s="45">
+        <v>0.80930000000000002</v>
+      </c>
+      <c r="M24" s="45">
+        <v>0.4218870666026</v>
       </c>
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="1">
-        <v>2.4449390000000001E-2</v>
-      </c>
-      <c r="D25" s="1">
-        <v>4.0505119999999999E-2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>15.698370000000001</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0.60361220000000004</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0.55472399999999999</v>
+      <c r="C25" s="45">
+        <v>-7.6752669999999995E-2</v>
+      </c>
+      <c r="D25" s="45">
+        <v>5.0189159999999997E-2</v>
+      </c>
+      <c r="E25" s="45">
+        <v>16.372039999999998</v>
+      </c>
+      <c r="F25" s="45">
+        <v>-1.5292680000000001</v>
+      </c>
+      <c r="G25" s="46">
+        <v>0.14528840000000001</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="1">
-        <v>-0.11951639999999999</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0.1459646</v>
-      </c>
-      <c r="K25" s="1">
-        <v>11.39526</v>
-      </c>
-      <c r="L25" s="1">
-        <v>-0.81880399999999998</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0.4296896</v>
+      <c r="I25" s="45">
+        <v>-2.3284180000000001E-3</v>
+      </c>
+      <c r="J25" s="45">
+        <v>4.9925909999999998E-4</v>
+      </c>
+      <c r="K25" s="45">
+        <v>11.371589999999999</v>
+      </c>
+      <c r="L25" s="45">
+        <v>-4.6637459999999997</v>
+      </c>
+      <c r="M25" s="45">
+        <v>6.3120474729999999E-4</v>
       </c>
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="1">
-        <v>-2.5180310000000001E-2</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2.9583849999999998E-2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>15.65354</v>
-      </c>
-      <c r="F26" s="1">
-        <v>-0.85115050000000003</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0.4075182</v>
+      <c r="C26" s="45">
+        <v>-6.6752569999999997E-2</v>
+      </c>
+      <c r="D26" s="45">
+        <v>3.12787E-2</v>
+      </c>
+      <c r="E26" s="45">
+        <v>14.8775</v>
+      </c>
+      <c r="F26" s="45">
+        <v>-2.1341220000000001</v>
+      </c>
+      <c r="G26" s="46">
+        <v>4.9892260000000001E-2</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1">
-        <v>0.1035258</v>
-      </c>
-      <c r="J26" s="1">
-        <v>8.4846459999999999E-2</v>
-      </c>
-      <c r="K26" s="1">
-        <v>10.68332</v>
-      </c>
-      <c r="L26" s="1">
-        <v>1.2201550000000001</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.2486556</v>
+      <c r="I26" s="45">
+        <v>-1.939112E-3</v>
+      </c>
+      <c r="J26" s="45">
+        <v>3.8723229999999999E-4</v>
+      </c>
+      <c r="K26" s="45">
+        <v>13.92292</v>
+      </c>
+      <c r="L26" s="45">
+        <v>-5.0076210000000003</v>
+      </c>
+      <c r="M26" s="45" t="s">
+        <v>146</v>
       </c>
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
-        <v>14</v>
+      <c r="A27" s="50" t="s">
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C27" s="1">
-        <v>0.16815289999999999</v>
+        <v>0.26141530000000002</v>
       </c>
       <c r="D27" s="1">
-        <v>1.333603E-2</v>
+        <v>2.107347E-2</v>
       </c>
       <c r="E27" s="1">
-        <v>22.543147000000001</v>
+        <v>22.795461</v>
       </c>
       <c r="F27" s="1">
-        <v>12.608919999999999</v>
+        <v>12.404952</v>
       </c>
       <c r="G27" s="2">
-        <v>1.085642E-11</v>
+        <v>1.2861529999999999E-11</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1">
-        <v>5.9286020000000002E-2</v>
+        <v>0.1080815</v>
       </c>
       <c r="J27" s="1">
-        <v>0.1302239</v>
+        <v>6.8329970000000004E-2</v>
       </c>
       <c r="K27" s="1">
-        <v>55.180911999999999</v>
+        <v>55.203989999999997</v>
       </c>
       <c r="L27" s="1">
-        <v>0.45526230000000001</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0.65070680000000003</v>
+        <v>1.581758</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0.11941789999999999</v>
       </c>
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C28" s="1">
-        <v>0.1095054</v>
+        <v>0.16795750000000001</v>
       </c>
       <c r="D28" s="1">
-        <v>7.9211479999999994E-3</v>
+        <v>1.305196E-2</v>
       </c>
       <c r="E28" s="1">
-        <v>39.579543000000001</v>
+        <v>38.406829999999999</v>
       </c>
       <c r="F28" s="1">
-        <v>13.82443</v>
+        <v>12.86838</v>
       </c>
       <c r="G28" s="2">
-        <v>9.7457139999999995E-17</v>
+        <v>1.6708039999999999E-15</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1">
-        <v>0.51176239999999995</v>
+        <v>0.34042270000000002</v>
       </c>
       <c r="J28" s="1">
-        <v>0.1491497</v>
+        <v>7.1749140000000003E-2</v>
       </c>
       <c r="K28" s="1">
-        <v>54.192520000000002</v>
+        <v>54.122332999999998</v>
       </c>
       <c r="L28" s="1">
-        <v>3.4312</v>
+        <v>4.7446250000000001</v>
       </c>
       <c r="M28" s="2">
-        <v>1.157145E-3</v>
+        <v>1.5661770000000001E-5</v>
       </c>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C29" s="1">
-        <v>4.9169679999999999E-3</v>
+        <v>2.4449390000000001E-2</v>
       </c>
       <c r="D29" s="1">
-        <v>2.157123E-2</v>
+        <v>4.0505119999999999E-2</v>
       </c>
       <c r="E29" s="1">
-        <v>14.439249999999999</v>
+        <v>15.698370000000001</v>
       </c>
       <c r="F29" s="1">
-        <v>0.227941</v>
+        <v>0.60361220000000004</v>
       </c>
       <c r="G29" s="1">
-        <v>0.82288839999999996</v>
+        <v>0.55472399999999999</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1">
-        <v>-0.38848120000000003</v>
+        <v>-0.11951639999999999</v>
       </c>
       <c r="J29" s="1">
-        <v>0.30375679999999999</v>
+        <v>0.1459646</v>
       </c>
       <c r="K29" s="1">
-        <v>10.94359</v>
+        <v>11.39526</v>
       </c>
       <c r="L29" s="1">
-        <v>-1.2789219999999999</v>
+        <v>-0.81880399999999998</v>
       </c>
       <c r="M29" s="1">
-        <v>0.22737859999999999</v>
+        <v>0.4296896</v>
       </c>
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C30" s="1">
-        <v>-2.9254499999999999E-2</v>
+        <v>-2.5180310000000001E-2</v>
       </c>
       <c r="D30" s="1">
-        <v>1.6422550000000001E-2</v>
+        <v>2.9583849999999998E-2</v>
       </c>
       <c r="E30" s="1">
-        <v>14.43604</v>
+        <v>15.65354</v>
       </c>
       <c r="F30" s="1">
-        <v>-1.781361</v>
-      </c>
-      <c r="G30" s="3">
-        <v>9.5896949999999995E-2</v>
+        <v>-0.85115050000000003</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.4075182</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1">
-        <v>5.3543380000000002E-2</v>
+        <v>0.1035258</v>
       </c>
       <c r="J30" s="1">
-        <v>0.17968680000000001</v>
+        <v>8.4846459999999999E-2</v>
       </c>
       <c r="K30" s="1">
-        <v>11.420360000000001</v>
+        <v>10.68332</v>
       </c>
       <c r="L30" s="1">
-        <v>0.29798170000000002</v>
+        <v>1.2201550000000001</v>
       </c>
       <c r="M30" s="1">
-        <v>0.77106850000000005</v>
+        <v>0.2486556</v>
       </c>
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
-        <v>15</v>
+      <c r="A31" s="50" t="s">
+        <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C31" s="1">
-        <v>0.10404770000000001</v>
+        <v>0.16815289999999999</v>
       </c>
       <c r="D31" s="1">
-        <v>1.3194920000000001E-2</v>
+        <v>1.333603E-2</v>
       </c>
       <c r="E31" s="1">
-        <v>22.166536000000001</v>
+        <v>22.543147000000001</v>
       </c>
       <c r="F31" s="1">
-        <v>7.8854410000000001</v>
+        <v>12.608919999999999</v>
       </c>
       <c r="G31" s="2">
-        <v>7.1088440000000002E-8</v>
+        <v>1.085642E-11</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1">
-        <v>3.2186840000000001E-2</v>
+        <v>5.9286020000000002E-2</v>
       </c>
       <c r="J31" s="1">
-        <v>1.052636E-2</v>
+        <v>0.1302239</v>
       </c>
       <c r="K31" s="1">
-        <v>55.036504999999998</v>
+        <v>55.180911999999999</v>
       </c>
       <c r="L31" s="1">
-        <v>3.0577380000000001</v>
-      </c>
-      <c r="M31" s="2">
-        <v>3.439386E-3</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>0.45526230000000001</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0.65070680000000003</v>
+      </c>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
+      <c r="A32" s="51"/>
       <c r="B32" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C32" s="1">
-        <v>3.6833039999999997E-2</v>
+        <v>0.1095054</v>
       </c>
       <c r="D32" s="1">
-        <v>8.9172230000000002E-3</v>
+        <v>7.9211479999999994E-3</v>
       </c>
       <c r="E32" s="1">
-        <v>38.799550000000004</v>
+        <v>39.579543000000001</v>
       </c>
       <c r="F32" s="1">
-        <v>4.1305500000000004</v>
+        <v>13.82443</v>
       </c>
       <c r="G32" s="2">
-        <v>1.8621800000000001E-4</v>
+        <v>9.7457139999999995E-17</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1">
-        <v>5.4472277E-2</v>
+        <v>0.51176239999999995</v>
       </c>
       <c r="J32" s="1">
-        <v>8.6164620000000001E-3</v>
+        <v>0.1491497</v>
       </c>
       <c r="K32" s="1">
-        <v>52.260210000000001</v>
+        <v>54.192520000000002</v>
       </c>
       <c r="L32" s="1">
-        <v>6.321885</v>
+        <v>3.4312</v>
       </c>
       <c r="M32" s="2">
-        <v>5.8418710000000002E-8</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>1.157145E-3</v>
+      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C33" s="1">
-        <v>0.1045321</v>
+        <v>4.9169679999999999E-3</v>
       </c>
       <c r="D33" s="1">
-        <v>8.9959949999999997E-3</v>
+        <v>2.157123E-2</v>
       </c>
       <c r="E33" s="1">
-        <v>41</v>
+        <v>14.439249999999999</v>
       </c>
       <c r="F33" s="1">
-        <v>11.61985</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1.497837E-14</v>
+        <v>0.227941</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.82288839999999996</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1">
-        <v>9.9455870000000002E-2</v>
+        <v>-0.38848120000000003</v>
       </c>
       <c r="J33" s="1">
-        <v>1.0855979999999999E-2</v>
+        <v>0.30375679999999999</v>
       </c>
       <c r="K33" s="1">
-        <v>13.36983</v>
+        <v>10.94359</v>
       </c>
       <c r="L33" s="1">
-        <v>9.1613889999999998</v>
-      </c>
-      <c r="M33" s="2">
-        <v>3.9456639999999998E-7</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>123</v>
-      </c>
+        <v>-1.2789219999999999</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0.22737859999999999</v>
+      </c>
+      <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="51"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C34" s="1">
-        <v>3.843543E-2</v>
+        <v>-2.9254499999999999E-2</v>
       </c>
       <c r="D34" s="1">
-        <v>1.6573709999999998E-2</v>
+        <v>1.6422550000000001E-2</v>
       </c>
       <c r="E34" s="1">
-        <v>12.793609999999999</v>
+        <v>14.43604</v>
       </c>
       <c r="F34" s="1">
-        <v>2.319061</v>
-      </c>
-      <c r="G34" s="2">
-        <v>3.7607300000000003E-2</v>
+        <v>-1.781361</v>
+      </c>
+      <c r="G34" s="3">
+        <v>9.5896949999999995E-2</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1">
-        <v>0.12323046</v>
+        <v>5.3543380000000002E-2</v>
       </c>
       <c r="J34" s="1">
-        <v>1.5396505E-2</v>
+        <v>0.17968680000000001</v>
       </c>
       <c r="K34" s="1">
-        <v>15.15973</v>
+        <v>11.420360000000001</v>
       </c>
       <c r="L34" s="1">
-        <v>8.0037950000000002</v>
-      </c>
-      <c r="M34" s="2">
-        <v>7.9669659999999998E-7</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>0.29798170000000002</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0.77106850000000005</v>
+      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
-        <v>16</v>
+      <c r="A35" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C35" s="1">
-        <v>-9.9169900000000005E-2</v>
+        <v>0.10404770000000001</v>
       </c>
       <c r="D35" s="1">
-        <v>7.6156770000000004E-3</v>
+        <v>1.3194920000000001E-2</v>
       </c>
       <c r="E35" s="1">
-        <v>24.117732</v>
+        <v>22.166536000000001</v>
       </c>
       <c r="F35" s="1">
-        <v>-13.02181</v>
+        <v>7.8854410000000001</v>
       </c>
       <c r="G35" s="2">
-        <v>2.1010249999999999E-12</v>
+        <v>7.1088440000000002E-8</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1">
-        <v>-3.4572279999999997E-2</v>
+        <v>3.2186840000000001E-2</v>
       </c>
       <c r="J35" s="1">
-        <v>8.7322029999999991E-3</v>
+        <v>1.052636E-2</v>
       </c>
       <c r="K35" s="1">
-        <v>60</v>
+        <v>55.036504999999998</v>
       </c>
       <c r="L35" s="1">
-        <v>-3.9591699999999999</v>
+        <v>3.0577380000000001</v>
       </c>
       <c r="M35" s="2">
-        <v>2.0194479999999999E-4</v>
+        <v>3.439386E-3</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C36" s="1">
-        <v>-5.779488E-2</v>
+        <v>3.6833039999999997E-2</v>
       </c>
       <c r="D36" s="1">
-        <v>5.7489029999999997E-3</v>
+        <v>8.9172230000000002E-3</v>
       </c>
       <c r="E36" s="1">
-        <v>40.271169999999998</v>
+        <v>38.799550000000004</v>
       </c>
       <c r="F36" s="1">
-        <v>-10.0532</v>
+        <v>4.1305500000000004</v>
       </c>
       <c r="G36" s="2">
-        <v>1.5358250000000001E-12</v>
+        <v>1.8621800000000001E-4</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1">
-        <v>-5.8530619999999998E-2</v>
+        <v>5.4472277E-2</v>
       </c>
       <c r="J36" s="1">
-        <v>9.5787719999999993E-3</v>
+        <v>8.6164620000000001E-3</v>
       </c>
       <c r="K36" s="1">
-        <v>51.236131</v>
+        <v>52.260210000000001</v>
       </c>
       <c r="L36" s="1">
-        <v>-6.1104520000000004</v>
+        <v>6.321885</v>
       </c>
       <c r="M36" s="2">
-        <v>1.3548390000000001E-7</v>
+        <v>5.8418710000000002E-8</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C37" s="1">
-        <v>-4.2352229999999998E-2</v>
+        <v>0.1045321</v>
       </c>
       <c r="D37" s="1">
-        <v>7.6791539999999997E-3</v>
+        <v>8.9959949999999997E-3</v>
       </c>
       <c r="E37" s="1">
-        <v>17.375530000000001</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1">
-        <v>-5.5152200000000002</v>
+        <v>11.61985</v>
       </c>
       <c r="G37" s="2">
-        <v>3.5006389999999997E-5</v>
+        <v>1.497837E-14</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1">
-        <v>-3.2332029999999998E-2</v>
+        <v>9.9455870000000002E-2</v>
       </c>
       <c r="J37" s="1">
-        <v>1.088914E-2</v>
+        <v>1.0855979999999999E-2</v>
       </c>
       <c r="K37" s="1">
-        <v>61</v>
+        <v>13.36983</v>
       </c>
       <c r="L37" s="1">
-        <v>-2.9692001000000001</v>
+        <v>9.1613889999999998</v>
       </c>
       <c r="M37" s="2">
-        <v>4.2635360000000001E-3</v>
+        <v>3.9456639999999998E-7</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="51"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C38" s="1">
-        <v>7.5999539999999999E-3</v>
+        <v>3.843543E-2</v>
       </c>
       <c r="D38" s="1">
-        <v>1.132999E-2</v>
+        <v>1.6573709999999998E-2</v>
       </c>
       <c r="E38" s="1">
-        <v>12.42445</v>
+        <v>12.793609999999999</v>
       </c>
       <c r="F38" s="1">
-        <v>0.67078190000000004</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0.51463610000000004</v>
+        <v>2.319061</v>
+      </c>
+      <c r="G38" s="2">
+        <v>3.7607300000000003E-2</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1">
-        <v>-5.6981190000000001E-2</v>
+        <v>0.12323046</v>
       </c>
       <c r="J38" s="1">
-        <v>9.5599729999999994E-3</v>
+        <v>1.5396505E-2</v>
       </c>
       <c r="K38" s="1">
-        <v>16.19933</v>
+        <v>15.15973</v>
       </c>
       <c r="L38" s="1">
-        <v>-5.9603929999999998</v>
+        <v>8.0037950000000002</v>
       </c>
       <c r="M38" s="2">
-        <v>1.895906E-5</v>
+        <v>7.9669659999999998E-7</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="49" t="s">
-        <v>17</v>
+      <c r="A39" s="50" t="s">
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C39" s="1">
-        <v>3.6476649999999999E-2</v>
+        <v>-9.9169900000000005E-2</v>
       </c>
       <c r="D39" s="1">
-        <v>5.8868899999999997E-3</v>
+        <v>7.6156770000000004E-3</v>
       </c>
       <c r="E39" s="1">
-        <v>25.09554</v>
+        <v>24.117732</v>
       </c>
       <c r="F39" s="1">
-        <v>6.1962510000000002</v>
+        <v>-13.02181</v>
       </c>
       <c r="G39" s="2">
-        <v>1.7340119999999999E-6</v>
+        <v>2.1010249999999999E-12</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1">
-        <v>5.2231909999999999E-2</v>
+        <v>-3.4572279999999997E-2</v>
       </c>
       <c r="J39" s="1">
-        <v>3.8609439999999998E-3</v>
+        <v>8.7322029999999991E-3</v>
       </c>
       <c r="K39" s="1">
-        <v>57.451040999999996</v>
+        <v>60</v>
       </c>
       <c r="L39" s="1">
-        <v>13.528280000000001</v>
+        <v>-3.9591699999999999</v>
       </c>
       <c r="M39" s="2">
-        <v>1.648921E-19</v>
-      </c>
-      <c r="N39" s="1"/>
+        <v>2.0194479999999999E-4</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C40" s="1">
-        <v>2.235734E-2</v>
+        <v>-5.779488E-2</v>
       </c>
       <c r="D40" s="1">
-        <v>4.8859400000000001E-3</v>
+        <v>5.7489029999999997E-3</v>
       </c>
       <c r="E40" s="1">
-        <v>41.205199999999998</v>
+        <v>40.271169999999998</v>
       </c>
       <c r="F40" s="1">
-        <v>4.5758530000000004</v>
+        <v>-10.0532</v>
       </c>
       <c r="G40" s="2">
-        <v>4.3017260000000003E-5</v>
+        <v>1.5358250000000001E-12</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1">
-        <v>3.4868650000000001E-2</v>
+        <v>-5.8530619999999998E-2</v>
       </c>
       <c r="J40" s="1">
-        <v>4.8541469999999996E-3</v>
+        <v>9.5787719999999993E-3</v>
       </c>
       <c r="K40" s="1">
-        <v>52.909427000000001</v>
+        <v>51.236131</v>
       </c>
       <c r="L40" s="1">
-        <v>7.1832700000000003</v>
+        <v>-6.1104520000000004</v>
       </c>
       <c r="M40" s="2">
-        <v>2.3070910000000001E-9</v>
-      </c>
-      <c r="N40" s="1"/>
+        <v>1.3548390000000001E-7</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1">
-        <v>4.6180759999999996E-3</v>
+        <v>-4.2352229999999998E-2</v>
       </c>
       <c r="D41" s="1">
-        <v>6.2062740000000003E-3</v>
+        <v>7.6791539999999997E-3</v>
       </c>
       <c r="E41" s="1">
-        <v>9.3979540000000004</v>
+        <v>17.375530000000001</v>
       </c>
       <c r="F41" s="1">
-        <v>0.74409800000000004</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0.4750103</v>
+        <v>-5.5152200000000002</v>
+      </c>
+      <c r="G41" s="2">
+        <v>3.5006389999999997E-5</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1">
-        <v>-8.2717769999999993E-3</v>
+        <v>-3.2332029999999998E-2</v>
       </c>
       <c r="J41" s="1">
-        <v>4.5580619999999999E-3</v>
+        <v>1.088914E-2</v>
       </c>
       <c r="K41" s="1">
-        <v>11.38397</v>
+        <v>61</v>
       </c>
       <c r="L41" s="1">
-        <v>-1.8147580000000001</v>
-      </c>
-      <c r="M41" s="3">
-        <v>9.5976409999999998E-2</v>
-      </c>
-      <c r="N41" s="1"/>
+        <v>-2.9692001000000001</v>
+      </c>
+      <c r="M41" s="2">
+        <v>4.2635360000000001E-3</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="51"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C42" s="1">
-        <v>-8.7482029999999995E-3</v>
+        <v>7.5999539999999999E-3</v>
       </c>
       <c r="D42" s="1">
-        <v>6.7380959999999998E-3</v>
+        <v>1.132999E-2</v>
       </c>
       <c r="E42" s="1">
-        <v>11.10463</v>
+        <v>12.42445</v>
       </c>
       <c r="F42" s="1">
-        <v>-1.2983199999999999</v>
+        <v>0.67078190000000004</v>
       </c>
       <c r="G42" s="1">
-        <v>0.22049369999999999</v>
+        <v>0.51463610000000004</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1">
-        <v>-2.4618979999999999E-2</v>
+        <v>-5.6981190000000001E-2</v>
       </c>
       <c r="J42" s="1">
-        <v>6.5856999999999999E-3</v>
+        <v>9.5599729999999994E-3</v>
       </c>
       <c r="K42" s="1">
-        <v>14.47678</v>
+        <v>16.19933</v>
       </c>
       <c r="L42" s="1">
-        <v>-3.738248</v>
+        <v>-5.9603929999999998</v>
       </c>
       <c r="M42" s="2">
-        <v>2.090588E-3</v>
-      </c>
-      <c r="N42" s="1"/>
+        <v>1.895906E-5</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="49" t="s">
-        <v>147</v>
+      <c r="A43" s="50" t="s">
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
+      <c r="C43" s="1">
+        <v>3.6476649999999999E-2</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5.8868899999999997E-3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>25.09554</v>
+      </c>
+      <c r="F43" s="1">
+        <v>6.1962510000000002</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1.7340119999999999E-6</v>
+      </c>
       <c r="H43" s="1"/>
-      <c r="I43" s="45">
-        <v>-1.7478199999999999E-2</v>
-      </c>
-      <c r="J43" s="45">
-        <v>7.7458099999999997E-3</v>
-      </c>
-      <c r="K43" s="45">
-        <v>56.319026999999998</v>
-      </c>
-      <c r="L43" s="45">
-        <v>-2.256472</v>
-      </c>
-      <c r="M43" s="46">
-        <v>2.2794061000000001E-2</v>
+      <c r="I43" s="1">
+        <v>5.2231909999999999E-2</v>
+      </c>
+      <c r="J43" s="1">
+        <v>3.8609439999999998E-3</v>
+      </c>
+      <c r="K43" s="1">
+        <v>57.451040999999996</v>
+      </c>
+      <c r="L43" s="1">
+        <v>13.528280000000001</v>
+      </c>
+      <c r="M43" s="2">
+        <v>1.648921E-19</v>
       </c>
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
+      <c r="C44" s="1">
+        <v>2.235734E-2</v>
+      </c>
+      <c r="D44" s="1">
+        <v>4.8859400000000001E-3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>41.205199999999998</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4.5758530000000004</v>
+      </c>
+      <c r="G44" s="2">
+        <v>4.3017260000000003E-5</v>
+      </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="45">
-        <v>-2.3552070000000001E-2</v>
-      </c>
-      <c r="J44" s="45">
-        <v>6.7560479999999997E-3</v>
-      </c>
-      <c r="K44" s="45">
-        <v>54.097791000000001</v>
-      </c>
-      <c r="L44" s="45">
-        <v>-3.4860709999999999</v>
-      </c>
-      <c r="M44" s="46">
-        <v>9.8065299999999995E-4</v>
+      <c r="I44" s="1">
+        <v>3.4868650000000001E-2</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4.8541469999999996E-3</v>
+      </c>
+      <c r="K44" s="1">
+        <v>52.909427000000001</v>
+      </c>
+      <c r="L44" s="1">
+        <v>7.1832700000000003</v>
+      </c>
+      <c r="M44" s="2">
+        <v>2.3070910000000001E-9</v>
       </c>
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
+      <c r="C45" s="1">
+        <v>4.6180759999999996E-3</v>
+      </c>
+      <c r="D45" s="1">
+        <v>6.2062740000000003E-3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>9.3979540000000004</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0.74409800000000004</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.4750103</v>
+      </c>
       <c r="H45" s="1"/>
-      <c r="I45" s="45">
-        <v>-2.6797439999999999E-2</v>
-      </c>
-      <c r="J45" s="45">
-        <v>1.099955E-2</v>
-      </c>
-      <c r="K45" s="45">
-        <v>13.570510000000001</v>
-      </c>
-      <c r="L45" s="45">
-        <v>-2.4262299999999999</v>
-      </c>
-      <c r="M45" s="46">
-        <v>2.928103E-2</v>
+      <c r="I45" s="1">
+        <v>-8.2717769999999993E-3</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4.5580619999999999E-3</v>
+      </c>
+      <c r="K45" s="1">
+        <v>11.38397</v>
+      </c>
+      <c r="L45" s="1">
+        <v>-1.8147580000000001</v>
+      </c>
+      <c r="M45" s="3">
+        <v>9.5976409999999998E-2</v>
       </c>
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="51"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
+      <c r="C46" s="1">
+        <v>-8.7482029999999995E-3</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6.7380959999999998E-3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>11.10463</v>
+      </c>
+      <c r="F46" s="1">
+        <v>-1.2983199999999999</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.22049369999999999</v>
+      </c>
       <c r="H46" s="1"/>
-      <c r="I46" s="45">
-        <v>-3.3645590000000003E-2</v>
-      </c>
-      <c r="J46" s="45">
-        <v>1.265696E-2</v>
-      </c>
-      <c r="K46" s="45">
-        <v>13.256600000000001</v>
-      </c>
-      <c r="L46" s="45">
-        <v>-2.6582690000000002</v>
-      </c>
-      <c r="M46" s="46">
-        <v>1.943344E-2</v>
+      <c r="I46" s="1">
+        <v>-2.4618979999999999E-2</v>
+      </c>
+      <c r="J46" s="1">
+        <v>6.5856999999999999E-3</v>
+      </c>
+      <c r="K46" s="1">
+        <v>14.47678</v>
+      </c>
+      <c r="L46" s="1">
+        <v>-3.738248</v>
+      </c>
+      <c r="M46" s="2">
+        <v>2.090588E-3</v>
       </c>
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="49" t="s">
-        <v>143</v>
+      <c r="A47" s="50" t="s">
+        <v>147</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
       <c r="H47" s="1"/>
       <c r="I47" s="45">
-        <v>-8.3753321000000006E-3</v>
+        <v>-1.7478199999999999E-2</v>
       </c>
       <c r="J47" s="45">
-        <v>8.9984460000000002E-3</v>
+        <v>7.7458099999999997E-3</v>
       </c>
       <c r="K47" s="45">
-        <v>56.69021</v>
+        <v>56.319026999999998</v>
       </c>
       <c r="L47" s="45">
-        <v>-0.93075200000000002</v>
+        <v>-2.256472</v>
       </c>
       <c r="M47" s="46">
-        <v>0.35592869999999999</v>
+        <v>2.2794061000000001E-2</v>
       </c>
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
       <c r="H48" s="1"/>
       <c r="I48" s="45">
-        <v>6.2885479999999997E-3</v>
+        <v>-2.3552070000000001E-2</v>
       </c>
       <c r="J48" s="45">
-        <v>1.0130220000000001E-2</v>
+        <v>6.7560479999999997E-3</v>
       </c>
       <c r="K48" s="45">
-        <v>54.056728</v>
+        <v>54.097791000000001</v>
       </c>
       <c r="L48" s="45">
-        <v>0.62077130000000003</v>
+        <v>-3.4860709999999999</v>
       </c>
       <c r="M48" s="46">
-        <v>0.53735880000000003</v>
+        <v>9.8065299999999995E-4</v>
       </c>
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="1"/>
       <c r="I49" s="45">
-        <v>-0.1092133</v>
+        <v>-2.6797439999999999E-2</v>
       </c>
       <c r="J49" s="45">
-        <v>2.1070729999999999E-2</v>
+        <v>1.099955E-2</v>
       </c>
       <c r="K49" s="45">
-        <v>11.89181</v>
+        <v>13.570510000000001</v>
       </c>
       <c r="L49" s="45">
-        <v>-5.1831759999999996</v>
+        <v>-2.4262299999999999</v>
       </c>
       <c r="M49" s="46">
-        <v>2.34916E-4</v>
+        <v>2.928103E-2</v>
       </c>
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="51"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
       <c r="H50" s="1"/>
       <c r="I50" s="45">
-        <v>-9.8989809999999998E-2</v>
+        <v>-3.3645590000000003E-2</v>
       </c>
       <c r="J50" s="45">
-        <v>1.5884120000000002E-2</v>
+        <v>1.265696E-2</v>
       </c>
       <c r="K50" s="45">
-        <v>13.67961</v>
+        <v>13.256600000000001</v>
       </c>
       <c r="L50" s="45">
-        <v>-6.2319979999999999</v>
+        <v>-2.6582690000000002</v>
       </c>
       <c r="M50" s="46">
-        <v>2.433112E-5</v>
+        <v>1.943344E-2</v>
       </c>
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="49" t="s">
-        <v>144</v>
+      <c r="A51" s="50" t="s">
+        <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="45">
-        <v>-4.1460160000000004</v>
-      </c>
-      <c r="D51" s="45">
-        <v>0.6769811</v>
-      </c>
-      <c r="E51" s="45">
-        <v>24.376617</v>
-      </c>
-      <c r="F51" s="45">
-        <v>-6.1242720000000004</v>
-      </c>
-      <c r="G51" s="45">
-        <v>2.350653E-6</v>
-      </c>
+      <c r="C51" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="52"/>
+      <c r="I51" s="45">
+        <v>-8.3753321000000006E-3</v>
+      </c>
+      <c r="J51" s="45">
+        <v>8.9984460000000002E-3</v>
+      </c>
+      <c r="K51" s="45">
+        <v>56.69021</v>
+      </c>
+      <c r="L51" s="45">
+        <v>-0.93075200000000002</v>
+      </c>
+      <c r="M51" s="46">
+        <v>0.35592869999999999</v>
+      </c>
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="45">
-        <v>-5.1080050000000004</v>
-      </c>
-      <c r="D52" s="45">
-        <v>0.46945019999999998</v>
-      </c>
-      <c r="E52" s="45">
-        <v>38.858649999999997</v>
-      </c>
-      <c r="F52" s="45">
-        <v>-10.88082</v>
-      </c>
-      <c r="G52" s="46">
-        <v>2.3278650000000001E-13</v>
-      </c>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
+      <c r="I52" s="45">
+        <v>6.2885479999999997E-3</v>
+      </c>
+      <c r="J52" s="45">
+        <v>1.0130220000000001E-2</v>
+      </c>
+      <c r="K52" s="45">
+        <v>54.056728</v>
+      </c>
+      <c r="L52" s="45">
+        <v>0.62077130000000003</v>
+      </c>
+      <c r="M52" s="46">
+        <v>0.53735880000000003</v>
+      </c>
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="45">
-        <v>-3.7989480000000002</v>
-      </c>
-      <c r="D53" s="45">
-        <v>1.208588</v>
-      </c>
-      <c r="E53" s="45">
-        <v>17.432320000000001</v>
-      </c>
-      <c r="F53" s="45">
-        <v>-3.143294</v>
-      </c>
-      <c r="G53" s="46">
-        <v>5.789537E-3</v>
-      </c>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="52"/>
-      <c r="J53" s="52"/>
-      <c r="K53" s="52"/>
-      <c r="L53" s="52"/>
-      <c r="M53" s="52"/>
+      <c r="I53" s="45">
+        <v>-0.1092133</v>
+      </c>
+      <c r="J53" s="45">
+        <v>2.1070729999999999E-2</v>
+      </c>
+      <c r="K53" s="45">
+        <v>11.89181</v>
+      </c>
+      <c r="L53" s="45">
+        <v>-5.1831759999999996</v>
+      </c>
+      <c r="M53" s="46">
+        <v>2.34916E-4</v>
+      </c>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="51"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="45">
-        <v>-4.4755320000000003</v>
-      </c>
-      <c r="D54" s="45">
-        <v>0.98680710000000005</v>
-      </c>
-      <c r="E54" s="45">
-        <v>15.62265</v>
-      </c>
-      <c r="F54" s="45">
-        <v>-4.5353669999999999</v>
-      </c>
-      <c r="G54" s="46">
-        <v>3.5774789999999998E-4</v>
-      </c>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="52"/>
-      <c r="L54" s="52"/>
-      <c r="M54" s="52"/>
+      <c r="I54" s="45">
+        <v>-9.8989809999999998E-2</v>
+      </c>
+      <c r="J54" s="45">
+        <v>1.5884120000000002E-2</v>
+      </c>
+      <c r="K54" s="45">
+        <v>13.67961</v>
+      </c>
+      <c r="L54" s="45">
+        <v>-6.2319979999999999</v>
+      </c>
+      <c r="M54" s="46">
+        <v>2.433112E-5</v>
+      </c>
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="49" t="s">
-        <v>39</v>
+      <c r="A55" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="47">
-        <v>0.142703</v>
-      </c>
-      <c r="D55" s="47">
-        <v>2.4577999999999999E-2</v>
-      </c>
-      <c r="E55" s="47">
-        <v>23.670773000000001</v>
-      </c>
-      <c r="F55" s="47">
-        <v>5.5574009999999996</v>
-      </c>
-      <c r="G55" s="47">
-        <v>1.0710269999999999E-5</v>
+      <c r="C55" s="45">
+        <v>-4.1460160000000004</v>
+      </c>
+      <c r="D55" s="45">
+        <v>0.6769811</v>
+      </c>
+      <c r="E55" s="45">
+        <v>24.376617</v>
+      </c>
+      <c r="F55" s="45">
+        <v>-6.1242720000000004</v>
+      </c>
+      <c r="G55" s="45">
+        <v>2.350653E-6</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="52" t="s">
+      <c r="I55" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="52"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="53"/>
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+      <c r="A56" s="51"/>
       <c r="B56" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C56" s="47">
-        <v>0.10728550000000001</v>
-      </c>
-      <c r="D56" s="47">
-        <v>1.8656389999999998E-2</v>
-      </c>
-      <c r="E56" s="47">
-        <v>36.899675999999999</v>
-      </c>
-      <c r="F56" s="47">
-        <v>5.7506050000000002</v>
-      </c>
-      <c r="G56" s="47">
-        <v>1.3791302849E-6</v>
+      <c r="C56" s="45">
+        <v>-5.1080050000000004</v>
+      </c>
+      <c r="D56" s="45">
+        <v>0.46945019999999998</v>
+      </c>
+      <c r="E56" s="45">
+        <v>38.858649999999997</v>
+      </c>
+      <c r="F56" s="45">
+        <v>-10.88082</v>
+      </c>
+      <c r="G56" s="46">
+        <v>2.3278650000000001E-13</v>
       </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
-      <c r="K56" s="52"/>
-      <c r="L56" s="52"/>
-      <c r="M56" s="52"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
+      <c r="M56" s="53"/>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
+      <c r="A57" s="51"/>
       <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="47">
-        <v>-0.1020605</v>
-      </c>
-      <c r="D57" s="47">
-        <v>5.7317760000000002E-2</v>
-      </c>
-      <c r="E57" s="47">
-        <v>16.319230000000001</v>
-      </c>
-      <c r="F57" s="47">
-        <v>-1.7806090000000001</v>
-      </c>
-      <c r="G57" s="47">
-        <v>9.3598610230064994E-2</v>
+      <c r="C57" s="45">
+        <v>-3.7989480000000002</v>
+      </c>
+      <c r="D57" s="45">
+        <v>1.208588</v>
+      </c>
+      <c r="E57" s="45">
+        <v>17.432320000000001</v>
+      </c>
+      <c r="F57" s="45">
+        <v>-3.143294</v>
+      </c>
+      <c r="G57" s="46">
+        <v>5.789537E-3</v>
       </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
-      <c r="K57" s="52"/>
-      <c r="L57" s="52"/>
-      <c r="M57" s="52"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="53"/>
+      <c r="M57" s="53"/>
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="51"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="47">
-        <v>-8.9823520000000004E-2</v>
-      </c>
-      <c r="D58" s="47">
-        <v>3.9384450000000001E-2</v>
-      </c>
-      <c r="E58" s="47">
-        <v>14.65358</v>
-      </c>
-      <c r="F58" s="47">
-        <v>-2.2806850000000001</v>
-      </c>
-      <c r="G58" s="48">
-        <v>3.7977520000000001E-2</v>
+      <c r="C58" s="45">
+        <v>-4.4755320000000003</v>
+      </c>
+      <c r="D58" s="45">
+        <v>0.98680710000000005</v>
+      </c>
+      <c r="E58" s="45">
+        <v>15.62265</v>
+      </c>
+      <c r="F58" s="45">
+        <v>-4.5353669999999999</v>
+      </c>
+      <c r="G58" s="46">
+        <v>3.5774789999999998E-4</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
-      <c r="M58" s="52"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
+      <c r="M58" s="53"/>
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="49" t="s">
-        <v>150</v>
+      <c r="A59" s="50" t="s">
+        <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C59" s="47">
-        <v>0.3732317</v>
+        <v>0.142703</v>
       </c>
       <c r="D59" s="47">
-        <v>2.314503E-2</v>
+        <v>2.4577999999999999E-2</v>
       </c>
       <c r="E59" s="47">
-        <v>22.935904000000001</v>
+        <v>23.670773000000001</v>
       </c>
       <c r="F59" s="47">
-        <v>16.125781</v>
+        <v>5.5574009999999996</v>
       </c>
       <c r="G59" s="47">
-        <v>5.242662E-14</v>
+        <v>1.0710269999999999E-5</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="52" t="s">
+      <c r="I59" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
+      <c r="A60" s="51"/>
       <c r="B60" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C60" s="47">
-        <v>0.39719009999999999</v>
+        <v>0.10728550000000001</v>
       </c>
       <c r="D60" s="47">
-        <v>3.5684239999999999E-2</v>
+        <v>1.8656389999999998E-2</v>
       </c>
       <c r="E60" s="47">
-        <v>42.630980000000001</v>
+        <v>36.899675999999999</v>
       </c>
       <c r="F60" s="47">
-        <v>11.130687</v>
+        <v>5.7506050000000002</v>
       </c>
       <c r="G60" s="47">
-        <v>3.4043159999999998E-14</v>
+        <v>1.3791302849E-6</v>
       </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
-      <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
+      <c r="M60" s="53"/>
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="47">
-        <v>-2.5815100000000001E-2</v>
+        <v>-0.1020605</v>
       </c>
       <c r="D61" s="47">
-        <v>5.5261520000000001E-2</v>
+        <v>5.7317760000000002E-2</v>
       </c>
       <c r="E61" s="47">
-        <v>21.336089999999999</v>
+        <v>16.319230000000001</v>
       </c>
       <c r="F61" s="47">
-        <v>-0.46714420000000001</v>
+        <v>-1.7806090000000001</v>
       </c>
       <c r="G61" s="47">
-        <v>0.64513220100000002</v>
+        <v>9.3598610230064994E-2</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="52"/>
-      <c r="J61" s="52"/>
-      <c r="K61" s="52"/>
-      <c r="L61" s="52"/>
-      <c r="M61" s="52"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
+      <c r="M61" s="53"/>
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="51"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C62" s="47">
-        <v>2.8353639999999999E-2</v>
+        <v>-8.9823520000000004E-2</v>
       </c>
       <c r="D62" s="47">
-        <v>3.0635989999999998E-2</v>
+        <v>3.9384450000000001E-2</v>
       </c>
       <c r="E62" s="47">
-        <v>18.611360000000001</v>
+        <v>14.65358</v>
       </c>
       <c r="F62" s="47">
-        <v>0.92550100000000002</v>
-      </c>
-      <c r="G62" s="47">
-        <v>0.36655130000000002</v>
+        <v>-2.2806850000000001</v>
+      </c>
+      <c r="G62" s="48">
+        <v>3.7977520000000001E-2</v>
       </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="52"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
+      <c r="M62" s="53"/>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="49" t="s">
-        <v>38</v>
+      <c r="A63" s="50" t="s">
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="47">
+        <v>0.3732317</v>
+      </c>
+      <c r="D63" s="47">
+        <v>2.314503E-2</v>
+      </c>
+      <c r="E63" s="47">
+        <v>22.935904000000001</v>
+      </c>
+      <c r="F63" s="47">
+        <v>16.125781</v>
+      </c>
+      <c r="G63" s="47">
+        <v>5.242662E-14</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1">
-        <v>5.4104409999999999E-2</v>
-      </c>
-      <c r="J63" s="1">
-        <v>1.586684E-2</v>
-      </c>
-      <c r="K63" s="1">
-        <v>55.294079000000004</v>
-      </c>
-      <c r="L63" s="1">
-        <v>3.4099050000000002</v>
-      </c>
-      <c r="M63" s="2">
-        <v>1.2200878E-3</v>
-      </c>
+      <c r="J63" s="53"/>
+      <c r="K63" s="53"/>
+      <c r="L63" s="53"/>
+      <c r="M63" s="53"/>
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
+      <c r="C64" s="47">
+        <v>0.39719009999999999</v>
+      </c>
+      <c r="D64" s="47">
+        <v>3.5684239999999999E-2</v>
+      </c>
+      <c r="E64" s="47">
+        <v>42.630980000000001</v>
+      </c>
+      <c r="F64" s="47">
+        <v>11.130687</v>
+      </c>
+      <c r="G64" s="47">
+        <v>3.4043159999999998E-14</v>
+      </c>
       <c r="H64" s="1"/>
-      <c r="I64" s="1">
-        <v>4.687269E-3</v>
-      </c>
-      <c r="J64" s="1">
-        <v>1.2589380000000001E-2</v>
-      </c>
-      <c r="K64" s="1">
-        <v>54.088656</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0.37231940000000002</v>
-      </c>
-      <c r="M64" s="1">
-        <v>0.71110989999999996</v>
-      </c>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="53"/>
+      <c r="L64" s="53"/>
+      <c r="M64" s="53"/>
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
+      <c r="C65" s="47">
+        <v>-2.5815100000000001E-2</v>
+      </c>
+      <c r="D65" s="47">
+        <v>5.5261520000000001E-2</v>
+      </c>
+      <c r="E65" s="47">
+        <v>21.336089999999999</v>
+      </c>
+      <c r="F65" s="47">
+        <v>-0.46714420000000001</v>
+      </c>
+      <c r="G65" s="47">
+        <v>0.64513220100000002</v>
+      </c>
       <c r="H65" s="1"/>
-      <c r="I65" s="1">
-        <v>-0.16190650000000001</v>
-      </c>
-      <c r="J65" s="1">
-        <v>4.2269439999999998E-2</v>
-      </c>
-      <c r="K65" s="1">
-        <v>12.56658</v>
-      </c>
-      <c r="L65" s="1">
-        <v>-3.8303449999999999</v>
-      </c>
-      <c r="M65" s="2">
-        <v>2.2091979999999999E-3</v>
-      </c>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="53"/>
+      <c r="M65" s="53"/>
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="51"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
+      <c r="C66" s="47">
+        <v>2.8353639999999999E-2</v>
+      </c>
+      <c r="D66" s="47">
+        <v>3.0635989999999998E-2</v>
+      </c>
+      <c r="E66" s="47">
+        <v>18.611360000000001</v>
+      </c>
+      <c r="F66" s="47">
+        <v>0.92550100000000002</v>
+      </c>
+      <c r="G66" s="47">
+        <v>0.36655130000000002</v>
+      </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="1">
-        <v>-0.22064059999999999</v>
-      </c>
-      <c r="J66" s="1">
-        <v>3.0408129999999998E-2</v>
-      </c>
-      <c r="K66" s="1">
-        <v>12.94289</v>
-      </c>
-      <c r="L66" s="1">
-        <v>-7.2559740000000001</v>
-      </c>
-      <c r="M66" s="2">
-        <v>6.5639129999999997E-6</v>
-      </c>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="53"/>
+      <c r="M66" s="53"/>
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="49" t="s">
-        <v>145</v>
+      <c r="A67" s="50" t="s">
+        <v>38</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C67" s="47">
-        <v>0.2325074</v>
-      </c>
-      <c r="D67" s="47">
-        <v>1.6652759999999999E-2</v>
-      </c>
-      <c r="E67" s="47">
-        <v>25.056222999999999</v>
-      </c>
-      <c r="F67" s="47">
-        <v>13.96209</v>
-      </c>
-      <c r="G67" s="48">
-        <v>2.524047E-13</v>
-      </c>
+      <c r="C67" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="J67" s="52"/>
-      <c r="K67" s="52"/>
-      <c r="L67" s="52"/>
-      <c r="M67" s="52"/>
+      <c r="I67" s="1">
+        <v>5.4104409999999999E-2</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1.586684E-2</v>
+      </c>
+      <c r="K67" s="1">
+        <v>55.294079000000004</v>
+      </c>
+      <c r="L67" s="1">
+        <v>3.4099050000000002</v>
+      </c>
+      <c r="M67" s="2">
+        <v>1.2200878E-3</v>
+      </c>
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
+      <c r="A68" s="51"/>
       <c r="B68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C68" s="47">
-        <v>0.28619260000000002</v>
-      </c>
-      <c r="D68" s="47">
-        <v>3.6218710000000001E-2</v>
-      </c>
-      <c r="E68" s="47">
-        <v>41.139429999999997</v>
-      </c>
-      <c r="F68" s="47">
-        <v>7.901789</v>
-      </c>
-      <c r="G68" s="47">
-        <v>8.8521990000000004E-10</v>
-      </c>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="52"/>
-      <c r="J68" s="52"/>
-      <c r="K68" s="52"/>
-      <c r="L68" s="52"/>
-      <c r="M68" s="52"/>
+      <c r="I68" s="1">
+        <v>4.687269E-3</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1.2589380000000001E-2</v>
+      </c>
+      <c r="K68" s="1">
+        <v>54.088656</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0.37231940000000002</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0.71110989999999996</v>
+      </c>
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="47">
-        <v>8.0073980000000003E-2</v>
-      </c>
-      <c r="D69" s="47">
-        <v>4.5945039999999999E-2</v>
-      </c>
-      <c r="E69" s="47">
-        <v>20.778459999999999</v>
-      </c>
-      <c r="F69" s="47">
-        <v>1.742821</v>
-      </c>
-      <c r="G69" s="48">
-        <v>9.6146709999999996E-2</v>
-      </c>
+      <c r="C69" s="53"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="52"/>
-      <c r="J69" s="52"/>
-      <c r="K69" s="52"/>
-      <c r="L69" s="52"/>
-      <c r="M69" s="52"/>
+      <c r="I69" s="1">
+        <v>-0.16190650000000001</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4.2269439999999998E-2</v>
+      </c>
+      <c r="K69" s="1">
+        <v>12.56658</v>
+      </c>
+      <c r="L69" s="1">
+        <v>-3.8303449999999999</v>
+      </c>
+      <c r="M69" s="2">
+        <v>2.2091979999999999E-3</v>
+      </c>
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="51"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C70" s="47">
-        <v>0.1221365</v>
-      </c>
-      <c r="D70" s="47">
-        <v>3.947755E-2</v>
-      </c>
-      <c r="E70" s="47">
-        <v>16.65624</v>
-      </c>
-      <c r="F70" s="47">
-        <v>3.0938219999999998</v>
-      </c>
-      <c r="G70" s="47">
-        <v>6.7150146952E-3</v>
-      </c>
+      <c r="C70" s="53"/>
+      <c r="D70" s="53"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="52"/>
-      <c r="J70" s="52"/>
-      <c r="K70" s="52"/>
-      <c r="L70" s="52"/>
-      <c r="M70" s="52"/>
+      <c r="I70" s="1">
+        <v>-0.22064059999999999</v>
+      </c>
+      <c r="J70" s="1">
+        <v>3.0408129999999998E-2</v>
+      </c>
+      <c r="K70" s="1">
+        <v>12.94289</v>
+      </c>
+      <c r="L70" s="1">
+        <v>-7.2559740000000001</v>
+      </c>
+      <c r="M70" s="2">
+        <v>6.5639129999999997E-6</v>
+      </c>
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="49" t="s">
-        <v>148</v>
+      <c r="A71" s="50" t="s">
+        <v>145</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C71" s="52" t="s">
+      <c r="C71" s="47">
+        <v>0.2325074</v>
+      </c>
+      <c r="D71" s="47">
+        <v>1.6652759999999999E-2</v>
+      </c>
+      <c r="E71" s="47">
+        <v>25.056222999999999</v>
+      </c>
+      <c r="F71" s="47">
+        <v>13.96209</v>
+      </c>
+      <c r="G71" s="48">
+        <v>2.524047E-13</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D71" s="52"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="52"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="45">
-        <v>3.8010990000000001E-3</v>
-      </c>
-      <c r="J71" s="45">
-        <v>1.2390599999999999E-3</v>
-      </c>
-      <c r="K71" s="45">
-        <v>56.226177999999997</v>
-      </c>
-      <c r="L71" s="45">
-        <v>3.0677270000000001</v>
-      </c>
-      <c r="M71" s="45">
-        <v>3.3149447299999999E-3</v>
-      </c>
+      <c r="J71" s="53"/>
+      <c r="K71" s="53"/>
+      <c r="L71" s="53"/>
+      <c r="M71" s="53"/>
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
+      <c r="A72" s="51"/>
       <c r="B72" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
+      <c r="C72" s="47">
+        <v>0.28619260000000002</v>
+      </c>
+      <c r="D72" s="47">
+        <v>3.6218710000000001E-2</v>
+      </c>
+      <c r="E72" s="47">
+        <v>41.139429999999997</v>
+      </c>
+      <c r="F72" s="47">
+        <v>7.901789</v>
+      </c>
+      <c r="G72" s="47">
+        <v>8.8521990000000004E-10</v>
+      </c>
       <c r="H72" s="1"/>
-      <c r="I72" s="45">
-        <v>2.6998579999999999E-3</v>
-      </c>
-      <c r="J72" s="45">
-        <v>1.7967930000000001E-3</v>
-      </c>
-      <c r="K72" s="45">
-        <v>54.259734999999999</v>
-      </c>
-      <c r="L72" s="45">
-        <v>1.502599</v>
-      </c>
-      <c r="M72" s="45">
-        <v>0.13874061215931999</v>
-      </c>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53"/>
+      <c r="M72" s="53"/>
       <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
+      <c r="A73" s="51"/>
       <c r="B73" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="52"/>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="52"/>
+      <c r="C73" s="47">
+        <v>8.0073980000000003E-2</v>
+      </c>
+      <c r="D73" s="47">
+        <v>4.5945039999999999E-2</v>
+      </c>
+      <c r="E73" s="47">
+        <v>20.778459999999999</v>
+      </c>
+      <c r="F73" s="47">
+        <v>1.742821</v>
+      </c>
+      <c r="G73" s="48">
+        <v>9.6146709999999996E-2</v>
+      </c>
       <c r="H73" s="1"/>
-      <c r="I73" s="45">
-        <v>-1.146374E-2</v>
-      </c>
-      <c r="J73" s="45">
-        <v>2.9301919999999999E-3</v>
-      </c>
-      <c r="K73" s="45">
-        <v>12.84609</v>
-      </c>
-      <c r="L73" s="45">
-        <v>-3.9122840000000001</v>
-      </c>
-      <c r="M73" s="45">
-        <v>1.8229571331547E-3</v>
-      </c>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="53"/>
+      <c r="M73" s="53"/>
       <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="51"/>
+      <c r="A74" s="52"/>
       <c r="B74" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
+      <c r="C74" s="47">
+        <v>0.1221365</v>
+      </c>
+      <c r="D74" s="47">
+        <v>3.947755E-2</v>
+      </c>
+      <c r="E74" s="47">
+        <v>16.65624</v>
+      </c>
+      <c r="F74" s="47">
+        <v>3.0938219999999998</v>
+      </c>
+      <c r="G74" s="47">
+        <v>6.7150146952E-3</v>
+      </c>
       <c r="H74" s="1"/>
-      <c r="I74" s="45">
-        <v>-1.288595E-2</v>
-      </c>
-      <c r="J74" s="45">
-        <v>2.4782379999999998E-3</v>
-      </c>
-      <c r="K74" s="45">
-        <v>14.11434</v>
-      </c>
-      <c r="L74" s="45">
-        <v>-5.1996440000000002</v>
-      </c>
-      <c r="M74" s="45">
-        <v>1.3118094177569999E-4</v>
-      </c>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="53"/>
+      <c r="M74" s="53"/>
       <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="49" t="s">
-        <v>29</v>
+      <c r="A75" s="50" t="s">
+        <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="52" t="s">
+      <c r="C75" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1">
-        <v>-1.7348269999999999E-2</v>
-      </c>
-      <c r="J75" s="1">
-        <v>6.5396389999999999E-3</v>
-      </c>
-      <c r="K75" s="1">
-        <v>55.709558000000001</v>
-      </c>
-      <c r="L75" s="1">
-        <v>-2.652787</v>
-      </c>
-      <c r="M75" s="2">
-        <v>1.038058E-2</v>
+      <c r="I75" s="45">
+        <v>3.8010990000000001E-3</v>
+      </c>
+      <c r="J75" s="45">
+        <v>1.2390599999999999E-3</v>
+      </c>
+      <c r="K75" s="45">
+        <v>56.226177999999997</v>
+      </c>
+      <c r="L75" s="45">
+        <v>3.0677270000000001</v>
+      </c>
+      <c r="M75" s="45">
+        <v>3.3149447299999999E-3</v>
       </c>
       <c r="N75" s="1"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="1">
-        <v>1.2575930000000001E-2</v>
-      </c>
-      <c r="J76" s="1">
-        <v>7.0812319999999998E-3</v>
-      </c>
-      <c r="K76" s="1">
-        <v>54.114787999999997</v>
-      </c>
-      <c r="L76" s="1">
-        <v>1.775952</v>
-      </c>
-      <c r="M76" s="3">
-        <v>8.1363409999999997E-2</v>
+      <c r="I76" s="45">
+        <v>2.6998579999999999E-3</v>
+      </c>
+      <c r="J76" s="45">
+        <v>1.7967930000000001E-3</v>
+      </c>
+      <c r="K76" s="45">
+        <v>54.259734999999999</v>
+      </c>
+      <c r="L76" s="45">
+        <v>1.502599</v>
+      </c>
+      <c r="M76" s="45">
+        <v>0.13874061215931999</v>
       </c>
       <c r="N76" s="1"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="1">
-        <v>3.5116069999999999E-2</v>
-      </c>
-      <c r="J77" s="1">
-        <v>1.7176980000000001E-2</v>
-      </c>
-      <c r="K77" s="1">
-        <v>13.180910000000001</v>
-      </c>
-      <c r="L77" s="1">
-        <v>2.044368</v>
-      </c>
-      <c r="M77" s="3">
-        <v>6.1427379999999997E-2</v>
+      <c r="I77" s="45">
+        <v>-1.146374E-2</v>
+      </c>
+      <c r="J77" s="45">
+        <v>2.9301919999999999E-3</v>
+      </c>
+      <c r="K77" s="45">
+        <v>12.84609</v>
+      </c>
+      <c r="L77" s="45">
+        <v>-3.9122840000000001</v>
+      </c>
+      <c r="M77" s="45">
+        <v>1.8229571331547E-3</v>
       </c>
       <c r="N77" s="1"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="51"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="1">
-        <v>6.7801109999999998E-2</v>
-      </c>
-      <c r="J78" s="1">
-        <v>1.328505E-2</v>
-      </c>
-      <c r="K78" s="1">
-        <v>13.75198</v>
-      </c>
-      <c r="L78" s="1">
-        <v>5.1035659999999998</v>
-      </c>
-      <c r="M78" s="2">
-        <v>1.698402E-4</v>
+      <c r="I78" s="45">
+        <v>-1.288595E-2</v>
+      </c>
+      <c r="J78" s="45">
+        <v>2.4782379999999998E-3</v>
+      </c>
+      <c r="K78" s="45">
+        <v>14.11434</v>
+      </c>
+      <c r="L78" s="45">
+        <v>-5.1996440000000002</v>
+      </c>
+      <c r="M78" s="45">
+        <v>1.3118094177569999E-4</v>
       </c>
       <c r="N78" s="1"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="49" t="s">
-        <v>24</v>
+      <c r="A79" s="50" t="s">
+        <v>29</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C79" s="1">
-        <v>-0.9841491</v>
-      </c>
-      <c r="D79" s="1">
-        <v>0.17118269999999999</v>
-      </c>
-      <c r="E79" s="1">
-        <v>23.803190000000001</v>
-      </c>
-      <c r="F79" s="1">
-        <v>-5.7491139999999996</v>
-      </c>
-      <c r="G79" s="2">
-        <v>6.5310590000000004E-6</v>
-      </c>
+      <c r="C79" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
       <c r="H79" s="1"/>
-      <c r="I79" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="J79" s="52"/>
-      <c r="K79" s="52"/>
-      <c r="L79" s="52"/>
-      <c r="M79" s="52"/>
+      <c r="I79" s="1">
+        <v>-1.7348269999999999E-2</v>
+      </c>
+      <c r="J79" s="1">
+        <v>6.5396389999999999E-3</v>
+      </c>
+      <c r="K79" s="1">
+        <v>55.709558000000001</v>
+      </c>
+      <c r="L79" s="1">
+        <v>-2.652787</v>
+      </c>
+      <c r="M79" s="2">
+        <v>1.038058E-2</v>
+      </c>
       <c r="N79" s="1"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="50"/>
+      <c r="A80" s="51"/>
       <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C80" s="1">
-        <v>0.17573549999999999</v>
-      </c>
-      <c r="D80" s="1">
-        <v>0.1739916</v>
-      </c>
-      <c r="E80" s="1">
-        <v>33.744075000000002</v>
-      </c>
-      <c r="F80" s="1">
-        <v>1.0100229999999999</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.31967210000000001</v>
-      </c>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
       <c r="H80" s="1"/>
-      <c r="I80" s="52"/>
-      <c r="J80" s="52"/>
-      <c r="K80" s="52"/>
-      <c r="L80" s="52"/>
-      <c r="M80" s="52"/>
+      <c r="I80" s="1">
+        <v>1.2575930000000001E-2</v>
+      </c>
+      <c r="J80" s="1">
+        <v>7.0812319999999998E-3</v>
+      </c>
+      <c r="K80" s="1">
+        <v>54.114787999999997</v>
+      </c>
+      <c r="L80" s="1">
+        <v>1.775952</v>
+      </c>
+      <c r="M80" s="3">
+        <v>8.1363409999999997E-2</v>
+      </c>
       <c r="N80" s="1"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="50"/>
+      <c r="A81" s="51"/>
       <c r="B81" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="1">
-        <v>-1.1202160000000001</v>
-      </c>
-      <c r="D81" s="1">
-        <v>0.33875499999999997</v>
-      </c>
-      <c r="E81" s="1">
-        <v>14.597720000000001</v>
-      </c>
-      <c r="F81" s="1">
-        <v>-3.3068610000000001</v>
-      </c>
-      <c r="G81" s="2">
-        <v>4.9434029999999999E-3</v>
-      </c>
+      <c r="C81" s="53"/>
+      <c r="D81" s="53"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
       <c r="H81" s="1"/>
-      <c r="I81" s="52"/>
-      <c r="J81" s="52"/>
-      <c r="K81" s="52"/>
-      <c r="L81" s="52"/>
-      <c r="M81" s="52"/>
+      <c r="I81" s="1">
+        <v>3.5116069999999999E-2</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1.7176980000000001E-2</v>
+      </c>
+      <c r="K81" s="1">
+        <v>13.180910000000001</v>
+      </c>
+      <c r="L81" s="1">
+        <v>2.044368</v>
+      </c>
+      <c r="M81" s="3">
+        <v>6.1427379999999997E-2</v>
+      </c>
       <c r="N81" s="1"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="51"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C82" s="1">
-        <v>0.14184459999999999</v>
-      </c>
-      <c r="D82" s="1">
-        <v>0.38861230000000002</v>
-      </c>
-      <c r="E82" s="1">
-        <v>15.02059</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0.36500280000000002</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.72019759999999999</v>
-      </c>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
       <c r="H82" s="1"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="52"/>
-      <c r="K82" s="52"/>
-      <c r="L82" s="52"/>
-      <c r="M82" s="52"/>
+      <c r="I82" s="1">
+        <v>6.7801109999999998E-2</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1.328505E-2</v>
+      </c>
+      <c r="K82" s="1">
+        <v>13.75198</v>
+      </c>
+      <c r="L82" s="1">
+        <v>5.1035659999999998</v>
+      </c>
+      <c r="M82" s="2">
+        <v>1.698402E-4</v>
+      </c>
       <c r="N82" s="1"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="49" t="s">
-        <v>20</v>
+      <c r="A83" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C83" s="1">
-        <v>1.6038840000000001</v>
+        <v>-0.9841491</v>
       </c>
       <c r="D83" s="1">
-        <v>0.37562440000000002</v>
+        <v>0.17118269999999999</v>
       </c>
       <c r="E83" s="1">
-        <v>26.557427000000001</v>
+        <v>23.803190000000001</v>
       </c>
       <c r="F83" s="1">
-        <v>4.2699150000000001</v>
+        <v>-5.7491139999999996</v>
       </c>
       <c r="G83" s="2">
-        <v>2.2222259999999999E-4</v>
+        <v>6.5310590000000004E-6</v>
       </c>
       <c r="H83" s="1"/>
-      <c r="I83" s="52" t="s">
+      <c r="I83" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
-      <c r="L83" s="52"/>
-      <c r="M83" s="52"/>
+      <c r="J83" s="53"/>
+      <c r="K83" s="53"/>
+      <c r="L83" s="53"/>
+      <c r="M83" s="53"/>
       <c r="N83" s="1"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="50"/>
+      <c r="A84" s="51"/>
       <c r="B84" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C84" s="1">
-        <v>2.5716009999999998</v>
+        <v>0.17573549999999999</v>
       </c>
       <c r="D84" s="1">
-        <v>0.35089939999999997</v>
+        <v>0.1739916</v>
       </c>
       <c r="E84" s="1">
-        <v>36.412089999999999</v>
+        <v>33.744075000000002</v>
       </c>
       <c r="F84" s="1">
-        <v>7.3285999999999998</v>
-      </c>
-      <c r="G84" s="2">
-        <v>1.142512E-8</v>
+        <v>1.0100229999999999</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.31967210000000001</v>
       </c>
       <c r="H84" s="1"/>
-      <c r="I84" s="52"/>
-      <c r="J84" s="52"/>
-      <c r="K84" s="52"/>
-      <c r="L84" s="52"/>
-      <c r="M84" s="52"/>
+      <c r="I84" s="53"/>
+      <c r="J84" s="53"/>
+      <c r="K84" s="53"/>
+      <c r="L84" s="53"/>
+      <c r="M84" s="53"/>
       <c r="N84" s="1"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="50"/>
+      <c r="A85" s="51"/>
       <c r="B85" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C85" s="1">
-        <v>0.61386540000000001</v>
+        <v>-1.1202160000000001</v>
       </c>
       <c r="D85" s="1">
-        <v>0.440166</v>
+        <v>0.33875499999999997</v>
       </c>
       <c r="E85" s="1">
-        <v>20.222460000000002</v>
+        <v>14.597720000000001</v>
       </c>
       <c r="F85" s="1">
-        <v>1.3946229999999999</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.17826230000000001</v>
+        <v>-3.3068610000000001</v>
+      </c>
+      <c r="G85" s="2">
+        <v>4.9434029999999999E-3</v>
       </c>
       <c r="H85" s="1"/>
-      <c r="I85" s="52"/>
-      <c r="J85" s="52"/>
-      <c r="K85" s="52"/>
-      <c r="L85" s="52"/>
-      <c r="M85" s="52"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
+      <c r="K85" s="53"/>
+      <c r="L85" s="53"/>
+      <c r="M85" s="53"/>
       <c r="N85" s="1"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="51"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C86" s="1">
-        <v>1.3966069999999999</v>
+        <v>0.14184459999999999</v>
       </c>
       <c r="D86" s="1">
-        <v>0.56956130000000005</v>
+        <v>0.38861230000000002</v>
       </c>
       <c r="E86" s="1">
-        <v>13.935140000000001</v>
+        <v>15.02059</v>
       </c>
       <c r="F86" s="1">
-        <v>2.4520749999999998</v>
-      </c>
-      <c r="G86" s="2">
-        <v>2.8002340000000001E-2</v>
+        <v>0.36500280000000002</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.72019759999999999</v>
       </c>
       <c r="H86" s="1"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="52"/>
-      <c r="K86" s="52"/>
-      <c r="L86" s="52"/>
-      <c r="M86" s="52"/>
+      <c r="I86" s="53"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="53"/>
+      <c r="L86" s="53"/>
+      <c r="M86" s="53"/>
       <c r="N86" s="1"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="49" t="s">
-        <v>21</v>
+      <c r="A87" s="50" t="s">
+        <v>20</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C87" s="1">
-        <v>16.64274</v>
+        <v>1.6038840000000001</v>
       </c>
       <c r="D87" s="1">
-        <v>1.1608540000000001</v>
+        <v>0.37562440000000002</v>
       </c>
       <c r="E87" s="1">
-        <v>4.8165345999999998</v>
+        <v>26.557427000000001</v>
       </c>
       <c r="F87" s="1">
-        <v>14.33663</v>
+        <v>4.2699150000000001</v>
       </c>
       <c r="G87" s="2">
-        <v>3.9052140000000001E-5</v>
+        <v>2.2222259999999999E-4</v>
       </c>
       <c r="H87" s="1"/>
-      <c r="I87" s="52" t="s">
+      <c r="I87" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
       <c r="N87" s="1"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="50"/>
+      <c r="A88" s="51"/>
       <c r="B88" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C88" s="1">
-        <v>19.986529999999998</v>
+        <v>2.5716009999999998</v>
       </c>
       <c r="D88" s="1">
-        <v>0.71962550000000003</v>
+        <v>0.35089939999999997</v>
       </c>
       <c r="E88" s="1">
-        <v>35.025179999999999</v>
+        <v>36.412089999999999</v>
       </c>
       <c r="F88" s="1">
-        <v>27.773520000000001</v>
+        <v>7.3285999999999998</v>
       </c>
       <c r="G88" s="2">
-        <v>1.9085240000000001E-25</v>
+        <v>1.142512E-8</v>
       </c>
       <c r="H88" s="1"/>
-      <c r="I88" s="52"/>
-      <c r="J88" s="52"/>
-      <c r="K88" s="52"/>
-      <c r="L88" s="52"/>
-      <c r="M88" s="52"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
       <c r="N88" s="1"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="50"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C89" s="1">
-        <v>-4.4803540000000002</v>
+        <v>0.61386540000000001</v>
       </c>
       <c r="D89" s="1">
-        <v>1.6178699999999999</v>
+        <v>0.440166</v>
       </c>
       <c r="E89" s="1">
-        <v>15.836600000000001</v>
+        <v>20.222460000000002</v>
       </c>
       <c r="F89" s="1">
-        <v>-2.7692920000000001</v>
-      </c>
-      <c r="G89" s="2">
-        <v>1.377838E-2</v>
+        <v>1.3946229999999999</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.17826230000000001</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
+      <c r="M89" s="53"/>
       <c r="N89" s="1"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="51"/>
+      <c r="A90" s="52"/>
       <c r="B90" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C90" s="1">
-        <v>-0.82880399999999999</v>
+        <v>1.3966069999999999</v>
       </c>
       <c r="D90" s="1">
-        <v>1.112787</v>
+        <v>0.56956130000000005</v>
       </c>
       <c r="E90" s="1">
-        <v>15.309240000000001</v>
+        <v>13.935140000000001</v>
       </c>
       <c r="F90" s="1">
-        <v>-0.74480009999999996</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0.46767300000000001</v>
+        <v>2.4520749999999998</v>
+      </c>
+      <c r="G90" s="2">
+        <v>2.8002340000000001E-2</v>
       </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
       <c r="N90" s="1"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="70" t="s">
-        <v>151</v>
+      <c r="A91" s="50" t="s">
+        <v>21</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C91" s="45">
-        <v>264.8</v>
-      </c>
-      <c r="D91" s="45">
-        <v>32.234110000000001</v>
-      </c>
-      <c r="E91" s="45">
-        <v>30.811264000000001</v>
-      </c>
-      <c r="F91" s="45">
-        <v>8.2149009999999993</v>
-      </c>
-      <c r="G91" s="45">
-        <v>2.9384279999999999E-9</v>
+      <c r="C91" s="1">
+        <v>16.64274</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1.1608540000000001</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4.8165345999999998</v>
+      </c>
+      <c r="F91" s="1">
+        <v>14.33663</v>
+      </c>
+      <c r="G91" s="2">
+        <v>3.9052140000000001E-5</v>
       </c>
       <c r="H91" s="1"/>
-      <c r="I91" s="52" t="s">
+      <c r="I91" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J91" s="52"/>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="53"/>
+      <c r="M91" s="53"/>
       <c r="N91" s="1"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="71"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C92" s="45">
-        <v>249.71430000000001</v>
-      </c>
-      <c r="D92" s="45">
-        <v>24.47692</v>
-      </c>
-      <c r="E92" s="45">
-        <v>40.626759999999997</v>
-      </c>
-      <c r="F92" s="45">
-        <v>10.202030000000001</v>
-      </c>
-      <c r="G92" s="45">
-        <v>9.0369680000000005E-13</v>
+      <c r="C92" s="1">
+        <v>19.986529999999998</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0.71962550000000003</v>
+      </c>
+      <c r="E92" s="1">
+        <v>35.025179999999999</v>
+      </c>
+      <c r="F92" s="1">
+        <v>27.773520000000001</v>
+      </c>
+      <c r="G92" s="2">
+        <v>1.9085240000000001E-25</v>
       </c>
       <c r="H92" s="1"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="52"/>
+      <c r="I92" s="53"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="53"/>
+      <c r="M92" s="53"/>
       <c r="N92" s="1"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="71"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C93" s="45">
-        <v>43.209679999999999</v>
-      </c>
-      <c r="D93" s="45">
-        <v>56.537500000000001</v>
-      </c>
-      <c r="E93" s="45">
-        <v>16.96773</v>
-      </c>
-      <c r="F93" s="45">
-        <v>0.7642658</v>
-      </c>
-      <c r="G93" s="45">
-        <v>0.45520664523399601</v>
+      <c r="C93" s="1">
+        <v>-4.4803540000000002</v>
+      </c>
+      <c r="D93" s="1">
+        <v>1.6178699999999999</v>
+      </c>
+      <c r="E93" s="1">
+        <v>15.836600000000001</v>
+      </c>
+      <c r="F93" s="1">
+        <v>-2.7692920000000001</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1.377838E-2</v>
       </c>
       <c r="H93" s="1"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
+      <c r="I93" s="53"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="53"/>
+      <c r="L93" s="53"/>
+      <c r="M93" s="53"/>
       <c r="N93" s="1"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
+      <c r="A94" s="52"/>
       <c r="B94" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C94" s="45">
-        <v>32.259779999999999</v>
-      </c>
-      <c r="D94" s="45">
-        <v>15.415459999999999</v>
-      </c>
-      <c r="E94" s="45">
-        <v>17.28622</v>
-      </c>
-      <c r="F94" s="45">
-        <v>2.0926900000000002</v>
-      </c>
-      <c r="G94" s="45">
-        <v>5.14251187538E-2</v>
+      <c r="C94" s="1">
+        <v>-0.82880399999999999</v>
+      </c>
+      <c r="D94" s="1">
+        <v>1.112787</v>
+      </c>
+      <c r="E94" s="1">
+        <v>15.309240000000001</v>
+      </c>
+      <c r="F94" s="1">
+        <v>-0.74480009999999996</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.46767300000000001</v>
       </c>
       <c r="H94" s="1"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
-      <c r="L94" s="52"/>
-      <c r="M94" s="52"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
       <c r="N94" s="1"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="49" t="s">
-        <v>35</v>
+      <c r="A95" s="50" t="s">
+        <v>151</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C95" s="1">
-        <v>1.3623919999999999E-2</v>
-      </c>
-      <c r="D95" s="1">
-        <v>1.319795E-2</v>
-      </c>
-      <c r="E95" s="1">
-        <v>31</v>
-      </c>
-      <c r="F95" s="1">
-        <v>1.032276</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.30992960000000003</v>
+      <c r="C95" s="45">
+        <v>264.8</v>
+      </c>
+      <c r="D95" s="45">
+        <v>32.234110000000001</v>
+      </c>
+      <c r="E95" s="45">
+        <v>30.811264000000001</v>
+      </c>
+      <c r="F95" s="45">
+        <v>8.2149009999999993</v>
+      </c>
+      <c r="G95" s="45">
+        <v>2.9384279999999999E-9</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="I95" s="52" t="s">
+      <c r="I95" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-      <c r="L95" s="52"/>
-      <c r="M95" s="52"/>
+      <c r="J95" s="53"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="53"/>
+      <c r="M95" s="53"/>
       <c r="N95" s="1"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="50"/>
+      <c r="A96" s="51"/>
       <c r="B96" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C96" s="1">
-        <v>7.6710570000000006E-2</v>
-      </c>
-      <c r="D96" s="1">
-        <v>8.8472120000000001E-3</v>
-      </c>
-      <c r="E96" s="1">
-        <v>43</v>
-      </c>
-      <c r="F96" s="1">
-        <v>8.6705930000000002</v>
-      </c>
-      <c r="G96" s="2">
-        <v>5.4385229999999998E-11</v>
+      <c r="C96" s="45">
+        <v>249.71430000000001</v>
+      </c>
+      <c r="D96" s="45">
+        <v>24.47692</v>
+      </c>
+      <c r="E96" s="45">
+        <v>40.626759999999997</v>
+      </c>
+      <c r="F96" s="45">
+        <v>10.202030000000001</v>
+      </c>
+      <c r="G96" s="45">
+        <v>9.0369680000000005E-13</v>
       </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
-      <c r="L96" s="52"/>
-      <c r="M96" s="52"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
+      <c r="M96" s="53"/>
       <c r="N96" s="1"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="50"/>
+      <c r="A97" s="51"/>
       <c r="B97" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C97" s="1">
-        <v>-6.9491259999999999E-2</v>
-      </c>
-      <c r="D97" s="1">
-        <v>1.0221040000000001E-2</v>
-      </c>
-      <c r="E97" s="1">
-        <v>12.84778</v>
-      </c>
-      <c r="F97" s="1">
-        <v>-6.7988470000000003</v>
-      </c>
-      <c r="G97" s="2">
-        <v>1.343811E-5</v>
+      <c r="C97" s="45">
+        <v>43.209679999999999</v>
+      </c>
+      <c r="D97" s="45">
+        <v>56.537500000000001</v>
+      </c>
+      <c r="E97" s="45">
+        <v>16.96773</v>
+      </c>
+      <c r="F97" s="45">
+        <v>0.7642658</v>
+      </c>
+      <c r="G97" s="45">
+        <v>0.45520664523399601</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="52"/>
+      <c r="I97" s="53"/>
+      <c r="J97" s="53"/>
+      <c r="K97" s="53"/>
+      <c r="L97" s="53"/>
+      <c r="M97" s="53"/>
       <c r="N97" s="1"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="51"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C98" s="1">
-        <v>-6.8129929999999998E-3</v>
-      </c>
-      <c r="D98" s="1">
-        <v>1.1591260000000001E-2</v>
-      </c>
-      <c r="E98" s="1">
-        <v>34</v>
-      </c>
-      <c r="F98" s="1">
-        <v>-0.58776980000000001</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0.56057069999999998</v>
+      <c r="C98" s="45">
+        <v>32.259779999999999</v>
+      </c>
+      <c r="D98" s="45">
+        <v>15.415459999999999</v>
+      </c>
+      <c r="E98" s="45">
+        <v>17.28622</v>
+      </c>
+      <c r="F98" s="45">
+        <v>2.0926900000000002</v>
+      </c>
+      <c r="G98" s="45">
+        <v>5.14251187538E-2</v>
       </c>
       <c r="H98" s="1"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
-      <c r="M98" s="52"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
       <c r="N98" s="1"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="49" t="s">
-        <v>149</v>
+      <c r="A99" s="50" t="s">
+        <v>35</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C99" s="45">
-        <v>2.012891E-5</v>
-      </c>
-      <c r="D99" s="45">
-        <v>4.0825490000000002E-4</v>
-      </c>
-      <c r="E99" s="45">
-        <v>25.336739999999999</v>
-      </c>
-      <c r="F99" s="45">
-        <v>4.9304760000000003E-2</v>
-      </c>
-      <c r="G99" s="45">
-        <v>0.96106304949900001</v>
+      <c r="C99" s="1">
+        <v>1.3623919999999999E-2</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1.319795E-2</v>
+      </c>
+      <c r="E99" s="1">
+        <v>31</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1.032276</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0.30992960000000003</v>
       </c>
       <c r="H99" s="1"/>
-      <c r="I99" s="52" t="s">
+      <c r="I99" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J99" s="52"/>
-      <c r="K99" s="52"/>
-      <c r="L99" s="52"/>
-      <c r="M99" s="52"/>
+      <c r="J99" s="53"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="53"/>
+      <c r="M99" s="53"/>
       <c r="N99" s="1"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="50"/>
+      <c r="A100" s="51"/>
       <c r="B100" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C100" s="45">
-        <v>8.7200299999999999E-4</v>
-      </c>
-      <c r="D100" s="45">
-        <v>7.1735829999999997E-4</v>
-      </c>
-      <c r="E100" s="45">
+      <c r="C100" s="1">
+        <v>7.6710570000000006E-2</v>
+      </c>
+      <c r="D100" s="1">
+        <v>8.8472120000000001E-3</v>
+      </c>
+      <c r="E100" s="1">
         <v>43</v>
       </c>
-      <c r="F100" s="45">
-        <v>1.2155750000000001</v>
-      </c>
-      <c r="G100" s="46">
-        <v>0.2307786</v>
+      <c r="F100" s="1">
+        <v>8.6705930000000002</v>
+      </c>
+      <c r="G100" s="2">
+        <v>5.4385229999999998E-11</v>
       </c>
       <c r="H100" s="1"/>
-      <c r="I100" s="52"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
-      <c r="L100" s="52"/>
-      <c r="M100" s="52"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="53"/>
+      <c r="K100" s="53"/>
+      <c r="L100" s="53"/>
+      <c r="M100" s="53"/>
       <c r="N100" s="1"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
+      <c r="A101" s="51"/>
       <c r="B101" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C101" s="45">
-        <v>-2.0367390000000001E-3</v>
-      </c>
-      <c r="D101" s="45">
-        <v>6.5130869999999999E-4</v>
-      </c>
-      <c r="E101" s="45">
-        <v>40</v>
-      </c>
-      <c r="F101" s="45">
-        <v>-3.127148</v>
-      </c>
-      <c r="G101" s="46">
-        <v>3.2851500000000001E-3</v>
+      <c r="C101" s="1">
+        <v>-6.9491259999999999E-2</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1.0221040000000001E-2</v>
+      </c>
+      <c r="E101" s="1">
+        <v>12.84778</v>
+      </c>
+      <c r="F101" s="1">
+        <v>-6.7988470000000003</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1.343811E-5</v>
       </c>
       <c r="H101" s="1"/>
-      <c r="I101" s="52"/>
-      <c r="J101" s="52"/>
-      <c r="K101" s="52"/>
-      <c r="L101" s="52"/>
-      <c r="M101" s="52"/>
+      <c r="I101" s="53"/>
+      <c r="J101" s="53"/>
+      <c r="K101" s="53"/>
+      <c r="L101" s="53"/>
+      <c r="M101" s="53"/>
       <c r="N101" s="1"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="51"/>
+      <c r="A102" s="52"/>
       <c r="B102" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="45">
-        <v>-1.576327E-3</v>
-      </c>
-      <c r="D102" s="45">
-        <v>8.643317E-4</v>
-      </c>
-      <c r="E102" s="45">
-        <v>11.874320000000001</v>
-      </c>
-      <c r="F102" s="45">
-        <v>-1.823752</v>
-      </c>
-      <c r="G102" s="46">
-        <v>9.3442800000000006E-2</v>
+      <c r="C102" s="1">
+        <v>-6.8129929999999998E-3</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1.1591260000000001E-2</v>
+      </c>
+      <c r="E102" s="1">
+        <v>34</v>
+      </c>
+      <c r="F102" s="1">
+        <v>-0.58776980000000001</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.56057069999999998</v>
       </c>
       <c r="H102" s="1"/>
-      <c r="I102" s="52"/>
-      <c r="J102" s="52"/>
-      <c r="K102" s="52"/>
-      <c r="L102" s="52"/>
-      <c r="M102" s="52"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
+      <c r="M102" s="53"/>
       <c r="N102" s="1"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="70" t="s">
-        <v>25</v>
+      <c r="A103" s="50" t="s">
+        <v>149</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C103" s="1">
-        <v>0.29653109999999999</v>
-      </c>
-      <c r="D103" s="1">
-        <v>3.0081920000000002E-2</v>
-      </c>
-      <c r="E103" s="1">
-        <v>12.984576000000001</v>
-      </c>
-      <c r="F103" s="1">
-        <v>9.8574540000000006</v>
-      </c>
-      <c r="G103" s="2">
-        <v>2.1465810000000001E-7</v>
+      <c r="C103" s="45">
+        <v>2.012891E-5</v>
+      </c>
+      <c r="D103" s="45">
+        <v>4.0825490000000002E-4</v>
+      </c>
+      <c r="E103" s="45">
+        <v>25.336739999999999</v>
+      </c>
+      <c r="F103" s="45">
+        <v>4.9304760000000003E-2</v>
+      </c>
+      <c r="G103" s="45">
+        <v>0.96106304949900001</v>
       </c>
       <c r="H103" s="1"/>
-      <c r="I103" s="52" t="s">
+      <c r="I103" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J103" s="52"/>
-      <c r="K103" s="52"/>
-      <c r="L103" s="52"/>
-      <c r="M103" s="52"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="53"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="53"/>
       <c r="N103" s="1"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="71"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C104" s="1">
-        <v>0.48443409999999998</v>
-      </c>
-      <c r="D104" s="1">
-        <v>1.925058E-2</v>
-      </c>
-      <c r="E104" s="1">
-        <v>33.275270999999996</v>
-      </c>
-      <c r="F104" s="1">
-        <v>25.164650000000002</v>
-      </c>
-      <c r="G104" s="2">
-        <v>3.0964249999999998E-23</v>
+      <c r="C104" s="45">
+        <v>8.7200299999999999E-4</v>
+      </c>
+      <c r="D104" s="45">
+        <v>7.1735829999999997E-4</v>
+      </c>
+      <c r="E104" s="45">
+        <v>43</v>
+      </c>
+      <c r="F104" s="45">
+        <v>1.2155750000000001</v>
+      </c>
+      <c r="G104" s="46">
+        <v>0.2307786</v>
       </c>
       <c r="H104" s="1"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="52"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="53"/>
+      <c r="L104" s="53"/>
+      <c r="M104" s="53"/>
       <c r="N104" s="1"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="71"/>
+      <c r="A105" s="51"/>
       <c r="B105" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C105" s="1">
-        <v>-4.9176770000000002E-2</v>
-      </c>
-      <c r="D105" s="1">
-        <v>3.2182200000000001E-2</v>
-      </c>
-      <c r="E105" s="1">
-        <v>6.754302</v>
-      </c>
-      <c r="F105" s="1">
-        <v>-1.5280739999999999</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.17187649999999999</v>
+      <c r="C105" s="45">
+        <v>-2.0367390000000001E-3</v>
+      </c>
+      <c r="D105" s="45">
+        <v>6.5130869999999999E-4</v>
+      </c>
+      <c r="E105" s="45">
+        <v>40</v>
+      </c>
+      <c r="F105" s="45">
+        <v>-3.127148</v>
+      </c>
+      <c r="G105" s="46">
+        <v>3.2851500000000001E-3</v>
       </c>
       <c r="H105" s="1"/>
-      <c r="I105" s="52"/>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52"/>
-      <c r="L105" s="52"/>
-      <c r="M105" s="52"/>
+      <c r="I105" s="53"/>
+      <c r="J105" s="53"/>
+      <c r="K105" s="53"/>
+      <c r="L105" s="53"/>
+      <c r="M105" s="53"/>
       <c r="N105" s="1"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="72"/>
+      <c r="A106" s="52"/>
       <c r="B106" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="45">
+        <v>-1.576327E-3</v>
+      </c>
+      <c r="D106" s="45">
+        <v>8.643317E-4</v>
+      </c>
+      <c r="E106" s="45">
+        <v>11.874320000000001</v>
+      </c>
+      <c r="F106" s="45">
+        <v>-1.823752</v>
+      </c>
+      <c r="G106" s="46">
+        <v>9.3442800000000006E-2</v>
+      </c>
+      <c r="H106" s="1"/>
+      <c r="I106" s="53"/>
+      <c r="J106" s="53"/>
+      <c r="K106" s="53"/>
+      <c r="L106" s="53"/>
+      <c r="M106" s="53"/>
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.29653109999999999</v>
+      </c>
+      <c r="D107" s="1">
+        <v>3.0081920000000002E-2</v>
+      </c>
+      <c r="E107" s="1">
+        <v>12.984576000000001</v>
+      </c>
+      <c r="F107" s="1">
+        <v>9.8574540000000006</v>
+      </c>
+      <c r="G107" s="2">
+        <v>2.1465810000000001E-7</v>
+      </c>
+      <c r="H107" s="1"/>
+      <c r="I107" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="J107" s="53"/>
+      <c r="K107" s="53"/>
+      <c r="L107" s="53"/>
+      <c r="M107" s="53"/>
+      <c r="N107" s="1"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="51"/>
+      <c r="B108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.48443409999999998</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1.925058E-2</v>
+      </c>
+      <c r="E108" s="1">
+        <v>33.275270999999996</v>
+      </c>
+      <c r="F108" s="1">
+        <v>25.164650000000002</v>
+      </c>
+      <c r="G108" s="2">
+        <v>3.0964249999999998E-23</v>
+      </c>
+      <c r="H108" s="1"/>
+      <c r="I108" s="53"/>
+      <c r="J108" s="53"/>
+      <c r="K108" s="53"/>
+      <c r="L108" s="53"/>
+      <c r="M108" s="53"/>
+      <c r="N108" s="1"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="51"/>
+      <c r="B109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" s="1">
+        <v>-4.9176770000000002E-2</v>
+      </c>
+      <c r="D109" s="1">
+        <v>3.2182200000000001E-2</v>
+      </c>
+      <c r="E109" s="1">
+        <v>6.754302</v>
+      </c>
+      <c r="F109" s="1">
+        <v>-1.5280739999999999</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.17187649999999999</v>
+      </c>
+      <c r="H109" s="1"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
+      <c r="M109" s="53"/>
+      <c r="N109" s="1"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="52"/>
+      <c r="B110" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="1">
         <v>0.14682600000000001</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D110" s="1">
         <v>2.4250879999999999E-2</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E110" s="1">
         <v>6.7890449999999998</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F110" s="1">
         <v>6.0544589999999996</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G110" s="2">
         <v>5.7776140000000001E-4</v>
       </c>
-      <c r="H106" s="1"/>
-      <c r="I106" s="52"/>
-      <c r="J106" s="52"/>
-      <c r="K106" s="52"/>
-      <c r="L106" s="52"/>
-      <c r="M106" s="52"/>
-      <c r="N106" s="1"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="6"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="6"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="6"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="53"/>
+      <c r="J110" s="53"/>
+      <c r="K110" s="53"/>
+      <c r="L110" s="53"/>
+      <c r="M110" s="53"/>
+      <c r="N110" s="1"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="6"/>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
     </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="6"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="6"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="47">
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="I3:M6"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="I11:M14"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="C51:G54"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="C47:G50"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="I55:M58"/>
+    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="I71:M74"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="C67:G70"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="C79:G82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="I83:M86"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="I107:M110"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="I95:M98"/>
     <mergeCell ref="A103:A106"/>
     <mergeCell ref="I103:M106"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="I91:M94"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="I99:M102"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C75:G78"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="I79:M82"/>
-    <mergeCell ref="C47:G50"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C43:G46"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="I83:M86"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="C71:G74"/>
-    <mergeCell ref="I51:M54"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="I67:M70"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="C63:G66"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="I3:M6"/>
-    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1387" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5163F1B2-54E7-46DB-B0D6-4C771C00F6A8}"/>
+  <xr:revisionPtr revIDLastSave="1457" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F75214E-41B3-4FAC-B1FE-81C08D122DC2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="3" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
-    <sheet name="ModelResults" sheetId="1" r:id="rId1"/>
-    <sheet name="ModelPatterns_all" sheetId="2" r:id="rId2"/>
-    <sheet name="ModelPatterns_story" sheetId="4" r:id="rId3"/>
-    <sheet name="PostHocAnalyses" sheetId="3" r:id="rId4"/>
+    <sheet name="ModelResults_ManuTraits" sheetId="5" r:id="rId1"/>
+    <sheet name="PostHocAnalyses" sheetId="3" r:id="rId2"/>
+    <sheet name="ModelResults_all" sheetId="1" r:id="rId3"/>
+    <sheet name="PostHocAnalyses_all" sheetId="6" r:id="rId4"/>
+    <sheet name="ModelPatterns_all" sheetId="2" r:id="rId5"/>
+    <sheet name="ModelPatterns_story" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,11 +43,12 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={570935C8-6458-4EEB-A2AF-555E0C399256}</author>
-    <author>tc={CE7F8062-35FE-4678-A2E8-310B247760E6}</author>
+    <author>tc={A3BFD695-45B1-4A9F-B5BF-A66BCF1701C9}</author>
+    <author>tc={CC54245A-1779-42DD-987C-D6760465E73C}</author>
+    <author>tc={6603DDC0-52ED-4921-940A-3AEFD2332E6D}</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{570935C8-6458-4EEB-A2AF-555E0C399256}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{A3BFD695-45B1-4A9F-B5BF-A66BCF1701C9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -53,7 +56,7 @@
     Positive value means larger in current environment than in future environment.</t>
       </text>
     </comment>
-    <comment ref="B5" authorId="1" shapeId="0" xr:uid="{CE7F8062-35FE-4678-A2E8-310B247760E6}">
+    <comment ref="B5" authorId="1" shapeId="0" xr:uid="{CC54245A-1779-42DD-987C-D6760465E73C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -61,12 +64,20 @@
     Positive value means larger in Italy than in Sweden</t>
       </text>
     </comment>
+    <comment ref="C7" authorId="2" shapeId="0" xr:uid="{6603DDC0-52ED-4921-940A-3AEFD2332E6D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Something is wrong here because these are identical</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="154">
   <si>
     <t>Experiment</t>
   </si>
@@ -523,12 +534,18 @@
   <si>
     <t>Fruit Number - BL counts</t>
   </si>
+  <si>
+    <t>2021 Post hoc</t>
+  </si>
+  <si>
+    <t>2022 Post Hoc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +596,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -952,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1043,6 +1066,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1051,21 +1077,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1093,6 +1104,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1445,16 +1474,6492 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B3" dT="2024-08-06T14:06:52.71" personId="{C735A381-161A-41C0-857C-66BC75C09C4B}" id="{570935C8-6458-4EEB-A2AF-555E0C399256}">
+  <threadedComment ref="B3" dT="2024-08-06T14:06:52.71" personId="{C735A381-161A-41C0-857C-66BC75C09C4B}" id="{A3BFD695-45B1-4A9F-B5BF-A66BCF1701C9}">
     <text>Positive value means larger in current environment than in future environment.</text>
   </threadedComment>
-  <threadedComment ref="B5" dT="2024-08-06T14:07:09.22" personId="{C735A381-161A-41C0-857C-66BC75C09C4B}" id="{CE7F8062-35FE-4678-A2E8-310B247760E6}">
+  <threadedComment ref="B5" dT="2024-08-06T14:07:09.22" personId="{C735A381-161A-41C0-857C-66BC75C09C4B}" id="{CC54245A-1779-42DD-987C-D6760465E73C}">
     <text>Positive value means larger in Italy than in Sweden</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2025-02-18T20:48:08.20" personId="{C735A381-161A-41C0-857C-66BC75C09C4B}" id="{6603DDC0-52ED-4921-940A-3AEFD2332E6D}">
+    <text>Something is wrong here because these are identical</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A69572B-FB2B-42F9-9C34-22CDDD22EAA2}">
+  <dimension ref="A1:AC104"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="17" max="17" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="55">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="55">
+        <v>2022</v>
+      </c>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="57"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1">
+        <v>358.70759863636101</v>
+      </c>
+      <c r="D3" s="1">
+        <v>358.70759863636101</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>59.157813740273902</v>
+      </c>
+      <c r="G3" s="1">
+        <v>18.038962106465899</v>
+      </c>
+      <c r="H3" s="4">
+        <v>7.7626636560708203E-5</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1">
+        <v>14.714053584253</v>
+      </c>
+      <c r="K3" s="1">
+        <v>14.714053584253</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1">
+        <v>94.081070542958201</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1.6096699122529901</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.20766835063809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="51"/>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1698.51494995505</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1698.51494995505</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>13.5791949559923</v>
+      </c>
+      <c r="G4" s="1">
+        <v>85.416219048555902</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3.1444870334230001E-7</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>1262.59067308865</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1262.59067308865</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>13.7512473298267</v>
+      </c>
+      <c r="N4" s="1">
+        <v>138.12333945399499</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1.48088800061958E-8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
+      <c r="B5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>17.857799301657501</v>
+      </c>
+      <c r="D5" s="1">
+        <v>17.857799301657501</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>59.157813740157302</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.89804667125002302</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.34716114290433903</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>95.797908974956599</v>
+      </c>
+      <c r="K5" s="1">
+        <v>95.797908974956599</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>93.841119050677193</v>
+      </c>
+      <c r="N5" s="1">
+        <v>10.4799816618017</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.66841619906704E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="52"/>
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
+        <v>8.3492792785920695</v>
+      </c>
+      <c r="K6" s="1">
+        <v>4.1746396392960303</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>93.681264974682804</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.45669208579375198</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.63477790451296301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>47.107649150023398</v>
+      </c>
+      <c r="D7" s="1">
+        <v>47.107649150023398</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>57.289916371421597</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3.32662663622179</v>
+      </c>
+      <c r="H7" s="3">
+        <v>7.3383790508167401E-2</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R7" s="40">
+        <v>-0.67962469999999997</v>
+      </c>
+      <c r="S7" s="40">
+        <v>0.72532470000000004</v>
+      </c>
+      <c r="T7" s="40">
+        <v>23.402695999999999</v>
+      </c>
+      <c r="U7" s="40">
+        <v>-0.93699370000000004</v>
+      </c>
+      <c r="V7" s="40">
+        <v>0.35833147122850001</v>
+      </c>
+      <c r="W7" s="1"/>
+      <c r="X7" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="59"/>
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="1"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="51"/>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1124.2901171196299</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1124.2901171196299</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>13.2534687161866</v>
+      </c>
+      <c r="G8" s="1">
+        <v>79.394610385672607</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5.8229847066576205E-7</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R8" s="40">
+        <v>-0.8024289</v>
+      </c>
+      <c r="S8" s="40">
+        <v>0.50150589999999995</v>
+      </c>
+      <c r="T8" s="40">
+        <v>37.766705999999999</v>
+      </c>
+      <c r="U8" s="40">
+        <v>-1.600039</v>
+      </c>
+      <c r="V8" s="40">
+        <v>0.11792329999999999</v>
+      </c>
+      <c r="W8" s="1"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="62"/>
+      <c r="AB8" s="63"/>
+      <c r="AC8" s="1"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.222326126836178</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.222326126836178</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>57.289916368165599</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.5700125750403499E-2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.90072460165650603</v>
+      </c>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" s="40">
+        <v>-11.448639999999999</v>
+      </c>
+      <c r="S9" s="40">
+        <v>1.2781750000000001</v>
+      </c>
+      <c r="T9" s="40">
+        <v>14.82489</v>
+      </c>
+      <c r="U9" s="40">
+        <v>-8.9570209999999992</v>
+      </c>
+      <c r="V9" s="40">
+        <v>2.2889089999999999E-7</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="61"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="63"/>
+      <c r="AC9" s="1"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" s="52"/>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10" s="40">
+        <v>-10.27468</v>
+      </c>
+      <c r="S10" s="40">
+        <v>1.2625949999999999</v>
+      </c>
+      <c r="T10" s="40">
+        <v>13.73147</v>
+      </c>
+      <c r="U10" s="40">
+        <v>-8.1377450000000007</v>
+      </c>
+      <c r="V10" s="40">
+        <v>1.280514E-6</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="1"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.37589798145214498</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.37589798145214498</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>62.693513739662698</v>
+      </c>
+      <c r="G11" s="1">
+        <v>83.6813648995563</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3.75722082106105E-13</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>0.25198523874622702</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.25198523874622702</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>110.096333617363</v>
+      </c>
+      <c r="N11" s="1">
+        <v>42.058288147666097</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2.5984972877347698E-9</v>
+      </c>
+      <c r="P11" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.10404770000000001</v>
+      </c>
+      <c r="S11" s="1">
+        <v>1.3194920000000001E-2</v>
+      </c>
+      <c r="T11" s="1">
+        <v>22.166536000000001</v>
+      </c>
+      <c r="U11" s="1">
+        <v>7.8854410000000001</v>
+      </c>
+      <c r="V11" s="2">
+        <v>7.1088440000000002E-8</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1">
+        <v>3.2186840000000001E-2</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1.052636E-2</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>55.036504999999998</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>3.0577380000000001</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>3.439386E-3</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.18866486223902701</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.18866486223902701</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>12.9224641855406</v>
+      </c>
+      <c r="G12" s="1">
+        <v>42.000047778278599</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2.1245490728025998E-5</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>0.73996860487093596</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.73996860487093596</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>14.054733420670001</v>
+      </c>
+      <c r="N12" s="1">
+        <v>123.506491724426</v>
+      </c>
+      <c r="O12" s="4">
+        <v>2.3925201381821199E-8</v>
+      </c>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R12" s="1">
+        <v>3.6833039999999997E-2</v>
+      </c>
+      <c r="S12" s="1">
+        <v>8.9172230000000002E-3</v>
+      </c>
+      <c r="T12" s="1">
+        <v>38.799550000000004</v>
+      </c>
+      <c r="U12" s="1">
+        <v>4.1305500000000004</v>
+      </c>
+      <c r="V12" s="2">
+        <v>1.8621800000000001E-4</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1">
+        <v>5.4472277E-2</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>8.6164620000000001E-3</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>52.260210000000001</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>6.321885</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>5.8418710000000002E-8</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8.5519255858093002E-2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8.5519255858093002E-2</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>62.6935137438185</v>
+      </c>
+      <c r="G13" s="1">
+        <v>19.0380592834087</v>
+      </c>
+      <c r="H13" s="4">
+        <v>4.8750646383530901E-5</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>1.5798173670143599E-2</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.5798173670143599E-2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>109.918842223097</v>
+      </c>
+      <c r="N13" s="1">
+        <v>2.6368375533891002</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.107275586121823</v>
+      </c>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0.1045321</v>
+      </c>
+      <c r="S13" s="1">
+        <v>8.9959949999999997E-3</v>
+      </c>
+      <c r="T13" s="1">
+        <v>41</v>
+      </c>
+      <c r="U13" s="1">
+        <v>11.61985</v>
+      </c>
+      <c r="V13" s="2">
+        <v>1.497837E-14</v>
+      </c>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1">
+        <v>9.9455870000000002E-2</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1.0855979999999999E-2</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>13.36983</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>9.1613889999999998</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>3.9456639999999998E-7</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>4.9184876384352101E-2</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2.4592438192175999E-2</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2</v>
+      </c>
+      <c r="M14" s="1">
+        <v>110.02134132950501</v>
+      </c>
+      <c r="N14" s="1">
+        <v>4.1046684198111398</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1.9087014953066299E-2</v>
+      </c>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R14" s="1">
+        <v>3.843543E-2</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1.6573709999999998E-2</v>
+      </c>
+      <c r="T14" s="1">
+        <v>12.793609999999999</v>
+      </c>
+      <c r="U14" s="1">
+        <v>2.319061</v>
+      </c>
+      <c r="V14" s="2">
+        <v>3.7607300000000003E-2</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1">
+        <v>0.12323046</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1.5396505E-2</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>15.15973</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>8.0037950000000002</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>7.9669659999999998E-7</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.48460569188395097</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.48460569188395097</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>66.433120310954493</v>
+      </c>
+      <c r="G15" s="1">
+        <v>275.25199949565803</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2.5677289076389099E-25</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <v>120.000000000931</v>
+      </c>
+      <c r="N15" s="1">
+        <v>45.935699808275302</v>
+      </c>
+      <c r="O15" s="4">
+        <v>4.8525436598560696E-10</v>
+      </c>
+      <c r="P15" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R15" s="1">
+        <v>-9.9169900000000005E-2</v>
+      </c>
+      <c r="S15" s="1">
+        <v>7.6156770000000004E-3</v>
+      </c>
+      <c r="T15" s="1">
+        <v>24.117732</v>
+      </c>
+      <c r="U15" s="1">
+        <v>-13.02181</v>
+      </c>
+      <c r="V15" s="2">
+        <v>2.1010249999999999E-12</v>
+      </c>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1">
+        <v>-3.4572279999999997E-2</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>8.7322029999999991E-3</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>60</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>-3.9591699999999999</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>2.0194479999999999E-4</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.0223913414274E-2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1.0223913414274E-2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>16.820702919437998</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5.8070977231181704</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2.77082234476239E-2</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N16" s="1">
+        <v>45.138923567144403</v>
+      </c>
+      <c r="O16" s="4">
+        <v>6.5162497916437297E-10</v>
+      </c>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R16" s="1">
+        <v>-5.779488E-2</v>
+      </c>
+      <c r="S16" s="1">
+        <v>5.7489029999999997E-3</v>
+      </c>
+      <c r="T16" s="1">
+        <v>40.271169999999998</v>
+      </c>
+      <c r="U16" s="1">
+        <v>-10.0532</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1.5358250000000001E-12</v>
+      </c>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1">
+        <v>-5.8530619999999998E-2</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>9.5787719999999993E-3</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>51.236131</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>-6.1104520000000004</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>1.3548390000000001E-7</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3.4754513300900097E-2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3.4754513300900097E-2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>66.433120314017799</v>
+      </c>
+      <c r="G17" s="1">
+        <v>19.740274284401199</v>
+      </c>
+      <c r="H17" s="4">
+        <v>3.4416590783058898E-5</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N17" s="1">
+        <v>3.3163842710393201</v>
+      </c>
+      <c r="O17" s="3">
+        <v>7.1083850624745398E-2</v>
+      </c>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R17" s="1">
+        <v>-4.2352229999999998E-2</v>
+      </c>
+      <c r="S17" s="1">
+        <v>7.6791539999999997E-3</v>
+      </c>
+      <c r="T17" s="1">
+        <v>17.375530000000001</v>
+      </c>
+      <c r="U17" s="1">
+        <v>-5.5152200000000002</v>
+      </c>
+      <c r="V17" s="2">
+        <v>3.5006389999999997E-5</v>
+      </c>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1">
+        <v>-3.2332029999999998E-2</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1.088914E-2</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>61</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>-2.9692001000000001</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>4.2635360000000001E-3</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>3.6858467316493698E-2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.8429233658246901E-2</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2</v>
+      </c>
+      <c r="M18" s="1">
+        <v>120.00000000096099</v>
+      </c>
+      <c r="N18" s="1">
+        <v>3.3604437171390802</v>
+      </c>
+      <c r="O18" s="2">
+        <v>3.8017401028842102E-2</v>
+      </c>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R18" s="1">
+        <v>7.5999539999999999E-3</v>
+      </c>
+      <c r="S18" s="1">
+        <v>1.132999E-2</v>
+      </c>
+      <c r="T18" s="1">
+        <v>12.42445</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0.67078190000000004</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0.51463610000000004</v>
+      </c>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1">
+        <v>-5.6981190000000001E-2</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>9.5599729999999994E-3</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>16.19933</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>-5.9603929999999998</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>1.895906E-5</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A19" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6.7693630421350404E-2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6.7693630421350404E-2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>67.474634134516194</v>
+      </c>
+      <c r="G19" s="1">
+        <v>56.9929468926208</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1.50306538610143E-10</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>9.6428494366839604E-2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>9.6428494366839604E-2</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <v>108.528246395583</v>
+      </c>
+      <c r="N19" s="1">
+        <v>81.178081408719805</v>
+      </c>
+      <c r="O19" s="4">
+        <v>7.9655542624253594E-15</v>
+      </c>
+      <c r="P19" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R19" s="1">
+        <v>3.6476649999999999E-2</v>
+      </c>
+      <c r="S19" s="1">
+        <v>5.8868899999999997E-3</v>
+      </c>
+      <c r="T19" s="1">
+        <v>25.09554</v>
+      </c>
+      <c r="U19" s="1">
+        <v>6.1962510000000002</v>
+      </c>
+      <c r="V19" s="2">
+        <v>1.7340119999999999E-6</v>
+      </c>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1">
+        <v>5.2231909999999999E-2</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>3.8609439999999998E-3</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>57.451040999999996</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>13.528280000000001</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>1.648921E-19</v>
+      </c>
+      <c r="AC19" s="1"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A20" s="51"/>
+      <c r="B20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0802366421830801E-4</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2.0802366421830801E-4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>15.419684823909099</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.17514028385546801</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.68135395106469998</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>1.64063711986129E-2</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.64063711986129E-2</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>13.3017704428868</v>
+      </c>
+      <c r="N20" s="1">
+        <v>13.811661641381701</v>
+      </c>
+      <c r="O20" s="2">
+        <v>2.49480079562349E-3</v>
+      </c>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R20" s="1">
+        <v>2.235734E-2</v>
+      </c>
+      <c r="S20" s="1">
+        <v>4.8859400000000001E-3</v>
+      </c>
+      <c r="T20" s="1">
+        <v>41.205199999999998</v>
+      </c>
+      <c r="U20" s="1">
+        <v>4.5758530000000004</v>
+      </c>
+      <c r="V20" s="2">
+        <v>4.3017260000000003E-5</v>
+      </c>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1">
+        <v>3.4868650000000001E-2</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>4.8541469999999996E-3</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>52.909427000000001</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>7.1832700000000003</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>2.3070910000000001E-9</v>
+      </c>
+      <c r="AC20" s="1"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A21" s="51"/>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.8321573511002202E-3</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3.8321573511002202E-3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>67.4746341327685</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3.2263883475591602</v>
+      </c>
+      <c r="H21" s="3">
+        <v>7.6936893211417001E-2</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
+        <v>9.3368633870387803E-3</v>
+      </c>
+      <c r="K21" s="1">
+        <v>9.3368633870387803E-3</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>108.444542227017</v>
+      </c>
+      <c r="N21" s="1">
+        <v>7.8602145674046398</v>
+      </c>
+      <c r="O21" s="2">
+        <v>5.9886663878832899E-3</v>
+      </c>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R21" s="1">
+        <v>4.6180759999999996E-3</v>
+      </c>
+      <c r="S21" s="1">
+        <v>6.2062740000000003E-3</v>
+      </c>
+      <c r="T21" s="1">
+        <v>9.3979540000000004</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0.74409800000000004</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0.4750103</v>
+      </c>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1">
+        <v>-8.2717769999999993E-3</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>4.5580619999999999E-3</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>11.38397</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>-1.8147580000000001</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>9.5976409999999998E-2</v>
+      </c>
+      <c r="AC21" s="1"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>3.4846897009296399E-3</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.7423448504648199E-3</v>
+      </c>
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1">
+        <v>108.56084481953199</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1.4667885570734001</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0.23519968422781001</v>
+      </c>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R22" s="1">
+        <v>-8.7482029999999995E-3</v>
+      </c>
+      <c r="S22" s="1">
+        <v>6.7380959999999998E-3</v>
+      </c>
+      <c r="T22" s="1">
+        <v>11.10463</v>
+      </c>
+      <c r="U22" s="1">
+        <v>-1.2983199999999999</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0.22049369999999999</v>
+      </c>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1">
+        <v>-2.4618979999999999E-2</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>6.5856999999999999E-3</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>14.47678</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>-3.738248</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>2.090588E-3</v>
+      </c>
+      <c r="AC22" s="1"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>2.20343269025562E-2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>2.20343269025562E-2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>108.759068663758</v>
+      </c>
+      <c r="N23" s="1">
+        <v>6.5138864797470797</v>
+      </c>
+      <c r="O23" s="2">
+        <v>1.20915323151938E-2</v>
+      </c>
+      <c r="P23" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R23" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="45">
+        <v>-1.7478199999999999E-2</v>
+      </c>
+      <c r="Y23" s="45">
+        <v>7.7458099999999997E-3</v>
+      </c>
+      <c r="Z23" s="45">
+        <v>56.319026999999998</v>
+      </c>
+      <c r="AA23" s="45">
+        <v>-2.256472</v>
+      </c>
+      <c r="AB23" s="46">
+        <v>2.2794061000000001E-2</v>
+      </c>
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51"/>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>2.98483856205864E-2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>2.98483856205864E-2</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>13.393007197198701</v>
+      </c>
+      <c r="N24" s="1">
+        <v>8.8239135416321304</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1.05420955332634E-2</v>
+      </c>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
+      <c r="U24" s="53"/>
+      <c r="V24" s="53"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="45">
+        <v>-2.3552070000000001E-2</v>
+      </c>
+      <c r="Y24" s="45">
+        <v>6.7560479999999997E-3</v>
+      </c>
+      <c r="Z24" s="45">
+        <v>54.097791000000001</v>
+      </c>
+      <c r="AA24" s="45">
+        <v>-3.4860709999999999</v>
+      </c>
+      <c r="AB24" s="46">
+        <v>9.8065299999999995E-4</v>
+      </c>
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A25" s="51"/>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1">
+        <v>1.15818782663304E-3</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1.15818782663304E-3</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>108.463193154259</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0.342388676462696</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0.55966903975183102</v>
+      </c>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="53"/>
+      <c r="U25" s="53"/>
+      <c r="V25" s="53"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="45">
+        <v>-2.6797439999999999E-2</v>
+      </c>
+      <c r="Y25" s="45">
+        <v>1.099955E-2</v>
+      </c>
+      <c r="Z25" s="45">
+        <v>13.570510000000001</v>
+      </c>
+      <c r="AA25" s="45">
+        <v>-2.4262299999999999</v>
+      </c>
+      <c r="AB25" s="46">
+        <v>2.928103E-2</v>
+      </c>
+      <c r="AC25" s="1"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A26" s="52"/>
+      <c r="B26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <v>2.0797141885883202E-3</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.0398570942941601E-3</v>
+      </c>
+      <c r="L26" s="1">
+        <v>2</v>
+      </c>
+      <c r="M26" s="1">
+        <v>108.513064659973</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0.30740721499443802</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0.73598934665486404</v>
+      </c>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="45">
+        <v>-3.3645590000000003E-2</v>
+      </c>
+      <c r="Y26" s="45">
+        <v>1.265696E-2</v>
+      </c>
+      <c r="Z26" s="45">
+        <v>13.256600000000001</v>
+      </c>
+      <c r="AA26" s="45">
+        <v>-2.6582690000000002</v>
+      </c>
+      <c r="AB26" s="46">
+        <v>1.943344E-2</v>
+      </c>
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
+        <v>107.364526662513</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3.06304929618606</v>
+      </c>
+      <c r="O27" s="3">
+        <v>8.2948057027609101E-2</v>
+      </c>
+      <c r="P27" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R27" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1">
+        <v>5.4104409999999999E-2</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>1.586684E-2</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>55.294079000000004</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>3.4099050000000002</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>1.2200878E-3</v>
+      </c>
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="51"/>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>13.0099671316875</v>
+      </c>
+      <c r="N28" s="1">
+        <v>32.060536946437701</v>
+      </c>
+      <c r="O28" s="4">
+        <v>7.7465741239532106E-5</v>
+      </c>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
+      <c r="U28" s="53"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1">
+        <v>4.687269E-3</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>1.2589380000000001E-2</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>54.088656</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0.37231940000000002</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0.71110989999999996</v>
+      </c>
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="K29" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>106.96971991586101</v>
+      </c>
+      <c r="N29" s="1">
+        <v>5.9547780655825902</v>
+      </c>
+      <c r="O29" s="2">
+        <v>1.63202510112339E-2</v>
+      </c>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="53"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1">
+        <v>-0.16190650000000001</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>4.2269439999999998E-2</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>12.56658</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>-3.8303449999999999</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>2.2091979999999999E-3</v>
+      </c>
+      <c r="AC29" s="1"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A30" s="52"/>
+      <c r="B30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1">
+        <v>2.6614614752845599E-3</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.33073073764228E-3</v>
+      </c>
+      <c r="L30" s="1">
+        <v>2</v>
+      </c>
+      <c r="M30" s="1">
+        <v>106.998307117191</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0.101262165795663</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0.90378258302877301</v>
+      </c>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
+      <c r="U30" s="53"/>
+      <c r="V30" s="53"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1">
+        <v>-0.22064059999999999</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>3.0408129999999998E-2</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>12.94289</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>-7.2559740000000001</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>6.5639129999999997E-6</v>
+      </c>
+      <c r="AC30" s="1"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1.1481734714944201</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1.1481734714944201</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>57.458627569308902</v>
+      </c>
+      <c r="G31" s="1">
+        <v>62.871367396090498</v>
+      </c>
+      <c r="H31" s="4">
+        <v>8.5554572534297795E-11</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R31" s="47">
+        <v>0.142703</v>
+      </c>
+      <c r="S31" s="47">
+        <v>2.4577999999999999E-2</v>
+      </c>
+      <c r="T31" s="47">
+        <v>23.670773000000001</v>
+      </c>
+      <c r="U31" s="47">
+        <v>5.5574009999999996</v>
+      </c>
+      <c r="V31" s="47">
+        <v>1.0710269999999999E-5</v>
+      </c>
+      <c r="W31" s="1"/>
+      <c r="X31" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y31" s="53"/>
+      <c r="Z31" s="53"/>
+      <c r="AA31" s="53"/>
+      <c r="AB31" s="53"/>
+      <c r="AC31" s="1"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A32" s="51"/>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1">
+        <v>9.2911254906166099E-2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>9.2911254906166099E-2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>14.883763903298201</v>
+      </c>
+      <c r="G32" s="1">
+        <v>5.0876089610695701</v>
+      </c>
+      <c r="H32" s="2">
+        <v>3.9589780561885203E-2</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R32" s="47">
+        <v>0.10728550000000001</v>
+      </c>
+      <c r="S32" s="47">
+        <v>1.8656389999999998E-2</v>
+      </c>
+      <c r="T32" s="47">
+        <v>36.899675999999999</v>
+      </c>
+      <c r="U32" s="47">
+        <v>5.7506050000000002</v>
+      </c>
+      <c r="V32" s="47">
+        <v>1.3791302849E-6</v>
+      </c>
+      <c r="W32" s="1"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="53"/>
+      <c r="Z32" s="53"/>
+      <c r="AA32" s="53"/>
+      <c r="AB32" s="53"/>
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1.37366591368214E-2</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1.37366591368214E-2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>57.458627570771498</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.75218820572632805</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.38939195861388898</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R33" s="47">
+        <v>-0.1020605</v>
+      </c>
+      <c r="S33" s="47">
+        <v>5.7317760000000002E-2</v>
+      </c>
+      <c r="T33" s="47">
+        <v>16.319230000000001</v>
+      </c>
+      <c r="U33" s="47">
+        <v>-1.7806090000000001</v>
+      </c>
+      <c r="V33" s="47">
+        <v>9.3598610230064994E-2</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="53"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="53"/>
+      <c r="AB33" s="53"/>
+      <c r="AC33" s="1"/>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A34" s="52"/>
+      <c r="B34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="52"/>
+      <c r="Q34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R34" s="47">
+        <v>-8.9823520000000004E-2</v>
+      </c>
+      <c r="S34" s="47">
+        <v>3.9384450000000001E-2</v>
+      </c>
+      <c r="T34" s="47">
+        <v>14.65358</v>
+      </c>
+      <c r="U34" s="47">
+        <v>-2.2806850000000001</v>
+      </c>
+      <c r="V34" s="48">
+        <v>3.7977520000000001E-2</v>
+      </c>
+      <c r="W34" s="1"/>
+      <c r="X34" s="53"/>
+      <c r="Y34" s="53"/>
+      <c r="Z34" s="53"/>
+      <c r="AA34" s="53"/>
+      <c r="AB34" s="53"/>
+      <c r="AC34" s="1"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A35" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1">
+        <v>5.0694430563116102</v>
+      </c>
+      <c r="D35" s="1">
+        <v>5.0694430563116102</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>67.962550016506</v>
+      </c>
+      <c r="G35" s="1">
+        <v>123.23450697288</v>
+      </c>
+      <c r="H35" s="8">
+        <v>6.4779999000469503E-17</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R35" s="47">
+        <v>0.2325074</v>
+      </c>
+      <c r="S35" s="47">
+        <v>1.6652759999999999E-2</v>
+      </c>
+      <c r="T35" s="47">
+        <v>25.056222999999999</v>
+      </c>
+      <c r="U35" s="47">
+        <v>13.96209</v>
+      </c>
+      <c r="V35" s="48">
+        <v>2.524047E-13</v>
+      </c>
+      <c r="W35" s="1"/>
+      <c r="X35" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y35" s="53"/>
+      <c r="Z35" s="53"/>
+      <c r="AA35" s="53"/>
+      <c r="AB35" s="53"/>
+      <c r="AC35" s="1"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A36" s="51"/>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.289278337816473</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.289278337816473</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>23.487577951072801</v>
+      </c>
+      <c r="G36" s="1">
+        <v>7.0321478992377502</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1.4106574908243E-2</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R36" s="47">
+        <v>0.28619260000000002</v>
+      </c>
+      <c r="S36" s="47">
+        <v>3.6218710000000001E-2</v>
+      </c>
+      <c r="T36" s="47">
+        <v>41.139429999999997</v>
+      </c>
+      <c r="U36" s="47">
+        <v>7.901789</v>
+      </c>
+      <c r="V36" s="47">
+        <v>8.8521990000000004E-10</v>
+      </c>
+      <c r="W36" s="1"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="53"/>
+      <c r="AC36" s="1"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A37" s="51"/>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1">
+        <v>5.3673365621619298E-2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5.3673365621619298E-2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>67.962550017652504</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1.30476083397765</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.25735376158301099</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R37" s="47">
+        <v>8.0073980000000003E-2</v>
+      </c>
+      <c r="S37" s="47">
+        <v>4.5945039999999999E-2</v>
+      </c>
+      <c r="T37" s="47">
+        <v>20.778459999999999</v>
+      </c>
+      <c r="U37" s="47">
+        <v>1.742821</v>
+      </c>
+      <c r="V37" s="48">
+        <v>9.6146709999999996E-2</v>
+      </c>
+      <c r="W37" s="1"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
+      <c r="AA37" s="53"/>
+      <c r="AB37" s="53"/>
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A38" s="52"/>
+      <c r="B38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R38" s="47">
+        <v>0.1221365</v>
+      </c>
+      <c r="S38" s="47">
+        <v>3.947755E-2</v>
+      </c>
+      <c r="T38" s="47">
+        <v>16.65624</v>
+      </c>
+      <c r="U38" s="47">
+        <v>3.0938219999999998</v>
+      </c>
+      <c r="V38" s="47">
+        <v>6.7150146952E-3</v>
+      </c>
+      <c r="W38" s="1"/>
+      <c r="X38" s="53"/>
+      <c r="Y38" s="53"/>
+      <c r="Z38" s="53"/>
+      <c r="AA38" s="53"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="1"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1">
+        <v>1.4241127553301099E-4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1.4241127553301099E-4</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>108.252981550744</v>
+      </c>
+      <c r="N39" s="1">
+        <v>4.8961312702676701E-2</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0.82529746395827397</v>
+      </c>
+      <c r="P39" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R39" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S39" s="53"/>
+      <c r="T39" s="53"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="53"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1">
+        <v>-1.7348269999999999E-2</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>6.5396389999999999E-3</v>
+      </c>
+      <c r="Z39" s="1">
+        <v>55.709558000000001</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>-2.652787</v>
+      </c>
+      <c r="AB39" s="2">
+        <v>1.038058E-2</v>
+      </c>
+      <c r="AC39" s="1"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A40" s="51"/>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1">
+        <v>4.6725153189010001E-2</v>
+      </c>
+      <c r="K40" s="1">
+        <v>4.6725153189010001E-2</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>13.540354095849599</v>
+      </c>
+      <c r="N40" s="1">
+        <v>16.0642114032417</v>
+      </c>
+      <c r="O40" s="2">
+        <v>1.3790795758093499E-3</v>
+      </c>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="53"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1">
+        <v>1.2575930000000001E-2</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>7.0812319999999998E-3</v>
+      </c>
+      <c r="Z40" s="1">
+        <v>54.114787999999997</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>1.775952</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>8.1363409999999997E-2</v>
+      </c>
+      <c r="AC40" s="1"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A41" s="51"/>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1">
+        <v>2.8302586845141399E-2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>2.8302586845141399E-2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
+        <v>107.87081438761901</v>
+      </c>
+      <c r="N41" s="1">
+        <v>9.7304921933546105</v>
+      </c>
+      <c r="O41" s="2">
+        <v>2.3248319291652099E-3</v>
+      </c>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R41" s="53"/>
+      <c r="S41" s="53"/>
+      <c r="T41" s="53"/>
+      <c r="U41" s="53"/>
+      <c r="V41" s="53"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1">
+        <v>3.5116069999999999E-2</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>1.7176980000000001E-2</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>13.180910000000001</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>2.044368</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>6.1427379999999997E-2</v>
+      </c>
+      <c r="AC41" s="1"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A42" s="52"/>
+      <c r="B42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1">
+        <v>6.3796317056246301E-3</v>
+      </c>
+      <c r="K42" s="1">
+        <v>3.1898158528123098E-3</v>
+      </c>
+      <c r="L42" s="1">
+        <v>2</v>
+      </c>
+      <c r="M42" s="1">
+        <v>107.90322647445799</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1.0966657720673001</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0.33767591593294399</v>
+      </c>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R42" s="53"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="53"/>
+      <c r="U42" s="53"/>
+      <c r="V42" s="53"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1">
+        <v>6.7801109999999998E-2</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1.328505E-2</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>13.75198</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>5.1035659999999998</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>1.698402E-4</v>
+      </c>
+      <c r="AC42" s="1"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A43" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1.2047850194397301E-5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1.2047850194397301E-5</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>59.264824422698197</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.77970315894266595</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.38079976992345599</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="53"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="53"/>
+      <c r="P43" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R43" s="45">
+        <v>2.012891E-5</v>
+      </c>
+      <c r="S43" s="45">
+        <v>4.0825490000000002E-4</v>
+      </c>
+      <c r="T43" s="45">
+        <v>25.336739999999999</v>
+      </c>
+      <c r="U43" s="45">
+        <v>4.9304760000000003E-2</v>
+      </c>
+      <c r="V43" s="45">
+        <v>0.96106304949900001</v>
+      </c>
+      <c r="W43" s="1"/>
+      <c r="X43" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="53"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="1"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A44" s="51"/>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1.70151152581477E-4</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1.70151152581477E-4</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>12.5741045864533</v>
+      </c>
+      <c r="G44" s="1">
+        <v>11.0117065721159</v>
+      </c>
+      <c r="H44" s="2">
+        <v>5.7804446105462802E-3</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="53"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R44" s="45">
+        <v>8.7200299999999999E-4</v>
+      </c>
+      <c r="S44" s="45">
+        <v>7.1735829999999997E-4</v>
+      </c>
+      <c r="T44" s="45">
+        <v>43</v>
+      </c>
+      <c r="U44" s="45">
+        <v>1.2155750000000001</v>
+      </c>
+      <c r="V44" s="46">
+        <v>0.2307786</v>
+      </c>
+      <c r="W44" s="1"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="53"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="53"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A45" s="51"/>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1.25476892781706E-5</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1.25476892781706E-5</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>59.264824426186202</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.81205134607087903</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.37116202943872301</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R45" s="45">
+        <v>-2.0367390000000001E-3</v>
+      </c>
+      <c r="S45" s="45">
+        <v>6.5130869999999999E-4</v>
+      </c>
+      <c r="T45" s="45">
+        <v>40</v>
+      </c>
+      <c r="U45" s="45">
+        <v>-3.127148</v>
+      </c>
+      <c r="V45" s="46">
+        <v>3.2851500000000001E-3</v>
+      </c>
+      <c r="W45" s="1"/>
+      <c r="X45" s="53"/>
+      <c r="Y45" s="53"/>
+      <c r="Z45" s="53"/>
+      <c r="AA45" s="53"/>
+      <c r="AB45" s="53"/>
+      <c r="AC45" s="1"/>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A46" s="52"/>
+      <c r="B46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="53"/>
+      <c r="N46" s="53"/>
+      <c r="O46" s="53"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R46" s="45">
+        <v>-1.576327E-3</v>
+      </c>
+      <c r="S46" s="45">
+        <v>8.643317E-4</v>
+      </c>
+      <c r="T46" s="45">
+        <v>11.874320000000001</v>
+      </c>
+      <c r="U46" s="45">
+        <v>-1.823752</v>
+      </c>
+      <c r="V46" s="46">
+        <v>9.3442800000000006E-2</v>
+      </c>
+      <c r="W46" s="1"/>
+      <c r="X46" s="53"/>
+      <c r="Y46" s="53"/>
+      <c r="Z46" s="53"/>
+      <c r="AA46" s="53"/>
+      <c r="AB46" s="53"/>
+      <c r="AC46" s="1"/>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>73.999999999267601</v>
+      </c>
+      <c r="G47" s="1">
+        <v>34.870200464865299</v>
+      </c>
+      <c r="H47" s="4">
+        <v>9.94550983787633E-8</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="53"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="53"/>
+      <c r="P47" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R47" s="1">
+        <v>1.3623919999999999E-2</v>
+      </c>
+      <c r="S47" s="1">
+        <v>1.319795E-2</v>
+      </c>
+      <c r="T47" s="1">
+        <v>31</v>
+      </c>
+      <c r="U47" s="1">
+        <v>1.032276</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0.30992960000000003</v>
+      </c>
+      <c r="W47" s="1"/>
+      <c r="X47" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y47" s="53"/>
+      <c r="Z47" s="53"/>
+      <c r="AA47" s="53"/>
+      <c r="AB47" s="53"/>
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A48" s="51"/>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.111292819337707</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.111292819337707</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>73.999999999267601</v>
+      </c>
+      <c r="G48" s="1">
+        <v>25.146700660135899</v>
+      </c>
+      <c r="H48" s="4">
+        <v>3.5283045440115499E-6</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="53"/>
+      <c r="P48" s="51"/>
+      <c r="Q48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R48" s="1">
+        <v>7.6710570000000006E-2</v>
+      </c>
+      <c r="S48" s="1">
+        <v>8.8472120000000001E-3</v>
+      </c>
+      <c r="T48" s="1">
+        <v>43</v>
+      </c>
+      <c r="U48" s="1">
+        <v>8.6705930000000002</v>
+      </c>
+      <c r="V48" s="2">
+        <v>5.4385229999999998E-11</v>
+      </c>
+      <c r="W48" s="1"/>
+      <c r="X48" s="53"/>
+      <c r="Y48" s="53"/>
+      <c r="Z48" s="53"/>
+      <c r="AA48" s="53"/>
+      <c r="AB48" s="53"/>
+      <c r="AC48" s="1"/>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A49" s="51"/>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="1">
+        <v>7.5267632704079004E-2</v>
+      </c>
+      <c r="D49" s="1">
+        <v>7.5267632704079004E-2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>73.999999999270102</v>
+      </c>
+      <c r="G49" s="1">
+        <v>17.006781212570601</v>
+      </c>
+      <c r="H49" s="4">
+        <v>9.6345615419962495E-5</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="53"/>
+      <c r="P49" s="51"/>
+      <c r="Q49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R49" s="1">
+        <v>-6.9491259999999999E-2</v>
+      </c>
+      <c r="S49" s="1">
+        <v>1.0221040000000001E-2</v>
+      </c>
+      <c r="T49" s="1">
+        <v>12.84778</v>
+      </c>
+      <c r="U49" s="1">
+        <v>-6.7988470000000003</v>
+      </c>
+      <c r="V49" s="2">
+        <v>1.343811E-5</v>
+      </c>
+      <c r="W49" s="1"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="53"/>
+      <c r="Z49" s="53"/>
+      <c r="AA49" s="53"/>
+      <c r="AB49" s="53"/>
+      <c r="AC49" s="1"/>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A50" s="52"/>
+      <c r="B50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="53"/>
+      <c r="P50" s="52"/>
+      <c r="Q50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R50" s="1">
+        <v>-6.8129929999999998E-3</v>
+      </c>
+      <c r="S50" s="1">
+        <v>1.1591260000000001E-2</v>
+      </c>
+      <c r="T50" s="1">
+        <v>34</v>
+      </c>
+      <c r="U50" s="1">
+        <v>-0.58776980000000001</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0.56057069999999998</v>
+      </c>
+      <c r="W50" s="1"/>
+      <c r="X50" s="53"/>
+      <c r="Y50" s="53"/>
+      <c r="Z50" s="53"/>
+      <c r="AA50" s="53"/>
+      <c r="AB50" s="53"/>
+      <c r="AC50" s="1"/>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A51" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="1">
+        <v>11.200752100000001</v>
+      </c>
+      <c r="D51" s="1">
+        <v>11.200752100000001</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
+        <v>51.667794999999998</v>
+      </c>
+      <c r="G51" s="1">
+        <v>471.893664</v>
+      </c>
+      <c r="H51" s="4">
+        <v>1.209274E-27</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0.29653109999999999</v>
+      </c>
+      <c r="S51" s="1">
+        <v>3.0081920000000002E-2</v>
+      </c>
+      <c r="T51" s="1">
+        <v>12.984576000000001</v>
+      </c>
+      <c r="U51" s="1">
+        <v>9.8574540000000006</v>
+      </c>
+      <c r="V51" s="2">
+        <v>2.1465810000000001E-7</v>
+      </c>
+      <c r="W51" s="1"/>
+      <c r="X51" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y51" s="53"/>
+      <c r="Z51" s="53"/>
+      <c r="AA51" s="53"/>
+      <c r="AB51" s="53"/>
+      <c r="AC51" s="1"/>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A52" s="51"/>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.12802530000000001</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.12802530000000001</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>6.2246040000000002</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5.3937730000000004</v>
+      </c>
+      <c r="H52" s="4">
+        <v>5.7713939999999998E-2</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="53"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0.48443409999999998</v>
+      </c>
+      <c r="S52" s="1">
+        <v>1.925058E-2</v>
+      </c>
+      <c r="T52" s="1">
+        <v>33.275270999999996</v>
+      </c>
+      <c r="U52" s="1">
+        <v>25.164650000000002</v>
+      </c>
+      <c r="V52" s="2">
+        <v>3.0964249999999998E-23</v>
+      </c>
+      <c r="W52" s="1"/>
+      <c r="X52" s="53"/>
+      <c r="Y52" s="53"/>
+      <c r="Z52" s="53"/>
+      <c r="AA52" s="53"/>
+      <c r="AB52" s="53"/>
+      <c r="AC52" s="1"/>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A53" s="51"/>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.70815150000000004</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.70815150000000004</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
+        <v>51.667794999999998</v>
+      </c>
+      <c r="G53" s="1">
+        <v>29.834802</v>
+      </c>
+      <c r="H53" s="4">
+        <v>1.363103E-6</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="53"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R53" s="1">
+        <v>-4.9176770000000002E-2</v>
+      </c>
+      <c r="S53" s="1">
+        <v>3.2182200000000001E-2</v>
+      </c>
+      <c r="T53" s="1">
+        <v>6.754302</v>
+      </c>
+      <c r="U53" s="1">
+        <v>-1.5280739999999999</v>
+      </c>
+      <c r="V53" s="1">
+        <v>0.17187649999999999</v>
+      </c>
+      <c r="W53" s="1"/>
+      <c r="X53" s="53"/>
+      <c r="Y53" s="53"/>
+      <c r="Z53" s="53"/>
+      <c r="AA53" s="53"/>
+      <c r="AB53" s="53"/>
+      <c r="AC53" s="1"/>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A54" s="52"/>
+      <c r="B54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
+      <c r="L54" s="53"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="53"/>
+      <c r="P54" s="52"/>
+      <c r="Q54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0.14682600000000001</v>
+      </c>
+      <c r="S54" s="1">
+        <v>2.4250879999999999E-2</v>
+      </c>
+      <c r="T54" s="1">
+        <v>6.7890449999999998</v>
+      </c>
+      <c r="U54" s="1">
+        <v>6.0544589999999996</v>
+      </c>
+      <c r="V54" s="2">
+        <v>5.7776140000000001E-4</v>
+      </c>
+      <c r="W54" s="1"/>
+      <c r="X54" s="53"/>
+      <c r="Y54" s="53"/>
+      <c r="Z54" s="53"/>
+      <c r="AA54" s="53"/>
+      <c r="AB54" s="53"/>
+      <c r="AC54" s="1"/>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A57" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="1">
+        <v>4.1857799097373602</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4.1857799097373602</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>58.775295215237101</v>
+      </c>
+      <c r="G57" s="1">
+        <v>309.45174334807001</v>
+      </c>
+      <c r="H57" s="4">
+        <v>4.2882526567544902E-25</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1">
+        <v>0.23998054577629399</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0.23998054577629399</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1">
+        <v>107.186966242618</v>
+      </c>
+      <c r="N57" s="1">
+        <v>18.487688610543501</v>
+      </c>
+      <c r="O57" s="4">
+        <v>3.7826149790259799E-5</v>
+      </c>
+      <c r="P57" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0.27505610000000003</v>
+      </c>
+      <c r="S57" s="1">
+        <v>2.398492E-2</v>
+      </c>
+      <c r="T57" s="1">
+        <v>23.545262000000001</v>
+      </c>
+      <c r="U57" s="1">
+        <v>11.467879999999999</v>
+      </c>
+      <c r="V57" s="2">
+        <v>4.0475789999999998E-11</v>
+      </c>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1">
+        <v>3.6012679999999998E-2</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>1.375581E-2</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>55.148274000000001</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>2.617998</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>1.1395529999999999E-2</v>
+      </c>
+      <c r="AC57" s="1"/>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A58" s="51"/>
+      <c r="B58" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="1">
+        <v>3.6571648177047403E-2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3.6571648177047403E-2</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
+        <v>14.508066856775899</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2.7037160408679202</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.121602132726155</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1">
+        <v>0.14769196366738499</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0.14769196366738499</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1">
+        <v>12.379734112886799</v>
+      </c>
+      <c r="N58" s="1">
+        <v>11.3779349310574</v>
+      </c>
+      <c r="O58" s="2">
+        <v>5.3176769657787898E-3</v>
+      </c>
+      <c r="P58" s="51"/>
+      <c r="Q58" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0.19852059999999999</v>
+      </c>
+      <c r="S58" s="1">
+        <v>1.444864E-2</v>
+      </c>
+      <c r="T58" s="1">
+        <v>39.39331</v>
+      </c>
+      <c r="U58" s="1">
+        <v>13.739739999999999</v>
+      </c>
+      <c r="V58" s="2">
+        <v>1.3031699999999999E-16</v>
+      </c>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1">
+        <v>7.6390949999999999E-2</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>1.4668270000000001E-2</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>54.133626</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>5.2079060000000004</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>3.0402339999999998E-6</v>
+      </c>
+      <c r="AC58" s="1"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A59" s="51"/>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="1">
+        <v>9.5456152618234799E-2</v>
+      </c>
+      <c r="D59" s="1">
+        <v>9.5456152618234799E-2</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
+        <v>58.775295214428802</v>
+      </c>
+      <c r="G59" s="1">
+        <v>7.0570057379977396</v>
+      </c>
+      <c r="H59" s="2">
+        <v>1.01489929112641E-2</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1">
+        <v>4.6084357610204602E-2</v>
+      </c>
+      <c r="K59" s="1">
+        <v>4.6084357610204602E-2</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <v>106.783841827976</v>
+      </c>
+      <c r="N59" s="1">
+        <v>3.5502596702509801</v>
+      </c>
+      <c r="O59" s="3">
+        <v>6.2255752292747699E-2</v>
+      </c>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R59" s="1">
+        <v>-3.3437139999999997E-2</v>
+      </c>
+      <c r="S59" s="1">
+        <v>4.8165840000000001E-2</v>
+      </c>
+      <c r="T59" s="1">
+        <v>16.692450000000001</v>
+      </c>
+      <c r="U59" s="1">
+        <v>-0.69420850000000001</v>
+      </c>
+      <c r="V59" s="1">
+        <v>0.49710019999999999</v>
+      </c>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1">
+        <v>-0.1025577</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>3.6524609999999999E-2</v>
+      </c>
+      <c r="Z59" s="1">
+        <v>11.814360000000001</v>
+      </c>
+      <c r="AA59" s="1">
+        <v>-2.8079070000000002</v>
+      </c>
+      <c r="AB59" s="2">
+        <v>1.6019390000000001E-2</v>
+      </c>
+      <c r="AC59" s="1"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A60" s="52"/>
+      <c r="B60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1">
+        <v>5.2456643231190104E-3</v>
+      </c>
+      <c r="K60" s="1">
+        <v>2.6228321615595E-3</v>
+      </c>
+      <c r="L60" s="1">
+        <v>2</v>
+      </c>
+      <c r="M60" s="1">
+        <v>106.82092564483</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0.202058479881251</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0.81735870029617597</v>
+      </c>
+      <c r="P60" s="52"/>
+      <c r="Q60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R60" s="1">
+        <v>-7.4605980000000002E-2</v>
+      </c>
+      <c r="S60" s="1">
+        <v>3.2539319999999997E-2</v>
+      </c>
+      <c r="T60" s="1">
+        <v>15.191789999999999</v>
+      </c>
+      <c r="U60" s="1">
+        <v>-2.2927949999999999</v>
+      </c>
+      <c r="V60" s="2">
+        <v>3.6532830000000002E-2</v>
+      </c>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1">
+        <v>-6.5260349999999995E-2</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>2.0409139999999999E-2</v>
+      </c>
+      <c r="Z60" s="1">
+        <v>10.9194</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>-3.1976040000000001</v>
+      </c>
+      <c r="AB60" s="2">
+        <v>8.565675E-3</v>
+      </c>
+      <c r="AC60" s="1"/>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A61" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="1">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
+        <v>58.450172749992298</v>
+      </c>
+      <c r="G61" s="1">
+        <v>275.61367619126997</v>
+      </c>
+      <c r="H61" s="4">
+        <v>8.5561055144156804E-24</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1">
+        <v>0.12745796635020001</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0.12745796635020001</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <v>106.169152592015</v>
+      </c>
+      <c r="N61" s="1">
+        <v>9.7924313998268993</v>
+      </c>
+      <c r="O61" s="2">
+        <v>2.2627938793836001E-3</v>
+      </c>
+      <c r="P61" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0.25910539999999999</v>
+      </c>
+      <c r="S61" s="1">
+        <v>2.38897E-2</v>
+      </c>
+      <c r="T61" s="1">
+        <v>23.495559</v>
+      </c>
+      <c r="U61" s="1">
+        <v>10.8459</v>
+      </c>
+      <c r="V61" s="2">
+        <v>1.261363E-10</v>
+      </c>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1">
+        <v>1.180838E-2</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>1.3507180000000001E-2</v>
+      </c>
+      <c r="Z61" s="1">
+        <v>55.127535999999999</v>
+      </c>
+      <c r="AA61" s="1">
+        <v>0.8742297</v>
+      </c>
+      <c r="AB61" s="1">
+        <v>0.38578590000000001</v>
+      </c>
+      <c r="AC61" s="1"/>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A62" s="51"/>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>14.0776142021772</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2.7892973561671002</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0.116971279359414</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1">
+        <v>0.116553339771977</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0.116553339771977</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <v>12.391275226041101</v>
+      </c>
+      <c r="N62" s="1">
+        <v>8.9546429840398503</v>
+      </c>
+      <c r="O62" s="2">
+        <v>1.08776102041225E-2</v>
+      </c>
+      <c r="P62" s="51"/>
+      <c r="Q62" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0.1893232</v>
+      </c>
+      <c r="S62" s="1">
+        <v>1.4590860000000001E-2</v>
+      </c>
+      <c r="T62" s="1">
+        <v>39.182360000000003</v>
+      </c>
+      <c r="U62" s="1">
+        <v>12.97547</v>
+      </c>
+      <c r="V62" s="2">
+        <v>9.1451869999999996E-16</v>
+      </c>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1">
+        <v>6.3492019999999996E-2</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>1.5105850000000001E-2</v>
+      </c>
+      <c r="Z62" s="1">
+        <v>53.118403999999998</v>
+      </c>
+      <c r="AA62" s="1">
+        <v>4.2031409999999996</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>1.0131990000000001E-4</v>
+      </c>
+      <c r="AC62" s="1"/>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A63" s="51"/>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="D63" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>58.450172750997197</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5.6910096770543701</v>
+      </c>
+      <c r="H63" s="2">
+        <v>2.0312618497821299E-2</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1">
+        <v>7.3363893765149693E-2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>7.3363893765149693E-2</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <v>105.814592900958</v>
+      </c>
+      <c r="N63" s="1">
+        <v>5.6364534716137902</v>
+      </c>
+      <c r="O63" s="2">
+        <v>1.9393437026140801E-2</v>
+      </c>
+      <c r="P63" s="51"/>
+      <c r="Q63" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R63" s="1">
+        <v>-3.3733069999999997E-2</v>
+      </c>
+      <c r="S63" s="1">
+        <v>4.5654569999999998E-2</v>
+      </c>
+      <c r="T63" s="1">
+        <v>16.29635</v>
+      </c>
+      <c r="U63" s="1">
+        <v>-0.73887599999999998</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0.4704913</v>
+      </c>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1">
+        <v>-9.7459550000000006E-2</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>3.5986459999999998E-2</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>11.75554</v>
+      </c>
+      <c r="AA63" s="1">
+        <v>-2.7082280000000001</v>
+      </c>
+      <c r="AB63" s="2">
+        <v>1.9320850000000001E-2</v>
+      </c>
+      <c r="AC63" s="1"/>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A64" s="52"/>
+      <c r="B64" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1">
+        <v>7.5239018444935397E-3</v>
+      </c>
+      <c r="K64" s="1">
+        <v>3.7619509222467699E-3</v>
+      </c>
+      <c r="L64" s="1">
+        <v>2</v>
+      </c>
+      <c r="M64" s="1">
+        <v>105.84740366368401</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0.28902584428814998</v>
+      </c>
+      <c r="O64" s="1">
+        <v>0.74958204967156605</v>
+      </c>
+      <c r="P64" s="52"/>
+      <c r="Q64" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R64" s="1">
+        <v>-7.235192E-2</v>
+      </c>
+      <c r="S64" s="1">
+        <v>3.050694E-2</v>
+      </c>
+      <c r="T64" s="1">
+        <v>14.92966</v>
+      </c>
+      <c r="U64" s="1">
+        <v>-2.3716539999999999</v>
+      </c>
+      <c r="V64" s="2">
+        <v>3.1591439999999998E-2</v>
+      </c>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1">
+        <v>-5.128456E-2</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>2.117863E-2</v>
+      </c>
+      <c r="Z64" s="1">
+        <v>11.11552</v>
+      </c>
+      <c r="AA64" s="1">
+        <v>-2.4215239999999998</v>
+      </c>
+      <c r="AB64" s="2">
+        <v>3.3703570000000002E-2</v>
+      </c>
+      <c r="AC64" s="1"/>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A65" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="D65">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>57.941257724360497</v>
+      </c>
+      <c r="G65">
+        <v>114.44647303148901</v>
+      </c>
+      <c r="H65" s="7">
+        <v>2.4310901681812699E-15</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="5">
+        <v>3.27228460982109E-6</v>
+      </c>
+      <c r="K65" s="5">
+        <v>3.27228460982109E-6</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>108.162570470471</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0.81526923567301701</v>
+      </c>
+      <c r="O65" s="1">
+        <v>0.36857341395755699</v>
+      </c>
+      <c r="P65" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R65" s="45">
+        <v>0.16267690000000001</v>
+      </c>
+      <c r="S65" s="45">
+        <v>2.342762E-2</v>
+      </c>
+      <c r="T65" s="45">
+        <v>23.465475999999999</v>
+      </c>
+      <c r="U65" s="45">
+        <v>6.9438079999999998</v>
+      </c>
+      <c r="V65" s="45">
+        <v>3.98194E-7</v>
+      </c>
+      <c r="W65" s="1"/>
+      <c r="X65" s="45">
+        <v>-2.5494809999999999E-4</v>
+      </c>
+      <c r="Y65" s="45">
+        <v>1.9431219999999999E-4</v>
+      </c>
+      <c r="Z65" s="45">
+        <v>55.507640000000002</v>
+      </c>
+      <c r="AA65" s="45">
+        <v>-1.3120540000000001</v>
+      </c>
+      <c r="AB65" s="45">
+        <v>0.19490214432</v>
+      </c>
+      <c r="AC65" s="1"/>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A66" s="51"/>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="D66">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>14.016499111022799</v>
+      </c>
+      <c r="G66">
+        <v>4.0830664272103698</v>
+      </c>
+      <c r="H66" s="9">
+        <v>6.28474981350714E-2</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1">
+        <v>1.1254087942051899E-4</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1.1254087942051899E-4</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>13.1287610221782</v>
+      </c>
+      <c r="N66" s="1">
+        <v>28.038855933179999</v>
+      </c>
+      <c r="O66" s="2">
+        <v>1.4035037213878999E-4</v>
+      </c>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R66" s="45">
+        <v>0.1318241</v>
+      </c>
+      <c r="S66" s="45">
+        <v>1.53215E-2</v>
+      </c>
+      <c r="T66" s="45">
+        <v>38.868819999999999</v>
+      </c>
+      <c r="U66" s="45">
+        <v>8.603866</v>
+      </c>
+      <c r="V66" s="46">
+        <v>1.5523469999999999E-10</v>
+      </c>
+      <c r="W66" s="1"/>
+      <c r="X66" s="45">
+        <v>2.431771E-4</v>
+      </c>
+      <c r="Y66" s="45">
+        <v>3.0047830000000001E-4</v>
+      </c>
+      <c r="Z66" s="45">
+        <v>54.111055</v>
+      </c>
+      <c r="AA66" s="45">
+        <v>0.80930000000000002</v>
+      </c>
+      <c r="AB66" s="45">
+        <v>0.4218870666026</v>
+      </c>
+      <c r="AC66" s="1"/>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A67" s="51"/>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="D67">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>57.941257724235903</v>
+      </c>
+      <c r="G67">
+        <v>0.82228421440567401</v>
+      </c>
+      <c r="H67">
+        <v>0.36826900260683199</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="5">
+        <v>7.3359735284969697E-6</v>
+      </c>
+      <c r="K67" s="5">
+        <v>7.3359735284969697E-6</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>107.80326229592799</v>
+      </c>
+      <c r="N67" s="1">
+        <v>1.82771190303713</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0.179227673464389</v>
+      </c>
+      <c r="P67" s="51"/>
+      <c r="Q67" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R67" s="45">
+        <v>-7.6752669999999995E-2</v>
+      </c>
+      <c r="S67" s="45">
+        <v>5.0189159999999997E-2</v>
+      </c>
+      <c r="T67" s="45">
+        <v>16.372039999999998</v>
+      </c>
+      <c r="U67" s="45">
+        <v>-1.5292680000000001</v>
+      </c>
+      <c r="V67" s="46">
+        <v>0.14528840000000001</v>
+      </c>
+      <c r="W67" s="1"/>
+      <c r="X67" s="45">
+        <v>-2.3284180000000001E-3</v>
+      </c>
+      <c r="Y67" s="45">
+        <v>4.9925909999999998E-4</v>
+      </c>
+      <c r="Z67" s="45">
+        <v>11.371589999999999</v>
+      </c>
+      <c r="AA67" s="45">
+        <v>-4.6637459999999997</v>
+      </c>
+      <c r="AB67" s="45">
+        <v>6.3120474729999999E-4</v>
+      </c>
+      <c r="AC67" s="1"/>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A68" s="52"/>
+      <c r="B68" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="5">
+        <v>7.2143853443936604E-6</v>
+      </c>
+      <c r="K68" s="5">
+        <v>3.6071926721968302E-6</v>
+      </c>
+      <c r="L68" s="1">
+        <v>2</v>
+      </c>
+      <c r="M68" s="1">
+        <v>107.842517864377</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0.89870948387585703</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0.41012132536637402</v>
+      </c>
+      <c r="P68" s="52"/>
+      <c r="Q68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R68" s="45">
+        <v>-6.6752569999999997E-2</v>
+      </c>
+      <c r="S68" s="45">
+        <v>3.12787E-2</v>
+      </c>
+      <c r="T68" s="45">
+        <v>14.8775</v>
+      </c>
+      <c r="U68" s="45">
+        <v>-2.1341220000000001</v>
+      </c>
+      <c r="V68" s="46">
+        <v>4.9892260000000001E-2</v>
+      </c>
+      <c r="W68" s="1"/>
+      <c r="X68" s="45">
+        <v>-1.939112E-3</v>
+      </c>
+      <c r="Y68" s="45">
+        <v>3.8723229999999999E-4</v>
+      </c>
+      <c r="Z68" s="45">
+        <v>13.92292</v>
+      </c>
+      <c r="AA68" s="45">
+        <v>-5.0076210000000003</v>
+      </c>
+      <c r="AB68" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC68" s="1"/>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3.2828058473639601</v>
+      </c>
+      <c r="D69" s="1">
+        <v>3.2828058473639601</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>57.1027846481349</v>
+      </c>
+      <c r="G69" s="1">
+        <v>315.57785828471202</v>
+      </c>
+      <c r="H69" s="4">
+        <v>6.2556135251351003E-25</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1">
+        <v>4.9581564592565801</v>
+      </c>
+      <c r="K69" s="1">
+        <v>4.9581564592565801</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
+        <v>107.087389174327</v>
+      </c>
+      <c r="N69" s="1">
+        <v>15.8163561438312</v>
+      </c>
+      <c r="O69" s="2">
+        <v>1.2711861864362099E-4</v>
+      </c>
+      <c r="P69" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0.26141530000000002</v>
+      </c>
+      <c r="S69" s="1">
+        <v>2.107347E-2</v>
+      </c>
+      <c r="T69" s="1">
+        <v>22.795461</v>
+      </c>
+      <c r="U69" s="1">
+        <v>12.404952</v>
+      </c>
+      <c r="V69" s="2">
+        <v>1.2861529999999999E-11</v>
+      </c>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1">
+        <v>0.1080815</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>6.8329970000000004E-2</v>
+      </c>
+      <c r="Z69" s="1">
+        <v>55.203989999999997</v>
+      </c>
+      <c r="AA69" s="1">
+        <v>1.581758</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0.11941789999999999</v>
+      </c>
+      <c r="AC69" s="1"/>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A70" s="51"/>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="1">
+        <v>6.9098899300225596E-4</v>
+      </c>
+      <c r="D70" s="1">
+        <v>6.9098899300225596E-4</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>13.6400199665374</v>
+      </c>
+      <c r="G70" s="1">
+        <v>6.6425136498724599E-2</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0.80046236006191795</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1">
+        <v>1.93826224654098E-2</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1.93826224654098E-2</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <v>11.8724826464864</v>
+      </c>
+      <c r="N70" s="1">
+        <v>6.1829928610262298E-2</v>
+      </c>
+      <c r="O70" s="1">
+        <v>0.80787586394532096</v>
+      </c>
+      <c r="P70" s="51"/>
+      <c r="Q70" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0.16795750000000001</v>
+      </c>
+      <c r="S70" s="1">
+        <v>1.305196E-2</v>
+      </c>
+      <c r="T70" s="1">
+        <v>38.406829999999999</v>
+      </c>
+      <c r="U70" s="1">
+        <v>12.86838</v>
+      </c>
+      <c r="V70" s="2">
+        <v>1.6708039999999999E-15</v>
+      </c>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1">
+        <v>0.34042270000000002</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>7.1749140000000003E-2</v>
+      </c>
+      <c r="Z70" s="1">
+        <v>54.122332999999998</v>
+      </c>
+      <c r="AA70" s="1">
+        <v>4.7446250000000001</v>
+      </c>
+      <c r="AB70" s="2">
+        <v>1.5661770000000001E-5</v>
+      </c>
+      <c r="AC70" s="1"/>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A71" s="51"/>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.13315844295854501</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0.13315844295854501</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>57.102784645779103</v>
+      </c>
+      <c r="G71" s="1">
+        <v>12.800591382864701</v>
+      </c>
+      <c r="H71" s="2">
+        <v>7.1467481949516205E-4</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1">
+        <v>1.5642063102591399</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1.5642063102591399</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
+        <v>106.739383464101</v>
+      </c>
+      <c r="N71" s="1">
+        <v>4.9897667184944403</v>
+      </c>
+      <c r="O71" s="2">
+        <v>2.7582949079364601E-2</v>
+      </c>
+      <c r="P71" s="51"/>
+      <c r="Q71" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R71" s="1">
+        <v>2.4449390000000001E-2</v>
+      </c>
+      <c r="S71" s="1">
+        <v>4.0505119999999999E-2</v>
+      </c>
+      <c r="T71" s="1">
+        <v>15.698370000000001</v>
+      </c>
+      <c r="U71" s="1">
+        <v>0.60361220000000004</v>
+      </c>
+      <c r="V71" s="1">
+        <v>0.55472399999999999</v>
+      </c>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1">
+        <v>-0.11951639999999999</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>0.1459646</v>
+      </c>
+      <c r="Z71" s="1">
+        <v>11.39526</v>
+      </c>
+      <c r="AA71" s="1">
+        <v>-0.81880399999999998</v>
+      </c>
+      <c r="AB71" s="1">
+        <v>0.4296896</v>
+      </c>
+      <c r="AC71" s="1"/>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A72" s="52"/>
+      <c r="B72" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1">
+        <v>0.34951867520347901</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0.17475933760173901</v>
+      </c>
+      <c r="L72" s="1">
+        <v>2</v>
+      </c>
+      <c r="M72" s="1">
+        <v>106.790362785864</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0.55747654308262395</v>
+      </c>
+      <c r="O72" s="1">
+        <v>0.57430971602825098</v>
+      </c>
+      <c r="P72" s="52"/>
+      <c r="Q72" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R72" s="1">
+        <v>-2.5180310000000001E-2</v>
+      </c>
+      <c r="S72" s="1">
+        <v>2.9583849999999998E-2</v>
+      </c>
+      <c r="T72" s="1">
+        <v>15.65354</v>
+      </c>
+      <c r="U72" s="1">
+        <v>-0.85115050000000003</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0.4075182</v>
+      </c>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1">
+        <v>0.1035258</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>8.4846459999999999E-2</v>
+      </c>
+      <c r="Z72" s="1">
+        <v>10.68332</v>
+      </c>
+      <c r="AA72" s="1">
+        <v>1.2201550000000001</v>
+      </c>
+      <c r="AB72" s="1">
+        <v>0.2486556</v>
+      </c>
+      <c r="AC72" s="1"/>
+    </row>
+    <row r="73" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1.36628969679729</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1.36628969679729</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>54.103865456753802</v>
+      </c>
+      <c r="G73" s="1">
+        <v>323.52191769489502</v>
+      </c>
+      <c r="H73" s="4">
+        <v>1.7309716058161699E-24</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1">
+        <v>11.8595223504753</v>
+      </c>
+      <c r="K73" s="1">
+        <v>11.8595223504753</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <v>107.201241552043</v>
+      </c>
+      <c r="N73" s="1">
+        <v>9.5506130348868208</v>
+      </c>
+      <c r="O73" s="2">
+        <v>2.54688520800141E-3</v>
+      </c>
+      <c r="P73" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0.16815289999999999</v>
+      </c>
+      <c r="S73" s="1">
+        <v>1.333603E-2</v>
+      </c>
+      <c r="T73" s="1">
+        <v>22.543147000000001</v>
+      </c>
+      <c r="U73" s="1">
+        <v>12.608919999999999</v>
+      </c>
+      <c r="V73" s="2">
+        <v>1.085642E-11</v>
+      </c>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1">
+        <v>5.9286020000000002E-2</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>0.1302239</v>
+      </c>
+      <c r="Z73" s="1">
+        <v>55.180911999999999</v>
+      </c>
+      <c r="AA73" s="1">
+        <v>0.45526230000000001</v>
+      </c>
+      <c r="AB73" s="1">
+        <v>0.65070680000000003</v>
+      </c>
+      <c r="AC73" s="1"/>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A74" s="51"/>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="1">
+        <v>3.0303710819429698E-3</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3.0303710819429698E-3</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>10.659214250737501</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.71755753267807798</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0.41556047753360997</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1">
+        <v>1.06298370497324</v>
+      </c>
+      <c r="K74" s="1">
+        <v>1.06298370497324</v>
+      </c>
+      <c r="L74" s="1">
+        <v>1</v>
+      </c>
+      <c r="M74" s="1">
+        <v>12.0506128910075</v>
+      </c>
+      <c r="N74" s="1">
+        <v>0.85603329784886595</v>
+      </c>
+      <c r="O74" s="1">
+        <v>0.37300851361203902</v>
+      </c>
+      <c r="P74" s="51"/>
+      <c r="Q74" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0.1095054</v>
+      </c>
+      <c r="S74" s="1">
+        <v>7.9211479999999994E-3</v>
+      </c>
+      <c r="T74" s="1">
+        <v>39.579543000000001</v>
+      </c>
+      <c r="U74" s="1">
+        <v>13.82443</v>
+      </c>
+      <c r="V74" s="2">
+        <v>9.7457139999999995E-17</v>
+      </c>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1">
+        <v>0.51176239999999995</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>0.1491497</v>
+      </c>
+      <c r="Z74" s="1">
+        <v>54.192520000000002</v>
+      </c>
+      <c r="AA74" s="1">
+        <v>3.4312</v>
+      </c>
+      <c r="AB74" s="2">
+        <v>1.157145E-3</v>
+      </c>
+      <c r="AC74" s="1"/>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A75" s="51"/>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5.2728177270368402E-2</v>
+      </c>
+      <c r="D75" s="1">
+        <v>5.2728177270368402E-2</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>54.1038654583488</v>
+      </c>
+      <c r="G75" s="1">
+        <v>12.4854348730384</v>
+      </c>
+      <c r="H75" s="2">
+        <v>8.48284866637566E-4</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1">
+        <v>5.8391786603145501</v>
+      </c>
+      <c r="K75" s="1">
+        <v>5.8391786603145501</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
+        <v>106.84246065981201</v>
+      </c>
+      <c r="N75" s="1">
+        <v>4.7023593512598696</v>
+      </c>
+      <c r="O75" s="2">
+        <v>3.23394599501459E-2</v>
+      </c>
+      <c r="P75" s="51"/>
+      <c r="Q75" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R75" s="1">
+        <v>4.9169679999999999E-3</v>
+      </c>
+      <c r="S75" s="1">
+        <v>2.157123E-2</v>
+      </c>
+      <c r="T75" s="1">
+        <v>14.439249999999999</v>
+      </c>
+      <c r="U75" s="1">
+        <v>0.227941</v>
+      </c>
+      <c r="V75" s="1">
+        <v>0.82288839999999996</v>
+      </c>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1">
+        <v>-0.38848120000000003</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>0.30375679999999999</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>10.94359</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>-1.2789219999999999</v>
+      </c>
+      <c r="AB75" s="1">
+        <v>0.22737859999999999</v>
+      </c>
+      <c r="AC75" s="1"/>
+    </row>
+    <row r="76" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="52"/>
+      <c r="B76" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1">
+        <v>2.5021778012642701</v>
+      </c>
+      <c r="K76" s="1">
+        <v>1.25108890063213</v>
+      </c>
+      <c r="L76" s="1">
+        <v>2</v>
+      </c>
+      <c r="M76" s="1">
+        <v>106.889741706824</v>
+      </c>
+      <c r="N76" s="1">
+        <v>1.0075166274888401</v>
+      </c>
+      <c r="O76" s="1">
+        <v>0.36856517791115101</v>
+      </c>
+      <c r="P76" s="52"/>
+      <c r="Q76" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R76" s="1">
+        <v>-2.9254499999999999E-2</v>
+      </c>
+      <c r="S76" s="1">
+        <v>1.6422550000000001E-2</v>
+      </c>
+      <c r="T76" s="1">
+        <v>14.43604</v>
+      </c>
+      <c r="U76" s="1">
+        <v>-1.781361</v>
+      </c>
+      <c r="V76" s="3">
+        <v>9.5896949999999995E-2</v>
+      </c>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1">
+        <v>5.3543380000000002E-2</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>0.17968680000000001</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>11.420360000000001</v>
+      </c>
+      <c r="AA76" s="1">
+        <v>0.29798170000000002</v>
+      </c>
+      <c r="AB76" s="1">
+        <v>0.77106850000000005</v>
+      </c>
+      <c r="AC76" s="1"/>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="53"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="K77" s="1">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1">
+        <v>109.162762099391</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0.132778478118667</v>
+      </c>
+      <c r="O77" s="1">
+        <v>0.71627332791354703</v>
+      </c>
+      <c r="P77" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R77" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S77" s="53"/>
+      <c r="T77" s="53"/>
+      <c r="U77" s="53"/>
+      <c r="V77" s="53"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="45">
+        <v>-8.3753321000000006E-3</v>
+      </c>
+      <c r="Y77" s="45">
+        <v>8.9984460000000002E-3</v>
+      </c>
+      <c r="Z77" s="45">
+        <v>56.69021</v>
+      </c>
+      <c r="AA77" s="45">
+        <v>-0.93075200000000002</v>
+      </c>
+      <c r="AB77" s="46">
+        <v>0.35592869999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A78" s="51"/>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1">
+        <v>14.2035557007019</v>
+      </c>
+      <c r="N78" s="1">
+        <v>45.384240792485897</v>
+      </c>
+      <c r="O78" s="4">
+        <v>8.8402488312841299E-6</v>
+      </c>
+      <c r="P78" s="51"/>
+      <c r="Q78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R78" s="53"/>
+      <c r="S78" s="53"/>
+      <c r="T78" s="53"/>
+      <c r="U78" s="53"/>
+      <c r="V78" s="53"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="45">
+        <v>6.2885479999999997E-3</v>
+      </c>
+      <c r="Y78" s="45">
+        <v>1.0130220000000001E-2</v>
+      </c>
+      <c r="Z78" s="45">
+        <v>54.056728</v>
+      </c>
+      <c r="AA78" s="45">
+        <v>0.62077130000000003</v>
+      </c>
+      <c r="AB78" s="46">
+        <v>0.53735880000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A79" s="51"/>
+      <c r="B79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="K79" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="L79" s="1">
+        <v>1</v>
+      </c>
+      <c r="M79" s="1">
+        <v>108.83042432675499</v>
+      </c>
+      <c r="N79" s="1">
+        <v>1.12322676673025</v>
+      </c>
+      <c r="O79" s="1">
+        <v>0.29157119540922299</v>
+      </c>
+      <c r="P79" s="51"/>
+      <c r="Q79" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R79" s="53"/>
+      <c r="S79" s="53"/>
+      <c r="T79" s="53"/>
+      <c r="U79" s="53"/>
+      <c r="V79" s="53"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="45">
+        <v>-0.1092133</v>
+      </c>
+      <c r="Y79" s="45">
+        <v>2.1070729999999999E-2</v>
+      </c>
+      <c r="Z79" s="45">
+        <v>11.89181</v>
+      </c>
+      <c r="AA79" s="45">
+        <v>-5.1831759999999996</v>
+      </c>
+      <c r="AB79" s="46">
+        <v>2.34916E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A80" s="52"/>
+      <c r="B80" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1">
+        <v>7.3489818378573097E-3</v>
+      </c>
+      <c r="K80" s="1">
+        <v>3.6744909189286501E-3</v>
+      </c>
+      <c r="L80" s="1">
+        <v>2</v>
+      </c>
+      <c r="M80" s="1">
+        <v>108.867449329857</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0.63206652031892696</v>
+      </c>
+      <c r="O80" s="1">
+        <v>0.53343128963438502</v>
+      </c>
+      <c r="P80" s="52"/>
+      <c r="Q80" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R80" s="53"/>
+      <c r="S80" s="53"/>
+      <c r="T80" s="53"/>
+      <c r="U80" s="53"/>
+      <c r="V80" s="53"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="45">
+        <v>-9.8989809999999998E-2</v>
+      </c>
+      <c r="Y80" s="45">
+        <v>1.5884120000000002E-2</v>
+      </c>
+      <c r="Z80" s="45">
+        <v>13.67961</v>
+      </c>
+      <c r="AA80" s="45">
+        <v>-6.2319979999999999</v>
+      </c>
+      <c r="AB80" s="46">
+        <v>2.433112E-5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A81" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1628.5396493139699</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1628.5396493139699</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>62.368989869052001</v>
+      </c>
+      <c r="G81" s="1">
+        <v>132.99387365734901</v>
+      </c>
+      <c r="H81" s="4">
+        <v>4.1643897411378698E-17</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K81" s="53"/>
+      <c r="L81" s="53"/>
+      <c r="M81" s="53"/>
+      <c r="N81" s="53"/>
+      <c r="O81" s="53"/>
+      <c r="P81" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R81" s="45">
+        <v>-4.1460160000000004</v>
+      </c>
+      <c r="S81" s="45">
+        <v>0.6769811</v>
+      </c>
+      <c r="T81" s="45">
+        <v>24.376617</v>
+      </c>
+      <c r="U81" s="45">
+        <v>-6.1242720000000004</v>
+      </c>
+      <c r="V81" s="45">
+        <v>2.350653E-6</v>
+      </c>
+      <c r="W81" s="1"/>
+      <c r="X81" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y81" s="53"/>
+      <c r="Z81" s="53"/>
+      <c r="AA81" s="53"/>
+      <c r="AB81" s="53"/>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A82" s="51"/>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="1">
+        <v>230.82876413714999</v>
+      </c>
+      <c r="D82" s="1">
+        <v>230.82876413714999</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1">
+        <v>16.563800911315401</v>
+      </c>
+      <c r="G82" s="1">
+        <v>18.8505152497026</v>
+      </c>
+      <c r="H82" s="2">
+        <v>4.6861954719532999E-4</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="53"/>
+      <c r="M82" s="53"/>
+      <c r="N82" s="53"/>
+      <c r="O82" s="53"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R82" s="45">
+        <v>-5.1080050000000004</v>
+      </c>
+      <c r="S82" s="45">
+        <v>0.46945019999999998</v>
+      </c>
+      <c r="T82" s="45">
+        <v>38.858649999999997</v>
+      </c>
+      <c r="U82" s="45">
+        <v>-10.88082</v>
+      </c>
+      <c r="V82" s="46">
+        <v>2.3278650000000001E-13</v>
+      </c>
+      <c r="W82" s="1"/>
+      <c r="X82" s="53"/>
+      <c r="Y82" s="53"/>
+      <c r="Z82" s="53"/>
+      <c r="AA82" s="53"/>
+      <c r="AB82" s="53"/>
+    </row>
+    <row r="83" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="51"/>
+      <c r="B83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="1">
+        <v>14.980580034264699</v>
+      </c>
+      <c r="D83" s="1">
+        <v>14.980580034264699</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>62.368989867379298</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1.22338155489803</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0.27294624360005199</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="53"/>
+      <c r="K83" s="53"/>
+      <c r="L83" s="53"/>
+      <c r="M83" s="53"/>
+      <c r="N83" s="53"/>
+      <c r="O83" s="53"/>
+      <c r="P83" s="51"/>
+      <c r="Q83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R83" s="45">
+        <v>-3.7989480000000002</v>
+      </c>
+      <c r="S83" s="45">
+        <v>1.208588</v>
+      </c>
+      <c r="T83" s="45">
+        <v>17.432320000000001</v>
+      </c>
+      <c r="U83" s="45">
+        <v>-3.143294</v>
+      </c>
+      <c r="V83" s="46">
+        <v>5.789537E-3</v>
+      </c>
+      <c r="W83" s="1"/>
+      <c r="X83" s="53"/>
+      <c r="Y83" s="53"/>
+      <c r="Z83" s="53"/>
+      <c r="AA83" s="53"/>
+      <c r="AB83" s="53"/>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A84" s="52"/>
+      <c r="B84" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="53"/>
+      <c r="K84" s="53"/>
+      <c r="L84" s="53"/>
+      <c r="M84" s="53"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="53"/>
+      <c r="P84" s="52"/>
+      <c r="Q84" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R84" s="45">
+        <v>-4.4755320000000003</v>
+      </c>
+      <c r="S84" s="45">
+        <v>0.98680710000000005</v>
+      </c>
+      <c r="T84" s="45">
+        <v>15.62265</v>
+      </c>
+      <c r="U84" s="45">
+        <v>-4.5353669999999999</v>
+      </c>
+      <c r="V84" s="46">
+        <v>3.5774789999999998E-4</v>
+      </c>
+      <c r="W84" s="1"/>
+      <c r="X84" s="53"/>
+      <c r="Y84" s="53"/>
+      <c r="Z84" s="53"/>
+      <c r="AA84" s="53"/>
+      <c r="AB84" s="53"/>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A85" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="1">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="D85" s="1">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1">
+        <v>67.383586408567496</v>
+      </c>
+      <c r="G85" s="1">
+        <v>224.10765385608801</v>
+      </c>
+      <c r="H85" s="4">
+        <v>4.0821399088527701E-23</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K85" s="53"/>
+      <c r="L85" s="53"/>
+      <c r="M85" s="53"/>
+      <c r="N85" s="53"/>
+      <c r="O85" s="53"/>
+      <c r="P85" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q85" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R85" s="47">
+        <v>0.3732317</v>
+      </c>
+      <c r="S85" s="47">
+        <v>2.314503E-2</v>
+      </c>
+      <c r="T85" s="47">
+        <v>22.935904000000001</v>
+      </c>
+      <c r="U85" s="47">
+        <v>16.125781</v>
+      </c>
+      <c r="V85" s="47">
+        <v>5.242662E-14</v>
+      </c>
+      <c r="W85" s="1"/>
+      <c r="X85" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y85" s="53"/>
+      <c r="Z85" s="53"/>
+      <c r="AA85" s="53"/>
+      <c r="AB85" s="53"/>
+      <c r="AC85" s="1"/>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A86" s="51"/>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="D86" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1">
+        <v>19.7769266057722</v>
+      </c>
+      <c r="G86" s="1">
+        <v>6.8764153859934604E-2</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0.79585674296255904</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="53"/>
+      <c r="L86" s="53"/>
+      <c r="M86" s="53"/>
+      <c r="N86" s="53"/>
+      <c r="O86" s="53"/>
+      <c r="P86" s="51"/>
+      <c r="Q86" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R86" s="47">
+        <v>0.39719009999999999</v>
+      </c>
+      <c r="S86" s="47">
+        <v>3.5684239999999999E-2</v>
+      </c>
+      <c r="T86" s="47">
+        <v>42.630980000000001</v>
+      </c>
+      <c r="U86" s="47">
+        <v>11.130687</v>
+      </c>
+      <c r="V86" s="47">
+        <v>3.4043159999999998E-14</v>
+      </c>
+      <c r="W86" s="1"/>
+      <c r="X86" s="53"/>
+      <c r="Y86" s="53"/>
+      <c r="Z86" s="53"/>
+      <c r="AA86" s="53"/>
+      <c r="AB86" s="53"/>
+      <c r="AC86" s="1"/>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A87" s="51"/>
+      <c r="B87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="D87" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1">
+        <v>67.3835864091361</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.63854715062201595</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0.42704513346780898</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
+      <c r="P87" s="51"/>
+      <c r="Q87" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R87" s="47">
+        <v>-2.5815100000000001E-2</v>
+      </c>
+      <c r="S87" s="47">
+        <v>5.5261520000000001E-2</v>
+      </c>
+      <c r="T87" s="47">
+        <v>21.336089999999999</v>
+      </c>
+      <c r="U87" s="47">
+        <v>-0.46714420000000001</v>
+      </c>
+      <c r="V87" s="47">
+        <v>0.64513220100000002</v>
+      </c>
+      <c r="W87" s="1"/>
+      <c r="X87" s="53"/>
+      <c r="Y87" s="53"/>
+      <c r="Z87" s="53"/>
+      <c r="AA87" s="53"/>
+      <c r="AB87" s="53"/>
+      <c r="AC87" s="1"/>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A88" s="52"/>
+      <c r="B88" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="54"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="53"/>
+      <c r="O88" s="53"/>
+      <c r="P88" s="52"/>
+      <c r="Q88" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R88" s="47">
+        <v>2.8353639999999999E-2</v>
+      </c>
+      <c r="S88" s="47">
+        <v>3.0635989999999998E-2</v>
+      </c>
+      <c r="T88" s="47">
+        <v>18.611360000000001</v>
+      </c>
+      <c r="U88" s="47">
+        <v>0.92550100000000002</v>
+      </c>
+      <c r="V88" s="47">
+        <v>0.36655130000000002</v>
+      </c>
+      <c r="W88" s="1"/>
+      <c r="X88" s="53"/>
+      <c r="Y88" s="53"/>
+      <c r="Z88" s="53"/>
+      <c r="AA88" s="53"/>
+      <c r="AB88" s="53"/>
+      <c r="AC88" s="1"/>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A89" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="1">
+        <v>7.8223335347028398</v>
+      </c>
+      <c r="D89" s="1">
+        <v>7.8223335347028398</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1">
+        <v>56.420511723736702</v>
+      </c>
+      <c r="G89" s="1">
+        <v>269.35108163868898</v>
+      </c>
+      <c r="H89" s="4">
+        <v>3.8248319558473298E-23</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
+      <c r="M89" s="53"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A90" s="51"/>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="1">
+        <v>3.7421662066775302E-2</v>
+      </c>
+      <c r="D90" s="1">
+        <v>3.7421662066775302E-2</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1">
+        <v>11.2818684676293</v>
+      </c>
+      <c r="G90" s="1">
+        <v>1.28856243596449</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0.27985440517664001</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="53"/>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A91" s="51"/>
+      <c r="B91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3.631254937336E-3</v>
+      </c>
+      <c r="D91" s="1">
+        <v>3.631254937336E-3</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1">
+        <v>56.420511720510099</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0.125037169629515</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0.72495214931683005</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="53"/>
+      <c r="M91" s="53"/>
+      <c r="N91" s="53"/>
+      <c r="O91" s="53"/>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A92" s="52"/>
+      <c r="B92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="54"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="53"/>
+      <c r="M92" s="53"/>
+      <c r="N92" s="53"/>
+      <c r="O92" s="53"/>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A93" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D93" s="53"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53"/>
+      <c r="H93" s="53"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1">
+        <v>4.9920514192076698E-4</v>
+      </c>
+      <c r="K93" s="1">
+        <v>4.9920514192076698E-4</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
+        <v>109.501348528158</v>
+      </c>
+      <c r="N93" s="1">
+        <v>3.3446840501390498</v>
+      </c>
+      <c r="O93" s="3">
+        <v>7.0143959578357298E-2</v>
+      </c>
+      <c r="P93" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R93" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S93" s="53"/>
+      <c r="T93" s="53"/>
+      <c r="U93" s="53"/>
+      <c r="V93" s="53"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="45">
+        <v>3.8010990000000001E-3</v>
+      </c>
+      <c r="Y93" s="45">
+        <v>1.2390599999999999E-3</v>
+      </c>
+      <c r="Z93" s="45">
+        <v>56.226177999999997</v>
+      </c>
+      <c r="AA93" s="45">
+        <v>3.0677270000000001</v>
+      </c>
+      <c r="AB93" s="45">
+        <v>3.3149447299999999E-3</v>
+      </c>
+      <c r="AC93" s="1"/>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A94" s="51"/>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1">
+        <v>4.3245963051368403E-3</v>
+      </c>
+      <c r="K94" s="1">
+        <v>4.3245963051368403E-3</v>
+      </c>
+      <c r="L94" s="1">
+        <v>1</v>
+      </c>
+      <c r="M94" s="1">
+        <v>14.3846326295774</v>
+      </c>
+      <c r="N94" s="1">
+        <v>28.974878402548999</v>
+      </c>
+      <c r="O94" s="4">
+        <v>8.7931651517614295E-5</v>
+      </c>
+      <c r="P94" s="51"/>
+      <c r="Q94" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R94" s="53"/>
+      <c r="S94" s="53"/>
+      <c r="T94" s="53"/>
+      <c r="U94" s="53"/>
+      <c r="V94" s="53"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="45">
+        <v>2.6998579999999999E-3</v>
+      </c>
+      <c r="Y94" s="45">
+        <v>1.7967930000000001E-3</v>
+      </c>
+      <c r="Z94" s="45">
+        <v>54.259734999999999</v>
+      </c>
+      <c r="AA94" s="45">
+        <v>1.502599</v>
+      </c>
+      <c r="AB94" s="45">
+        <v>0.13874061215931999</v>
+      </c>
+      <c r="AC94" s="1"/>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A95" s="51"/>
+      <c r="B95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="53"/>
+      <c r="D95" s="53"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53"/>
+      <c r="H95" s="53"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="5">
+        <v>4.4673218852987901E-5</v>
+      </c>
+      <c r="K95" s="5">
+        <v>4.4673218852987901E-5</v>
+      </c>
+      <c r="L95" s="1">
+        <v>1</v>
+      </c>
+      <c r="M95" s="1">
+        <v>109.203333776652</v>
+      </c>
+      <c r="N95" s="1">
+        <v>0.29931142534119798</v>
+      </c>
+      <c r="O95" s="1">
+        <v>0.58543070585289902</v>
+      </c>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R95" s="53"/>
+      <c r="S95" s="53"/>
+      <c r="T95" s="53"/>
+      <c r="U95" s="53"/>
+      <c r="V95" s="53"/>
+      <c r="W95" s="1"/>
+      <c r="X95" s="45">
+        <v>-1.146374E-2</v>
+      </c>
+      <c r="Y95" s="45">
+        <v>2.9301919999999999E-3</v>
+      </c>
+      <c r="Z95" s="45">
+        <v>12.84609</v>
+      </c>
+      <c r="AA95" s="45">
+        <v>-3.9122840000000001</v>
+      </c>
+      <c r="AB95" s="45">
+        <v>1.8229571331547E-3</v>
+      </c>
+      <c r="AC95" s="1"/>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A96" s="52"/>
+      <c r="B96" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C96" s="53"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1">
+        <v>2.5092673060789E-4</v>
+      </c>
+      <c r="K96" s="1">
+        <v>1.25463365303945E-4</v>
+      </c>
+      <c r="L96" s="1">
+        <v>2</v>
+      </c>
+      <c r="M96" s="1">
+        <v>109.245496603218</v>
+      </c>
+      <c r="N96" s="1">
+        <v>0.84060696008511204</v>
+      </c>
+      <c r="O96" s="1">
+        <v>0.43421981831232398</v>
+      </c>
+      <c r="P96" s="52"/>
+      <c r="Q96" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R96" s="53"/>
+      <c r="S96" s="53"/>
+      <c r="T96" s="53"/>
+      <c r="U96" s="53"/>
+      <c r="V96" s="53"/>
+      <c r="W96" s="1"/>
+      <c r="X96" s="45">
+        <v>-1.288595E-2</v>
+      </c>
+      <c r="Y96" s="45">
+        <v>2.4782379999999998E-3</v>
+      </c>
+      <c r="Z96" s="45">
+        <v>14.11434</v>
+      </c>
+      <c r="AA96" s="45">
+        <v>-5.1996440000000002</v>
+      </c>
+      <c r="AB96" s="45">
+        <v>1.3118094177569999E-4</v>
+      </c>
+      <c r="AC96" s="1"/>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A97" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="1">
+        <v>24482.794046813899</v>
+      </c>
+      <c r="D97" s="1">
+        <v>24482.794046813899</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
+      </c>
+      <c r="F97" s="1">
+        <v>54.370003117736701</v>
+      </c>
+      <c r="G97" s="1">
+        <v>850.32626657220897</v>
+      </c>
+      <c r="H97" s="4">
+        <v>7.05414701429731E-35</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K97" s="53"/>
+      <c r="L97" s="53"/>
+      <c r="M97" s="53"/>
+      <c r="N97" s="53"/>
+      <c r="O97" s="53"/>
+      <c r="P97" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R97" s="1">
+        <v>16.64274</v>
+      </c>
+      <c r="S97" s="1">
+        <v>1.1608540000000001</v>
+      </c>
+      <c r="T97" s="1">
+        <v>4.8165345999999998</v>
+      </c>
+      <c r="U97" s="1">
+        <v>14.33663</v>
+      </c>
+      <c r="V97" s="2">
+        <v>3.9052140000000001E-5</v>
+      </c>
+      <c r="W97" s="1"/>
+      <c r="X97" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y97" s="53"/>
+      <c r="Z97" s="53"/>
+      <c r="AA97" s="53"/>
+      <c r="AB97" s="53"/>
+      <c r="AC97" s="1"/>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A98" s="51"/>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="1">
+        <v>151.803221723246</v>
+      </c>
+      <c r="D98" s="1">
+        <v>151.803221723246</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1">
+        <v>12.607670268557801</v>
+      </c>
+      <c r="G98" s="1">
+        <v>5.2723666479708697</v>
+      </c>
+      <c r="H98" s="2">
+        <v>3.9509565365961799E-2</v>
+      </c>
+      <c r="I98" s="1"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
+      <c r="N98" s="53"/>
+      <c r="O98" s="53"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R98" s="1">
+        <v>19.986529999999998</v>
+      </c>
+      <c r="S98" s="1">
+        <v>0.71962550000000003</v>
+      </c>
+      <c r="T98" s="1">
+        <v>35.025179999999999</v>
+      </c>
+      <c r="U98" s="1">
+        <v>27.773520000000001</v>
+      </c>
+      <c r="V98" s="2">
+        <v>1.9085240000000001E-25</v>
+      </c>
+      <c r="W98" s="1"/>
+      <c r="X98" s="53"/>
+      <c r="Y98" s="53"/>
+      <c r="Z98" s="53"/>
+      <c r="AA98" s="53"/>
+      <c r="AB98" s="53"/>
+      <c r="AC98" s="1"/>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A99" s="51"/>
+      <c r="B99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1">
+        <v>191.244540460943</v>
+      </c>
+      <c r="D99" s="1">
+        <v>191.244540460943</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1">
+        <v>54.370003120174303</v>
+      </c>
+      <c r="G99" s="1">
+        <v>6.64222620104238</v>
+      </c>
+      <c r="H99" s="2">
+        <v>1.2703272318058401E-2</v>
+      </c>
+      <c r="I99" s="1"/>
+      <c r="J99" s="53"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="53"/>
+      <c r="M99" s="53"/>
+      <c r="N99" s="53"/>
+      <c r="O99" s="53"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R99" s="1">
+        <v>-4.4803540000000002</v>
+      </c>
+      <c r="S99" s="1">
+        <v>1.6178699999999999</v>
+      </c>
+      <c r="T99" s="1">
+        <v>15.836600000000001</v>
+      </c>
+      <c r="U99" s="1">
+        <v>-2.7692920000000001</v>
+      </c>
+      <c r="V99" s="2">
+        <v>1.377838E-2</v>
+      </c>
+      <c r="W99" s="1"/>
+      <c r="X99" s="53"/>
+      <c r="Y99" s="53"/>
+      <c r="Z99" s="53"/>
+      <c r="AA99" s="53"/>
+      <c r="AB99" s="53"/>
+      <c r="AC99" s="1"/>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A100" s="52"/>
+      <c r="B100" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="54"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="53"/>
+      <c r="K100" s="53"/>
+      <c r="L100" s="53"/>
+      <c r="M100" s="53"/>
+      <c r="N100" s="53"/>
+      <c r="O100" s="53"/>
+      <c r="P100" s="52"/>
+      <c r="Q100" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R100" s="1">
+        <v>-0.82880399999999999</v>
+      </c>
+      <c r="S100" s="1">
+        <v>1.112787</v>
+      </c>
+      <c r="T100" s="1">
+        <v>15.309240000000001</v>
+      </c>
+      <c r="U100" s="1">
+        <v>-0.74480009999999996</v>
+      </c>
+      <c r="V100" s="1">
+        <v>0.46767300000000001</v>
+      </c>
+      <c r="W100" s="1"/>
+      <c r="X100" s="53"/>
+      <c r="Y100" s="53"/>
+      <c r="Z100" s="53"/>
+      <c r="AA100" s="53"/>
+      <c r="AB100" s="53"/>
+      <c r="AC100" s="1"/>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A101" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="D101" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1">
+        <v>71.888440000000003</v>
+      </c>
+      <c r="G101" s="1">
+        <v>167.3449876</v>
+      </c>
+      <c r="H101" s="4">
+        <v>1.898803E-20</v>
+      </c>
+      <c r="I101" s="1"/>
+      <c r="J101" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K101" s="53"/>
+      <c r="L101" s="53"/>
+      <c r="M101" s="53"/>
+      <c r="N101" s="53"/>
+      <c r="O101" s="53"/>
+      <c r="P101" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R101" s="45">
+        <v>264.8</v>
+      </c>
+      <c r="S101" s="45">
+        <v>32.234110000000001</v>
+      </c>
+      <c r="T101" s="45">
+        <v>30.811264000000001</v>
+      </c>
+      <c r="U101" s="45">
+        <v>8.2149009999999993</v>
+      </c>
+      <c r="V101" s="45">
+        <v>2.9384279999999999E-9</v>
+      </c>
+      <c r="W101" s="1"/>
+      <c r="X101" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y101" s="53"/>
+      <c r="Z101" s="53"/>
+      <c r="AA101" s="53"/>
+      <c r="AB101" s="53"/>
+      <c r="AC101" s="1"/>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A102" s="51"/>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="1">
+        <v>50157.928</v>
+      </c>
+      <c r="D102" s="1">
+        <v>50157.928</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1">
+        <v>17.04102</v>
+      </c>
+      <c r="G102" s="1">
+        <v>1.3588785000000001</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0.2597892</v>
+      </c>
+      <c r="I102" s="1"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
+      <c r="M102" s="53"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="53"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R102" s="45">
+        <v>249.71430000000001</v>
+      </c>
+      <c r="S102" s="45">
+        <v>24.47692</v>
+      </c>
+      <c r="T102" s="45">
+        <v>40.626759999999997</v>
+      </c>
+      <c r="U102" s="45">
+        <v>10.202030000000001</v>
+      </c>
+      <c r="V102" s="45">
+        <v>9.0369680000000005E-13</v>
+      </c>
+      <c r="W102" s="1"/>
+      <c r="X102" s="53"/>
+      <c r="Y102" s="53"/>
+      <c r="Z102" s="53"/>
+      <c r="AA102" s="53"/>
+      <c r="AB102" s="53"/>
+      <c r="AC102" s="1"/>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A103" s="51"/>
+      <c r="B103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
+        <v>5310.1710000000003</v>
+      </c>
+      <c r="D103" s="1">
+        <v>5310.1710000000003</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1">
+        <v>71.888440000000003</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.1438632</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0.7055884</v>
+      </c>
+      <c r="I103" s="1"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="53"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="53"/>
+      <c r="N103" s="53"/>
+      <c r="O103" s="53"/>
+      <c r="P103" s="51"/>
+      <c r="Q103" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R103" s="45">
+        <v>43.209679999999999</v>
+      </c>
+      <c r="S103" s="45">
+        <v>56.537500000000001</v>
+      </c>
+      <c r="T103" s="45">
+        <v>16.96773</v>
+      </c>
+      <c r="U103" s="45">
+        <v>0.7642658</v>
+      </c>
+      <c r="V103" s="45">
+        <v>0.45520664523399601</v>
+      </c>
+      <c r="W103" s="1"/>
+      <c r="X103" s="53"/>
+      <c r="Y103" s="53"/>
+      <c r="Z103" s="53"/>
+      <c r="AA103" s="53"/>
+      <c r="AB103" s="53"/>
+      <c r="AC103" s="1"/>
+    </row>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A104" s="52"/>
+      <c r="B104" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="54"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="53"/>
+      <c r="L104" s="53"/>
+      <c r="M104" s="53"/>
+      <c r="N104" s="53"/>
+      <c r="O104" s="53"/>
+      <c r="P104" s="52"/>
+      <c r="Q104" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R104" s="45">
+        <v>32.259779999999999</v>
+      </c>
+      <c r="S104" s="45">
+        <v>15.415459999999999</v>
+      </c>
+      <c r="T104" s="45">
+        <v>17.28622</v>
+      </c>
+      <c r="U104" s="45">
+        <v>2.0926900000000002</v>
+      </c>
+      <c r="V104" s="45">
+        <v>5.14251187538E-2</v>
+      </c>
+      <c r="W104" s="1"/>
+      <c r="X104" s="53"/>
+      <c r="Y104" s="53"/>
+      <c r="Z104" s="53"/>
+      <c r="AA104" s="53"/>
+      <c r="AB104" s="53"/>
+      <c r="AC104" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="104">
+    <mergeCell ref="X1:AC1"/>
+    <mergeCell ref="P69:P72"/>
+    <mergeCell ref="P7:P10"/>
+    <mergeCell ref="X7:AB10"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P81:P84"/>
+    <mergeCell ref="P73:P76"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="P65:P68"/>
+    <mergeCell ref="X35:AB38"/>
+    <mergeCell ref="P27:P30"/>
+    <mergeCell ref="R27:V30"/>
+    <mergeCell ref="P85:P88"/>
+    <mergeCell ref="X85:AB88"/>
+    <mergeCell ref="P11:P14"/>
+    <mergeCell ref="P15:P18"/>
+    <mergeCell ref="P19:P22"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="P77:P80"/>
+    <mergeCell ref="R77:V80"/>
+    <mergeCell ref="P23:P26"/>
+    <mergeCell ref="R23:V26"/>
+    <mergeCell ref="P93:P96"/>
+    <mergeCell ref="R93:V96"/>
+    <mergeCell ref="X81:AB84"/>
+    <mergeCell ref="X31:AB34"/>
+    <mergeCell ref="P35:P38"/>
+    <mergeCell ref="X43:AB46"/>
+    <mergeCell ref="P97:P100"/>
+    <mergeCell ref="X97:AB100"/>
+    <mergeCell ref="P39:P42"/>
+    <mergeCell ref="R39:V42"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="J51:O54"/>
+    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="P47:P50"/>
+    <mergeCell ref="X47:AB50"/>
+    <mergeCell ref="P51:P54"/>
+    <mergeCell ref="X51:AB54"/>
+    <mergeCell ref="P101:P104"/>
+    <mergeCell ref="X101:AB104"/>
+    <mergeCell ref="P43:P46"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="J43:O46"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="J47:O50"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="J97:O100"/>
+    <mergeCell ref="C100:H100"/>
+    <mergeCell ref="A101:A104"/>
+    <mergeCell ref="J101:O104"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="A89:A92"/>
+    <mergeCell ref="J89:O92"/>
+    <mergeCell ref="C92:H92"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="C93:H96"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="C39:H42"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="J85:O88"/>
+    <mergeCell ref="C88:H88"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="J35:O38"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="A81:A84"/>
+    <mergeCell ref="J81:O84"/>
+    <mergeCell ref="C84:H84"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="C27:H30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="J31:O34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="C77:H80"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:H26"/>
+    <mergeCell ref="A69:A72"/>
+    <mergeCell ref="C72:H72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A57:A60"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="C64:H64"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="J7:O10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDA28D4-5A8D-4B82-B1F2-D70FA6918129}">
+  <dimension ref="A103:A110"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="6"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5A7F3D-2808-4753-A174-BBEAF62E0D16}">
   <dimension ref="A1:P146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1470,24 +7975,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="54">
+      <c r="C1" s="55">
         <v>2021</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="54">
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="55">
         <v>2022</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="57"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1678,12 +8183,12 @@
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -1844,12 +8349,12 @@
       <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -1976,12 +8481,12 @@
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="1"/>
       <c r="J14" s="53"/>
       <c r="K14" s="53"/>
@@ -2095,12 +8600,12 @@
       <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
       <c r="I18" s="1"/>
       <c r="J18" s="53"/>
       <c r="K18" s="53"/>
@@ -2249,12 +8754,12 @@
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -2415,12 +8920,12 @@
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -2581,12 +9086,12 @@
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -2747,12 +9252,12 @@
       <c r="B34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -2913,12 +9418,12 @@
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -3079,12 +9584,12 @@
       <c r="B42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -3245,12 +9750,12 @@
       <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -3411,12 +9916,12 @@
       <c r="B50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -3711,12 +10216,12 @@
       <c r="B58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="57"/>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -3843,12 +10348,12 @@
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="57"/>
-      <c r="D62" s="57"/>
-      <c r="E62" s="57"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
       <c r="I62" s="1"/>
       <c r="J62" s="53"/>
       <c r="K62" s="53"/>
@@ -4227,12 +10732,12 @@
       <c r="B74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
       <c r="I74" s="1"/>
       <c r="J74" s="53"/>
       <c r="K74" s="53"/>
@@ -4479,12 +10984,12 @@
       <c r="B82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="54"/>
       <c r="I82" s="1"/>
       <c r="J82" s="53"/>
       <c r="K82" s="53"/>
@@ -4731,12 +11236,12 @@
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="57"/>
-      <c r="D90" s="57"/>
-      <c r="E90" s="57"/>
-      <c r="F90" s="57"/>
-      <c r="G90" s="57"/>
-      <c r="H90" s="57"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="54"/>
       <c r="I90" s="1"/>
       <c r="J90" s="53"/>
       <c r="K90" s="53"/>
@@ -4851,12 +11356,12 @@
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="57"/>
-      <c r="D94" s="57"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="57"/>
-      <c r="G94" s="57"/>
-      <c r="H94" s="57"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="54"/>
       <c r="I94" s="1"/>
       <c r="J94" s="53"/>
       <c r="K94" s="53"/>
@@ -4971,12 +11476,12 @@
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="57"/>
-      <c r="D98" s="57"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="57"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
       <c r="I98" s="1"/>
       <c r="J98" s="53"/>
       <c r="K98" s="53"/>
@@ -5091,12 +11596,12 @@
       <c r="B102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="54"/>
+      <c r="G102" s="54"/>
+      <c r="H102" s="54"/>
       <c r="I102" s="1"/>
       <c r="J102" s="53"/>
       <c r="K102" s="53"/>
@@ -5475,12 +11980,12 @@
       <c r="B114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="57"/>
-      <c r="D114" s="57"/>
-      <c r="E114" s="57"/>
-      <c r="F114" s="57"/>
-      <c r="G114" s="57"/>
-      <c r="H114" s="57"/>
+      <c r="C114" s="54"/>
+      <c r="D114" s="54"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="54"/>
+      <c r="H114" s="54"/>
       <c r="I114" s="1"/>
       <c r="J114" s="53"/>
       <c r="K114" s="53"/>
@@ -5595,12 +12100,12 @@
       <c r="B118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="57"/>
-      <c r="D118" s="57"/>
-      <c r="E118" s="57"/>
-      <c r="F118" s="57"/>
-      <c r="G118" s="57"/>
-      <c r="H118" s="57"/>
+      <c r="C118" s="54"/>
+      <c r="D118" s="54"/>
+      <c r="E118" s="54"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="54"/>
+      <c r="H118" s="54"/>
       <c r="I118" s="1"/>
       <c r="J118" s="53"/>
       <c r="K118" s="53"/>
@@ -5715,12 +12220,12 @@
       <c r="B122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="57"/>
-      <c r="D122" s="57"/>
-      <c r="E122" s="57"/>
-      <c r="F122" s="57"/>
-      <c r="G122" s="57"/>
-      <c r="H122" s="57"/>
+      <c r="C122" s="54"/>
+      <c r="D122" s="54"/>
+      <c r="E122" s="54"/>
+      <c r="F122" s="54"/>
+      <c r="G122" s="54"/>
+      <c r="H122" s="54"/>
       <c r="I122" s="1"/>
       <c r="J122" s="53"/>
       <c r="K122" s="53"/>
@@ -5835,12 +12340,12 @@
       <c r="B126" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="57"/>
-      <c r="D126" s="57"/>
-      <c r="E126" s="57"/>
-      <c r="F126" s="57"/>
-      <c r="G126" s="57"/>
-      <c r="H126" s="57"/>
+      <c r="C126" s="54"/>
+      <c r="D126" s="54"/>
+      <c r="E126" s="54"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="54"/>
+      <c r="H126" s="54"/>
       <c r="I126" s="1"/>
       <c r="J126" s="53"/>
       <c r="K126" s="53"/>
@@ -5955,12 +12460,12 @@
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C130" s="57"/>
-      <c r="D130" s="57"/>
-      <c r="E130" s="57"/>
-      <c r="F130" s="57"/>
-      <c r="G130" s="57"/>
-      <c r="H130" s="57"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="54"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
+      <c r="H130" s="54"/>
       <c r="I130" s="1"/>
       <c r="J130" s="53"/>
       <c r="K130" s="53"/>
@@ -6075,12 +12580,12 @@
       <c r="B134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="57"/>
-      <c r="D134" s="57"/>
-      <c r="E134" s="57"/>
-      <c r="F134" s="57"/>
-      <c r="G134" s="57"/>
-      <c r="H134" s="57"/>
+      <c r="C134" s="54"/>
+      <c r="D134" s="54"/>
+      <c r="E134" s="54"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="54"/>
+      <c r="H134" s="54"/>
       <c r="I134" s="1"/>
       <c r="J134" s="53"/>
       <c r="K134" s="53"/>
@@ -6195,12 +12700,12 @@
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="57"/>
-      <c r="D138" s="57"/>
-      <c r="E138" s="57"/>
-      <c r="F138" s="57"/>
-      <c r="G138" s="57"/>
-      <c r="H138" s="57"/>
+      <c r="C138" s="54"/>
+      <c r="D138" s="54"/>
+      <c r="E138" s="54"/>
+      <c r="F138" s="54"/>
+      <c r="G138" s="54"/>
+      <c r="H138" s="54"/>
       <c r="I138" s="1"/>
       <c r="J138" s="53"/>
       <c r="K138" s="53"/>
@@ -6230,68 +12735,14 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -6308,806 +12759,76 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B906023B-20D8-44CB-AA51-E431F089CEA5}">
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="58">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="K9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="25" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="58">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="59"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="59"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A18"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055498A3-AD3E-49E0-8565-96458FC406F5}">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="58">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="E4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="24"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="H6" s="27" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="26"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="J9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="25" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="58">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="59"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="26"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="59"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A18"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDA28D4-5A8D-4B82-B1F2-D70FA6918129}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9438BA21-D660-4EA0-B17F-FB6ACE0033C1}">
   <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7137,22 +12858,22 @@
       <c r="B1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="54">
+      <c r="C1" s="55">
         <v>2021</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="54">
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="55">
         <v>2022</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="57"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7219,13 +12940,13 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="64"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -7249,11 +12970,11 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="67"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="63"/>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -7277,11 +12998,11 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="67"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="63"/>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -7305,11 +13026,11 @@
         <v>0.1837454</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="70"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -7489,13 +13210,13 @@
         <v>0.35833147122850001</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -7519,11 +13240,11 @@
         <v>0.11792329999999999</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="67"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="63"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -7547,11 +13268,11 @@
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="67"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="63"/>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -7575,11 +13296,11 @@
         <v>1.280514E-6</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="70"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="66"/>
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -10706,56 +16427,840 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="I3:M6"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="I11:M14"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="C51:G54"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="C47:G50"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C75:G78"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="I71:M74"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="C67:G70"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="I103:M106"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="I107:M110"/>
     <mergeCell ref="A91:A94"/>
     <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
     <mergeCell ref="A79:A82"/>
     <mergeCell ref="C79:G82"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="I83:M86"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="I99:M102"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="I107:M110"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="I95:M98"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="I103:M106"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="C67:G70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="I71:M74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="I55:M58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="C47:G50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C51:G54"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="I3:M6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="I11:M14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B906023B-20D8-44CB-AA51-E431F089CEA5}">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="67">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="68"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="68"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="68"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="68"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="68"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="68"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="68"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="69"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="67">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="68"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="68"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="68"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="68"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="68"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="68"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055498A3-AD3E-49E0-8565-96458FC406F5}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="67">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="68"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="68"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="E4" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="68"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="24"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="68"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="H6" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="68"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="68"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="26"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="68"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="69"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="67">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="34"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="68"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="68"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="68"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="68"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="68"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="26"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="68"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="26"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1545" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C216709-DF06-4732-B60E-D9AA8A081B9C}"/>
+  <xr:revisionPtr revIDLastSave="1580" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF89575-650D-4FF2-9675-FC5C491FDF16}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults_ManuTraits" sheetId="5" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="156">
   <si>
     <t>Experiment</t>
   </si>
@@ -545,9 +545,6 @@
   </si>
   <si>
     <t>Avg weight of Seed Collected (wt divided by count)</t>
-  </si>
-  <si>
-    <t>Fitness - log</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1175,11 +1172,29 @@
     <xf numFmtId="11" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1191,9 +1206,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1235,15 +1247,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1251,9 +1254,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1275,10 +1275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1660,43 +1656,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="81">
+      <c r="C1" s="87">
         <v>2021</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="81">
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="87">
         <v>2022</v>
       </c>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
       <c r="P1" s="20"/>
-      <c r="Q1" s="97" t="s">
+      <c r="Q1" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="81" t="s">
+      <c r="R1" s="87" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="81" t="s">
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="83"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="89"/>
     </row>
     <row r="2" spans="1:29" s="55" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
@@ -1745,7 +1741,7 @@
       <c r="P2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="98"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="14" t="s">
         <v>112</v>
       </c>
@@ -1784,7 +1780,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="92" t="s">
         <v>141</v>
       </c>
       <c r="B3" s="51" t="s">
@@ -1809,15 +1805,15 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I3" s="51"/>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="87" t="s">
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="92" t="s">
         <v>141</v>
       </c>
       <c r="Q3" s="51" t="s">
@@ -1839,17 +1835,17 @@
         <v>0.35833147122850001</v>
       </c>
       <c r="W3" s="51"/>
-      <c r="X3" s="88" t="s">
+      <c r="X3" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="90"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
+      <c r="AB3" s="95"/>
       <c r="AC3" s="51"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1872,13 +1868,13 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="85"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="79"/>
       <c r="Q4" s="1" t="s">
         <v>107</v>
       </c>
@@ -1898,15 +1894,15 @@
         <v>0.11792329999999999</v>
       </c>
       <c r="W4" s="1"/>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="92"/>
-      <c r="Z4" s="92"/>
-      <c r="AA4" s="92"/>
-      <c r="AB4" s="93"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+      <c r="AA4" s="97"/>
+      <c r="AB4" s="98"/>
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="85"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1928,13 +1924,13 @@
       <c r="H5" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="85"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="79"/>
       <c r="Q5" s="1" t="s">
         <v>108</v>
       </c>
@@ -1954,32 +1950,32 @@
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="W5" s="1"/>
-      <c r="X5" s="91"/>
-      <c r="Y5" s="92"/>
-      <c r="Z5" s="92"/>
-      <c r="AA5" s="92"/>
-      <c r="AB5" s="93"/>
+      <c r="X5" s="96"/>
+      <c r="Y5" s="97"/>
+      <c r="Z5" s="97"/>
+      <c r="AA5" s="97"/>
+      <c r="AB5" s="98"/>
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="86"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="91"/>
       <c r="Q6" s="14" t="s">
         <v>109</v>
       </c>
@@ -1999,15 +1995,15 @@
         <v>1.280514E-6</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="94"/>
-      <c r="Y6" s="95"/>
-      <c r="Z6" s="95"/>
-      <c r="AA6" s="95"/>
-      <c r="AB6" s="96"/>
+      <c r="X6" s="99"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="100"/>
+      <c r="AA6" s="100"/>
+      <c r="AB6" s="101"/>
       <c r="AC6" s="14"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="90" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="51" t="s">
@@ -2050,7 +2046,7 @@
       <c r="O7" s="52">
         <v>7.9655542624253594E-15</v>
       </c>
-      <c r="P7" s="87" t="s">
+      <c r="P7" s="92" t="s">
         <v>17</v>
       </c>
       <c r="Q7" s="51" t="s">
@@ -2090,7 +2086,7 @@
       <c r="AC7" s="51"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2131,7 +2127,7 @@
       <c r="O8" s="2">
         <v>2.49480079562349E-3</v>
       </c>
-      <c r="P8" s="85"/>
+      <c r="P8" s="79"/>
       <c r="Q8" s="1" t="s">
         <v>107</v>
       </c>
@@ -2169,7 +2165,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="85"/>
+      <c r="A9" s="79"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2210,7 +2206,7 @@
       <c r="O9" s="2">
         <v>5.9886663878832899E-3</v>
       </c>
-      <c r="P9" s="85"/>
+      <c r="P9" s="79"/>
       <c r="Q9" s="1" t="s">
         <v>108</v>
       </c>
@@ -2248,16 +2244,16 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+      <c r="A10" s="91"/>
       <c r="B10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14">
         <v>3.4846897009296399E-3</v>
@@ -2277,7 +2273,7 @@
       <c r="O10" s="14">
         <v>0.23519968422781001</v>
       </c>
-      <c r="P10" s="99"/>
+      <c r="P10" s="80"/>
       <c r="Q10" s="14" t="s">
         <v>109</v>
       </c>
@@ -2315,20 +2311,20 @@
       <c r="AC10" s="14"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="79" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51">
         <v>2.20343269025562E-2</v>
@@ -2348,19 +2344,19 @@
       <c r="O11" s="53">
         <v>1.20915323151938E-2</v>
       </c>
-      <c r="P11" s="87" t="s">
+      <c r="P11" s="92" t="s">
         <v>147</v>
       </c>
       <c r="Q11" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R11" s="79" t="s">
+      <c r="R11" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="S11" s="79"/>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79"/>
-      <c r="V11" s="79"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
       <c r="W11" s="51"/>
       <c r="X11" s="58">
         <v>-1.7478199999999999E-2</v>
@@ -2380,16 +2376,16 @@
       <c r="AC11" s="51"/>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="85"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>2.98483856205864E-2</v>
@@ -2409,15 +2405,15 @@
       <c r="O12" s="2">
         <v>1.05420955332634E-2</v>
       </c>
-      <c r="P12" s="85"/>
+      <c r="P12" s="79"/>
       <c r="Q12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="79"/>
-      <c r="V12" s="79"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
       <c r="W12" s="1"/>
       <c r="X12" s="45">
         <v>-2.3552070000000001E-2</v>
@@ -2437,16 +2433,16 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>1.15818782663304E-3</v>
@@ -2466,15 +2462,15 @@
       <c r="O13" s="1">
         <v>0.55966903975183102</v>
       </c>
-      <c r="P13" s="85"/>
+      <c r="P13" s="79"/>
       <c r="Q13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R13" s="79"/>
-      <c r="S13" s="79"/>
-      <c r="T13" s="79"/>
-      <c r="U13" s="79"/>
-      <c r="V13" s="79"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
       <c r="W13" s="1"/>
       <c r="X13" s="45">
         <v>-2.6797439999999999E-2</v>
@@ -2494,16 +2490,16 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
+      <c r="A14" s="91"/>
       <c r="B14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14">
         <v>2.0797141885883202E-3</v>
@@ -2523,15 +2519,15 @@
       <c r="O14" s="14">
         <v>0.73598934665486404</v>
       </c>
-      <c r="P14" s="86"/>
+      <c r="P14" s="91"/>
       <c r="Q14" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R14" s="80"/>
-      <c r="S14" s="80"/>
-      <c r="T14" s="80"/>
-      <c r="U14" s="80"/>
-      <c r="V14" s="80"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
+      <c r="T14" s="84"/>
+      <c r="U14" s="84"/>
+      <c r="V14" s="84"/>
       <c r="W14" s="14"/>
       <c r="X14" s="61">
         <v>-3.3645590000000003E-2</v>
@@ -2551,7 +2547,7 @@
       <c r="AC14" s="14"/>
     </row>
     <row r="15" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="90" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -2594,7 +2590,7 @@
       <c r="O15" s="63">
         <v>2.5984972877347698E-9</v>
       </c>
-      <c r="P15" s="84" t="s">
+      <c r="P15" s="90" t="s">
         <v>15</v>
       </c>
       <c r="Q15" s="13" t="s">
@@ -2636,7 +2632,7 @@
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -2677,7 +2673,7 @@
       <c r="O16" s="4">
         <v>2.3925201381821199E-8</v>
       </c>
-      <c r="P16" s="85"/>
+      <c r="P16" s="79"/>
       <c r="Q16" s="1" t="s">
         <v>107</v>
       </c>
@@ -2717,7 +2713,7 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2758,7 +2754,7 @@
       <c r="O17" s="3">
         <v>0.107275586121823</v>
       </c>
-      <c r="P17" s="85"/>
+      <c r="P17" s="79"/>
       <c r="Q17" s="1" t="s">
         <v>108</v>
       </c>
@@ -2798,16 +2794,16 @@
       </c>
     </row>
     <row r="18" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14">
         <v>4.9184876384352101E-2</v>
@@ -2827,7 +2823,7 @@
       <c r="O18" s="60">
         <v>1.9087014953066299E-2</v>
       </c>
-      <c r="P18" s="86"/>
+      <c r="P18" s="91"/>
       <c r="Q18" s="14" t="s">
         <v>109</v>
       </c>
@@ -2867,20 +2863,20 @@
       </c>
     </row>
     <row r="19" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="90" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13">
         <v>1.4241127553301099E-4</v>
@@ -2900,19 +2896,19 @@
       <c r="O19" s="13">
         <v>0.82529746395827397</v>
       </c>
-      <c r="P19" s="84" t="s">
+      <c r="P19" s="90" t="s">
         <v>29</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R19" s="100" t="s">
+      <c r="R19" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="S19" s="100"/>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="100"/>
+      <c r="S19" s="83"/>
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="83"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13">
         <v>-1.7348269999999999E-2</v>
@@ -2932,16 +2928,16 @@
       <c r="AC19" s="13"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="85"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>4.6725153189010001E-2</v>
@@ -2961,15 +2957,15 @@
       <c r="O20" s="2">
         <v>1.3790795758093499E-3</v>
       </c>
-      <c r="P20" s="85"/>
+      <c r="P20" s="79"/>
       <c r="Q20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="79"/>
-      <c r="U20" s="79"/>
-      <c r="V20" s="79"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
         <v>1.2575930000000001E-2</v>
@@ -2989,16 +2985,16 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2.8302586845141399E-2</v>
@@ -3018,15 +3014,15 @@
       <c r="O21" s="2">
         <v>2.3248319291652099E-3</v>
       </c>
-      <c r="P21" s="85"/>
+      <c r="P21" s="79"/>
       <c r="Q21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R21" s="79"/>
-      <c r="S21" s="79"/>
-      <c r="T21" s="79"/>
-      <c r="U21" s="79"/>
-      <c r="V21" s="79"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
         <v>3.5116069999999999E-2</v>
@@ -3046,16 +3042,16 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="86"/>
+      <c r="A22" s="91"/>
       <c r="B22" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14">
         <v>6.3796317056246301E-3</v>
@@ -3075,15 +3071,15 @@
       <c r="O22" s="14">
         <v>0.33767591593294399</v>
       </c>
-      <c r="P22" s="86"/>
+      <c r="P22" s="91"/>
       <c r="Q22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R22" s="80"/>
-      <c r="S22" s="80"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="84"/>
+      <c r="U22" s="84"/>
+      <c r="V22" s="84"/>
       <c r="W22" s="14"/>
       <c r="X22" s="14">
         <v>6.7801109999999998E-2</v>
@@ -3102,8 +3098,8 @@
       </c>
       <c r="AC22" s="14"/>
     </row>
-    <row r="23" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84" t="s">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A23" s="90" t="s">
         <v>151</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3128,14 +3124,14 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="100" t="s">
+      <c r="J23" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="100"/>
-      <c r="N23" s="100"/>
-      <c r="O23" s="100"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
         <v>106</v>
@@ -3156,17 +3152,17 @@
         <v>2.9384279999999999E-9</v>
       </c>
       <c r="W23" s="1"/>
-      <c r="X23" s="100" t="s">
+      <c r="X23" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y23" s="100"/>
-      <c r="Z23" s="100"/>
-      <c r="AA23" s="100"/>
-      <c r="AB23" s="100"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="83"/>
+      <c r="AB23" s="83"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A24" s="79"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3189,12 +3185,12 @@
         <v>0.2597892</v>
       </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
         <v>107</v>
@@ -3215,15 +3211,15 @@
         <v>9.0369680000000005E-13</v>
       </c>
       <c r="W24" s="1"/>
-      <c r="X24" s="79"/>
-      <c r="Y24" s="79"/>
-      <c r="Z24" s="79"/>
-      <c r="AA24" s="79"/>
-      <c r="AB24" s="79"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A25" s="79"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -3246,12 +3242,12 @@
         <v>0.7055884</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
         <v>108</v>
@@ -3272,31 +3268,31 @@
         <v>0.45520664523399601</v>
       </c>
       <c r="W25" s="1"/>
-      <c r="X25" s="79"/>
-      <c r="Y25" s="79"/>
-      <c r="Z25" s="79"/>
-      <c r="AA25" s="79"/>
-      <c r="AB25" s="79"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" s="113" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
+    <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="91"/>
       <c r="B26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="84"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="14" t="s">
         <v>109</v>
@@ -3317,15 +3313,15 @@
         <v>5.14251187538E-2</v>
       </c>
       <c r="W26" s="14"/>
-      <c r="X26" s="80"/>
-      <c r="Y26" s="80"/>
-      <c r="Z26" s="80"/>
-      <c r="AA26" s="80"/>
-      <c r="AB26" s="80"/>
+      <c r="X26" s="84"/>
+      <c r="Y26" s="84"/>
+      <c r="Z26" s="84"/>
+      <c r="AA26" s="84"/>
+      <c r="AB26" s="84"/>
       <c r="AC26" s="14"/>
     </row>
-    <row r="27" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="85" t="s">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A27" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="51" t="s">
@@ -3350,14 +3346,14 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I27" s="51"/>
-      <c r="J27" s="114" t="s">
+      <c r="J27" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="81"/>
       <c r="P27" s="51"/>
       <c r="Q27" s="51" t="s">
         <v>106</v>
@@ -3378,17 +3374,17 @@
         <v>0.30992960000000003</v>
       </c>
       <c r="W27" s="51"/>
-      <c r="X27" s="114" t="s">
+      <c r="X27" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="Y27" s="114"/>
-      <c r="Z27" s="114"/>
-      <c r="AA27" s="114"/>
-      <c r="AB27" s="114"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="81"/>
+      <c r="AA27" s="81"/>
+      <c r="AB27" s="81"/>
       <c r="AC27" s="51"/>
     </row>
-    <row r="28" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="79"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -3411,12 +3407,12 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I28" s="1"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
         <v>107</v>
@@ -3437,15 +3433,15 @@
         <v>5.4385229999999998E-11</v>
       </c>
       <c r="W28" s="1"/>
-      <c r="X28" s="79"/>
-      <c r="Y28" s="79"/>
-      <c r="Z28" s="79"/>
-      <c r="AA28" s="79"/>
-      <c r="AB28" s="79"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A29" s="79"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -3468,12 +3464,12 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I29" s="1"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
+      <c r="J29" s="82"/>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="82"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>108</v>
@@ -3494,31 +3490,31 @@
         <v>1.343811E-5</v>
       </c>
       <c r="W29" s="1"/>
-      <c r="X29" s="79"/>
-      <c r="Y29" s="79"/>
-      <c r="Z29" s="79"/>
-      <c r="AA29" s="79"/>
-      <c r="AB29" s="79"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" s="113" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
+    <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="80"/>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
         <v>109</v>
@@ -3539,235 +3535,235 @@
         <v>0.56057069999999998</v>
       </c>
       <c r="W30" s="1"/>
-      <c r="X30" s="79"/>
-      <c r="Y30" s="79"/>
-      <c r="Z30" s="79"/>
-      <c r="AA30" s="79"/>
-      <c r="AB30" s="79"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84" t="s">
-        <v>156</v>
+      <c r="A31" s="90" t="s">
+        <v>25</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="13">
-        <v>11.200752100000001</v>
-      </c>
-      <c r="D31" s="13">
-        <v>11.200752100000001</v>
-      </c>
-      <c r="E31" s="13">
-        <v>1</v>
-      </c>
-      <c r="F31" s="13">
-        <v>51.667794999999998</v>
-      </c>
-      <c r="G31" s="13">
-        <v>471.893664</v>
-      </c>
-      <c r="H31" s="63">
-        <v>1.209274E-27</v>
+      <c r="C31" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="D31" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>69.360025998764399</v>
+      </c>
+      <c r="G31" s="1">
+        <v>150.637001976226</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4.7200869189182898E-19</v>
       </c>
       <c r="I31" s="13"/>
-      <c r="J31" s="100" t="s">
+      <c r="J31" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K31" s="100"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="100"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="84" t="s">
-        <v>156</v>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="90" t="s">
+        <v>25</v>
       </c>
       <c r="Q31" s="13" t="s">
         <v>106</v>
       </c>
       <c r="R31" s="13">
-        <v>0.29653109999999999</v>
+        <v>13476.24</v>
       </c>
       <c r="S31" s="13">
-        <v>3.0081920000000002E-2</v>
+        <v>1799.34</v>
       </c>
       <c r="T31" s="13">
-        <v>12.984576000000001</v>
+        <v>30.823322999999998</v>
       </c>
       <c r="U31" s="13">
-        <v>9.8574540000000006</v>
-      </c>
-      <c r="V31" s="64">
-        <v>2.1465810000000001E-7</v>
+        <v>7.4895490000000002</v>
+      </c>
+      <c r="V31" s="2">
+        <v>2.0108260000000001E-8</v>
       </c>
       <c r="W31" s="13"/>
-      <c r="X31" s="100" t="s">
+      <c r="X31" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y31" s="100"/>
-      <c r="Z31" s="100"/>
-      <c r="AA31" s="100"/>
-      <c r="AB31" s="100"/>
+      <c r="Y31" s="83"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="83"/>
+      <c r="AB31" s="83"/>
       <c r="AC31" s="13"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>0.12802530000000001</v>
+        <v>11545764.943964699</v>
       </c>
       <c r="D32" s="1">
-        <v>0.12802530000000001</v>
+        <v>11545764.943964699</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>6.2246040000000002</v>
+        <v>16.5068331927068</v>
       </c>
       <c r="G32" s="1">
-        <v>5.3937730000000004</v>
-      </c>
-      <c r="H32" s="4">
-        <v>5.7713939999999998E-2</v>
+        <v>7.9675190272952195E-2</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.78124664232875995</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="85"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="82"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="79"/>
       <c r="Q32" s="1" t="s">
         <v>107</v>
       </c>
       <c r="R32" s="1">
-        <v>0.48443409999999998</v>
+        <v>17505.57</v>
       </c>
       <c r="S32" s="1">
-        <v>1.925058E-2</v>
+        <v>1724.873</v>
       </c>
       <c r="T32" s="1">
-        <v>33.275270999999996</v>
+        <v>38.6235</v>
       </c>
       <c r="U32" s="1">
-        <v>25.164650000000002</v>
+        <v>10.148899999999999</v>
       </c>
       <c r="V32" s="2">
-        <v>3.0964249999999998E-23</v>
+        <v>1.8776299999999999E-12</v>
       </c>
       <c r="W32" s="1"/>
-      <c r="X32" s="79"/>
-      <c r="Y32" s="79"/>
-      <c r="Z32" s="79"/>
-      <c r="AA32" s="79"/>
-      <c r="AB32" s="79"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="1">
-        <v>0.70815150000000004</v>
+        <v>366508256.45689797</v>
       </c>
       <c r="D33" s="1">
-        <v>0.70815150000000004</v>
+        <v>366508256.45689797</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>51.667794999999998</v>
+        <v>69.360026001368695</v>
       </c>
       <c r="G33" s="1">
-        <v>29.834802</v>
-      </c>
-      <c r="H33" s="4">
-        <v>1.363103E-6</v>
+        <v>2.52920574873438</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0.116304482817742</v>
       </c>
       <c r="I33" s="1"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="85"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="79"/>
       <c r="Q33" s="1" t="s">
         <v>108</v>
       </c>
       <c r="R33" s="1">
-        <v>-4.9176770000000002E-2</v>
+        <v>-2538.4699999999998</v>
       </c>
       <c r="S33" s="1">
-        <v>3.2182200000000001E-2</v>
+        <v>3439.5279999999998</v>
       </c>
       <c r="T33" s="1">
-        <v>6.754302</v>
+        <v>16.46264</v>
       </c>
       <c r="U33" s="1">
-        <v>-1.5280739999999999</v>
+        <v>-0.73802849999999998</v>
       </c>
       <c r="V33" s="1">
-        <v>0.17187649999999999</v>
+        <v>0.47088761094748599</v>
       </c>
       <c r="W33" s="1"/>
-      <c r="X33" s="79"/>
-      <c r="Y33" s="79"/>
-      <c r="Z33" s="79"/>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="79"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
       <c r="AC33" s="1"/>
     </row>
     <row r="34" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
+      <c r="A34" s="91"/>
       <c r="B34" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="101"/>
-      <c r="H34" s="101"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="86"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="84"/>
+      <c r="N34" s="84"/>
+      <c r="O34" s="84"/>
+      <c r="P34" s="91"/>
       <c r="Q34" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R34" s="14">
-        <v>0.14682600000000001</v>
-      </c>
-      <c r="S34" s="14">
-        <v>2.4250879999999999E-2</v>
-      </c>
-      <c r="T34" s="14">
-        <v>6.7890449999999998</v>
-      </c>
-      <c r="U34" s="14">
-        <v>6.0544589999999996</v>
-      </c>
-      <c r="V34" s="60">
-        <v>5.7776140000000001E-4</v>
+      <c r="R34" s="1">
+        <v>1460.6780000000001</v>
+      </c>
+      <c r="S34" s="1">
+        <v>724.09180000000003</v>
+      </c>
+      <c r="T34" s="1">
+        <v>16.867750000000001</v>
+      </c>
+      <c r="U34" s="1">
+        <v>2.0172560000000002</v>
+      </c>
+      <c r="V34" s="2">
+        <v>5.9871192312700001E-2</v>
       </c>
       <c r="W34" s="14"/>
-      <c r="X34" s="80"/>
-      <c r="Y34" s="80"/>
-      <c r="Z34" s="80"/>
-      <c r="AA34" s="80"/>
-      <c r="AB34" s="80"/>
+      <c r="X34" s="84"/>
+      <c r="Y34" s="84"/>
+      <c r="Z34" s="84"/>
+      <c r="AA34" s="84"/>
+      <c r="AB34" s="84"/>
       <c r="AC34" s="14"/>
     </row>
     <row r="35" spans="1:29" s="67" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3776,7 +3772,7 @@
       </c>
     </row>
     <row r="36" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="90" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -3819,7 +3815,7 @@
       <c r="O36" s="63">
         <v>3.7826149790259799E-5</v>
       </c>
-      <c r="P36" s="84" t="s">
+      <c r="P36" s="90" t="s">
         <v>11</v>
       </c>
       <c r="Q36" s="13" t="s">
@@ -3859,7 +3855,7 @@
       <c r="AC36" s="13"/>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
@@ -3900,7 +3896,7 @@
       <c r="O37" s="2">
         <v>5.3176769657787898E-3</v>
       </c>
-      <c r="P37" s="85"/>
+      <c r="P37" s="79"/>
       <c r="Q37" s="1" t="s">
         <v>107</v>
       </c>
@@ -3938,7 +3934,7 @@
       <c r="AC37" s="1"/>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
+      <c r="A38" s="79"/>
       <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
@@ -3979,7 +3975,7 @@
       <c r="O38" s="3">
         <v>6.2255752292747699E-2</v>
       </c>
-      <c r="P38" s="85"/>
+      <c r="P38" s="79"/>
       <c r="Q38" s="1" t="s">
         <v>108</v>
       </c>
@@ -4017,16 +4013,16 @@
       <c r="AC38" s="1"/>
     </row>
     <row r="39" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="86"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="101"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="86"/>
+      <c r="F39" s="86"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14">
         <v>5.2456643231190104E-3</v>
@@ -4046,7 +4042,7 @@
       <c r="O39" s="14">
         <v>0.81735870029617597</v>
       </c>
-      <c r="P39" s="86"/>
+      <c r="P39" s="91"/>
       <c r="Q39" s="14" t="s">
         <v>109</v>
       </c>
@@ -4084,7 +4080,7 @@
       <c r="AC39" s="14"/>
     </row>
     <row r="40" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="90" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -4127,7 +4123,7 @@
       <c r="O40" s="64">
         <v>2.2627938793836001E-3</v>
       </c>
-      <c r="P40" s="84" t="s">
+      <c r="P40" s="90" t="s">
         <v>36</v>
       </c>
       <c r="Q40" s="13" t="s">
@@ -4167,7 +4163,7 @@
       <c r="AC40" s="13"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
@@ -4208,7 +4204,7 @@
       <c r="O41" s="2">
         <v>1.08776102041225E-2</v>
       </c>
-      <c r="P41" s="85"/>
+      <c r="P41" s="79"/>
       <c r="Q41" s="1" t="s">
         <v>107</v>
       </c>
@@ -4246,7 +4242,7 @@
       <c r="AC41" s="1"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
+      <c r="A42" s="79"/>
       <c r="B42" s="1" t="s">
         <v>8</v>
       </c>
@@ -4287,7 +4283,7 @@
       <c r="O42" s="2">
         <v>1.9393437026140801E-2</v>
       </c>
-      <c r="P42" s="85"/>
+      <c r="P42" s="79"/>
       <c r="Q42" s="1" t="s">
         <v>108</v>
       </c>
@@ -4325,16 +4321,16 @@
       <c r="AC42" s="1"/>
     </row>
     <row r="43" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="86"/>
+      <c r="A43" s="91"/>
       <c r="B43" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="101"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="86"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14">
         <v>7.5239018444935397E-3</v>
@@ -4354,7 +4350,7 @@
       <c r="O43" s="14">
         <v>0.74958204967156605</v>
       </c>
-      <c r="P43" s="86"/>
+      <c r="P43" s="91"/>
       <c r="Q43" s="14" t="s">
         <v>109</v>
       </c>
@@ -4392,7 +4388,7 @@
       <c r="AC43" s="14"/>
     </row>
     <row r="44" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="90" t="s">
         <v>12</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -4435,7 +4431,7 @@
       <c r="O44" s="13">
         <v>0.36857341395755699</v>
       </c>
-      <c r="P44" s="84" t="s">
+      <c r="P44" s="90" t="s">
         <v>12</v>
       </c>
       <c r="Q44" s="13" t="s">
@@ -4475,7 +4471,7 @@
       <c r="AC44" s="13"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="85"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
@@ -4516,7 +4512,7 @@
       <c r="O45" s="2">
         <v>1.4035037213878999E-4</v>
       </c>
-      <c r="P45" s="85"/>
+      <c r="P45" s="79"/>
       <c r="Q45" s="1" t="s">
         <v>107</v>
       </c>
@@ -4554,7 +4550,7 @@
       <c r="AC45" s="1"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="85"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
@@ -4595,7 +4591,7 @@
       <c r="O46" s="1">
         <v>0.179227673464389</v>
       </c>
-      <c r="P46" s="85"/>
+      <c r="P46" s="79"/>
       <c r="Q46" s="1" t="s">
         <v>108</v>
       </c>
@@ -4633,16 +4629,16 @@
       <c r="AC46" s="1"/>
     </row>
     <row r="47" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="86"/>
+      <c r="A47" s="91"/>
       <c r="B47" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="101"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="101"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="101"/>
-      <c r="H47" s="101"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="86"/>
+      <c r="E47" s="86"/>
+      <c r="F47" s="86"/>
+      <c r="G47" s="86"/>
+      <c r="H47" s="86"/>
       <c r="I47" s="14"/>
       <c r="J47" s="71">
         <v>7.2143853443936604E-6</v>
@@ -4662,7 +4658,7 @@
       <c r="O47" s="14">
         <v>0.41012132536637402</v>
       </c>
-      <c r="P47" s="86"/>
+      <c r="P47" s="91"/>
       <c r="Q47" s="14" t="s">
         <v>109</v>
       </c>
@@ -4700,7 +4696,7 @@
       <c r="AC47" s="14"/>
     </row>
     <row r="48" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -4743,7 +4739,7 @@
       <c r="O48" s="64">
         <v>1.2711861864362099E-4</v>
       </c>
-      <c r="P48" s="84" t="s">
+      <c r="P48" s="90" t="s">
         <v>13</v>
       </c>
       <c r="Q48" s="13" t="s">
@@ -4783,7 +4779,7 @@
       <c r="AC48" s="13"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
@@ -4824,7 +4820,7 @@
       <c r="O49" s="1">
         <v>0.80787586394532096</v>
       </c>
-      <c r="P49" s="85"/>
+      <c r="P49" s="79"/>
       <c r="Q49" s="1" t="s">
         <v>107</v>
       </c>
@@ -4862,7 +4858,7 @@
       <c r="AC49" s="1"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="85"/>
+      <c r="A50" s="79"/>
       <c r="B50" s="1" t="s">
         <v>8</v>
       </c>
@@ -4903,7 +4899,7 @@
       <c r="O50" s="2">
         <v>2.7582949079364601E-2</v>
       </c>
-      <c r="P50" s="85"/>
+      <c r="P50" s="79"/>
       <c r="Q50" s="1" t="s">
         <v>108</v>
       </c>
@@ -4941,16 +4937,16 @@
       <c r="AC50" s="1"/>
     </row>
     <row r="51" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="86"/>
+      <c r="A51" s="91"/>
       <c r="B51" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="101"/>
-      <c r="D51" s="101"/>
-      <c r="E51" s="101"/>
-      <c r="F51" s="101"/>
-      <c r="G51" s="101"/>
-      <c r="H51" s="101"/>
+      <c r="C51" s="86"/>
+      <c r="D51" s="86"/>
+      <c r="E51" s="86"/>
+      <c r="F51" s="86"/>
+      <c r="G51" s="86"/>
+      <c r="H51" s="86"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14">
         <v>0.34951867520347901</v>
@@ -4970,7 +4966,7 @@
       <c r="O51" s="14">
         <v>0.57430971602825098</v>
       </c>
-      <c r="P51" s="86"/>
+      <c r="P51" s="91"/>
       <c r="Q51" s="14" t="s">
         <v>109</v>
       </c>
@@ -5008,7 +5004,7 @@
       <c r="AC51" s="14"/>
     </row>
     <row r="52" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="84" t="s">
+      <c r="A52" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B52" s="13" t="s">
@@ -5051,7 +5047,7 @@
       <c r="O52" s="63">
         <v>4.8525436598560696E-10</v>
       </c>
-      <c r="P52" s="84" t="s">
+      <c r="P52" s="90" t="s">
         <v>16</v>
       </c>
       <c r="Q52" s="13" t="s">
@@ -5093,7 +5089,7 @@
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="85"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
@@ -5134,7 +5130,7 @@
       <c r="O53" s="4">
         <v>6.5162497916437297E-10</v>
       </c>
-      <c r="P53" s="85"/>
+      <c r="P53" s="79"/>
       <c r="Q53" s="1" t="s">
         <v>107</v>
       </c>
@@ -5174,7 +5170,7 @@
       </c>
     </row>
     <row r="54" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="85"/>
+      <c r="A54" s="79"/>
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
@@ -5215,7 +5211,7 @@
       <c r="O54" s="3">
         <v>7.1083850624745398E-2</v>
       </c>
-      <c r="P54" s="85"/>
+      <c r="P54" s="79"/>
       <c r="Q54" s="1" t="s">
         <v>108</v>
       </c>
@@ -5255,16 +5251,16 @@
       </c>
     </row>
     <row r="55" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="86"/>
+      <c r="A55" s="91"/>
       <c r="B55" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C55" s="101"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="101"/>
-      <c r="F55" s="101"/>
-      <c r="G55" s="101"/>
-      <c r="H55" s="101"/>
+      <c r="C55" s="86"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
+      <c r="H55" s="86"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14">
         <v>3.6858467316493698E-2</v>
@@ -5284,7 +5280,7 @@
       <c r="O55" s="60">
         <v>3.8017401028842102E-2</v>
       </c>
-      <c r="P55" s="86"/>
+      <c r="P55" s="91"/>
       <c r="Q55" s="14" t="s">
         <v>109</v>
       </c>
@@ -5324,20 +5320,20 @@
       </c>
     </row>
     <row r="56" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="84" t="s">
+      <c r="A56" s="90" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="100" t="s">
+      <c r="C56" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="100"/>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="83"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13">
         <v>4.0252880405239402E-2</v>
@@ -5357,19 +5353,19 @@
       <c r="O56" s="72">
         <v>8.2948057027609101E-2</v>
       </c>
-      <c r="P56" s="84" t="s">
+      <c r="P56" s="90" t="s">
         <v>38</v>
       </c>
       <c r="Q56" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R56" s="100" t="s">
+      <c r="R56" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="S56" s="100"/>
-      <c r="T56" s="100"/>
-      <c r="U56" s="100"/>
-      <c r="V56" s="100"/>
+      <c r="S56" s="83"/>
+      <c r="T56" s="83"/>
+      <c r="U56" s="83"/>
+      <c r="V56" s="83"/>
       <c r="W56" s="13"/>
       <c r="X56" s="13">
         <v>5.4104409999999999E-2</v>
@@ -5389,16 +5385,16 @@
       <c r="AC56" s="13"/>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="85"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="79"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
+      <c r="E57" s="82"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="82"/>
+      <c r="H57" s="82"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
         <v>0.42132164214255802</v>
@@ -5418,15 +5414,15 @@
       <c r="O57" s="4">
         <v>7.7465741239532106E-5</v>
       </c>
-      <c r="P57" s="85"/>
+      <c r="P57" s="79"/>
       <c r="Q57" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R57" s="79"/>
-      <c r="S57" s="79"/>
-      <c r="T57" s="79"/>
-      <c r="U57" s="79"/>
-      <c r="V57" s="79"/>
+      <c r="R57" s="82"/>
+      <c r="S57" s="82"/>
+      <c r="T57" s="82"/>
+      <c r="U57" s="82"/>
+      <c r="V57" s="82"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1">
         <v>4.687269E-3</v>
@@ -5446,16 +5442,16 @@
       <c r="AC57" s="1"/>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="85"/>
+      <c r="A58" s="79"/>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="79"/>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-      <c r="F58" s="79"/>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>7.8254362282741005E-2</v>
@@ -5475,15 +5471,15 @@
       <c r="O58" s="2">
         <v>1.63202510112339E-2</v>
       </c>
-      <c r="P58" s="85"/>
+      <c r="P58" s="79"/>
       <c r="Q58" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R58" s="79"/>
-      <c r="S58" s="79"/>
-      <c r="T58" s="79"/>
-      <c r="U58" s="79"/>
-      <c r="V58" s="79"/>
+      <c r="R58" s="82"/>
+      <c r="S58" s="82"/>
+      <c r="T58" s="82"/>
+      <c r="U58" s="82"/>
+      <c r="V58" s="82"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1">
         <v>-0.16190650000000001</v>
@@ -5503,16 +5499,16 @@
       <c r="AC58" s="1"/>
     </row>
     <row r="59" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="86"/>
+      <c r="A59" s="91"/>
       <c r="B59" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="80"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="80"/>
-      <c r="H59" s="80"/>
+      <c r="C59" s="84"/>
+      <c r="D59" s="84"/>
+      <c r="E59" s="84"/>
+      <c r="F59" s="84"/>
+      <c r="G59" s="84"/>
+      <c r="H59" s="84"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14">
         <v>2.6614614752845599E-3</v>
@@ -5532,15 +5528,15 @@
       <c r="O59" s="14">
         <v>0.90378258302877301</v>
       </c>
-      <c r="P59" s="86"/>
+      <c r="P59" s="91"/>
       <c r="Q59" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R59" s="80"/>
-      <c r="S59" s="80"/>
-      <c r="T59" s="80"/>
-      <c r="U59" s="80"/>
-      <c r="V59" s="80"/>
+      <c r="R59" s="84"/>
+      <c r="S59" s="84"/>
+      <c r="T59" s="84"/>
+      <c r="U59" s="84"/>
+      <c r="V59" s="84"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14">
         <v>-0.22064059999999999</v>
@@ -5560,7 +5556,7 @@
       <c r="AC59" s="14"/>
     </row>
     <row r="60" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="90" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="13" t="s">
@@ -5585,15 +5581,15 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I60" s="13"/>
-      <c r="J60" s="100" t="s">
+      <c r="J60" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K60" s="100"/>
-      <c r="L60" s="100"/>
-      <c r="M60" s="100"/>
-      <c r="N60" s="100"/>
-      <c r="O60" s="100"/>
-      <c r="P60" s="84" t="s">
+      <c r="K60" s="83"/>
+      <c r="L60" s="83"/>
+      <c r="M60" s="83"/>
+      <c r="N60" s="83"/>
+      <c r="O60" s="83"/>
+      <c r="P60" s="90" t="s">
         <v>39</v>
       </c>
       <c r="Q60" s="13" t="s">
@@ -5615,17 +5611,17 @@
         <v>1.0710269999999999E-5</v>
       </c>
       <c r="W60" s="13"/>
-      <c r="X60" s="100" t="s">
+      <c r="X60" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y60" s="100"/>
-      <c r="Z60" s="100"/>
-      <c r="AA60" s="100"/>
-      <c r="AB60" s="100"/>
+      <c r="Y60" s="83"/>
+      <c r="Z60" s="83"/>
+      <c r="AA60" s="83"/>
+      <c r="AB60" s="83"/>
       <c r="AC60" s="13"/>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="85"/>
+      <c r="A61" s="79"/>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
@@ -5648,13 +5644,13 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="79"/>
-      <c r="P61" s="85"/>
+      <c r="J61" s="82"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="82"/>
+      <c r="M61" s="82"/>
+      <c r="N61" s="82"/>
+      <c r="O61" s="82"/>
+      <c r="P61" s="79"/>
       <c r="Q61" s="1" t="s">
         <v>107</v>
       </c>
@@ -5674,15 +5670,15 @@
         <v>1.3791302849E-6</v>
       </c>
       <c r="W61" s="1"/>
-      <c r="X61" s="79"/>
-      <c r="Y61" s="79"/>
-      <c r="Z61" s="79"/>
-      <c r="AA61" s="79"/>
-      <c r="AB61" s="79"/>
+      <c r="X61" s="82"/>
+      <c r="Y61" s="82"/>
+      <c r="Z61" s="82"/>
+      <c r="AA61" s="82"/>
+      <c r="AB61" s="82"/>
       <c r="AC61" s="1"/>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="85"/>
+      <c r="A62" s="79"/>
       <c r="B62" s="1" t="s">
         <v>8</v>
       </c>
@@ -5705,13 +5701,13 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="79"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
-      <c r="N62" s="79"/>
-      <c r="O62" s="79"/>
-      <c r="P62" s="85"/>
+      <c r="J62" s="82"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="82"/>
+      <c r="M62" s="82"/>
+      <c r="N62" s="82"/>
+      <c r="O62" s="82"/>
+      <c r="P62" s="79"/>
       <c r="Q62" s="1" t="s">
         <v>108</v>
       </c>
@@ -5731,32 +5727,32 @@
         <v>9.3598610230064994E-2</v>
       </c>
       <c r="W62" s="1"/>
-      <c r="X62" s="79"/>
-      <c r="Y62" s="79"/>
-      <c r="Z62" s="79"/>
-      <c r="AA62" s="79"/>
-      <c r="AB62" s="79"/>
+      <c r="X62" s="82"/>
+      <c r="Y62" s="82"/>
+      <c r="Z62" s="82"/>
+      <c r="AA62" s="82"/>
+      <c r="AB62" s="82"/>
       <c r="AC62" s="1"/>
     </row>
     <row r="63" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="86"/>
+      <c r="A63" s="91"/>
       <c r="B63" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="101"/>
-      <c r="D63" s="101"/>
-      <c r="E63" s="101"/>
-      <c r="F63" s="101"/>
-      <c r="G63" s="101"/>
-      <c r="H63" s="101"/>
+      <c r="C63" s="86"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
+      <c r="H63" s="86"/>
       <c r="I63" s="14"/>
-      <c r="J63" s="80"/>
-      <c r="K63" s="80"/>
-      <c r="L63" s="80"/>
-      <c r="M63" s="80"/>
-      <c r="N63" s="80"/>
-      <c r="O63" s="80"/>
-      <c r="P63" s="86"/>
+      <c r="J63" s="84"/>
+      <c r="K63" s="84"/>
+      <c r="L63" s="84"/>
+      <c r="M63" s="84"/>
+      <c r="N63" s="84"/>
+      <c r="O63" s="84"/>
+      <c r="P63" s="91"/>
       <c r="Q63" s="14" t="s">
         <v>109</v>
       </c>
@@ -5776,15 +5772,15 @@
         <v>3.7977520000000001E-2</v>
       </c>
       <c r="W63" s="14"/>
-      <c r="X63" s="80"/>
-      <c r="Y63" s="80"/>
-      <c r="Z63" s="80"/>
-      <c r="AA63" s="80"/>
-      <c r="AB63" s="80"/>
+      <c r="X63" s="84"/>
+      <c r="Y63" s="84"/>
+      <c r="Z63" s="84"/>
+      <c r="AA63" s="84"/>
+      <c r="AB63" s="84"/>
       <c r="AC63" s="14"/>
     </row>
     <row r="64" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="90" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="13" t="s">
@@ -5809,15 +5805,15 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I64" s="13"/>
-      <c r="J64" s="100" t="s">
+      <c r="J64" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K64" s="100"/>
-      <c r="L64" s="100"/>
-      <c r="M64" s="100"/>
-      <c r="N64" s="100"/>
-      <c r="O64" s="100"/>
-      <c r="P64" s="84" t="s">
+      <c r="K64" s="83"/>
+      <c r="L64" s="83"/>
+      <c r="M64" s="83"/>
+      <c r="N64" s="83"/>
+      <c r="O64" s="83"/>
+      <c r="P64" s="90" t="s">
         <v>150</v>
       </c>
       <c r="Q64" s="13" t="s">
@@ -5839,17 +5835,17 @@
         <v>5.242662E-14</v>
       </c>
       <c r="W64" s="13"/>
-      <c r="X64" s="100" t="s">
+      <c r="X64" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y64" s="100"/>
-      <c r="Z64" s="100"/>
-      <c r="AA64" s="100"/>
-      <c r="AB64" s="100"/>
+      <c r="Y64" s="83"/>
+      <c r="Z64" s="83"/>
+      <c r="AA64" s="83"/>
+      <c r="AB64" s="83"/>
       <c r="AC64" s="13"/>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="85"/>
+      <c r="A65" s="79"/>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
@@ -5872,13 +5868,13 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="79"/>
-      <c r="K65" s="79"/>
-      <c r="L65" s="79"/>
-      <c r="M65" s="79"/>
-      <c r="N65" s="79"/>
-      <c r="O65" s="79"/>
-      <c r="P65" s="85"/>
+      <c r="J65" s="82"/>
+      <c r="K65" s="82"/>
+      <c r="L65" s="82"/>
+      <c r="M65" s="82"/>
+      <c r="N65" s="82"/>
+      <c r="O65" s="82"/>
+      <c r="P65" s="79"/>
       <c r="Q65" s="1" t="s">
         <v>107</v>
       </c>
@@ -5898,15 +5894,15 @@
         <v>3.4043159999999998E-14</v>
       </c>
       <c r="W65" s="1"/>
-      <c r="X65" s="79"/>
-      <c r="Y65" s="79"/>
-      <c r="Z65" s="79"/>
-      <c r="AA65" s="79"/>
-      <c r="AB65" s="79"/>
+      <c r="X65" s="82"/>
+      <c r="Y65" s="82"/>
+      <c r="Z65" s="82"/>
+      <c r="AA65" s="82"/>
+      <c r="AB65" s="82"/>
       <c r="AC65" s="1"/>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="85"/>
+      <c r="A66" s="79"/>
       <c r="B66" s="1" t="s">
         <v>8</v>
       </c>
@@ -5929,13 +5925,13 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="79"/>
-      <c r="K66" s="79"/>
-      <c r="L66" s="79"/>
-      <c r="M66" s="79"/>
-      <c r="N66" s="79"/>
-      <c r="O66" s="79"/>
-      <c r="P66" s="85"/>
+      <c r="J66" s="82"/>
+      <c r="K66" s="82"/>
+      <c r="L66" s="82"/>
+      <c r="M66" s="82"/>
+      <c r="N66" s="82"/>
+      <c r="O66" s="82"/>
+      <c r="P66" s="79"/>
       <c r="Q66" s="1" t="s">
         <v>108</v>
       </c>
@@ -5955,32 +5951,32 @@
         <v>0.64513220100000002</v>
       </c>
       <c r="W66" s="1"/>
-      <c r="X66" s="79"/>
-      <c r="Y66" s="79"/>
-      <c r="Z66" s="79"/>
-      <c r="AA66" s="79"/>
-      <c r="AB66" s="79"/>
+      <c r="X66" s="82"/>
+      <c r="Y66" s="82"/>
+      <c r="Z66" s="82"/>
+      <c r="AA66" s="82"/>
+      <c r="AB66" s="82"/>
       <c r="AC66" s="1"/>
     </row>
     <row r="67" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="86"/>
+      <c r="A67" s="91"/>
       <c r="B67" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="101"/>
-      <c r="D67" s="101"/>
-      <c r="E67" s="101"/>
-      <c r="F67" s="101"/>
-      <c r="G67" s="101"/>
-      <c r="H67" s="101"/>
+      <c r="C67" s="86"/>
+      <c r="D67" s="86"/>
+      <c r="E67" s="86"/>
+      <c r="F67" s="86"/>
+      <c r="G67" s="86"/>
+      <c r="H67" s="86"/>
       <c r="I67" s="14"/>
-      <c r="J67" s="80"/>
-      <c r="K67" s="80"/>
-      <c r="L67" s="80"/>
-      <c r="M67" s="80"/>
-      <c r="N67" s="80"/>
-      <c r="O67" s="80"/>
-      <c r="P67" s="86"/>
+      <c r="J67" s="84"/>
+      <c r="K67" s="84"/>
+      <c r="L67" s="84"/>
+      <c r="M67" s="84"/>
+      <c r="N67" s="84"/>
+      <c r="O67" s="84"/>
+      <c r="P67" s="91"/>
       <c r="Q67" s="14" t="s">
         <v>109</v>
       </c>
@@ -6000,28 +5996,28 @@
         <v>0.36655130000000002</v>
       </c>
       <c r="W67" s="14"/>
-      <c r="X67" s="80"/>
-      <c r="Y67" s="80"/>
-      <c r="Z67" s="80"/>
-      <c r="AA67" s="80"/>
-      <c r="AB67" s="80"/>
+      <c r="X67" s="84"/>
+      <c r="Y67" s="84"/>
+      <c r="Z67" s="84"/>
+      <c r="AA67" s="84"/>
+      <c r="AB67" s="84"/>
       <c r="AC67" s="14"/>
     </row>
     <row r="68" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="84" t="s">
+      <c r="A68" s="90" t="s">
         <v>28</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="100" t="s">
+      <c r="C68" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="D68" s="100"/>
-      <c r="E68" s="100"/>
-      <c r="F68" s="100"/>
-      <c r="G68" s="100"/>
-      <c r="H68" s="100"/>
+      <c r="D68" s="83"/>
+      <c r="E68" s="83"/>
+      <c r="F68" s="83"/>
+      <c r="G68" s="83"/>
+      <c r="H68" s="83"/>
       <c r="I68" s="13"/>
       <c r="J68" s="13">
         <v>4.9920514192076698E-4</v>
@@ -6041,19 +6037,19 @@
       <c r="O68" s="72">
         <v>7.0143959578357298E-2</v>
       </c>
-      <c r="P68" s="84" t="s">
+      <c r="P68" s="90" t="s">
         <v>148</v>
       </c>
       <c r="Q68" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R68" s="100" t="s">
+      <c r="R68" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="S68" s="100"/>
-      <c r="T68" s="100"/>
-      <c r="U68" s="100"/>
-      <c r="V68" s="100"/>
+      <c r="S68" s="83"/>
+      <c r="T68" s="83"/>
+      <c r="U68" s="83"/>
+      <c r="V68" s="83"/>
       <c r="W68" s="13"/>
       <c r="X68" s="70">
         <v>3.8010990000000001E-3</v>
@@ -6073,16 +6069,16 @@
       <c r="AC68" s="13"/>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="85"/>
+      <c r="A69" s="79"/>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="79"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="79"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="82"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>4.3245963051368403E-3</v>
@@ -6102,15 +6098,15 @@
       <c r="O69" s="4">
         <v>8.7931651517614295E-5</v>
       </c>
-      <c r="P69" s="85"/>
+      <c r="P69" s="79"/>
       <c r="Q69" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R69" s="79"/>
-      <c r="S69" s="79"/>
-      <c r="T69" s="79"/>
-      <c r="U69" s="79"/>
-      <c r="V69" s="79"/>
+      <c r="R69" s="82"/>
+      <c r="S69" s="82"/>
+      <c r="T69" s="82"/>
+      <c r="U69" s="82"/>
+      <c r="V69" s="82"/>
       <c r="W69" s="1"/>
       <c r="X69" s="45">
         <v>2.6998579999999999E-3</v>
@@ -6130,16 +6126,16 @@
       <c r="AC69" s="1"/>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="85"/>
+      <c r="A70" s="79"/>
       <c r="B70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
       <c r="I70" s="1"/>
       <c r="J70" s="5">
         <v>4.4673218852987901E-5</v>
@@ -6159,15 +6155,15 @@
       <c r="O70" s="1">
         <v>0.58543070585289902</v>
       </c>
-      <c r="P70" s="85"/>
+      <c r="P70" s="79"/>
       <c r="Q70" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R70" s="79"/>
-      <c r="S70" s="79"/>
-      <c r="T70" s="79"/>
-      <c r="U70" s="79"/>
-      <c r="V70" s="79"/>
+      <c r="R70" s="82"/>
+      <c r="S70" s="82"/>
+      <c r="T70" s="82"/>
+      <c r="U70" s="82"/>
+      <c r="V70" s="82"/>
       <c r="W70" s="1"/>
       <c r="X70" s="45">
         <v>-1.146374E-2</v>
@@ -6187,16 +6183,16 @@
       <c r="AC70" s="1"/>
     </row>
     <row r="71" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="86"/>
+      <c r="A71" s="91"/>
       <c r="B71" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="80"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="80"/>
+      <c r="C71" s="84"/>
+      <c r="D71" s="84"/>
+      <c r="E71" s="84"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="84"/>
+      <c r="H71" s="84"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14">
         <v>2.5092673060789E-4</v>
@@ -6216,15 +6212,15 @@
       <c r="O71" s="14">
         <v>0.43421981831232398</v>
       </c>
-      <c r="P71" s="86"/>
+      <c r="P71" s="91"/>
       <c r="Q71" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R71" s="80"/>
-      <c r="S71" s="80"/>
-      <c r="T71" s="80"/>
-      <c r="U71" s="80"/>
-      <c r="V71" s="80"/>
+      <c r="R71" s="84"/>
+      <c r="S71" s="84"/>
+      <c r="T71" s="84"/>
+      <c r="U71" s="84"/>
+      <c r="V71" s="84"/>
       <c r="W71" s="14"/>
       <c r="X71" s="61">
         <v>-1.288595E-2</v>
@@ -6244,20 +6240,20 @@
       <c r="AC71" s="14"/>
     </row>
     <row r="72" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="90" t="s">
         <v>18</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="100" t="s">
+      <c r="C72" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="100"/>
-      <c r="E72" s="100"/>
-      <c r="F72" s="100"/>
-      <c r="G72" s="100"/>
-      <c r="H72" s="100"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="83"/>
+      <c r="G72" s="83"/>
+      <c r="H72" s="83"/>
       <c r="I72" s="13"/>
       <c r="J72" s="13">
         <v>7.7190184322692705E-4</v>
@@ -6277,19 +6273,19 @@
       <c r="O72" s="13">
         <v>0.71627332791354703</v>
       </c>
-      <c r="P72" s="84" t="s">
+      <c r="P72" s="90" t="s">
         <v>143</v>
       </c>
       <c r="Q72" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R72" s="100" t="s">
+      <c r="R72" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="S72" s="100"/>
-      <c r="T72" s="100"/>
-      <c r="U72" s="100"/>
-      <c r="V72" s="100"/>
+      <c r="S72" s="83"/>
+      <c r="T72" s="83"/>
+      <c r="U72" s="83"/>
+      <c r="V72" s="83"/>
       <c r="W72" s="13"/>
       <c r="X72" s="70">
         <v>-8.3753321000000006E-3</v>
@@ -6308,16 +6304,16 @@
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="85"/>
+      <c r="A73" s="79"/>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="79"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="79"/>
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="82"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1">
         <v>0.26383928794443301</v>
@@ -6337,15 +6333,15 @@
       <c r="O73" s="4">
         <v>8.8402488312841299E-6</v>
       </c>
-      <c r="P73" s="85"/>
+      <c r="P73" s="79"/>
       <c r="Q73" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R73" s="79"/>
-      <c r="S73" s="79"/>
-      <c r="T73" s="79"/>
-      <c r="U73" s="79"/>
-      <c r="V73" s="79"/>
+      <c r="R73" s="82"/>
+      <c r="S73" s="82"/>
+      <c r="T73" s="82"/>
+      <c r="U73" s="82"/>
+      <c r="V73" s="82"/>
       <c r="W73" s="1"/>
       <c r="X73" s="45">
         <v>6.2885479999999997E-3</v>
@@ -6364,16 +6360,16 @@
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="85"/>
+      <c r="A74" s="79"/>
       <c r="B74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="79"/>
-      <c r="D74" s="79"/>
-      <c r="E74" s="79"/>
-      <c r="F74" s="79"/>
-      <c r="G74" s="79"/>
-      <c r="H74" s="79"/>
+      <c r="C74" s="82"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="82"/>
+      <c r="F74" s="82"/>
+      <c r="G74" s="82"/>
+      <c r="H74" s="82"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1">
         <v>6.5298294112546198E-3</v>
@@ -6393,15 +6389,15 @@
       <c r="O74" s="1">
         <v>0.29157119540922299</v>
       </c>
-      <c r="P74" s="85"/>
+      <c r="P74" s="79"/>
       <c r="Q74" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R74" s="79"/>
-      <c r="S74" s="79"/>
-      <c r="T74" s="79"/>
-      <c r="U74" s="79"/>
-      <c r="V74" s="79"/>
+      <c r="R74" s="82"/>
+      <c r="S74" s="82"/>
+      <c r="T74" s="82"/>
+      <c r="U74" s="82"/>
+      <c r="V74" s="82"/>
       <c r="W74" s="1"/>
       <c r="X74" s="45">
         <v>-0.1092133</v>
@@ -6420,16 +6416,16 @@
       </c>
     </row>
     <row r="75" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="86"/>
+      <c r="A75" s="91"/>
       <c r="B75" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C75" s="80"/>
-      <c r="D75" s="80"/>
-      <c r="E75" s="80"/>
-      <c r="F75" s="80"/>
-      <c r="G75" s="80"/>
-      <c r="H75" s="80"/>
+      <c r="C75" s="84"/>
+      <c r="D75" s="84"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="84"/>
+      <c r="G75" s="84"/>
+      <c r="H75" s="84"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14">
         <v>7.3489818378573097E-3</v>
@@ -6449,15 +6445,15 @@
       <c r="O75" s="14">
         <v>0.53343128963438502</v>
       </c>
-      <c r="P75" s="86"/>
+      <c r="P75" s="91"/>
       <c r="Q75" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R75" s="80"/>
-      <c r="S75" s="80"/>
-      <c r="T75" s="80"/>
-      <c r="U75" s="80"/>
-      <c r="V75" s="80"/>
+      <c r="R75" s="84"/>
+      <c r="S75" s="84"/>
+      <c r="T75" s="84"/>
+      <c r="U75" s="84"/>
+      <c r="V75" s="84"/>
       <c r="W75" s="14"/>
       <c r="X75" s="61">
         <v>-9.8989809999999998E-2</v>
@@ -6476,7 +6472,7 @@
       </c>
     </row>
     <row r="76" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>19</v>
       </c>
       <c r="B76" s="13" t="s">
@@ -6501,15 +6497,15 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I76" s="13"/>
-      <c r="J76" s="100" t="s">
+      <c r="J76" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="100"/>
-      <c r="N76" s="100"/>
-      <c r="O76" s="100"/>
-      <c r="P76" s="84" t="s">
+      <c r="K76" s="83"/>
+      <c r="L76" s="83"/>
+      <c r="M76" s="83"/>
+      <c r="N76" s="83"/>
+      <c r="O76" s="83"/>
+      <c r="P76" s="90" t="s">
         <v>144</v>
       </c>
       <c r="Q76" s="13" t="s">
@@ -6531,16 +6527,16 @@
         <v>2.350653E-6</v>
       </c>
       <c r="W76" s="13"/>
-      <c r="X76" s="100" t="s">
+      <c r="X76" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y76" s="100"/>
-      <c r="Z76" s="100"/>
-      <c r="AA76" s="100"/>
-      <c r="AB76" s="100"/>
+      <c r="Y76" s="83"/>
+      <c r="Z76" s="83"/>
+      <c r="AA76" s="83"/>
+      <c r="AB76" s="83"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="85"/>
+      <c r="A77" s="79"/>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
@@ -6563,13 +6559,13 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="79"/>
-      <c r="K77" s="79"/>
-      <c r="L77" s="79"/>
-      <c r="M77" s="79"/>
-      <c r="N77" s="79"/>
-      <c r="O77" s="79"/>
-      <c r="P77" s="85"/>
+      <c r="J77" s="82"/>
+      <c r="K77" s="82"/>
+      <c r="L77" s="82"/>
+      <c r="M77" s="82"/>
+      <c r="N77" s="82"/>
+      <c r="O77" s="82"/>
+      <c r="P77" s="79"/>
       <c r="Q77" s="1" t="s">
         <v>107</v>
       </c>
@@ -6589,14 +6585,14 @@
         <v>2.3278650000000001E-13</v>
       </c>
       <c r="W77" s="1"/>
-      <c r="X77" s="79"/>
-      <c r="Y77" s="79"/>
-      <c r="Z77" s="79"/>
-      <c r="AA77" s="79"/>
-      <c r="AB77" s="79"/>
+      <c r="X77" s="82"/>
+      <c r="Y77" s="82"/>
+      <c r="Z77" s="82"/>
+      <c r="AA77" s="82"/>
+      <c r="AB77" s="82"/>
     </row>
     <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="85"/>
+      <c r="A78" s="79"/>
       <c r="B78" s="1" t="s">
         <v>8</v>
       </c>
@@ -6619,13 +6615,13 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I78" s="1"/>
-      <c r="J78" s="79"/>
-      <c r="K78" s="79"/>
-      <c r="L78" s="79"/>
-      <c r="M78" s="79"/>
-      <c r="N78" s="79"/>
-      <c r="O78" s="79"/>
-      <c r="P78" s="85"/>
+      <c r="J78" s="82"/>
+      <c r="K78" s="82"/>
+      <c r="L78" s="82"/>
+      <c r="M78" s="82"/>
+      <c r="N78" s="82"/>
+      <c r="O78" s="82"/>
+      <c r="P78" s="79"/>
       <c r="Q78" s="1" t="s">
         <v>108</v>
       </c>
@@ -6645,31 +6641,31 @@
         <v>5.789537E-3</v>
       </c>
       <c r="W78" s="1"/>
-      <c r="X78" s="79"/>
-      <c r="Y78" s="79"/>
-      <c r="Z78" s="79"/>
-      <c r="AA78" s="79"/>
-      <c r="AB78" s="79"/>
+      <c r="X78" s="82"/>
+      <c r="Y78" s="82"/>
+      <c r="Z78" s="82"/>
+      <c r="AA78" s="82"/>
+      <c r="AB78" s="82"/>
     </row>
     <row r="79" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="86"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="101"/>
-      <c r="D79" s="101"/>
-      <c r="E79" s="101"/>
-      <c r="F79" s="101"/>
-      <c r="G79" s="101"/>
-      <c r="H79" s="101"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="86"/>
+      <c r="E79" s="86"/>
+      <c r="F79" s="86"/>
+      <c r="G79" s="86"/>
+      <c r="H79" s="86"/>
       <c r="I79" s="14"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="80"/>
-      <c r="L79" s="80"/>
-      <c r="M79" s="80"/>
-      <c r="N79" s="80"/>
-      <c r="O79" s="80"/>
-      <c r="P79" s="86"/>
+      <c r="J79" s="84"/>
+      <c r="K79" s="84"/>
+      <c r="L79" s="84"/>
+      <c r="M79" s="84"/>
+      <c r="N79" s="84"/>
+      <c r="O79" s="84"/>
+      <c r="P79" s="91"/>
       <c r="Q79" s="14" t="s">
         <v>109</v>
       </c>
@@ -6689,14 +6685,14 @@
         <v>3.5774789999999998E-4</v>
       </c>
       <c r="W79" s="14"/>
-      <c r="X79" s="80"/>
-      <c r="Y79" s="80"/>
-      <c r="Z79" s="80"/>
-      <c r="AA79" s="80"/>
-      <c r="AB79" s="80"/>
+      <c r="X79" s="84"/>
+      <c r="Y79" s="84"/>
+      <c r="Z79" s="84"/>
+      <c r="AA79" s="84"/>
+      <c r="AB79" s="84"/>
     </row>
     <row r="80" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="90" t="s">
         <v>23</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -6721,15 +6717,15 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I80" s="13"/>
-      <c r="J80" s="100" t="s">
+      <c r="J80" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K80" s="100"/>
-      <c r="L80" s="100"/>
-      <c r="M80" s="100"/>
-      <c r="N80" s="100"/>
-      <c r="O80" s="100"/>
-      <c r="P80" s="84" t="s">
+      <c r="K80" s="83"/>
+      <c r="L80" s="83"/>
+      <c r="M80" s="83"/>
+      <c r="N80" s="83"/>
+      <c r="O80" s="83"/>
+      <c r="P80" s="90" t="s">
         <v>145</v>
       </c>
       <c r="Q80" s="13" t="s">
@@ -6751,17 +6747,17 @@
         <v>2.524047E-13</v>
       </c>
       <c r="W80" s="13"/>
-      <c r="X80" s="100" t="s">
+      <c r="X80" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y80" s="100"/>
-      <c r="Z80" s="100"/>
-      <c r="AA80" s="100"/>
-      <c r="AB80" s="100"/>
+      <c r="Y80" s="83"/>
+      <c r="Z80" s="83"/>
+      <c r="AA80" s="83"/>
+      <c r="AB80" s="83"/>
       <c r="AC80" s="13"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A81" s="85"/>
+      <c r="A81" s="79"/>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
@@ -6784,13 +6780,13 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="79"/>
-      <c r="L81" s="79"/>
-      <c r="M81" s="79"/>
-      <c r="N81" s="79"/>
-      <c r="O81" s="79"/>
-      <c r="P81" s="85"/>
+      <c r="J81" s="82"/>
+      <c r="K81" s="82"/>
+      <c r="L81" s="82"/>
+      <c r="M81" s="82"/>
+      <c r="N81" s="82"/>
+      <c r="O81" s="82"/>
+      <c r="P81" s="79"/>
       <c r="Q81" s="1" t="s">
         <v>107</v>
       </c>
@@ -6810,15 +6806,15 @@
         <v>8.8521990000000004E-10</v>
       </c>
       <c r="W81" s="1"/>
-      <c r="X81" s="79"/>
-      <c r="Y81" s="79"/>
-      <c r="Z81" s="79"/>
-      <c r="AA81" s="79"/>
-      <c r="AB81" s="79"/>
+      <c r="X81" s="82"/>
+      <c r="Y81" s="82"/>
+      <c r="Z81" s="82"/>
+      <c r="AA81" s="82"/>
+      <c r="AB81" s="82"/>
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A82" s="85"/>
+      <c r="A82" s="79"/>
       <c r="B82" s="1" t="s">
         <v>8</v>
       </c>
@@ -6841,13 +6837,13 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="79"/>
-      <c r="K82" s="79"/>
-      <c r="L82" s="79"/>
-      <c r="M82" s="79"/>
-      <c r="N82" s="79"/>
-      <c r="O82" s="79"/>
-      <c r="P82" s="85"/>
+      <c r="J82" s="82"/>
+      <c r="K82" s="82"/>
+      <c r="L82" s="82"/>
+      <c r="M82" s="82"/>
+      <c r="N82" s="82"/>
+      <c r="O82" s="82"/>
+      <c r="P82" s="79"/>
       <c r="Q82" s="1" t="s">
         <v>108</v>
       </c>
@@ -6867,32 +6863,32 @@
         <v>9.6146709999999996E-2</v>
       </c>
       <c r="W82" s="1"/>
-      <c r="X82" s="79"/>
-      <c r="Y82" s="79"/>
-      <c r="Z82" s="79"/>
-      <c r="AA82" s="79"/>
-      <c r="AB82" s="79"/>
+      <c r="X82" s="82"/>
+      <c r="Y82" s="82"/>
+      <c r="Z82" s="82"/>
+      <c r="AA82" s="82"/>
+      <c r="AB82" s="82"/>
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="86"/>
+      <c r="A83" s="91"/>
       <c r="B83" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C83" s="101"/>
-      <c r="D83" s="101"/>
-      <c r="E83" s="101"/>
-      <c r="F83" s="101"/>
-      <c r="G83" s="101"/>
-      <c r="H83" s="101"/>
+      <c r="C83" s="86"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="86"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="86"/>
+      <c r="H83" s="86"/>
       <c r="I83" s="14"/>
-      <c r="J83" s="80"/>
-      <c r="K83" s="80"/>
-      <c r="L83" s="80"/>
-      <c r="M83" s="80"/>
-      <c r="N83" s="80"/>
-      <c r="O83" s="80"/>
-      <c r="P83" s="86"/>
+      <c r="J83" s="84"/>
+      <c r="K83" s="84"/>
+      <c r="L83" s="84"/>
+      <c r="M83" s="84"/>
+      <c r="N83" s="84"/>
+      <c r="O83" s="84"/>
+      <c r="P83" s="91"/>
       <c r="Q83" s="14" t="s">
         <v>109</v>
       </c>
@@ -6912,15 +6908,15 @@
         <v>6.7150146952E-3</v>
       </c>
       <c r="W83" s="14"/>
-      <c r="X83" s="80"/>
-      <c r="Y83" s="80"/>
-      <c r="Z83" s="80"/>
-      <c r="AA83" s="80"/>
-      <c r="AB83" s="80"/>
+      <c r="X83" s="84"/>
+      <c r="Y83" s="84"/>
+      <c r="Z83" s="84"/>
+      <c r="AA83" s="84"/>
+      <c r="AB83" s="84"/>
       <c r="AC83" s="14"/>
     </row>
     <row r="84" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="90" t="s">
         <v>155</v>
       </c>
       <c r="B84" s="13" t="s">
@@ -6945,15 +6941,15 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I84" s="13"/>
-      <c r="J84" s="100" t="s">
+      <c r="J84" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="K84" s="100"/>
-      <c r="L84" s="100"/>
-      <c r="M84" s="100"/>
-      <c r="N84" s="100"/>
-      <c r="O84" s="100"/>
-      <c r="P84" s="84" t="s">
+      <c r="K84" s="83"/>
+      <c r="L84" s="83"/>
+      <c r="M84" s="83"/>
+      <c r="N84" s="83"/>
+      <c r="O84" s="83"/>
+      <c r="P84" s="90" t="s">
         <v>149</v>
       </c>
       <c r="Q84" s="13" t="s">
@@ -6975,17 +6971,17 @@
         <v>0.96106304949900001</v>
       </c>
       <c r="W84" s="13"/>
-      <c r="X84" s="100" t="s">
+      <c r="X84" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Y84" s="100"/>
-      <c r="Z84" s="100"/>
-      <c r="AA84" s="100"/>
-      <c r="AB84" s="100"/>
+      <c r="Y84" s="83"/>
+      <c r="Z84" s="83"/>
+      <c r="AA84" s="83"/>
+      <c r="AB84" s="83"/>
       <c r="AC84" s="13"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A85" s="85"/>
+      <c r="A85" s="79"/>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
@@ -7008,13 +7004,13 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="79"/>
-      <c r="K85" s="79"/>
-      <c r="L85" s="79"/>
-      <c r="M85" s="79"/>
-      <c r="N85" s="79"/>
-      <c r="O85" s="79"/>
-      <c r="P85" s="85"/>
+      <c r="J85" s="82"/>
+      <c r="K85" s="82"/>
+      <c r="L85" s="82"/>
+      <c r="M85" s="82"/>
+      <c r="N85" s="82"/>
+      <c r="O85" s="82"/>
+      <c r="P85" s="79"/>
       <c r="Q85" s="1" t="s">
         <v>107</v>
       </c>
@@ -7034,15 +7030,15 @@
         <v>0.2307786</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="79"/>
-      <c r="Y85" s="79"/>
-      <c r="Z85" s="79"/>
-      <c r="AA85" s="79"/>
-      <c r="AB85" s="79"/>
+      <c r="X85" s="82"/>
+      <c r="Y85" s="82"/>
+      <c r="Z85" s="82"/>
+      <c r="AA85" s="82"/>
+      <c r="AB85" s="82"/>
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A86" s="85"/>
+      <c r="A86" s="79"/>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
@@ -7065,13 +7061,13 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I86" s="1"/>
-      <c r="J86" s="79"/>
-      <c r="K86" s="79"/>
-      <c r="L86" s="79"/>
-      <c r="M86" s="79"/>
-      <c r="N86" s="79"/>
-      <c r="O86" s="79"/>
-      <c r="P86" s="85"/>
+      <c r="J86" s="82"/>
+      <c r="K86" s="82"/>
+      <c r="L86" s="82"/>
+      <c r="M86" s="82"/>
+      <c r="N86" s="82"/>
+      <c r="O86" s="82"/>
+      <c r="P86" s="79"/>
       <c r="Q86" s="1" t="s">
         <v>108</v>
       </c>
@@ -7091,32 +7087,32 @@
         <v>3.2851500000000001E-3</v>
       </c>
       <c r="W86" s="1"/>
-      <c r="X86" s="79"/>
-      <c r="Y86" s="79"/>
-      <c r="Z86" s="79"/>
-      <c r="AA86" s="79"/>
-      <c r="AB86" s="79"/>
+      <c r="X86" s="82"/>
+      <c r="Y86" s="82"/>
+      <c r="Z86" s="82"/>
+      <c r="AA86" s="82"/>
+      <c r="AB86" s="82"/>
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="86"/>
+      <c r="A87" s="91"/>
       <c r="B87" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C87" s="101"/>
-      <c r="D87" s="101"/>
-      <c r="E87" s="101"/>
-      <c r="F87" s="101"/>
-      <c r="G87" s="101"/>
-      <c r="H87" s="101"/>
+      <c r="C87" s="86"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="86"/>
+      <c r="F87" s="86"/>
+      <c r="G87" s="86"/>
+      <c r="H87" s="86"/>
       <c r="I87" s="14"/>
-      <c r="J87" s="80"/>
-      <c r="K87" s="80"/>
-      <c r="L87" s="80"/>
-      <c r="M87" s="80"/>
-      <c r="N87" s="80"/>
-      <c r="O87" s="80"/>
-      <c r="P87" s="86"/>
+      <c r="J87" s="84"/>
+      <c r="K87" s="84"/>
+      <c r="L87" s="84"/>
+      <c r="M87" s="84"/>
+      <c r="N87" s="84"/>
+      <c r="O87" s="84"/>
+      <c r="P87" s="91"/>
       <c r="Q87" s="14" t="s">
         <v>109</v>
       </c>
@@ -7136,49 +7132,54 @@
         <v>9.3442800000000006E-2</v>
       </c>
       <c r="W87" s="14"/>
-      <c r="X87" s="80"/>
-      <c r="Y87" s="80"/>
-      <c r="Z87" s="80"/>
-      <c r="AA87" s="80"/>
-      <c r="AB87" s="80"/>
+      <c r="X87" s="84"/>
+      <c r="Y87" s="84"/>
+      <c r="Z87" s="84"/>
+      <c r="AA87" s="84"/>
+      <c r="AB87" s="84"/>
       <c r="AC87" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="J27:O30"/>
-    <mergeCell ref="X23:AB26"/>
-    <mergeCell ref="X27:AB30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J23:O26"/>
-    <mergeCell ref="J3:O6"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C56:H59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="C11:H14"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="R11:V14"/>
+    <mergeCell ref="X1:AC1"/>
+    <mergeCell ref="P48:P51"/>
+    <mergeCell ref="P3:P6"/>
+    <mergeCell ref="X3:AB6"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P36:P39"/>
+    <mergeCell ref="P40:P43"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="P44:P47"/>
+    <mergeCell ref="P15:P18"/>
+    <mergeCell ref="P7:P10"/>
+    <mergeCell ref="P60:P63"/>
+    <mergeCell ref="P72:P75"/>
+    <mergeCell ref="P11:P14"/>
+    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="X76:AB79"/>
+    <mergeCell ref="X60:AB63"/>
+    <mergeCell ref="P80:P83"/>
+    <mergeCell ref="X84:AB87"/>
+    <mergeCell ref="P19:P22"/>
+    <mergeCell ref="R19:V22"/>
+    <mergeCell ref="P84:P87"/>
+    <mergeCell ref="P64:P67"/>
+    <mergeCell ref="X64:AB67"/>
+    <mergeCell ref="R72:V75"/>
+    <mergeCell ref="P76:P79"/>
+    <mergeCell ref="X80:AB83"/>
+    <mergeCell ref="R56:V59"/>
+    <mergeCell ref="P52:P55"/>
+    <mergeCell ref="J31:O34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="X31:AB34"/>
+    <mergeCell ref="P68:P71"/>
+    <mergeCell ref="R68:V71"/>
+    <mergeCell ref="J64:O67"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="J60:O63"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="C19:H22"/>
     <mergeCell ref="A23:A26"/>
@@ -7195,45 +7196,40 @@
     <mergeCell ref="C79:H79"/>
     <mergeCell ref="A72:A75"/>
     <mergeCell ref="C72:H75"/>
-    <mergeCell ref="J31:O34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="P31:P34"/>
-    <mergeCell ref="X31:AB34"/>
-    <mergeCell ref="P68:P71"/>
-    <mergeCell ref="R68:V71"/>
-    <mergeCell ref="J64:O67"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="J60:O63"/>
-    <mergeCell ref="X76:AB79"/>
-    <mergeCell ref="X60:AB63"/>
-    <mergeCell ref="P80:P83"/>
-    <mergeCell ref="X84:AB87"/>
-    <mergeCell ref="P19:P22"/>
-    <mergeCell ref="R19:V22"/>
-    <mergeCell ref="P84:P87"/>
-    <mergeCell ref="P64:P67"/>
-    <mergeCell ref="X64:AB67"/>
-    <mergeCell ref="R72:V75"/>
-    <mergeCell ref="P76:P79"/>
-    <mergeCell ref="X80:AB83"/>
-    <mergeCell ref="R56:V59"/>
-    <mergeCell ref="P52:P55"/>
-    <mergeCell ref="P7:P10"/>
-    <mergeCell ref="P60:P63"/>
-    <mergeCell ref="P72:P75"/>
-    <mergeCell ref="P11:P14"/>
-    <mergeCell ref="P56:P59"/>
-    <mergeCell ref="R11:V14"/>
-    <mergeCell ref="X1:AC1"/>
-    <mergeCell ref="P48:P51"/>
-    <mergeCell ref="P3:P6"/>
-    <mergeCell ref="X3:AB6"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="P36:P39"/>
-    <mergeCell ref="P40:P43"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="P44:P47"/>
-    <mergeCell ref="P15:P18"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C56:H59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="C63:H63"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="J3:O6"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="C11:H14"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="J27:O30"/>
+    <mergeCell ref="X23:AB26"/>
+    <mergeCell ref="X27:AB30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J23:O26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7303,24 +7299,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="102">
+      <c r="C1" s="104">
         <v>2021</v>
       </c>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="102">
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="104">
         <v>2022</v>
       </c>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="104"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="106"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7371,7 +7367,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="92" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7419,7 +7415,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -7463,7 +7459,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="85"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7507,16 +7503,16 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="99"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -7539,7 +7535,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="92" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -7585,7 +7581,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -7629,7 +7625,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="85"/>
+      <c r="A9" s="79"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -7673,16 +7669,16 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="99"/>
+      <c r="A10" s="80"/>
       <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -7705,7 +7701,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="92" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -7730,18 +7726,18 @@
         <v>3.2053459705297903E-5</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="79" t="s">
+      <c r="J11" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="85"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -7764,16 +7760,16 @@
         <v>2.0059373392474201E-2</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -7796,36 +7792,36 @@
         <v>0.213540969734523</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
+      <c r="A14" s="80"/>
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="79"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="82"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="92" t="s">
         <v>141</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -7850,18 +7846,18 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="79" t="s">
+      <c r="J15" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="79"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="82"/>
+      <c r="O15" s="82"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -7884,16 +7880,16 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="82"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="82"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -7915,36 +7911,36 @@
       <c r="H17" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="82"/>
+      <c r="N17" s="82"/>
+      <c r="O17" s="82"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="82"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="82"/>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="92" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -7990,7 +7986,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="85"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="11" t="s">
         <v>7</v>
       </c>
@@ -8034,7 +8030,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -8078,16 +8074,16 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
+      <c r="A22" s="80"/>
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="105"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -8110,7 +8106,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -8156,7 +8152,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -8200,7 +8196,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -8244,16 +8240,16 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
+      <c r="A26" s="80"/>
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -8276,7 +8272,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="92" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -8322,7 +8318,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -8366,7 +8362,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -8410,16 +8406,16 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="99"/>
+      <c r="A30" s="80"/>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -8442,7 +8438,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="92" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -8488,7 +8484,7 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -8532,7 +8528,7 @@
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -8576,16 +8572,16 @@
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
+      <c r="A34" s="80"/>
       <c r="B34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -8608,7 +8604,7 @@
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="92" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8654,7 +8650,7 @@
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -8698,7 +8694,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -8742,16 +8738,16 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
+      <c r="A38" s="80"/>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -8774,7 +8770,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="92" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -8820,7 +8816,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
+      <c r="A40" s="79"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -8864,7 +8860,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -8908,16 +8904,16 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
+      <c r="A42" s="80"/>
       <c r="B42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
-      <c r="H42" s="105"/>
+      <c r="C42" s="85"/>
+      <c r="D42" s="85"/>
+      <c r="E42" s="85"/>
+      <c r="F42" s="85"/>
+      <c r="G42" s="85"/>
+      <c r="H42" s="85"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -8940,7 +8936,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="87" t="s">
+      <c r="A43" s="92" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -8986,7 +8982,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
+      <c r="A44" s="79"/>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -9030,7 +9026,7 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="85"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
@@ -9074,16 +9070,16 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="99"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="85"/>
+      <c r="H46" s="85"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -9106,7 +9102,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="92" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -9152,7 +9148,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="85"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="10" t="s">
         <v>7</v>
       </c>
@@ -9196,7 +9192,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -9240,16 +9236,16 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="99"/>
+      <c r="A50" s="80"/>
       <c r="B50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="85"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -9272,20 +9268,20 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="92" t="s">
         <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="82"/>
+      <c r="H51" s="82"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
         <v>2.20343269025562E-2</v>
@@ -9308,16 +9304,16 @@
       <c r="P51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="85"/>
+      <c r="A52" s="79"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="79"/>
-      <c r="D52" s="79"/>
-      <c r="E52" s="79"/>
-      <c r="F52" s="79"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="82"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
         <v>2.98483856205864E-2</v>
@@ -9340,16 +9336,16 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="85"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="79"/>
-      <c r="D53" s="79"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
         <v>1.15818782663304E-3</v>
@@ -9372,16 +9368,16 @@
       <c r="P53" s="1"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="99"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
         <v>2.0797141885883202E-3</v>
@@ -9404,7 +9400,7 @@
       <c r="P54" s="1"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="87" t="s">
+      <c r="A55" s="92" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -9452,7 +9448,7 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="85"/>
+      <c r="A56" s="79"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -9496,7 +9492,7 @@
       <c r="P56" s="1"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="85"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -9540,16 +9536,16 @@
       <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="99"/>
+      <c r="A58" s="80"/>
       <c r="B58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="105"/>
-      <c r="H58" s="105"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="85"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -9572,7 +9568,7 @@
       <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="87" t="s">
+      <c r="A59" s="92" t="s">
         <v>64</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -9597,18 +9593,18 @@
         <v>1.61142062466842E-3</v>
       </c>
       <c r="I59" s="1"/>
-      <c r="J59" s="79" t="s">
+      <c r="J59" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K59" s="79"/>
-      <c r="L59" s="79"/>
-      <c r="M59" s="79"/>
-      <c r="N59" s="79"/>
-      <c r="O59" s="79"/>
+      <c r="K59" s="82"/>
+      <c r="L59" s="82"/>
+      <c r="M59" s="82"/>
+      <c r="N59" s="82"/>
+      <c r="O59" s="82"/>
       <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="85"/>
+      <c r="A60" s="79"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
@@ -9631,16 +9627,16 @@
         <v>0.83160181683106904</v>
       </c>
       <c r="I60" s="1"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="79"/>
-      <c r="L60" s="79"/>
-      <c r="M60" s="79"/>
-      <c r="N60" s="79"/>
-      <c r="O60" s="79"/>
+      <c r="J60" s="82"/>
+      <c r="K60" s="82"/>
+      <c r="L60" s="82"/>
+      <c r="M60" s="82"/>
+      <c r="N60" s="82"/>
+      <c r="O60" s="82"/>
       <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="85"/>
+      <c r="A61" s="79"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
@@ -9663,49 +9659,49 @@
         <v>0.64170681971566501</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="79"/>
+      <c r="J61" s="82"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="82"/>
+      <c r="M61" s="82"/>
+      <c r="N61" s="82"/>
+      <c r="O61" s="82"/>
       <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="99"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="105"/>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
-      <c r="F62" s="105"/>
-      <c r="G62" s="105"/>
-      <c r="H62" s="105"/>
+      <c r="C62" s="85"/>
+      <c r="D62" s="85"/>
+      <c r="E62" s="85"/>
+      <c r="F62" s="85"/>
+      <c r="G62" s="85"/>
+      <c r="H62" s="85"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="79"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
-      <c r="N62" s="79"/>
-      <c r="O62" s="79"/>
+      <c r="J62" s="82"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="82"/>
+      <c r="M62" s="82"/>
+      <c r="N62" s="82"/>
+      <c r="O62" s="82"/>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="92" t="s">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="79" t="s">
+      <c r="C63" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="79"/>
-      <c r="G63" s="79"/>
-      <c r="H63" s="79"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="82"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
         <v>40.695777417400599</v>
@@ -9728,16 +9724,16 @@
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="85"/>
+      <c r="A64" s="79"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="79"/>
-      <c r="D64" s="79"/>
-      <c r="E64" s="79"/>
-      <c r="F64" s="79"/>
-      <c r="G64" s="79"/>
-      <c r="H64" s="79"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
+      <c r="H64" s="82"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
         <v>0.27305635622259</v>
@@ -9760,16 +9756,16 @@
       <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="85"/>
+      <c r="A65" s="79"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="79"/>
-      <c r="D65" s="79"/>
-      <c r="E65" s="79"/>
-      <c r="F65" s="79"/>
-      <c r="G65" s="79"/>
-      <c r="H65" s="79"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
+      <c r="H65" s="82"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
         <v>3.4613576315483399</v>
@@ -9792,16 +9788,16 @@
       <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="99"/>
+      <c r="A66" s="80"/>
       <c r="B66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="79"/>
-      <c r="D66" s="79"/>
-      <c r="E66" s="79"/>
-      <c r="F66" s="79"/>
-      <c r="G66" s="79"/>
-      <c r="H66" s="79"/>
+      <c r="C66" s="82"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
+      <c r="H66" s="82"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
         <v>0.72850411949349603</v>
@@ -9824,20 +9820,20 @@
       <c r="P66" s="1"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="87" t="s">
+      <c r="A67" s="92" t="s">
         <v>41</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="79" t="s">
+      <c r="C67" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="79"/>
-      <c r="E67" s="79"/>
-      <c r="F67" s="79"/>
-      <c r="G67" s="79"/>
-      <c r="H67" s="79"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="82"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
         <v>948.25120936445398</v>
@@ -9860,16 +9856,16 @@
       <c r="P67" s="1"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="85"/>
+      <c r="A68" s="79"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="82"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
         <v>0.22870622612837599</v>
@@ -9892,16 +9888,16 @@
       <c r="P68" s="1"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="85"/>
+      <c r="A69" s="79"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="79"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="79"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="82"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>37.771893612281502</v>
@@ -9924,16 +9920,16 @@
       <c r="P69" s="1"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="99"/>
+      <c r="A70" s="80"/>
       <c r="B70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
         <v>3.9110782596565699</v>
@@ -9956,7 +9952,7 @@
       <c r="P70" s="1"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="87" t="s">
+      <c r="A71" s="92" t="s">
         <v>42</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -9981,18 +9977,18 @@
         <v>2.3819311555743102E-16</v>
       </c>
       <c r="I71" s="1"/>
-      <c r="J71" s="79" t="s">
+      <c r="J71" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K71" s="79"/>
-      <c r="L71" s="79"/>
-      <c r="M71" s="79"/>
-      <c r="N71" s="79"/>
-      <c r="O71" s="79"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="82"/>
+      <c r="N71" s="82"/>
+      <c r="O71" s="82"/>
       <c r="P71" s="1"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="85"/>
+      <c r="A72" s="79"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
@@ -10015,16 +10011,16 @@
         <v>1.0894169628446399E-3</v>
       </c>
       <c r="I72" s="1"/>
-      <c r="J72" s="79"/>
-      <c r="K72" s="79"/>
-      <c r="L72" s="79"/>
-      <c r="M72" s="79"/>
-      <c r="N72" s="79"/>
-      <c r="O72" s="79"/>
+      <c r="J72" s="82"/>
+      <c r="K72" s="82"/>
+      <c r="L72" s="82"/>
+      <c r="M72" s="82"/>
+      <c r="N72" s="82"/>
+      <c r="O72" s="82"/>
       <c r="P72" s="1"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="85"/>
+      <c r="A73" s="79"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
@@ -10047,49 +10043,49 @@
         <v>0.84541099798019603</v>
       </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="79"/>
-      <c r="K73" s="79"/>
-      <c r="L73" s="79"/>
-      <c r="M73" s="79"/>
-      <c r="N73" s="79"/>
-      <c r="O73" s="79"/>
+      <c r="J73" s="82"/>
+      <c r="K73" s="82"/>
+      <c r="L73" s="82"/>
+      <c r="M73" s="82"/>
+      <c r="N73" s="82"/>
+      <c r="O73" s="82"/>
       <c r="P73" s="1"/>
     </row>
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="99"/>
+      <c r="A74" s="80"/>
       <c r="B74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="105"/>
-      <c r="D74" s="105"/>
-      <c r="E74" s="105"/>
-      <c r="F74" s="105"/>
-      <c r="G74" s="105"/>
-      <c r="H74" s="105"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="85"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="85"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="85"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="79"/>
-      <c r="K74" s="79"/>
-      <c r="L74" s="79"/>
-      <c r="M74" s="79"/>
-      <c r="N74" s="79"/>
-      <c r="O74" s="79"/>
+      <c r="J74" s="82"/>
+      <c r="K74" s="82"/>
+      <c r="L74" s="82"/>
+      <c r="M74" s="82"/>
+      <c r="N74" s="82"/>
+      <c r="O74" s="82"/>
       <c r="P74" s="1"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="87" t="s">
+      <c r="A75" s="92" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="79" t="s">
+      <c r="C75" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="79"/>
-      <c r="H75" s="79"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1">
         <v>7.7190184322692705E-4</v>
@@ -10112,16 +10108,16 @@
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="85"/>
+      <c r="A76" s="79"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="79"/>
-      <c r="D76" s="79"/>
-      <c r="E76" s="79"/>
-      <c r="F76" s="79"/>
-      <c r="G76" s="79"/>
-      <c r="H76" s="79"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
+      <c r="E76" s="82"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="82"/>
+      <c r="H76" s="82"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1">
         <v>0.26383928794443301</v>
@@ -10144,16 +10140,16 @@
       <c r="P76" s="1"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="85"/>
+      <c r="A77" s="79"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="79"/>
-      <c r="D77" s="79"/>
-      <c r="E77" s="79"/>
-      <c r="F77" s="79"/>
-      <c r="G77" s="79"/>
-      <c r="H77" s="79"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1">
         <v>6.5298294112546198E-3</v>
@@ -10176,16 +10172,16 @@
       <c r="P77" s="1"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="99"/>
+      <c r="A78" s="80"/>
       <c r="B78" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C78" s="79"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="79"/>
-      <c r="F78" s="79"/>
-      <c r="G78" s="79"/>
-      <c r="H78" s="79"/>
+      <c r="C78" s="82"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="82"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="82"/>
+      <c r="H78" s="82"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1">
         <v>7.3489818378573097E-3</v>
@@ -10208,7 +10204,7 @@
       <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="87" t="s">
+      <c r="A79" s="92" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -10233,18 +10229,18 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I79" s="1"/>
-      <c r="J79" s="79" t="s">
+      <c r="J79" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K79" s="79"/>
-      <c r="L79" s="79"/>
-      <c r="M79" s="79"/>
-      <c r="N79" s="79"/>
-      <c r="O79" s="79"/>
+      <c r="K79" s="82"/>
+      <c r="L79" s="82"/>
+      <c r="M79" s="82"/>
+      <c r="N79" s="82"/>
+      <c r="O79" s="82"/>
       <c r="P79" s="1"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="85"/>
+      <c r="A80" s="79"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
@@ -10267,16 +10263,16 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="79"/>
-      <c r="K80" s="79"/>
-      <c r="L80" s="79"/>
-      <c r="M80" s="79"/>
-      <c r="N80" s="79"/>
-      <c r="O80" s="79"/>
+      <c r="J80" s="82"/>
+      <c r="K80" s="82"/>
+      <c r="L80" s="82"/>
+      <c r="M80" s="82"/>
+      <c r="N80" s="82"/>
+      <c r="O80" s="82"/>
       <c r="P80" s="1"/>
     </row>
     <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="85"/>
+      <c r="A81" s="79"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
@@ -10299,49 +10295,49 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="79"/>
-      <c r="L81" s="79"/>
-      <c r="M81" s="79"/>
-      <c r="N81" s="79"/>
-      <c r="O81" s="79"/>
+      <c r="J81" s="82"/>
+      <c r="K81" s="82"/>
+      <c r="L81" s="82"/>
+      <c r="M81" s="82"/>
+      <c r="N81" s="82"/>
+      <c r="O81" s="82"/>
       <c r="P81" s="1"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="99"/>
+      <c r="A82" s="80"/>
       <c r="B82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="105"/>
-      <c r="D82" s="105"/>
-      <c r="E82" s="105"/>
-      <c r="F82" s="105"/>
-      <c r="G82" s="105"/>
-      <c r="H82" s="105"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
+      <c r="E82" s="85"/>
+      <c r="F82" s="85"/>
+      <c r="G82" s="85"/>
+      <c r="H82" s="85"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="79"/>
-      <c r="K82" s="79"/>
-      <c r="L82" s="79"/>
-      <c r="M82" s="79"/>
-      <c r="N82" s="79"/>
-      <c r="O82" s="79"/>
+      <c r="J82" s="82"/>
+      <c r="K82" s="82"/>
+      <c r="L82" s="82"/>
+      <c r="M82" s="82"/>
+      <c r="N82" s="82"/>
+      <c r="O82" s="82"/>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="87" t="s">
+      <c r="A83" s="92" t="s">
         <v>38</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="79" t="s">
+      <c r="C83" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D83" s="79"/>
-      <c r="E83" s="79"/>
-      <c r="F83" s="79"/>
-      <c r="G83" s="79"/>
-      <c r="H83" s="79"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="82"/>
+      <c r="F83" s="82"/>
+      <c r="G83" s="82"/>
+      <c r="H83" s="82"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1">
         <v>4.0252880405239402E-2</v>
@@ -10364,16 +10360,16 @@
       <c r="P83" s="1"/>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="85"/>
+      <c r="A84" s="79"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="79"/>
-      <c r="D84" s="79"/>
-      <c r="E84" s="79"/>
-      <c r="F84" s="79"/>
-      <c r="G84" s="79"/>
-      <c r="H84" s="79"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1">
         <v>0.42132164214255802</v>
@@ -10396,16 +10392,16 @@
       <c r="P84" s="1"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="85"/>
+      <c r="A85" s="79"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="79"/>
+      <c r="C85" s="82"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
+      <c r="H85" s="82"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1">
         <v>7.8254362282741005E-2</v>
@@ -10428,16 +10424,16 @@
       <c r="P85" s="1"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="99"/>
+      <c r="A86" s="80"/>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="79"/>
+      <c r="C86" s="82"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1">
         <v>2.6614614752845599E-3</v>
@@ -10460,7 +10456,7 @@
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="87" t="s">
+      <c r="A87" s="92" t="s">
         <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -10485,18 +10481,18 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I87" s="1"/>
-      <c r="J87" s="79" t="s">
+      <c r="J87" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K87" s="79"/>
-      <c r="L87" s="79"/>
-      <c r="M87" s="79"/>
-      <c r="N87" s="79"/>
-      <c r="O87" s="79"/>
+      <c r="K87" s="82"/>
+      <c r="L87" s="82"/>
+      <c r="M87" s="82"/>
+      <c r="N87" s="82"/>
+      <c r="O87" s="82"/>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="85"/>
+      <c r="A88" s="79"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
@@ -10519,16 +10515,16 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I88" s="1"/>
-      <c r="J88" s="79"/>
-      <c r="K88" s="79"/>
-      <c r="L88" s="79"/>
-      <c r="M88" s="79"/>
-      <c r="N88" s="79"/>
-      <c r="O88" s="79"/>
+      <c r="J88" s="82"/>
+      <c r="K88" s="82"/>
+      <c r="L88" s="82"/>
+      <c r="M88" s="82"/>
+      <c r="N88" s="82"/>
+      <c r="O88" s="82"/>
       <c r="P88" s="1"/>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="85"/>
+      <c r="A89" s="79"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
       </c>
@@ -10551,36 +10547,36 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I89" s="1"/>
-      <c r="J89" s="79"/>
-      <c r="K89" s="79"/>
-      <c r="L89" s="79"/>
-      <c r="M89" s="79"/>
-      <c r="N89" s="79"/>
-      <c r="O89" s="79"/>
+      <c r="J89" s="82"/>
+      <c r="K89" s="82"/>
+      <c r="L89" s="82"/>
+      <c r="M89" s="82"/>
+      <c r="N89" s="82"/>
+      <c r="O89" s="82"/>
       <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="99"/>
+      <c r="A90" s="80"/>
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="105"/>
-      <c r="D90" s="105"/>
-      <c r="E90" s="105"/>
-      <c r="F90" s="105"/>
-      <c r="G90" s="105"/>
-      <c r="H90" s="105"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
+      <c r="E90" s="85"/>
+      <c r="F90" s="85"/>
+      <c r="G90" s="85"/>
+      <c r="H90" s="85"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="79"/>
-      <c r="K90" s="79"/>
-      <c r="L90" s="79"/>
-      <c r="M90" s="79"/>
-      <c r="N90" s="79"/>
-      <c r="O90" s="79"/>
+      <c r="J90" s="82"/>
+      <c r="K90" s="82"/>
+      <c r="L90" s="82"/>
+      <c r="M90" s="82"/>
+      <c r="N90" s="82"/>
+      <c r="O90" s="82"/>
       <c r="P90" s="1"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="87" t="s">
+      <c r="A91" s="92" t="s">
         <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -10605,18 +10601,18 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I91" s="1"/>
-      <c r="J91" s="79" t="s">
+      <c r="J91" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K91" s="79"/>
-      <c r="L91" s="79"/>
-      <c r="M91" s="79"/>
-      <c r="N91" s="79"/>
-      <c r="O91" s="79"/>
+      <c r="K91" s="82"/>
+      <c r="L91" s="82"/>
+      <c r="M91" s="82"/>
+      <c r="N91" s="82"/>
+      <c r="O91" s="82"/>
       <c r="P91" s="1"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="85"/>
+      <c r="A92" s="79"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
@@ -10639,16 +10635,16 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="79"/>
-      <c r="K92" s="79"/>
-      <c r="L92" s="79"/>
-      <c r="M92" s="79"/>
-      <c r="N92" s="79"/>
-      <c r="O92" s="79"/>
+      <c r="J92" s="82"/>
+      <c r="K92" s="82"/>
+      <c r="L92" s="82"/>
+      <c r="M92" s="82"/>
+      <c r="N92" s="82"/>
+      <c r="O92" s="82"/>
       <c r="P92" s="1"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="85"/>
+      <c r="A93" s="79"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
@@ -10671,36 +10667,36 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I93" s="1"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="79"/>
-      <c r="L93" s="79"/>
-      <c r="M93" s="79"/>
-      <c r="N93" s="79"/>
-      <c r="O93" s="79"/>
+      <c r="J93" s="82"/>
+      <c r="K93" s="82"/>
+      <c r="L93" s="82"/>
+      <c r="M93" s="82"/>
+      <c r="N93" s="82"/>
+      <c r="O93" s="82"/>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="99"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="105"/>
-      <c r="D94" s="105"/>
-      <c r="E94" s="105"/>
-      <c r="F94" s="105"/>
-      <c r="G94" s="105"/>
-      <c r="H94" s="105"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
+      <c r="E94" s="85"/>
+      <c r="F94" s="85"/>
+      <c r="G94" s="85"/>
+      <c r="H94" s="85"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="79"/>
-      <c r="K94" s="79"/>
-      <c r="L94" s="79"/>
-      <c r="M94" s="79"/>
-      <c r="N94" s="79"/>
-      <c r="O94" s="79"/>
+      <c r="J94" s="82"/>
+      <c r="K94" s="82"/>
+      <c r="L94" s="82"/>
+      <c r="M94" s="82"/>
+      <c r="N94" s="82"/>
+      <c r="O94" s="82"/>
       <c r="P94" s="1"/>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="87" t="s">
+      <c r="A95" s="92" t="s">
         <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -10725,18 +10721,18 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I95" s="1"/>
-      <c r="J95" s="79" t="s">
+      <c r="J95" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K95" s="79"/>
-      <c r="L95" s="79"/>
-      <c r="M95" s="79"/>
-      <c r="N95" s="79"/>
-      <c r="O95" s="79"/>
+      <c r="K95" s="82"/>
+      <c r="L95" s="82"/>
+      <c r="M95" s="82"/>
+      <c r="N95" s="82"/>
+      <c r="O95" s="82"/>
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="85"/>
+      <c r="A96" s="79"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
@@ -10759,16 +10755,16 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I96" s="1"/>
-      <c r="J96" s="79"/>
-      <c r="K96" s="79"/>
-      <c r="L96" s="79"/>
-      <c r="M96" s="79"/>
-      <c r="N96" s="79"/>
-      <c r="O96" s="79"/>
+      <c r="J96" s="82"/>
+      <c r="K96" s="82"/>
+      <c r="L96" s="82"/>
+      <c r="M96" s="82"/>
+      <c r="N96" s="82"/>
+      <c r="O96" s="82"/>
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="85"/>
+      <c r="A97" s="79"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
       </c>
@@ -10791,36 +10787,36 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="79"/>
-      <c r="K97" s="79"/>
-      <c r="L97" s="79"/>
-      <c r="M97" s="79"/>
-      <c r="N97" s="79"/>
-      <c r="O97" s="79"/>
+      <c r="J97" s="82"/>
+      <c r="K97" s="82"/>
+      <c r="L97" s="82"/>
+      <c r="M97" s="82"/>
+      <c r="N97" s="82"/>
+      <c r="O97" s="82"/>
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="99"/>
+      <c r="A98" s="80"/>
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="105"/>
-      <c r="D98" s="105"/>
-      <c r="E98" s="105"/>
-      <c r="F98" s="105"/>
-      <c r="G98" s="105"/>
-      <c r="H98" s="105"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
+      <c r="E98" s="85"/>
+      <c r="F98" s="85"/>
+      <c r="G98" s="85"/>
+      <c r="H98" s="85"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="79"/>
-      <c r="K98" s="79"/>
-      <c r="L98" s="79"/>
-      <c r="M98" s="79"/>
-      <c r="N98" s="79"/>
-      <c r="O98" s="79"/>
+      <c r="J98" s="82"/>
+      <c r="K98" s="82"/>
+      <c r="L98" s="82"/>
+      <c r="M98" s="82"/>
+      <c r="N98" s="82"/>
+      <c r="O98" s="82"/>
       <c r="P98" s="1"/>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="87" t="s">
+      <c r="A99" s="92" t="s">
         <v>30</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -10845,18 +10841,18 @@
         <v>3.8248319558473298E-23</v>
       </c>
       <c r="I99" s="1"/>
-      <c r="J99" s="79" t="s">
+      <c r="J99" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K99" s="79"/>
-      <c r="L99" s="79"/>
-      <c r="M99" s="79"/>
-      <c r="N99" s="79"/>
-      <c r="O99" s="79"/>
+      <c r="K99" s="82"/>
+      <c r="L99" s="82"/>
+      <c r="M99" s="82"/>
+      <c r="N99" s="82"/>
+      <c r="O99" s="82"/>
       <c r="P99" s="1"/>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="85"/>
+      <c r="A100" s="79"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
@@ -10879,16 +10875,16 @@
         <v>0.27985440517664001</v>
       </c>
       <c r="I100" s="1"/>
-      <c r="J100" s="79"/>
-      <c r="K100" s="79"/>
-      <c r="L100" s="79"/>
-      <c r="M100" s="79"/>
-      <c r="N100" s="79"/>
-      <c r="O100" s="79"/>
+      <c r="J100" s="82"/>
+      <c r="K100" s="82"/>
+      <c r="L100" s="82"/>
+      <c r="M100" s="82"/>
+      <c r="N100" s="82"/>
+      <c r="O100" s="82"/>
       <c r="P100" s="1"/>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="85"/>
+      <c r="A101" s="79"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
       </c>
@@ -10911,49 +10907,49 @@
         <v>0.72495214931683005</v>
       </c>
       <c r="I101" s="1"/>
-      <c r="J101" s="79"/>
-      <c r="K101" s="79"/>
-      <c r="L101" s="79"/>
-      <c r="M101" s="79"/>
-      <c r="N101" s="79"/>
-      <c r="O101" s="79"/>
+      <c r="J101" s="82"/>
+      <c r="K101" s="82"/>
+      <c r="L101" s="82"/>
+      <c r="M101" s="82"/>
+      <c r="N101" s="82"/>
+      <c r="O101" s="82"/>
       <c r="P101" s="1"/>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="99"/>
+      <c r="A102" s="80"/>
       <c r="B102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C102" s="105"/>
-      <c r="D102" s="105"/>
-      <c r="E102" s="105"/>
-      <c r="F102" s="105"/>
-      <c r="G102" s="105"/>
-      <c r="H102" s="105"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="79"/>
-      <c r="K102" s="79"/>
-      <c r="L102" s="79"/>
-      <c r="M102" s="79"/>
-      <c r="N102" s="79"/>
-      <c r="O102" s="79"/>
+      <c r="J102" s="82"/>
+      <c r="K102" s="82"/>
+      <c r="L102" s="82"/>
+      <c r="M102" s="82"/>
+      <c r="N102" s="82"/>
+      <c r="O102" s="82"/>
       <c r="P102" s="1"/>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="87" t="s">
+      <c r="A103" s="92" t="s">
         <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="79" t="s">
+      <c r="C103" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D103" s="79"/>
-      <c r="E103" s="79"/>
-      <c r="F103" s="79"/>
-      <c r="G103" s="79"/>
-      <c r="H103" s="79"/>
+      <c r="D103" s="82"/>
+      <c r="E103" s="82"/>
+      <c r="F103" s="82"/>
+      <c r="G103" s="82"/>
+      <c r="H103" s="82"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
         <v>4.9920514192076698E-4</v>
@@ -10976,16 +10972,16 @@
       <c r="P103" s="1"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="85"/>
+      <c r="A104" s="79"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="79"/>
-      <c r="D104" s="79"/>
-      <c r="E104" s="79"/>
-      <c r="F104" s="79"/>
-      <c r="G104" s="79"/>
-      <c r="H104" s="79"/>
+      <c r="C104" s="82"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="82"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="82"/>
+      <c r="H104" s="82"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
         <v>4.3245963051368403E-3</v>
@@ -11008,16 +11004,16 @@
       <c r="P104" s="1"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="85"/>
+      <c r="A105" s="79"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="79"/>
-      <c r="D105" s="79"/>
-      <c r="E105" s="79"/>
-      <c r="F105" s="79"/>
-      <c r="G105" s="79"/>
-      <c r="H105" s="79"/>
+      <c r="C105" s="82"/>
+      <c r="D105" s="82"/>
+      <c r="E105" s="82"/>
+      <c r="F105" s="82"/>
+      <c r="G105" s="82"/>
+      <c r="H105" s="82"/>
       <c r="I105" s="1"/>
       <c r="J105" s="5">
         <v>4.4673218852987901E-5</v>
@@ -11040,16 +11036,16 @@
       <c r="P105" s="1"/>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="99"/>
+      <c r="A106" s="80"/>
       <c r="B106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C106" s="79"/>
-      <c r="D106" s="79"/>
-      <c r="E106" s="79"/>
-      <c r="F106" s="79"/>
-      <c r="G106" s="79"/>
-      <c r="H106" s="79"/>
+      <c r="C106" s="82"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="82"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
+      <c r="H106" s="82"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
         <v>2.5092673060789E-4</v>
@@ -11072,20 +11068,20 @@
       <c r="P106" s="1"/>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="92" t="s">
         <v>29</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="79" t="s">
+      <c r="C107" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D107" s="79"/>
-      <c r="E107" s="79"/>
-      <c r="F107" s="79"/>
-      <c r="G107" s="79"/>
-      <c r="H107" s="79"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="82"/>
+      <c r="H107" s="82"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
         <v>1.4241127553301099E-4</v>
@@ -11108,16 +11104,16 @@
       <c r="P107" s="1"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="85"/>
+      <c r="A108" s="79"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="79"/>
-      <c r="D108" s="79"/>
-      <c r="E108" s="79"/>
-      <c r="F108" s="79"/>
-      <c r="G108" s="79"/>
-      <c r="H108" s="79"/>
+      <c r="C108" s="82"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="82"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="82"/>
+      <c r="H108" s="82"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
         <v>4.6725153189010001E-2</v>
@@ -11140,16 +11136,16 @@
       <c r="P108" s="1"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="85"/>
+      <c r="A109" s="79"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="79"/>
-      <c r="D109" s="79"/>
-      <c r="E109" s="79"/>
-      <c r="F109" s="79"/>
-      <c r="G109" s="79"/>
-      <c r="H109" s="79"/>
+      <c r="C109" s="82"/>
+      <c r="D109" s="82"/>
+      <c r="E109" s="82"/>
+      <c r="F109" s="82"/>
+      <c r="G109" s="82"/>
+      <c r="H109" s="82"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1">
         <v>2.8302586845141399E-2</v>
@@ -11172,16 +11168,16 @@
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="99"/>
+      <c r="A110" s="80"/>
       <c r="B110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C110" s="79"/>
-      <c r="D110" s="79"/>
-      <c r="E110" s="79"/>
-      <c r="F110" s="79"/>
-      <c r="G110" s="79"/>
-      <c r="H110" s="79"/>
+      <c r="C110" s="82"/>
+      <c r="D110" s="82"/>
+      <c r="E110" s="82"/>
+      <c r="F110" s="82"/>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1">
         <v>6.3796317056246301E-3</v>
@@ -11204,7 +11200,7 @@
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="87" t="s">
+      <c r="A111" s="92" t="s">
         <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -11229,18 +11225,18 @@
         <v>2.5160186313214301E-3</v>
       </c>
       <c r="I111" s="1"/>
-      <c r="J111" s="79" t="s">
+      <c r="J111" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K111" s="79"/>
-      <c r="L111" s="79"/>
-      <c r="M111" s="79"/>
-      <c r="N111" s="79"/>
-      <c r="O111" s="79"/>
+      <c r="K111" s="82"/>
+      <c r="L111" s="82"/>
+      <c r="M111" s="82"/>
+      <c r="N111" s="82"/>
+      <c r="O111" s="82"/>
       <c r="P111" s="1"/>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="85"/>
+      <c r="A112" s="79"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
@@ -11263,16 +11259,16 @@
         <v>0.13226601261193599</v>
       </c>
       <c r="I112" s="1"/>
-      <c r="J112" s="79"/>
-      <c r="K112" s="79"/>
-      <c r="L112" s="79"/>
-      <c r="M112" s="79"/>
-      <c r="N112" s="79"/>
-      <c r="O112" s="79"/>
+      <c r="J112" s="82"/>
+      <c r="K112" s="82"/>
+      <c r="L112" s="82"/>
+      <c r="M112" s="82"/>
+      <c r="N112" s="82"/>
+      <c r="O112" s="82"/>
       <c r="P112" s="1"/>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" s="85"/>
+      <c r="A113" s="79"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
       </c>
@@ -11295,36 +11291,36 @@
         <v>1.67603779088435E-5</v>
       </c>
       <c r="I113" s="1"/>
-      <c r="J113" s="79"/>
-      <c r="K113" s="79"/>
-      <c r="L113" s="79"/>
-      <c r="M113" s="79"/>
-      <c r="N113" s="79"/>
-      <c r="O113" s="79"/>
+      <c r="J113" s="82"/>
+      <c r="K113" s="82"/>
+      <c r="L113" s="82"/>
+      <c r="M113" s="82"/>
+      <c r="N113" s="82"/>
+      <c r="O113" s="82"/>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" s="99"/>
+      <c r="A114" s="80"/>
       <c r="B114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="105"/>
-      <c r="D114" s="105"/>
-      <c r="E114" s="105"/>
-      <c r="F114" s="105"/>
-      <c r="G114" s="105"/>
-      <c r="H114" s="105"/>
+      <c r="C114" s="85"/>
+      <c r="D114" s="85"/>
+      <c r="E114" s="85"/>
+      <c r="F114" s="85"/>
+      <c r="G114" s="85"/>
+      <c r="H114" s="85"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="79"/>
-      <c r="K114" s="79"/>
-      <c r="L114" s="79"/>
-      <c r="M114" s="79"/>
-      <c r="N114" s="79"/>
-      <c r="O114" s="79"/>
+      <c r="J114" s="82"/>
+      <c r="K114" s="82"/>
+      <c r="L114" s="82"/>
+      <c r="M114" s="82"/>
+      <c r="N114" s="82"/>
+      <c r="O114" s="82"/>
       <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" s="87" t="s">
+      <c r="A115" s="92" t="s">
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -11349,18 +11345,18 @@
         <v>3.1891308959839999E-11</v>
       </c>
       <c r="I115" s="1"/>
-      <c r="J115" s="79" t="s">
+      <c r="J115" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K115" s="79"/>
-      <c r="L115" s="79"/>
-      <c r="M115" s="79"/>
-      <c r="N115" s="79"/>
-      <c r="O115" s="79"/>
+      <c r="K115" s="82"/>
+      <c r="L115" s="82"/>
+      <c r="M115" s="82"/>
+      <c r="N115" s="82"/>
+      <c r="O115" s="82"/>
       <c r="P115" s="1"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A116" s="85"/>
+      <c r="A116" s="79"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
@@ -11383,16 +11379,16 @@
         <v>1.9668218703936501E-2</v>
       </c>
       <c r="I116" s="1"/>
-      <c r="J116" s="79"/>
-      <c r="K116" s="79"/>
-      <c r="L116" s="79"/>
-      <c r="M116" s="79"/>
-      <c r="N116" s="79"/>
-      <c r="O116" s="79"/>
+      <c r="J116" s="82"/>
+      <c r="K116" s="82"/>
+      <c r="L116" s="82"/>
+      <c r="M116" s="82"/>
+      <c r="N116" s="82"/>
+      <c r="O116" s="82"/>
       <c r="P116" s="1"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="85"/>
+      <c r="A117" s="79"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
       </c>
@@ -11415,36 +11411,36 @@
         <v>6.4583181614334004E-2</v>
       </c>
       <c r="I117" s="1"/>
-      <c r="J117" s="79"/>
-      <c r="K117" s="79"/>
-      <c r="L117" s="79"/>
-      <c r="M117" s="79"/>
-      <c r="N117" s="79"/>
-      <c r="O117" s="79"/>
+      <c r="J117" s="82"/>
+      <c r="K117" s="82"/>
+      <c r="L117" s="82"/>
+      <c r="M117" s="82"/>
+      <c r="N117" s="82"/>
+      <c r="O117" s="82"/>
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A118" s="99"/>
+      <c r="A118" s="80"/>
       <c r="B118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="105"/>
-      <c r="D118" s="105"/>
-      <c r="E118" s="105"/>
-      <c r="F118" s="105"/>
-      <c r="G118" s="105"/>
-      <c r="H118" s="105"/>
+      <c r="C118" s="85"/>
+      <c r="D118" s="85"/>
+      <c r="E118" s="85"/>
+      <c r="F118" s="85"/>
+      <c r="G118" s="85"/>
+      <c r="H118" s="85"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="79"/>
-      <c r="K118" s="79"/>
-      <c r="L118" s="79"/>
-      <c r="M118" s="79"/>
-      <c r="N118" s="79"/>
-      <c r="O118" s="79"/>
+      <c r="J118" s="82"/>
+      <c r="K118" s="82"/>
+      <c r="L118" s="82"/>
+      <c r="M118" s="82"/>
+      <c r="N118" s="82"/>
+      <c r="O118" s="82"/>
       <c r="P118" s="1"/>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A119" s="87" t="s">
+      <c r="A119" s="92" t="s">
         <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -11469,18 +11465,18 @@
         <v>7.05414701429731E-35</v>
       </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="79" t="s">
+      <c r="J119" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K119" s="79"/>
-      <c r="L119" s="79"/>
-      <c r="M119" s="79"/>
-      <c r="N119" s="79"/>
-      <c r="O119" s="79"/>
+      <c r="K119" s="82"/>
+      <c r="L119" s="82"/>
+      <c r="M119" s="82"/>
+      <c r="N119" s="82"/>
+      <c r="O119" s="82"/>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" s="85"/>
+      <c r="A120" s="79"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
@@ -11503,16 +11499,16 @@
         <v>3.9509565365961799E-2</v>
       </c>
       <c r="I120" s="1"/>
-      <c r="J120" s="79"/>
-      <c r="K120" s="79"/>
-      <c r="L120" s="79"/>
-      <c r="M120" s="79"/>
-      <c r="N120" s="79"/>
-      <c r="O120" s="79"/>
+      <c r="J120" s="82"/>
+      <c r="K120" s="82"/>
+      <c r="L120" s="82"/>
+      <c r="M120" s="82"/>
+      <c r="N120" s="82"/>
+      <c r="O120" s="82"/>
       <c r="P120" s="1"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" s="85"/>
+      <c r="A121" s="79"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
       </c>
@@ -11535,36 +11531,36 @@
         <v>1.2703272318058401E-2</v>
       </c>
       <c r="I121" s="1"/>
-      <c r="J121" s="79"/>
-      <c r="K121" s="79"/>
-      <c r="L121" s="79"/>
-      <c r="M121" s="79"/>
-      <c r="N121" s="79"/>
-      <c r="O121" s="79"/>
+      <c r="J121" s="82"/>
+      <c r="K121" s="82"/>
+      <c r="L121" s="82"/>
+      <c r="M121" s="82"/>
+      <c r="N121" s="82"/>
+      <c r="O121" s="82"/>
       <c r="P121" s="1"/>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" s="99"/>
+      <c r="A122" s="80"/>
       <c r="B122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="105"/>
-      <c r="D122" s="105"/>
-      <c r="E122" s="105"/>
-      <c r="F122" s="105"/>
-      <c r="G122" s="105"/>
-      <c r="H122" s="105"/>
+      <c r="C122" s="85"/>
+      <c r="D122" s="85"/>
+      <c r="E122" s="85"/>
+      <c r="F122" s="85"/>
+      <c r="G122" s="85"/>
+      <c r="H122" s="85"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="79"/>
-      <c r="K122" s="79"/>
-      <c r="L122" s="79"/>
-      <c r="M122" s="79"/>
-      <c r="N122" s="79"/>
-      <c r="O122" s="79"/>
+      <c r="J122" s="82"/>
+      <c r="K122" s="82"/>
+      <c r="L122" s="82"/>
+      <c r="M122" s="82"/>
+      <c r="N122" s="82"/>
+      <c r="O122" s="82"/>
       <c r="P122" s="1"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="87" t="s">
+      <c r="A123" s="92" t="s">
         <v>151</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -11589,18 +11585,18 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I123" s="1"/>
-      <c r="J123" s="79" t="s">
+      <c r="J123" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K123" s="79"/>
-      <c r="L123" s="79"/>
-      <c r="M123" s="79"/>
-      <c r="N123" s="79"/>
-      <c r="O123" s="79"/>
+      <c r="K123" s="82"/>
+      <c r="L123" s="82"/>
+      <c r="M123" s="82"/>
+      <c r="N123" s="82"/>
+      <c r="O123" s="82"/>
       <c r="P123" s="1"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" s="85"/>
+      <c r="A124" s="79"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
@@ -11623,16 +11619,16 @@
         <v>0.2597892</v>
       </c>
       <c r="I124" s="1"/>
-      <c r="J124" s="79"/>
-      <c r="K124" s="79"/>
-      <c r="L124" s="79"/>
-      <c r="M124" s="79"/>
-      <c r="N124" s="79"/>
-      <c r="O124" s="79"/>
+      <c r="J124" s="82"/>
+      <c r="K124" s="82"/>
+      <c r="L124" s="82"/>
+      <c r="M124" s="82"/>
+      <c r="N124" s="82"/>
+      <c r="O124" s="82"/>
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="85"/>
+      <c r="A125" s="79"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
@@ -11655,36 +11651,36 @@
         <v>0.7055884</v>
       </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="79"/>
-      <c r="K125" s="79"/>
-      <c r="L125" s="79"/>
-      <c r="M125" s="79"/>
-      <c r="N125" s="79"/>
-      <c r="O125" s="79"/>
+      <c r="J125" s="82"/>
+      <c r="K125" s="82"/>
+      <c r="L125" s="82"/>
+      <c r="M125" s="82"/>
+      <c r="N125" s="82"/>
+      <c r="O125" s="82"/>
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="99"/>
+      <c r="A126" s="80"/>
       <c r="B126" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="105"/>
-      <c r="D126" s="105"/>
-      <c r="E126" s="105"/>
-      <c r="F126" s="105"/>
-      <c r="G126" s="105"/>
-      <c r="H126" s="105"/>
+      <c r="C126" s="85"/>
+      <c r="D126" s="85"/>
+      <c r="E126" s="85"/>
+      <c r="F126" s="85"/>
+      <c r="G126" s="85"/>
+      <c r="H126" s="85"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="79"/>
-      <c r="K126" s="79"/>
-      <c r="L126" s="79"/>
-      <c r="M126" s="79"/>
-      <c r="N126" s="79"/>
-      <c r="O126" s="79"/>
+      <c r="J126" s="82"/>
+      <c r="K126" s="82"/>
+      <c r="L126" s="82"/>
+      <c r="M126" s="82"/>
+      <c r="N126" s="82"/>
+      <c r="O126" s="82"/>
       <c r="P126" s="1"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" s="87" t="s">
+      <c r="A127" s="92" t="s">
         <v>34</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -11709,18 +11705,18 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I127" s="1"/>
-      <c r="J127" s="79" t="s">
+      <c r="J127" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K127" s="79"/>
-      <c r="L127" s="79"/>
-      <c r="M127" s="79"/>
-      <c r="N127" s="79"/>
-      <c r="O127" s="79"/>
+      <c r="K127" s="82"/>
+      <c r="L127" s="82"/>
+      <c r="M127" s="82"/>
+      <c r="N127" s="82"/>
+      <c r="O127" s="82"/>
       <c r="P127" s="1"/>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" s="85"/>
+      <c r="A128" s="79"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
@@ -11743,16 +11739,16 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I128" s="1"/>
-      <c r="J128" s="79"/>
-      <c r="K128" s="79"/>
-      <c r="L128" s="79"/>
-      <c r="M128" s="79"/>
-      <c r="N128" s="79"/>
-      <c r="O128" s="79"/>
+      <c r="J128" s="82"/>
+      <c r="K128" s="82"/>
+      <c r="L128" s="82"/>
+      <c r="M128" s="82"/>
+      <c r="N128" s="82"/>
+      <c r="O128" s="82"/>
       <c r="P128" s="1"/>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" s="85"/>
+      <c r="A129" s="79"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
       </c>
@@ -11775,36 +11771,36 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I129" s="1"/>
-      <c r="J129" s="79"/>
-      <c r="K129" s="79"/>
-      <c r="L129" s="79"/>
-      <c r="M129" s="79"/>
-      <c r="N129" s="79"/>
-      <c r="O129" s="79"/>
+      <c r="J129" s="82"/>
+      <c r="K129" s="82"/>
+      <c r="L129" s="82"/>
+      <c r="M129" s="82"/>
+      <c r="N129" s="82"/>
+      <c r="O129" s="82"/>
       <c r="P129" s="1"/>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" s="99"/>
+      <c r="A130" s="80"/>
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C130" s="105"/>
-      <c r="D130" s="105"/>
-      <c r="E130" s="105"/>
-      <c r="F130" s="105"/>
-      <c r="G130" s="105"/>
-      <c r="H130" s="105"/>
+      <c r="C130" s="85"/>
+      <c r="D130" s="85"/>
+      <c r="E130" s="85"/>
+      <c r="F130" s="85"/>
+      <c r="G130" s="85"/>
+      <c r="H130" s="85"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="79"/>
-      <c r="K130" s="79"/>
-      <c r="L130" s="79"/>
-      <c r="M130" s="79"/>
-      <c r="N130" s="79"/>
-      <c r="O130" s="79"/>
+      <c r="J130" s="82"/>
+      <c r="K130" s="82"/>
+      <c r="L130" s="82"/>
+      <c r="M130" s="82"/>
+      <c r="N130" s="82"/>
+      <c r="O130" s="82"/>
       <c r="P130" s="1"/>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" s="87" t="s">
+      <c r="A131" s="92" t="s">
         <v>35</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -11829,18 +11825,18 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I131" s="1"/>
-      <c r="J131" s="79" t="s">
+      <c r="J131" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K131" s="79"/>
-      <c r="L131" s="79"/>
-      <c r="M131" s="79"/>
-      <c r="N131" s="79"/>
-      <c r="O131" s="79"/>
+      <c r="K131" s="82"/>
+      <c r="L131" s="82"/>
+      <c r="M131" s="82"/>
+      <c r="N131" s="82"/>
+      <c r="O131" s="82"/>
       <c r="P131" s="1"/>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" s="85"/>
+      <c r="A132" s="79"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
@@ -11863,16 +11859,16 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I132" s="1"/>
-      <c r="J132" s="79"/>
-      <c r="K132" s="79"/>
-      <c r="L132" s="79"/>
-      <c r="M132" s="79"/>
-      <c r="N132" s="79"/>
-      <c r="O132" s="79"/>
+      <c r="J132" s="82"/>
+      <c r="K132" s="82"/>
+      <c r="L132" s="82"/>
+      <c r="M132" s="82"/>
+      <c r="N132" s="82"/>
+      <c r="O132" s="82"/>
       <c r="P132" s="1"/>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" s="85"/>
+      <c r="A133" s="79"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
       </c>
@@ -11895,36 +11891,36 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I133" s="1"/>
-      <c r="J133" s="79"/>
-      <c r="K133" s="79"/>
-      <c r="L133" s="79"/>
-      <c r="M133" s="79"/>
-      <c r="N133" s="79"/>
-      <c r="O133" s="79"/>
+      <c r="J133" s="82"/>
+      <c r="K133" s="82"/>
+      <c r="L133" s="82"/>
+      <c r="M133" s="82"/>
+      <c r="N133" s="82"/>
+      <c r="O133" s="82"/>
       <c r="P133" s="1"/>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" s="99"/>
+      <c r="A134" s="80"/>
       <c r="B134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="105"/>
-      <c r="D134" s="105"/>
-      <c r="E134" s="105"/>
-      <c r="F134" s="105"/>
-      <c r="G134" s="105"/>
-      <c r="H134" s="105"/>
+      <c r="C134" s="85"/>
+      <c r="D134" s="85"/>
+      <c r="E134" s="85"/>
+      <c r="F134" s="85"/>
+      <c r="G134" s="85"/>
+      <c r="H134" s="85"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="79"/>
-      <c r="K134" s="79"/>
-      <c r="L134" s="79"/>
-      <c r="M134" s="79"/>
-      <c r="N134" s="79"/>
-      <c r="O134" s="79"/>
+      <c r="J134" s="82"/>
+      <c r="K134" s="82"/>
+      <c r="L134" s="82"/>
+      <c r="M134" s="82"/>
+      <c r="N134" s="82"/>
+      <c r="O134" s="82"/>
       <c r="P134" s="1"/>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" s="87" t="s">
+      <c r="A135" s="92" t="s">
         <v>25</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -11949,18 +11945,18 @@
         <v>1.209274E-27</v>
       </c>
       <c r="I135" s="1"/>
-      <c r="J135" s="79" t="s">
+      <c r="J135" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="K135" s="79"/>
-      <c r="L135" s="79"/>
-      <c r="M135" s="79"/>
-      <c r="N135" s="79"/>
-      <c r="O135" s="79"/>
+      <c r="K135" s="82"/>
+      <c r="L135" s="82"/>
+      <c r="M135" s="82"/>
+      <c r="N135" s="82"/>
+      <c r="O135" s="82"/>
       <c r="P135" s="1"/>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" s="85"/>
+      <c r="A136" s="79"/>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
@@ -11983,16 +11979,16 @@
         <v>5.7713939999999998E-2</v>
       </c>
       <c r="I136" s="1"/>
-      <c r="J136" s="79"/>
-      <c r="K136" s="79"/>
-      <c r="L136" s="79"/>
-      <c r="M136" s="79"/>
-      <c r="N136" s="79"/>
-      <c r="O136" s="79"/>
+      <c r="J136" s="82"/>
+      <c r="K136" s="82"/>
+      <c r="L136" s="82"/>
+      <c r="M136" s="82"/>
+      <c r="N136" s="82"/>
+      <c r="O136" s="82"/>
       <c r="P136" s="1"/>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" s="85"/>
+      <c r="A137" s="79"/>
       <c r="B137" s="1" t="s">
         <v>8</v>
       </c>
@@ -12015,32 +12011,32 @@
         <v>1.363103E-6</v>
       </c>
       <c r="I137" s="1"/>
-      <c r="J137" s="79"/>
-      <c r="K137" s="79"/>
-      <c r="L137" s="79"/>
-      <c r="M137" s="79"/>
-      <c r="N137" s="79"/>
-      <c r="O137" s="79"/>
+      <c r="J137" s="82"/>
+      <c r="K137" s="82"/>
+      <c r="L137" s="82"/>
+      <c r="M137" s="82"/>
+      <c r="N137" s="82"/>
+      <c r="O137" s="82"/>
       <c r="P137" s="1"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" s="99"/>
+      <c r="A138" s="80"/>
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="105"/>
-      <c r="D138" s="105"/>
-      <c r="E138" s="105"/>
-      <c r="F138" s="105"/>
-      <c r="G138" s="105"/>
-      <c r="H138" s="105"/>
+      <c r="C138" s="85"/>
+      <c r="D138" s="85"/>
+      <c r="E138" s="85"/>
+      <c r="F138" s="85"/>
+      <c r="G138" s="85"/>
+      <c r="H138" s="85"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="79"/>
-      <c r="K138" s="79"/>
-      <c r="L138" s="79"/>
-      <c r="M138" s="79"/>
-      <c r="N138" s="79"/>
-      <c r="O138" s="79"/>
+      <c r="J138" s="82"/>
+      <c r="K138" s="82"/>
+      <c r="L138" s="82"/>
+      <c r="M138" s="82"/>
+      <c r="N138" s="82"/>
+      <c r="O138" s="82"/>
       <c r="P138" s="1"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
@@ -12063,68 +12059,14 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -12141,14 +12083,68 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12186,22 +12182,22 @@
       <c r="B1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="102">
+      <c r="C1" s="104">
         <v>2021</v>
       </c>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="102">
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="104">
         <v>2022</v>
       </c>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="104"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="106"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12246,7 +12242,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="92" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -12268,17 +12264,17 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="90"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="95"/>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="1" t="s">
         <v>107</v>
       </c>
@@ -12298,15 +12294,15 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="93"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="98"/>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="85"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="1" t="s">
         <v>117</v>
       </c>
@@ -12326,15 +12322,15 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="93"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="98"/>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="99"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="1" t="s">
         <v>109</v>
       </c>
@@ -12354,15 +12350,15 @@
         <v>0.1837454</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="108"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="109"/>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="92" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -12402,7 +12398,7 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="1" t="s">
         <v>107</v>
       </c>
@@ -12440,7 +12436,7 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="85"/>
+      <c r="A9" s="79"/>
       <c r="B9" s="1" t="s">
         <v>108</v>
       </c>
@@ -12478,7 +12474,7 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="99"/>
+      <c r="A10" s="80"/>
       <c r="B10" s="1" t="s">
         <v>109</v>
       </c>
@@ -12516,7 +12512,7 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="92" t="s">
         <v>141</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -12538,17 +12534,17 @@
         <v>0.35833147122850001</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="88" t="s">
+      <c r="I11" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="90"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="95"/>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="85"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="1" t="s">
         <v>107</v>
       </c>
@@ -12568,15 +12564,15 @@
         <v>0.11792329999999999</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="93"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="98"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="1" t="s">
         <v>108</v>
       </c>
@@ -12596,15 +12592,15 @@
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="93"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="98"/>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="99"/>
+      <c r="A14" s="80"/>
       <c r="B14" s="1" t="s">
         <v>109</v>
       </c>
@@ -12624,15 +12620,15 @@
         <v>1.280514E-6</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="108"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="109"/>
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="92" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -12672,7 +12668,7 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
@@ -12710,7 +12706,7 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="1" t="s">
         <v>108</v>
       </c>
@@ -12748,7 +12744,7 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="99"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="1" t="s">
         <v>109</v>
       </c>
@@ -12786,7 +12782,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="92" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -12826,7 +12822,7 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="85"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="1" t="s">
         <v>107</v>
       </c>
@@ -12864,7 +12860,7 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="1" t="s">
         <v>108</v>
       </c>
@@ -12902,7 +12898,7 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
+      <c r="A22" s="80"/>
       <c r="B22" s="1" t="s">
         <v>109</v>
       </c>
@@ -12940,7 +12936,7 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -12980,7 +12976,7 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="1" t="s">
         <v>107</v>
       </c>
@@ -13018,7 +13014,7 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="1" t="s">
         <v>108</v>
       </c>
@@ -13056,7 +13052,7 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
+      <c r="A26" s="80"/>
       <c r="B26" s="1" t="s">
         <v>109</v>
       </c>
@@ -13094,7 +13090,7 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="92" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -13134,7 +13130,7 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="1" t="s">
         <v>107</v>
       </c>
@@ -13172,7 +13168,7 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="1" t="s">
         <v>108</v>
       </c>
@@ -13210,7 +13206,7 @@
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="99"/>
+      <c r="A30" s="80"/>
       <c r="B30" s="1" t="s">
         <v>109</v>
       </c>
@@ -13248,7 +13244,7 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="92" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -13288,7 +13284,7 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="1" t="s">
         <v>107</v>
       </c>
@@ -13326,7 +13322,7 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
@@ -13364,7 +13360,7 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
+      <c r="A34" s="80"/>
       <c r="B34" s="1" t="s">
         <v>109</v>
       </c>
@@ -13402,7 +13398,7 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="92" t="s">
         <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -13444,7 +13440,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="1" t="s">
         <v>107</v>
       </c>
@@ -13484,7 +13480,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="1" t="s">
         <v>108</v>
       </c>
@@ -13524,7 +13520,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
+      <c r="A38" s="80"/>
       <c r="B38" s="1" t="s">
         <v>109</v>
       </c>
@@ -13564,7 +13560,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="92" t="s">
         <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -13606,7 +13602,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
+      <c r="A40" s="79"/>
       <c r="B40" s="1" t="s">
         <v>107</v>
       </c>
@@ -13646,7 +13642,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
@@ -13686,7 +13682,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
+      <c r="A42" s="80"/>
       <c r="B42" s="1" t="s">
         <v>109</v>
       </c>
@@ -13726,7 +13722,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="87" t="s">
+      <c r="A43" s="92" t="s">
         <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -13766,7 +13762,7 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
+      <c r="A44" s="79"/>
       <c r="B44" s="1" t="s">
         <v>107</v>
       </c>
@@ -13804,7 +13800,7 @@
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="85"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="1" t="s">
         <v>108</v>
       </c>
@@ -13842,7 +13838,7 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="99"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
@@ -13880,19 +13876,19 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="92" t="s">
         <v>147</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="79" t="s">
+      <c r="C47" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="82"/>
+      <c r="F47" s="82"/>
+      <c r="G47" s="82"/>
       <c r="H47" s="1"/>
       <c r="I47" s="45">
         <v>-1.7478199999999999E-2</v>
@@ -13912,15 +13908,15 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="85"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="82"/>
+      <c r="F48" s="82"/>
+      <c r="G48" s="82"/>
       <c r="H48" s="1"/>
       <c r="I48" s="45">
         <v>-2.3552070000000001E-2</v>
@@ -13940,15 +13936,15 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="79"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="79"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="79"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="82"/>
       <c r="H49" s="1"/>
       <c r="I49" s="45">
         <v>-2.6797439999999999E-2</v>
@@ -13968,15 +13964,15 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="99"/>
+      <c r="A50" s="80"/>
       <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="79"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="79"/>
-      <c r="F50" s="79"/>
-      <c r="G50" s="79"/>
+      <c r="C50" s="82"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="82"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="82"/>
       <c r="H50" s="1"/>
       <c r="I50" s="45">
         <v>-3.3645590000000003E-2</v>
@@ -13996,19 +13992,19 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="92" t="s">
         <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="79" t="s">
+      <c r="C51" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="82"/>
       <c r="H51" s="1"/>
       <c r="I51" s="45">
         <v>-8.3753321000000006E-3</v>
@@ -14028,15 +14024,15 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="85"/>
+      <c r="A52" s="79"/>
       <c r="B52" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="79"/>
-      <c r="D52" s="79"/>
-      <c r="E52" s="79"/>
-      <c r="F52" s="79"/>
-      <c r="G52" s="79"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
       <c r="H52" s="1"/>
       <c r="I52" s="45">
         <v>6.2885479999999997E-3</v>
@@ -14056,15 +14052,15 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="85"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="79"/>
-      <c r="D53" s="79"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
       <c r="H53" s="1"/>
       <c r="I53" s="45">
         <v>-0.1092133</v>
@@ -14084,15 +14080,15 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="99"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
       <c r="H54" s="1"/>
       <c r="I54" s="45">
         <v>-9.8989809999999998E-2</v>
@@ -14112,7 +14108,7 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="87" t="s">
+      <c r="A55" s="92" t="s">
         <v>144</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -14134,17 +14130,17 @@
         <v>2.350653E-6</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="79" t="s">
+      <c r="I55" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J55" s="79"/>
-      <c r="K55" s="79"/>
-      <c r="L55" s="79"/>
-      <c r="M55" s="79"/>
+      <c r="J55" s="82"/>
+      <c r="K55" s="82"/>
+      <c r="L55" s="82"/>
+      <c r="M55" s="82"/>
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="85"/>
+      <c r="A56" s="79"/>
       <c r="B56" s="1" t="s">
         <v>107</v>
       </c>
@@ -14164,15 +14160,15 @@
         <v>2.3278650000000001E-13</v>
       </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="79"/>
-      <c r="K56" s="79"/>
-      <c r="L56" s="79"/>
-      <c r="M56" s="79"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="82"/>
+      <c r="K56" s="82"/>
+      <c r="L56" s="82"/>
+      <c r="M56" s="82"/>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="85"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
@@ -14192,15 +14188,15 @@
         <v>5.789537E-3</v>
       </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="79"/>
-      <c r="L57" s="79"/>
-      <c r="M57" s="79"/>
+      <c r="I57" s="82"/>
+      <c r="J57" s="82"/>
+      <c r="K57" s="82"/>
+      <c r="L57" s="82"/>
+      <c r="M57" s="82"/>
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="99"/>
+      <c r="A58" s="80"/>
       <c r="B58" s="1" t="s">
         <v>109</v>
       </c>
@@ -14220,15 +14216,15 @@
         <v>3.5774789999999998E-4</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="79"/>
-      <c r="J58" s="79"/>
-      <c r="K58" s="79"/>
-      <c r="L58" s="79"/>
-      <c r="M58" s="79"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="82"/>
+      <c r="K58" s="82"/>
+      <c r="L58" s="82"/>
+      <c r="M58" s="82"/>
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="87" t="s">
+      <c r="A59" s="92" t="s">
         <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -14250,17 +14246,17 @@
         <v>1.0710269999999999E-5</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="79" t="s">
+      <c r="I59" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J59" s="79"/>
-      <c r="K59" s="79"/>
-      <c r="L59" s="79"/>
-      <c r="M59" s="79"/>
+      <c r="J59" s="82"/>
+      <c r="K59" s="82"/>
+      <c r="L59" s="82"/>
+      <c r="M59" s="82"/>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="85"/>
+      <c r="A60" s="79"/>
       <c r="B60" s="1" t="s">
         <v>107</v>
       </c>
@@ -14280,15 +14276,15 @@
         <v>1.3791302849E-6</v>
       </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="79"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="79"/>
-      <c r="L60" s="79"/>
-      <c r="M60" s="79"/>
+      <c r="I60" s="82"/>
+      <c r="J60" s="82"/>
+      <c r="K60" s="82"/>
+      <c r="L60" s="82"/>
+      <c r="M60" s="82"/>
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="85"/>
+      <c r="A61" s="79"/>
       <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
@@ -14308,15 +14304,15 @@
         <v>9.3598610230064994E-2</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
+      <c r="I61" s="82"/>
+      <c r="J61" s="82"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="82"/>
+      <c r="M61" s="82"/>
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="99"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="1" t="s">
         <v>109</v>
       </c>
@@ -14336,15 +14332,15 @@
         <v>3.7977520000000001E-2</v>
       </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="79"/>
-      <c r="J62" s="79"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
+      <c r="I62" s="82"/>
+      <c r="J62" s="82"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="82"/>
+      <c r="M62" s="82"/>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="92" t="s">
         <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -14366,17 +14362,17 @@
         <v>5.242662E-14</v>
       </c>
       <c r="H63" s="1"/>
-      <c r="I63" s="79" t="s">
+      <c r="I63" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J63" s="79"/>
-      <c r="K63" s="79"/>
-      <c r="L63" s="79"/>
-      <c r="M63" s="79"/>
+      <c r="J63" s="82"/>
+      <c r="K63" s="82"/>
+      <c r="L63" s="82"/>
+      <c r="M63" s="82"/>
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="85"/>
+      <c r="A64" s="79"/>
       <c r="B64" s="1" t="s">
         <v>107</v>
       </c>
@@ -14396,15 +14392,15 @@
         <v>3.4043159999999998E-14</v>
       </c>
       <c r="H64" s="1"/>
-      <c r="I64" s="79"/>
-      <c r="J64" s="79"/>
-      <c r="K64" s="79"/>
-      <c r="L64" s="79"/>
-      <c r="M64" s="79"/>
+      <c r="I64" s="82"/>
+      <c r="J64" s="82"/>
+      <c r="K64" s="82"/>
+      <c r="L64" s="82"/>
+      <c r="M64" s="82"/>
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="85"/>
+      <c r="A65" s="79"/>
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
@@ -14424,15 +14420,15 @@
         <v>0.64513220100000002</v>
       </c>
       <c r="H65" s="1"/>
-      <c r="I65" s="79"/>
-      <c r="J65" s="79"/>
-      <c r="K65" s="79"/>
-      <c r="L65" s="79"/>
-      <c r="M65" s="79"/>
+      <c r="I65" s="82"/>
+      <c r="J65" s="82"/>
+      <c r="K65" s="82"/>
+      <c r="L65" s="82"/>
+      <c r="M65" s="82"/>
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="99"/>
+      <c r="A66" s="80"/>
       <c r="B66" s="1" t="s">
         <v>109</v>
       </c>
@@ -14452,27 +14448,27 @@
         <v>0.36655130000000002</v>
       </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="79"/>
-      <c r="J66" s="79"/>
-      <c r="K66" s="79"/>
-      <c r="L66" s="79"/>
-      <c r="M66" s="79"/>
+      <c r="I66" s="82"/>
+      <c r="J66" s="82"/>
+      <c r="K66" s="82"/>
+      <c r="L66" s="82"/>
+      <c r="M66" s="82"/>
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="87" t="s">
+      <c r="A67" s="92" t="s">
         <v>38</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C67" s="79" t="s">
+      <c r="C67" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="79"/>
-      <c r="E67" s="79"/>
-      <c r="F67" s="79"/>
-      <c r="G67" s="79"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1">
         <v>5.4104409999999999E-2</v>
@@ -14492,15 +14488,15 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="85"/>
+      <c r="A68" s="79"/>
       <c r="B68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1">
         <v>4.687269E-3</v>
@@ -14520,15 +14516,15 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="85"/>
+      <c r="A69" s="79"/>
       <c r="B69" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="79"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1">
         <v>-0.16190650000000001</v>
@@ -14548,15 +14544,15 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="99"/>
+      <c r="A70" s="80"/>
       <c r="B70" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1">
         <v>-0.22064059999999999</v>
@@ -14576,7 +14572,7 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="87" t="s">
+      <c r="A71" s="92" t="s">
         <v>145</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -14598,17 +14594,17 @@
         <v>2.524047E-13</v>
       </c>
       <c r="H71" s="1"/>
-      <c r="I71" s="79" t="s">
+      <c r="I71" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J71" s="79"/>
-      <c r="K71" s="79"/>
-      <c r="L71" s="79"/>
-      <c r="M71" s="79"/>
+      <c r="J71" s="82"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="82"/>
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="85"/>
+      <c r="A72" s="79"/>
       <c r="B72" s="1" t="s">
         <v>107</v>
       </c>
@@ -14628,15 +14624,15 @@
         <v>8.8521990000000004E-10</v>
       </c>
       <c r="H72" s="1"/>
-      <c r="I72" s="79"/>
-      <c r="J72" s="79"/>
-      <c r="K72" s="79"/>
-      <c r="L72" s="79"/>
-      <c r="M72" s="79"/>
+      <c r="I72" s="82"/>
+      <c r="J72" s="82"/>
+      <c r="K72" s="82"/>
+      <c r="L72" s="82"/>
+      <c r="M72" s="82"/>
       <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="85"/>
+      <c r="A73" s="79"/>
       <c r="B73" s="1" t="s">
         <v>108</v>
       </c>
@@ -14656,15 +14652,15 @@
         <v>9.6146709999999996E-2</v>
       </c>
       <c r="H73" s="1"/>
-      <c r="I73" s="79"/>
-      <c r="J73" s="79"/>
-      <c r="K73" s="79"/>
-      <c r="L73" s="79"/>
-      <c r="M73" s="79"/>
+      <c r="I73" s="82"/>
+      <c r="J73" s="82"/>
+      <c r="K73" s="82"/>
+      <c r="L73" s="82"/>
+      <c r="M73" s="82"/>
       <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="99"/>
+      <c r="A74" s="80"/>
       <c r="B74" s="1" t="s">
         <v>109</v>
       </c>
@@ -14684,27 +14680,27 @@
         <v>6.7150146952E-3</v>
       </c>
       <c r="H74" s="1"/>
-      <c r="I74" s="79"/>
-      <c r="J74" s="79"/>
-      <c r="K74" s="79"/>
-      <c r="L74" s="79"/>
-      <c r="M74" s="79"/>
+      <c r="I74" s="82"/>
+      <c r="J74" s="82"/>
+      <c r="K74" s="82"/>
+      <c r="L74" s="82"/>
+      <c r="M74" s="82"/>
       <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="87" t="s">
+      <c r="A75" s="92" t="s">
         <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="79" t="s">
+      <c r="C75" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="79"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
       <c r="H75" s="1"/>
       <c r="I75" s="45">
         <v>3.8010990000000001E-3</v>
@@ -14724,15 +14720,15 @@
       <c r="N75" s="1"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="85"/>
+      <c r="A76" s="79"/>
       <c r="B76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="79"/>
-      <c r="D76" s="79"/>
-      <c r="E76" s="79"/>
-      <c r="F76" s="79"/>
-      <c r="G76" s="79"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
+      <c r="E76" s="82"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="82"/>
       <c r="H76" s="1"/>
       <c r="I76" s="45">
         <v>2.6998579999999999E-3</v>
@@ -14752,15 +14748,15 @@
       <c r="N76" s="1"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="85"/>
+      <c r="A77" s="79"/>
       <c r="B77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="79"/>
-      <c r="D77" s="79"/>
-      <c r="E77" s="79"/>
-      <c r="F77" s="79"/>
-      <c r="G77" s="79"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
       <c r="H77" s="1"/>
       <c r="I77" s="45">
         <v>-1.146374E-2</v>
@@ -14780,15 +14776,15 @@
       <c r="N77" s="1"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="99"/>
+      <c r="A78" s="80"/>
       <c r="B78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C78" s="79"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="79"/>
-      <c r="F78" s="79"/>
-      <c r="G78" s="79"/>
+      <c r="C78" s="82"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="82"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="82"/>
       <c r="H78" s="1"/>
       <c r="I78" s="45">
         <v>-1.288595E-2</v>
@@ -14808,19 +14804,19 @@
       <c r="N78" s="1"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="87" t="s">
+      <c r="A79" s="92" t="s">
         <v>29</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C79" s="79" t="s">
+      <c r="C79" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D79" s="79"/>
-      <c r="E79" s="79"/>
-      <c r="F79" s="79"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1">
         <v>-1.7348269999999999E-2</v>
@@ -14840,15 +14836,15 @@
       <c r="N79" s="1"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="85"/>
+      <c r="A80" s="79"/>
       <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="79"/>
-      <c r="G80" s="79"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1">
         <v>1.2575930000000001E-2</v>
@@ -14868,15 +14864,15 @@
       <c r="N80" s="1"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="85"/>
+      <c r="A81" s="79"/>
       <c r="B81" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="79"/>
-      <c r="D81" s="79"/>
-      <c r="E81" s="79"/>
-      <c r="F81" s="79"/>
-      <c r="G81" s="79"/>
+      <c r="C81" s="82"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="82"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1">
         <v>3.5116069999999999E-2</v>
@@ -14896,15 +14892,15 @@
       <c r="N81" s="1"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="99"/>
+      <c r="A82" s="80"/>
       <c r="B82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C82" s="79"/>
-      <c r="D82" s="79"/>
-      <c r="E82" s="79"/>
-      <c r="F82" s="79"/>
-      <c r="G82" s="79"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1">
         <v>6.7801109999999998E-2</v>
@@ -14924,7 +14920,7 @@
       <c r="N82" s="1"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="87" t="s">
+      <c r="A83" s="92" t="s">
         <v>24</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -14946,17 +14942,17 @@
         <v>6.5310590000000004E-6</v>
       </c>
       <c r="H83" s="1"/>
-      <c r="I83" s="79" t="s">
+      <c r="I83" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J83" s="79"/>
-      <c r="K83" s="79"/>
-      <c r="L83" s="79"/>
-      <c r="M83" s="79"/>
+      <c r="J83" s="82"/>
+      <c r="K83" s="82"/>
+      <c r="L83" s="82"/>
+      <c r="M83" s="82"/>
       <c r="N83" s="1"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="85"/>
+      <c r="A84" s="79"/>
       <c r="B84" s="1" t="s">
         <v>107</v>
       </c>
@@ -14976,15 +14972,15 @@
         <v>0.31967210000000001</v>
       </c>
       <c r="H84" s="1"/>
-      <c r="I84" s="79"/>
-      <c r="J84" s="79"/>
-      <c r="K84" s="79"/>
-      <c r="L84" s="79"/>
-      <c r="M84" s="79"/>
+      <c r="I84" s="82"/>
+      <c r="J84" s="82"/>
+      <c r="K84" s="82"/>
+      <c r="L84" s="82"/>
+      <c r="M84" s="82"/>
       <c r="N84" s="1"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="85"/>
+      <c r="A85" s="79"/>
       <c r="B85" s="1" t="s">
         <v>108</v>
       </c>
@@ -15004,15 +15000,15 @@
         <v>4.9434029999999999E-3</v>
       </c>
       <c r="H85" s="1"/>
-      <c r="I85" s="79"/>
-      <c r="J85" s="79"/>
-      <c r="K85" s="79"/>
-      <c r="L85" s="79"/>
-      <c r="M85" s="79"/>
+      <c r="I85" s="82"/>
+      <c r="J85" s="82"/>
+      <c r="K85" s="82"/>
+      <c r="L85" s="82"/>
+      <c r="M85" s="82"/>
       <c r="N85" s="1"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="99"/>
+      <c r="A86" s="80"/>
       <c r="B86" s="1" t="s">
         <v>109</v>
       </c>
@@ -15032,15 +15028,15 @@
         <v>0.72019759999999999</v>
       </c>
       <c r="H86" s="1"/>
-      <c r="I86" s="79"/>
-      <c r="J86" s="79"/>
-      <c r="K86" s="79"/>
-      <c r="L86" s="79"/>
-      <c r="M86" s="79"/>
+      <c r="I86" s="82"/>
+      <c r="J86" s="82"/>
+      <c r="K86" s="82"/>
+      <c r="L86" s="82"/>
+      <c r="M86" s="82"/>
       <c r="N86" s="1"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="87" t="s">
+      <c r="A87" s="92" t="s">
         <v>20</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -15062,17 +15058,17 @@
         <v>2.2222259999999999E-4</v>
       </c>
       <c r="H87" s="1"/>
-      <c r="I87" s="79" t="s">
+      <c r="I87" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J87" s="79"/>
-      <c r="K87" s="79"/>
-      <c r="L87" s="79"/>
-      <c r="M87" s="79"/>
+      <c r="J87" s="82"/>
+      <c r="K87" s="82"/>
+      <c r="L87" s="82"/>
+      <c r="M87" s="82"/>
       <c r="N87" s="1"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="85"/>
+      <c r="A88" s="79"/>
       <c r="B88" s="1" t="s">
         <v>107</v>
       </c>
@@ -15092,15 +15088,15 @@
         <v>1.142512E-8</v>
       </c>
       <c r="H88" s="1"/>
-      <c r="I88" s="79"/>
-      <c r="J88" s="79"/>
-      <c r="K88" s="79"/>
-      <c r="L88" s="79"/>
-      <c r="M88" s="79"/>
+      <c r="I88" s="82"/>
+      <c r="J88" s="82"/>
+      <c r="K88" s="82"/>
+      <c r="L88" s="82"/>
+      <c r="M88" s="82"/>
       <c r="N88" s="1"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="85"/>
+      <c r="A89" s="79"/>
       <c r="B89" s="1" t="s">
         <v>108</v>
       </c>
@@ -15120,15 +15116,15 @@
         <v>0.17826230000000001</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="79"/>
-      <c r="J89" s="79"/>
-      <c r="K89" s="79"/>
-      <c r="L89" s="79"/>
-      <c r="M89" s="79"/>
+      <c r="I89" s="82"/>
+      <c r="J89" s="82"/>
+      <c r="K89" s="82"/>
+      <c r="L89" s="82"/>
+      <c r="M89" s="82"/>
       <c r="N89" s="1"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="99"/>
+      <c r="A90" s="80"/>
       <c r="B90" s="1" t="s">
         <v>109</v>
       </c>
@@ -15148,15 +15144,15 @@
         <v>2.8002340000000001E-2</v>
       </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="79"/>
-      <c r="J90" s="79"/>
-      <c r="K90" s="79"/>
-      <c r="L90" s="79"/>
-      <c r="M90" s="79"/>
+      <c r="I90" s="82"/>
+      <c r="J90" s="82"/>
+      <c r="K90" s="82"/>
+      <c r="L90" s="82"/>
+      <c r="M90" s="82"/>
       <c r="N90" s="1"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="87" t="s">
+      <c r="A91" s="92" t="s">
         <v>21</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -15178,17 +15174,17 @@
         <v>3.9052140000000001E-5</v>
       </c>
       <c r="H91" s="1"/>
-      <c r="I91" s="79" t="s">
+      <c r="I91" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J91" s="79"/>
-      <c r="K91" s="79"/>
-      <c r="L91" s="79"/>
-      <c r="M91" s="79"/>
+      <c r="J91" s="82"/>
+      <c r="K91" s="82"/>
+      <c r="L91" s="82"/>
+      <c r="M91" s="82"/>
       <c r="N91" s="1"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="85"/>
+      <c r="A92" s="79"/>
       <c r="B92" s="1" t="s">
         <v>107</v>
       </c>
@@ -15208,15 +15204,15 @@
         <v>1.9085240000000001E-25</v>
       </c>
       <c r="H92" s="1"/>
-      <c r="I92" s="79"/>
-      <c r="J92" s="79"/>
-      <c r="K92" s="79"/>
-      <c r="L92" s="79"/>
-      <c r="M92" s="79"/>
+      <c r="I92" s="82"/>
+      <c r="J92" s="82"/>
+      <c r="K92" s="82"/>
+      <c r="L92" s="82"/>
+      <c r="M92" s="82"/>
       <c r="N92" s="1"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="85"/>
+      <c r="A93" s="79"/>
       <c r="B93" s="1" t="s">
         <v>108</v>
       </c>
@@ -15236,15 +15232,15 @@
         <v>1.377838E-2</v>
       </c>
       <c r="H93" s="1"/>
-      <c r="I93" s="79"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="79"/>
-      <c r="L93" s="79"/>
-      <c r="M93" s="79"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="82"/>
+      <c r="K93" s="82"/>
+      <c r="L93" s="82"/>
+      <c r="M93" s="82"/>
       <c r="N93" s="1"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="99"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="1" t="s">
         <v>109</v>
       </c>
@@ -15264,15 +15260,15 @@
         <v>0.46767300000000001</v>
       </c>
       <c r="H94" s="1"/>
-      <c r="I94" s="79"/>
-      <c r="J94" s="79"/>
-      <c r="K94" s="79"/>
-      <c r="L94" s="79"/>
-      <c r="M94" s="79"/>
+      <c r="I94" s="82"/>
+      <c r="J94" s="82"/>
+      <c r="K94" s="82"/>
+      <c r="L94" s="82"/>
+      <c r="M94" s="82"/>
       <c r="N94" s="1"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="87" t="s">
+      <c r="A95" s="92" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -15294,17 +15290,17 @@
         <v>2.9384279999999999E-9</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="I95" s="79" t="s">
+      <c r="I95" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J95" s="79"/>
-      <c r="K95" s="79"/>
-      <c r="L95" s="79"/>
-      <c r="M95" s="79"/>
+      <c r="J95" s="82"/>
+      <c r="K95" s="82"/>
+      <c r="L95" s="82"/>
+      <c r="M95" s="82"/>
       <c r="N95" s="1"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="85"/>
+      <c r="A96" s="79"/>
       <c r="B96" s="1" t="s">
         <v>107</v>
       </c>
@@ -15324,15 +15320,15 @@
         <v>9.0369680000000005E-13</v>
       </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="79"/>
-      <c r="J96" s="79"/>
-      <c r="K96" s="79"/>
-      <c r="L96" s="79"/>
-      <c r="M96" s="79"/>
+      <c r="I96" s="82"/>
+      <c r="J96" s="82"/>
+      <c r="K96" s="82"/>
+      <c r="L96" s="82"/>
+      <c r="M96" s="82"/>
       <c r="N96" s="1"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="85"/>
+      <c r="A97" s="79"/>
       <c r="B97" s="1" t="s">
         <v>108</v>
       </c>
@@ -15352,15 +15348,15 @@
         <v>0.45520664523399601</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="79"/>
-      <c r="J97" s="79"/>
-      <c r="K97" s="79"/>
-      <c r="L97" s="79"/>
-      <c r="M97" s="79"/>
+      <c r="I97" s="82"/>
+      <c r="J97" s="82"/>
+      <c r="K97" s="82"/>
+      <c r="L97" s="82"/>
+      <c r="M97" s="82"/>
       <c r="N97" s="1"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="99"/>
+      <c r="A98" s="80"/>
       <c r="B98" s="1" t="s">
         <v>109</v>
       </c>
@@ -15380,15 +15376,15 @@
         <v>5.14251187538E-2</v>
       </c>
       <c r="H98" s="1"/>
-      <c r="I98" s="79"/>
-      <c r="J98" s="79"/>
-      <c r="K98" s="79"/>
-      <c r="L98" s="79"/>
-      <c r="M98" s="79"/>
+      <c r="I98" s="82"/>
+      <c r="J98" s="82"/>
+      <c r="K98" s="82"/>
+      <c r="L98" s="82"/>
+      <c r="M98" s="82"/>
       <c r="N98" s="1"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="87" t="s">
+      <c r="A99" s="92" t="s">
         <v>35</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -15410,17 +15406,17 @@
         <v>0.30992960000000003</v>
       </c>
       <c r="H99" s="1"/>
-      <c r="I99" s="79" t="s">
+      <c r="I99" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J99" s="79"/>
-      <c r="K99" s="79"/>
-      <c r="L99" s="79"/>
-      <c r="M99" s="79"/>
+      <c r="J99" s="82"/>
+      <c r="K99" s="82"/>
+      <c r="L99" s="82"/>
+      <c r="M99" s="82"/>
       <c r="N99" s="1"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="85"/>
+      <c r="A100" s="79"/>
       <c r="B100" s="1" t="s">
         <v>107</v>
       </c>
@@ -15440,15 +15436,15 @@
         <v>5.4385229999999998E-11</v>
       </c>
       <c r="H100" s="1"/>
-      <c r="I100" s="79"/>
-      <c r="J100" s="79"/>
-      <c r="K100" s="79"/>
-      <c r="L100" s="79"/>
-      <c r="M100" s="79"/>
+      <c r="I100" s="82"/>
+      <c r="J100" s="82"/>
+      <c r="K100" s="82"/>
+      <c r="L100" s="82"/>
+      <c r="M100" s="82"/>
       <c r="N100" s="1"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="85"/>
+      <c r="A101" s="79"/>
       <c r="B101" s="1" t="s">
         <v>108</v>
       </c>
@@ -15468,15 +15464,15 @@
         <v>1.343811E-5</v>
       </c>
       <c r="H101" s="1"/>
-      <c r="I101" s="79"/>
-      <c r="J101" s="79"/>
-      <c r="K101" s="79"/>
-      <c r="L101" s="79"/>
-      <c r="M101" s="79"/>
+      <c r="I101" s="82"/>
+      <c r="J101" s="82"/>
+      <c r="K101" s="82"/>
+      <c r="L101" s="82"/>
+      <c r="M101" s="82"/>
       <c r="N101" s="1"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="99"/>
+      <c r="A102" s="80"/>
       <c r="B102" s="1" t="s">
         <v>109</v>
       </c>
@@ -15496,15 +15492,15 @@
         <v>0.56057069999999998</v>
       </c>
       <c r="H102" s="1"/>
-      <c r="I102" s="79"/>
-      <c r="J102" s="79"/>
-      <c r="K102" s="79"/>
-      <c r="L102" s="79"/>
-      <c r="M102" s="79"/>
+      <c r="I102" s="82"/>
+      <c r="J102" s="82"/>
+      <c r="K102" s="82"/>
+      <c r="L102" s="82"/>
+      <c r="M102" s="82"/>
       <c r="N102" s="1"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="87" t="s">
+      <c r="A103" s="92" t="s">
         <v>149</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -15526,17 +15522,17 @@
         <v>0.96106304949900001</v>
       </c>
       <c r="H103" s="1"/>
-      <c r="I103" s="79" t="s">
+      <c r="I103" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J103" s="79"/>
-      <c r="K103" s="79"/>
-      <c r="L103" s="79"/>
-      <c r="M103" s="79"/>
+      <c r="J103" s="82"/>
+      <c r="K103" s="82"/>
+      <c r="L103" s="82"/>
+      <c r="M103" s="82"/>
       <c r="N103" s="1"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="85"/>
+      <c r="A104" s="79"/>
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
@@ -15556,15 +15552,15 @@
         <v>0.2307786</v>
       </c>
       <c r="H104" s="1"/>
-      <c r="I104" s="79"/>
-      <c r="J104" s="79"/>
-      <c r="K104" s="79"/>
-      <c r="L104" s="79"/>
-      <c r="M104" s="79"/>
+      <c r="I104" s="82"/>
+      <c r="J104" s="82"/>
+      <c r="K104" s="82"/>
+      <c r="L104" s="82"/>
+      <c r="M104" s="82"/>
       <c r="N104" s="1"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="85"/>
+      <c r="A105" s="79"/>
       <c r="B105" s="1" t="s">
         <v>108</v>
       </c>
@@ -15584,15 +15580,15 @@
         <v>3.2851500000000001E-3</v>
       </c>
       <c r="H105" s="1"/>
-      <c r="I105" s="79"/>
-      <c r="J105" s="79"/>
-      <c r="K105" s="79"/>
-      <c r="L105" s="79"/>
-      <c r="M105" s="79"/>
+      <c r="I105" s="82"/>
+      <c r="J105" s="82"/>
+      <c r="K105" s="82"/>
+      <c r="L105" s="82"/>
+      <c r="M105" s="82"/>
       <c r="N105" s="1"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="99"/>
+      <c r="A106" s="80"/>
       <c r="B106" s="1" t="s">
         <v>109</v>
       </c>
@@ -15612,15 +15608,15 @@
         <v>9.3442800000000006E-2</v>
       </c>
       <c r="H106" s="1"/>
-      <c r="I106" s="79"/>
-      <c r="J106" s="79"/>
-      <c r="K106" s="79"/>
-      <c r="L106" s="79"/>
-      <c r="M106" s="79"/>
+      <c r="I106" s="82"/>
+      <c r="J106" s="82"/>
+      <c r="K106" s="82"/>
+      <c r="L106" s="82"/>
+      <c r="M106" s="82"/>
       <c r="N106" s="1"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="92" t="s">
         <v>25</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -15642,17 +15638,17 @@
         <v>2.1465810000000001E-7</v>
       </c>
       <c r="H107" s="1"/>
-      <c r="I107" s="79" t="s">
+      <c r="I107" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="J107" s="79"/>
-      <c r="K107" s="79"/>
-      <c r="L107" s="79"/>
-      <c r="M107" s="79"/>
+      <c r="J107" s="82"/>
+      <c r="K107" s="82"/>
+      <c r="L107" s="82"/>
+      <c r="M107" s="82"/>
       <c r="N107" s="1"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="85"/>
+      <c r="A108" s="79"/>
       <c r="B108" s="1" t="s">
         <v>107</v>
       </c>
@@ -15672,15 +15668,15 @@
         <v>3.0964249999999998E-23</v>
       </c>
       <c r="H108" s="1"/>
-      <c r="I108" s="79"/>
-      <c r="J108" s="79"/>
-      <c r="K108" s="79"/>
-      <c r="L108" s="79"/>
-      <c r="M108" s="79"/>
+      <c r="I108" s="82"/>
+      <c r="J108" s="82"/>
+      <c r="K108" s="82"/>
+      <c r="L108" s="82"/>
+      <c r="M108" s="82"/>
       <c r="N108" s="1"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="85"/>
+      <c r="A109" s="79"/>
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
@@ -15700,15 +15696,15 @@
         <v>0.17187649999999999</v>
       </c>
       <c r="H109" s="1"/>
-      <c r="I109" s="79"/>
-      <c r="J109" s="79"/>
-      <c r="K109" s="79"/>
-      <c r="L109" s="79"/>
-      <c r="M109" s="79"/>
+      <c r="I109" s="82"/>
+      <c r="J109" s="82"/>
+      <c r="K109" s="82"/>
+      <c r="L109" s="82"/>
+      <c r="M109" s="82"/>
       <c r="N109" s="1"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="99"/>
+      <c r="A110" s="80"/>
       <c r="B110" s="1" t="s">
         <v>109</v>
       </c>
@@ -15728,11 +15724,11 @@
         <v>5.7776140000000001E-4</v>
       </c>
       <c r="H110" s="1"/>
-      <c r="I110" s="79"/>
-      <c r="J110" s="79"/>
-      <c r="K110" s="79"/>
-      <c r="L110" s="79"/>
-      <c r="M110" s="79"/>
+      <c r="I110" s="82"/>
+      <c r="J110" s="82"/>
+      <c r="K110" s="82"/>
+      <c r="L110" s="82"/>
+      <c r="M110" s="82"/>
       <c r="N110" s="1"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -15755,6 +15751,40 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="I103:M106"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="I107:M110"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="C79:G82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="I83:M86"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="C67:G70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="I71:M74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="I55:M58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="C47:G50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C51:G54"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="I1:N1"/>
@@ -15768,40 +15798,6 @@
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="C47:G50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="C51:G54"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="I63:M66"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="C67:G70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="I71:M74"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C75:G78"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="C79:G82"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="I83:M86"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="I103:M106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="I107:M110"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="I91:M94"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="I95:M98"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="I99:M102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15855,7 +15851,7 @@
       <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="109">
+      <c r="A2" s="110">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -15878,7 +15874,7 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -15897,7 +15893,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="110"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -15917,7 +15913,7 @@
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="110"/>
+      <c r="A5" s="111"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -15937,7 +15933,7 @@
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="110"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="49" t="s">
@@ -15956,7 +15952,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -15971,7 +15967,7 @@
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -15987,7 +15983,7 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -16005,7 +16001,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="111"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -16019,7 +16015,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="109">
+      <c r="A11" s="110">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -16047,7 +16043,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="110"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>80</v>
@@ -16068,7 +16064,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
+      <c r="A13" s="111"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -16085,7 +16081,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="110"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -16098,7 +16094,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="110"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -16111,7 +16107,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="110"/>
+      <c r="A16" s="111"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -16124,7 +16120,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
+      <c r="A17" s="111"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -16137,7 +16133,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="112"/>
+      <c r="A18" s="113"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -16269,7 +16265,7 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="109">
+      <c r="A2" s="110">
         <v>2021</v>
       </c>
       <c r="B2" s="13"/>
@@ -16292,7 +16288,7 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="49" t="s">
@@ -16308,7 +16304,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="110"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="E4" s="20" t="s">
@@ -16322,7 +16318,7 @@
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="110"/>
+      <c r="A5" s="111"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -16334,7 +16330,7 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="110"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -16347,7 +16343,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -16359,7 +16355,7 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -16370,7 +16366,7 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -16386,7 +16382,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="111"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -16399,7 +16395,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="109">
+      <c r="A11" s="110">
         <v>2022</v>
       </c>
       <c r="B11" s="13"/>
@@ -16418,7 +16414,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="110"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="1"/>
       <c r="C12" s="20" t="s">
         <v>80</v>
@@ -16434,7 +16430,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
+      <c r="A13" s="111"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -16445,7 +16441,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="110"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -16457,7 +16453,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="110"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -16469,7 +16465,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="110"/>
+      <c r="A16" s="111"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -16479,7 +16475,7 @@
       <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
+      <c r="A17" s="111"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -16489,7 +16485,7 @@
       <c r="H17" s="26"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="112"/>
+      <c r="A18" s="113"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>

--- a/data/ModelResults.xlsx
+++ b/data/ModelResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1580" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF89575-650D-4FF2-9675-FC5C491FDF16}"/>
+  <xr:revisionPtr revIDLastSave="1581" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B178DFB7-5D00-416B-AAB2-5C64FF76EF03}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="157">
   <si>
     <t>Experiment</t>
   </si>
@@ -545,6 +545,9 @@
   </si>
   <si>
     <t>Avg weight of Seed Collected (wt divided by count)</t>
+  </si>
+  <si>
+    <t>Avg Seed Num (seed collected count / fruit collected count) - log</t>
   </si>
 </sst>
 </file>
@@ -1172,29 +1175,11 @@
     <xf numFmtId="11" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1206,6 +1191,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1246,6 +1234,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1656,43 +1659,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="87">
+      <c r="C1" s="81">
         <v>2021</v>
       </c>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="87">
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="81">
         <v>2022</v>
       </c>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
       <c r="P1" s="20"/>
-      <c r="Q1" s="102" t="s">
+      <c r="Q1" s="97" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="87" t="s">
+      <c r="R1" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="89"/>
-      <c r="X1" s="87" t="s">
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="89"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="83"/>
     </row>
     <row r="2" spans="1:29" s="55" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
@@ -1741,7 +1744,7 @@
       <c r="P2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="103"/>
+      <c r="Q2" s="98"/>
       <c r="R2" s="14" t="s">
         <v>112</v>
       </c>
@@ -1780,7 +1783,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="87" t="s">
         <v>141</v>
       </c>
       <c r="B3" s="51" t="s">
@@ -1805,15 +1808,15 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I3" s="51"/>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="92" t="s">
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="87" t="s">
         <v>141</v>
       </c>
       <c r="Q3" s="51" t="s">
@@ -1835,17 +1838,17 @@
         <v>0.35833147122850001</v>
       </c>
       <c r="W3" s="51"/>
-      <c r="X3" s="93" t="s">
+      <c r="X3" s="88" t="s">
         <v>111</v>
       </c>
-      <c r="Y3" s="94"/>
-      <c r="Z3" s="94"/>
-      <c r="AA3" s="94"/>
-      <c r="AB3" s="95"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
+      <c r="AB3" s="90"/>
       <c r="AC3" s="51"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
+      <c r="A4" s="85"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1868,13 +1871,13 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="85"/>
       <c r="Q4" s="1" t="s">
         <v>107</v>
       </c>
@@ -1894,15 +1897,15 @@
         <v>0.11792329999999999</v>
       </c>
       <c r="W4" s="1"/>
-      <c r="X4" s="96"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="98"/>
+      <c r="X4" s="91"/>
+      <c r="Y4" s="92"/>
+      <c r="Z4" s="92"/>
+      <c r="AA4" s="92"/>
+      <c r="AB4" s="93"/>
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1924,13 +1927,13 @@
       <c r="H5" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="85"/>
       <c r="Q5" s="1" t="s">
         <v>108</v>
       </c>
@@ -1950,32 +1953,32 @@
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="W5" s="1"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="97"/>
-      <c r="Z5" s="97"/>
-      <c r="AA5" s="97"/>
-      <c r="AB5" s="98"/>
+      <c r="X5" s="91"/>
+      <c r="Y5" s="92"/>
+      <c r="Z5" s="92"/>
+      <c r="AA5" s="92"/>
+      <c r="AB5" s="93"/>
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="91"/>
+      <c r="A6" s="86"/>
       <c r="B6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="84"/>
-      <c r="P6" s="91"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="86"/>
       <c r="Q6" s="14" t="s">
         <v>109</v>
       </c>
@@ -1995,15 +1998,15 @@
         <v>1.280514E-6</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="99"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="100"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="101"/>
+      <c r="X6" s="94"/>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="95"/>
+      <c r="AA6" s="95"/>
+      <c r="AB6" s="96"/>
       <c r="AC6" s="14"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="84" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="51" t="s">
@@ -2046,7 +2049,7 @@
       <c r="O7" s="52">
         <v>7.9655542624253594E-15</v>
       </c>
-      <c r="P7" s="92" t="s">
+      <c r="P7" s="87" t="s">
         <v>17</v>
       </c>
       <c r="Q7" s="51" t="s">
@@ -2086,7 +2089,7 @@
       <c r="AC7" s="51"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2127,7 +2130,7 @@
       <c r="O8" s="2">
         <v>2.49480079562349E-3</v>
       </c>
-      <c r="P8" s="79"/>
+      <c r="P8" s="85"/>
       <c r="Q8" s="1" t="s">
         <v>107</v>
       </c>
@@ -2165,7 +2168,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="79"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2206,7 +2209,7 @@
       <c r="O9" s="2">
         <v>5.9886663878832899E-3</v>
       </c>
-      <c r="P9" s="79"/>
+      <c r="P9" s="85"/>
       <c r="Q9" s="1" t="s">
         <v>108</v>
       </c>
@@ -2244,16 +2247,16 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14">
         <v>3.4846897009296399E-3</v>
@@ -2273,7 +2276,7 @@
       <c r="O10" s="14">
         <v>0.23519968422781001</v>
       </c>
-      <c r="P10" s="80"/>
+      <c r="P10" s="99"/>
       <c r="Q10" s="14" t="s">
         <v>109</v>
       </c>
@@ -2311,20 +2314,20 @@
       <c r="AC10" s="14"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="85" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51">
         <v>2.20343269025562E-2</v>
@@ -2344,19 +2347,19 @@
       <c r="O11" s="53">
         <v>1.20915323151938E-2</v>
       </c>
-      <c r="P11" s="92" t="s">
+      <c r="P11" s="87" t="s">
         <v>147</v>
       </c>
       <c r="Q11" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="R11" s="82" t="s">
+      <c r="R11" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="S11" s="82"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="82"/>
-      <c r="V11" s="82"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="79"/>
+      <c r="V11" s="79"/>
       <c r="W11" s="51"/>
       <c r="X11" s="58">
         <v>-1.7478199999999999E-2</v>
@@ -2376,16 +2379,16 @@
       <c r="AC11" s="51"/>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
+      <c r="A12" s="85"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>2.98483856205864E-2</v>
@@ -2405,15 +2408,15 @@
       <c r="O12" s="2">
         <v>1.05420955332634E-2</v>
       </c>
-      <c r="P12" s="79"/>
+      <c r="P12" s="85"/>
       <c r="Q12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R12" s="82"/>
-      <c r="S12" s="82"/>
-      <c r="T12" s="82"/>
-      <c r="U12" s="82"/>
-      <c r="V12" s="82"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="79"/>
       <c r="W12" s="1"/>
       <c r="X12" s="45">
         <v>-2.3552070000000001E-2</v>
@@ -2433,16 +2436,16 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="79"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>1.15818782663304E-3</v>
@@ -2462,15 +2465,15 @@
       <c r="O13" s="1">
         <v>0.55966903975183102</v>
       </c>
-      <c r="P13" s="79"/>
+      <c r="P13" s="85"/>
       <c r="Q13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="82"/>
-      <c r="U13" s="82"/>
-      <c r="V13" s="82"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="79"/>
+      <c r="V13" s="79"/>
       <c r="W13" s="1"/>
       <c r="X13" s="45">
         <v>-2.6797439999999999E-2</v>
@@ -2490,16 +2493,16 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
+      <c r="A14" s="86"/>
       <c r="B14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14">
         <v>2.0797141885883202E-3</v>
@@ -2519,15 +2522,15 @@
       <c r="O14" s="14">
         <v>0.73598934665486404</v>
       </c>
-      <c r="P14" s="91"/>
+      <c r="P14" s="86"/>
       <c r="Q14" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R14" s="84"/>
-      <c r="S14" s="84"/>
-      <c r="T14" s="84"/>
-      <c r="U14" s="84"/>
-      <c r="V14" s="84"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
       <c r="W14" s="14"/>
       <c r="X14" s="61">
         <v>-3.3645590000000003E-2</v>
@@ -2547,7 +2550,7 @@
       <c r="AC14" s="14"/>
     </row>
     <row r="15" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="84" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -2590,7 +2593,7 @@
       <c r="O15" s="63">
         <v>2.5984972877347698E-9</v>
       </c>
-      <c r="P15" s="90" t="s">
+      <c r="P15" s="84" t="s">
         <v>15</v>
       </c>
       <c r="Q15" s="13" t="s">
@@ -2632,7 +2635,7 @@
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -2673,7 +2676,7 @@
       <c r="O16" s="4">
         <v>2.3925201381821199E-8</v>
       </c>
-      <c r="P16" s="79"/>
+      <c r="P16" s="85"/>
       <c r="Q16" s="1" t="s">
         <v>107</v>
       </c>
@@ -2713,7 +2716,7 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2754,7 +2757,7 @@
       <c r="O17" s="3">
         <v>0.107275586121823</v>
       </c>
-      <c r="P17" s="79"/>
+      <c r="P17" s="85"/>
       <c r="Q17" s="1" t="s">
         <v>108</v>
       </c>
@@ -2794,16 +2797,16 @@
       </c>
     </row>
     <row r="18" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="101"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14">
         <v>4.9184876384352101E-2</v>
@@ -2823,7 +2826,7 @@
       <c r="O18" s="60">
         <v>1.9087014953066299E-2</v>
       </c>
-      <c r="P18" s="91"/>
+      <c r="P18" s="86"/>
       <c r="Q18" s="14" t="s">
         <v>109</v>
       </c>
@@ -2863,20 +2866,20 @@
       </c>
     </row>
     <row r="19" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="84" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13">
         <v>1.4241127553301099E-4</v>
@@ -2896,19 +2899,19 @@
       <c r="O19" s="13">
         <v>0.82529746395827397</v>
       </c>
-      <c r="P19" s="90" t="s">
+      <c r="P19" s="84" t="s">
         <v>29</v>
       </c>
       <c r="Q19" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R19" s="83" t="s">
+      <c r="R19" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="S19" s="83"/>
-      <c r="T19" s="83"/>
-      <c r="U19" s="83"/>
-      <c r="V19" s="83"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13">
         <v>-1.7348269999999999E-2</v>
@@ -2928,16 +2931,16 @@
       <c r="AC19" s="13"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>4.6725153189010001E-2</v>
@@ -2957,15 +2960,15 @@
       <c r="O20" s="2">
         <v>1.3790795758093499E-3</v>
       </c>
-      <c r="P20" s="79"/>
+      <c r="P20" s="85"/>
       <c r="Q20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
+      <c r="R20" s="79"/>
+      <c r="S20" s="79"/>
+      <c r="T20" s="79"/>
+      <c r="U20" s="79"/>
+      <c r="V20" s="79"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
         <v>1.2575930000000001E-2</v>
@@ -2985,16 +2988,16 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2.8302586845141399E-2</v>
@@ -3014,15 +3017,15 @@
       <c r="O21" s="2">
         <v>2.3248319291652099E-3</v>
       </c>
-      <c r="P21" s="79"/>
+      <c r="P21" s="85"/>
       <c r="Q21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R21" s="82"/>
-      <c r="S21" s="82"/>
-      <c r="T21" s="82"/>
-      <c r="U21" s="82"/>
-      <c r="V21" s="82"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
         <v>3.5116069999999999E-2</v>
@@ -3042,16 +3045,16 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="91"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14">
         <v>6.3796317056246301E-3</v>
@@ -3071,15 +3074,15 @@
       <c r="O22" s="14">
         <v>0.33767591593294399</v>
       </c>
-      <c r="P22" s="91"/>
+      <c r="P22" s="86"/>
       <c r="Q22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="84"/>
-      <c r="U22" s="84"/>
-      <c r="V22" s="84"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
       <c r="W22" s="14"/>
       <c r="X22" s="14">
         <v>6.7801109999999998E-2</v>
@@ -3099,7 +3102,7 @@
       <c r="AC22" s="14"/>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="84" t="s">
         <v>151</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3124,14 +3127,14 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="83" t="s">
+      <c r="J23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100"/>
+      <c r="O23" s="100"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
         <v>106</v>
@@ -3152,17 +3155,17 @@
         <v>2.9384279999999999E-9</v>
       </c>
       <c r="W23" s="1"/>
-      <c r="X23" s="83" t="s">
+      <c r="X23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y23" s="83"/>
-      <c r="Z23" s="83"/>
-      <c r="AA23" s="83"/>
-      <c r="AB23" s="83"/>
+      <c r="Y23" s="100"/>
+      <c r="Z23" s="100"/>
+      <c r="AA23" s="100"/>
+      <c r="AB23" s="100"/>
       <c r="AC23" s="1"/>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="79"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3185,12 +3188,12 @@
         <v>0.2597892</v>
       </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="82"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
         <v>107</v>
@@ -3211,15 +3214,15 @@
         <v>9.0369680000000005E-13</v>
       </c>
       <c r="W24" s="1"/>
-      <c r="X24" s="82"/>
-      <c r="Y24" s="82"/>
-      <c r="Z24" s="82"/>
-      <c r="AA24" s="82"/>
-      <c r="AB24" s="82"/>
+      <c r="X24" s="79"/>
+      <c r="Y24" s="79"/>
+      <c r="Z24" s="79"/>
+      <c r="AA24" s="79"/>
+      <c r="AB24" s="79"/>
       <c r="AC24" s="1"/>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="79"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -3242,12 +3245,12 @@
         <v>0.7055884</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="82"/>
-      <c r="O25" s="82"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="79"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
         <v>108</v>
@@ -3268,31 +3271,31 @@
         <v>0.45520664523399601</v>
       </c>
       <c r="W25" s="1"/>
-      <c r="X25" s="82"/>
-      <c r="Y25" s="82"/>
-      <c r="Z25" s="82"/>
-      <c r="AA25" s="82"/>
-      <c r="AB25" s="82"/>
+      <c r="X25" s="79"/>
+      <c r="Y25" s="79"/>
+      <c r="Z25" s="79"/>
+      <c r="AA25" s="79"/>
+      <c r="AB25" s="79"/>
       <c r="AC25" s="1"/>
     </row>
     <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="84"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="80"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="14" t="s">
         <v>109</v>
@@ -3313,16 +3316,16 @@
         <v>5.14251187538E-2</v>
       </c>
       <c r="W26" s="14"/>
-      <c r="X26" s="84"/>
-      <c r="Y26" s="84"/>
-      <c r="Z26" s="84"/>
-      <c r="AA26" s="84"/>
-      <c r="AB26" s="84"/>
+      <c r="X26" s="80"/>
+      <c r="Y26" s="80"/>
+      <c r="Z26" s="80"/>
+      <c r="AA26" s="80"/>
+      <c r="AB26" s="80"/>
       <c r="AC26" s="14"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="79" t="s">
-        <v>35</v>
+      <c r="A27" s="85" t="s">
+        <v>156</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>9</v>
@@ -3346,14 +3349,14 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I27" s="51"/>
-      <c r="J27" s="81" t="s">
+      <c r="J27" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="81"/>
+      <c r="K27" s="102"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="102"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="51"/>
       <c r="Q27" s="51" t="s">
         <v>106</v>
@@ -3374,17 +3377,17 @@
         <v>0.30992960000000003</v>
       </c>
       <c r="W27" s="51"/>
-      <c r="X27" s="81" t="s">
+      <c r="X27" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
+      <c r="Y27" s="102"/>
+      <c r="Z27" s="102"/>
+      <c r="AA27" s="102"/>
+      <c r="AB27" s="102"/>
       <c r="AC27" s="51"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="79"/>
+      <c r="A28" s="85"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -3407,12 +3410,12 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I28" s="1"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
         <v>107</v>
@@ -3433,15 +3436,15 @@
         <v>5.4385229999999998E-11</v>
       </c>
       <c r="W28" s="1"/>
-      <c r="X28" s="82"/>
-      <c r="Y28" s="82"/>
-      <c r="Z28" s="82"/>
-      <c r="AA28" s="82"/>
-      <c r="AB28" s="82"/>
+      <c r="X28" s="79"/>
+      <c r="Y28" s="79"/>
+      <c r="Z28" s="79"/>
+      <c r="AA28" s="79"/>
+      <c r="AB28" s="79"/>
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="79"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -3464,12 +3467,12 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I29" s="1"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
-      <c r="N29" s="82"/>
-      <c r="O29" s="82"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>108</v>
@@ -3490,31 +3493,31 @@
         <v>1.343811E-5</v>
       </c>
       <c r="W29" s="1"/>
-      <c r="X29" s="82"/>
-      <c r="Y29" s="82"/>
-      <c r="Z29" s="82"/>
-      <c r="AA29" s="82"/>
-      <c r="AB29" s="82"/>
+      <c r="X29" s="79"/>
+      <c r="Y29" s="79"/>
+      <c r="Z29" s="79"/>
+      <c r="AA29" s="79"/>
+      <c r="AB29" s="79"/>
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="82"/>
-      <c r="K30" s="82"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="82"/>
-      <c r="N30" s="82"/>
-      <c r="O30" s="82"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
         <v>109</v>
@@ -3535,15 +3538,15 @@
         <v>0.56057069999999998</v>
       </c>
       <c r="W30" s="1"/>
-      <c r="X30" s="82"/>
-      <c r="Y30" s="82"/>
-      <c r="Z30" s="82"/>
-      <c r="AA30" s="82"/>
-      <c r="AB30" s="82"/>
+      <c r="X30" s="79"/>
+      <c r="Y30" s="79"/>
+      <c r="Z30" s="79"/>
+      <c r="AA30" s="79"/>
+      <c r="AB30" s="79"/>
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="84" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -3568,15 +3571,15 @@
         <v>4.7200869189182898E-19</v>
       </c>
       <c r="I31" s="13"/>
-      <c r="J31" s="83" t="s">
+      <c r="J31" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="90" t="s">
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="100"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="84" t="s">
         <v>25</v>
       </c>
       <c r="Q31" s="13" t="s">
@@ -3598,17 +3601,17 @@
         <v>2.0108260000000001E-8</v>
       </c>
       <c r="W31" s="13"/>
-      <c r="X31" s="83" t="s">
+      <c r="X31" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y31" s="83"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="83"/>
-      <c r="AB31" s="83"/>
+      <c r="Y31" s="100"/>
+      <c r="Z31" s="100"/>
+      <c r="AA31" s="100"/>
+      <c r="AB31" s="100"/>
       <c r="AC31" s="13"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="79"/>
+      <c r="A32" s="85"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -3631,13 +3634,13 @@
         <v>0.78124664232875995</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="82"/>
-      <c r="O32" s="82"/>
-      <c r="P32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="79"/>
+      <c r="P32" s="85"/>
       <c r="Q32" s="1" t="s">
         <v>107</v>
       </c>
@@ -3657,15 +3660,15 @@
         <v>1.8776299999999999E-12</v>
       </c>
       <c r="W32" s="1"/>
-      <c r="X32" s="82"/>
-      <c r="Y32" s="82"/>
-      <c r="Z32" s="82"/>
-      <c r="AA32" s="82"/>
-      <c r="AB32" s="82"/>
+      <c r="X32" s="79"/>
+      <c r="Y32" s="79"/>
+      <c r="Z32" s="79"/>
+      <c r="AA32" s="79"/>
+      <c r="AB32" s="79"/>
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="79"/>
+      <c r="A33" s="85"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -3688,13 +3691,13 @@
         <v>0.116304482817742</v>
       </c>
       <c r="I33" s="1"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
-      <c r="N33" s="82"/>
-      <c r="O33" s="82"/>
-      <c r="P33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="85"/>
       <c r="Q33" s="1" t="s">
         <v>108</v>
       </c>
@@ -3714,32 +3717,32 @@
         <v>0.47088761094748599</v>
       </c>
       <c r="W33" s="1"/>
-      <c r="X33" s="82"/>
-      <c r="Y33" s="82"/>
-      <c r="Z33" s="82"/>
-      <c r="AA33" s="82"/>
-      <c r="AB33" s="82"/>
+      <c r="X33" s="79"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="79"/>
+      <c r="AB33" s="79"/>
       <c r="AC33" s="1"/>
     </row>
     <row r="34" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
+      <c r="A34" s="86"/>
       <c r="B34" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="84"/>
-      <c r="M34" s="84"/>
-      <c r="N34" s="84"/>
-      <c r="O34" s="84"/>
-      <c r="P34" s="91"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="86"/>
       <c r="Q34" s="14" t="s">
         <v>109</v>
       </c>
@@ -3759,11 +3762,11 @@
         <v>5.9871192312700001E-2</v>
       </c>
       <c r="W34" s="14"/>
-      <c r="X34" s="84"/>
-      <c r="Y34" s="84"/>
-      <c r="Z34" s="84"/>
-      <c r="AA34" s="84"/>
-      <c r="AB34" s="84"/>
+      <c r="X34" s="80"/>
+      <c r="Y34" s="80"/>
+      <c r="Z34" s="80"/>
+      <c r="AA34" s="80"/>
+      <c r="AB34" s="80"/>
       <c r="AC34" s="14"/>
     </row>
     <row r="35" spans="1:29" s="67" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3772,7 +3775,7 @@
       </c>
     </row>
     <row r="36" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="84" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -3815,7 +3818,7 @@
       <c r="O36" s="63">
         <v>3.7826149790259799E-5</v>
       </c>
-      <c r="P36" s="90" t="s">
+      <c r="P36" s="84" t="s">
         <v>11</v>
       </c>
       <c r="Q36" s="13" t="s">
@@ -3855,7 +3858,7 @@
       <c r="AC36" s="13"/>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="79"/>
+      <c r="A37" s="85"/>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
@@ -3896,7 +3899,7 @@
       <c r="O37" s="2">
         <v>5.3176769657787898E-3</v>
       </c>
-      <c r="P37" s="79"/>
+      <c r="P37" s="85"/>
       <c r="Q37" s="1" t="s">
         <v>107</v>
       </c>
@@ -3934,7 +3937,7 @@
       <c r="AC37" s="1"/>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" s="79"/>
+      <c r="A38" s="85"/>
       <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
@@ -3975,7 +3978,7 @@
       <c r="O38" s="3">
         <v>6.2255752292747699E-2</v>
       </c>
-      <c r="P38" s="79"/>
+      <c r="P38" s="85"/>
       <c r="Q38" s="1" t="s">
         <v>108</v>
       </c>
@@ -4013,16 +4016,16 @@
       <c r="AC38" s="1"/>
     </row>
     <row r="39" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="86"/>
       <c r="B39" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
+      <c r="C39" s="101"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="101"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14">
         <v>5.2456643231190104E-3</v>
@@ -4042,7 +4045,7 @@
       <c r="O39" s="14">
         <v>0.81735870029617597</v>
       </c>
-      <c r="P39" s="91"/>
+      <c r="P39" s="86"/>
       <c r="Q39" s="14" t="s">
         <v>109</v>
       </c>
@@ -4080,7 +4083,7 @@
       <c r="AC39" s="14"/>
     </row>
     <row r="40" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="84" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -4123,7 +4126,7 @@
       <c r="O40" s="64">
         <v>2.2627938793836001E-3</v>
       </c>
-      <c r="P40" s="90" t="s">
+      <c r="P40" s="84" t="s">
         <v>36</v>
       </c>
       <c r="Q40" s="13" t="s">
@@ -4163,7 +4166,7 @@
       <c r="AC40" s="13"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="79"/>
+      <c r="A41" s="85"/>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
@@ -4204,7 +4207,7 @@
       <c r="O41" s="2">
         <v>1.08776102041225E-2</v>
       </c>
-      <c r="P41" s="79"/>
+      <c r="P41" s="85"/>
       <c r="Q41" s="1" t="s">
         <v>107</v>
       </c>
@@ -4242,7 +4245,7 @@
       <c r="AC41" s="1"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="79"/>
+      <c r="A42" s="85"/>
       <c r="B42" s="1" t="s">
         <v>8</v>
       </c>
@@ -4283,7 +4286,7 @@
       <c r="O42" s="2">
         <v>1.9393437026140801E-2</v>
       </c>
-      <c r="P42" s="79"/>
+      <c r="P42" s="85"/>
       <c r="Q42" s="1" t="s">
         <v>108</v>
       </c>
@@ -4321,16 +4324,16 @@
       <c r="AC42" s="1"/>
     </row>
     <row r="43" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="91"/>
+      <c r="A43" s="86"/>
       <c r="B43" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="86"/>
-      <c r="D43" s="86"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="86"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="86"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14">
         <v>7.5239018444935397E-3</v>
@@ -4350,7 +4353,7 @@
       <c r="O43" s="14">
         <v>0.74958204967156605</v>
       </c>
-      <c r="P43" s="91"/>
+      <c r="P43" s="86"/>
       <c r="Q43" s="14" t="s">
         <v>109</v>
       </c>
@@ -4388,7 +4391,7 @@
       <c r="AC43" s="14"/>
     </row>
     <row r="44" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="90" t="s">
+      <c r="A44" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -4431,7 +4434,7 @@
       <c r="O44" s="13">
         <v>0.36857341395755699</v>
       </c>
-      <c r="P44" s="90" t="s">
+      <c r="P44" s="84" t="s">
         <v>12</v>
       </c>
       <c r="Q44" s="13" t="s">
@@ -4471,7 +4474,7 @@
       <c r="AC44" s="13"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="79"/>
+      <c r="A45" s="85"/>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
@@ -4512,7 +4515,7 @@
       <c r="O45" s="2">
         <v>1.4035037213878999E-4</v>
       </c>
-      <c r="P45" s="79"/>
+      <c r="P45" s="85"/>
       <c r="Q45" s="1" t="s">
         <v>107</v>
       </c>
@@ -4550,7 +4553,7 @@
       <c r="AC45" s="1"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="79"/>
+      <c r="A46" s="85"/>
       <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
@@ -4591,7 +4594,7 @@
       <c r="O46" s="1">
         <v>0.179227673464389</v>
       </c>
-      <c r="P46" s="79"/>
+      <c r="P46" s="85"/>
       <c r="Q46" s="1" t="s">
         <v>108</v>
       </c>
@@ -4629,16 +4632,16 @@
       <c r="AC46" s="1"/>
     </row>
     <row r="47" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="91"/>
+      <c r="A47" s="86"/>
       <c r="B47" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="86"/>
-      <c r="D47" s="86"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="86"/>
-      <c r="G47" s="86"/>
-      <c r="H47" s="86"/>
+      <c r="C47" s="101"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="101"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="101"/>
       <c r="I47" s="14"/>
       <c r="J47" s="71">
         <v>7.2143853443936604E-6</v>
@@ -4658,7 +4661,7 @@
       <c r="O47" s="14">
         <v>0.41012132536637402</v>
       </c>
-      <c r="P47" s="91"/>
+      <c r="P47" s="86"/>
       <c r="Q47" s="14" t="s">
         <v>109</v>
       </c>
@@ -4696,7 +4699,7 @@
       <c r="AC47" s="14"/>
     </row>
     <row r="48" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="90" t="s">
+      <c r="A48" s="84" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -4739,7 +4742,7 @@
       <c r="O48" s="64">
         <v>1.2711861864362099E-4</v>
       </c>
-      <c r="P48" s="90" t="s">
+      <c r="P48" s="84" t="s">
         <v>13</v>
       </c>
       <c r="Q48" s="13" t="s">
@@ -4779,7 +4782,7 @@
       <c r="AC48" s="13"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="79"/>
+      <c r="A49" s="85"/>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
@@ -4820,7 +4823,7 @@
       <c r="O49" s="1">
         <v>0.80787586394532096</v>
       </c>
-      <c r="P49" s="79"/>
+      <c r="P49" s="85"/>
       <c r="Q49" s="1" t="s">
         <v>107</v>
       </c>
@@ -4858,7 +4861,7 @@
       <c r="AC49" s="1"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="79"/>
+      <c r="A50" s="85"/>
       <c r="B50" s="1" t="s">
         <v>8</v>
       </c>
@@ -4899,7 +4902,7 @@
       <c r="O50" s="2">
         <v>2.7582949079364601E-2</v>
       </c>
-      <c r="P50" s="79"/>
+      <c r="P50" s="85"/>
       <c r="Q50" s="1" t="s">
         <v>108</v>
       </c>
@@ -4937,16 +4940,16 @@
       <c r="AC50" s="1"/>
     </row>
     <row r="51" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="91"/>
+      <c r="A51" s="86"/>
       <c r="B51" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="86"/>
-      <c r="D51" s="86"/>
-      <c r="E51" s="86"/>
-      <c r="F51" s="86"/>
-      <c r="G51" s="86"/>
-      <c r="H51" s="86"/>
+      <c r="C51" s="101"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="101"/>
+      <c r="F51" s="101"/>
+      <c r="G51" s="101"/>
+      <c r="H51" s="101"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14">
         <v>0.34951867520347901</v>
@@ -4966,7 +4969,7 @@
       <c r="O51" s="14">
         <v>0.57430971602825098</v>
       </c>
-      <c r="P51" s="91"/>
+      <c r="P51" s="86"/>
       <c r="Q51" s="14" t="s">
         <v>109</v>
       </c>
@@ -5004,7 +5007,7 @@
       <c r="AC51" s="14"/>
     </row>
     <row r="52" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="90" t="s">
+      <c r="A52" s="84" t="s">
         <v>16</v>
       </c>
       <c r="B52" s="13" t="s">
@@ -5047,7 +5050,7 @@
       <c r="O52" s="63">
         <v>4.8525436598560696E-10</v>
       </c>
-      <c r="P52" s="90" t="s">
+      <c r="P52" s="84" t="s">
         <v>16</v>
       </c>
       <c r="Q52" s="13" t="s">
@@ -5089,7 +5092,7 @@
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="79"/>
+      <c r="A53" s="85"/>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
@@ -5130,7 +5133,7 @@
       <c r="O53" s="4">
         <v>6.5162497916437297E-10</v>
       </c>
-      <c r="P53" s="79"/>
+      <c r="P53" s="85"/>
       <c r="Q53" s="1" t="s">
         <v>107</v>
       </c>
@@ -5170,7 +5173,7 @@
       </c>
     </row>
     <row r="54" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="79"/>
+      <c r="A54" s="85"/>
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
@@ -5211,7 +5214,7 @@
       <c r="O54" s="3">
         <v>7.1083850624745398E-2</v>
       </c>
-      <c r="P54" s="79"/>
+      <c r="P54" s="85"/>
       <c r="Q54" s="1" t="s">
         <v>108</v>
       </c>
@@ -5251,16 +5254,16 @@
       </c>
     </row>
     <row r="55" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="91"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C55" s="86"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
-      <c r="H55" s="86"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14">
         <v>3.6858467316493698E-2</v>
@@ -5280,7 +5283,7 @@
       <c r="O55" s="60">
         <v>3.8017401028842102E-2</v>
       </c>
-      <c r="P55" s="91"/>
+      <c r="P55" s="86"/>
       <c r="Q55" s="14" t="s">
         <v>109</v>
       </c>
@@ -5320,20 +5323,20 @@
       </c>
     </row>
     <row r="56" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="90" t="s">
+      <c r="A56" s="84" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="83" t="s">
+      <c r="C56" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
+      <c r="D56" s="100"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="100"/>
+      <c r="G56" s="100"/>
+      <c r="H56" s="100"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13">
         <v>4.0252880405239402E-2</v>
@@ -5353,19 +5356,19 @@
       <c r="O56" s="72">
         <v>8.2948057027609101E-2</v>
       </c>
-      <c r="P56" s="90" t="s">
+      <c r="P56" s="84" t="s">
         <v>38</v>
       </c>
       <c r="Q56" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R56" s="83" t="s">
+      <c r="R56" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="S56" s="83"/>
-      <c r="T56" s="83"/>
-      <c r="U56" s="83"/>
-      <c r="V56" s="83"/>
+      <c r="S56" s="100"/>
+      <c r="T56" s="100"/>
+      <c r="U56" s="100"/>
+      <c r="V56" s="100"/>
       <c r="W56" s="13"/>
       <c r="X56" s="13">
         <v>5.4104409999999999E-2</v>
@@ -5385,16 +5388,16 @@
       <c r="AC56" s="13"/>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="79"/>
+      <c r="A57" s="85"/>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="82"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="82"/>
-      <c r="F57" s="82"/>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
         <v>0.42132164214255802</v>
@@ -5414,15 +5417,15 @@
       <c r="O57" s="4">
         <v>7.7465741239532106E-5</v>
       </c>
-      <c r="P57" s="79"/>
+      <c r="P57" s="85"/>
       <c r="Q57" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R57" s="82"/>
-      <c r="S57" s="82"/>
-      <c r="T57" s="82"/>
-      <c r="U57" s="82"/>
-      <c r="V57" s="82"/>
+      <c r="R57" s="79"/>
+      <c r="S57" s="79"/>
+      <c r="T57" s="79"/>
+      <c r="U57" s="79"/>
+      <c r="V57" s="79"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1">
         <v>4.687269E-3</v>
@@ -5442,16 +5445,16 @@
       <c r="AC57" s="1"/>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="79"/>
+      <c r="A58" s="85"/>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
+      <c r="C58" s="79"/>
+      <c r="D58" s="79"/>
+      <c r="E58" s="79"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="79"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>7.8254362282741005E-2</v>
@@ -5471,15 +5474,15 @@
       <c r="O58" s="2">
         <v>1.63202510112339E-2</v>
       </c>
-      <c r="P58" s="79"/>
+      <c r="P58" s="85"/>
       <c r="Q58" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R58" s="82"/>
-      <c r="S58" s="82"/>
-      <c r="T58" s="82"/>
-      <c r="U58" s="82"/>
-      <c r="V58" s="82"/>
+      <c r="R58" s="79"/>
+      <c r="S58" s="79"/>
+      <c r="T58" s="79"/>
+      <c r="U58" s="79"/>
+      <c r="V58" s="79"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1">
         <v>-0.16190650000000001</v>
@@ -5499,16 +5502,16 @@
       <c r="AC58" s="1"/>
     </row>
     <row r="59" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="91"/>
+      <c r="A59" s="86"/>
       <c r="B59" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C59" s="84"/>
-      <c r="D59" s="84"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="84"/>
-      <c r="G59" s="84"/>
-      <c r="H59" s="84"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="80"/>
+      <c r="F59" s="80"/>
+      <c r="G59" s="80"/>
+      <c r="H59" s="80"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14">
         <v>2.6614614752845599E-3</v>
@@ -5528,15 +5531,15 @@
       <c r="O59" s="14">
         <v>0.90378258302877301</v>
       </c>
-      <c r="P59" s="91"/>
+      <c r="P59" s="86"/>
       <c r="Q59" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R59" s="84"/>
-      <c r="S59" s="84"/>
-      <c r="T59" s="84"/>
-      <c r="U59" s="84"/>
-      <c r="V59" s="84"/>
+      <c r="R59" s="80"/>
+      <c r="S59" s="80"/>
+      <c r="T59" s="80"/>
+      <c r="U59" s="80"/>
+      <c r="V59" s="80"/>
       <c r="W59" s="14"/>
       <c r="X59" s="14">
         <v>-0.22064059999999999</v>
@@ -5556,7 +5559,7 @@
       <c r="AC59" s="14"/>
     </row>
     <row r="60" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="84" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="13" t="s">
@@ -5581,15 +5584,15 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I60" s="13"/>
-      <c r="J60" s="83" t="s">
+      <c r="J60" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="83"/>
-      <c r="N60" s="83"/>
-      <c r="O60" s="83"/>
-      <c r="P60" s="90" t="s">
+      <c r="K60" s="100"/>
+      <c r="L60" s="100"/>
+      <c r="M60" s="100"/>
+      <c r="N60" s="100"/>
+      <c r="O60" s="100"/>
+      <c r="P60" s="84" t="s">
         <v>39</v>
       </c>
       <c r="Q60" s="13" t="s">
@@ -5611,17 +5614,17 @@
         <v>1.0710269999999999E-5</v>
       </c>
       <c r="W60" s="13"/>
-      <c r="X60" s="83" t="s">
+      <c r="X60" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y60" s="83"/>
-      <c r="Z60" s="83"/>
-      <c r="AA60" s="83"/>
-      <c r="AB60" s="83"/>
+      <c r="Y60" s="100"/>
+      <c r="Z60" s="100"/>
+      <c r="AA60" s="100"/>
+      <c r="AB60" s="100"/>
       <c r="AC60" s="13"/>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
@@ -5644,13 +5647,13 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="82"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="82"/>
-      <c r="M61" s="82"/>
-      <c r="N61" s="82"/>
-      <c r="O61" s="82"/>
-      <c r="P61" s="79"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="79"/>
+      <c r="L61" s="79"/>
+      <c r="M61" s="79"/>
+      <c r="N61" s="79"/>
+      <c r="O61" s="79"/>
+      <c r="P61" s="85"/>
       <c r="Q61" s="1" t="s">
         <v>107</v>
       </c>
@@ -5670,15 +5673,15 @@
         <v>1.3791302849E-6</v>
       </c>
       <c r="W61" s="1"/>
-      <c r="X61" s="82"/>
-      <c r="Y61" s="82"/>
-      <c r="Z61" s="82"/>
-      <c r="AA61" s="82"/>
-      <c r="AB61" s="82"/>
+      <c r="X61" s="79"/>
+      <c r="Y61" s="79"/>
+      <c r="Z61" s="79"/>
+      <c r="AA61" s="79"/>
+      <c r="AB61" s="79"/>
       <c r="AC61" s="1"/>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="1" t="s">
         <v>8</v>
       </c>
@@ -5701,13 +5704,13 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="82"/>
-      <c r="K62" s="82"/>
-      <c r="L62" s="82"/>
-      <c r="M62" s="82"/>
-      <c r="N62" s="82"/>
-      <c r="O62" s="82"/>
-      <c r="P62" s="79"/>
+      <c r="J62" s="79"/>
+      <c r="K62" s="79"/>
+      <c r="L62" s="79"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="79"/>
+      <c r="O62" s="79"/>
+      <c r="P62" s="85"/>
       <c r="Q62" s="1" t="s">
         <v>108</v>
       </c>
@@ -5727,32 +5730,32 @@
         <v>9.3598610230064994E-2</v>
       </c>
       <c r="W62" s="1"/>
-      <c r="X62" s="82"/>
-      <c r="Y62" s="82"/>
-      <c r="Z62" s="82"/>
-      <c r="AA62" s="82"/>
-      <c r="AB62" s="82"/>
+      <c r="X62" s="79"/>
+      <c r="Y62" s="79"/>
+      <c r="Z62" s="79"/>
+      <c r="AA62" s="79"/>
+      <c r="AB62" s="79"/>
       <c r="AC62" s="1"/>
     </row>
     <row r="63" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="91"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="86"/>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
-      <c r="H63" s="86"/>
+      <c r="C63" s="101"/>
+      <c r="D63" s="101"/>
+      <c r="E63" s="101"/>
+      <c r="F63" s="101"/>
+      <c r="G63" s="101"/>
+      <c r="H63" s="101"/>
       <c r="I63" s="14"/>
-      <c r="J63" s="84"/>
-      <c r="K63" s="84"/>
-      <c r="L63" s="84"/>
-      <c r="M63" s="84"/>
-      <c r="N63" s="84"/>
-      <c r="O63" s="84"/>
-      <c r="P63" s="91"/>
+      <c r="J63" s="80"/>
+      <c r="K63" s="80"/>
+      <c r="L63" s="80"/>
+      <c r="M63" s="80"/>
+      <c r="N63" s="80"/>
+      <c r="O63" s="80"/>
+      <c r="P63" s="86"/>
       <c r="Q63" s="14" t="s">
         <v>109</v>
       </c>
@@ -5772,15 +5775,15 @@
         <v>3.7977520000000001E-2</v>
       </c>
       <c r="W63" s="14"/>
-      <c r="X63" s="84"/>
-      <c r="Y63" s="84"/>
-      <c r="Z63" s="84"/>
-      <c r="AA63" s="84"/>
-      <c r="AB63" s="84"/>
+      <c r="X63" s="80"/>
+      <c r="Y63" s="80"/>
+      <c r="Z63" s="80"/>
+      <c r="AA63" s="80"/>
+      <c r="AB63" s="80"/>
       <c r="AC63" s="14"/>
     </row>
     <row r="64" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="90" t="s">
+      <c r="A64" s="84" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="13" t="s">
@@ -5805,15 +5808,15 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I64" s="13"/>
-      <c r="J64" s="83" t="s">
+      <c r="J64" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K64" s="83"/>
-      <c r="L64" s="83"/>
-      <c r="M64" s="83"/>
-      <c r="N64" s="83"/>
-      <c r="O64" s="83"/>
-      <c r="P64" s="90" t="s">
+      <c r="K64" s="100"/>
+      <c r="L64" s="100"/>
+      <c r="M64" s="100"/>
+      <c r="N64" s="100"/>
+      <c r="O64" s="100"/>
+      <c r="P64" s="84" t="s">
         <v>150</v>
       </c>
       <c r="Q64" s="13" t="s">
@@ -5835,17 +5838,17 @@
         <v>5.242662E-14</v>
       </c>
       <c r="W64" s="13"/>
-      <c r="X64" s="83" t="s">
+      <c r="X64" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y64" s="83"/>
-      <c r="Z64" s="83"/>
-      <c r="AA64" s="83"/>
-      <c r="AB64" s="83"/>
+      <c r="Y64" s="100"/>
+      <c r="Z64" s="100"/>
+      <c r="AA64" s="100"/>
+      <c r="AB64" s="100"/>
       <c r="AC64" s="13"/>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="79"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
@@ -5868,13 +5871,13 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="82"/>
-      <c r="K65" s="82"/>
-      <c r="L65" s="82"/>
-      <c r="M65" s="82"/>
-      <c r="N65" s="82"/>
-      <c r="O65" s="82"/>
-      <c r="P65" s="79"/>
+      <c r="J65" s="79"/>
+      <c r="K65" s="79"/>
+      <c r="L65" s="79"/>
+      <c r="M65" s="79"/>
+      <c r="N65" s="79"/>
+      <c r="O65" s="79"/>
+      <c r="P65" s="85"/>
       <c r="Q65" s="1" t="s">
         <v>107</v>
       </c>
@@ -5894,15 +5897,15 @@
         <v>3.4043159999999998E-14</v>
       </c>
       <c r="W65" s="1"/>
-      <c r="X65" s="82"/>
-      <c r="Y65" s="82"/>
-      <c r="Z65" s="82"/>
-      <c r="AA65" s="82"/>
-      <c r="AB65" s="82"/>
+      <c r="X65" s="79"/>
+      <c r="Y65" s="79"/>
+      <c r="Z65" s="79"/>
+      <c r="AA65" s="79"/>
+      <c r="AB65" s="79"/>
       <c r="AC65" s="1"/>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="79"/>
+      <c r="A66" s="85"/>
       <c r="B66" s="1" t="s">
         <v>8</v>
       </c>
@@ -5925,13 +5928,13 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="82"/>
-      <c r="K66" s="82"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="82"/>
-      <c r="N66" s="82"/>
-      <c r="O66" s="82"/>
-      <c r="P66" s="79"/>
+      <c r="J66" s="79"/>
+      <c r="K66" s="79"/>
+      <c r="L66" s="79"/>
+      <c r="M66" s="79"/>
+      <c r="N66" s="79"/>
+      <c r="O66" s="79"/>
+      <c r="P66" s="85"/>
       <c r="Q66" s="1" t="s">
         <v>108</v>
       </c>
@@ -5951,32 +5954,32 @@
         <v>0.64513220100000002</v>
       </c>
       <c r="W66" s="1"/>
-      <c r="X66" s="82"/>
-      <c r="Y66" s="82"/>
-      <c r="Z66" s="82"/>
-      <c r="AA66" s="82"/>
-      <c r="AB66" s="82"/>
+      <c r="X66" s="79"/>
+      <c r="Y66" s="79"/>
+      <c r="Z66" s="79"/>
+      <c r="AA66" s="79"/>
+      <c r="AB66" s="79"/>
       <c r="AC66" s="1"/>
     </row>
     <row r="67" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="86"/>
-      <c r="D67" s="86"/>
-      <c r="E67" s="86"/>
-      <c r="F67" s="86"/>
-      <c r="G67" s="86"/>
-      <c r="H67" s="86"/>
+      <c r="C67" s="101"/>
+      <c r="D67" s="101"/>
+      <c r="E67" s="101"/>
+      <c r="F67" s="101"/>
+      <c r="G67" s="101"/>
+      <c r="H67" s="101"/>
       <c r="I67" s="14"/>
-      <c r="J67" s="84"/>
-      <c r="K67" s="84"/>
-      <c r="L67" s="84"/>
-      <c r="M67" s="84"/>
-      <c r="N67" s="84"/>
-      <c r="O67" s="84"/>
-      <c r="P67" s="91"/>
+      <c r="J67" s="80"/>
+      <c r="K67" s="80"/>
+      <c r="L67" s="80"/>
+      <c r="M67" s="80"/>
+      <c r="N67" s="80"/>
+      <c r="O67" s="80"/>
+      <c r="P67" s="86"/>
       <c r="Q67" s="14" t="s">
         <v>109</v>
       </c>
@@ -5996,28 +5999,28 @@
         <v>0.36655130000000002</v>
       </c>
       <c r="W67" s="14"/>
-      <c r="X67" s="84"/>
-      <c r="Y67" s="84"/>
-      <c r="Z67" s="84"/>
-      <c r="AA67" s="84"/>
-      <c r="AB67" s="84"/>
+      <c r="X67" s="80"/>
+      <c r="Y67" s="80"/>
+      <c r="Z67" s="80"/>
+      <c r="AA67" s="80"/>
+      <c r="AB67" s="80"/>
       <c r="AC67" s="14"/>
     </row>
     <row r="68" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="90" t="s">
+      <c r="A68" s="84" t="s">
         <v>28</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="83" t="s">
+      <c r="C68" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D68" s="83"/>
-      <c r="E68" s="83"/>
-      <c r="F68" s="83"/>
-      <c r="G68" s="83"/>
-      <c r="H68" s="83"/>
+      <c r="D68" s="100"/>
+      <c r="E68" s="100"/>
+      <c r="F68" s="100"/>
+      <c r="G68" s="100"/>
+      <c r="H68" s="100"/>
       <c r="I68" s="13"/>
       <c r="J68" s="13">
         <v>4.9920514192076698E-4</v>
@@ -6037,19 +6040,19 @@
       <c r="O68" s="72">
         <v>7.0143959578357298E-2</v>
       </c>
-      <c r="P68" s="90" t="s">
+      <c r="P68" s="84" t="s">
         <v>148</v>
       </c>
       <c r="Q68" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R68" s="83" t="s">
+      <c r="R68" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="S68" s="83"/>
-      <c r="T68" s="83"/>
-      <c r="U68" s="83"/>
-      <c r="V68" s="83"/>
+      <c r="S68" s="100"/>
+      <c r="T68" s="100"/>
+      <c r="U68" s="100"/>
+      <c r="V68" s="100"/>
       <c r="W68" s="13"/>
       <c r="X68" s="70">
         <v>3.8010990000000001E-3</v>
@@ -6069,16 +6072,16 @@
       <c r="AC68" s="13"/>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="79"/>
+      <c r="A69" s="85"/>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
-      <c r="H69" s="82"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="79"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>4.3245963051368403E-3</v>
@@ -6098,15 +6101,15 @@
       <c r="O69" s="4">
         <v>8.7931651517614295E-5</v>
       </c>
-      <c r="P69" s="79"/>
+      <c r="P69" s="85"/>
       <c r="Q69" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R69" s="82"/>
-      <c r="S69" s="82"/>
-      <c r="T69" s="82"/>
-      <c r="U69" s="82"/>
-      <c r="V69" s="82"/>
+      <c r="R69" s="79"/>
+      <c r="S69" s="79"/>
+      <c r="T69" s="79"/>
+      <c r="U69" s="79"/>
+      <c r="V69" s="79"/>
       <c r="W69" s="1"/>
       <c r="X69" s="45">
         <v>2.6998579999999999E-3</v>
@@ -6126,16 +6129,16 @@
       <c r="AC69" s="1"/>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="79"/>
+      <c r="A70" s="85"/>
       <c r="B70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="82"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="79"/>
       <c r="I70" s="1"/>
       <c r="J70" s="5">
         <v>4.4673218852987901E-5</v>
@@ -6155,15 +6158,15 @@
       <c r="O70" s="1">
         <v>0.58543070585289902</v>
       </c>
-      <c r="P70" s="79"/>
+      <c r="P70" s="85"/>
       <c r="Q70" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R70" s="82"/>
-      <c r="S70" s="82"/>
-      <c r="T70" s="82"/>
-      <c r="U70" s="82"/>
-      <c r="V70" s="82"/>
+      <c r="R70" s="79"/>
+      <c r="S70" s="79"/>
+      <c r="T70" s="79"/>
+      <c r="U70" s="79"/>
+      <c r="V70" s="79"/>
       <c r="W70" s="1"/>
       <c r="X70" s="45">
         <v>-1.146374E-2</v>
@@ -6183,16 +6186,16 @@
       <c r="AC70" s="1"/>
     </row>
     <row r="71" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="84"/>
-      <c r="D71" s="84"/>
-      <c r="E71" s="84"/>
-      <c r="F71" s="84"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="84"/>
+      <c r="C71" s="80"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="80"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="80"/>
+      <c r="H71" s="80"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14">
         <v>2.5092673060789E-4</v>
@@ -6212,15 +6215,15 @@
       <c r="O71" s="14">
         <v>0.43421981831232398</v>
       </c>
-      <c r="P71" s="91"/>
+      <c r="P71" s="86"/>
       <c r="Q71" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R71" s="84"/>
-      <c r="S71" s="84"/>
-      <c r="T71" s="84"/>
-      <c r="U71" s="84"/>
-      <c r="V71" s="84"/>
+      <c r="R71" s="80"/>
+      <c r="S71" s="80"/>
+      <c r="T71" s="80"/>
+      <c r="U71" s="80"/>
+      <c r="V71" s="80"/>
       <c r="W71" s="14"/>
       <c r="X71" s="61">
         <v>-1.288595E-2</v>
@@ -6240,20 +6243,20 @@
       <c r="AC71" s="14"/>
     </row>
     <row r="72" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="84" t="s">
         <v>18</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="83" t="s">
+      <c r="C72" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="83"/>
-      <c r="H72" s="83"/>
+      <c r="D72" s="100"/>
+      <c r="E72" s="100"/>
+      <c r="F72" s="100"/>
+      <c r="G72" s="100"/>
+      <c r="H72" s="100"/>
       <c r="I72" s="13"/>
       <c r="J72" s="13">
         <v>7.7190184322692705E-4</v>
@@ -6273,19 +6276,19 @@
       <c r="O72" s="13">
         <v>0.71627332791354703</v>
       </c>
-      <c r="P72" s="90" t="s">
+      <c r="P72" s="84" t="s">
         <v>143</v>
       </c>
       <c r="Q72" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R72" s="83" t="s">
+      <c r="R72" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="S72" s="83"/>
-      <c r="T72" s="83"/>
-      <c r="U72" s="83"/>
-      <c r="V72" s="83"/>
+      <c r="S72" s="100"/>
+      <c r="T72" s="100"/>
+      <c r="U72" s="100"/>
+      <c r="V72" s="100"/>
       <c r="W72" s="13"/>
       <c r="X72" s="70">
         <v>-8.3753321000000006E-3</v>
@@ -6304,16 +6307,16 @@
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="79"/>
+      <c r="A73" s="85"/>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="82"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="82"/>
-      <c r="F73" s="82"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
+      <c r="C73" s="79"/>
+      <c r="D73" s="79"/>
+      <c r="E73" s="79"/>
+      <c r="F73" s="79"/>
+      <c r="G73" s="79"/>
+      <c r="H73" s="79"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1">
         <v>0.26383928794443301</v>
@@ -6333,15 +6336,15 @@
       <c r="O73" s="4">
         <v>8.8402488312841299E-6</v>
       </c>
-      <c r="P73" s="79"/>
+      <c r="P73" s="85"/>
       <c r="Q73" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R73" s="82"/>
-      <c r="S73" s="82"/>
-      <c r="T73" s="82"/>
-      <c r="U73" s="82"/>
-      <c r="V73" s="82"/>
+      <c r="R73" s="79"/>
+      <c r="S73" s="79"/>
+      <c r="T73" s="79"/>
+      <c r="U73" s="79"/>
+      <c r="V73" s="79"/>
       <c r="W73" s="1"/>
       <c r="X73" s="45">
         <v>6.2885479999999997E-3</v>
@@ -6360,16 +6363,16 @@
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="79"/>
+      <c r="A74" s="85"/>
       <c r="B74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="82"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="82"/>
-      <c r="F74" s="82"/>
-      <c r="G74" s="82"/>
-      <c r="H74" s="82"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="79"/>
+      <c r="E74" s="79"/>
+      <c r="F74" s="79"/>
+      <c r="G74" s="79"/>
+      <c r="H74" s="79"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1">
         <v>6.5298294112546198E-3</v>
@@ -6389,15 +6392,15 @@
       <c r="O74" s="1">
         <v>0.29157119540922299</v>
       </c>
-      <c r="P74" s="79"/>
+      <c r="P74" s="85"/>
       <c r="Q74" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R74" s="82"/>
-      <c r="S74" s="82"/>
-      <c r="T74" s="82"/>
-      <c r="U74" s="82"/>
-      <c r="V74" s="82"/>
+      <c r="R74" s="79"/>
+      <c r="S74" s="79"/>
+      <c r="T74" s="79"/>
+      <c r="U74" s="79"/>
+      <c r="V74" s="79"/>
       <c r="W74" s="1"/>
       <c r="X74" s="45">
         <v>-0.1092133</v>
@@ -6416,16 +6419,16 @@
       </c>
     </row>
     <row r="75" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="91"/>
+      <c r="A75" s="86"/>
       <c r="B75" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C75" s="84"/>
-      <c r="D75" s="84"/>
-      <c r="E75" s="84"/>
-      <c r="F75" s="84"/>
-      <c r="G75" s="84"/>
-      <c r="H75" s="84"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="80"/>
+      <c r="F75" s="80"/>
+      <c r="G75" s="80"/>
+      <c r="H75" s="80"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14">
         <v>7.3489818378573097E-3</v>
@@ -6445,15 +6448,15 @@
       <c r="O75" s="14">
         <v>0.53343128963438502</v>
       </c>
-      <c r="P75" s="91"/>
+      <c r="P75" s="86"/>
       <c r="Q75" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="R75" s="84"/>
-      <c r="S75" s="84"/>
-      <c r="T75" s="84"/>
-      <c r="U75" s="84"/>
-      <c r="V75" s="84"/>
+      <c r="R75" s="80"/>
+      <c r="S75" s="80"/>
+      <c r="T75" s="80"/>
+      <c r="U75" s="80"/>
+      <c r="V75" s="80"/>
       <c r="W75" s="14"/>
       <c r="X75" s="61">
         <v>-9.8989809999999998E-2</v>
@@ -6472,7 +6475,7 @@
       </c>
     </row>
     <row r="76" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="84" t="s">
         <v>19</v>
       </c>
       <c r="B76" s="13" t="s">
@@ -6497,15 +6500,15 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I76" s="13"/>
-      <c r="J76" s="83" t="s">
+      <c r="J76" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K76" s="83"/>
-      <c r="L76" s="83"/>
-      <c r="M76" s="83"/>
-      <c r="N76" s="83"/>
-      <c r="O76" s="83"/>
-      <c r="P76" s="90" t="s">
+      <c r="K76" s="100"/>
+      <c r="L76" s="100"/>
+      <c r="M76" s="100"/>
+      <c r="N76" s="100"/>
+      <c r="O76" s="100"/>
+      <c r="P76" s="84" t="s">
         <v>144</v>
       </c>
       <c r="Q76" s="13" t="s">
@@ -6527,16 +6530,16 @@
         <v>2.350653E-6</v>
       </c>
       <c r="W76" s="13"/>
-      <c r="X76" s="83" t="s">
+      <c r="X76" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y76" s="83"/>
-      <c r="Z76" s="83"/>
-      <c r="AA76" s="83"/>
-      <c r="AB76" s="83"/>
+      <c r="Y76" s="100"/>
+      <c r="Z76" s="100"/>
+      <c r="AA76" s="100"/>
+      <c r="AB76" s="100"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="79"/>
+      <c r="A77" s="85"/>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
@@ -6559,13 +6562,13 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="82"/>
-      <c r="L77" s="82"/>
-      <c r="M77" s="82"/>
-      <c r="N77" s="82"/>
-      <c r="O77" s="82"/>
-      <c r="P77" s="79"/>
+      <c r="J77" s="79"/>
+      <c r="K77" s="79"/>
+      <c r="L77" s="79"/>
+      <c r="M77" s="79"/>
+      <c r="N77" s="79"/>
+      <c r="O77" s="79"/>
+      <c r="P77" s="85"/>
       <c r="Q77" s="1" t="s">
         <v>107</v>
       </c>
@@ -6585,14 +6588,14 @@
         <v>2.3278650000000001E-13</v>
       </c>
       <c r="W77" s="1"/>
-      <c r="X77" s="82"/>
-      <c r="Y77" s="82"/>
-      <c r="Z77" s="82"/>
-      <c r="AA77" s="82"/>
-      <c r="AB77" s="82"/>
+      <c r="X77" s="79"/>
+      <c r="Y77" s="79"/>
+      <c r="Z77" s="79"/>
+      <c r="AA77" s="79"/>
+      <c r="AB77" s="79"/>
     </row>
     <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="79"/>
+      <c r="A78" s="85"/>
       <c r="B78" s="1" t="s">
         <v>8</v>
       </c>
@@ -6615,13 +6618,13 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I78" s="1"/>
-      <c r="J78" s="82"/>
-      <c r="K78" s="82"/>
-      <c r="L78" s="82"/>
-      <c r="M78" s="82"/>
-      <c r="N78" s="82"/>
-      <c r="O78" s="82"/>
-      <c r="P78" s="79"/>
+      <c r="J78" s="79"/>
+      <c r="K78" s="79"/>
+      <c r="L78" s="79"/>
+      <c r="M78" s="79"/>
+      <c r="N78" s="79"/>
+      <c r="O78" s="79"/>
+      <c r="P78" s="85"/>
       <c r="Q78" s="1" t="s">
         <v>108</v>
       </c>
@@ -6641,31 +6644,31 @@
         <v>5.789537E-3</v>
       </c>
       <c r="W78" s="1"/>
-      <c r="X78" s="82"/>
-      <c r="Y78" s="82"/>
-      <c r="Z78" s="82"/>
-      <c r="AA78" s="82"/>
-      <c r="AB78" s="82"/>
+      <c r="X78" s="79"/>
+      <c r="Y78" s="79"/>
+      <c r="Z78" s="79"/>
+      <c r="AA78" s="79"/>
+      <c r="AB78" s="79"/>
     </row>
     <row r="79" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="91"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="86"/>
-      <c r="D79" s="86"/>
-      <c r="E79" s="86"/>
-      <c r="F79" s="86"/>
-      <c r="G79" s="86"/>
-      <c r="H79" s="86"/>
+      <c r="C79" s="101"/>
+      <c r="D79" s="101"/>
+      <c r="E79" s="101"/>
+      <c r="F79" s="101"/>
+      <c r="G79" s="101"/>
+      <c r="H79" s="101"/>
       <c r="I79" s="14"/>
-      <c r="J79" s="84"/>
-      <c r="K79" s="84"/>
-      <c r="L79" s="84"/>
-      <c r="M79" s="84"/>
-      <c r="N79" s="84"/>
-      <c r="O79" s="84"/>
-      <c r="P79" s="91"/>
+      <c r="J79" s="80"/>
+      <c r="K79" s="80"/>
+      <c r="L79" s="80"/>
+      <c r="M79" s="80"/>
+      <c r="N79" s="80"/>
+      <c r="O79" s="80"/>
+      <c r="P79" s="86"/>
       <c r="Q79" s="14" t="s">
         <v>109</v>
       </c>
@@ -6685,14 +6688,14 @@
         <v>3.5774789999999998E-4</v>
       </c>
       <c r="W79" s="14"/>
-      <c r="X79" s="84"/>
-      <c r="Y79" s="84"/>
-      <c r="Z79" s="84"/>
-      <c r="AA79" s="84"/>
-      <c r="AB79" s="84"/>
+      <c r="X79" s="80"/>
+      <c r="Y79" s="80"/>
+      <c r="Z79" s="80"/>
+      <c r="AA79" s="80"/>
+      <c r="AB79" s="80"/>
     </row>
     <row r="80" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="90" t="s">
+      <c r="A80" s="84" t="s">
         <v>23</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -6717,15 +6720,15 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I80" s="13"/>
-      <c r="J80" s="83" t="s">
+      <c r="J80" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K80" s="83"/>
-      <c r="L80" s="83"/>
-      <c r="M80" s="83"/>
-      <c r="N80" s="83"/>
-      <c r="O80" s="83"/>
-      <c r="P80" s="90" t="s">
+      <c r="K80" s="100"/>
+      <c r="L80" s="100"/>
+      <c r="M80" s="100"/>
+      <c r="N80" s="100"/>
+      <c r="O80" s="100"/>
+      <c r="P80" s="84" t="s">
         <v>145</v>
       </c>
       <c r="Q80" s="13" t="s">
@@ -6747,17 +6750,17 @@
         <v>2.524047E-13</v>
       </c>
       <c r="W80" s="13"/>
-      <c r="X80" s="83" t="s">
+      <c r="X80" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y80" s="83"/>
-      <c r="Z80" s="83"/>
-      <c r="AA80" s="83"/>
-      <c r="AB80" s="83"/>
+      <c r="Y80" s="100"/>
+      <c r="Z80" s="100"/>
+      <c r="AA80" s="100"/>
+      <c r="AB80" s="100"/>
       <c r="AC80" s="13"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A81" s="79"/>
+      <c r="A81" s="85"/>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
@@ -6780,13 +6783,13 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="82"/>
-      <c r="K81" s="82"/>
-      <c r="L81" s="82"/>
-      <c r="M81" s="82"/>
-      <c r="N81" s="82"/>
-      <c r="O81" s="82"/>
-      <c r="P81" s="79"/>
+      <c r="J81" s="79"/>
+      <c r="K81" s="79"/>
+      <c r="L81" s="79"/>
+      <c r="M81" s="79"/>
+      <c r="N81" s="79"/>
+      <c r="O81" s="79"/>
+      <c r="P81" s="85"/>
       <c r="Q81" s="1" t="s">
         <v>107</v>
       </c>
@@ -6806,15 +6809,15 @@
         <v>8.8521990000000004E-10</v>
       </c>
       <c r="W81" s="1"/>
-      <c r="X81" s="82"/>
-      <c r="Y81" s="82"/>
-      <c r="Z81" s="82"/>
-      <c r="AA81" s="82"/>
-      <c r="AB81" s="82"/>
+      <c r="X81" s="79"/>
+      <c r="Y81" s="79"/>
+      <c r="Z81" s="79"/>
+      <c r="AA81" s="79"/>
+      <c r="AB81" s="79"/>
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A82" s="79"/>
+      <c r="A82" s="85"/>
       <c r="B82" s="1" t="s">
         <v>8</v>
       </c>
@@ -6837,13 +6840,13 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="82"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
-      <c r="P82" s="79"/>
+      <c r="J82" s="79"/>
+      <c r="K82" s="79"/>
+      <c r="L82" s="79"/>
+      <c r="M82" s="79"/>
+      <c r="N82" s="79"/>
+      <c r="O82" s="79"/>
+      <c r="P82" s="85"/>
       <c r="Q82" s="1" t="s">
         <v>108</v>
       </c>
@@ -6863,32 +6866,32 @@
         <v>9.6146709999999996E-2</v>
       </c>
       <c r="W82" s="1"/>
-      <c r="X82" s="82"/>
-      <c r="Y82" s="82"/>
-      <c r="Z82" s="82"/>
-      <c r="AA82" s="82"/>
-      <c r="AB82" s="82"/>
+      <c r="X82" s="79"/>
+      <c r="Y82" s="79"/>
+      <c r="Z82" s="79"/>
+      <c r="AA82" s="79"/>
+      <c r="AB82" s="79"/>
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="91"/>
+      <c r="A83" s="86"/>
       <c r="B83" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C83" s="86"/>
-      <c r="D83" s="86"/>
-      <c r="E83" s="86"/>
-      <c r="F83" s="86"/>
-      <c r="G83" s="86"/>
-      <c r="H83" s="86"/>
+      <c r="C83" s="101"/>
+      <c r="D83" s="101"/>
+      <c r="E83" s="101"/>
+      <c r="F83" s="101"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="101"/>
       <c r="I83" s="14"/>
-      <c r="J83" s="84"/>
-      <c r="K83" s="84"/>
-      <c r="L83" s="84"/>
-      <c r="M83" s="84"/>
-      <c r="N83" s="84"/>
-      <c r="O83" s="84"/>
-      <c r="P83" s="91"/>
+      <c r="J83" s="80"/>
+      <c r="K83" s="80"/>
+      <c r="L83" s="80"/>
+      <c r="M83" s="80"/>
+      <c r="N83" s="80"/>
+      <c r="O83" s="80"/>
+      <c r="P83" s="86"/>
       <c r="Q83" s="14" t="s">
         <v>109</v>
       </c>
@@ -6908,15 +6911,15 @@
         <v>6.7150146952E-3</v>
       </c>
       <c r="W83" s="14"/>
-      <c r="X83" s="84"/>
-      <c r="Y83" s="84"/>
-      <c r="Z83" s="84"/>
-      <c r="AA83" s="84"/>
-      <c r="AB83" s="84"/>
+      <c r="X83" s="80"/>
+      <c r="Y83" s="80"/>
+      <c r="Z83" s="80"/>
+      <c r="AA83" s="80"/>
+      <c r="AB83" s="80"/>
       <c r="AC83" s="14"/>
     </row>
     <row r="84" spans="1:29" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="90" t="s">
+      <c r="A84" s="84" t="s">
         <v>155</v>
       </c>
       <c r="B84" s="13" t="s">
@@ -6941,15 +6944,15 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I84" s="13"/>
-      <c r="J84" s="83" t="s">
+      <c r="J84" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="K84" s="83"/>
-      <c r="L84" s="83"/>
-      <c r="M84" s="83"/>
-      <c r="N84" s="83"/>
-      <c r="O84" s="83"/>
-      <c r="P84" s="90" t="s">
+      <c r="K84" s="100"/>
+      <c r="L84" s="100"/>
+      <c r="M84" s="100"/>
+      <c r="N84" s="100"/>
+      <c r="O84" s="100"/>
+      <c r="P84" s="84" t="s">
         <v>149</v>
       </c>
       <c r="Q84" s="13" t="s">
@@ -6971,17 +6974,17 @@
         <v>0.96106304949900001</v>
       </c>
       <c r="W84" s="13"/>
-      <c r="X84" s="83" t="s">
+      <c r="X84" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="Y84" s="83"/>
-      <c r="Z84" s="83"/>
-      <c r="AA84" s="83"/>
-      <c r="AB84" s="83"/>
+      <c r="Y84" s="100"/>
+      <c r="Z84" s="100"/>
+      <c r="AA84" s="100"/>
+      <c r="AB84" s="100"/>
       <c r="AC84" s="13"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A85" s="79"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
@@ -7004,13 +7007,13 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
-      <c r="N85" s="82"/>
-      <c r="O85" s="82"/>
-      <c r="P85" s="79"/>
+      <c r="J85" s="79"/>
+      <c r="K85" s="79"/>
+      <c r="L85" s="79"/>
+      <c r="M85" s="79"/>
+      <c r="N85" s="79"/>
+      <c r="O85" s="79"/>
+      <c r="P85" s="85"/>
       <c r="Q85" s="1" t="s">
         <v>107</v>
       </c>
@@ -7030,15 +7033,15 @@
         <v>0.2307786</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="82"/>
-      <c r="Y85" s="82"/>
-      <c r="Z85" s="82"/>
-      <c r="AA85" s="82"/>
-      <c r="AB85" s="82"/>
+      <c r="X85" s="79"/>
+      <c r="Y85" s="79"/>
+      <c r="Z85" s="79"/>
+      <c r="AA85" s="79"/>
+      <c r="AB85" s="79"/>
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A86" s="79"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
@@ -7061,13 +7064,13 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I86" s="1"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
-      <c r="N86" s="82"/>
-      <c r="O86" s="82"/>
-      <c r="P86" s="79"/>
+      <c r="J86" s="79"/>
+      <c r="K86" s="79"/>
+      <c r="L86" s="79"/>
+      <c r="M86" s="79"/>
+      <c r="N86" s="79"/>
+      <c r="O86" s="79"/>
+      <c r="P86" s="85"/>
       <c r="Q86" s="1" t="s">
         <v>108</v>
       </c>
@@ -7087,32 +7090,32 @@
         <v>3.2851500000000001E-3</v>
       </c>
       <c r="W86" s="1"/>
-      <c r="X86" s="82"/>
-      <c r="Y86" s="82"/>
-      <c r="Z86" s="82"/>
-      <c r="AA86" s="82"/>
-      <c r="AB86" s="82"/>
+      <c r="X86" s="79"/>
+      <c r="Y86" s="79"/>
+      <c r="Z86" s="79"/>
+      <c r="AA86" s="79"/>
+      <c r="AB86" s="79"/>
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" s="55" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="91"/>
+      <c r="A87" s="86"/>
       <c r="B87" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C87" s="86"/>
-      <c r="D87" s="86"/>
-      <c r="E87" s="86"/>
-      <c r="F87" s="86"/>
-      <c r="G87" s="86"/>
-      <c r="H87" s="86"/>
+      <c r="C87" s="101"/>
+      <c r="D87" s="101"/>
+      <c r="E87" s="101"/>
+      <c r="F87" s="101"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="101"/>
       <c r="I87" s="14"/>
-      <c r="J87" s="84"/>
-      <c r="K87" s="84"/>
-      <c r="L87" s="84"/>
-      <c r="M87" s="84"/>
-      <c r="N87" s="84"/>
-      <c r="O87" s="84"/>
-      <c r="P87" s="91"/>
+      <c r="J87" s="80"/>
+      <c r="K87" s="80"/>
+      <c r="L87" s="80"/>
+      <c r="M87" s="80"/>
+      <c r="N87" s="80"/>
+      <c r="O87" s="80"/>
+      <c r="P87" s="86"/>
       <c r="Q87" s="14" t="s">
         <v>109</v>
       </c>
@@ -7132,54 +7135,49 @@
         <v>9.3442800000000006E-2</v>
       </c>
       <c r="W87" s="14"/>
-      <c r="X87" s="84"/>
-      <c r="Y87" s="84"/>
-      <c r="Z87" s="84"/>
-      <c r="AA87" s="84"/>
-      <c r="AB87" s="84"/>
+      <c r="X87" s="80"/>
+      <c r="Y87" s="80"/>
+      <c r="Z87" s="80"/>
+      <c r="AA87" s="80"/>
+      <c r="AB87" s="80"/>
       <c r="AC87" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="R11:V14"/>
-    <mergeCell ref="X1:AC1"/>
-    <mergeCell ref="P48:P51"/>
-    <mergeCell ref="P3:P6"/>
-    <mergeCell ref="X3:AB6"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="P36:P39"/>
-    <mergeCell ref="P40:P43"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="P44:P47"/>
-    <mergeCell ref="P15:P18"/>
-    <mergeCell ref="P7:P10"/>
-    <mergeCell ref="P60:P63"/>
-    <mergeCell ref="P72:P75"/>
-    <mergeCell ref="P11:P14"/>
-    <mergeCell ref="P56:P59"/>
-    <mergeCell ref="X76:AB79"/>
-    <mergeCell ref="X60:AB63"/>
-    <mergeCell ref="P80:P83"/>
-    <mergeCell ref="X84:AB87"/>
-    <mergeCell ref="P19:P22"/>
-    <mergeCell ref="R19:V22"/>
-    <mergeCell ref="P84:P87"/>
-    <mergeCell ref="P64:P67"/>
-    <mergeCell ref="X64:AB67"/>
-    <mergeCell ref="R72:V75"/>
-    <mergeCell ref="P76:P79"/>
-    <mergeCell ref="X80:AB83"/>
-    <mergeCell ref="R56:V59"/>
-    <mergeCell ref="P52:P55"/>
-    <mergeCell ref="J31:O34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="P31:P34"/>
-    <mergeCell ref="X31:AB34"/>
-    <mergeCell ref="P68:P71"/>
-    <mergeCell ref="R68:V71"/>
-    <mergeCell ref="J64:O67"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="J60:O63"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="J27:O30"/>
+    <mergeCell ref="X23:AB26"/>
+    <mergeCell ref="X27:AB30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="J23:O26"/>
+    <mergeCell ref="J3:O6"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="C11:H14"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C56:H59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="C63:H63"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="C51:H51"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="C19:H22"/>
     <mergeCell ref="A23:A26"/>
@@ -7196,40 +7194,45 @@
     <mergeCell ref="C79:H79"/>
     <mergeCell ref="A72:A75"/>
     <mergeCell ref="C72:H75"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C56:H59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="C51:H51"/>
-    <mergeCell ref="J3:O6"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="C11:H14"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="J27:O30"/>
-    <mergeCell ref="X23:AB26"/>
-    <mergeCell ref="X27:AB30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J23:O26"/>
+    <mergeCell ref="J31:O34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="X31:AB34"/>
+    <mergeCell ref="P68:P71"/>
+    <mergeCell ref="R68:V71"/>
+    <mergeCell ref="J64:O67"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="J60:O63"/>
+    <mergeCell ref="P80:P83"/>
+    <mergeCell ref="X84:AB87"/>
+    <mergeCell ref="P19:P22"/>
+    <mergeCell ref="R19:V22"/>
+    <mergeCell ref="P84:P87"/>
+    <mergeCell ref="P64:P67"/>
+    <mergeCell ref="X64:AB67"/>
+    <mergeCell ref="R72:V75"/>
+    <mergeCell ref="P76:P79"/>
+    <mergeCell ref="X80:AB83"/>
+    <mergeCell ref="R56:V59"/>
+    <mergeCell ref="P52:P55"/>
+    <mergeCell ref="P60:P63"/>
+    <mergeCell ref="P72:P75"/>
+    <mergeCell ref="P11:P14"/>
+    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="X76:AB79"/>
+    <mergeCell ref="X60:AB63"/>
+    <mergeCell ref="R11:V14"/>
+    <mergeCell ref="X1:AC1"/>
+    <mergeCell ref="P48:P51"/>
+    <mergeCell ref="P3:P6"/>
+    <mergeCell ref="X3:AB6"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P36:P39"/>
+    <mergeCell ref="P40:P43"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="P44:P47"/>
+    <mergeCell ref="P15:P18"/>
+    <mergeCell ref="P7:P10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7367,7 +7370,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="87" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7415,7 +7418,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
+      <c r="A4" s="85"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -7459,7 +7462,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7503,16 +7506,16 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>3.5658276954852297E-2</v>
@@ -7535,7 +7538,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="87" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -7581,7 +7584,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -7625,7 +7628,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="79"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
@@ -7669,16 +7672,16 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
         <v>8.3492792785920695</v>
@@ -7701,7 +7704,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="87" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -7726,18 +7729,18 @@
         <v>3.2053459705297903E-5</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="82"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="79"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
+      <c r="A12" s="85"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -7760,16 +7763,16 @@
         <v>2.0059373392474201E-2</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="79"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -7792,36 +7795,36 @@
         <v>0.213540969734523</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="80"/>
+      <c r="A14" s="99"/>
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="82"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="87" t="s">
         <v>141</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -7846,18 +7849,18 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="82" t="s">
+      <c r="J15" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="79"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -7880,16 +7883,16 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="79"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -7911,36 +7914,36 @@
       <c r="H17" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="80"/>
+      <c r="A18" s="99"/>
       <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="87" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -7986,7 +7989,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="11" t="s">
         <v>7</v>
       </c>
@@ -8030,7 +8033,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -8074,16 +8077,16 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="80"/>
+      <c r="A22" s="99"/>
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>5.2456643231190104E-3</v>
@@ -8106,7 +8109,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="87" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -8152,7 +8155,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="79"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -8196,7 +8199,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="79"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
@@ -8240,16 +8243,16 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="80"/>
+      <c r="A26" s="99"/>
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>7.5239018444935397E-3</v>
@@ -8272,7 +8275,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="92" t="s">
+      <c r="A27" s="87" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -8318,7 +8321,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="79"/>
+      <c r="A28" s="85"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
@@ -8362,7 +8365,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="79"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
@@ -8406,16 +8409,16 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="80"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
       <c r="I30" s="1"/>
       <c r="J30" s="5">
         <v>7.2143853443936604E-6</v>
@@ -8438,7 +8441,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="92" t="s">
+      <c r="A31" s="87" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -8484,7 +8487,7 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="79"/>
+      <c r="A32" s="85"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -8528,7 +8531,7 @@
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="79"/>
+      <c r="A33" s="85"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -8572,16 +8575,16 @@
       <c r="P33" s="1"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="80"/>
+      <c r="A34" s="99"/>
       <c r="B34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>0.34951867520347901</v>
@@ -8604,7 +8607,7 @@
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="92" t="s">
+      <c r="A35" s="87" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8650,7 +8653,7 @@
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="79"/>
+      <c r="A36" s="85"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -8694,7 +8697,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="79"/>
+      <c r="A37" s="85"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -8738,16 +8741,16 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="80"/>
+      <c r="A38" s="99"/>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1">
         <v>2.5021778012642701</v>
@@ -8770,7 +8773,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="92" t="s">
+      <c r="A39" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -8816,7 +8819,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="79"/>
+      <c r="A40" s="85"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -8860,7 +8863,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="79"/>
+      <c r="A41" s="85"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -8904,16 +8907,16 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="80"/>
+      <c r="A42" s="99"/>
       <c r="B42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1">
         <v>4.9184876384352101E-2</v>
@@ -8936,7 +8939,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="92" t="s">
+      <c r="A43" s="87" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -8982,7 +8985,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="79"/>
+      <c r="A44" s="85"/>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -9026,7 +9029,7 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="79"/>
+      <c r="A45" s="85"/>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
@@ -9070,16 +9073,16 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="80"/>
+      <c r="A46" s="99"/>
       <c r="B46" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85"/>
-      <c r="F46" s="85"/>
-      <c r="G46" s="85"/>
-      <c r="H46" s="85"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
         <v>3.6858467316493698E-2</v>
@@ -9102,7 +9105,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="92" t="s">
+      <c r="A47" s="87" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -9148,7 +9151,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="79"/>
+      <c r="A48" s="85"/>
       <c r="B48" s="10" t="s">
         <v>7</v>
       </c>
@@ -9192,7 +9195,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="79"/>
+      <c r="A49" s="85"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -9236,16 +9239,16 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="80"/>
+      <c r="A50" s="99"/>
       <c r="B50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="85"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
         <v>3.4846897009296399E-3</v>
@@ -9268,20 +9271,20 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="87" t="s">
         <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="79"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="79"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
         <v>2.20343269025562E-2</v>
@@ -9304,16 +9307,16 @@
       <c r="P51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="79"/>
+      <c r="A52" s="85"/>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="79"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="79"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
         <v>2.98483856205864E-2</v>
@@ -9336,16 +9339,16 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="79"/>
+      <c r="A53" s="85"/>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="82"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="79"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="79"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="79"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
         <v>1.15818782663304E-3</v>
@@ -9368,16 +9371,16 @@
       <c r="P53" s="1"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="80"/>
+      <c r="A54" s="99"/>
       <c r="B54" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C54" s="82"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="79"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
         <v>2.0797141885883202E-3</v>
@@ -9400,7 +9403,7 @@
       <c r="P54" s="1"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="87" t="s">
         <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -9448,7 +9451,7 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="79"/>
+      <c r="A56" s="85"/>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
@@ -9492,7 +9495,7 @@
       <c r="P56" s="1"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="79"/>
+      <c r="A57" s="85"/>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
@@ -9536,16 +9539,16 @@
       <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
+      <c r="A58" s="99"/>
       <c r="B58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="85"/>
+      <c r="C58" s="103"/>
+      <c r="D58" s="103"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="103"/>
+      <c r="G58" s="103"/>
+      <c r="H58" s="103"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
         <v>1.0524858270047699</v>
@@ -9568,7 +9571,7 @@
       <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="87" t="s">
         <v>64</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -9593,18 +9596,18 @@
         <v>1.61142062466842E-3</v>
       </c>
       <c r="I59" s="1"/>
-      <c r="J59" s="82" t="s">
+      <c r="J59" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K59" s="82"/>
-      <c r="L59" s="82"/>
-      <c r="M59" s="82"/>
-      <c r="N59" s="82"/>
-      <c r="O59" s="82"/>
+      <c r="K59" s="79"/>
+      <c r="L59" s="79"/>
+      <c r="M59" s="79"/>
+      <c r="N59" s="79"/>
+      <c r="O59" s="79"/>
       <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="79"/>
+      <c r="A60" s="85"/>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
@@ -9627,16 +9630,16 @@
         <v>0.83160181683106904</v>
       </c>
       <c r="I60" s="1"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
-      <c r="M60" s="82"/>
-      <c r="N60" s="82"/>
-      <c r="O60" s="82"/>
+      <c r="J60" s="79"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="79"/>
+      <c r="M60" s="79"/>
+      <c r="N60" s="79"/>
+      <c r="O60" s="79"/>
       <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
@@ -9659,49 +9662,49 @@
         <v>0.64170681971566501</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="82"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="82"/>
-      <c r="M61" s="82"/>
-      <c r="N61" s="82"/>
-      <c r="O61" s="82"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="79"/>
+      <c r="L61" s="79"/>
+      <c r="M61" s="79"/>
+      <c r="N61" s="79"/>
+      <c r="O61" s="79"/>
       <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="80"/>
+      <c r="A62" s="99"/>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="85"/>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="85"/>
-      <c r="H62" s="85"/>
+      <c r="C62" s="103"/>
+      <c r="D62" s="103"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="103"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="103"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="82"/>
-      <c r="K62" s="82"/>
-      <c r="L62" s="82"/>
-      <c r="M62" s="82"/>
-      <c r="N62" s="82"/>
-      <c r="O62" s="82"/>
+      <c r="J62" s="79"/>
+      <c r="K62" s="79"/>
+      <c r="L62" s="79"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="79"/>
+      <c r="O62" s="79"/>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="92" t="s">
+      <c r="A63" s="87" t="s">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="82" t="s">
+      <c r="C63" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="82"/>
-      <c r="H63" s="82"/>
+      <c r="D63" s="79"/>
+      <c r="E63" s="79"/>
+      <c r="F63" s="79"/>
+      <c r="G63" s="79"/>
+      <c r="H63" s="79"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
         <v>40.695777417400599</v>
@@ -9724,16 +9727,16 @@
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="82"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
-      <c r="H64" s="82"/>
+      <c r="C64" s="79"/>
+      <c r="D64" s="79"/>
+      <c r="E64" s="79"/>
+      <c r="F64" s="79"/>
+      <c r="G64" s="79"/>
+      <c r="H64" s="79"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
         <v>0.27305635622259</v>
@@ -9756,16 +9759,16 @@
       <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="79"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="82"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="82"/>
-      <c r="H65" s="82"/>
+      <c r="C65" s="79"/>
+      <c r="D65" s="79"/>
+      <c r="E65" s="79"/>
+      <c r="F65" s="79"/>
+      <c r="G65" s="79"/>
+      <c r="H65" s="79"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
         <v>3.4613576315483399</v>
@@ -9788,16 +9791,16 @@
       <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
+      <c r="A66" s="99"/>
       <c r="B66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="82"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
-      <c r="H66" s="82"/>
+      <c r="C66" s="79"/>
+      <c r="D66" s="79"/>
+      <c r="E66" s="79"/>
+      <c r="F66" s="79"/>
+      <c r="G66" s="79"/>
+      <c r="H66" s="79"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
         <v>0.72850411949349603</v>
@@ -9820,20 +9823,20 @@
       <c r="P66" s="1"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="92" t="s">
+      <c r="A67" s="87" t="s">
         <v>41</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="82"/>
-      <c r="G67" s="82"/>
-      <c r="H67" s="82"/>
+      <c r="D67" s="79"/>
+      <c r="E67" s="79"/>
+      <c r="F67" s="79"/>
+      <c r="G67" s="79"/>
+      <c r="H67" s="79"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
         <v>948.25120936445398</v>
@@ -9856,16 +9859,16 @@
       <c r="P67" s="1"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="79"/>
+      <c r="A68" s="85"/>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="82"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="82"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="82"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="79"/>
+      <c r="E68" s="79"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="79"/>
+      <c r="H68" s="79"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
         <v>0.22870622612837599</v>
@@ -9888,16 +9891,16 @@
       <c r="P68" s="1"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="79"/>
+      <c r="A69" s="85"/>
       <c r="B69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
-      <c r="H69" s="82"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="79"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
         <v>37.771893612281502</v>
@@ -9920,16 +9923,16 @@
       <c r="P69" s="1"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="80"/>
+      <c r="A70" s="99"/>
       <c r="B70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="82"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="79"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
         <v>3.9110782596565699</v>
@@ -9952,7 +9955,7 @@
       <c r="P70" s="1"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="92" t="s">
+      <c r="A71" s="87" t="s">
         <v>42</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -9977,18 +9980,18 @@
         <v>2.3819311555743102E-16</v>
       </c>
       <c r="I71" s="1"/>
-      <c r="J71" s="82" t="s">
+      <c r="J71" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K71" s="82"/>
-      <c r="L71" s="82"/>
-      <c r="M71" s="82"/>
-      <c r="N71" s="82"/>
-      <c r="O71" s="82"/>
+      <c r="K71" s="79"/>
+      <c r="L71" s="79"/>
+      <c r="M71" s="79"/>
+      <c r="N71" s="79"/>
+      <c r="O71" s="79"/>
       <c r="P71" s="1"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="79"/>
+      <c r="A72" s="85"/>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
@@ -10011,16 +10014,16 @@
         <v>1.0894169628446399E-3</v>
       </c>
       <c r="I72" s="1"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="82"/>
-      <c r="L72" s="82"/>
-      <c r="M72" s="82"/>
-      <c r="N72" s="82"/>
-      <c r="O72" s="82"/>
+      <c r="J72" s="79"/>
+      <c r="K72" s="79"/>
+      <c r="L72" s="79"/>
+      <c r="M72" s="79"/>
+      <c r="N72" s="79"/>
+      <c r="O72" s="79"/>
       <c r="P72" s="1"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="79"/>
+      <c r="A73" s="85"/>
       <c r="B73" s="1" t="s">
         <v>8</v>
       </c>
@@ -10043,49 +10046,49 @@
         <v>0.84541099798019603</v>
       </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="82"/>
-      <c r="K73" s="82"/>
-      <c r="L73" s="82"/>
-      <c r="M73" s="82"/>
-      <c r="N73" s="82"/>
-      <c r="O73" s="82"/>
+      <c r="J73" s="79"/>
+      <c r="K73" s="79"/>
+      <c r="L73" s="79"/>
+      <c r="M73" s="79"/>
+      <c r="N73" s="79"/>
+      <c r="O73" s="79"/>
       <c r="P73" s="1"/>
     </row>
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
+      <c r="A74" s="99"/>
       <c r="B74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="85"/>
-      <c r="D74" s="85"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="85"/>
-      <c r="G74" s="85"/>
-      <c r="H74" s="85"/>
+      <c r="C74" s="103"/>
+      <c r="D74" s="103"/>
+      <c r="E74" s="103"/>
+      <c r="F74" s="103"/>
+      <c r="G74" s="103"/>
+      <c r="H74" s="103"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="82"/>
-      <c r="K74" s="82"/>
-      <c r="L74" s="82"/>
-      <c r="M74" s="82"/>
-      <c r="N74" s="82"/>
-      <c r="O74" s="82"/>
+      <c r="J74" s="79"/>
+      <c r="K74" s="79"/>
+      <c r="L74" s="79"/>
+      <c r="M74" s="79"/>
+      <c r="N74" s="79"/>
+      <c r="O74" s="79"/>
       <c r="P74" s="1"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="87" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C75" s="82" t="s">
+      <c r="C75" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="82"/>
-      <c r="E75" s="82"/>
-      <c r="F75" s="82"/>
-      <c r="G75" s="82"/>
-      <c r="H75" s="82"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
+      <c r="F75" s="79"/>
+      <c r="G75" s="79"/>
+      <c r="H75" s="79"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1">
         <v>7.7190184322692705E-4</v>
@@ -10108,16 +10111,16 @@
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="79"/>
+      <c r="A76" s="85"/>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="82"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="82"/>
-      <c r="F76" s="82"/>
-      <c r="G76" s="82"/>
-      <c r="H76" s="82"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="79"/>
+      <c r="E76" s="79"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="79"/>
+      <c r="H76" s="79"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1">
         <v>0.26383928794443301</v>
@@ -10140,16 +10143,16 @@
       <c r="P76" s="1"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="79"/>
+      <c r="A77" s="85"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="82"/>
-      <c r="D77" s="82"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="82"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="79"/>
+      <c r="E77" s="79"/>
+      <c r="F77" s="79"/>
+      <c r="G77" s="79"/>
+      <c r="H77" s="79"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1">
         <v>6.5298294112546198E-3</v>
@@ -10172,16 +10175,16 @@
       <c r="P77" s="1"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
+      <c r="A78" s="99"/>
       <c r="B78" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C78" s="82"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="82"/>
-      <c r="F78" s="82"/>
-      <c r="G78" s="82"/>
-      <c r="H78" s="82"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="79"/>
+      <c r="E78" s="79"/>
+      <c r="F78" s="79"/>
+      <c r="G78" s="79"/>
+      <c r="H78" s="79"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1">
         <v>7.3489818378573097E-3</v>
@@ -10204,7 +10207,7 @@
       <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="92" t="s">
+      <c r="A79" s="87" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -10229,18 +10232,18 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I79" s="1"/>
-      <c r="J79" s="82" t="s">
+      <c r="J79" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K79" s="82"/>
-      <c r="L79" s="82"/>
-      <c r="M79" s="82"/>
-      <c r="N79" s="82"/>
-      <c r="O79" s="82"/>
+      <c r="K79" s="79"/>
+      <c r="L79" s="79"/>
+      <c r="M79" s="79"/>
+      <c r="N79" s="79"/>
+      <c r="O79" s="79"/>
       <c r="P79" s="1"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="79"/>
+      <c r="A80" s="85"/>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
@@ -10263,16 +10266,16 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="82"/>
-      <c r="K80" s="82"/>
-      <c r="L80" s="82"/>
-      <c r="M80" s="82"/>
-      <c r="N80" s="82"/>
-      <c r="O80" s="82"/>
+      <c r="J80" s="79"/>
+      <c r="K80" s="79"/>
+      <c r="L80" s="79"/>
+      <c r="M80" s="79"/>
+      <c r="N80" s="79"/>
+      <c r="O80" s="79"/>
       <c r="P80" s="1"/>
     </row>
     <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="79"/>
+      <c r="A81" s="85"/>
       <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
@@ -10295,49 +10298,49 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="82"/>
-      <c r="K81" s="82"/>
-      <c r="L81" s="82"/>
-      <c r="M81" s="82"/>
-      <c r="N81" s="82"/>
-      <c r="O81" s="82"/>
+      <c r="J81" s="79"/>
+      <c r="K81" s="79"/>
+      <c r="L81" s="79"/>
+      <c r="M81" s="79"/>
+      <c r="N81" s="79"/>
+      <c r="O81" s="79"/>
       <c r="P81" s="1"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="80"/>
+      <c r="A82" s="99"/>
       <c r="B82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
-      <c r="E82" s="85"/>
-      <c r="F82" s="85"/>
-      <c r="G82" s="85"/>
-      <c r="H82" s="85"/>
+      <c r="C82" s="103"/>
+      <c r="D82" s="103"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="103"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="82"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
+      <c r="J82" s="79"/>
+      <c r="K82" s="79"/>
+      <c r="L82" s="79"/>
+      <c r="M82" s="79"/>
+      <c r="N82" s="79"/>
+      <c r="O82" s="79"/>
       <c r="P82" s="1"/>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="92" t="s">
+      <c r="A83" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="82" t="s">
+      <c r="C83" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D83" s="82"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
-      <c r="H83" s="82"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="79"/>
+      <c r="F83" s="79"/>
+      <c r="G83" s="79"/>
+      <c r="H83" s="79"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1">
         <v>4.0252880405239402E-2</v>
@@ -10360,16 +10363,16 @@
       <c r="P83" s="1"/>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="79"/>
+      <c r="A84" s="85"/>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="82"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
+      <c r="F84" s="79"/>
+      <c r="G84" s="79"/>
+      <c r="H84" s="79"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1">
         <v>0.42132164214255802</v>
@@ -10392,16 +10395,16 @@
       <c r="P84" s="1"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="79"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="82"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="79"/>
+      <c r="F85" s="79"/>
+      <c r="G85" s="79"/>
+      <c r="H85" s="79"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1">
         <v>7.8254362282741005E-2</v>
@@ -10424,16 +10427,16 @@
       <c r="P85" s="1"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="80"/>
+      <c r="A86" s="99"/>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="82"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="79"/>
+      <c r="E86" s="79"/>
+      <c r="F86" s="79"/>
+      <c r="G86" s="79"/>
+      <c r="H86" s="79"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1">
         <v>2.6614614752845599E-3</v>
@@ -10456,7 +10459,7 @@
       <c r="P86" s="1"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="87" t="s">
         <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -10481,18 +10484,18 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I87" s="1"/>
-      <c r="J87" s="82" t="s">
+      <c r="J87" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="82"/>
-      <c r="O87" s="82"/>
+      <c r="K87" s="79"/>
+      <c r="L87" s="79"/>
+      <c r="M87" s="79"/>
+      <c r="N87" s="79"/>
+      <c r="O87" s="79"/>
       <c r="P87" s="1"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="79"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
@@ -10515,16 +10518,16 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I88" s="1"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
-      <c r="N88" s="82"/>
-      <c r="O88" s="82"/>
+      <c r="J88" s="79"/>
+      <c r="K88" s="79"/>
+      <c r="L88" s="79"/>
+      <c r="M88" s="79"/>
+      <c r="N88" s="79"/>
+      <c r="O88" s="79"/>
       <c r="P88" s="1"/>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="79"/>
+      <c r="A89" s="85"/>
       <c r="B89" s="1" t="s">
         <v>8</v>
       </c>
@@ -10547,36 +10550,36 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I89" s="1"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
-      <c r="N89" s="82"/>
-      <c r="O89" s="82"/>
+      <c r="J89" s="79"/>
+      <c r="K89" s="79"/>
+      <c r="L89" s="79"/>
+      <c r="M89" s="79"/>
+      <c r="N89" s="79"/>
+      <c r="O89" s="79"/>
       <c r="P89" s="1"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="80"/>
+      <c r="A90" s="99"/>
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="85"/>
-      <c r="D90" s="85"/>
-      <c r="E90" s="85"/>
-      <c r="F90" s="85"/>
-      <c r="G90" s="85"/>
-      <c r="H90" s="85"/>
+      <c r="C90" s="103"/>
+      <c r="D90" s="103"/>
+      <c r="E90" s="103"/>
+      <c r="F90" s="103"/>
+      <c r="G90" s="103"/>
+      <c r="H90" s="103"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
-      <c r="N90" s="82"/>
-      <c r="O90" s="82"/>
+      <c r="J90" s="79"/>
+      <c r="K90" s="79"/>
+      <c r="L90" s="79"/>
+      <c r="M90" s="79"/>
+      <c r="N90" s="79"/>
+      <c r="O90" s="79"/>
       <c r="P90" s="1"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="92" t="s">
+      <c r="A91" s="87" t="s">
         <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -10601,18 +10604,18 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I91" s="1"/>
-      <c r="J91" s="82" t="s">
+      <c r="J91" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
-      <c r="N91" s="82"/>
-      <c r="O91" s="82"/>
+      <c r="K91" s="79"/>
+      <c r="L91" s="79"/>
+      <c r="M91" s="79"/>
+      <c r="N91" s="79"/>
+      <c r="O91" s="79"/>
       <c r="P91" s="1"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
+      <c r="A92" s="85"/>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
@@ -10635,16 +10638,16 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="82"/>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
-      <c r="N92" s="82"/>
-      <c r="O92" s="82"/>
+      <c r="J92" s="79"/>
+      <c r="K92" s="79"/>
+      <c r="L92" s="79"/>
+      <c r="M92" s="79"/>
+      <c r="N92" s="79"/>
+      <c r="O92" s="79"/>
       <c r="P92" s="1"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="79"/>
+      <c r="A93" s="85"/>
       <c r="B93" s="1" t="s">
         <v>8</v>
       </c>
@@ -10667,36 +10670,36 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I93" s="1"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
-      <c r="N93" s="82"/>
-      <c r="O93" s="82"/>
+      <c r="J93" s="79"/>
+      <c r="K93" s="79"/>
+      <c r="L93" s="79"/>
+      <c r="M93" s="79"/>
+      <c r="N93" s="79"/>
+      <c r="O93" s="79"/>
       <c r="P93" s="1"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
+      <c r="A94" s="99"/>
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
-      <c r="E94" s="85"/>
-      <c r="F94" s="85"/>
-      <c r="G94" s="85"/>
-      <c r="H94" s="85"/>
+      <c r="C94" s="103"/>
+      <c r="D94" s="103"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="103"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="82"/>
-      <c r="K94" s="82"/>
-      <c r="L94" s="82"/>
-      <c r="M94" s="82"/>
-      <c r="N94" s="82"/>
-      <c r="O94" s="82"/>
+      <c r="J94" s="79"/>
+      <c r="K94" s="79"/>
+      <c r="L94" s="79"/>
+      <c r="M94" s="79"/>
+      <c r="N94" s="79"/>
+      <c r="O94" s="79"/>
       <c r="P94" s="1"/>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="92" t="s">
+      <c r="A95" s="87" t="s">
         <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -10721,18 +10724,18 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I95" s="1"/>
-      <c r="J95" s="82" t="s">
+      <c r="J95" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K95" s="82"/>
-      <c r="L95" s="82"/>
-      <c r="M95" s="82"/>
-      <c r="N95" s="82"/>
-      <c r="O95" s="82"/>
+      <c r="K95" s="79"/>
+      <c r="L95" s="79"/>
+      <c r="M95" s="79"/>
+      <c r="N95" s="79"/>
+      <c r="O95" s="79"/>
       <c r="P95" s="1"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="79"/>
+      <c r="A96" s="85"/>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
@@ -10755,16 +10758,16 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I96" s="1"/>
-      <c r="J96" s="82"/>
-      <c r="K96" s="82"/>
-      <c r="L96" s="82"/>
-      <c r="M96" s="82"/>
-      <c r="N96" s="82"/>
-      <c r="O96" s="82"/>
+      <c r="J96" s="79"/>
+      <c r="K96" s="79"/>
+      <c r="L96" s="79"/>
+      <c r="M96" s="79"/>
+      <c r="N96" s="79"/>
+      <c r="O96" s="79"/>
       <c r="P96" s="1"/>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="79"/>
+      <c r="A97" s="85"/>
       <c r="B97" s="1" t="s">
         <v>8</v>
       </c>
@@ -10787,36 +10790,36 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="82"/>
-      <c r="K97" s="82"/>
-      <c r="L97" s="82"/>
-      <c r="M97" s="82"/>
-      <c r="N97" s="82"/>
-      <c r="O97" s="82"/>
+      <c r="J97" s="79"/>
+      <c r="K97" s="79"/>
+      <c r="L97" s="79"/>
+      <c r="M97" s="79"/>
+      <c r="N97" s="79"/>
+      <c r="O97" s="79"/>
       <c r="P97" s="1"/>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="80"/>
+      <c r="A98" s="99"/>
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="85"/>
-      <c r="D98" s="85"/>
-      <c r="E98" s="85"/>
-      <c r="F98" s="85"/>
-      <c r="G98" s="85"/>
-      <c r="H98" s="85"/>
+      <c r="C98" s="103"/>
+      <c r="D98" s="103"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="103"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="82"/>
-      <c r="K98" s="82"/>
-      <c r="L98" s="82"/>
-      <c r="M98" s="82"/>
-      <c r="N98" s="82"/>
-      <c r="O98" s="82"/>
+      <c r="J98" s="79"/>
+      <c r="K98" s="79"/>
+      <c r="L98" s="79"/>
+      <c r="M98" s="79"/>
+      <c r="N98" s="79"/>
+      <c r="O98" s="79"/>
       <c r="P98" s="1"/>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="92" t="s">
+      <c r="A99" s="87" t="s">
         <v>30</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -10841,18 +10844,18 @@
         <v>3.8248319558473298E-23</v>
       </c>
       <c r="I99" s="1"/>
-      <c r="J99" s="82" t="s">
+      <c r="J99" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K99" s="82"/>
-      <c r="L99" s="82"/>
-      <c r="M99" s="82"/>
-      <c r="N99" s="82"/>
-      <c r="O99" s="82"/>
+      <c r="K99" s="79"/>
+      <c r="L99" s="79"/>
+      <c r="M99" s="79"/>
+      <c r="N99" s="79"/>
+      <c r="O99" s="79"/>
       <c r="P99" s="1"/>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="79"/>
+      <c r="A100" s="85"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
@@ -10875,16 +10878,16 @@
         <v>0.27985440517664001</v>
       </c>
       <c r="I100" s="1"/>
-      <c r="J100" s="82"/>
-      <c r="K100" s="82"/>
-      <c r="L100" s="82"/>
-      <c r="M100" s="82"/>
-      <c r="N100" s="82"/>
-      <c r="O100" s="82"/>
+      <c r="J100" s="79"/>
+      <c r="K100" s="79"/>
+      <c r="L100" s="79"/>
+      <c r="M100" s="79"/>
+      <c r="N100" s="79"/>
+      <c r="O100" s="79"/>
       <c r="P100" s="1"/>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="79"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="1" t="s">
         <v>8</v>
       </c>
@@ -10907,49 +10910,49 @@
         <v>0.72495214931683005</v>
       </c>
       <c r="I101" s="1"/>
-      <c r="J101" s="82"/>
-      <c r="K101" s="82"/>
-      <c r="L101" s="82"/>
-      <c r="M101" s="82"/>
-      <c r="N101" s="82"/>
-      <c r="O101" s="82"/>
+      <c r="J101" s="79"/>
+      <c r="K101" s="79"/>
+      <c r="L101" s="79"/>
+      <c r="M101" s="79"/>
+      <c r="N101" s="79"/>
+      <c r="O101" s="79"/>
       <c r="P101" s="1"/>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
+      <c r="A102" s="99"/>
       <c r="B102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="85"/>
-      <c r="H102" s="85"/>
+      <c r="C102" s="103"/>
+      <c r="D102" s="103"/>
+      <c r="E102" s="103"/>
+      <c r="F102" s="103"/>
+      <c r="G102" s="103"/>
+      <c r="H102" s="103"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="82"/>
-      <c r="K102" s="82"/>
-      <c r="L102" s="82"/>
-      <c r="M102" s="82"/>
-      <c r="N102" s="82"/>
-      <c r="O102" s="82"/>
+      <c r="J102" s="79"/>
+      <c r="K102" s="79"/>
+      <c r="L102" s="79"/>
+      <c r="M102" s="79"/>
+      <c r="N102" s="79"/>
+      <c r="O102" s="79"/>
       <c r="P102" s="1"/>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="92" t="s">
+      <c r="A103" s="87" t="s">
         <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="82" t="s">
+      <c r="C103" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D103" s="82"/>
-      <c r="E103" s="82"/>
-      <c r="F103" s="82"/>
-      <c r="G103" s="82"/>
-      <c r="H103" s="82"/>
+      <c r="D103" s="79"/>
+      <c r="E103" s="79"/>
+      <c r="F103" s="79"/>
+      <c r="G103" s="79"/>
+      <c r="H103" s="79"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1">
         <v>4.9920514192076698E-4</v>
@@ -10972,16 +10975,16 @@
       <c r="P103" s="1"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="79"/>
+      <c r="A104" s="85"/>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="82"/>
-      <c r="D104" s="82"/>
-      <c r="E104" s="82"/>
-      <c r="F104" s="82"/>
-      <c r="G104" s="82"/>
-      <c r="H104" s="82"/>
+      <c r="C104" s="79"/>
+      <c r="D104" s="79"/>
+      <c r="E104" s="79"/>
+      <c r="F104" s="79"/>
+      <c r="G104" s="79"/>
+      <c r="H104" s="79"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1">
         <v>4.3245963051368403E-3</v>
@@ -11004,16 +11007,16 @@
       <c r="P104" s="1"/>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="79"/>
+      <c r="A105" s="85"/>
       <c r="B105" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="82"/>
-      <c r="D105" s="82"/>
-      <c r="E105" s="82"/>
-      <c r="F105" s="82"/>
-      <c r="G105" s="82"/>
-      <c r="H105" s="82"/>
+      <c r="C105" s="79"/>
+      <c r="D105" s="79"/>
+      <c r="E105" s="79"/>
+      <c r="F105" s="79"/>
+      <c r="G105" s="79"/>
+      <c r="H105" s="79"/>
       <c r="I105" s="1"/>
       <c r="J105" s="5">
         <v>4.4673218852987901E-5</v>
@@ -11036,16 +11039,16 @@
       <c r="P105" s="1"/>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="80"/>
+      <c r="A106" s="99"/>
       <c r="B106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C106" s="82"/>
-      <c r="D106" s="82"/>
-      <c r="E106" s="82"/>
-      <c r="F106" s="82"/>
-      <c r="G106" s="82"/>
-      <c r="H106" s="82"/>
+      <c r="C106" s="79"/>
+      <c r="D106" s="79"/>
+      <c r="E106" s="79"/>
+      <c r="F106" s="79"/>
+      <c r="G106" s="79"/>
+      <c r="H106" s="79"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1">
         <v>2.5092673060789E-4</v>
@@ -11068,20 +11071,20 @@
       <c r="P106" s="1"/>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="92" t="s">
+      <c r="A107" s="87" t="s">
         <v>29</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="82" t="s">
+      <c r="C107" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D107" s="82"/>
-      <c r="E107" s="82"/>
-      <c r="F107" s="82"/>
-      <c r="G107" s="82"/>
-      <c r="H107" s="82"/>
+      <c r="D107" s="79"/>
+      <c r="E107" s="79"/>
+      <c r="F107" s="79"/>
+      <c r="G107" s="79"/>
+      <c r="H107" s="79"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1">
         <v>1.4241127553301099E-4</v>
@@ -11104,16 +11107,16 @@
       <c r="P107" s="1"/>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="79"/>
+      <c r="A108" s="85"/>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="82"/>
-      <c r="D108" s="82"/>
-      <c r="E108" s="82"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="82"/>
-      <c r="H108" s="82"/>
+      <c r="C108" s="79"/>
+      <c r="D108" s="79"/>
+      <c r="E108" s="79"/>
+      <c r="F108" s="79"/>
+      <c r="G108" s="79"/>
+      <c r="H108" s="79"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
         <v>4.6725153189010001E-2</v>
@@ -11136,16 +11139,16 @@
       <c r="P108" s="1"/>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="79"/>
+      <c r="A109" s="85"/>
       <c r="B109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="82"/>
-      <c r="D109" s="82"/>
-      <c r="E109" s="82"/>
-      <c r="F109" s="82"/>
-      <c r="G109" s="82"/>
-      <c r="H109" s="82"/>
+      <c r="C109" s="79"/>
+      <c r="D109" s="79"/>
+      <c r="E109" s="79"/>
+      <c r="F109" s="79"/>
+      <c r="G109" s="79"/>
+      <c r="H109" s="79"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1">
         <v>2.8302586845141399E-2</v>
@@ -11168,16 +11171,16 @@
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="80"/>
+      <c r="A110" s="99"/>
       <c r="B110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C110" s="82"/>
-      <c r="D110" s="82"/>
-      <c r="E110" s="82"/>
-      <c r="F110" s="82"/>
-      <c r="G110" s="82"/>
-      <c r="H110" s="82"/>
+      <c r="C110" s="79"/>
+      <c r="D110" s="79"/>
+      <c r="E110" s="79"/>
+      <c r="F110" s="79"/>
+      <c r="G110" s="79"/>
+      <c r="H110" s="79"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1">
         <v>6.3796317056246301E-3</v>
@@ -11200,7 +11203,7 @@
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="92" t="s">
+      <c r="A111" s="87" t="s">
         <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -11225,18 +11228,18 @@
         <v>2.5160186313214301E-3</v>
       </c>
       <c r="I111" s="1"/>
-      <c r="J111" s="82" t="s">
+      <c r="J111" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K111" s="82"/>
-      <c r="L111" s="82"/>
-      <c r="M111" s="82"/>
-      <c r="N111" s="82"/>
-      <c r="O111" s="82"/>
+      <c r="K111" s="79"/>
+      <c r="L111" s="79"/>
+      <c r="M111" s="79"/>
+      <c r="N111" s="79"/>
+      <c r="O111" s="79"/>
       <c r="P111" s="1"/>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="79"/>
+      <c r="A112" s="85"/>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
@@ -11259,16 +11262,16 @@
         <v>0.13226601261193599</v>
       </c>
       <c r="I112" s="1"/>
-      <c r="J112" s="82"/>
-      <c r="K112" s="82"/>
-      <c r="L112" s="82"/>
-      <c r="M112" s="82"/>
-      <c r="N112" s="82"/>
-      <c r="O112" s="82"/>
+      <c r="J112" s="79"/>
+      <c r="K112" s="79"/>
+      <c r="L112" s="79"/>
+      <c r="M112" s="79"/>
+      <c r="N112" s="79"/>
+      <c r="O112" s="79"/>
       <c r="P112" s="1"/>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" s="79"/>
+      <c r="A113" s="85"/>
       <c r="B113" s="1" t="s">
         <v>8</v>
       </c>
@@ -11291,36 +11294,36 @@
         <v>1.67603779088435E-5</v>
       </c>
       <c r="I113" s="1"/>
-      <c r="J113" s="82"/>
-      <c r="K113" s="82"/>
-      <c r="L113" s="82"/>
-      <c r="M113" s="82"/>
-      <c r="N113" s="82"/>
-      <c r="O113" s="82"/>
+      <c r="J113" s="79"/>
+      <c r="K113" s="79"/>
+      <c r="L113" s="79"/>
+      <c r="M113" s="79"/>
+      <c r="N113" s="79"/>
+      <c r="O113" s="79"/>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" s="80"/>
+      <c r="A114" s="99"/>
       <c r="B114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="85"/>
-      <c r="D114" s="85"/>
-      <c r="E114" s="85"/>
-      <c r="F114" s="85"/>
-      <c r="G114" s="85"/>
-      <c r="H114" s="85"/>
+      <c r="C114" s="103"/>
+      <c r="D114" s="103"/>
+      <c r="E114" s="103"/>
+      <c r="F114" s="103"/>
+      <c r="G114" s="103"/>
+      <c r="H114" s="103"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="82"/>
-      <c r="K114" s="82"/>
-      <c r="L114" s="82"/>
-      <c r="M114" s="82"/>
-      <c r="N114" s="82"/>
-      <c r="O114" s="82"/>
+      <c r="J114" s="79"/>
+      <c r="K114" s="79"/>
+      <c r="L114" s="79"/>
+      <c r="M114" s="79"/>
+      <c r="N114" s="79"/>
+      <c r="O114" s="79"/>
       <c r="P114" s="1"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" s="92" t="s">
+      <c r="A115" s="87" t="s">
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -11345,18 +11348,18 @@
         <v>3.1891308959839999E-11</v>
       </c>
       <c r="I115" s="1"/>
-      <c r="J115" s="82" t="s">
+      <c r="J115" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K115" s="82"/>
-      <c r="L115" s="82"/>
-      <c r="M115" s="82"/>
-      <c r="N115" s="82"/>
-      <c r="O115" s="82"/>
+      <c r="K115" s="79"/>
+      <c r="L115" s="79"/>
+      <c r="M115" s="79"/>
+      <c r="N115" s="79"/>
+      <c r="O115" s="79"/>
       <c r="P115" s="1"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A116" s="79"/>
+      <c r="A116" s="85"/>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
@@ -11379,16 +11382,16 @@
         <v>1.9668218703936501E-2</v>
       </c>
       <c r="I116" s="1"/>
-      <c r="J116" s="82"/>
-      <c r="K116" s="82"/>
-      <c r="L116" s="82"/>
-      <c r="M116" s="82"/>
-      <c r="N116" s="82"/>
-      <c r="O116" s="82"/>
+      <c r="J116" s="79"/>
+      <c r="K116" s="79"/>
+      <c r="L116" s="79"/>
+      <c r="M116" s="79"/>
+      <c r="N116" s="79"/>
+      <c r="O116" s="79"/>
       <c r="P116" s="1"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="79"/>
+      <c r="A117" s="85"/>
       <c r="B117" s="1" t="s">
         <v>8</v>
       </c>
@@ -11411,36 +11414,36 @@
         <v>6.4583181614334004E-2</v>
       </c>
       <c r="I117" s="1"/>
-      <c r="J117" s="82"/>
-      <c r="K117" s="82"/>
-      <c r="L117" s="82"/>
-      <c r="M117" s="82"/>
-      <c r="N117" s="82"/>
-      <c r="O117" s="82"/>
+      <c r="J117" s="79"/>
+      <c r="K117" s="79"/>
+      <c r="L117" s="79"/>
+      <c r="M117" s="79"/>
+      <c r="N117" s="79"/>
+      <c r="O117" s="79"/>
       <c r="P117" s="1"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A118" s="80"/>
+      <c r="A118" s="99"/>
       <c r="B118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="85"/>
-      <c r="D118" s="85"/>
-      <c r="E118" s="85"/>
-      <c r="F118" s="85"/>
-      <c r="G118" s="85"/>
-      <c r="H118" s="85"/>
+      <c r="C118" s="103"/>
+      <c r="D118" s="103"/>
+      <c r="E118" s="103"/>
+      <c r="F118" s="103"/>
+      <c r="G118" s="103"/>
+      <c r="H118" s="103"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="82"/>
-      <c r="K118" s="82"/>
-      <c r="L118" s="82"/>
-      <c r="M118" s="82"/>
-      <c r="N118" s="82"/>
-      <c r="O118" s="82"/>
+      <c r="J118" s="79"/>
+      <c r="K118" s="79"/>
+      <c r="L118" s="79"/>
+      <c r="M118" s="79"/>
+      <c r="N118" s="79"/>
+      <c r="O118" s="79"/>
       <c r="P118" s="1"/>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A119" s="92" t="s">
+      <c r="A119" s="87" t="s">
         <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -11465,18 +11468,18 @@
         <v>7.05414701429731E-35</v>
       </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="82" t="s">
+      <c r="J119" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K119" s="82"/>
-      <c r="L119" s="82"/>
-      <c r="M119" s="82"/>
-      <c r="N119" s="82"/>
-      <c r="O119" s="82"/>
+      <c r="K119" s="79"/>
+      <c r="L119" s="79"/>
+      <c r="M119" s="79"/>
+      <c r="N119" s="79"/>
+      <c r="O119" s="79"/>
       <c r="P119" s="1"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" s="79"/>
+      <c r="A120" s="85"/>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
@@ -11499,16 +11502,16 @@
         <v>3.9509565365961799E-2</v>
       </c>
       <c r="I120" s="1"/>
-      <c r="J120" s="82"/>
-      <c r="K120" s="82"/>
-      <c r="L120" s="82"/>
-      <c r="M120" s="82"/>
-      <c r="N120" s="82"/>
-      <c r="O120" s="82"/>
+      <c r="J120" s="79"/>
+      <c r="K120" s="79"/>
+      <c r="L120" s="79"/>
+      <c r="M120" s="79"/>
+      <c r="N120" s="79"/>
+      <c r="O120" s="79"/>
       <c r="P120" s="1"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" s="79"/>
+      <c r="A121" s="85"/>
       <c r="B121" s="1" t="s">
         <v>8</v>
       </c>
@@ -11531,36 +11534,36 @@
         <v>1.2703272318058401E-2</v>
       </c>
       <c r="I121" s="1"/>
-      <c r="J121" s="82"/>
-      <c r="K121" s="82"/>
-      <c r="L121" s="82"/>
-      <c r="M121" s="82"/>
-      <c r="N121" s="82"/>
-      <c r="O121" s="82"/>
+      <c r="J121" s="79"/>
+      <c r="K121" s="79"/>
+      <c r="L121" s="79"/>
+      <c r="M121" s="79"/>
+      <c r="N121" s="79"/>
+      <c r="O121" s="79"/>
       <c r="P121" s="1"/>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" s="80"/>
+      <c r="A122" s="99"/>
       <c r="B122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="85"/>
-      <c r="D122" s="85"/>
-      <c r="E122" s="85"/>
-      <c r="F122" s="85"/>
-      <c r="G122" s="85"/>
-      <c r="H122" s="85"/>
+      <c r="C122" s="103"/>
+      <c r="D122" s="103"/>
+      <c r="E122" s="103"/>
+      <c r="F122" s="103"/>
+      <c r="G122" s="103"/>
+      <c r="H122" s="103"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="82"/>
-      <c r="K122" s="82"/>
-      <c r="L122" s="82"/>
-      <c r="M122" s="82"/>
-      <c r="N122" s="82"/>
-      <c r="O122" s="82"/>
+      <c r="J122" s="79"/>
+      <c r="K122" s="79"/>
+      <c r="L122" s="79"/>
+      <c r="M122" s="79"/>
+      <c r="N122" s="79"/>
+      <c r="O122" s="79"/>
       <c r="P122" s="1"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" s="92" t="s">
+      <c r="A123" s="87" t="s">
         <v>151</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -11585,18 +11588,18 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I123" s="1"/>
-      <c r="J123" s="82" t="s">
+      <c r="J123" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K123" s="82"/>
-      <c r="L123" s="82"/>
-      <c r="M123" s="82"/>
-      <c r="N123" s="82"/>
-      <c r="O123" s="82"/>
+      <c r="K123" s="79"/>
+      <c r="L123" s="79"/>
+      <c r="M123" s="79"/>
+      <c r="N123" s="79"/>
+      <c r="O123" s="79"/>
       <c r="P123" s="1"/>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" s="79"/>
+      <c r="A124" s="85"/>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
@@ -11619,16 +11622,16 @@
         <v>0.2597892</v>
       </c>
       <c r="I124" s="1"/>
-      <c r="J124" s="82"/>
-      <c r="K124" s="82"/>
-      <c r="L124" s="82"/>
-      <c r="M124" s="82"/>
-      <c r="N124" s="82"/>
-      <c r="O124" s="82"/>
+      <c r="J124" s="79"/>
+      <c r="K124" s="79"/>
+      <c r="L124" s="79"/>
+      <c r="M124" s="79"/>
+      <c r="N124" s="79"/>
+      <c r="O124" s="79"/>
       <c r="P124" s="1"/>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="79"/>
+      <c r="A125" s="85"/>
       <c r="B125" s="1" t="s">
         <v>8</v>
       </c>
@@ -11651,36 +11654,36 @@
         <v>0.7055884</v>
       </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="82"/>
-      <c r="K125" s="82"/>
-      <c r="L125" s="82"/>
-      <c r="M125" s="82"/>
-      <c r="N125" s="82"/>
-      <c r="O125" s="82"/>
+      <c r="J125" s="79"/>
+      <c r="K125" s="79"/>
+      <c r="L125" s="79"/>
+      <c r="M125" s="79"/>
+      <c r="N125" s="79"/>
+      <c r="O125" s="79"/>
       <c r="P125" s="1"/>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="80"/>
+      <c r="A126" s="99"/>
       <c r="B126" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="85"/>
-      <c r="D126" s="85"/>
-      <c r="E126" s="85"/>
-      <c r="F126" s="85"/>
-      <c r="G126" s="85"/>
-      <c r="H126" s="85"/>
+      <c r="C126" s="103"/>
+      <c r="D126" s="103"/>
+      <c r="E126" s="103"/>
+      <c r="F126" s="103"/>
+      <c r="G126" s="103"/>
+      <c r="H126" s="103"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="82"/>
-      <c r="K126" s="82"/>
-      <c r="L126" s="82"/>
-      <c r="M126" s="82"/>
-      <c r="N126" s="82"/>
-      <c r="O126" s="82"/>
+      <c r="J126" s="79"/>
+      <c r="K126" s="79"/>
+      <c r="L126" s="79"/>
+      <c r="M126" s="79"/>
+      <c r="N126" s="79"/>
+      <c r="O126" s="79"/>
       <c r="P126" s="1"/>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" s="92" t="s">
+      <c r="A127" s="87" t="s">
         <v>34</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -11705,18 +11708,18 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I127" s="1"/>
-      <c r="J127" s="82" t="s">
+      <c r="J127" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K127" s="82"/>
-      <c r="L127" s="82"/>
-      <c r="M127" s="82"/>
-      <c r="N127" s="82"/>
-      <c r="O127" s="82"/>
+      <c r="K127" s="79"/>
+      <c r="L127" s="79"/>
+      <c r="M127" s="79"/>
+      <c r="N127" s="79"/>
+      <c r="O127" s="79"/>
       <c r="P127" s="1"/>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" s="79"/>
+      <c r="A128" s="85"/>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
@@ -11739,16 +11742,16 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I128" s="1"/>
-      <c r="J128" s="82"/>
-      <c r="K128" s="82"/>
-      <c r="L128" s="82"/>
-      <c r="M128" s="82"/>
-      <c r="N128" s="82"/>
-      <c r="O128" s="82"/>
+      <c r="J128" s="79"/>
+      <c r="K128" s="79"/>
+      <c r="L128" s="79"/>
+      <c r="M128" s="79"/>
+      <c r="N128" s="79"/>
+      <c r="O128" s="79"/>
       <c r="P128" s="1"/>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" s="79"/>
+      <c r="A129" s="85"/>
       <c r="B129" s="1" t="s">
         <v>8</v>
       </c>
@@ -11771,36 +11774,36 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I129" s="1"/>
-      <c r="J129" s="82"/>
-      <c r="K129" s="82"/>
-      <c r="L129" s="82"/>
-      <c r="M129" s="82"/>
-      <c r="N129" s="82"/>
-      <c r="O129" s="82"/>
+      <c r="J129" s="79"/>
+      <c r="K129" s="79"/>
+      <c r="L129" s="79"/>
+      <c r="M129" s="79"/>
+      <c r="N129" s="79"/>
+      <c r="O129" s="79"/>
       <c r="P129" s="1"/>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" s="80"/>
+      <c r="A130" s="99"/>
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C130" s="85"/>
-      <c r="D130" s="85"/>
-      <c r="E130" s="85"/>
-      <c r="F130" s="85"/>
-      <c r="G130" s="85"/>
-      <c r="H130" s="85"/>
+      <c r="C130" s="103"/>
+      <c r="D130" s="103"/>
+      <c r="E130" s="103"/>
+      <c r="F130" s="103"/>
+      <c r="G130" s="103"/>
+      <c r="H130" s="103"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="82"/>
-      <c r="K130" s="82"/>
-      <c r="L130" s="82"/>
-      <c r="M130" s="82"/>
-      <c r="N130" s="82"/>
-      <c r="O130" s="82"/>
+      <c r="J130" s="79"/>
+      <c r="K130" s="79"/>
+      <c r="L130" s="79"/>
+      <c r="M130" s="79"/>
+      <c r="N130" s="79"/>
+      <c r="O130" s="79"/>
       <c r="P130" s="1"/>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" s="92" t="s">
+      <c r="A131" s="87" t="s">
         <v>35</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -11825,18 +11828,18 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I131" s="1"/>
-      <c r="J131" s="82" t="s">
+      <c r="J131" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K131" s="82"/>
-      <c r="L131" s="82"/>
-      <c r="M131" s="82"/>
-      <c r="N131" s="82"/>
-      <c r="O131" s="82"/>
+      <c r="K131" s="79"/>
+      <c r="L131" s="79"/>
+      <c r="M131" s="79"/>
+      <c r="N131" s="79"/>
+      <c r="O131" s="79"/>
       <c r="P131" s="1"/>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" s="79"/>
+      <c r="A132" s="85"/>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
@@ -11859,16 +11862,16 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I132" s="1"/>
-      <c r="J132" s="82"/>
-      <c r="K132" s="82"/>
-      <c r="L132" s="82"/>
-      <c r="M132" s="82"/>
-      <c r="N132" s="82"/>
-      <c r="O132" s="82"/>
+      <c r="J132" s="79"/>
+      <c r="K132" s="79"/>
+      <c r="L132" s="79"/>
+      <c r="M132" s="79"/>
+      <c r="N132" s="79"/>
+      <c r="O132" s="79"/>
       <c r="P132" s="1"/>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" s="79"/>
+      <c r="A133" s="85"/>
       <c r="B133" s="1" t="s">
         <v>8</v>
       </c>
@@ -11891,36 +11894,36 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I133" s="1"/>
-      <c r="J133" s="82"/>
-      <c r="K133" s="82"/>
-      <c r="L133" s="82"/>
-      <c r="M133" s="82"/>
-      <c r="N133" s="82"/>
-      <c r="O133" s="82"/>
+      <c r="J133" s="79"/>
+      <c r="K133" s="79"/>
+      <c r="L133" s="79"/>
+      <c r="M133" s="79"/>
+      <c r="N133" s="79"/>
+      <c r="O133" s="79"/>
       <c r="P133" s="1"/>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" s="80"/>
+      <c r="A134" s="99"/>
       <c r="B134" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="85"/>
-      <c r="D134" s="85"/>
-      <c r="E134" s="85"/>
-      <c r="F134" s="85"/>
-      <c r="G134" s="85"/>
-      <c r="H134" s="85"/>
+      <c r="C134" s="103"/>
+      <c r="D134" s="103"/>
+      <c r="E134" s="103"/>
+      <c r="F134" s="103"/>
+      <c r="G134" s="103"/>
+      <c r="H134" s="103"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="82"/>
-      <c r="K134" s="82"/>
-      <c r="L134" s="82"/>
-      <c r="M134" s="82"/>
-      <c r="N134" s="82"/>
-      <c r="O134" s="82"/>
+      <c r="J134" s="79"/>
+      <c r="K134" s="79"/>
+      <c r="L134" s="79"/>
+      <c r="M134" s="79"/>
+      <c r="N134" s="79"/>
+      <c r="O134" s="79"/>
       <c r="P134" s="1"/>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" s="92" t="s">
+      <c r="A135" s="87" t="s">
         <v>25</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -11945,18 +11948,18 @@
         <v>1.209274E-27</v>
       </c>
       <c r="I135" s="1"/>
-      <c r="J135" s="82" t="s">
+      <c r="J135" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="K135" s="82"/>
-      <c r="L135" s="82"/>
-      <c r="M135" s="82"/>
-      <c r="N135" s="82"/>
-      <c r="O135" s="82"/>
+      <c r="K135" s="79"/>
+      <c r="L135" s="79"/>
+      <c r="M135" s="79"/>
+      <c r="N135" s="79"/>
+      <c r="O135" s="79"/>
       <c r="P135" s="1"/>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" s="79"/>
+      <c r="A136" s="85"/>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
@@ -11979,16 +11982,16 @@
         <v>5.7713939999999998E-2</v>
       </c>
       <c r="I136" s="1"/>
-      <c r="J136" s="82"/>
-      <c r="K136" s="82"/>
-      <c r="L136" s="82"/>
-      <c r="M136" s="82"/>
-      <c r="N136" s="82"/>
-      <c r="O136" s="82"/>
+      <c r="J136" s="79"/>
+      <c r="K136" s="79"/>
+      <c r="L136" s="79"/>
+      <c r="M136" s="79"/>
+      <c r="N136" s="79"/>
+      <c r="O136" s="79"/>
       <c r="P136" s="1"/>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" s="79"/>
+      <c r="A137" s="85"/>
       <c r="B137" s="1" t="s">
         <v>8</v>
       </c>
@@ -12011,32 +12014,32 @@
         <v>1.363103E-6</v>
       </c>
       <c r="I137" s="1"/>
-      <c r="J137" s="82"/>
-      <c r="K137" s="82"/>
-      <c r="L137" s="82"/>
-      <c r="M137" s="82"/>
-      <c r="N137" s="82"/>
-      <c r="O137" s="82"/>
+      <c r="J137" s="79"/>
+      <c r="K137" s="79"/>
+      <c r="L137" s="79"/>
+      <c r="M137" s="79"/>
+      <c r="N137" s="79"/>
+      <c r="O137" s="79"/>
       <c r="P137" s="1"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" s="80"/>
+      <c r="A138" s="99"/>
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="85"/>
-      <c r="D138" s="85"/>
-      <c r="E138" s="85"/>
-      <c r="F138" s="85"/>
-      <c r="G138" s="85"/>
-      <c r="H138" s="85"/>
+      <c r="C138" s="103"/>
+      <c r="D138" s="103"/>
+      <c r="E138" s="103"/>
+      <c r="F138" s="103"/>
+      <c r="G138" s="103"/>
+      <c r="H138" s="103"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="82"/>
-      <c r="K138" s="82"/>
-      <c r="L138" s="82"/>
-      <c r="M138" s="82"/>
-      <c r="N138" s="82"/>
-      <c r="O138" s="82"/>
+      <c r="J138" s="79"/>
+      <c r="K138" s="79"/>
+      <c r="L138" s="79"/>
+      <c r="M138" s="79"/>
+      <c r="N138" s="79"/>
+      <c r="O138" s="79"/>
       <c r="P138" s="1"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
@@ -12059,14 +12062,68 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="A111:A114"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A127:A130"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="J15:O18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C82:H82"/>
+    <mergeCell ref="C51:H54"/>
+    <mergeCell ref="J91:O94"/>
+    <mergeCell ref="J95:O98"/>
+    <mergeCell ref="J99:O102"/>
+    <mergeCell ref="C103:H106"/>
+    <mergeCell ref="C107:H110"/>
+    <mergeCell ref="C94:H94"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="J71:O74"/>
+    <mergeCell ref="C75:H78"/>
+    <mergeCell ref="J79:O82"/>
+    <mergeCell ref="C83:H86"/>
+    <mergeCell ref="J87:O90"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="J59:O62"/>
+    <mergeCell ref="C63:H66"/>
+    <mergeCell ref="C67:H70"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="J115:O118"/>
+    <mergeCell ref="J119:O122"/>
+    <mergeCell ref="J123:O126"/>
+    <mergeCell ref="J127:O130"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="J131:O134"/>
+    <mergeCell ref="J135:O138"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="J11:O14"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="J111:O114"/>
     <mergeCell ref="A51:A54"/>
@@ -12083,68 +12140,14 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="A99:A102"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="J11:O14"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="J115:O118"/>
-    <mergeCell ref="J119:O122"/>
-    <mergeCell ref="J123:O126"/>
-    <mergeCell ref="J127:O130"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="J131:O134"/>
-    <mergeCell ref="J135:O138"/>
-    <mergeCell ref="J59:O62"/>
-    <mergeCell ref="C63:H66"/>
-    <mergeCell ref="C67:H70"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="J71:O74"/>
-    <mergeCell ref="C75:H78"/>
-    <mergeCell ref="J79:O82"/>
-    <mergeCell ref="C83:H86"/>
-    <mergeCell ref="J87:O90"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="J91:O94"/>
-    <mergeCell ref="J95:O98"/>
-    <mergeCell ref="J99:O102"/>
-    <mergeCell ref="C103:H106"/>
-    <mergeCell ref="C107:H110"/>
-    <mergeCell ref="C94:H94"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="C51:H54"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="J15:O18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A127:A130"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12242,7 +12245,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="87" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -12264,17 +12267,17 @@
         <v>8.4954609999999993E-3</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="95"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="90"/>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
+      <c r="A4" s="85"/>
       <c r="B4" s="1" t="s">
         <v>107</v>
       </c>
@@ -12294,15 +12297,15 @@
         <v>6.4644240000000001E-6</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="98"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="93"/>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="1" t="s">
         <v>117</v>
       </c>
@@ -12322,15 +12325,15 @@
         <v>6.9540716799999999E-2</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="98"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="93"/>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="1" t="s">
         <v>109</v>
       </c>
@@ -12358,7 +12361,7 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="87" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -12398,7 +12401,7 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="1" t="s">
         <v>107</v>
       </c>
@@ -12436,7 +12439,7 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="79"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="1" t="s">
         <v>108</v>
       </c>
@@ -12474,7 +12477,7 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="1" t="s">
         <v>109</v>
       </c>
@@ -12512,7 +12515,7 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="87" t="s">
         <v>141</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -12534,17 +12537,17 @@
         <v>0.35833147122850001</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="93" t="s">
+      <c r="I11" s="88" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="95"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="90"/>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
+      <c r="A12" s="85"/>
       <c r="B12" s="1" t="s">
         <v>107</v>
       </c>
@@ -12564,15 +12567,15 @@
         <v>0.11792329999999999</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="98"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="93"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="79"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="1" t="s">
         <v>108</v>
       </c>
@@ -12592,15 +12595,15 @@
         <v>2.2889089999999999E-7</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="98"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="93"/>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="80"/>
+      <c r="A14" s="99"/>
       <c r="B14" s="1" t="s">
         <v>109</v>
       </c>
@@ -12628,7 +12631,7 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="87" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -12668,7 +12671,7 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
@@ -12706,7 +12709,7 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="1" t="s">
         <v>108</v>
       </c>
@@ -12744,7 +12747,7 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="80"/>
+      <c r="A18" s="99"/>
       <c r="B18" s="1" t="s">
         <v>109</v>
       </c>
@@ -12782,7 +12785,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="87" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -12822,7 +12825,7 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="1" t="s">
         <v>107</v>
       </c>
@@ -12860,7 +12863,7 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="1" t="s">
         <v>108</v>
       </c>
@@ -12898,7 +12901,7 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="80"/>
+      <c r="A22" s="99"/>
       <c r="B22" s="1" t="s">
         <v>109</v>
       </c>
@@ -12936,7 +12939,7 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="87" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -12976,7 +12979,7 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="79"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="1" t="s">
         <v>107</v>
       </c>
@@ -13014,7 +13017,7 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="79"/>
+      <c r="A25" s="85"/>
       <c r="B25" s="1" t="s">
         <v>108</v>
       </c>
@@ -13052,7 +13055,7 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="80"/>
+      <c r="A26" s="99"/>
       <c r="B26" s="1" t="s">
         <v>109</v>
       </c>
@@ -13090,7 +13093,7 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="92" t="s">
+      <c r="A27" s="87" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -13130,7 +13133,7 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="79"/>
+      <c r="A28" s="85"/>
       <c r="B28" s="1" t="s">
         <v>107</v>
       </c>
@@ -13168,7 +13171,7 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="79"/>
+      <c r="A29" s="85"/>
       <c r="B29" s="1" t="s">
         <v>108</v>
       </c>
@@ -13206,7 +13209,7 @@
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="80"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="1" t="s">
         <v>109</v>
       </c>
@@ -13244,7 +13247,7 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="92" t="s">
+      <c r="A31" s="87" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -13284,7 +13287,7 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="79"/>
+      <c r="A32" s="85"/>
       <c r="B32" s="1" t="s">
         <v>107</v>
       </c>
@@ -13322,7 +13325,7 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="79"/>
+      <c r="A33" s="85"/>
       <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
@@ -13360,7 +13363,7 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="80"/>
+      <c r="A34" s="99"/>
       <c r="B34" s="1" t="s">
         <v>109</v>
       </c>
@@ -13398,7 +13401,7 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="92" t="s">
+      <c r="A35" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -13440,7 +13443,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="79"/>
+      <c r="A36" s="85"/>
       <c r="B36" s="1" t="s">
         <v>107</v>
       </c>
@@ -13480,7 +13483,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="79"/>
+      <c r="A37" s="85"/>
       <c r="B37" s="1" t="s">
         <v>108</v>
       </c>
@@ -13520,7 +13523,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="80"/>
+      <c r="A38" s="99"/>
       <c r="B38" s="1" t="s">
         <v>109</v>
       </c>
@@ -13560,7 +13563,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="92" t="s">
+      <c r="A39" s="87" t="s">
         <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -13602,7 +13605,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="79"/>
+      <c r="A40" s="85"/>
       <c r="B40" s="1" t="s">
         <v>107</v>
       </c>
@@ -13642,7 +13645,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="79"/>
+      <c r="A41" s="85"/>
       <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
@@ -13682,7 +13685,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="80"/>
+      <c r="A42" s="99"/>
       <c r="B42" s="1" t="s">
         <v>109</v>
       </c>
@@ -13722,7 +13725,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="92" t="s">
+      <c r="A43" s="87" t="s">
         <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -13762,7 +13765,7 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="79"/>
+      <c r="A44" s="85"/>
       <c r="B44" s="1" t="s">
         <v>107</v>
       </c>
@@ -13800,7 +13803,7 @@
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="79"/>
+      <c r="A45" s="85"/>
       <c r="B45" s="1" t="s">
         <v>108</v>
       </c>
@@ -13838,7 +13841,7 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="80"/>
+      <c r="A46" s="99"/>
       <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
@@ -13876,19 +13879,19 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="92" t="s">
+      <c r="A47" s="87" t="s">
         <v>147</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="79"/>
       <c r="H47" s="1"/>
       <c r="I47" s="45">
         <v>-1.7478199999999999E-2</v>
@@ -13908,15 +13911,15 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="79"/>
+      <c r="A48" s="85"/>
       <c r="B48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="82"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="79"/>
       <c r="H48" s="1"/>
       <c r="I48" s="45">
         <v>-2.3552070000000001E-2</v>
@@ -13936,15 +13939,15 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="79"/>
+      <c r="A49" s="85"/>
       <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="82"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="82"/>
-      <c r="G49" s="82"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="79"/>
+      <c r="G49" s="79"/>
       <c r="H49" s="1"/>
       <c r="I49" s="45">
         <v>-2.6797439999999999E-2</v>
@@ -13964,15 +13967,15 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="80"/>
+      <c r="A50" s="99"/>
       <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="82"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="82"/>
+      <c r="C50" s="79"/>
+      <c r="D50" s="79"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="79"/>
+      <c r="G50" s="79"/>
       <c r="H50" s="1"/>
       <c r="I50" s="45">
         <v>-3.3645590000000003E-2</v>
@@ -13992,19 +13995,19 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="87" t="s">
         <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="79"/>
+      <c r="G51" s="79"/>
       <c r="H51" s="1"/>
       <c r="I51" s="45">
         <v>-8.3753321000000006E-3</v>
@@ -14024,15 +14027,15 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="79"/>
+      <c r="A52" s="85"/>
       <c r="B52" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="79"/>
+      <c r="G52" s="79"/>
       <c r="H52" s="1"/>
       <c r="I52" s="45">
         <v>6.2885479999999997E-3</v>
@@ -14052,15 +14055,15 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="79"/>
+      <c r="A53" s="85"/>
       <c r="B53" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="82"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="79"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="79"/>
+      <c r="G53" s="79"/>
       <c r="H53" s="1"/>
       <c r="I53" s="45">
         <v>-0.1092133</v>
@@ -14080,15 +14083,15 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="80"/>
+      <c r="A54" s="99"/>
       <c r="B54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="82"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="79"/>
       <c r="H54" s="1"/>
       <c r="I54" s="45">
         <v>-9.8989809999999998E-2</v>
@@ -14108,7 +14111,7 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="87" t="s">
         <v>144</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -14130,17 +14133,17 @@
         <v>2.350653E-6</v>
       </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="82" t="s">
+      <c r="I55" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
+      <c r="J55" s="79"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="79"/>
+      <c r="M55" s="79"/>
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="79"/>
+      <c r="A56" s="85"/>
       <c r="B56" s="1" t="s">
         <v>107</v>
       </c>
@@ -14160,15 +14163,15 @@
         <v>2.3278650000000001E-13</v>
       </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="82"/>
-      <c r="K56" s="82"/>
-      <c r="L56" s="82"/>
-      <c r="M56" s="82"/>
+      <c r="I56" s="79"/>
+      <c r="J56" s="79"/>
+      <c r="K56" s="79"/>
+      <c r="L56" s="79"/>
+      <c r="M56" s="79"/>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="79"/>
+      <c r="A57" s="85"/>
       <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
@@ -14188,15 +14191,15 @@
         <v>5.789537E-3</v>
       </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="82"/>
-      <c r="J57" s="82"/>
-      <c r="K57" s="82"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="82"/>
+      <c r="I57" s="79"/>
+      <c r="J57" s="79"/>
+      <c r="K57" s="79"/>
+      <c r="L57" s="79"/>
+      <c r="M57" s="79"/>
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
+      <c r="A58" s="99"/>
       <c r="B58" s="1" t="s">
         <v>109</v>
       </c>
@@ -14216,15 +14219,15 @@
         <v>3.5774789999999998E-4</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="82"/>
-      <c r="K58" s="82"/>
-      <c r="L58" s="82"/>
-      <c r="M58" s="82"/>
+      <c r="I58" s="79"/>
+      <c r="J58" s="79"/>
+      <c r="K58" s="79"/>
+      <c r="L58" s="79"/>
+      <c r="M58" s="79"/>
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="87" t="s">
         <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -14246,17 +14249,17 @@
         <v>1.0710269999999999E-5</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="82" t="s">
+      <c r="I59" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J59" s="82"/>
-      <c r="K59" s="82"/>
-      <c r="L59" s="82"/>
-      <c r="M59" s="82"/>
+      <c r="J59" s="79"/>
+      <c r="K59" s="79"/>
+      <c r="L59" s="79"/>
+      <c r="M59" s="79"/>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="79"/>
+      <c r="A60" s="85"/>
       <c r="B60" s="1" t="s">
         <v>107</v>
       </c>
@@ -14276,15 +14279,15 @@
         <v>1.3791302849E-6</v>
       </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
-      <c r="M60" s="82"/>
+      <c r="I60" s="79"/>
+      <c r="J60" s="79"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="79"/>
+      <c r="M60" s="79"/>
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
@@ -14304,15 +14307,15 @@
         <v>9.3598610230064994E-2</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="82"/>
-      <c r="J61" s="82"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="82"/>
-      <c r="M61" s="82"/>
+      <c r="I61" s="79"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="79"/>
+      <c r="L61" s="79"/>
+      <c r="M61" s="79"/>
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="80"/>
+      <c r="A62" s="99"/>
       <c r="B62" s="1" t="s">
         <v>109</v>
       </c>
@@ -14332,15 +14335,15 @@
         <v>3.7977520000000001E-2</v>
       </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="82"/>
-      <c r="J62" s="82"/>
-      <c r="K62" s="82"/>
-      <c r="L62" s="82"/>
-      <c r="M62" s="82"/>
+      <c r="I62" s="79"/>
+      <c r="J62" s="79"/>
+      <c r="K62" s="79"/>
+      <c r="L62" s="79"/>
+      <c r="M62" s="79"/>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="92" t="s">
+      <c r="A63" s="87" t="s">
         <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -14362,17 +14365,17 @@
         <v>5.242662E-14</v>
       </c>
       <c r="H63" s="1"/>
-      <c r="I63" s="82" t="s">
+      <c r="I63" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J63" s="82"/>
-      <c r="K63" s="82"/>
-      <c r="L63" s="82"/>
-      <c r="M63" s="82"/>
+      <c r="J63" s="79"/>
+      <c r="K63" s="79"/>
+      <c r="L63" s="79"/>
+      <c r="M63" s="79"/>
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="1" t="s">
         <v>107</v>
       </c>
@@ -14392,15 +14395,15 @@
         <v>3.4043159999999998E-14</v>
       </c>
       <c r="H64" s="1"/>
-      <c r="I64" s="82"/>
-      <c r="J64" s="82"/>
-      <c r="K64" s="82"/>
-      <c r="L64" s="82"/>
-      <c r="M64" s="82"/>
+      <c r="I64" s="79"/>
+      <c r="J64" s="79"/>
+      <c r="K64" s="79"/>
+      <c r="L64" s="79"/>
+      <c r="M64" s="79"/>
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="79"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
@@ -14420,15 +14423,15 @@
         <v>0.64513220100000002</v>
       </c>
       <c r="H65" s="1"/>
-      <c r="I65" s="82"/>
-      <c r="J65" s="82"/>
-      <c r="K65" s="82"/>
-      <c r="L65" s="82"/>
-      <c r="M65" s="82"/>
+      <c r="I65" s="79"/>
+      <c r="J65" s="79"/>
+      <c r="K65" s="79"/>
+      <c r="L65" s="79"/>
+      <c r="M65" s="79"/>
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
+      <c r="A66" s="99"/>
       <c r="B66" s="1" t="s">
         <v>109</v>
       </c>
@@ -14448,27 +14451,27 @@
         <v>0.36655130000000002</v>
       </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="82"/>
-      <c r="J66" s="82"/>
-      <c r="K66" s="82"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="82"/>
+      <c r="I66" s="79"/>
+      <c r="J66" s="79"/>
+      <c r="K66" s="79"/>
+      <c r="L66" s="79"/>
+      <c r="M66" s="79"/>
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="92" t="s">
+      <c r="A67" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="82"/>
-      <c r="G67" s="82"/>
+      <c r="D67" s="79"/>
+      <c r="E67" s="79"/>
+      <c r="F67" s="79"/>
+      <c r="G67" s="79"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1">
         <v>5.4104409999999999E-2</v>
@@ -14488,15 +14491,15 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="79"/>
+      <c r="A68" s="85"/>
       <c r="B68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C68" s="82"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="82"/>
-      <c r="G68" s="82"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="79"/>
+      <c r="E68" s="79"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="79"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1">
         <v>4.687269E-3</v>
@@ -14516,15 +14519,15 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="79"/>
+      <c r="A69" s="85"/>
       <c r="B69" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1">
         <v>-0.16190650000000001</v>
@@ -14544,15 +14547,15 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="80"/>
+      <c r="A70" s="99"/>
       <c r="B70" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C70" s="82"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="79"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1">
         <v>-0.22064059999999999</v>
@@ -14572,7 +14575,7 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="92" t="s">
+      <c r="A71" s="87" t="s">
         <v>145</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -14594,17 +14597,17 @@
         <v>2.524047E-13</v>
       </c>
       <c r="H71" s="1"/>
-      <c r="I71" s="82" t="s">
+      <c r="I71" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J71" s="82"/>
-      <c r="K71" s="82"/>
-      <c r="L71" s="82"/>
-      <c r="M71" s="82"/>
+      <c r="J71" s="79"/>
+      <c r="K71" s="79"/>
+      <c r="L71" s="79"/>
+      <c r="M71" s="79"/>
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="79"/>
+      <c r="A72" s="85"/>
       <c r="B72" s="1" t="s">
         <v>107</v>
       </c>
@@ -14624,15 +14627,15 @@
         <v>8.8521990000000004E-10</v>
       </c>
       <c r="H72" s="1"/>
-      <c r="I72" s="82"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="82"/>
-      <c r="L72" s="82"/>
-      <c r="M72" s="82"/>
+      <c r="I72" s="79"/>
+      <c r="J72" s="79"/>
+      <c r="K72" s="79"/>
+      <c r="L72" s="79"/>
+      <c r="M72" s="79"/>
       <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="79"/>
+      <c r="A73" s="85"/>
       <c r="B73" s="1" t="s">
         <v>108</v>
       </c>
@@ -14652,15 +14655,15 @@
         <v>9.6146709999999996E-2</v>
       </c>
       <c r="H73" s="1"/>
-      <c r="I73" s="82"/>
-      <c r="J73" s="82"/>
-      <c r="K73" s="82"/>
-      <c r="L73" s="82"/>
-      <c r="M73" s="82"/>
+      <c r="I73" s="79"/>
+      <c r="J73" s="79"/>
+      <c r="K73" s="79"/>
+      <c r="L73" s="79"/>
+      <c r="M73" s="79"/>
       <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
+      <c r="A74" s="99"/>
       <c r="B74" s="1" t="s">
         <v>109</v>
       </c>
@@ -14680,27 +14683,27 @@
         <v>6.7150146952E-3</v>
       </c>
       <c r="H74" s="1"/>
-      <c r="I74" s="82"/>
-      <c r="J74" s="82"/>
-      <c r="K74" s="82"/>
-      <c r="L74" s="82"/>
-      <c r="M74" s="82"/>
+      <c r="I74" s="79"/>
+      <c r="J74" s="79"/>
+      <c r="K74" s="79"/>
+      <c r="L74" s="79"/>
+      <c r="M74" s="79"/>
       <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="87" t="s">
         <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="82" t="s">
+      <c r="C75" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="82"/>
-      <c r="E75" s="82"/>
-      <c r="F75" s="82"/>
-      <c r="G75" s="82"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
+      <c r="F75" s="79"/>
+      <c r="G75" s="79"/>
       <c r="H75" s="1"/>
       <c r="I75" s="45">
         <v>3.8010990000000001E-3</v>
@@ -14720,15 +14723,15 @@
       <c r="N75" s="1"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="79"/>
+      <c r="A76" s="85"/>
       <c r="B76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="82"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="82"/>
-      <c r="F76" s="82"/>
-      <c r="G76" s="82"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="79"/>
+      <c r="E76" s="79"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="79"/>
       <c r="H76" s="1"/>
       <c r="I76" s="45">
         <v>2.6998579999999999E-3</v>
@@ -14748,15 +14751,15 @@
       <c r="N76" s="1"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="79"/>
+      <c r="A77" s="85"/>
       <c r="B77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="82"/>
-      <c r="D77" s="82"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="79"/>
+      <c r="E77" s="79"/>
+      <c r="F77" s="79"/>
+      <c r="G77" s="79"/>
       <c r="H77" s="1"/>
       <c r="I77" s="45">
         <v>-1.146374E-2</v>
@@ -14776,15 +14779,15 @@
       <c r="N77" s="1"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
+      <c r="A78" s="99"/>
       <c r="B78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C78" s="82"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="82"/>
-      <c r="F78" s="82"/>
-      <c r="G78" s="82"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="79"/>
+      <c r="E78" s="79"/>
+      <c r="F78" s="79"/>
+      <c r="G78" s="79"/>
       <c r="H78" s="1"/>
       <c r="I78" s="45">
         <v>-1.288595E-2</v>
@@ -14804,19 +14807,19 @@
       <c r="N78" s="1"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="92" t="s">
+      <c r="A79" s="87" t="s">
         <v>29</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C79" s="82" t="s">
+      <c r="C79" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D79" s="82"/>
-      <c r="E79" s="82"/>
-      <c r="F79" s="82"/>
-      <c r="G79" s="82"/>
+      <c r="D79" s="79"/>
+      <c r="E79" s="79"/>
+      <c r="F79" s="79"/>
+      <c r="G79" s="79"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1">
         <v>-1.7348269999999999E-2</v>
@@ -14836,15 +14839,15 @@
       <c r="N79" s="1"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="79"/>
+      <c r="A80" s="85"/>
       <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C80" s="82"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
-      <c r="F80" s="82"/>
-      <c r="G80" s="82"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="79"/>
+      <c r="F80" s="79"/>
+      <c r="G80" s="79"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1">
         <v>1.2575930000000001E-2</v>
@@ -14864,15 +14867,15 @@
       <c r="N80" s="1"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="79"/>
+      <c r="A81" s="85"/>
       <c r="B81" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="82"/>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
-      <c r="F81" s="82"/>
-      <c r="G81" s="82"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="79"/>
+      <c r="G81" s="79"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1">
         <v>3.5116069999999999E-2</v>
@@ -14892,15 +14895,15 @@
       <c r="N81" s="1"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="80"/>
+      <c r="A82" s="99"/>
       <c r="B82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="79"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1">
         <v>6.7801109999999998E-2</v>
@@ -14920,7 +14923,7 @@
       <c r="N82" s="1"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="92" t="s">
+      <c r="A83" s="87" t="s">
         <v>24</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -14942,17 +14945,17 @@
         <v>6.5310590000000004E-6</v>
       </c>
       <c r="H83" s="1"/>
-      <c r="I83" s="82" t="s">
+      <c r="I83" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J83" s="82"/>
-      <c r="K83" s="82"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="82"/>
+      <c r="J83" s="79"/>
+      <c r="K83" s="79"/>
+      <c r="L83" s="79"/>
+      <c r="M83" s="79"/>
       <c r="N83" s="1"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="79"/>
+      <c r="A84" s="85"/>
       <c r="B84" s="1" t="s">
         <v>107</v>
       </c>
@@ -14972,15 +14975,15 @@
         <v>0.31967210000000001</v>
       </c>
       <c r="H84" s="1"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
+      <c r="I84" s="79"/>
+      <c r="J84" s="79"/>
+      <c r="K84" s="79"/>
+      <c r="L84" s="79"/>
+      <c r="M84" s="79"/>
       <c r="N84" s="1"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="79"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="1" t="s">
         <v>108</v>
       </c>
@@ -15000,15 +15003,15 @@
         <v>4.9434029999999999E-3</v>
       </c>
       <c r="H85" s="1"/>
-      <c r="I85" s="82"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
+      <c r="I85" s="79"/>
+      <c r="J85" s="79"/>
+      <c r="K85" s="79"/>
+      <c r="L85" s="79"/>
+      <c r="M85" s="79"/>
       <c r="N85" s="1"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="80"/>
+      <c r="A86" s="99"/>
       <c r="B86" s="1" t="s">
         <v>109</v>
       </c>
@@ -15028,15 +15031,15 @@
         <v>0.72019759999999999</v>
       </c>
       <c r="H86" s="1"/>
-      <c r="I86" s="82"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
+      <c r="I86" s="79"/>
+      <c r="J86" s="79"/>
+      <c r="K86" s="79"/>
+      <c r="L86" s="79"/>
+      <c r="M86" s="79"/>
       <c r="N86" s="1"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="87" t="s">
         <v>20</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -15058,17 +15061,17 @@
         <v>2.2222259999999999E-4</v>
       </c>
       <c r="H87" s="1"/>
-      <c r="I87" s="82" t="s">
+      <c r="I87" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
+      <c r="J87" s="79"/>
+      <c r="K87" s="79"/>
+      <c r="L87" s="79"/>
+      <c r="M87" s="79"/>
       <c r="N87" s="1"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="79"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="1" t="s">
         <v>107</v>
       </c>
@@ -15088,15 +15091,15 @@
         <v>1.142512E-8</v>
       </c>
       <c r="H88" s="1"/>
-      <c r="I88" s="82"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
+      <c r="I88" s="79"/>
+      <c r="J88" s="79"/>
+      <c r="K88" s="79"/>
+      <c r="L88" s="79"/>
+      <c r="M88" s="79"/>
       <c r="N88" s="1"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="79"/>
+      <c r="A89" s="85"/>
       <c r="B89" s="1" t="s">
         <v>108</v>
       </c>
@@ -15116,15 +15119,15 @@
         <v>0.17826230000000001</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="82"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
+      <c r="I89" s="79"/>
+      <c r="J89" s="79"/>
+      <c r="K89" s="79"/>
+      <c r="L89" s="79"/>
+      <c r="M89" s="79"/>
       <c r="N89" s="1"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="80"/>
+      <c r="A90" s="99"/>
       <c r="B90" s="1" t="s">
         <v>109</v>
       </c>
@@ -15144,15 +15147,15 @@
         <v>2.8002340000000001E-2</v>
       </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
+      <c r="I90" s="79"/>
+      <c r="J90" s="79"/>
+      <c r="K90" s="79"/>
+      <c r="L90" s="79"/>
+      <c r="M90" s="79"/>
       <c r="N90" s="1"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="92" t="s">
+      <c r="A91" s="87" t="s">
         <v>21</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -15174,17 +15177,17 @@
         <v>3.9052140000000001E-5</v>
       </c>
       <c r="H91" s="1"/>
-      <c r="I91" s="82" t="s">
+      <c r="I91" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J91" s="82"/>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
+      <c r="J91" s="79"/>
+      <c r="K91" s="79"/>
+      <c r="L91" s="79"/>
+      <c r="M91" s="79"/>
       <c r="N91" s="1"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
+      <c r="A92" s="85"/>
       <c r="B92" s="1" t="s">
         <v>107</v>
       </c>
@@ -15204,15 +15207,15 @@
         <v>1.9085240000000001E-25</v>
       </c>
       <c r="H92" s="1"/>
-      <c r="I92" s="82"/>
-      <c r="J92" s="82"/>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
+      <c r="I92" s="79"/>
+      <c r="J92" s="79"/>
+      <c r="K92" s="79"/>
+      <c r="L92" s="79"/>
+      <c r="M92" s="79"/>
       <c r="N92" s="1"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="79"/>
+      <c r="A93" s="85"/>
       <c r="B93" s="1" t="s">
         <v>108</v>
       </c>
@@ -15232,15 +15235,15 @@
         <v>1.377838E-2</v>
       </c>
       <c r="H93" s="1"/>
-      <c r="I93" s="82"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
+      <c r="I93" s="79"/>
+      <c r="J93" s="79"/>
+      <c r="K93" s="79"/>
+      <c r="L93" s="79"/>
+      <c r="M93" s="79"/>
       <c r="N93" s="1"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
+      <c r="A94" s="99"/>
       <c r="B94" s="1" t="s">
         <v>109</v>
       </c>
@@ -15260,15 +15263,15 @@
         <v>0.46767300000000001</v>
       </c>
       <c r="H94" s="1"/>
-      <c r="I94" s="82"/>
-      <c r="J94" s="82"/>
-      <c r="K94" s="82"/>
-      <c r="L94" s="82"/>
-      <c r="M94" s="82"/>
+      <c r="I94" s="79"/>
+      <c r="J94" s="79"/>
+      <c r="K94" s="79"/>
+      <c r="L94" s="79"/>
+      <c r="M94" s="79"/>
       <c r="N94" s="1"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="92" t="s">
+      <c r="A95" s="87" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -15290,17 +15293,17 @@
         <v>2.9384279999999999E-9</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="I95" s="82" t="s">
+      <c r="I95" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J95" s="82"/>
-      <c r="K95" s="82"/>
-      <c r="L95" s="82"/>
-      <c r="M95" s="82"/>
+      <c r="J95" s="79"/>
+      <c r="K95" s="79"/>
+      <c r="L95" s="79"/>
+      <c r="M95" s="79"/>
       <c r="N95" s="1"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="79"/>
+      <c r="A96" s="85"/>
       <c r="B96" s="1" t="s">
         <v>107</v>
       </c>
@@ -15320,15 +15323,15 @@
         <v>9.0369680000000005E-13</v>
       </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="82"/>
-      <c r="J96" s="82"/>
-      <c r="K96" s="82"/>
-      <c r="L96" s="82"/>
-      <c r="M96" s="82"/>
+      <c r="I96" s="79"/>
+      <c r="J96" s="79"/>
+      <c r="K96" s="79"/>
+      <c r="L96" s="79"/>
+      <c r="M96" s="79"/>
       <c r="N96" s="1"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="79"/>
+      <c r="A97" s="85"/>
       <c r="B97" s="1" t="s">
         <v>108</v>
       </c>
@@ -15348,15 +15351,15 @@
         <v>0.45520664523399601</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="82"/>
-      <c r="J97" s="82"/>
-      <c r="K97" s="82"/>
-      <c r="L97" s="82"/>
-      <c r="M97" s="82"/>
+      <c r="I97" s="79"/>
+      <c r="J97" s="79"/>
+      <c r="K97" s="79"/>
+      <c r="L97" s="79"/>
+      <c r="M97" s="79"/>
       <c r="N97" s="1"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="80"/>
+      <c r="A98" s="99"/>
       <c r="B98" s="1" t="s">
         <v>109</v>
       </c>
@@ -15376,15 +15379,15 @@
         <v>5.14251187538E-2</v>
       </c>
       <c r="H98" s="1"/>
-      <c r="I98" s="82"/>
-      <c r="J98" s="82"/>
-      <c r="K98" s="82"/>
-      <c r="L98" s="82"/>
-      <c r="M98" s="82"/>
+      <c r="I98" s="79"/>
+      <c r="J98" s="79"/>
+      <c r="K98" s="79"/>
+      <c r="L98" s="79"/>
+      <c r="M98" s="79"/>
       <c r="N98" s="1"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="92" t="s">
+      <c r="A99" s="87" t="s">
         <v>35</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -15406,17 +15409,17 @@
         <v>0.30992960000000003</v>
       </c>
       <c r="H99" s="1"/>
-      <c r="I99" s="82" t="s">
+      <c r="I99" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J99" s="82"/>
-      <c r="K99" s="82"/>
-      <c r="L99" s="82"/>
-      <c r="M99" s="82"/>
+      <c r="J99" s="79"/>
+      <c r="K99" s="79"/>
+      <c r="L99" s="79"/>
+      <c r="M99" s="79"/>
       <c r="N99" s="1"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="79"/>
+      <c r="A100" s="85"/>
       <c r="B100" s="1" t="s">
         <v>107</v>
       </c>
@@ -15436,15 +15439,15 @@
         <v>5.4385229999999998E-11</v>
       </c>
       <c r="H100" s="1"/>
-      <c r="I100" s="82"/>
-      <c r="J100" s="82"/>
-      <c r="K100" s="82"/>
-      <c r="L100" s="82"/>
-      <c r="M100" s="82"/>
+      <c r="I100" s="79"/>
+      <c r="J100" s="79"/>
+      <c r="K100" s="79"/>
+      <c r="L100" s="79"/>
+      <c r="M100" s="79"/>
       <c r="N100" s="1"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="79"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="1" t="s">
         <v>108</v>
       </c>
@@ -15464,15 +15467,15 @@
         <v>1.343811E-5</v>
       </c>
       <c r="H101" s="1"/>
-      <c r="I101" s="82"/>
-      <c r="J101" s="82"/>
-      <c r="K101" s="82"/>
-      <c r="L101" s="82"/>
-      <c r="M101" s="82"/>
+      <c r="I101" s="79"/>
+      <c r="J101" s="79"/>
+      <c r="K101" s="79"/>
+      <c r="L101" s="79"/>
+      <c r="M101" s="79"/>
       <c r="N101" s="1"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
+      <c r="A102" s="99"/>
       <c r="B102" s="1" t="s">
         <v>109</v>
       </c>
@@ -15492,15 +15495,15 @@
         <v>0.56057069999999998</v>
       </c>
       <c r="H102" s="1"/>
-      <c r="I102" s="82"/>
-      <c r="J102" s="82"/>
-      <c r="K102" s="82"/>
-      <c r="L102" s="82"/>
-      <c r="M102" s="82"/>
+      <c r="I102" s="79"/>
+      <c r="J102" s="79"/>
+      <c r="K102" s="79"/>
+      <c r="L102" s="79"/>
+      <c r="M102" s="79"/>
       <c r="N102" s="1"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="92" t="s">
+      <c r="A103" s="87" t="s">
         <v>149</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -15522,17 +15525,17 @@
         <v>0.96106304949900001</v>
       </c>
       <c r="H103" s="1"/>
-      <c r="I103" s="82" t="s">
+      <c r="I103" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J103" s="82"/>
-      <c r="K103" s="82"/>
-      <c r="L103" s="82"/>
-      <c r="M103" s="82"/>
+      <c r="J103" s="79"/>
+      <c r="K103" s="79"/>
+      <c r="L103" s="79"/>
+      <c r="M103" s="79"/>
       <c r="N103" s="1"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="79"/>
+      <c r="A104" s="85"/>
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
@@ -15552,15 +15555,15 @@
         <v>0.2307786</v>
       </c>
       <c r="H104" s="1"/>
-      <c r="I104" s="82"/>
-      <c r="J104" s="82"/>
-      <c r="K104" s="82"/>
-      <c r="L104" s="82"/>
-      <c r="M104" s="82"/>
+      <c r="I104" s="79"/>
+      <c r="J104" s="79"/>
+      <c r="K104" s="79"/>
+      <c r="L104" s="79"/>
+      <c r="M104" s="79"/>
       <c r="N104" s="1"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="79"/>
+      <c r="A105" s="85"/>
       <c r="B105" s="1" t="s">
         <v>108</v>
       </c>
@@ -15580,15 +15583,15 @@
         <v>3.2851500000000001E-3</v>
       </c>
       <c r="H105" s="1"/>
-      <c r="I105" s="82"/>
-      <c r="J105" s="82"/>
-      <c r="K105" s="82"/>
-      <c r="L105" s="82"/>
-      <c r="M105" s="82"/>
+      <c r="I105" s="79"/>
+      <c r="J105" s="79"/>
+      <c r="K105" s="79"/>
+      <c r="L105" s="79"/>
+      <c r="M105" s="79"/>
       <c r="N105" s="1"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="80"/>
+      <c r="A106" s="99"/>
       <c r="B106" s="1" t="s">
         <v>109</v>
       </c>
@@ -15608,15 +15611,15 @@
         <v>9.3442800000000006E-2</v>
       </c>
       <c r="H106" s="1"/>
-      <c r="I106" s="82"/>
-      <c r="J106" s="82"/>
-      <c r="K106" s="82"/>
-      <c r="L106" s="82"/>
-      <c r="M106" s="82"/>
+      <c r="I106" s="79"/>
+      <c r="J106" s="79"/>
+      <c r="K106" s="79"/>
+      <c r="L106" s="79"/>
+      <c r="M106" s="79"/>
       <c r="N106" s="1"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="92" t="s">
+      <c r="A107" s="87" t="s">
         <v>25</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -15638,17 +15641,17 @@
         <v>2.1465810000000001E-7</v>
       </c>
       <c r="H107" s="1"/>
-      <c r="I107" s="82" t="s">
+      <c r="I107" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="J107" s="82"/>
-      <c r="K107" s="82"/>
-      <c r="L107" s="82"/>
-      <c r="M107" s="82"/>
+      <c r="J107" s="79"/>
+      <c r="K107" s="79"/>
+      <c r="L107" s="79"/>
+      <c r="M107" s="79"/>
       <c r="N107" s="1"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="79"/>
+      <c r="A108" s="85"/>
       <c r="B108" s="1" t="s">
         <v>107</v>
       </c>
@@ -15668,15 +15671,15 @@
         <v>3.0964249999999998E-23</v>
       </c>
       <c r="H108" s="1"/>
-      <c r="I108" s="82"/>
-      <c r="J108" s="82"/>
-      <c r="K108" s="82"/>
-      <c r="L108" s="82"/>
-      <c r="M108" s="82"/>
+      <c r="I108" s="79"/>
+      <c r="J108" s="79"/>
+      <c r="K108" s="79"/>
+      <c r="L108" s="79"/>
+      <c r="M108" s="79"/>
       <c r="N108" s="1"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="79"/>
+      <c r="A109" s="85"/>
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
@@ -15696,15 +15699,15 @@
         <v>0.17187649999999999</v>
       </c>
       <c r="H109" s="1"/>
-      <c r="I109" s="82"/>
-      <c r="J109" s="82"/>
-      <c r="K109" s="82"/>
-      <c r="L109" s="82"/>
-      <c r="M109" s="82"/>
+      <c r="I109" s="79"/>
+      <c r="J109" s="79"/>
+      <c r="K109" s="79"/>
+      <c r="L109" s="79"/>
+      <c r="M109" s="79"/>
       <c r="N109" s="1"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="80"/>
+      <c r="A110" s="99"/>
       <c r="B110" s="1" t="s">
         <v>109</v>
       </c>
@@ -15724,11 +15727,11 @@
         <v>5.7776140000000001E-4</v>
       </c>
       <c r="H110" s="1"/>
-      <c r="I110" s="82"/>
-      <c r="J110" s="82"/>
-      <c r="K110" s="82"/>
-      <c r="L110" s="82"/>
-      <c r="M110" s="82"/>
+      <c r="I110" s="79"/>
+      <c r="J110" s="79"/>
+      <c r="K110" s="79"/>
+      <c r="L110" s="79"/>
+      <c r="M110" s="79"/>
       <c r="N110" s="1"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -15751,40 +15754,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="I103:M106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="I107:M110"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="I91:M94"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="I95:M98"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="I99:M102"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="C79:G82"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="I83:M86"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I87:M90"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="C67:G70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="I71:M74"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C75:G78"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="I55:M58"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="I59:M62"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="I63:M66"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="C47:G50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="C51:G54"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="I1:N1"/>
@@ -15798,6 +15767,40 @@
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="C47:G50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C51:G54"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="I55:M58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="I59:M62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="I63:M66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="C67:G70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="I71:M74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C75:G78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="C79:G82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="I83:M86"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="I87:M90"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="I103:M106"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="I107:M110"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="I91:M94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="I95:M98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="I99:M102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
